--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -4549,7 +4549,7 @@
         <v>1.0851</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.2512</v>
+        <v>-8.365399999999999</v>
       </c>
     </row>
     <row r="3">
@@ -4622,7 +4622,7 @@
         <v>1.1575</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2107</v>
+        <v>-8.8292</v>
       </c>
     </row>
     <row r="4">
@@ -4707,7 +4707,7 @@
         <v>1.3439</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.2099</v>
+        <v>-7.7444</v>
       </c>
       <c r="AB4" t="n">
         <v>1.4047</v>
@@ -4804,7 +4804,7 @@
         <v>1.7612</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.0692</v>
+        <v>-6.4706</v>
       </c>
       <c r="AB5" t="n">
         <v>1.4047</v>
@@ -4901,7 +4901,7 @@
         <v>1.9537</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0917</v>
+        <v>-5.7256</v>
       </c>
       <c r="AB6" t="n">
         <v>1.4047</v>
@@ -4998,7 +4998,7 @@
         <v>1.505</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0086</v>
+        <v>-5.4672</v>
       </c>
       <c r="AB7" t="n">
         <v>1.3922</v>
@@ -5095,7 +5095,7 @@
         <v>2.1369</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1148</v>
+        <v>-5</v>
       </c>
       <c r="AB8" t="n">
         <v>1.3922</v>
@@ -5192,7 +5192,7 @@
         <v>2.1182</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1631</v>
+        <v>-4.6138</v>
       </c>
       <c r="AB9" t="n">
         <v>1.3922</v>
@@ -5289,7 +5289,7 @@
         <v>2.3802</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2267</v>
+        <v>-3.0488</v>
       </c>
       <c r="AB10" t="n">
         <v>1.3493</v>
@@ -5386,7 +5386,7 @@
         <v>2.4564</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2806</v>
+        <v>-0.8316</v>
       </c>
       <c r="AB11" t="n">
         <v>1.3493</v>
@@ -5483,7 +5483,7 @@
         <v>2.6686</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.3596</v>
+        <v>-1.0417</v>
       </c>
       <c r="AB12" t="n">
         <v>1.3493</v>
@@ -5580,7 +5580,7 @@
         <v>2.7107</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.4121</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>1.345</v>
@@ -5677,7 +5677,7 @@
         <v>2.8519</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.381</v>
+        <v>-0.1049</v>
       </c>
       <c r="AB14" t="n">
         <v>1.345</v>
@@ -5774,7 +5774,7 @@
         <v>2.9007</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.4851</v>
+        <v>-0.1053</v>
       </c>
       <c r="AB15" t="n">
         <v>1.345</v>
@@ -5871,7 +5871,7 @@
         <v>3.0448</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.509</v>
+        <v>-0.2099</v>
       </c>
       <c r="AB16" t="n">
         <v>1.3676</v>
@@ -5968,7 +5968,7 @@
         <v>2.8976</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.5827</v>
+        <v>-0.1048</v>
       </c>
       <c r="AB17" t="n">
         <v>1.3676</v>
@@ -6065,7 +6065,7 @@
         <v>3.1181</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.6499</v>
+        <v>0.1047</v>
       </c>
       <c r="AB18" t="n">
         <v>1.3676</v>
@@ -6162,7 +6162,7 @@
         <v>3.8205</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.7322</v>
+        <v>0.5258</v>
       </c>
       <c r="AB19" t="n">
         <v>1.3038</v>
@@ -6259,7 +6259,7 @@
         <v>3.9486</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.774</v>
+        <v>0.3158</v>
       </c>
       <c r="AB20" t="n">
         <v>1.3038</v>
@@ -6356,7 +6356,7 @@
         <v>3.6851</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.8157</v>
+        <v>0.9464</v>
       </c>
       <c r="AB21" t="n">
         <v>1.3038</v>
@@ -6453,7 +6453,7 @@
         <v>3.9738</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.9184</v>
+        <v>0.6289</v>
       </c>
       <c r="AB22" t="n">
         <v>1.3185</v>
@@ -6550,7 +6550,7 @@
         <v>3.8656</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.9611</v>
+        <v>0.4193</v>
       </c>
       <c r="AB23" t="n">
         <v>1.3185</v>
@@ -6647,7 +6647,7 @@
         <v>4.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.0035</v>
+        <v>0.3158</v>
       </c>
       <c r="AB24" t="n">
         <v>1.3185</v>
@@ -6744,7 +6744,7 @@
         <v>4.6623</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.1225</v>
+        <v>0.3141</v>
       </c>
       <c r="AB25" t="n">
         <v>1.2761</v>
@@ -6841,7 +6841,7 @@
         <v>4.7167</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.2293</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>1.2761</v>
@@ -6938,7 +6938,7 @@
         <v>4.3724</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.1886</v>
+        <v>-0.2107</v>
       </c>
       <c r="AB27" t="n">
         <v>1.2761</v>
@@ -7035,7 +7035,7 @@
         <v>4.7572</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.2565</v>
+        <v>-0.1052</v>
       </c>
       <c r="AB28" t="n">
         <v>1.2935</v>
@@ -7132,7 +7132,7 @@
         <v>4.8137</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.3129</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>1.2935</v>
@@ -7229,7 +7229,7 @@
         <v>5.4772</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.4046</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>1.2935</v>
@@ -7326,7 +7326,7 @@
         <v>5.0325</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.5328</v>
+        <v>-0.2092</v>
       </c>
       <c r="AB31" t="n">
         <v>1.2782</v>
@@ -7423,7 +7423,7 @@
         <v>5.5881</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.5456</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>1.2782</v>
@@ -7520,7 +7520,7 @@
         <v>5.7055</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6602</v>
+        <v>-0.2083</v>
       </c>
       <c r="AB33" t="n">
         <v>1.2782</v>
@@ -7617,7 +7617,7 @@
         <v>6.0632</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.6286</v>
+        <v>-0.2083</v>
       </c>
       <c r="AB34" t="n">
         <v>1.2546</v>
@@ -7714,7 +7714,7 @@
         <v>5.972</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.6925</v>
+        <v>0.2088</v>
       </c>
       <c r="AB35" t="n">
         <v>1.2546</v>
@@ -7811,7 +7811,7 @@
         <v>6.1512</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.7496</v>
+        <v>0.6296</v>
       </c>
       <c r="AB36" t="n">
         <v>1.2546</v>
@@ -7908,7 +7908,7 @@
         <v>6.5018</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8686</v>
+        <v>2.714</v>
       </c>
       <c r="AB37" t="n">
         <v>1.2412</v>
@@ -8005,7 +8005,7 @@
         <v>6.4813</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.8882</v>
+        <v>0.7353</v>
       </c>
       <c r="AB38" t="n">
         <v>1.2412</v>
@@ -8102,7 +8102,7 @@
         <v>6.6136</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.0074</v>
+        <v>1.056</v>
       </c>
       <c r="AB39" t="n">
         <v>1.2412</v>
@@ -8199,7 +8199,7 @@
         <v>6.7147</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.0689</v>
+        <v>1.1579</v>
       </c>
       <c r="AB40" t="n">
         <v>1.1885</v>
@@ -8296,7 +8296,7 @@
         <v>6.7982</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.0721</v>
+        <v>0.7345</v>
       </c>
       <c r="AB41" t="n">
         <v>1.1885</v>
@@ -8393,7 +8393,7 @@
         <v>7.0319</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.1893</v>
+        <v>1.2552</v>
       </c>
       <c r="AB42" t="n">
         <v>1.1885</v>
@@ -8490,7 +8490,7 @@
         <v>7.2732</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.1574</v>
+        <v>2.8302</v>
       </c>
       <c r="AB43" t="n">
         <v>1.1972</v>
@@ -8587,7 +8587,7 @@
         <v>7.0198</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.3343</v>
+        <v>3.148</v>
       </c>
       <c r="AB44" t="n">
         <v>1.1972</v>
@@ -8684,7 +8684,7 @@
         <v>7.7711</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2897</v>
+        <v>2.714</v>
       </c>
       <c r="AB45" t="n">
         <v>1.1972</v>
@@ -8781,7 +8781,7 @@
         <v>7.7861</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.3989</v>
+        <v>2.9228</v>
       </c>
       <c r="AB46" t="n">
         <v>0.9696</v>
@@ -8878,7 +8878,7 @@
         <v>7.6124</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.0056</v>
+        <v>3.4375</v>
       </c>
       <c r="AB47" t="n">
         <v>0.9696</v>
@@ -8975,7 +8975,7 @@
         <v>7.5954</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.5359</v>
+        <v>3.6496</v>
       </c>
       <c r="AB48" t="n">
         <v>0.9696</v>
@@ -9072,7 +9072,7 @@
         <v>8.0928</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.1189</v>
+        <v>0.9146</v>
       </c>
       <c r="AB49" t="n">
         <v>0.8003</v>
@@ -9169,7 +9169,7 @@
         <v>7.7002</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.6654</v>
+        <v>3.5454</v>
       </c>
       <c r="AB50" t="n">
         <v>0.8003</v>
@@ -9266,7 +9266,7 @@
         <v>7.2539</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.2776</v>
+        <v>3.8662</v>
       </c>
       <c r="AB51" t="n">
         <v>0.8003</v>
@@ -9363,7 +9363,7 @@
         <v>6.7264</v>
       </c>
       <c r="AA52" t="n">
-        <v>-0.2147</v>
+        <v>3.538</v>
       </c>
       <c r="AB52" t="n">
         <v>0.584</v>
@@ -9460,7 +9460,7 @@
         <v>5.6646</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.6347</v>
+        <v>3.0208</v>
       </c>
       <c r="AB53" t="n">
         <v>0.584</v>
@@ -9557,7 +9557,7 @@
         <v>5.4308</v>
       </c>
       <c r="AA54" t="n">
-        <v>-1.1229</v>
+        <v>1.343</v>
       </c>
       <c r="AB54" t="n">
         <v>0.584</v>
@@ -9654,7 +9654,7 @@
         <v>5.0829</v>
       </c>
       <c r="AA55" t="n">
-        <v>-1.5651</v>
+        <v>-0.2039</v>
       </c>
       <c r="AB55" t="n">
         <v>0.4235</v>
@@ -9751,7 +9751,7 @@
         <v>4.0792</v>
       </c>
       <c r="AA56" t="n">
-        <v>-1.9043</v>
+        <v>-0.7121</v>
       </c>
       <c r="AB56" t="n">
         <v>0.4235</v>
@@ -9848,7 +9848,7 @@
         <v>3.4376</v>
       </c>
       <c r="AA57" t="n">
-        <v>-2.3738</v>
+        <v>-1.1179</v>
       </c>
       <c r="AB57" t="n">
         <v>0.4235</v>
@@ -9945,7 +9945,7 @@
         <v>3.3332</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.3063</v>
+        <v>-1.3185</v>
       </c>
       <c r="AB58" t="n">
         <v>0.1783</v>
@@ -10042,7 +10042,7 @@
         <v>2.3908</v>
       </c>
       <c r="AA59" t="n">
-        <v>-2.2236</v>
+        <v>-2.6183</v>
       </c>
       <c r="AB59" t="n">
         <v>0.1783</v>
@@ -10139,7 +10139,7 @@
         <v>1.6949</v>
       </c>
       <c r="AA60" t="n">
-        <v>-2.2535</v>
+        <v>-3.1187</v>
       </c>
       <c r="AB60" t="n">
         <v>0.1783</v>
@@ -10236,7 +10236,7 @@
         <v>1.0316</v>
       </c>
       <c r="AA61" t="n">
-        <v>-2.1576</v>
+        <v>-3.424</v>
       </c>
       <c r="AB61" t="n">
         <v>0.2701</v>
@@ -10333,7 +10333,7 @@
         <v>0.8781</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.072</v>
+        <v>-3.5247</v>
       </c>
       <c r="AB62" t="n">
         <v>0.2701</v>
@@ -10430,7 +10430,7 @@
         <v>0.5513</v>
       </c>
       <c r="AA63" t="n">
-        <v>-2.0036</v>
+        <v>-3.7223</v>
       </c>
       <c r="AB63" t="n">
         <v>0.2701</v>
@@ -10527,7 +10527,7 @@
         <v>-0.6452</v>
       </c>
       <c r="AA64" t="n">
-        <v>-1.8633</v>
+        <v>-3.9196</v>
       </c>
       <c r="AB64" t="n">
         <v>0.2948</v>
@@ -10624,7 +10624,7 @@
         <v>-1.0417</v>
       </c>
       <c r="AA65" t="n">
-        <v>-1.8052</v>
+        <v>-3.4378</v>
       </c>
       <c r="AB65" t="n">
         <v>0.2948</v>
@@ -10721,7 +10721,7 @@
         <v>-1.262</v>
       </c>
       <c r="AA66" t="n">
-        <v>-1.7754</v>
+        <v>-2.7523</v>
       </c>
       <c r="AB66" t="n">
         <v>0.2948</v>
@@ -10818,7 +10818,7 @@
         <v>-2.0555</v>
       </c>
       <c r="AA67" t="n">
-        <v>-1.6892</v>
+        <v>-2.6558</v>
       </c>
       <c r="AB67" t="n">
         <v>0.3485</v>
@@ -10915,7 +10915,7 @@
         <v>-1.8571</v>
       </c>
       <c r="AA68" t="n">
-        <v>-1.6124</v>
+        <v>-2.6639</v>
       </c>
       <c r="AB68" t="n">
         <v>0.3485</v>
@@ -11012,7 +11012,7 @@
         <v>-1.7145</v>
       </c>
       <c r="AA69" t="n">
-        <v>-1.5456</v>
+        <v>-2.6721</v>
       </c>
       <c r="AB69" t="n">
         <v>0.3485</v>
@@ -11109,7 +11109,7 @@
         <v>-1.4931</v>
       </c>
       <c r="AA70" t="n">
-        <v>-1.5419</v>
+        <v>-2.6721</v>
       </c>
       <c r="AB70" t="n">
         <v>0.3674</v>
@@ -11206,7 +11206,7 @@
         <v>-1.2044</v>
       </c>
       <c r="AA71" t="n">
-        <v>-1.4072</v>
+        <v>-1.758</v>
       </c>
       <c r="AB71" t="n">
         <v>0.3674</v>
@@ -11303,7 +11303,7 @@
         <v>-1.5248</v>
       </c>
       <c r="AA72" t="n">
-        <v>-1.3218</v>
+        <v>-1.6615</v>
       </c>
       <c r="AB72" t="n">
         <v>0.3674</v>
@@ -11400,7 +11400,7 @@
         <v>-1.308</v>
       </c>
       <c r="AA73" t="n">
-        <v>-1.2498</v>
+        <v>-1.3556</v>
       </c>
       <c r="AB73" t="n">
         <v>0.4</v>
@@ -11497,7 +11497,7 @@
         <v>-1.2375</v>
       </c>
       <c r="AA74" t="n">
-        <v>-1.245</v>
+        <v>-1.4614</v>
       </c>
       <c r="AB74" t="n">
         <v>0.4</v>
@@ -11594,7 +11594,7 @@
         <v>-1.2782</v>
       </c>
       <c r="AA75" t="n">
-        <v>-1.2005</v>
+        <v>-1.3584</v>
       </c>
       <c r="AB75" t="n">
         <v>0.4</v>
@@ -11691,7 +11691,7 @@
         <v>-1.212</v>
       </c>
       <c r="AA76" t="n">
-        <v>-1.0431</v>
+        <v>-1.046</v>
       </c>
       <c r="AB76" t="n">
         <v>0.4988</v>
@@ -11788,7 +11788,7 @@
         <v>-0.6959</v>
       </c>
       <c r="AA77" t="n">
-        <v>-1.0215</v>
+        <v>-0.8377</v>
       </c>
       <c r="AB77" t="n">
         <v>0.4988</v>
@@ -11885,7 +11885,7 @@
         <v>-0.7255</v>
       </c>
       <c r="AA78" t="n">
-        <v>-0.9769</v>
+        <v>-0.7338</v>
       </c>
       <c r="AB78" t="n">
         <v>0.4988</v>
@@ -11982,7 +11982,7 @@
         <v>-0.4731</v>
       </c>
       <c r="AA79" t="n">
-        <v>-0.845</v>
+        <v>-0.7345</v>
       </c>
       <c r="AB79" t="n">
         <v>0.4974</v>
@@ -12079,7 +12079,7 @@
         <v>-0.72</v>
       </c>
       <c r="AA80" t="n">
-        <v>-0.7881</v>
+        <v>-0.4211</v>
       </c>
       <c r="AB80" t="n">
         <v>0.4974</v>
@@ -12176,7 +12176,7 @@
         <v>-0.8241000000000001</v>
       </c>
       <c r="AA81" t="n">
-        <v>-0.6995</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
         <v>0.4974</v>
@@ -12273,7 +12273,7 @@
         <v>0.0542</v>
       </c>
       <c r="AA82" t="n">
-        <v>-0.6819</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
         <v>0.5896</v>
@@ -12370,7 +12370,7 @@
         <v>-0.3324</v>
       </c>
       <c r="AA83" t="n">
-        <v>-0.6228</v>
+        <v>-0.1053</v>
       </c>
       <c r="AB83" t="n">
         <v>0.5896</v>
@@ -12467,7 +12467,7 @@
         <v>-0.3609</v>
       </c>
       <c r="AA84" t="n">
-        <v>-0.4963</v>
+        <v>0.7392</v>
       </c>
       <c r="AB84" t="n">
         <v>0.5896</v>
@@ -12564,7 +12564,7 @@
         <v>-0.2449</v>
       </c>
       <c r="AA85" t="n">
-        <v>-0.5424</v>
+        <v>1.4799</v>
       </c>
       <c r="AB85" t="n">
         <v>0.6029</v>
@@ -12661,7 +12661,7 @@
         <v>0.2528</v>
       </c>
       <c r="AA86" t="n">
-        <v>-0.387</v>
+        <v>1.2712</v>
       </c>
       <c r="AB86" t="n">
         <v>0.6029</v>
@@ -12758,7 +12758,7 @@
         <v>0.4438</v>
       </c>
       <c r="AA87" t="n">
-        <v>-0.3956</v>
+        <v>1.4831</v>
       </c>
       <c r="AB87" t="n">
         <v>0.6029</v>
@@ -12855,7 +12855,7 @@
         <v>0.6946</v>
       </c>
       <c r="AA88" t="n">
-        <v>-0.3258</v>
+        <v>1.2685</v>
       </c>
       <c r="AB88" t="n">
         <v>0.6332</v>
@@ -12952,7 +12952,7 @@
         <v>0.0603</v>
       </c>
       <c r="AA89" t="n">
-        <v>-0.1622</v>
+        <v>1.056</v>
       </c>
       <c r="AB89" t="n">
         <v>0.6332</v>
@@ -13049,7 +13049,7 @@
         <v>0.7246</v>
       </c>
       <c r="AA90" t="n">
-        <v>-0.1093</v>
+        <v>1.1616</v>
       </c>
       <c r="AB90" t="n">
         <v>0.6332</v>
@@ -13146,7 +13146,7 @@
         <v>0.8227</v>
       </c>
       <c r="AA91" t="n">
-        <v>-0.0369</v>
+        <v>1.5856</v>
       </c>
       <c r="AB91" t="n">
         <v>0.7039</v>
@@ -13243,7 +13243,7 @@
         <v>0.7957</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.0144</v>
+        <v>1.3742</v>
       </c>
       <c r="AB92" t="n">
         <v>0.7039</v>
@@ -13340,7 +13340,7 @@
         <v>1.1156</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.0114</v>
+        <v>1.1616</v>
       </c>
       <c r="AB93" t="n">
         <v>0.7039</v>
@@ -13437,7 +13437,7 @@
         <v>0.9438</v>
       </c>
       <c r="AA94" t="n">
-        <v>0.153</v>
+        <v>1.2672</v>
       </c>
       <c r="AB94" t="n">
         <v>0.6829</v>
@@ -13534,7 +13534,7 @@
         <v>0.7746</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.226</v>
+        <v>1.7914</v>
       </c>
       <c r="AB95" t="n">
         <v>0.6829</v>
@@ -13631,7 +13631,7 @@
         <v>1.523</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.2103</v>
+        <v>1.153</v>
       </c>
       <c r="AB96" t="n">
         <v>0.6829</v>
@@ -13728,7 +13728,7 @@
         <v>1.4989</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.3079</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
         <v>0.6928</v>
@@ -13825,7 +13825,7 @@
         <v>1.0699</v>
       </c>
       <c r="AA98" t="n">
-        <v>0.424</v>
+        <v>0.4184</v>
       </c>
       <c r="AB98" t="n">
         <v>0.6928</v>
@@ -13922,7 +13922,7 @@
         <v>1.833</v>
       </c>
       <c r="AA99" t="n">
-        <v>0.4185</v>
+        <v>0.2088</v>
       </c>
       <c r="AB99" t="n">
         <v>0.6928</v>
@@ -14019,7 +14019,7 @@
         <v>1.5392</v>
       </c>
       <c r="AA100" t="n">
-        <v>0.5052</v>
+        <v>0.1044</v>
       </c>
       <c r="AB100" t="n">
         <v>0.6798</v>
@@ -14116,7 +14116,7 @@
         <v>1.5944</v>
       </c>
       <c r="AA101" t="n">
-        <v>0.5693</v>
+        <v>0.209</v>
       </c>
       <c r="AB101" t="n">
         <v>0.6798</v>
@@ -14213,7 +14213,7 @@
         <v>1.8442</v>
       </c>
       <c r="AA102" t="n">
-        <v>0.6893</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
         <v>0.6798</v>
@@ -14310,7 +14310,7 @@
         <v>1.8746</v>
       </c>
       <c r="AA103" t="n">
-        <v>0.7354000000000001</v>
+        <v>-0.2081</v>
       </c>
       <c r="AB103" t="n">
         <v>0.6641</v>
@@ -14407,7 +14407,7 @@
         <v>2.3008</v>
       </c>
       <c r="AA104" t="n">
-        <v>0.8129</v>
+        <v>-0.1043</v>
       </c>
       <c r="AB104" t="n">
         <v>0.6641</v>
@@ -14504,7 +14504,7 @@
         <v>2.4073</v>
       </c>
       <c r="AA105" t="n">
-        <v>0.9274</v>
+        <v>-0.3132</v>
       </c>
       <c r="AB105" t="n">
         <v>0.6641</v>
@@ -14601,7 +14601,7 @@
         <v>1.9042</v>
       </c>
       <c r="AA106" t="n">
-        <v>0.9204</v>
+        <v>-0.3128</v>
       </c>
       <c r="AB106" t="n">
         <v>0.6577</v>
@@ -14698,7 +14698,7 @@
         <v>2.1355</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.0748</v>
+        <v>-1.1387</v>
       </c>
       <c r="AB107" t="n">
         <v>0.6577</v>
@@ -14795,7 +14795,7 @@
         <v>2.312</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.0465</v>
+        <v>-1.0363</v>
       </c>
       <c r="AB108" t="n">
         <v>0.6577</v>
@@ -14892,7 +14892,7 @@
         <v>2.1546</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.1538</v>
+        <v>2.0833</v>
       </c>
       <c r="AB109" t="n">
         <v>0.6385999999999999</v>
@@ -14989,7 +14989,7 @@
         <v>2.2887</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.1804</v>
+        <v>-0.5208</v>
       </c>
       <c r="AB110" t="n">
         <v>0.6385999999999999</v>
@@ -15086,7 +15086,7 @@
         <v>2.2999</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.2602</v>
+        <v>-0.5208</v>
       </c>
       <c r="AB111" t="n">
         <v>0.6385999999999999</v>
@@ -15183,7 +15183,7 @@
         <v>2.3079</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.3186</v>
+        <v>-0.2086</v>
       </c>
       <c r="AB112" t="n">
         <v>0.5942</v>
@@ -15280,7 +15280,7 @@
         <v>2.3606</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.4742</v>
+        <v>1.877</v>
       </c>
       <c r="AB113" t="n">
         <v>0.5942</v>
@@ -15377,7 +15377,7 @@
         <v>2.7128</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.5118</v>
+        <v>2.4008</v>
       </c>
       <c r="AB114" t="n">
         <v>0.5942</v>
@@ -15474,7 +15474,7 @@
         <v>2.5347</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.4689</v>
+        <v>2.1898</v>
       </c>
       <c r="AB115" t="n">
         <v>0.5928</v>
@@ -15571,7 +15571,7 @@
         <v>3.2265</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.4035</v>
+        <v>2.4008</v>
       </c>
       <c r="AB116" t="n">
         <v>0.5928</v>
@@ -15668,7 +15668,7 @@
         <v>3.1712</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.3596</v>
+        <v>2.9319</v>
       </c>
       <c r="AB117" t="n">
         <v>0.5928</v>
@@ -15765,7 +15765,7 @@
         <v>2.7064</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.208</v>
+        <v>3.0335</v>
       </c>
       <c r="AB118" t="n">
         <v>0.5985</v>
@@ -15862,7 +15862,7 @@
         <v>3.3567</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.1435</v>
+        <v>2.8272</v>
       </c>
       <c r="AB119" t="n">
         <v>0.5985</v>
@@ -15959,7 +15959,7 @@
         <v>3.3969</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.094</v>
+        <v>2.5131</v>
       </c>
       <c r="AB120" t="n">
         <v>0.5985</v>
@@ -16056,7 +16056,7 @@
         <v>3.604</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.072</v>
+        <v>0.2041</v>
       </c>
       <c r="AB121" t="n">
         <v>0.5954</v>
@@ -16153,7 +16153,7 @@
         <v>2.9619</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.0588</v>
+        <v>2.4084</v>
       </c>
       <c r="AB122" t="n">
         <v>0.5954</v>
@@ -16250,7 +16250,7 @@
         <v>3.3711</v>
       </c>
       <c r="AA123" t="n">
-        <v>0.9487</v>
+        <v>2.199</v>
       </c>
       <c r="AB123" t="n">
         <v>0.5954</v>
@@ -16347,7 +16347,7 @@
         <v>3.8472</v>
       </c>
       <c r="AA124" t="n">
-        <v>0.8761</v>
+        <v>2.2989</v>
       </c>
       <c r="AB124" t="n">
         <v>0.5616</v>
@@ -16444,7 +16444,7 @@
         <v>3.3063</v>
       </c>
       <c r="AA125" t="n">
-        <v>0.8573</v>
+        <v>0.7165</v>
       </c>
       <c r="AB125" t="n">
         <v>0.5616</v>
@@ -16541,7 +16541,7 @@
         <v>3.9174</v>
       </c>
       <c r="AA126" t="n">
-        <v>0.7473</v>
+        <v>0.6116</v>
       </c>
       <c r="AB126" t="n">
         <v>0.5616</v>
@@ -16638,7 +16638,7 @@
         <v>3.7774</v>
       </c>
       <c r="AA127" t="n">
-        <v>0.7607</v>
+        <v>0.4082</v>
       </c>
       <c r="AB127" t="n">
         <v>0.578</v>
@@ -16735,7 +16735,7 @@
         <v>4.0897</v>
       </c>
       <c r="AA128" t="n">
-        <v>0.7101</v>
+        <v>0.2039</v>
       </c>
       <c r="AB128" t="n">
         <v>0.578</v>
@@ -16832,7 +16832,7 @@
         <v>3.6481</v>
       </c>
       <c r="AA129" t="n">
-        <v>0.626</v>
+        <v>0.1017</v>
       </c>
       <c r="AB129" t="n">
         <v>0.578</v>
@@ -16929,7 +16929,7 @@
         <v>3.8803</v>
       </c>
       <c r="AA130" t="n">
-        <v>0.5109</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
         <v>0.5145999999999999</v>
@@ -17026,7 +17026,7 @@
         <v>3.6087</v>
       </c>
       <c r="AA131" t="n">
-        <v>0.5314</v>
+        <v>0.3055</v>
       </c>
       <c r="AB131" t="n">
         <v>0.5145999999999999</v>
@@ -17123,7 +17123,7 @@
         <v>3.7237</v>
       </c>
       <c r="AA132" t="n">
-        <v>0.3619</v>
+        <v>0.2043</v>
       </c>
       <c r="AB132" t="n">
         <v>0.5145999999999999</v>
@@ -17220,7 +17220,7 @@
         <v>3.8096</v>
       </c>
       <c r="AA133" t="n">
-        <v>0.3785</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
         <v>0.5435</v>
@@ -17317,7 +17317,7 @@
         <v>3.8219</v>
       </c>
       <c r="AA134" t="n">
-        <v>0.2992</v>
+        <v>-0.1022</v>
       </c>
       <c r="AB134" t="n">
         <v>0.5435</v>
@@ -17414,7 +17414,7 @@
         <v>4.2688</v>
       </c>
       <c r="AA135" t="n">
-        <v>0.2385</v>
+        <v>0.2049</v>
       </c>
       <c r="AB135" t="n">
         <v>0.5435</v>
@@ -17511,7 +17511,7 @@
         <v>4.0178</v>
       </c>
       <c r="AA136" t="n">
-        <v>0.1346</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
         <v>0.5258</v>
@@ -17608,7 +17608,7 @@
         <v>4.314</v>
       </c>
       <c r="AA137" t="n">
-        <v>0.1307</v>
+        <v>-0.3049</v>
       </c>
       <c r="AB137" t="n">
         <v>0.5258</v>
@@ -17705,7 +17705,7 @@
         <v>4.5253</v>
       </c>
       <c r="AA138" t="n">
-        <v>0.0655</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="AB138" t="n">
         <v>0.5258</v>
@@ -17802,7 +17802,7 @@
         <v>4.7573</v>
       </c>
       <c r="AA139" t="n">
-        <v>-0.0454</v>
+        <v>-0.3049</v>
       </c>
       <c r="AB139" t="n">
         <v>0.5296</v>
@@ -17899,7 +17899,7 @@
         <v>4.3998</v>
       </c>
       <c r="AA140" t="n">
-        <v>-0.0342</v>
+        <v>-0.4069</v>
       </c>
       <c r="AB140" t="n">
         <v>0.5296</v>
@@ -17996,7 +17996,7 @@
         <v>4.4364</v>
       </c>
       <c r="AA141" t="n">
-        <v>0.0155</v>
+        <v>-0.5081</v>
       </c>
       <c r="AB141" t="n">
         <v>0.5296</v>
@@ -18093,7 +18093,7 @@
         <v>4.8974</v>
       </c>
       <c r="AA142" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="AB142" t="n">
         <v>0.5544</v>
@@ -18190,7 +18190,7 @@
         <v>5.3294</v>
       </c>
       <c r="AA143" t="n">
-        <v>-0.08790000000000001</v>
+        <v>0.1015</v>
       </c>
       <c r="AB143" t="n">
         <v>0.5544</v>
@@ -18287,7 +18287,7 @@
         <v>5.286</v>
       </c>
       <c r="AA144" t="n">
-        <v>-0.0844</v>
+        <v>0.5097</v>
       </c>
       <c r="AB144" t="n">
         <v>0.5544</v>
@@ -18384,7 +18384,7 @@
         <v>5.7946</v>
       </c>
       <c r="AA145" t="n">
-        <v>-0.0582</v>
+        <v>0.7128</v>
       </c>
       <c r="AB145" t="n">
         <v>0.554</v>
@@ -18481,7 +18481,7 @@
         <v>5.7936</v>
       </c>
       <c r="AA146" t="n">
-        <v>-0.0414</v>
+        <v>0.5118</v>
       </c>
       <c r="AB146" t="n">
         <v>0.554</v>
@@ -18578,7 +18578,7 @@
         <v>6.0966</v>
       </c>
       <c r="AA147" t="n">
-        <v>-0.0256</v>
+        <v>0.3067</v>
       </c>
       <c r="AB147" t="n">
         <v>0.554</v>
@@ -18675,7 +18675,7 @@
         <v>5.5157</v>
       </c>
       <c r="AA148" t="n">
-        <v>-0.124</v>
+        <v>0.2043</v>
       </c>
       <c r="AB148" t="n">
         <v>0.5637</v>
@@ -18772,7 +18772,7 @@
         <v>6.4179</v>
       </c>
       <c r="AA149" t="n">
-        <v>-0.1597</v>
+        <v>0.4077</v>
       </c>
       <c r="AB149" t="n">
         <v>0.5637</v>
@@ -18869,7 +18869,7 @@
         <v>6.164</v>
       </c>
       <c r="AA150" t="n">
-        <v>-0.1485</v>
+        <v>0.4073</v>
       </c>
       <c r="AB150" t="n">
         <v>0.5637</v>
@@ -18966,7 +18966,7 @@
         <v>6.2628</v>
       </c>
       <c r="AA151" t="n">
-        <v>-0.1317</v>
+        <v>0.4077</v>
       </c>
       <c r="AB151" t="n">
         <v>0.605</v>
@@ -19063,7 +19063,7 @@
         <v>6.8027</v>
       </c>
       <c r="AA152" t="n">
-        <v>-0.161</v>
+        <v>0.4086</v>
       </c>
       <c r="AB152" t="n">
         <v>0.605</v>
@@ -19160,7 +19160,7 @@
         <v>6.4641</v>
       </c>
       <c r="AA153" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.6129</v>
       </c>
       <c r="AB153" t="n">
         <v>0.605</v>
@@ -19257,7 +19257,7 @@
         <v>6.8497</v>
       </c>
       <c r="AA154" t="n">
-        <v>-0.1543</v>
+        <v>0.8163</v>
       </c>
       <c r="AB154" t="n">
         <v>0.6524</v>
@@ -19354,7 +19354,7 @@
         <v>7.0352</v>
       </c>
       <c r="AA155" t="n">
-        <v>-0.1759</v>
+        <v>0.2028</v>
       </c>
       <c r="AB155" t="n">
         <v>0.6524</v>
@@ -19451,7 +19451,7 @@
         <v>6.8779</v>
       </c>
       <c r="AA156" t="n">
-        <v>-0.1185</v>
+        <v>0.5071</v>
       </c>
       <c r="AB156" t="n">
         <v>0.6524</v>
@@ -19548,7 +19548,7 @@
         <v>6.953</v>
       </c>
       <c r="AA157" t="n">
-        <v>-0.1443</v>
+        <v>0.7078</v>
       </c>
       <c r="AB157" t="n">
         <v>0.6642</v>
@@ -19645,7 +19645,7 @@
         <v>7.644</v>
       </c>
       <c r="AA158" t="n">
-        <v>-0.2306</v>
+        <v>1.9348</v>
       </c>
       <c r="AB158" t="n">
         <v>0.6642</v>
@@ -19742,7 +19742,7 @@
         <v>7.363</v>
       </c>
       <c r="AA159" t="n">
-        <v>-0.2059</v>
+        <v>1.5291</v>
       </c>
       <c r="AB159" t="n">
         <v>0.6642</v>
@@ -19839,7 +19839,7 @@
         <v>7.954</v>
       </c>
       <c r="AA160" t="n">
-        <v>-0.212</v>
+        <v>1.1213</v>
       </c>
       <c r="AB160" t="n">
         <v>0.6751</v>
@@ -19936,7 +19936,7 @@
         <v>7.8409</v>
       </c>
       <c r="AA161" t="n">
-        <v>-0.1826</v>
+        <v>0.6091</v>
       </c>
       <c r="AB161" t="n">
         <v>0.6751</v>
@@ -20033,7 +20033,7 @@
         <v>8.063599999999999</v>
       </c>
       <c r="AA162" t="n">
-        <v>-0.2394</v>
+        <v>0.7099</v>
       </c>
       <c r="AB162" t="n">
         <v>0.6751</v>
@@ -20130,7 +20130,7 @@
         <v>8.4268</v>
       </c>
       <c r="AA163" t="n">
-        <v>-0.2148</v>
+        <v>0.7107</v>
       </c>
       <c r="AB163" t="n">
         <v>0.6768999999999999</v>
@@ -20227,7 +20227,7 @@
         <v>8.6327</v>
       </c>
       <c r="AA164" t="n">
-        <v>-0.2162</v>
+        <v>0.9156</v>
       </c>
       <c r="AB164" t="n">
         <v>0.6768999999999999</v>
@@ -20324,7 +20324,7 @@
         <v>8.831200000000001</v>
       </c>
       <c r="AA165" t="n">
-        <v>-0.2652</v>
+        <v>1.3198</v>
       </c>
       <c r="AB165" t="n">
         <v>0.6768999999999999</v>
@@ -20421,7 +20421,7 @@
         <v>8.680400000000001</v>
       </c>
       <c r="AA166" t="n">
-        <v>-0.3191</v>
+        <v>1.1134</v>
       </c>
       <c r="AB166" t="n">
         <v>0.7045</v>
@@ -20518,7 +20518,7 @@
         <v>8.8995</v>
       </c>
       <c r="AA167" t="n">
-        <v>-0.2433</v>
+        <v>1.417</v>
       </c>
       <c r="AB167" t="n">
         <v>0.7045</v>
@@ -20615,7 +20615,7 @@
         <v>9.211600000000001</v>
       </c>
       <c r="AA168" t="n">
-        <v>-0.2787</v>
+        <v>0.9082</v>
       </c>
       <c r="AB168" t="n">
         <v>0.7045</v>
@@ -20712,7 +20712,7 @@
         <v>8.890700000000001</v>
       </c>
       <c r="AA169" t="n">
-        <v>-0.284</v>
+        <v>0.6024</v>
       </c>
       <c r="AB169" t="n">
         <v>0.7396</v>
@@ -20809,7 +20809,7 @@
         <v>9.510899999999999</v>
       </c>
       <c r="AA170" t="n">
-        <v>-0.3334</v>
+        <v>-0.3996</v>
       </c>
       <c r="AB170" t="n">
         <v>0.7396</v>
@@ -20906,7 +20906,7 @@
         <v>9.397500000000001</v>
       </c>
       <c r="AA171" t="n">
-        <v>-0.2814</v>
+        <v>0.1004</v>
       </c>
       <c r="AB171" t="n">
         <v>0.7396</v>
@@ -21003,7 +21003,7 @@
         <v>9.9002</v>
       </c>
       <c r="AA172" t="n">
-        <v>-0.3157</v>
+        <v>0.504</v>
       </c>
       <c r="AB172" t="n">
         <v>0.7796999999999999</v>
@@ -21100,7 +21100,7 @@
         <v>9.5806</v>
       </c>
       <c r="AA173" t="n">
-        <v>-0.3921</v>
+        <v>0.9082</v>
       </c>
       <c r="AB173" t="n">
         <v>0.7796999999999999</v>
@@ -21197,7 +21197,7 @@
         <v>10.0354</v>
       </c>
       <c r="AA174" t="n">
-        <v>-0.374</v>
+        <v>0.7049</v>
       </c>
       <c r="AB174" t="n">
         <v>0.7796999999999999</v>
@@ -21294,7 +21294,7 @@
         <v>10.3961</v>
       </c>
       <c r="AA175" t="n">
-        <v>-0.3515</v>
+        <v>0.8065</v>
       </c>
       <c r="AB175" t="n">
         <v>0.7991</v>
@@ -21391,7 +21391,7 @@
         <v>10.6124</v>
       </c>
       <c r="AA176" t="n">
-        <v>-0.3863</v>
+        <v>1.0081</v>
       </c>
       <c r="AB176" t="n">
         <v>0.7991</v>
@@ -21488,7 +21488,7 @@
         <v>10.6257</v>
       </c>
       <c r="AA177" t="n">
-        <v>-0.3366</v>
+        <v>0.2004</v>
       </c>
       <c r="AB177" t="n">
         <v>0.7991</v>
@@ -21585,7 +21585,7 @@
         <v>10.7821</v>
       </c>
       <c r="AA178" t="n">
-        <v>-0.4202</v>
+        <v>0.4004</v>
       </c>
       <c r="AB178" t="n">
         <v>0.6589</v>
@@ -21682,7 +21682,7 @@
         <v>10.9602</v>
       </c>
       <c r="AA179" t="n">
-        <v>-0.4685</v>
+        <v>0.499</v>
       </c>
       <c r="AB179" t="n">
         <v>0.6589</v>
@@ -21779,7 +21779,7 @@
         <v>10.6116</v>
       </c>
       <c r="AA180" t="n">
-        <v>-0.4126</v>
+        <v>0.5</v>
       </c>
       <c r="AB180" t="n">
         <v>0.6589</v>
@@ -21876,7 +21876,7 @@
         <v>10.7514</v>
       </c>
       <c r="AA181" t="n">
-        <v>-0.4181</v>
+        <v>0.2994</v>
       </c>
       <c r="AB181" t="n">
         <v>0.4732</v>
@@ -21973,7 +21973,7 @@
         <v>10.8966</v>
       </c>
       <c r="AA182" t="n">
-        <v>-0.4102</v>
+        <v>0.8024</v>
       </c>
       <c r="AB182" t="n">
         <v>0.4732</v>
@@ -22070,7 +22070,7 @@
         <v>11.771</v>
       </c>
       <c r="AA183" t="n">
-        <v>-0.4223</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="AB183" t="n">
         <v>0.4732</v>
@@ -22167,7 +22167,7 @@
         <v>11.2146</v>
       </c>
       <c r="AA184" t="n">
-        <v>-0.4146</v>
+        <v>0.6018</v>
       </c>
       <c r="AB184" t="n">
         <v>0.3311</v>
@@ -22264,7 +22264,7 @@
         <v>11.2935</v>
       </c>
       <c r="AA185" t="n">
-        <v>-0.4942</v>
+        <v>0.3</v>
       </c>
       <c r="AB185" t="n">
         <v>0.3311</v>
@@ -22361,7 +22361,7 @@
         <v>11.4924</v>
       </c>
       <c r="AA186" t="n">
-        <v>-0.522</v>
+        <v>0.3</v>
       </c>
       <c r="AB186" t="n">
         <v>0.3311</v>
@@ -22458,7 +22458,7 @@
         <v>11.7274</v>
       </c>
       <c r="AA187" t="n">
-        <v>-0.454</v>
+        <v>0.2</v>
       </c>
       <c r="AB187" t="n">
         <v>0.2213</v>
@@ -22555,7 +22555,7 @@
         <v>10.9582</v>
       </c>
       <c r="AA188" t="n">
-        <v>-0.3309</v>
+        <v>0.0998</v>
       </c>
       <c r="AB188" t="n">
         <v>0.2213</v>
@@ -22652,7 +22652,7 @@
         <v>10.1115</v>
       </c>
       <c r="AA189" t="n">
-        <v>-0.165</v>
+        <v>1</v>
       </c>
       <c r="AB189" t="n">
         <v>0.2213</v>
@@ -22749,7 +22749,7 @@
         <v>9.764200000000001</v>
       </c>
       <c r="AA190" t="n">
-        <v>-0.0184</v>
+        <v>0.1994</v>
       </c>
       <c r="AB190" t="n">
         <v>0.08</v>
@@ -22846,7 +22846,7 @@
         <v>9.0296</v>
       </c>
       <c r="AA191" t="n">
-        <v>0.1028</v>
+        <v>-0.2979</v>
       </c>
       <c r="AB191" t="n">
         <v>0.08</v>
@@ -22943,7 +22943,7 @@
         <v>8.3215</v>
       </c>
       <c r="AA192" t="n">
-        <v>0.2353</v>
+        <v>-0.995</v>
       </c>
       <c r="AB192" t="n">
         <v>0.08</v>
@@ -23040,7 +23040,7 @@
         <v>7.6248</v>
       </c>
       <c r="AA193" t="n">
-        <v>0.3748</v>
+        <v>0.199</v>
       </c>
       <c r="AB193" t="n">
         <v>0.08459999999999999</v>
@@ -23137,7 +23137,7 @@
         <v>6.4632</v>
       </c>
       <c r="AA194" t="n">
-        <v>0.5442</v>
+        <v>-0.4975</v>
       </c>
       <c r="AB194" t="n">
         <v>0.08459999999999999</v>
@@ -23234,7 +23234,7 @@
         <v>6.0074</v>
       </c>
       <c r="AA195" t="n">
-        <v>0.6829</v>
+        <v>-0.5976</v>
       </c>
       <c r="AB195" t="n">
         <v>0.08459999999999999</v>
@@ -23331,7 +23331,7 @@
         <v>4.9477</v>
       </c>
       <c r="AA196" t="n">
-        <v>0.8091</v>
+        <v>-0.3988</v>
       </c>
       <c r="AB196" t="n">
         <v>0.1371</v>
@@ -23428,7 +23428,7 @@
         <v>4.5654</v>
       </c>
       <c r="AA197" t="n">
-        <v>1.0111</v>
+        <v>-1.1964</v>
       </c>
       <c r="AB197" t="n">
         <v>0.1371</v>
@@ -23525,7 +23525,7 @@
         <v>3.7805</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.2043</v>
+        <v>-0.8973</v>
       </c>
       <c r="AB198" t="n">
         <v>0.1371</v>
@@ -23622,7 +23622,7 @@
         <v>2.8489</v>
       </c>
       <c r="AA199" t="n">
-        <v>1.2891</v>
+        <v>-0.2994</v>
       </c>
       <c r="AB199" t="n">
         <v>0.2511</v>
@@ -23719,7 +23719,7 @@
         <v>3.0793</v>
       </c>
       <c r="AA200" t="n">
-        <v>1.4875</v>
+        <v>-0.5982</v>
       </c>
       <c r="AB200" t="n">
         <v>0.2511</v>
@@ -23816,7 +23816,7 @@
         <v>3.0013</v>
       </c>
       <c r="AA201" t="n">
-        <v>1.6209</v>
+        <v>-1.0891</v>
       </c>
       <c r="AB201" t="n">
         <v>0.2511</v>
@@ -23913,7 +23913,7 @@
         <v>3.65</v>
       </c>
       <c r="AA202" t="n">
-        <v>1.718</v>
+        <v>0.8955</v>
       </c>
       <c r="AB202" t="n">
         <v>0.3019</v>
@@ -24010,7 +24010,7 @@
         <v>3.2718</v>
       </c>
       <c r="AA203" t="n">
-        <v>1.8785</v>
+        <v>0.3984</v>
       </c>
       <c r="AB203" t="n">
         <v>0.3019</v>
@@ -24107,7 +24107,7 @@
         <v>3.372</v>
       </c>
       <c r="AA204" t="n">
-        <v>2.0762</v>
+        <v>1.3065</v>
       </c>
       <c r="AB204" t="n">
         <v>0.3019</v>
@@ -24204,7 +24204,7 @@
         <v>3.2568</v>
       </c>
       <c r="AA205" t="n">
-        <v>2.2142</v>
+        <v>5.6604</v>
       </c>
       <c r="AB205" t="n">
         <v>0.3322</v>
@@ -24301,7 +24301,7 @@
         <v>3.977</v>
       </c>
       <c r="AA206" t="n">
-        <v>2.3726</v>
+        <v>2</v>
       </c>
       <c r="AB206" t="n">
         <v>0.3322</v>
@@ -24398,7 +24398,7 @@
         <v>3.9906</v>
       </c>
       <c r="AA207" t="n">
-        <v>2.5463</v>
+        <v>2.505</v>
       </c>
       <c r="AB207" t="n">
         <v>0.3322</v>
@@ -24495,7 +24495,7 @@
         <v>4.0512</v>
       </c>
       <c r="AA208" t="n">
-        <v>2.6486</v>
+        <v>2.6026</v>
       </c>
       <c r="AB208" t="n">
         <v>0.3687</v>
@@ -24592,7 +24592,7 @@
         <v>4.1731</v>
       </c>
       <c r="AA209" t="n">
-        <v>2.7713</v>
+        <v>3.8345</v>
       </c>
       <c r="AB209" t="n">
         <v>0.3687</v>
@@ -24689,7 +24689,7 @@
         <v>4.2301</v>
       </c>
       <c r="AA210" t="n">
-        <v>2.9557</v>
+        <v>4.0241</v>
       </c>
       <c r="AB210" t="n">
         <v>0.3687</v>
@@ -24786,7 +24786,7 @@
         <v>4.3464</v>
       </c>
       <c r="AA211" t="n">
-        <v>3.152</v>
+        <v>3.7037</v>
       </c>
       <c r="AB211" t="n">
         <v>0.4269</v>
@@ -24883,7 +24883,7 @@
         <v>4.1646</v>
       </c>
       <c r="AA212" t="n">
-        <v>3.2892</v>
+        <v>4.7141</v>
       </c>
       <c r="AB212" t="n">
         <v>0.4269</v>
@@ -24980,7 +24980,7 @@
         <v>3.94</v>
       </c>
       <c r="AA213" t="n">
-        <v>3.388</v>
+        <v>5.4054</v>
       </c>
       <c r="AB213" t="n">
         <v>0.4269</v>
@@ -25077,7 +25077,7 @@
         <v>4.6217</v>
       </c>
       <c r="AA214" t="n">
-        <v>3.5901</v>
+        <v>4.3393</v>
       </c>
       <c r="AB214" t="n">
         <v>0.4919</v>
@@ -25174,7 +25174,7 @@
         <v>4.4971</v>
       </c>
       <c r="AA215" t="n">
-        <v>3.694</v>
+        <v>6.25</v>
       </c>
       <c r="AB215" t="n">
         <v>0.4919</v>
@@ -25271,7 +25271,7 @@
         <v>4.0841</v>
       </c>
       <c r="AA216" t="n">
-        <v>3.8548</v>
+        <v>6.9444</v>
       </c>
       <c r="AB216" t="n">
         <v>0.4919</v>
@@ -25368,7 +25368,7 @@
         <v>4.858</v>
       </c>
       <c r="AA217" t="n">
-        <v>4.0354</v>
+        <v>7.4248</v>
       </c>
       <c r="AB217" t="n">
         <v>0.4908</v>
@@ -25465,7 +25465,7 @@
         <v>4.3604</v>
       </c>
       <c r="AA218" t="n">
-        <v>3.9303</v>
+        <v>7.3529</v>
       </c>
       <c r="AB218" t="n">
         <v>0.4908</v>
@@ -25562,7 +25562,7 @@
         <v>4.9338</v>
       </c>
       <c r="AA219" t="n">
-        <v>3.7637</v>
+        <v>7.5269</v>
       </c>
       <c r="AB219" t="n">
         <v>0.4908</v>
@@ -25659,7 +25659,7 @@
         <v>4.867</v>
       </c>
       <c r="AA220" t="n">
-        <v>3.6996</v>
+        <v>7.7073</v>
       </c>
       <c r="AB220" t="n">
         <v>0.4919</v>
@@ -25756,7 +25756,7 @@
         <v>5.1416</v>
       </c>
       <c r="AA221" t="n">
-        <v>3.5784</v>
+        <v>8.454800000000001</v>
       </c>
       <c r="AB221" t="n">
         <v>0.4919</v>
@@ -25853,7 +25853,7 @@
         <v>4.643</v>
       </c>
       <c r="AA222" t="n">
-        <v>3.4539</v>
+        <v>8.5106</v>
       </c>
       <c r="AB222" t="n">
         <v>0.4919</v>
@@ -25950,7 +25950,7 @@
         <v>4.8152</v>
       </c>
       <c r="AA223" t="n">
-        <v>3.3559</v>
+        <v>8.3012</v>
       </c>
       <c r="AB223" t="n">
         <v>0.5234</v>
@@ -26047,7 +26047,7 @@
         <v>5.2503</v>
       </c>
       <c r="AA224" t="n">
-        <v>3.1851</v>
+        <v>8.333299999999999</v>
       </c>
       <c r="AB224" t="n">
         <v>0.5234</v>
@@ -26144,7 +26144,7 @@
         <v>5.0888</v>
       </c>
       <c r="AA225" t="n">
-        <v>3.1532</v>
+        <v>7.7873</v>
       </c>
       <c r="AB225" t="n">
         <v>0.5234</v>
@@ -26241,7 +26241,7 @@
         <v>4.8444</v>
       </c>
       <c r="AA226" t="n">
-        <v>3.1703</v>
+        <v>8.6957</v>
       </c>
       <c r="AB226" t="n">
         <v>0.5189</v>
@@ -26338,7 +26338,7 @@
         <v>5.0473</v>
       </c>
       <c r="AA227" t="n">
-        <v>3.007</v>
+        <v>8.5901</v>
       </c>
       <c r="AB227" t="n">
         <v>0.5189</v>
@@ -26435,7 +26435,7 @@
         <v>5.0914</v>
       </c>
       <c r="AA228" t="n">
-        <v>2.9818</v>
+        <v>7.2356</v>
       </c>
       <c r="AB228" t="n">
         <v>0.5189</v>
@@ -26532,7 +26532,7 @@
         <v>5.0369</v>
       </c>
       <c r="AA229" t="n">
-        <v>2.9933</v>
+        <v>11.3736</v>
       </c>
       <c r="AB229" t="n">
         <v>0.5456</v>
@@ -26629,7 +26629,7 @@
         <v>5.6388</v>
       </c>
       <c r="AA230" t="n">
-        <v>2.8504</v>
+        <v>5.6621</v>
       </c>
       <c r="AB230" t="n">
         <v>0.5456</v>
@@ -26726,7 +26726,7 @@
         <v>5.5714</v>
       </c>
       <c r="AA231" t="n">
-        <v>2.8236</v>
+        <v>4.8182</v>
       </c>
       <c r="AB231" t="n">
         <v>0.5456</v>
@@ -26823,7 +26823,7 @@
         <v>5.9533</v>
       </c>
       <c r="AA232" t="n">
-        <v>2.732</v>
+        <v>4.8007</v>
       </c>
       <c r="AB232" t="n">
         <v>0.5908</v>
@@ -26920,7 +26920,7 @@
         <v>5.5307</v>
       </c>
       <c r="AA233" t="n">
-        <v>2.7356</v>
+        <v>4.3011</v>
       </c>
       <c r="AB233" t="n">
         <v>0.5908</v>
@@ -27017,7 +27017,7 @@
         <v>5.8388</v>
       </c>
       <c r="AA234" t="n">
-        <v>2.6954</v>
+        <v>4.0998</v>
       </c>
       <c r="AB234" t="n">
         <v>0.5908</v>
@@ -27114,7 +27114,7 @@
         <v>5.9071</v>
       </c>
       <c r="AA235" t="n">
-        <v>2.5612</v>
+        <v>3.6542</v>
       </c>
       <c r="AB235" t="n">
         <v>0.6291</v>
@@ -27211,7 +27211,7 @@
         <v>5.9006</v>
       </c>
       <c r="AA236" t="n">
-        <v>2.6109</v>
+        <v>3.8904</v>
       </c>
       <c r="AB236" t="n">
         <v>0.6291</v>
@@ -27308,7 +27308,7 @@
         <v>5.8624</v>
       </c>
       <c r="AA237" t="n">
-        <v>2.5543</v>
+        <v>6.4317</v>
       </c>
       <c r="AB237" t="n">
         <v>0.6291</v>
@@ -27405,7 +27405,7 @@
         <v>5.7622</v>
       </c>
       <c r="AA238" t="n">
-        <v>2.4955</v>
+        <v>9.2174</v>
       </c>
       <c r="AB238" t="n">
         <v>0.631</v>
@@ -27502,7 +27502,7 @@
         <v>6.3415</v>
       </c>
       <c r="AA239" t="n">
-        <v>2.4735</v>
+        <v>12.1238</v>
       </c>
       <c r="AB239" t="n">
         <v>0.631</v>
@@ -27599,7 +27599,7 @@
         <v>6.3011</v>
       </c>
       <c r="AA240" t="n">
-        <v>2.5345</v>
+        <v>14.7924</v>
       </c>
       <c r="AB240" t="n">
         <v>0.631</v>
@@ -27696,7 +27696,7 @@
         <v>6.3746</v>
       </c>
       <c r="AA241" t="n">
-        <v>2.5386</v>
+        <v>17.989</v>
       </c>
       <c r="AB241" t="n">
         <v>0.6032999999999999</v>
@@ -27793,7 +27793,7 @@
         <v>6.0521</v>
       </c>
       <c r="AA242" t="n">
-        <v>2.5154</v>
+        <v>17.6318</v>
       </c>
       <c r="AB242" t="n">
         <v>0.6032999999999999</v>
@@ -27890,7 +27890,7 @@
         <v>6.0744</v>
       </c>
       <c r="AA243" t="n">
-        <v>2.5114</v>
+        <v>21.856</v>
       </c>
       <c r="AB243" t="n">
         <v>0.6032999999999999</v>
@@ -27987,7 +27987,7 @@
         <v>6.5983</v>
       </c>
       <c r="AA244" t="n">
-        <v>2.3962</v>
+        <v>24.892</v>
       </c>
       <c r="AB244" t="n">
         <v>0.6354</v>
@@ -28084,7 +28084,7 @@
         <v>5.9781</v>
       </c>
       <c r="AA245" t="n">
-        <v>2.3935</v>
+        <v>25.945</v>
       </c>
       <c r="AB245" t="n">
         <v>0.6354</v>
@@ -28181,7 +28181,7 @@
         <v>6.556</v>
       </c>
       <c r="AA246" t="n">
-        <v>2.3937</v>
+        <v>27.5685</v>
       </c>
       <c r="AB246" t="n">
         <v>0.6354</v>
@@ -28278,7 +28278,7 @@
         <v>6.5037</v>
       </c>
       <c r="AA247" t="n">
-        <v>2.3445</v>
+        <v>28.9768</v>
       </c>
       <c r="AB247" t="n">
         <v>0.6381</v>
@@ -28375,7 +28375,7 @@
         <v>6.6021</v>
       </c>
       <c r="AA248" t="n">
-        <v>2.3398</v>
+        <v>27.4043</v>
       </c>
       <c r="AB248" t="n">
         <v>0.6381</v>
@@ -28472,7 +28472,7 @@
         <v>6.6087</v>
       </c>
       <c r="AA249" t="n">
-        <v>2.1791</v>
+        <v>22.6821</v>
       </c>
       <c r="AB249" t="n">
         <v>0.6381</v>
@@ -28569,7 +28569,7 @@
         <v>6.267</v>
       </c>
       <c r="AA250" t="n">
-        <v>2.1064</v>
+        <v>17.9936</v>
       </c>
       <c r="AB250" t="n">
         <v>0.6496</v>
@@ -28666,7 +28666,7 @@
         <v>6.2221</v>
       </c>
       <c r="AA251" t="n">
-        <v>2.0209</v>
+        <v>16.7178</v>
       </c>
       <c r="AB251" t="n">
         <v>0.6496</v>
@@ -28763,7 +28763,7 @@
         <v>6.4983</v>
       </c>
       <c r="AA252" t="n">
-        <v>1.9713</v>
+        <v>15.8252</v>
       </c>
       <c r="AB252" t="n">
         <v>0.6496</v>
@@ -28860,7 +28860,7 @@
         <v>6.2486</v>
       </c>
       <c r="AA253" t="n">
-        <v>1.8782</v>
+        <v>1.4647</v>
       </c>
       <c r="AB253" t="n">
         <v>0.7155</v>
@@ -28957,7 +28957,7 @@
         <v>6.0818</v>
       </c>
       <c r="AA254" t="n">
-        <v>1.7127</v>
+        <v>12.05</v>
       </c>
       <c r="AB254" t="n">
         <v>0.7155</v>
@@ -29054,7 +29054,7 @@
         <v>6.2818</v>
       </c>
       <c r="AA255" t="n">
-        <v>1.6836</v>
+        <v>7.331</v>
       </c>
       <c r="AB255" t="n">
         <v>0.7155</v>
@@ -29151,7 +29151,7 @@
         <v>6.3162</v>
       </c>
       <c r="AA256" t="n">
-        <v>1.6068</v>
+        <v>3.4602</v>
       </c>
       <c r="AB256" t="n">
         <v>0.6982</v>
@@ -29248,7 +29248,7 @@
         <v>5.8828</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.5329</v>
+        <v>1.296</v>
       </c>
       <c r="AB257" t="n">
         <v>0.6982</v>
@@ -29345,7 +29345,7 @@
         <v>6.0576</v>
       </c>
       <c r="AA258" t="n">
-        <v>1.5188</v>
+        <v>-0.8054</v>
       </c>
       <c r="AB258" t="n">
         <v>0.6982</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -4540,7 +4540,7 @@
         <v>1.0851</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4613,7 +4613,7 @@
         <v>1.1575</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4698,7 +4698,7 @@
         <v>1.3439</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.1042</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>1.4047</v>
@@ -4892,7 +4892,7 @@
         <v>1.9537</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>1.4047</v>
@@ -4989,7 +4989,7 @@
         <v>1.505</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.2077</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>1.3922</v>
@@ -5086,7 +5086,7 @@
         <v>2.1369</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.2079</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>1.3922</v>
@@ -5183,7 +5183,7 @@
         <v>2.1182</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.2077</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>1.3922</v>
@@ -5280,7 +5280,7 @@
         <v>2.3802</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.2073</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>1.3493</v>
@@ -5377,7 +5377,7 @@
         <v>2.4564</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.1036</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>1.3493</v>
@@ -5474,7 +5474,7 @@
         <v>2.6686</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.104</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>1.3493</v>
@@ -5571,7 +5571,7 @@
         <v>2.7107</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.1038</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>1.345</v>
@@ -5668,7 +5668,7 @@
         <v>2.8519</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.1043</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>1.345</v>
@@ -5862,7 +5862,7 @@
         <v>3.0448</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1043</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>1.3676</v>
@@ -5959,7 +5959,7 @@
         <v>2.8976</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.104</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>1.3676</v>
@@ -6153,7 +6153,7 @@
         <v>3.8205</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>1.3038</v>
@@ -6250,7 +6250,7 @@
         <v>3.9486</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.2083</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>1.3038</v>
@@ -6347,7 +6347,7 @@
         <v>3.6851</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.3122</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>1.3038</v>
@@ -6444,7 +6444,7 @@
         <v>3.9738</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.2077</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>1.3185</v>
@@ -6541,7 +6541,7 @@
         <v>3.8656</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.1037</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>1.3185</v>
@@ -6638,7 +6638,7 @@
         <v>4.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.2081</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>1.3185</v>
@@ -6735,7 +6735,7 @@
         <v>4.6623</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.3119</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>1.2761</v>
@@ -6929,7 +6929,7 @@
         <v>4.3724</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.1046</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>1.2761</v>
@@ -7026,7 +7026,7 @@
         <v>4.7572</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.3125</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>1.2935</v>
@@ -7123,7 +7123,7 @@
         <v>4.8137</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.1041</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>1.2935</v>
@@ -7220,7 +7220,7 @@
         <v>5.4772</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.1038</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>1.2935</v>
@@ -7317,7 +7317,7 @@
         <v>5.0325</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.1038</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>1.2782</v>
@@ -7414,7 +7414,7 @@
         <v>5.5881</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.104</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>1.2782</v>
@@ -7511,7 +7511,7 @@
         <v>5.7055</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.1037</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>1.2782</v>
@@ -7608,7 +7608,7 @@
         <v>6.0632</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.1036</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>1.2546</v>
@@ -7705,7 +7705,7 @@
         <v>5.972</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.1036</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>1.2546</v>
@@ -7802,7 +7802,7 @@
         <v>6.1512</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.4154</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>1.2546</v>
@@ -7899,7 +7899,7 @@
         <v>6.5018</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.1399</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>1.2412</v>
@@ -7996,7 +7996,7 @@
         <v>6.4813</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.8351</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>1.2412</v>
@@ -8093,7 +8093,7 @@
         <v>6.6136</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.0471</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>1.2412</v>
@@ -8190,7 +8190,7 @@
         <v>6.7147</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.2539</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>1.1885</v>
@@ -8287,7 +8287,7 @@
         <v>6.7982</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>1.1885</v>
@@ -8384,7 +8384,7 @@
         <v>7.0319</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.4553</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>1.1885</v>
@@ -8481,7 +8481,7 @@
         <v>7.2732</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.8711</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
         <v>1.1972</v>
@@ -8578,7 +8578,7 @@
         <v>7.0198</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.3933</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>1.1972</v>
@@ -8675,7 +8675,7 @@
         <v>7.7711</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.3884</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>1.1972</v>
@@ -8772,7 +8772,7 @@
         <v>7.7861</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2822</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0.9696</v>
@@ -8869,7 +8869,7 @@
         <v>7.6124</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.8634</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
         <v>0.9696</v>
@@ -8966,7 +8966,7 @@
         <v>7.5954</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.9307</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0.9696</v>
@@ -9063,7 +9063,7 @@
         <v>8.0928</v>
       </c>
       <c r="AA49" t="n">
-        <v>-0.4098</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0.8003</v>
@@ -9354,7 +9354,7 @@
         <v>6.7264</v>
       </c>
       <c r="AA52" t="n">
-        <v>-0.1032</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0.584</v>
@@ -9451,7 +9451,7 @@
         <v>5.6646</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.1032</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
         <v>0.584</v>
@@ -9548,7 +9548,7 @@
         <v>5.4308</v>
       </c>
       <c r="AA54" t="n">
-        <v>-1.0246</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
         <v>0.584</v>
@@ -9645,7 +9645,7 @@
         <v>5.0829</v>
       </c>
       <c r="AA55" t="n">
-        <v>-1.6327</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
         <v>0.4235</v>
@@ -9742,7 +9742,7 @@
         <v>4.0792</v>
       </c>
       <c r="AA56" t="n">
-        <v>-2.2358</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
         <v>0.4235</v>
@@ -9839,7 +9839,7 @@
         <v>3.4376</v>
       </c>
       <c r="AA57" t="n">
-        <v>-2.4341</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
         <v>0.4235</v>
@@ -9936,7 +9936,7 @@
         <v>3.3332</v>
       </c>
       <c r="AA58" t="n">
-        <v>-2.3327</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0.1783</v>
@@ -10033,7 +10033,7 @@
         <v>2.3908</v>
       </c>
       <c r="AA59" t="n">
-        <v>-2.2358</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
         <v>0.1783</v>
@@ -10130,7 +10130,7 @@
         <v>1.6949</v>
       </c>
       <c r="AA60" t="n">
-        <v>-1.6393</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
         <v>0.1783</v>
@@ -10227,7 +10227,7 @@
         <v>1.0316</v>
       </c>
       <c r="AA61" t="n">
-        <v>-1.3374</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
         <v>0.2701</v>
@@ -10324,7 +10324,7 @@
         <v>0.8781</v>
       </c>
       <c r="AA62" t="n">
-        <v>-1.0352</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
         <v>0.2701</v>
@@ -10421,7 +10421,7 @@
         <v>0.5513</v>
       </c>
       <c r="AA63" t="n">
-        <v>-0.9326</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
         <v>0.2701</v>
@@ -10518,7 +10518,7 @@
         <v>-0.6452</v>
       </c>
       <c r="AA64" t="n">
-        <v>-1.0331</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
         <v>0.2948</v>
@@ -10615,7 +10615,7 @@
         <v>-1.0417</v>
       </c>
       <c r="AA65" t="n">
-        <v>-1.1364</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
         <v>0.2948</v>
@@ -10712,7 +10712,7 @@
         <v>-1.262</v>
       </c>
       <c r="AA66" t="n">
-        <v>-0.9317</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
         <v>0.2948</v>
@@ -10809,7 +10809,7 @@
         <v>-2.0555</v>
       </c>
       <c r="AA67" t="n">
-        <v>-0.9336</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
         <v>0.3485</v>
@@ -10906,7 +10906,7 @@
         <v>-1.8571</v>
       </c>
       <c r="AA68" t="n">
-        <v>-1.1435</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
         <v>0.3485</v>
@@ -11003,7 +11003,7 @@
         <v>-1.7145</v>
       </c>
       <c r="AA69" t="n">
-        <v>-1.1435</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
         <v>0.3485</v>
@@ -11100,7 +11100,7 @@
         <v>-1.4931</v>
       </c>
       <c r="AA70" t="n">
-        <v>-1.2461</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
         <v>0.3674</v>
@@ -11197,7 +11197,7 @@
         <v>-1.2044</v>
       </c>
       <c r="AA71" t="n">
-        <v>-0.8316</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
         <v>0.3674</v>
@@ -11294,7 +11294,7 @@
         <v>-1.5248</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.8333</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
         <v>0.3674</v>
@@ -11391,7 +11391,7 @@
         <v>-1.308</v>
       </c>
       <c r="AA73" t="n">
-        <v>-0.7299</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
         <v>0.4</v>
@@ -11488,7 +11488,7 @@
         <v>-1.2375</v>
       </c>
       <c r="AA74" t="n">
-        <v>-0.8368</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
         <v>0.4</v>
@@ -11585,7 +11585,7 @@
         <v>-1.2782</v>
       </c>
       <c r="AA75" t="n">
-        <v>-0.8368</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
         <v>0.4</v>
@@ -11682,7 +11682,7 @@
         <v>-1.212</v>
       </c>
       <c r="AA76" t="n">
-        <v>-0.6263</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
         <v>0.4988</v>
@@ -11779,7 +11779,7 @@
         <v>-0.6959</v>
       </c>
       <c r="AA77" t="n">
-        <v>-0.3135</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
         <v>0.4988</v>
@@ -11876,7 +11876,7 @@
         <v>-0.7255</v>
       </c>
       <c r="AA78" t="n">
-        <v>-0.209</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
         <v>0.4988</v>
@@ -11973,7 +11973,7 @@
         <v>-0.4731</v>
       </c>
       <c r="AA79" t="n">
-        <v>-0.2094</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
         <v>0.4974</v>
@@ -12070,7 +12070,7 @@
         <v>-0.72</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.1052</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
         <v>0.4974</v>
@@ -12167,7 +12167,7 @@
         <v>-0.8241000000000001</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.2103</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
         <v>0.4974</v>
@@ -12264,7 +12264,7 @@
         <v>0.0542</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.2103</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
         <v>0.5896</v>
@@ -12361,7 +12361,7 @@
         <v>-0.3324</v>
       </c>
       <c r="AA83" t="n">
-        <v>-0.1048</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
         <v>0.5896</v>
@@ -12458,7 +12458,7 @@
         <v>-0.3609</v>
       </c>
       <c r="AA84" t="n">
-        <v>-0.2101</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
         <v>0.5896</v>
@@ -12555,7 +12555,7 @@
         <v>-0.2449</v>
       </c>
       <c r="AA85" t="n">
-        <v>-0.105</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
         <v>0.6029</v>
@@ -12749,7 +12749,7 @@
         <v>0.4438</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.1055</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
         <v>0.6029</v>
@@ -12846,7 +12846,7 @@
         <v>0.6946</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.2101</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
         <v>0.6332</v>
@@ -12943,7 +12943,7 @@
         <v>0.0603</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.2096</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
         <v>0.6332</v>
@@ -13040,7 +13040,7 @@
         <v>0.7246</v>
       </c>
       <c r="AA90" t="n">
-        <v>-0.1047</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
         <v>0.6332</v>
@@ -13137,7 +13137,7 @@
         <v>0.8227</v>
       </c>
       <c r="AA91" t="n">
-        <v>-0.2099</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
         <v>0.7039</v>
@@ -13234,7 +13234,7 @@
         <v>0.7957</v>
       </c>
       <c r="AA92" t="n">
-        <v>-0.3151</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
         <v>0.7039</v>
@@ -13331,7 +13331,7 @@
         <v>1.1156</v>
       </c>
       <c r="AA93" t="n">
-        <v>-0.2099</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
         <v>0.7039</v>
@@ -13719,7 +13719,7 @@
         <v>1.4989</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.7361</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
         <v>0.6928</v>
@@ -13816,7 +13816,7 @@
         <v>1.0699</v>
       </c>
       <c r="AA98" t="n">
-        <v>-0.3165</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
         <v>0.6928</v>
@@ -13913,7 +13913,7 @@
         <v>1.833</v>
       </c>
       <c r="AA99" t="n">
-        <v>-0.3161</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
         <v>0.6928</v>
@@ -14010,7 +14010,7 @@
         <v>1.5392</v>
       </c>
       <c r="AA100" t="n">
-        <v>-0.5241</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
         <v>0.6798</v>
@@ -14107,7 +14107,7 @@
         <v>1.5944</v>
       </c>
       <c r="AA101" t="n">
-        <v>-0.4184</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
         <v>0.6798</v>
@@ -14301,7 +14301,7 @@
         <v>1.8746</v>
       </c>
       <c r="AA103" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
         <v>0.6641</v>
@@ -14398,7 +14398,7 @@
         <v>2.3008</v>
       </c>
       <c r="AA104" t="n">
-        <v>0.6322</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
         <v>0.6641</v>
@@ -14495,7 +14495,7 @@
         <v>2.4073</v>
       </c>
       <c r="AA105" t="n">
-        <v>0.7361</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
         <v>0.6641</v>
@@ -14592,7 +14592,7 @@
         <v>1.9042</v>
       </c>
       <c r="AA106" t="n">
-        <v>0.6296</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
         <v>0.6577</v>
@@ -14689,7 +14689,7 @@
         <v>2.1355</v>
       </c>
       <c r="AA107" t="n">
-        <v>0.8395</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
         <v>0.6577</v>
@@ -14786,7 +14786,7 @@
         <v>2.312</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.1579</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
         <v>0.6577</v>
@@ -14883,7 +14883,7 @@
         <v>2.1546</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.8184</v>
+        <v>2.9221</v>
       </c>
       <c r="AB109" t="n">
         <v>0.6385999999999999</v>
@@ -14980,7 +14980,7 @@
         <v>2.2887</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.3757</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
         <v>0.6385999999999999</v>
@@ -15077,7 +15077,7 @@
         <v>2.2999</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.3742</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
         <v>0.6385999999999999</v>
@@ -15174,7 +15174,7 @@
         <v>2.3079</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.3699</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
         <v>0.5942</v>
@@ -15271,7 +15271,7 @@
         <v>2.3606</v>
       </c>
       <c r="AA113" t="n">
-        <v>3.2563</v>
+        <v>2.9221</v>
       </c>
       <c r="AB113" t="n">
         <v>0.5942</v>
@@ -15368,7 +15368,7 @@
         <v>2.7128</v>
       </c>
       <c r="AA114" t="n">
-        <v>3.3543</v>
+        <v>2.9221</v>
       </c>
       <c r="AB114" t="n">
         <v>0.5942</v>
@@ -15465,7 +15465,7 @@
         <v>2.5347</v>
       </c>
       <c r="AA115" t="n">
-        <v>3.3543</v>
+        <v>2.9221</v>
       </c>
       <c r="AB115" t="n">
         <v>0.5928</v>
@@ -15562,7 +15562,7 @@
         <v>3.2265</v>
       </c>
       <c r="AA116" t="n">
-        <v>3.3508</v>
+        <v>2.9221</v>
       </c>
       <c r="AB116" t="n">
         <v>0.5928</v>
@@ -15659,7 +15659,7 @@
         <v>3.1712</v>
       </c>
       <c r="AA117" t="n">
-        <v>3.1315</v>
+        <v>2.9221</v>
       </c>
       <c r="AB117" t="n">
         <v>0.5928</v>
@@ -15756,7 +15756,7 @@
         <v>2.7064</v>
       </c>
       <c r="AA118" t="n">
-        <v>3.024</v>
+        <v>2.9221</v>
       </c>
       <c r="AB118" t="n">
         <v>0.5985</v>
@@ -15853,7 +15853,7 @@
         <v>3.3567</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.9136</v>
+        <v>2.9221</v>
       </c>
       <c r="AB119" t="n">
         <v>0.5985</v>
@@ -15950,7 +15950,7 @@
         <v>3.3969</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.6015</v>
+        <v>2.9221</v>
       </c>
       <c r="AB120" t="n">
         <v>0.5985</v>
@@ -16144,7 +16144,7 @@
         <v>2.9619</v>
       </c>
       <c r="AA122" t="n">
-        <v>2.2965</v>
+        <v>2.9221</v>
       </c>
       <c r="AB122" t="n">
         <v>0.5954</v>
@@ -16241,7 +16241,7 @@
         <v>3.3711</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.0855</v>
+        <v>2.9221</v>
       </c>
       <c r="AB123" t="n">
         <v>0.5954</v>
@@ -16338,7 +16338,7 @@
         <v>3.8472</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.183</v>
+        <v>2.9221</v>
       </c>
       <c r="AB124" t="n">
         <v>0.5616</v>
@@ -16435,7 +16435,7 @@
         <v>3.3063</v>
       </c>
       <c r="AA125" t="n">
-        <v>0.4069</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
         <v>0.5616</v>
@@ -16532,7 +16532,7 @@
         <v>3.9174</v>
       </c>
       <c r="AA126" t="n">
-        <v>0.2028</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
         <v>0.5616</v>
@@ -16629,7 +16629,7 @@
         <v>3.7774</v>
       </c>
       <c r="AA127" t="n">
-        <v>0.1014</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
         <v>0.578</v>
@@ -16726,7 +16726,7 @@
         <v>4.0897</v>
       </c>
       <c r="AA128" t="n">
-        <v>-0.1013</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
         <v>0.578</v>
@@ -16823,7 +16823,7 @@
         <v>3.6481</v>
       </c>
       <c r="AA129" t="n">
-        <v>-0.2024</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
         <v>0.578</v>
@@ -16920,7 +16920,7 @@
         <v>3.8803</v>
       </c>
       <c r="AA130" t="n">
-        <v>-0.2024</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
         <v>0.5145999999999999</v>
@@ -17017,7 +17017,7 @@
         <v>3.6087</v>
       </c>
       <c r="AA131" t="n">
-        <v>-0.3033</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
         <v>0.5145999999999999</v>
@@ -17502,7 +17502,7 @@
         <v>4.0178</v>
       </c>
       <c r="AA136" t="n">
-        <v>-0.3052</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
         <v>0.5258</v>
@@ -17599,7 +17599,7 @@
         <v>4.314</v>
       </c>
       <c r="AA137" t="n">
-        <v>-0.4053</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
         <v>0.5258</v>
@@ -17696,7 +17696,7 @@
         <v>4.5253</v>
       </c>
       <c r="AA138" t="n">
-        <v>-0.4049</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
         <v>0.5258</v>
@@ -17793,7 +17793,7 @@
         <v>4.7573</v>
       </c>
       <c r="AA139" t="n">
-        <v>-0.4053</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
         <v>0.5296</v>
@@ -17890,7 +17890,7 @@
         <v>4.3998</v>
       </c>
       <c r="AA140" t="n">
-        <v>-0.5071</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
         <v>0.5296</v>
@@ -17987,7 +17987,7 @@
         <v>4.4364</v>
       </c>
       <c r="AA141" t="n">
-        <v>-0.5071</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
         <v>0.5296</v>
@@ -18084,7 +18084,7 @@
         <v>4.8974</v>
       </c>
       <c r="AA142" t="n">
-        <v>-0.5071</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
         <v>0.5544</v>
@@ -18181,7 +18181,7 @@
         <v>5.3294</v>
       </c>
       <c r="AA143" t="n">
-        <v>-0.3043</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
         <v>0.5544</v>
@@ -18278,7 +18278,7 @@
         <v>5.286</v>
       </c>
       <c r="AA144" t="n">
-        <v>-0.3043</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
         <v>0.5544</v>
@@ -18375,7 +18375,7 @@
         <v>5.7946</v>
       </c>
       <c r="AA145" t="n">
-        <v>0.4061</v>
+        <v>0.5258</v>
       </c>
       <c r="AB145" t="n">
         <v>0.554</v>
@@ -18472,7 +18472,7 @@
         <v>5.7936</v>
       </c>
       <c r="AA146" t="n">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
         <v>0.554</v>
@@ -18569,7 +18569,7 @@
         <v>6.0966</v>
       </c>
       <c r="AA147" t="n">
-        <v>0.2043</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
         <v>0.554</v>
@@ -18666,7 +18666,7 @@
         <v>5.5157</v>
       </c>
       <c r="AA148" t="n">
-        <v>0.3061</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
         <v>0.5637</v>
@@ -18763,7 +18763,7 @@
         <v>6.4179</v>
       </c>
       <c r="AA149" t="n">
-        <v>0.3052</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
         <v>0.5637</v>
@@ -18860,7 +18860,7 @@
         <v>6.164</v>
       </c>
       <c r="AA150" t="n">
-        <v>0.4065</v>
+        <v>0</v>
       </c>
       <c r="AB150" t="n">
         <v>0.5637</v>
@@ -18957,7 +18957,7 @@
         <v>6.2628</v>
       </c>
       <c r="AA151" t="n">
-        <v>0.4069</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
         <v>0.605</v>
@@ -19054,7 +19054,7 @@
         <v>6.8027</v>
       </c>
       <c r="AA152" t="n">
-        <v>0.5097</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
         <v>0.605</v>
@@ -19151,7 +19151,7 @@
         <v>6.4641</v>
       </c>
       <c r="AA153" t="n">
-        <v>0.7136</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
         <v>0.605</v>
@@ -19248,7 +19248,7 @@
         <v>6.8497</v>
       </c>
       <c r="AA154" t="n">
-        <v>0.7136</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
         <v>0.6524</v>
@@ -19345,7 +19345,7 @@
         <v>7.0352</v>
       </c>
       <c r="AA155" t="n">
-        <v>0.8138</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
         <v>0.6524</v>
@@ -19442,7 +19442,7 @@
         <v>6.8779</v>
       </c>
       <c r="AA156" t="n">
-        <v>0.9156</v>
+        <v>1.2618</v>
       </c>
       <c r="AB156" t="n">
         <v>0.6524</v>
@@ -19539,7 +19539,7 @@
         <v>6.953</v>
       </c>
       <c r="AA157" t="n">
-        <v>0.8089</v>
+        <v>1.6736</v>
       </c>
       <c r="AB157" t="n">
         <v>0.6642</v>
@@ -19636,7 +19636,7 @@
         <v>7.644</v>
       </c>
       <c r="AA158" t="n">
-        <v>0.8155</v>
+        <v>1.2618</v>
       </c>
       <c r="AB158" t="n">
         <v>0.6642</v>
@@ -19733,7 +19733,7 @@
         <v>7.363</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.0194</v>
+        <v>1.2618</v>
       </c>
       <c r="AB159" t="n">
         <v>0.6642</v>
@@ -19830,7 +19830,7 @@
         <v>7.954</v>
       </c>
       <c r="AA160" t="n">
-        <v>0.8138</v>
+        <v>1.2618</v>
       </c>
       <c r="AB160" t="n">
         <v>0.6751</v>
@@ -19927,7 +19927,7 @@
         <v>7.8409</v>
       </c>
       <c r="AA161" t="n">
-        <v>0.7099</v>
+        <v>1.2618</v>
       </c>
       <c r="AB161" t="n">
         <v>0.6751</v>
@@ -20024,7 +20024,7 @@
         <v>8.063599999999999</v>
       </c>
       <c r="AA162" t="n">
-        <v>0.7085</v>
+        <v>1.2618</v>
       </c>
       <c r="AB162" t="n">
         <v>0.6751</v>
@@ -20121,7 +20121,7 @@
         <v>8.4268</v>
       </c>
       <c r="AA163" t="n">
-        <v>0.8105</v>
+        <v>1.2618</v>
       </c>
       <c r="AB163" t="n">
         <v>0.6768999999999999</v>
@@ -20218,7 +20218,7 @@
         <v>8.6327</v>
       </c>
       <c r="AA164" t="n">
-        <v>0.8114</v>
+        <v>1.2618</v>
       </c>
       <c r="AB164" t="n">
         <v>0.6768999999999999</v>
@@ -20315,7 +20315,7 @@
         <v>8.831200000000001</v>
       </c>
       <c r="AA165" t="n">
-        <v>0.9109</v>
+        <v>1.2618</v>
       </c>
       <c r="AB165" t="n">
         <v>0.6768999999999999</v>
@@ -20412,7 +20412,7 @@
         <v>8.680400000000001</v>
       </c>
       <c r="AA166" t="n">
-        <v>0.9109</v>
+        <v>1.2618</v>
       </c>
       <c r="AB166" t="n">
         <v>0.7045</v>
@@ -20509,7 +20509,7 @@
         <v>8.8995</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.0091</v>
+        <v>1.2618</v>
       </c>
       <c r="AB167" t="n">
         <v>0.7045</v>
@@ -20606,7 +20606,7 @@
         <v>9.211600000000001</v>
       </c>
       <c r="AA168" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="AB168" t="n">
         <v>0.7045</v>
@@ -20703,7 +20703,7 @@
         <v>8.890700000000001</v>
       </c>
       <c r="AA169" t="n">
-        <v>0.6018</v>
+        <v>2.8807</v>
       </c>
       <c r="AB169" t="n">
         <v>0.7396</v>
@@ -20800,7 +20800,7 @@
         <v>9.510899999999999</v>
       </c>
       <c r="AA170" t="n">
-        <v>0.8089</v>
+        <v>3.8422</v>
       </c>
       <c r="AB170" t="n">
         <v>0.7396</v>
@@ -20897,7 +20897,7 @@
         <v>9.397500000000001</v>
       </c>
       <c r="AA171" t="n">
-        <v>0.7064</v>
+        <v>3.8422</v>
       </c>
       <c r="AB171" t="n">
         <v>0.7396</v>
@@ -20994,7 +20994,7 @@
         <v>9.9002</v>
       </c>
       <c r="AA172" t="n">
-        <v>0.8073</v>
+        <v>3.8422</v>
       </c>
       <c r="AB172" t="n">
         <v>0.7796999999999999</v>
@@ -21091,7 +21091,7 @@
         <v>9.5806</v>
       </c>
       <c r="AA173" t="n">
-        <v>0.9063</v>
+        <v>3.8422</v>
       </c>
       <c r="AB173" t="n">
         <v>0.7796999999999999</v>
@@ -21188,7 +21188,7 @@
         <v>10.0354</v>
       </c>
       <c r="AA174" t="n">
-        <v>0.7035</v>
+        <v>3.8422</v>
       </c>
       <c r="AB174" t="n">
         <v>0.7796999999999999</v>
@@ -21285,7 +21285,7 @@
         <v>10.3961</v>
       </c>
       <c r="AA175" t="n">
-        <v>0.603</v>
+        <v>3.8422</v>
       </c>
       <c r="AB175" t="n">
         <v>0.7991</v>
@@ -21382,7 +21382,7 @@
         <v>10.6124</v>
       </c>
       <c r="AA176" t="n">
-        <v>0.6036</v>
+        <v>3.8422</v>
       </c>
       <c r="AB176" t="n">
         <v>0.7991</v>
@@ -21479,7 +21479,7 @@
         <v>10.6257</v>
       </c>
       <c r="AA177" t="n">
-        <v>0.5014999999999999</v>
+        <v>3.8422</v>
       </c>
       <c r="AB177" t="n">
         <v>0.7991</v>
@@ -21576,7 +21576,7 @@
         <v>10.7821</v>
       </c>
       <c r="AA178" t="n">
-        <v>0.4012</v>
+        <v>3.8422</v>
       </c>
       <c r="AB178" t="n">
         <v>0.6589</v>
@@ -21673,7 +21673,7 @@
         <v>10.9602</v>
       </c>
       <c r="AA179" t="n">
-        <v>0.3996</v>
+        <v>3.8422</v>
       </c>
       <c r="AB179" t="n">
         <v>0.6589</v>
@@ -21770,7 +21770,7 @@
         <v>10.6116</v>
       </c>
       <c r="AA180" t="n">
-        <v>0.4995</v>
+        <v>3.8422</v>
       </c>
       <c r="AB180" t="n">
         <v>0.6589</v>
@@ -21867,7 +21867,7 @@
         <v>10.7514</v>
       </c>
       <c r="AA181" t="n">
-        <v>0.2991</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
         <v>0.4732</v>
@@ -21964,7 +21964,7 @@
         <v>10.8966</v>
       </c>
       <c r="AA182" t="n">
-        <v>0.8024</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
         <v>0.4732</v>
@@ -22061,7 +22061,7 @@
         <v>11.771</v>
       </c>
       <c r="AA183" t="n">
-        <v>0.6012</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
         <v>0.4732</v>
@@ -22158,7 +22158,7 @@
         <v>11.2146</v>
       </c>
       <c r="AA184" t="n">
-        <v>0.6006</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
         <v>0.3311</v>
@@ -22255,7 +22255,7 @@
         <v>11.2935</v>
       </c>
       <c r="AA185" t="n">
-        <v>-0.0998</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
         <v>0.3311</v>
@@ -22352,7 +22352,7 @@
         <v>11.4924</v>
       </c>
       <c r="AA186" t="n">
-        <v>-0.0998</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
         <v>0.3311</v>
@@ -22449,7 +22449,7 @@
         <v>11.7274</v>
       </c>
       <c r="AA187" t="n">
-        <v>-0.0999</v>
+        <v>0</v>
       </c>
       <c r="AB187" t="n">
         <v>0.2213</v>
@@ -22643,7 +22643,7 @@
         <v>10.1115</v>
       </c>
       <c r="AA189" t="n">
-        <v>-0.3992</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
         <v>0.2213</v>
@@ -22740,7 +22740,7 @@
         <v>9.764200000000001</v>
       </c>
       <c r="AA190" t="n">
-        <v>-0.3996</v>
+        <v>0</v>
       </c>
       <c r="AB190" t="n">
         <v>0.08</v>
@@ -22837,7 +22837,7 @@
         <v>9.0296</v>
       </c>
       <c r="AA191" t="n">
-        <v>-0.796</v>
+        <v>0</v>
       </c>
       <c r="AB191" t="n">
         <v>0.08</v>
@@ -22934,7 +22934,7 @@
         <v>8.3215</v>
       </c>
       <c r="AA192" t="n">
-        <v>-0.994</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="n">
         <v>0.08</v>
@@ -23031,7 +23031,7 @@
         <v>7.6248</v>
       </c>
       <c r="AA193" t="n">
-        <v>-0.6958</v>
+        <v>3.3</v>
       </c>
       <c r="AB193" t="n">
         <v>0.08459999999999999</v>
@@ -23128,7 +23128,7 @@
         <v>6.4632</v>
       </c>
       <c r="AA194" t="n">
-        <v>-0.6965</v>
+        <v>0</v>
       </c>
       <c r="AB194" t="n">
         <v>0.08459999999999999</v>
@@ -23225,7 +23225,7 @@
         <v>6.0074</v>
       </c>
       <c r="AA195" t="n">
-        <v>-0.498</v>
+        <v>0</v>
       </c>
       <c r="AB195" t="n">
         <v>0.08459999999999999</v>
@@ -23322,7 +23322,7 @@
         <v>4.9477</v>
       </c>
       <c r="AA196" t="n">
-        <v>-0.398</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
         <v>0.1371</v>
@@ -23419,7 +23419,7 @@
         <v>4.5654</v>
       </c>
       <c r="AA197" t="n">
-        <v>-0.7992</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
         <v>0.1371</v>
@@ -23516,7 +23516,7 @@
         <v>3.7805</v>
       </c>
       <c r="AA198" t="n">
-        <v>-0.5994</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
         <v>0.1371</v>
@@ -23613,7 +23613,7 @@
         <v>2.8489</v>
       </c>
       <c r="AA199" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AB199" t="n">
         <v>0.2511</v>
@@ -23710,7 +23710,7 @@
         <v>3.0793</v>
       </c>
       <c r="AA200" t="n">
-        <v>-0.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB200" t="n">
         <v>0.2511</v>
@@ -23807,7 +23807,7 @@
         <v>3.0013</v>
       </c>
       <c r="AA201" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB201" t="n">
         <v>0.2511</v>
@@ -23904,7 +23904,7 @@
         <v>3.65</v>
       </c>
       <c r="AA202" t="n">
-        <v>0.1003</v>
+        <v>4.3</v>
       </c>
       <c r="AB202" t="n">
         <v>0.3019</v>
@@ -24001,7 +24001,7 @@
         <v>3.2718</v>
       </c>
       <c r="AA203" t="n">
-        <v>0.2006</v>
+        <v>4.3</v>
       </c>
       <c r="AB203" t="n">
         <v>0.3019</v>
@@ -24098,7 +24098,7 @@
         <v>3.372</v>
       </c>
       <c r="AA204" t="n">
-        <v>0.502</v>
+        <v>4.3</v>
       </c>
       <c r="AB204" t="n">
         <v>0.3019</v>
@@ -24195,7 +24195,7 @@
         <v>3.2568</v>
       </c>
       <c r="AA205" t="n">
-        <v>3.1031</v>
+        <v>0.9681</v>
       </c>
       <c r="AB205" t="n">
         <v>0.3322</v>
@@ -24292,7 +24292,7 @@
         <v>3.977</v>
       </c>
       <c r="AA206" t="n">
-        <v>0.3006</v>
+        <v>4.3</v>
       </c>
       <c r="AB206" t="n">
         <v>0.3322</v>
@@ -24389,7 +24389,7 @@
         <v>3.9906</v>
       </c>
       <c r="AA207" t="n">
-        <v>0.6006</v>
+        <v>4.3</v>
       </c>
       <c r="AB207" t="n">
         <v>0.3322</v>
@@ -24486,7 +24486,7 @@
         <v>4.0512</v>
       </c>
       <c r="AA208" t="n">
-        <v>0.7992</v>
+        <v>4.3</v>
       </c>
       <c r="AB208" t="n">
         <v>0.3687</v>
@@ -24583,7 +24583,7 @@
         <v>4.1731</v>
       </c>
       <c r="AA209" t="n">
-        <v>2.1148</v>
+        <v>4.3</v>
       </c>
       <c r="AB209" t="n">
         <v>0.3687</v>
@@ -24680,7 +24680,7 @@
         <v>4.2301</v>
       </c>
       <c r="AA210" t="n">
-        <v>2.1106</v>
+        <v>4.3</v>
       </c>
       <c r="AB210" t="n">
         <v>0.3687</v>
@@ -24777,7 +24777,7 @@
         <v>4.3464</v>
       </c>
       <c r="AA211" t="n">
-        <v>2.2111</v>
+        <v>4.3</v>
       </c>
       <c r="AB211" t="n">
         <v>0.4269</v>
@@ -24874,7 +24874,7 @@
         <v>4.1646</v>
       </c>
       <c r="AA212" t="n">
-        <v>2.4048</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
         <v>0.4269</v>
@@ -24971,7 +24971,7 @@
         <v>3.94</v>
       </c>
       <c r="AA213" t="n">
-        <v>2.7054</v>
+        <v>0</v>
       </c>
       <c r="AB213" t="n">
         <v>0.4269</v>
@@ -25068,7 +25068,7 @@
         <v>4.6217</v>
       </c>
       <c r="AA214" t="n">
-        <v>3.1062</v>
+        <v>0</v>
       </c>
       <c r="AB214" t="n">
         <v>0.4919</v>
@@ -25165,7 +25165,7 @@
         <v>4.4971</v>
       </c>
       <c r="AA215" t="n">
-        <v>3.5035</v>
+        <v>0</v>
       </c>
       <c r="AB215" t="n">
         <v>0.4919</v>
@@ -25262,7 +25262,7 @@
         <v>4.0841</v>
       </c>
       <c r="AA216" t="n">
-        <v>3.6963</v>
+        <v>0</v>
       </c>
       <c r="AB216" t="n">
         <v>0.4919</v>
@@ -25359,7 +25359,7 @@
         <v>4.858</v>
       </c>
       <c r="AA217" t="n">
-        <v>2.8155</v>
+        <v>7.1908</v>
       </c>
       <c r="AB217" t="n">
         <v>0.4908</v>
@@ -25456,7 +25456,7 @@
         <v>4.3604</v>
       </c>
       <c r="AA218" t="n">
-        <v>4.1958</v>
+        <v>0</v>
       </c>
       <c r="AB218" t="n">
         <v>0.4908</v>
@@ -25553,7 +25553,7 @@
         <v>4.9338</v>
       </c>
       <c r="AA219" t="n">
-        <v>3.0846</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
         <v>0.4908</v>
@@ -25650,7 +25650,7 @@
         <v>4.867</v>
       </c>
       <c r="AA220" t="n">
-        <v>3.1715</v>
+        <v>0</v>
       </c>
       <c r="AB220" t="n">
         <v>0.4919</v>
@@ -25747,7 +25747,7 @@
         <v>5.1416</v>
       </c>
       <c r="AA221" t="n">
-        <v>3.3531</v>
+        <v>0</v>
       </c>
       <c r="AB221" t="n">
         <v>0.4919</v>
@@ -25844,7 +25844,7 @@
         <v>4.643</v>
       </c>
       <c r="AA222" t="n">
-        <v>3.1496</v>
+        <v>4.0268</v>
       </c>
       <c r="AB222" t="n">
         <v>0.4919</v>
@@ -25941,7 +25941,7 @@
         <v>4.8152</v>
       </c>
       <c r="AA223" t="n">
-        <v>3.2448</v>
+        <v>6.1361</v>
       </c>
       <c r="AB223" t="n">
         <v>0.5234</v>
@@ -26038,7 +26038,7 @@
         <v>5.2503</v>
       </c>
       <c r="AA224" t="n">
-        <v>3.1311</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB224" t="n">
         <v>0.5234</v>
@@ -26135,7 +26135,7 @@
         <v>5.0888</v>
       </c>
       <c r="AA225" t="n">
-        <v>3.122</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB225" t="n">
         <v>0.5234</v>
@@ -26232,7 +26232,7 @@
         <v>4.8444</v>
       </c>
       <c r="AA226" t="n">
-        <v>2.7211</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB226" t="n">
         <v>0.5189</v>
@@ -26329,7 +26329,7 @@
         <v>5.0473</v>
       </c>
       <c r="AA227" t="n">
-        <v>2.9014</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB227" t="n">
         <v>0.5189</v>
@@ -26426,7 +26426,7 @@
         <v>5.0914</v>
       </c>
       <c r="AA228" t="n">
-        <v>2.5048</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB228" t="n">
         <v>0.5189</v>
@@ -26523,7 +26523,7 @@
         <v>5.0369</v>
       </c>
       <c r="AA229" t="n">
-        <v>2.644</v>
+        <v>2.2361</v>
       </c>
       <c r="AB229" t="n">
         <v>0.5456</v>
@@ -26620,7 +26620,7 @@
         <v>5.6388</v>
       </c>
       <c r="AA230" t="n">
-        <v>2.0134</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB230" t="n">
         <v>0.5456</v>
@@ -26717,7 +26717,7 @@
         <v>5.5714</v>
       </c>
       <c r="AA231" t="n">
-        <v>2.7992</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB231" t="n">
         <v>0.5456</v>
@@ -26814,7 +26814,7 @@
         <v>5.9533</v>
       </c>
       <c r="AA232" t="n">
-        <v>2.5937</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB232" t="n">
         <v>0.5908</v>
@@ -26911,7 +26911,7 @@
         <v>5.5307</v>
       </c>
       <c r="AA233" t="n">
-        <v>2.1947</v>
+        <v>8.437200000000001</v>
       </c>
       <c r="AB233" t="n">
         <v>0.5908</v>
@@ -27008,7 +27008,7 @@
         <v>5.8388</v>
       </c>
       <c r="AA234" t="n">
-        <v>2.5763</v>
+        <v>4.2396</v>
       </c>
       <c r="AB234" t="n">
         <v>0.5908</v>
@@ -27105,7 +27105,7 @@
         <v>5.9071</v>
       </c>
       <c r="AA235" t="n">
-        <v>2.6667</v>
+        <v>2.168</v>
       </c>
       <c r="AB235" t="n">
         <v>0.6291</v>
@@ -27202,7 +27202,7 @@
         <v>5.9006</v>
       </c>
       <c r="AA236" t="n">
-        <v>2.7514</v>
+        <v>0</v>
       </c>
       <c r="AB236" t="n">
         <v>0.6291</v>
@@ -27299,7 +27299,7 @@
         <v>5.8624</v>
       </c>
       <c r="AA237" t="n">
-        <v>2.8382</v>
+        <v>0</v>
       </c>
       <c r="AB237" t="n">
         <v>0.6291</v>
@@ -27396,7 +27396,7 @@
         <v>5.7622</v>
       </c>
       <c r="AA238" t="n">
-        <v>2.3652</v>
+        <v>0</v>
       </c>
       <c r="AB238" t="n">
         <v>0.631</v>
@@ -27493,7 +27493,7 @@
         <v>6.3415</v>
       </c>
       <c r="AA239" t="n">
-        <v>2.2556</v>
+        <v>0</v>
       </c>
       <c r="AB239" t="n">
         <v>0.631</v>
@@ -27590,7 +27590,7 @@
         <v>6.3011</v>
       </c>
       <c r="AA240" t="n">
-        <v>2.6316</v>
+        <v>0</v>
       </c>
       <c r="AB240" t="n">
         <v>0.631</v>
@@ -27687,7 +27687,7 @@
         <v>6.3746</v>
       </c>
       <c r="AA241" t="n">
-        <v>2.7599</v>
+        <v>3.1496</v>
       </c>
       <c r="AB241" t="n">
         <v>0.6032999999999999</v>
@@ -27784,7 +27784,7 @@
         <v>6.0521</v>
       </c>
       <c r="AA242" t="n">
-        <v>3.1955</v>
+        <v>4.244</v>
       </c>
       <c r="AB242" t="n">
         <v>0.6032999999999999</v>
@@ -27881,7 +27881,7 @@
         <v>6.0744</v>
       </c>
       <c r="AA243" t="n">
-        <v>3.0047</v>
+        <v>4.244</v>
       </c>
       <c r="AB243" t="n">
         <v>0.6032999999999999</v>
@@ -27978,7 +27978,7 @@
         <v>6.5983</v>
       </c>
       <c r="AA244" t="n">
-        <v>3.1835</v>
+        <v>4.244</v>
       </c>
       <c r="AB244" t="n">
         <v>0.6354</v>
@@ -28075,7 +28075,7 @@
         <v>5.9781</v>
       </c>
       <c r="AA245" t="n">
-        <v>3.5481</v>
+        <v>4.244</v>
       </c>
       <c r="AB245" t="n">
         <v>0.6354</v>
@@ -28172,7 +28172,7 @@
         <v>6.556</v>
       </c>
       <c r="AA246" t="n">
-        <v>3.6279</v>
+        <v>4.244</v>
       </c>
       <c r="AB246" t="n">
         <v>0.6354</v>
@@ -28269,7 +28269,7 @@
         <v>6.5037</v>
       </c>
       <c r="AA247" t="n">
-        <v>3.3395</v>
+        <v>4.244</v>
       </c>
       <c r="AB247" t="n">
         <v>0.6381</v>
@@ -28366,7 +28366,7 @@
         <v>6.6021</v>
       </c>
       <c r="AA248" t="n">
-        <v>3.0471</v>
+        <v>4.244</v>
       </c>
       <c r="AB248" t="n">
         <v>0.6381</v>
@@ -28463,7 +28463,7 @@
         <v>6.6087</v>
       </c>
       <c r="AA249" t="n">
-        <v>2.6679</v>
+        <v>4.244</v>
       </c>
       <c r="AB249" t="n">
         <v>0.6381</v>
@@ -28560,7 +28560,7 @@
         <v>6.267</v>
       </c>
       <c r="AA250" t="n">
-        <v>2.9575</v>
+        <v>4.244</v>
       </c>
       <c r="AB250" t="n">
         <v>0.6496</v>
@@ -28657,7 +28657,7 @@
         <v>6.2221</v>
       </c>
       <c r="AA251" t="n">
-        <v>3.0331</v>
+        <v>4.244</v>
       </c>
       <c r="AB251" t="n">
         <v>0.6496</v>
@@ -28754,7 +28754,7 @@
         <v>6.4983</v>
       </c>
       <c r="AA252" t="n">
-        <v>3.022</v>
+        <v>4.244</v>
       </c>
       <c r="AB252" t="n">
         <v>0.6496</v>
@@ -28851,7 +28851,7 @@
         <v>6.2486</v>
       </c>
       <c r="AA253" t="n">
-        <v>0.4476</v>
+        <v>0</v>
       </c>
       <c r="AB253" t="n">
         <v>0.7155</v>
@@ -28948,7 +28948,7 @@
         <v>6.0818</v>
       </c>
       <c r="AA254" t="n">
-        <v>2.0036</v>
+        <v>0</v>
       </c>
       <c r="AB254" t="n">
         <v>0.7155</v>
@@ -29045,7 +29045,7 @@
         <v>6.2818</v>
       </c>
       <c r="AA255" t="n">
-        <v>1.5497</v>
+        <v>0</v>
       </c>
       <c r="AB255" t="n">
         <v>0.7155</v>
@@ -29142,7 +29142,7 @@
         <v>6.3162</v>
       </c>
       <c r="AA256" t="n">
-        <v>1.7241</v>
+        <v>0</v>
       </c>
       <c r="AB256" t="n">
         <v>0.6982</v>
@@ -29239,7 +29239,7 @@
         <v>5.8828</v>
       </c>
       <c r="AA257" t="n">
-        <v>1.4427</v>
+        <v>0</v>
       </c>
       <c r="AB257" t="n">
         <v>0.6982</v>
@@ -29336,7 +29336,7 @@
         <v>6.0576</v>
       </c>
       <c r="AA258" t="n">
-        <v>1.4363</v>
+        <v>0</v>
       </c>
       <c r="AB258" t="n">
         <v>0.6982</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -79,12 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-0.995</v>
+        <v>-0.657</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-0.975</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="4">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-0.857</v>
+        <v>-0.593</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-0.824</v>
+        <v>-0.574</v>
       </c>
     </row>
     <row r="6">
@@ -744,7 +744,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.71</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-0.803</v>
+        <v>-0.555</v>
       </c>
     </row>
     <row r="7">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-0.795</v>
+        <v>-0.5610000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-0.769</v>
+        <v>-0.541</v>
       </c>
     </row>
     <row r="9">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-0.802</v>
+        <v>-0.5629999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-0.74</v>
+        <v>-0.504</v>
       </c>
     </row>
     <row r="11">
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-0.784</v>
+        <v>-0.538</v>
       </c>
     </row>
     <row r="12">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>-0.763</v>
+        <v>-0.523</v>
       </c>
     </row>
     <row r="13">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-0.747</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="14">
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>-0.26</v>
+        <v>0.19</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Mildly restrictive</t>
+          <t>Mildly accommodative</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-0.733</v>
+        <v>-0.501</v>
       </c>
     </row>
     <row r="15">
@@ -910,10 +910,10 @@
           <t>Funding costs</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="10" t="n">
         <v>-0.89</v>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Restrictive</t>
         </is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-0.753</v>
+        <v>-0.503</v>
       </c>
     </row>
     <row r="16">
@@ -933,10 +933,10 @@
           <t>Availability of funds</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="8" t="n">
         <v>1.09</v>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Accommodative</t>
         </is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>-0.754</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="17">
@@ -956,10 +956,10 @@
           <t>Asset prices</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="8" t="n">
         <v>3.05</v>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Accommodative</t>
         </is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-0.783</v>
+        <v>-0.485</v>
       </c>
     </row>
     <row r="18">
@@ -979,10 +979,10 @@
           <t>Funding volumes</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="8" t="n">
         <v>0.55</v>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Accommodative</t>
         </is>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-0.802</v>
+        <v>-0.496</v>
       </c>
     </row>
     <row r="19">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-0.798</v>
+        <v>-0.483</v>
       </c>
     </row>
     <row r="20">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>-0.801</v>
+        <v>-0.492</v>
       </c>
     </row>
     <row r="21">
@@ -1028,11 +1028,11 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>-0.26</v>
+        <v>0.19</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Mildly restrictive</t>
+          <t>Mildly accommodative</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>-0.767</v>
+        <v>-0.479</v>
       </c>
     </row>
     <row r="22">
@@ -1050,7 +1050,7 @@
           <t>Stage 2 - Funding environment</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="8" t="n">
         <v>0.95</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-0.665</v>
+        <v>-0.412</v>
       </c>
     </row>
     <row r="23">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>-0.7</v>
+        <v>-0.432</v>
       </c>
     </row>
     <row r="24">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>-0.681</v>
+        <v>-0.405</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.71 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.83pp below the midpoint natural-rate estimate (-0.15%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.85% to +0.55%) means this read carries wide uncertainty. Note on horizon: the headline scores are z-scores against 2005-present history, a window dominated by ZIRP/NIRP, so a normalizing real rate scores as less accommodative than that norm. On longer ex-post baselines the real-rate stance is horizon-sensitive — mildly accommodative versus the full 1974+ history, broadly neutral versus 1990 — even though the level-based natural-rate read keeps the policy stance accommodative (see the horizon table).</t>
+          <t>The composite Financial Conditions Index reads +0.80 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.83pp below the midpoint natural-rate estimate (-0.15%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.85% to +0.55%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>-0.657</v>
+        <v>-0.386</v>
       </c>
     </row>
     <row r="26">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-0.63</v>
+        <v>-0.376</v>
       </c>
     </row>
     <row r="27">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>-0.647</v>
+        <v>-0.402</v>
       </c>
     </row>
     <row r="28">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-0.639</v>
+        <v>-0.392</v>
       </c>
     </row>
     <row r="29">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>-0.643</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="30">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-0.634</v>
+        <v>-0.395</v>
       </c>
     </row>
     <row r="31">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>-0.662</v>
+        <v>-0.382</v>
       </c>
     </row>
     <row r="32">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>-0.643</v>
+        <v>-0.369</v>
       </c>
     </row>
     <row r="33">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>-0.597</v>
+        <v>-0.365</v>
       </c>
     </row>
     <row r="34">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>-0.639</v>
+        <v>-0.436</v>
       </c>
     </row>
     <row r="35">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>-0.65</v>
+        <v>-0.445</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>-0.609</v>
+        <v>-0.433</v>
       </c>
     </row>
     <row r="37">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>-0.672</v>
+        <v>-0.498</v>
       </c>
     </row>
     <row r="38">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-0.65</v>
+        <v>-0.509</v>
       </c>
     </row>
     <row r="39">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>-0.631</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="40">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>-0.707</v>
+        <v>-0.587</v>
       </c>
     </row>
     <row r="41">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>-0.718</v>
+        <v>-0.597</v>
       </c>
     </row>
     <row r="42">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>-0.766</v>
+        <v>-0.597</v>
       </c>
     </row>
     <row r="43">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>-0.846</v>
+        <v>-0.673</v>
       </c>
     </row>
     <row r="44">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>-0.802</v>
+        <v>-0.652</v>
       </c>
     </row>
     <row r="45">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>-0.759</v>
+        <v>-0.644</v>
       </c>
     </row>
     <row r="46">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>-0.822</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="47">
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>-0.89</v>
+        <v>-0.736</v>
       </c>
     </row>
     <row r="48">
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>-0.872</v>
+        <v>-0.717</v>
       </c>
     </row>
     <row r="49">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>-0.949</v>
+        <v>-0.768</v>
       </c>
     </row>
     <row r="50">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>-0.974</v>
+        <v>-0.794</v>
       </c>
     </row>
     <row r="51">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>-1.071</v>
+        <v>-0.828</v>
       </c>
     </row>
     <row r="52">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>-1.206</v>
+        <v>-0.9379999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>-1.304</v>
+        <v>-0.987</v>
       </c>
     </row>
     <row r="54">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>-1.338</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="55">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>-1.418</v>
+        <v>-1.038</v>
       </c>
     </row>
     <row r="56">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>-1.42</v>
+        <v>-1.065</v>
       </c>
     </row>
     <row r="57">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>-1.457</v>
+        <v>-1.102</v>
       </c>
     </row>
     <row r="58">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>-1.394</v>
+        <v>-1.056</v>
       </c>
     </row>
     <row r="59">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>-1.436</v>
+        <v>-1.097</v>
       </c>
     </row>
     <row r="60">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>-1.446</v>
+        <v>-1.117</v>
       </c>
     </row>
     <row r="61">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>-1.399</v>
+        <v>-1.092</v>
       </c>
     </row>
     <row r="62">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>-1.417</v>
+        <v>-1.116</v>
       </c>
     </row>
     <row r="63">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>-1.423</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="64">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>-1.375</v>
+        <v>-1.098</v>
       </c>
     </row>
     <row r="65">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>-1.4</v>
+        <v>-1.118</v>
       </c>
     </row>
     <row r="66">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>-1.391</v>
+        <v>-1.136</v>
       </c>
     </row>
     <row r="67">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>-1.352</v>
+        <v>-1.099</v>
       </c>
     </row>
     <row r="68">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>-1.332</v>
+        <v>-1.095</v>
       </c>
     </row>
     <row r="69">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>-1.286</v>
+        <v>-1.071</v>
       </c>
     </row>
     <row r="70">
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>-1.194</v>
+        <v>-0.979</v>
       </c>
     </row>
     <row r="71">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>-1.158</v>
+        <v>-0.961</v>
       </c>
     </row>
     <row r="72">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>-1.169</v>
+        <v>-0.963</v>
       </c>
     </row>
     <row r="73">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>-1.117</v>
+        <v>-0.913</v>
       </c>
     </row>
     <row r="74">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>-1.109</v>
+        <v>-0.911</v>
       </c>
     </row>
     <row r="75">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>-1.1</v>
+        <v>-0.895</v>
       </c>
     </row>
     <row r="76">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>-0.991</v>
+        <v>-0.797</v>
       </c>
     </row>
     <row r="77">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>-0.945</v>
+        <v>-0.756</v>
       </c>
     </row>
     <row r="78">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>-0.931</v>
+        <v>-0.765</v>
       </c>
     </row>
     <row r="79">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>-0.885</v>
+        <v>-0.734</v>
       </c>
     </row>
     <row r="80">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>-0.879</v>
+        <v>-0.727</v>
       </c>
     </row>
     <row r="81">
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>-0.844</v>
+        <v>-0.707</v>
       </c>
     </row>
     <row r="82">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>-0.796</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="83">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>-0.798</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="84">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>-0.778</v>
+        <v>-0.663</v>
       </c>
     </row>
     <row r="85">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>-0.737</v>
+        <v>-0.638</v>
       </c>
     </row>
     <row r="86">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>-0.697</v>
+        <v>-0.605</v>
       </c>
     </row>
     <row r="87">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>-0.678</v>
+        <v>-0.584</v>
       </c>
     </row>
     <row r="88">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>-0.625</v>
+        <v>-0.5570000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>-0.614</v>
+        <v>-0.543</v>
       </c>
     </row>
     <row r="90">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>-0.572</v>
+        <v>-0.514</v>
       </c>
     </row>
     <row r="91">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>-0.523</v>
+        <v>-0.475</v>
       </c>
     </row>
     <row r="92">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>-0.483</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="93">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>-0.473</v>
+        <v>-0.445</v>
       </c>
     </row>
     <row r="94">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>-0.407</v>
+        <v>-0.395</v>
       </c>
     </row>
     <row r="95">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>-0.398</v>
+        <v>-0.383</v>
       </c>
     </row>
     <row r="96">
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>-0.342</v>
+        <v>-0.335</v>
       </c>
     </row>
     <row r="97">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>-0.302</v>
+        <v>-0.299</v>
       </c>
     </row>
     <row r="98">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>-0.29</v>
+        <v>-0.299</v>
       </c>
     </row>
     <row r="99">
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>-0.235</v>
+        <v>-0.262</v>
       </c>
     </row>
     <row r="100">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>-0.185</v>
+        <v>-0.229</v>
       </c>
     </row>
     <row r="101">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>-0.174</v>
+        <v>-0.205</v>
       </c>
     </row>
     <row r="102">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>-0.15</v>
+        <v>-0.184</v>
       </c>
     </row>
     <row r="103">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>-0.127</v>
+        <v>-0.157</v>
       </c>
     </row>
     <row r="104">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.116</v>
       </c>
     </row>
     <row r="105">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>-0.051</v>
+        <v>-0.111</v>
       </c>
     </row>
     <row r="106">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>-0.053</v>
+        <v>-0.117</v>
       </c>
     </row>
     <row r="107">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>-0.003</v>
+        <v>-0.08699999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>0.014</v>
+        <v>-0.079</v>
       </c>
     </row>
     <row r="109">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>0.067</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="110">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>0.089</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="111">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>0.103</v>
+        <v>-0.019</v>
       </c>
     </row>
     <row r="112">
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="113">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>0.147</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="114">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>0.172</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="115">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>0.156</v>
+        <v>0.254</v>
       </c>
     </row>
     <row r="116">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>0.202</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="117">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>0.193</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="118">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>0.206</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="119">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>0.232</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="120">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>0.246</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="121">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>0.275</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="122">
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>0.264</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="123">
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>0.241</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="124">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>0.315</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="125">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>0.299</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="126">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>0.319</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="127">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>0.319</v>
+        <v>0.281</v>
       </c>
     </row>
     <row r="128">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>0.3</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="129">
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>0.295</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="130">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>0.301</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="131">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>0.293</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="132">
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
     </row>
     <row r="133">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="134">
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>0.291</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="135">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>0.346</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="136">
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>0.356</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="137">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>0.34</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="138">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>0.361</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="139">
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>0.39</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="140">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>0.408</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="141">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="142">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>0.365</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="143">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>0.401</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="144">
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>0.399</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="145">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>0.421</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="146">
@@ -2314,7 +2314,7 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>0.413</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="147">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>0.409</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="148">
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>0.424</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="149">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>0.44</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="150">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>0.428</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="151">
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>0.424</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="152">
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>0.437</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="153">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>0.445</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="154">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>0.461</v>
+        <v>0.491</v>
       </c>
     </row>
     <row r="155">
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>0.482</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="156">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>0.466</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="157">
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>0.468</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="158">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>0.508</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="159">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>0.481</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="160">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>0.511</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="161">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.514</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="162">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>0.531</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="163">
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>0.546</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.543</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="166">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="167">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>0.579</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="168">
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>0.599</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="169">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>0.572</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="170">
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>0.605</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="171">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>0.59</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="172">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>0.633</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="173">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>0.609</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="174">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>0.628</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="175">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>0.646</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="176">
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>0.661</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="177">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>0.676</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="178">
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>0.588</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="179">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>0.6</v>
+        <v>0.899</v>
       </c>
     </row>
     <row r="180">
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>0.542</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="181">
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>0.465</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="182">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>0.484</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="183">
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>0.512</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="184">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>0.378</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="185">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>0.368</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="186">
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>0.387</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="187">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>0.357</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="188">
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>0.325</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="189">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>0.282</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="190">
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>0.308</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="191">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>0.294</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="192">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>0.271</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="193">
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>0.289</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="194">
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>0.254</v>
+        <v>0.251</v>
       </c>
     </row>
     <row r="195">
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>0.224</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="196">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>0.246</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="197">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>0.255</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="198">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>0.197</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="199">
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>0.188</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="200">
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>0.221</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="201">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>0.264</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="202">
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>0.374</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="203">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>0.344</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="204">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>0.397</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="205">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>0.447</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="206">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>0.477</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="207">
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>0.474</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="208">
@@ -2934,7 +2934,7 @@
         </is>
       </c>
       <c r="J208" t="n">
-        <v>0.515</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="209">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>0.57</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="210">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>0.581</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="211">
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>0.652</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="212">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>0.664</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="213">
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>0.699</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="214">
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>0.76</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="215">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>0.769</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="216">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>0.764</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="217">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>0.798</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="218">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>0.796</v>
+        <v>0.5679999999999999</v>
       </c>
     </row>
     <row r="219">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>0.873</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="220">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>0.945</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="221">
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>0.971</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="222">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>1.004</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="223">
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>1.065</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="224">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>1.071</v>
+        <v>1.329</v>
       </c>
     </row>
     <row r="225">
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>1.064</v>
+        <v>1.327</v>
       </c>
     </row>
     <row r="226">
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>1.06</v>
+        <v>1.343</v>
       </c>
     </row>
     <row r="227">
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>1.044</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="228">
@@ -3134,7 +3134,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>1.055</v>
+        <v>1.343</v>
       </c>
     </row>
     <row r="229">
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>1.1</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="230">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>1.157</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="231">
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>1.138</v>
+        <v>1.422</v>
       </c>
     </row>
     <row r="232">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>1.179</v>
+        <v>1.462</v>
       </c>
     </row>
     <row r="233">
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>1.151</v>
+        <v>1.453</v>
       </c>
     </row>
     <row r="234">
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>1.12</v>
+        <v>1.129</v>
       </c>
     </row>
     <row r="235">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>1.13</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="236">
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>1.119</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="237">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>1.096</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="238">
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>1.091</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="239">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>1.085</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="240">
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>1.035</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="241">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>1.023</v>
+        <v>1.005</v>
       </c>
     </row>
     <row r="242">
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>0.968</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="243">
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>0.92</v>
+        <v>1.039</v>
       </c>
     </row>
     <row r="244">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>0.93</v>
+        <v>1.064</v>
       </c>
     </row>
     <row r="245">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>0.924</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="246">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>0.946</v>
+        <v>1.046</v>
       </c>
     </row>
     <row r="247">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>0.892</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="248">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>0.879</v>
+        <v>1.003</v>
       </c>
     </row>
     <row r="249">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>0.891</v>
+        <v>1.021</v>
       </c>
     </row>
     <row r="250">
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>0.873</v>
+        <v>1.013</v>
       </c>
     </row>
     <row r="251">
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>0.878</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="252">
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>0.868</v>
+        <v>1.037</v>
       </c>
     </row>
     <row r="253">
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>0.825</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="254">
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>0.786</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="255">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>0.782</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="256">
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>0.736</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="257">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>0.655</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="258">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>0.697</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="259">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>0.706</v>
+        <v>0.795</v>
       </c>
     </row>
   </sheetData>
@@ -3756,7 +3756,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Real Interest Rate 1-Year</t>
+          <t>Real Interest Rate 1-Year (ex-ante)</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -3772,7 +3772,7 @@
           <t>percent</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="8" t="n">
         <v>0.27</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -3784,7 +3784,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Real Interest Rate 3-Year</t>
+          <t>Real Interest Rate 3-Year (ex-ante)</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -3800,7 +3800,7 @@
           <t>percent</t>
         </is>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="10" t="n">
         <v>-0.41</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -3812,7 +3812,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Real Interest Rate 10-Year</t>
+          <t>Real Interest Rate 10-Year (ex-ante)</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -3828,7 +3828,7 @@
           <t>percent</t>
         </is>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="10" t="n">
         <v>-1.04</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -3946,7 +3946,7 @@
           <t>percent</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="10" t="n">
         <v>-0.31</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -3974,7 +3974,7 @@
           <t>percent</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>-3.71</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -4002,7 +4002,7 @@
           <t>percent</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="8" t="n">
         <v>0.77</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -4030,7 +4030,7 @@
           <t>di_points</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="8" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -4058,7 +4058,7 @@
           <t>di_points</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="8" t="n">
         <v>1.13</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -4086,7 +4086,7 @@
           <t>di_points</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="8" t="n">
         <v>1.12</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -4114,7 +4114,7 @@
           <t>di_points</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="8" t="n">
         <v>1.19</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -4142,7 +4142,7 @@
           <t>index</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="8" t="n">
         <v>3.15</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -4170,7 +4170,7 @@
           <t>index</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="8" t="n">
         <v>4.31</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -4198,7 +4198,7 @@
           <t>yen_per_usd</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="8" t="n">
         <v>2.07</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -4226,7 +4226,7 @@
           <t>percent_yoy</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="8" t="n">
         <v>0.53</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -4254,7 +4254,7 @@
           <t>percent_yoy</t>
         </is>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="8" t="n">
         <v>0.58</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -31873,16 +31873,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.9953</v>
+        <v>-0.6574</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.2642</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>-0.9056999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2642</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>-0.3402</v>
@@ -31901,16 +31901,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9752</v>
+        <v>-0.6242</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.3211</v>
+        <v>0.0829</v>
       </c>
       <c r="E3" t="n">
         <v>-0.8599</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3211</v>
+        <v>0.0829</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3175</v>
@@ -31929,19 +31929,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.5926</v>
       </c>
       <c r="C4" t="n">
         <v>0.223</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.2475</v>
+        <v>0.0762</v>
       </c>
       <c r="E4" t="n">
         <v>-0.7599</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2475</v>
+        <v>0.0762</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4013</v>
@@ -31963,19 +31963,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.8237</v>
+        <v>-0.5737</v>
       </c>
       <c r="C5" t="n">
         <v>0.2218</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1551</v>
+        <v>0.0949</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7408</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1551</v>
+        <v>0.0949</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4712</v>
@@ -31997,19 +31997,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.8032</v>
+        <v>-0.5546</v>
       </c>
       <c r="C6" t="n">
         <v>0.1995</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1434</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7181999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1434</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4856</v>
@@ -32031,19 +32031,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.7954</v>
+        <v>-0.5615</v>
       </c>
       <c r="C7" t="n">
         <v>0.191</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0647</v>
+        <v>0.1047</v>
       </c>
       <c r="E7" t="n">
         <v>-0.728</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0647</v>
+        <v>0.1047</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5268</v>
@@ -32065,19 +32065,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.7692</v>
+        <v>-0.5412</v>
       </c>
       <c r="C8" t="n">
         <v>0.0866</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0384</v>
+        <v>0.1012</v>
       </c>
       <c r="E8" t="n">
         <v>-0.7018</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0384</v>
+        <v>0.1012</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5809</v>
@@ -32099,19 +32099,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.8024</v>
+        <v>-0.5626</v>
       </c>
       <c r="C9" t="n">
         <v>0.0555</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1252</v>
+        <v>0.0737</v>
       </c>
       <c r="E9" t="n">
         <v>-0.7217</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1252</v>
+        <v>0.0737</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6569</v>
@@ -32133,19 +32133,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.7403</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="C10" t="n">
         <v>0.08110000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1048</v>
+        <v>0.0743</v>
       </c>
       <c r="E10" t="n">
         <v>-0.6491</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1048</v>
+        <v>0.0743</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6909999999999999</v>
@@ -32167,19 +32167,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.7843</v>
+        <v>-0.5384</v>
       </c>
       <c r="C11" t="n">
         <v>0.0111</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.192</v>
+        <v>0.0372</v>
       </c>
       <c r="E11" t="n">
         <v>-0.6823</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.192</v>
+        <v>0.0372</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7927999999999999</v>
@@ -32201,19 +32201,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.7628</v>
+        <v>-0.5231</v>
       </c>
       <c r="C12" t="n">
         <v>-0.0322</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.168</v>
+        <v>0.0303</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6615</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.168</v>
+        <v>0.0303</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8329</v>
@@ -32235,19 +32235,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.7474</v>
+        <v>-0.5079</v>
       </c>
       <c r="C13" t="n">
         <v>-0.0309</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1641</v>
+        <v>0.0331</v>
       </c>
       <c r="E13" t="n">
         <v>-0.6432</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1641</v>
+        <v>0.0331</v>
       </c>
       <c r="G13" t="n">
         <v>-0.87</v>
@@ -32269,19 +32269,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.7326</v>
+        <v>-0.5006</v>
       </c>
       <c r="C14" t="n">
         <v>-0.0001</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.1204</v>
+        <v>0.0395</v>
       </c>
       <c r="E14" t="n">
         <v>-0.6356000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1204</v>
+        <v>0.0395</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9065</v>
@@ -32303,19 +32303,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.7532</v>
+        <v>-0.5027</v>
       </c>
       <c r="C15" t="n">
         <v>-0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.248</v>
+        <v>0.0044</v>
       </c>
       <c r="E15" t="n">
         <v>-0.6294999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.248</v>
+        <v>0.0044</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9376</v>
@@ -32337,19 +32337,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4803</v>
       </c>
       <c r="C16" t="n">
         <v>-0.1073</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4098</v>
+        <v>-0.0435</v>
       </c>
       <c r="E16" t="n">
         <v>-0.5895</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4098</v>
+        <v>-0.0435</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9836</v>
@@ -32371,19 +32371,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.7834</v>
+        <v>-0.485</v>
       </c>
       <c r="C17" t="n">
         <v>-0.1318</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.583</v>
+        <v>-0.091</v>
       </c>
       <c r="E17" t="n">
         <v>-0.5834</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.583</v>
+        <v>-0.091</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0033</v>
@@ -32405,19 +32405,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.8024</v>
+        <v>-0.4955</v>
       </c>
       <c r="C18" t="n">
         <v>-0.1566</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6553</v>
+        <v>-0.121</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5891</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6553</v>
+        <v>-0.121</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0636</v>
@@ -32439,19 +32439,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.7977</v>
+        <v>-0.4833</v>
       </c>
       <c r="C19" t="n">
         <v>-0.1514</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7043</v>
+        <v>-0.1324</v>
       </c>
       <c r="E19" t="n">
         <v>-0.5711000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7043</v>
+        <v>-0.1324</v>
       </c>
       <c r="G19" t="n">
         <v>-1.111</v>
@@ -32473,19 +32473,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.4921</v>
       </c>
       <c r="C20" t="n">
         <v>-0.0052</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6976</v>
+        <v>-0.1538</v>
       </c>
       <c r="E20" t="n">
         <v>-0.5767</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6976</v>
+        <v>-0.1538</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1803</v>
@@ -32507,19 +32507,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.7672</v>
+        <v>-0.479</v>
       </c>
       <c r="C21" t="n">
         <v>-0.038</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5664</v>
+        <v>-0.1254</v>
       </c>
       <c r="E21" t="n">
         <v>-0.5674</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5664</v>
+        <v>-0.1254</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2286</v>
@@ -32541,19 +32541,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.665</v>
+        <v>-0.4119</v>
       </c>
       <c r="C22" t="n">
         <v>-0.0047</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3426</v>
+        <v>-0.0771</v>
       </c>
       <c r="E22" t="n">
         <v>-0.4956</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3426</v>
+        <v>-0.0771</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2176</v>
@@ -32575,19 +32575,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.7</v>
+        <v>-0.432</v>
       </c>
       <c r="C23" t="n">
         <v>-0.0412</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.451</v>
+        <v>-0.111</v>
       </c>
       <c r="E23" t="n">
         <v>-0.5123</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.451</v>
+        <v>-0.111</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3467</v>
@@ -32609,19 +32609,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.6808</v>
+        <v>-0.4049</v>
       </c>
       <c r="C24" t="n">
         <v>-0.043</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5039</v>
+        <v>-0.1243</v>
       </c>
       <c r="E24" t="n">
         <v>-0.475</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5039</v>
+        <v>-0.1243</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3545</v>
@@ -32643,19 +32643,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6574</v>
+        <v>-0.3856</v>
       </c>
       <c r="C25" t="n">
         <v>-0.0643</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.4806</v>
+        <v>-0.1218</v>
       </c>
       <c r="E25" t="n">
         <v>-0.4516</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4806</v>
+        <v>-0.1218</v>
       </c>
       <c r="G25" t="n">
         <v>-1.4054</v>
@@ -32677,19 +32677,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6297</v>
+        <v>-0.3758</v>
       </c>
       <c r="C26" t="n">
         <v>-0.1258</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.3938</v>
+        <v>-0.124</v>
       </c>
       <c r="E26" t="n">
         <v>-0.4387</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3938</v>
+        <v>-0.124</v>
       </c>
       <c r="G26" t="n">
         <v>-1.4442</v>
@@ -32711,19 +32711,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6469</v>
+        <v>-0.4024</v>
       </c>
       <c r="C27" t="n">
         <v>0.0572</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.3471</v>
+        <v>-0.1244</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4719</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3471</v>
+        <v>-0.1244</v>
       </c>
       <c r="G27" t="n">
         <v>-1.5368</v>
@@ -32745,19 +32745,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6391</v>
+        <v>-0.3921</v>
       </c>
       <c r="C28" t="n">
         <v>0.0645</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.357</v>
+        <v>-0.1217</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4596</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.357</v>
+        <v>-0.1217</v>
       </c>
       <c r="G28" t="n">
         <v>-1.5891</v>
@@ -32779,19 +32779,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6429</v>
+        <v>-0.4002</v>
       </c>
       <c r="C29" t="n">
         <v>0.002</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.3451</v>
+        <v>-0.1317</v>
       </c>
       <c r="E29" t="n">
         <v>-0.4673</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.3451</v>
+        <v>-0.1317</v>
       </c>
       <c r="G29" t="n">
         <v>-1.6354</v>
@@ -32813,19 +32813,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.634</v>
+        <v>-0.3948</v>
       </c>
       <c r="C30" t="n">
         <v>-0.0314</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.3443</v>
+        <v>-0.1482</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4565</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.3443</v>
+        <v>-0.1482</v>
       </c>
       <c r="G30" t="n">
         <v>-1.6988</v>
@@ -32847,19 +32847,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6624</v>
+        <v>-0.3819</v>
       </c>
       <c r="C31" t="n">
         <v>-0.0235</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.6092</v>
+        <v>-0.2063</v>
       </c>
       <c r="E31" t="n">
         <v>-0.4258</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.6092</v>
+        <v>-0.2063</v>
       </c>
       <c r="G31" t="n">
         <v>-1.7104</v>
@@ -32881,19 +32881,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6435</v>
+        <v>-0.3685</v>
       </c>
       <c r="C32" t="n">
         <v>-0.0077</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.5831</v>
+        <v>-0.2085</v>
       </c>
       <c r="E32" t="n">
         <v>-0.4085</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.5831</v>
+        <v>-0.2085</v>
       </c>
       <c r="G32" t="n">
         <v>-1.7205</v>
@@ -32915,19 +32915,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5968</v>
+        <v>-0.3647</v>
       </c>
       <c r="C33" t="n">
         <v>-0.1114</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.3153</v>
+        <v>-0.1551</v>
       </c>
       <c r="E33" t="n">
         <v>-0.4171</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.3153</v>
+        <v>-0.1551</v>
       </c>
       <c r="G33" t="n">
         <v>-1.7264</v>
@@ -32949,19 +32949,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6392</v>
+        <v>-0.4359</v>
       </c>
       <c r="C34" t="n">
         <v>-0.1253</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1457</v>
+        <v>-0.1294</v>
       </c>
       <c r="E34" t="n">
         <v>-0.5125</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1457</v>
+        <v>-0.1294</v>
       </c>
       <c r="G34" t="n">
         <v>-1.7343</v>
@@ -32983,19 +32983,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6504</v>
+        <v>-0.4447</v>
       </c>
       <c r="C35" t="n">
         <v>-0.1221</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1639</v>
+        <v>-0.1354</v>
       </c>
       <c r="E35" t="n">
         <v>-0.522</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1639</v>
+        <v>-0.1354</v>
       </c>
       <c r="G35" t="n">
         <v>-1.7997</v>
@@ -33017,19 +33017,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6095</v>
+        <v>-0.4332</v>
       </c>
       <c r="C36" t="n">
         <v>-0.2038</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9877</v>
+        <v>-0.1064</v>
       </c>
       <c r="E36" t="n">
         <v>-0.5149</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9877</v>
+        <v>-0.1064</v>
       </c>
       <c r="G36" t="n">
         <v>-1.7541</v>
@@ -33051,19 +33051,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6725</v>
+        <v>-0.4982</v>
       </c>
       <c r="C37" t="n">
         <v>-0.1892</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9678</v>
+        <v>-0.0963</v>
       </c>
       <c r="E37" t="n">
         <v>-0.5987</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9678</v>
+        <v>-0.0963</v>
       </c>
       <c r="G37" t="n">
         <v>-1.7481</v>
@@ -33085,19 +33085,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6501</v>
+        <v>-0.5091</v>
       </c>
       <c r="C38" t="n">
         <v>-0.1758</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="E38" t="n">
         <v>-0.6222</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="G38" t="n">
         <v>-1.8252</v>
@@ -33119,19 +33119,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.6308</v>
+        <v>-0.5078</v>
       </c>
       <c r="C39" t="n">
         <v>-0.2892</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.6747</v>
+        <v>-0.0597</v>
       </c>
       <c r="E39" t="n">
         <v>-0.6198</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6747</v>
+        <v>-0.0597</v>
       </c>
       <c r="G39" t="n">
         <v>-1.7768</v>
@@ -33153,19 +33153,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.7075</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="C40" t="n">
         <v>-0.2515</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.64</v>
+        <v>-0.0387</v>
       </c>
       <c r="E40" t="n">
         <v>-0.7243000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.64</v>
+        <v>-0.0387</v>
       </c>
       <c r="G40" t="n">
         <v>-1.8351</v>
@@ -33187,19 +33187,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.7178</v>
+        <v>-0.5968</v>
       </c>
       <c r="C41" t="n">
         <v>-0.3416</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.6726</v>
+        <v>-0.0679</v>
       </c>
       <c r="E41" t="n">
         <v>-0.7291</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.6726</v>
+        <v>-0.0679</v>
       </c>
       <c r="G41" t="n">
         <v>-1.8045</v>
@@ -33221,19 +33221,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.7663</v>
+        <v>-0.5969</v>
       </c>
       <c r="C42" t="n">
         <v>-0.294</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.9837</v>
+        <v>-0.1367</v>
       </c>
       <c r="E42" t="n">
         <v>-0.7119</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.9837</v>
+        <v>-0.1367</v>
       </c>
       <c r="G42" t="n">
         <v>-1.8386</v>
@@ -33255,19 +33255,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.8455</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="C43" t="n">
         <v>-0.3262</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.0256</v>
+        <v>-0.1625</v>
       </c>
       <c r="E43" t="n">
         <v>-0.8005</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.0256</v>
+        <v>-0.1625</v>
       </c>
       <c r="G43" t="n">
         <v>-1.846</v>
@@ -33289,19 +33289,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.8016</v>
+        <v>-0.652</v>
       </c>
       <c r="C44" t="n">
         <v>-0.3489</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.8742</v>
+        <v>-0.126</v>
       </c>
       <c r="E44" t="n">
         <v>-0.7835</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.8742</v>
+        <v>-0.126</v>
       </c>
       <c r="G44" t="n">
         <v>-1.7569</v>
@@ -33323,19 +33323,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.7588</v>
+        <v>-0.644</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3811</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="E45" t="n">
         <v>-0.7826</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="G45" t="n">
         <v>-1.8631</v>
@@ -33357,19 +33357,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.822</v>
+        <v>-0.7097</v>
       </c>
       <c r="C46" t="n">
         <v>-0.3936</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6607</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="E46" t="n">
         <v>-0.8623</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6607</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="G46" t="n">
         <v>-1.7931</v>
@@ -33391,19 +33391,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.8897</v>
+        <v>-0.7362</v>
       </c>
       <c r="C47" t="n">
         <v>-0.3888</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.8711</v>
+        <v>-0.1036</v>
       </c>
       <c r="E47" t="n">
         <v>-0.8943</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.8711</v>
+        <v>-0.1036</v>
       </c>
       <c r="G47" t="n">
         <v>-1.7839</v>
@@ -33425,19 +33425,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.8721</v>
+        <v>-0.7168</v>
       </c>
       <c r="C48" t="n">
         <v>-0.2461</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.8318</v>
+        <v>-0.055</v>
       </c>
       <c r="E48" t="n">
         <v>-0.8822</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.8318</v>
+        <v>-0.055</v>
       </c>
       <c r="G48" t="n">
         <v>-1.7142</v>
@@ -33459,19 +33459,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.9488</v>
+        <v>-0.768</v>
       </c>
       <c r="C49" t="n">
         <v>-0.2033</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9283</v>
+        <v>-0.0243</v>
       </c>
       <c r="E49" t="n">
         <v>-0.954</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.9283</v>
+        <v>-0.0243</v>
       </c>
       <c r="G49" t="n">
         <v>-1.6767</v>
@@ -33493,19 +33493,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.9744</v>
+        <v>-0.7941</v>
       </c>
       <c r="C50" t="n">
         <v>-0.0545</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.8793</v>
+        <v>0.0226</v>
       </c>
       <c r="E50" t="n">
         <v>-0.9982</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.8793</v>
+        <v>0.0226</v>
       </c>
       <c r="G50" t="n">
         <v>-1.6241</v>
@@ -33527,19 +33527,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-1.0709</v>
+        <v>-0.8284</v>
       </c>
       <c r="C51" t="n">
         <v>0.2167</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.2063</v>
+        <v>0.0066</v>
       </c>
       <c r="E51" t="n">
         <v>-1.0371</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.2063</v>
+        <v>0.0066</v>
       </c>
       <c r="G51" t="n">
         <v>-1.5369</v>
@@ -33561,19 +33561,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.206</v>
+        <v>-0.9377</v>
       </c>
       <c r="C52" t="n">
         <v>0.3527</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.3327</v>
+        <v>0.0086</v>
       </c>
       <c r="E52" t="n">
         <v>-1.1743</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.3327</v>
+        <v>0.0086</v>
       </c>
       <c r="G52" t="n">
         <v>-1.4913</v>
@@ -33595,19 +33595,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.3041</v>
+        <v>-0.9875</v>
       </c>
       <c r="C53" t="n">
         <v>0.5456</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.5854</v>
+        <v>-0.002</v>
       </c>
       <c r="E53" t="n">
         <v>-1.2338</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.5854</v>
+        <v>-0.002</v>
       </c>
       <c r="G53" t="n">
         <v>-1.4266</v>
@@ -33629,19 +33629,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.3382</v>
+        <v>-0.9837</v>
       </c>
       <c r="C54" t="n">
         <v>0.8093</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.763</v>
+        <v>0.0091</v>
       </c>
       <c r="E54" t="n">
         <v>-1.2319</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.763</v>
+        <v>0.0091</v>
       </c>
       <c r="G54" t="n">
         <v>-1.344</v>
@@ -33663,19 +33663,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.4185</v>
+        <v>-1.0384</v>
       </c>
       <c r="C55" t="n">
         <v>0.9752999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.885</v>
+        <v>0.0157</v>
       </c>
       <c r="E55" t="n">
         <v>-1.3019</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.885</v>
+        <v>0.0157</v>
       </c>
       <c r="G55" t="n">
         <v>-1.2416</v>
@@ -33697,19 +33697,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.4202</v>
+        <v>-1.0652</v>
       </c>
       <c r="C56" t="n">
         <v>0.9336</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.7339</v>
+        <v>0.0414</v>
       </c>
       <c r="E56" t="n">
         <v>-1.3418</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.7339</v>
+        <v>0.0414</v>
       </c>
       <c r="G56" t="n">
         <v>-1.1579</v>
@@ -33731,19 +33731,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.4573</v>
+        <v>-1.102</v>
       </c>
       <c r="C57" t="n">
         <v>0.9248</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.738</v>
+        <v>0.0388</v>
       </c>
       <c r="E57" t="n">
         <v>-1.3872</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.738</v>
+        <v>0.0388</v>
       </c>
       <c r="G57" t="n">
         <v>-1.1782</v>
@@ -33765,19 +33765,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.3943</v>
+        <v>-1.0559</v>
       </c>
       <c r="C58" t="n">
         <v>0.9406</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.6378</v>
+        <v>0.054</v>
       </c>
       <c r="E58" t="n">
         <v>-1.3334</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.6378</v>
+        <v>0.054</v>
       </c>
       <c r="G58" t="n">
         <v>-1.0695</v>
@@ -33799,19 +33799,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.4364</v>
+        <v>-1.0969</v>
       </c>
       <c r="C59" t="n">
         <v>0.9092</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.6505</v>
+        <v>0.0474</v>
       </c>
       <c r="E59" t="n">
         <v>-1.3829</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.6505</v>
+        <v>0.0474</v>
       </c>
       <c r="G59" t="n">
         <v>-1.0233</v>
@@ -33833,19 +33833,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.446</v>
+        <v>-1.1172</v>
       </c>
       <c r="C60" t="n">
         <v>0.8671</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.6017</v>
+        <v>0.0426</v>
       </c>
       <c r="E60" t="n">
         <v>-1.4071</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.6017</v>
+        <v>0.0426</v>
       </c>
       <c r="G60" t="n">
         <v>-0.9379</v>
@@ -33867,19 +33867,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.3989</v>
+        <v>-1.0924</v>
       </c>
       <c r="C61" t="n">
         <v>0.8462</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.4589</v>
+        <v>0.0735</v>
       </c>
       <c r="E61" t="n">
         <v>-1.3839</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.4589</v>
+        <v>0.0735</v>
       </c>
       <c r="G61" t="n">
         <v>-0.882</v>
@@ -33901,19 +33901,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.4165</v>
+        <v>-1.1161</v>
       </c>
       <c r="C62" t="n">
         <v>0.8189</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.4338</v>
+        <v>0.0683</v>
       </c>
       <c r="E62" t="n">
         <v>-1.4122</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.4338</v>
+        <v>0.0683</v>
       </c>
       <c r="G62" t="n">
         <v>-0.8365</v>
@@ -33935,19 +33935,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.4233</v>
+        <v>-1.1305</v>
       </c>
       <c r="C63" t="n">
         <v>0.7642</v>
       </c>
       <c r="D63" t="n">
-        <v>-1.3962</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="E63" t="n">
         <v>-1.4301</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.3962</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G63" t="n">
         <v>-0.7643</v>
@@ -33969,19 +33969,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.3748</v>
+        <v>-1.0983</v>
       </c>
       <c r="C64" t="n">
         <v>0.7181</v>
       </c>
       <c r="D64" t="n">
-        <v>-1.3131</v>
+        <v>0.0696</v>
       </c>
       <c r="E64" t="n">
         <v>-1.3902</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.3131</v>
+        <v>0.0696</v>
       </c>
       <c r="G64" t="n">
         <v>-0.6711</v>
@@ -34003,19 +34003,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.4004</v>
+        <v>-1.1179</v>
       </c>
       <c r="C65" t="n">
         <v>0.7288</v>
       </c>
       <c r="D65" t="n">
-        <v>-1.3467</v>
+        <v>0.0658</v>
       </c>
       <c r="E65" t="n">
         <v>-1.4138</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.3467</v>
+        <v>0.0658</v>
       </c>
       <c r="G65" t="n">
         <v>-0.6303</v>
@@ -34037,19 +34037,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.3913</v>
+        <v>-1.1365</v>
       </c>
       <c r="C66" t="n">
         <v>0.6173999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.2011</v>
+        <v>0.0732</v>
       </c>
       <c r="E66" t="n">
         <v>-1.4389</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.2011</v>
+        <v>0.0732</v>
       </c>
       <c r="G66" t="n">
         <v>-0.5721000000000001</v>
@@ -34071,19 +34071,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.3522</v>
+        <v>-1.0987</v>
       </c>
       <c r="C67" t="n">
         <v>0.6747</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.1841</v>
+        <v>0.0835</v>
       </c>
       <c r="E67" t="n">
         <v>-1.3942</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.1841</v>
+        <v>0.0835</v>
       </c>
       <c r="G67" t="n">
         <v>-0.5256999999999999</v>
@@ -34105,19 +34105,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.3316</v>
+        <v>-1.0951</v>
       </c>
       <c r="C68" t="n">
         <v>0.6366000000000001</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.087</v>
+        <v>0.0954</v>
       </c>
       <c r="E68" t="n">
         <v>-1.3928</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.087</v>
+        <v>0.0954</v>
       </c>
       <c r="G68" t="n">
         <v>-0.5189</v>
@@ -34139,19 +34139,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2858</v>
+        <v>-1.0713</v>
       </c>
       <c r="C69" t="n">
         <v>0.5488</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9631</v>
+        <v>0.1094</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3665</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9631</v>
+        <v>0.1094</v>
       </c>
       <c r="G69" t="n">
         <v>-0.4544</v>
@@ -34173,19 +34173,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1941</v>
+        <v>-0.9788</v>
       </c>
       <c r="C70" t="n">
         <v>0.5564</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.972</v>
+        <v>0.1048</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2496</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.972</v>
+        <v>0.1048</v>
       </c>
       <c r="G70" t="n">
         <v>-0.4245</v>
@@ -34207,19 +34207,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.1583</v>
+        <v>-0.9614</v>
       </c>
       <c r="C71" t="n">
         <v>0.4596</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8626</v>
+        <v>0.1217</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2322</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.8626</v>
+        <v>0.1217</v>
       </c>
       <c r="G71" t="n">
         <v>-0.395</v>
@@ -34241,19 +34241,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1691</v>
+        <v>-0.9629</v>
       </c>
       <c r="C72" t="n">
         <v>0.4581</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9332</v>
+        <v>0.0979</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2281</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9332</v>
+        <v>0.0979</v>
       </c>
       <c r="G72" t="n">
         <v>-0.3903</v>
@@ -34275,19 +34275,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1166</v>
+        <v>-0.9134</v>
       </c>
       <c r="C73" t="n">
         <v>0.366</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9422</v>
+        <v>0.0737</v>
       </c>
       <c r="E73" t="n">
         <v>-1.1602</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.9422</v>
+        <v>0.0737</v>
       </c>
       <c r="G73" t="n">
         <v>-0.4221</v>
@@ -34309,19 +34309,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1087</v>
+        <v>-0.9112</v>
       </c>
       <c r="C74" t="n">
         <v>0.3275</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9129</v>
+        <v>0.0747</v>
       </c>
       <c r="E74" t="n">
         <v>-1.1576</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.9129</v>
+        <v>0.0747</v>
       </c>
       <c r="G74" t="n">
         <v>-0.4049</v>
@@ -34343,19 +34343,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.0996</v>
+        <v>-0.8949</v>
       </c>
       <c r="C75" t="n">
         <v>0.3123</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.966</v>
+        <v>0.0577</v>
       </c>
       <c r="E75" t="n">
         <v>-1.1331</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.966</v>
+        <v>0.0577</v>
       </c>
       <c r="G75" t="n">
         <v>-0.3271</v>
@@ -34377,19 +34377,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.9911</v>
+        <v>-0.7965</v>
       </c>
       <c r="C76" t="n">
         <v>0.2727</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9086</v>
+        <v>0.0643</v>
       </c>
       <c r="E76" t="n">
         <v>-1.0117</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.9086</v>
+        <v>0.0643</v>
       </c>
       <c r="G76" t="n">
         <v>-0.3432</v>
@@ -34411,19 +34411,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.9453</v>
+        <v>-0.7561</v>
       </c>
       <c r="C77" t="n">
         <v>0.318</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.8803</v>
+        <v>0.0658</v>
       </c>
       <c r="E77" t="n">
         <v>-0.9616</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.8803</v>
+        <v>0.0658</v>
       </c>
       <c r="G77" t="n">
         <v>-0.2362</v>
@@ -34445,19 +34445,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.9308</v>
+        <v>-0.7647</v>
       </c>
       <c r="C78" t="n">
         <v>0.2156</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.7499</v>
+        <v>0.0806</v>
       </c>
       <c r="E78" t="n">
         <v>-0.976</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.7499</v>
+        <v>0.0806</v>
       </c>
       <c r="G78" t="n">
         <v>-0.2434</v>
@@ -34479,19 +34479,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.8846000000000001</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="C79" t="n">
         <v>0.1924</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.6629</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="E79" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.6629</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G79" t="n">
         <v>-0.2437</v>
@@ -34513,19 +34513,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.8787</v>
+        <v>-0.7269</v>
       </c>
       <c r="C80" t="n">
         <v>0.1889</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.6676</v>
+        <v>0.0917</v>
       </c>
       <c r="E80" t="n">
         <v>-0.9315</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.6676</v>
+        <v>0.0917</v>
       </c>
       <c r="G80" t="n">
         <v>-0.2156</v>
@@ -34547,19 +34547,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.844</v>
+        <v>-0.7073</v>
       </c>
       <c r="C81" t="n">
         <v>0.1998</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.5807</v>
+        <v>0.103</v>
       </c>
       <c r="E81" t="n">
         <v>-0.9099</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.5807</v>
+        <v>0.103</v>
       </c>
       <c r="G81" t="n">
         <v>-0.1728</v>
@@ -34581,19 +34581,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.796</v>
+        <v>-0.6696</v>
       </c>
       <c r="C82" t="n">
         <v>0.1773</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.5248</v>
+        <v>0.1073</v>
       </c>
       <c r="E82" t="n">
         <v>-0.8638</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.5248</v>
+        <v>0.1073</v>
       </c>
       <c r="G82" t="n">
         <v>-0.176</v>
@@ -34615,19 +34615,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.798</v>
+        <v>-0.68</v>
       </c>
       <c r="C83" t="n">
         <v>0.057</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.4847</v>
+        <v>0.1051</v>
       </c>
       <c r="E83" t="n">
         <v>-0.8763</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.4847</v>
+        <v>0.1051</v>
       </c>
       <c r="G83" t="n">
         <v>-0.1968</v>
@@ -34649,19 +34649,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.7785</v>
+        <v>-0.6629</v>
       </c>
       <c r="C84" t="n">
         <v>0.0735</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.4712</v>
+        <v>0.1069</v>
       </c>
       <c r="E84" t="n">
         <v>-0.8552999999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.4712</v>
+        <v>0.1069</v>
       </c>
       <c r="G84" t="n">
         <v>-0.1605</v>
@@ -34683,19 +34683,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.7368</v>
+        <v>-0.6377</v>
       </c>
       <c r="C85" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.389</v>
+        <v>0.1065</v>
       </c>
       <c r="E85" t="n">
         <v>-0.8237</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.389</v>
+        <v>0.1065</v>
       </c>
       <c r="G85" t="n">
         <v>-0.1181</v>
@@ -34717,19 +34717,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.6967</v>
+        <v>-0.6048</v>
       </c>
       <c r="C86" t="n">
         <v>-0.0169</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.3506</v>
+        <v>0.1089</v>
       </c>
       <c r="E86" t="n">
         <v>-0.7833</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.3506</v>
+        <v>0.1089</v>
       </c>
       <c r="G86" t="n">
         <v>-0.1172</v>
@@ -34751,19 +34751,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.6778</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="C87" t="n">
         <v>0.0158</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.3558</v>
+        <v>0.112</v>
       </c>
       <c r="E87" t="n">
         <v>-0.7583</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.3558</v>
+        <v>0.112</v>
       </c>
       <c r="G87" t="n">
         <v>-0.07539999999999999</v>
@@ -34785,19 +34785,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.6246</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="C88" t="n">
         <v>-0.0888</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.2262</v>
+        <v>0.1119</v>
       </c>
       <c r="E88" t="n">
         <v>-0.7242</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.2262</v>
+        <v>0.1119</v>
       </c>
       <c r="G88" t="n">
         <v>-0.0843</v>
@@ -34819,19 +34819,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.6145</v>
+        <v>-0.5429</v>
       </c>
       <c r="C89" t="n">
         <v>-0.094</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.2417</v>
+        <v>0.1161</v>
       </c>
       <c r="E89" t="n">
         <v>-0.7077</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.2417</v>
+        <v>0.1161</v>
       </c>
       <c r="G89" t="n">
         <v>-0.0094</v>
@@ -34853,19 +34853,19 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.5725</v>
+        <v>-0.5137</v>
       </c>
       <c r="C90" t="n">
         <v>-0.0761</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.1673</v>
+        <v>0.1266</v>
       </c>
       <c r="E90" t="n">
         <v>-0.6738</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.1673</v>
+        <v>0.1266</v>
       </c>
       <c r="G90" t="n">
         <v>-0.0267</v>
@@ -34887,19 +34887,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.5228</v>
+        <v>-0.4755</v>
       </c>
       <c r="C91" t="n">
         <v>-0.1451</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.1048</v>
+        <v>0.1315</v>
       </c>
       <c r="E91" t="n">
         <v>-0.6272</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.1048</v>
+        <v>0.1315</v>
       </c>
       <c r="G91" t="n">
         <v>0.0213</v>
@@ -34921,19 +34921,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.4834</v>
+        <v>-0.4499</v>
       </c>
       <c r="C92" t="n">
         <v>-0.2106</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.0297</v>
+        <v>0.138</v>
       </c>
       <c r="E92" t="n">
         <v>-0.5969</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.0297</v>
+        <v>0.138</v>
       </c>
       <c r="G92" t="n">
         <v>0.0208</v>
@@ -34955,19 +34955,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4725</v>
+        <v>-0.4452</v>
       </c>
       <c r="C93" t="n">
         <v>-0.2003</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.0019</v>
+        <v>0.135</v>
       </c>
       <c r="E93" t="n">
         <v>-0.5901999999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.0019</v>
+        <v>0.135</v>
       </c>
       <c r="G93" t="n">
         <v>-0.0011</v>
@@ -34989,19 +34989,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.407</v>
+        <v>-0.3953</v>
       </c>
       <c r="C94" t="n">
         <v>-0.2764</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0779</v>
+        <v>0.1365</v>
       </c>
       <c r="E94" t="n">
         <v>-0.5282</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0779</v>
+        <v>0.1365</v>
       </c>
       <c r="G94" t="n">
         <v>0.0509</v>
@@ -35023,19 +35023,19 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.3976</v>
+        <v>-0.3826</v>
       </c>
       <c r="C95" t="n">
         <v>-0.2267</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0634</v>
+        <v>0.1387</v>
       </c>
       <c r="E95" t="n">
         <v>-0.5129</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0634</v>
+        <v>0.1387</v>
       </c>
       <c r="G95" t="n">
         <v>0.0814</v>
@@ -35057,19 +35057,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3423</v>
+        <v>-0.335</v>
       </c>
       <c r="C96" t="n">
         <v>-0.2546</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1039</v>
+        <v>0.1408</v>
       </c>
       <c r="E96" t="n">
         <v>-0.4539</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1039</v>
+        <v>0.1408</v>
       </c>
       <c r="G96" t="n">
         <v>0.131</v>
@@ -35091,19 +35091,19 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.3016</v>
+        <v>-0.2991</v>
       </c>
       <c r="C97" t="n">
         <v>-0.2788</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1307</v>
+        <v>0.143</v>
       </c>
       <c r="E97" t="n">
         <v>-0.4097</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1307</v>
+        <v>0.143</v>
       </c>
       <c r="G97" t="n">
         <v>0.1942</v>
@@ -35125,19 +35125,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.2899</v>
+        <v>-0.2988</v>
       </c>
       <c r="C98" t="n">
         <v>-0.3255</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1876</v>
+        <v>0.1433</v>
       </c>
       <c r="E98" t="n">
         <v>-0.4093</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1876</v>
+        <v>0.1433</v>
       </c>
       <c r="G98" t="n">
         <v>0.1494</v>
@@ -35159,19 +35159,19 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.2348</v>
+        <v>-0.2616</v>
       </c>
       <c r="C99" t="n">
         <v>-0.3433</v>
       </c>
       <c r="D99" t="n">
-        <v>0.287</v>
+        <v>0.1533</v>
       </c>
       <c r="E99" t="n">
         <v>-0.3653</v>
       </c>
       <c r="F99" t="n">
-        <v>0.287</v>
+        <v>0.1533</v>
       </c>
       <c r="G99" t="n">
         <v>0.183</v>
@@ -35193,19 +35193,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.1848</v>
+        <v>-0.2291</v>
       </c>
       <c r="C100" t="n">
         <v>-0.369</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3913</v>
+        <v>0.1696</v>
       </c>
       <c r="E100" t="n">
         <v>-0.3288</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3913</v>
+        <v>0.1696</v>
       </c>
       <c r="G100" t="n">
         <v>0.2241</v>
@@ -35227,19 +35227,19 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.1737</v>
+        <v>-0.205</v>
       </c>
       <c r="C101" t="n">
         <v>-0.3658</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3102</v>
+        <v>0.1535</v>
       </c>
       <c r="E101" t="n">
         <v>-0.2947</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3102</v>
+        <v>0.1535</v>
       </c>
       <c r="G101" t="n">
         <v>0.2488</v>
@@ -35261,19 +35261,19 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.1499</v>
+        <v>-0.1845</v>
       </c>
       <c r="C102" t="n">
         <v>-0.4643</v>
       </c>
       <c r="D102" t="n">
-        <v>0.299</v>
+        <v>0.1264</v>
       </c>
       <c r="E102" t="n">
         <v>-0.2622</v>
       </c>
       <c r="F102" t="n">
-        <v>0.299</v>
+        <v>0.1264</v>
       </c>
       <c r="G102" t="n">
         <v>0.2676</v>
@@ -35295,19 +35295,19 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.127</v>
+        <v>-0.1571</v>
       </c>
       <c r="C103" t="n">
         <v>-0.4159</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2747</v>
+        <v>0.1238</v>
       </c>
       <c r="E103" t="n">
         <v>-0.2274</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2747</v>
+        <v>0.1238</v>
       </c>
       <c r="G103" t="n">
         <v>0.3229</v>
@@ -35329,19 +35329,19 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.0689</v>
+        <v>-0.1159</v>
       </c>
       <c r="C104" t="n">
         <v>-0.5068</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3607</v>
+        <v>0.1256</v>
       </c>
       <c r="E104" t="n">
         <v>-0.1763</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3607</v>
+        <v>0.1256</v>
       </c>
       <c r="G104" t="n">
         <v>0.3181</v>
@@ -35363,19 +35363,19 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0509</v>
+        <v>-0.1111</v>
       </c>
       <c r="C105" t="n">
         <v>-0.5272</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4358</v>
+        <v>0.1344</v>
       </c>
       <c r="E105" t="n">
         <v>-0.1725</v>
       </c>
       <c r="F105" t="n">
-        <v>0.4358</v>
+        <v>0.1344</v>
       </c>
       <c r="G105" t="n">
         <v>0.3362</v>
@@ -35397,19 +35397,19 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.0526</v>
+        <v>-0.1165</v>
       </c>
       <c r="C106" t="n">
         <v>-0.5202</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4586</v>
+        <v>0.1391</v>
       </c>
       <c r="E106" t="n">
         <v>-0.1804</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4586</v>
+        <v>0.1391</v>
       </c>
       <c r="G106" t="n">
         <v>0.3423</v>
@@ -35431,19 +35431,19 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.0032</v>
+        <v>-0.0871</v>
       </c>
       <c r="C107" t="n">
         <v>-0.5985</v>
       </c>
       <c r="D107" t="n">
-        <v>0.5712</v>
+        <v>0.1517</v>
       </c>
       <c r="E107" t="n">
         <v>-0.1468</v>
       </c>
       <c r="F107" t="n">
-        <v>0.5712</v>
+        <v>0.1517</v>
       </c>
       <c r="G107" t="n">
         <v>0.3443</v>
@@ -35465,19 +35465,19 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0142</v>
+        <v>-0.0789</v>
       </c>
       <c r="C108" t="n">
         <v>-0.6315</v>
       </c>
       <c r="D108" t="n">
-        <v>0.6191</v>
+        <v>0.1536</v>
       </c>
       <c r="E108" t="n">
         <v>-0.137</v>
       </c>
       <c r="F108" t="n">
-        <v>0.6191</v>
+        <v>0.1536</v>
       </c>
       <c r="G108" t="n">
         <v>0.3754</v>
@@ -35499,19 +35499,19 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.176</v>
       </c>
       <c r="C109" t="n">
         <v>-0.6771</v>
       </c>
       <c r="D109" t="n">
-        <v>0.6873</v>
+        <v>1.2316</v>
       </c>
       <c r="E109" t="n">
         <v>-0.08790000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>0.6873</v>
+        <v>1.2316</v>
       </c>
       <c r="G109" t="n">
         <v>0.3372</v>
@@ -35533,19 +35533,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.089</v>
+        <v>-0.0238</v>
       </c>
       <c r="C110" t="n">
         <v>-0.7478</v>
       </c>
       <c r="D110" t="n">
-        <v>0.7143</v>
+        <v>0.1502</v>
       </c>
       <c r="E110" t="n">
         <v>-0.0673</v>
       </c>
       <c r="F110" t="n">
-        <v>0.7143</v>
+        <v>0.1502</v>
       </c>
       <c r="G110" t="n">
         <v>0.3704</v>
@@ -35567,19 +35567,19 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.103</v>
+        <v>-0.0191</v>
       </c>
       <c r="C111" t="n">
         <v>-0.7503</v>
       </c>
       <c r="D111" t="n">
-        <v>0.7683</v>
+        <v>0.1583</v>
       </c>
       <c r="E111" t="n">
         <v>-0.0634</v>
       </c>
       <c r="F111" t="n">
-        <v>0.7683</v>
+        <v>0.1583</v>
       </c>
       <c r="G111" t="n">
         <v>0.3386</v>
@@ -35601,19 +35601,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.1304</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="C112" t="n">
         <v>-0.7319</v>
       </c>
       <c r="D112" t="n">
-        <v>0.7642</v>
+        <v>0.16</v>
       </c>
       <c r="E112" t="n">
         <v>-0.028</v>
       </c>
       <c r="F112" t="n">
-        <v>0.7642</v>
+        <v>0.16</v>
       </c>
       <c r="G112" t="n">
         <v>0.4036</v>
@@ -35635,19 +35635,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.1473</v>
+        <v>0.2343</v>
       </c>
       <c r="C113" t="n">
         <v>-0.7782</v>
       </c>
       <c r="D113" t="n">
-        <v>0.8024</v>
+        <v>1.2372</v>
       </c>
       <c r="E113" t="n">
         <v>-0.0165</v>
       </c>
       <c r="F113" t="n">
-        <v>0.8024</v>
+        <v>1.2372</v>
       </c>
       <c r="G113" t="n">
         <v>0.4473</v>
@@ -35669,19 +35669,19 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.1715</v>
+        <v>0.2583</v>
       </c>
       <c r="C114" t="n">
         <v>-0.7962</v>
       </c>
       <c r="D114" t="n">
-        <v>0.8042</v>
+        <v>1.2383</v>
       </c>
       <c r="E114" t="n">
         <v>0.0133</v>
       </c>
       <c r="F114" t="n">
-        <v>0.8042</v>
+        <v>1.2383</v>
       </c>
       <c r="G114" t="n">
         <v>0.4802</v>
@@ -35703,19 +35703,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.1559</v>
+        <v>0.2538</v>
       </c>
       <c r="C115" t="n">
         <v>-0.7749</v>
       </c>
       <c r="D115" t="n">
-        <v>0.7509</v>
+        <v>1.2403</v>
       </c>
       <c r="E115" t="n">
         <v>0.0072</v>
       </c>
       <c r="F115" t="n">
-        <v>0.7509</v>
+        <v>1.2403</v>
       </c>
       <c r="G115" t="n">
         <v>0.4664</v>
@@ -35737,19 +35737,19 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.202</v>
+        <v>0.2956</v>
       </c>
       <c r="C116" t="n">
         <v>-0.7304</v>
       </c>
       <c r="D116" t="n">
-        <v>0.7821</v>
+        <v>1.2498</v>
       </c>
       <c r="E116" t="n">
         <v>0.057</v>
       </c>
       <c r="F116" t="n">
-        <v>0.7821</v>
+        <v>1.2498</v>
       </c>
       <c r="G116" t="n">
         <v>0.4959</v>
@@ -35771,19 +35771,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.1926</v>
+        <v>0.296</v>
       </c>
       <c r="C117" t="n">
         <v>-0.6811</v>
       </c>
       <c r="D117" t="n">
-        <v>0.7349</v>
+        <v>1.2518</v>
       </c>
       <c r="E117" t="n">
         <v>0.057</v>
       </c>
       <c r="F117" t="n">
-        <v>0.7349</v>
+        <v>1.2518</v>
       </c>
       <c r="G117" t="n">
         <v>0.4589</v>
@@ -35805,19 +35805,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.2055</v>
+        <v>0.3215</v>
       </c>
       <c r="C118" t="n">
         <v>-0.6401</v>
       </c>
       <c r="D118" t="n">
-        <v>0.6706</v>
+        <v>1.2507</v>
       </c>
       <c r="E118" t="n">
         <v>0.0892</v>
       </c>
       <c r="F118" t="n">
-        <v>0.6706</v>
+        <v>1.2507</v>
       </c>
       <c r="G118" t="n">
         <v>0.5006</v>
@@ -35839,19 +35839,19 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.2325</v>
+        <v>0.3483</v>
       </c>
       <c r="C119" t="n">
         <v>-0.5545</v>
       </c>
       <c r="D119" t="n">
-        <v>0.6836</v>
+        <v>1.2624</v>
       </c>
       <c r="E119" t="n">
         <v>0.1197</v>
       </c>
       <c r="F119" t="n">
-        <v>0.6836</v>
+        <v>1.2624</v>
       </c>
       <c r="G119" t="n">
         <v>0.5193</v>
@@ -35873,19 +35873,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.2459</v>
+        <v>0.3646</v>
       </c>
       <c r="C120" t="n">
         <v>-0.5393</v>
       </c>
       <c r="D120" t="n">
-        <v>0.6747</v>
+        <v>1.268</v>
       </c>
       <c r="E120" t="n">
         <v>0.1387</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6747</v>
+        <v>1.268</v>
       </c>
       <c r="G120" t="n">
         <v>0.5404</v>
@@ -35907,19 +35907,19 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.2751</v>
+        <v>0.1758</v>
       </c>
       <c r="C121" t="n">
         <v>-0.5256</v>
       </c>
       <c r="D121" t="n">
-        <v>0.7004</v>
+        <v>0.2039</v>
       </c>
       <c r="E121" t="n">
         <v>0.1688</v>
       </c>
       <c r="F121" t="n">
-        <v>0.7004</v>
+        <v>0.2039</v>
       </c>
       <c r="G121" t="n">
         <v>0.5435</v>
@@ -35941,19 +35941,19 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.2644</v>
+        <v>0.3876</v>
       </c>
       <c r="C122" t="n">
         <v>-0.4633</v>
       </c>
       <c r="D122" t="n">
-        <v>0.6814</v>
+        <v>1.297</v>
       </c>
       <c r="E122" t="n">
         <v>0.1602</v>
       </c>
       <c r="F122" t="n">
-        <v>0.6814</v>
+        <v>1.297</v>
       </c>
       <c r="G122" t="n">
         <v>0.5557</v>
@@ -35975,19 +35975,19 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.2413</v>
+        <v>0.3985</v>
       </c>
       <c r="C123" t="n">
         <v>-0.3805</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4897</v>
+        <v>1.2755</v>
       </c>
       <c r="E123" t="n">
         <v>0.1793</v>
       </c>
       <c r="F123" t="n">
-        <v>0.4897</v>
+        <v>1.2755</v>
       </c>
       <c r="G123" t="n">
         <v>0.5780999999999999</v>
@@ -36009,19 +36009,19 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.3149</v>
+        <v>0.4715</v>
       </c>
       <c r="C124" t="n">
         <v>-0.4008</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4938</v>
+        <v>1.2773</v>
       </c>
       <c r="E124" t="n">
         <v>0.2701</v>
       </c>
       <c r="F124" t="n">
-        <v>0.4938</v>
+        <v>1.2773</v>
       </c>
       <c r="G124" t="n">
         <v>0.6389</v>
@@ -36043,19 +36043,19 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.2985</v>
+        <v>0.2439</v>
       </c>
       <c r="C125" t="n">
         <v>-0.3135</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4756</v>
+        <v>0.2026</v>
       </c>
       <c r="E125" t="n">
         <v>0.2543</v>
       </c>
       <c r="F125" t="n">
-        <v>0.4756</v>
+        <v>0.2026</v>
       </c>
       <c r="G125" t="n">
         <v>0.5929</v>
@@ -36077,19 +36077,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.3194</v>
+        <v>0.2703</v>
       </c>
       <c r="C126" t="n">
         <v>-0.3233</v>
       </c>
       <c r="D126" t="n">
-        <v>0.442</v>
+        <v>0.1965</v>
       </c>
       <c r="E126" t="n">
         <v>0.2887</v>
       </c>
       <c r="F126" t="n">
-        <v>0.442</v>
+        <v>0.1965</v>
       </c>
       <c r="G126" t="n">
         <v>0.5956</v>
@@ -36111,19 +36111,19 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3189</v>
+        <v>0.2812</v>
       </c>
       <c r="C127" t="n">
         <v>-0.3127</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3807</v>
+        <v>0.1923</v>
       </c>
       <c r="E127" t="n">
         <v>0.3034</v>
       </c>
       <c r="F127" t="n">
-        <v>0.3807</v>
+        <v>0.1923</v>
       </c>
       <c r="G127" t="n">
         <v>0.6489</v>
@@ -36145,19 +36145,19 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.2998</v>
+        <v>0.2757</v>
       </c>
       <c r="C128" t="n">
         <v>-0.2012</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3134</v>
+        <v>0.1933</v>
       </c>
       <c r="E128" t="n">
         <v>0.2964</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3134</v>
+        <v>0.1933</v>
       </c>
       <c r="G128" t="n">
         <v>0.673</v>
@@ -36179,19 +36179,19 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.2952</v>
+        <v>0.2667</v>
       </c>
       <c r="C129" t="n">
         <v>-0.2455</v>
       </c>
       <c r="D129" t="n">
-        <v>0.3403</v>
+        <v>0.1981</v>
       </c>
       <c r="E129" t="n">
         <v>0.2839</v>
       </c>
       <c r="F129" t="n">
-        <v>0.3403</v>
+        <v>0.1981</v>
       </c>
       <c r="G129" t="n">
         <v>0.661</v>
@@ -36213,19 +36213,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.3005</v>
+        <v>0.2875</v>
       </c>
       <c r="C130" t="n">
         <v>-0.1268</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2665</v>
+        <v>0.2012</v>
       </c>
       <c r="E130" t="n">
         <v>0.3091</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2665</v>
+        <v>0.2012</v>
       </c>
       <c r="G130" t="n">
         <v>0.6983</v>
@@ -36247,19 +36247,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.2929</v>
+        <v>0.2822</v>
       </c>
       <c r="C131" t="n">
         <v>-0.1192</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2596</v>
+        <v>0.2062</v>
       </c>
       <c r="E131" t="n">
         <v>0.3013</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2596</v>
+        <v>0.2062</v>
       </c>
       <c r="G131" t="n">
         <v>0.7432</v>
@@ -36281,19 +36281,19 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.2796</v>
+        <v>0.2811</v>
       </c>
       <c r="C132" t="n">
         <v>-0.0614</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2008</v>
+        <v>0.2087</v>
       </c>
       <c r="E132" t="n">
         <v>0.2992</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2008</v>
+        <v>0.2087</v>
       </c>
       <c r="G132" t="n">
         <v>0.6868</v>
@@ -36315,19 +36315,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3167</v>
+        <v>0.3175</v>
       </c>
       <c r="C133" t="n">
         <v>-0.08550000000000001</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2132</v>
+        <v>0.2175</v>
       </c>
       <c r="E133" t="n">
         <v>0.3425</v>
       </c>
       <c r="F133" t="n">
-        <v>0.2132</v>
+        <v>0.2175</v>
       </c>
       <c r="G133" t="n">
         <v>0.7591</v>
@@ -36349,19 +36349,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.2913</v>
+        <v>0.2962</v>
       </c>
       <c r="C134" t="n">
         <v>-0.0362</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2005</v>
+        <v>0.2247</v>
       </c>
       <c r="E134" t="n">
         <v>0.314</v>
       </c>
       <c r="F134" t="n">
-        <v>0.2005</v>
+        <v>0.2247</v>
       </c>
       <c r="G134" t="n">
         <v>0.7682</v>
@@ -36383,19 +36383,19 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.3465</v>
+        <v>0.3194</v>
       </c>
       <c r="C135" t="n">
         <v>-0.1889</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4217</v>
+        <v>0.2864</v>
       </c>
       <c r="E135" t="n">
         <v>0.3276</v>
       </c>
       <c r="F135" t="n">
-        <v>0.4217</v>
+        <v>0.2864</v>
       </c>
       <c r="G135" t="n">
         <v>0.8167</v>
@@ -36417,19 +36417,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3561</v>
+        <v>0.3323</v>
       </c>
       <c r="C136" t="n">
         <v>-0.1694</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4115</v>
+        <v>0.2926</v>
       </c>
       <c r="E136" t="n">
         <v>0.3423</v>
       </c>
       <c r="F136" t="n">
-        <v>0.4115</v>
+        <v>0.2926</v>
       </c>
       <c r="G136" t="n">
         <v>0.8161</v>
@@ -36451,19 +36451,19 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.3402</v>
+        <v>0.3217</v>
       </c>
       <c r="C137" t="n">
         <v>-0.13</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4004</v>
+        <v>0.3076</v>
       </c>
       <c r="E137" t="n">
         <v>0.3252</v>
       </c>
       <c r="F137" t="n">
-        <v>0.4004</v>
+        <v>0.3076</v>
       </c>
       <c r="G137" t="n">
         <v>0.7715</v>
@@ -36485,19 +36485,19 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.3605</v>
+        <v>0.3342</v>
       </c>
       <c r="C138" t="n">
         <v>-0.092</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4481</v>
+        <v>0.3166</v>
       </c>
       <c r="E138" t="n">
         <v>0.3386</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4481</v>
+        <v>0.3166</v>
       </c>
       <c r="G138" t="n">
         <v>0.8219</v>
@@ -36519,19 +36519,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.39</v>
+        <v>0.3763</v>
       </c>
       <c r="C139" t="n">
         <v>0.0015</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3953</v>
+        <v>0.3268</v>
       </c>
       <c r="E139" t="n">
         <v>0.3887</v>
       </c>
       <c r="F139" t="n">
-        <v>0.3953</v>
+        <v>0.3268</v>
       </c>
       <c r="G139" t="n">
         <v>0.8822</v>
@@ -36553,19 +36553,19 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4081</v>
+        <v>0.3737</v>
       </c>
       <c r="C140" t="n">
         <v>-0.0521</v>
       </c>
       <c r="D140" t="n">
-        <v>0.5268</v>
+        <v>0.3549</v>
       </c>
       <c r="E140" t="n">
         <v>0.3785</v>
       </c>
       <c r="F140" t="n">
-        <v>0.5268</v>
+        <v>0.3549</v>
       </c>
       <c r="G140" t="n">
         <v>0.8445</v>
@@ -36587,19 +36587,19 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3423</v>
+        <v>0.3454</v>
       </c>
       <c r="C141" t="n">
         <v>-0.0198</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2853</v>
+        <v>0.3006</v>
       </c>
       <c r="E141" t="n">
         <v>0.3566</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2853</v>
+        <v>0.3006</v>
       </c>
       <c r="G141" t="n">
         <v>0.7781</v>
@@ -36621,19 +36621,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.3645</v>
+        <v>0.3605</v>
       </c>
       <c r="C142" t="n">
         <v>-0.0544</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3301</v>
+        <v>0.3097</v>
       </c>
       <c r="E142" t="n">
         <v>0.3731</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3301</v>
+        <v>0.3097</v>
       </c>
       <c r="G142" t="n">
         <v>0.8106</v>
@@ -36655,19 +36655,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4007</v>
+        <v>0.3864</v>
       </c>
       <c r="C143" t="n">
         <v>-0.0471</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3922</v>
+        <v>0.321</v>
       </c>
       <c r="E143" t="n">
         <v>0.4028</v>
       </c>
       <c r="F143" t="n">
-        <v>0.3922</v>
+        <v>0.321</v>
       </c>
       <c r="G143" t="n">
         <v>0.8022</v>
@@ -36689,19 +36689,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.399</v>
+        <v>0.4018</v>
       </c>
       <c r="C144" t="n">
         <v>0.0078</v>
       </c>
       <c r="D144" t="n">
-        <v>0.2915</v>
+        <v>0.3052</v>
       </c>
       <c r="E144" t="n">
         <v>0.4259</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2915</v>
+        <v>0.3052</v>
       </c>
       <c r="G144" t="n">
         <v>0.7982</v>
@@ -36723,19 +36723,19 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4212</v>
+        <v>0.4666</v>
       </c>
       <c r="C145" t="n">
         <v>0.0054</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2634</v>
+        <v>0.4904</v>
       </c>
       <c r="E145" t="n">
         <v>0.4607</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2634</v>
+        <v>0.4904</v>
       </c>
       <c r="G145" t="n">
         <v>0.8061</v>
@@ -36757,19 +36757,19 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4127</v>
+        <v>0.4271</v>
       </c>
       <c r="C146" t="n">
         <v>0.0278</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2303</v>
+        <v>0.3023</v>
       </c>
       <c r="E146" t="n">
         <v>0.4583</v>
       </c>
       <c r="F146" t="n">
-        <v>0.2303</v>
+        <v>0.3023</v>
       </c>
       <c r="G146" t="n">
         <v>0.8096</v>
@@ -36791,19 +36791,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4085</v>
+        <v>0.4283</v>
       </c>
       <c r="C147" t="n">
         <v>0.0566</v>
       </c>
       <c r="D147" t="n">
-        <v>0.1965</v>
+        <v>0.2953</v>
       </c>
       <c r="E147" t="n">
         <v>0.4615</v>
       </c>
       <c r="F147" t="n">
-        <v>0.1965</v>
+        <v>0.2953</v>
       </c>
       <c r="G147" t="n">
         <v>0.803</v>
@@ -36825,19 +36825,19 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4241</v>
+        <v>0.4202</v>
       </c>
       <c r="C148" t="n">
         <v>-0.0332</v>
       </c>
       <c r="D148" t="n">
-        <v>0.3263</v>
+        <v>0.3065</v>
       </c>
       <c r="E148" t="n">
         <v>0.4486</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3263</v>
+        <v>0.3065</v>
       </c>
       <c r="G148" t="n">
         <v>0.7075</v>
@@ -36859,19 +36859,19 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4402</v>
+        <v>0.4553</v>
       </c>
       <c r="C149" t="n">
         <v>0.0354</v>
       </c>
       <c r="D149" t="n">
-        <v>0.2162</v>
+        <v>0.2918</v>
       </c>
       <c r="E149" t="n">
         <v>0.4962</v>
       </c>
       <c r="F149" t="n">
-        <v>0.2162</v>
+        <v>0.2918</v>
       </c>
       <c r="G149" t="n">
         <v>0.7519</v>
@@ -36893,19 +36893,19 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4283</v>
+        <v>0.4579</v>
       </c>
       <c r="C150" t="n">
         <v>0.0617</v>
       </c>
       <c r="D150" t="n">
-        <v>0.1319</v>
+        <v>0.2799</v>
       </c>
       <c r="E150" t="n">
         <v>0.5024</v>
       </c>
       <c r="F150" t="n">
-        <v>0.1319</v>
+        <v>0.2799</v>
       </c>
       <c r="G150" t="n">
         <v>0.7962</v>
@@ -36927,19 +36927,19 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4238</v>
+        <v>0.4557</v>
       </c>
       <c r="C151" t="n">
         <v>0.0464</v>
       </c>
       <c r="D151" t="n">
-        <v>0.1061</v>
+        <v>0.2655</v>
       </c>
       <c r="E151" t="n">
         <v>0.5033</v>
       </c>
       <c r="F151" t="n">
-        <v>0.1061</v>
+        <v>0.2655</v>
       </c>
       <c r="G151" t="n">
         <v>0.7719</v>
@@ -36961,19 +36961,19 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.437</v>
+        <v>0.4758</v>
       </c>
       <c r="C152" t="n">
         <v>0.0346</v>
       </c>
       <c r="D152" t="n">
-        <v>0.064</v>
+        <v>0.258</v>
       </c>
       <c r="E152" t="n">
         <v>0.5303</v>
       </c>
       <c r="F152" t="n">
-        <v>0.064</v>
+        <v>0.258</v>
       </c>
       <c r="G152" t="n">
         <v>0.7383999999999999</v>
@@ -36995,19 +36995,19 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4453</v>
+        <v>0.4721</v>
       </c>
       <c r="C153" t="n">
         <v>-0.0031</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1322</v>
+        <v>0.266</v>
       </c>
       <c r="E153" t="n">
         <v>0.5236</v>
       </c>
       <c r="F153" t="n">
-        <v>0.1322</v>
+        <v>0.266</v>
       </c>
       <c r="G153" t="n">
         <v>0.7215</v>
@@ -37029,19 +37029,19 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4614</v>
+        <v>0.4911</v>
       </c>
       <c r="C154" t="n">
         <v>-0.0027</v>
       </c>
       <c r="D154" t="n">
-        <v>0.1254</v>
+        <v>0.2741</v>
       </c>
       <c r="E154" t="n">
         <v>0.5454</v>
       </c>
       <c r="F154" t="n">
-        <v>0.1254</v>
+        <v>0.2741</v>
       </c>
       <c r="G154" t="n">
         <v>0.7735</v>
@@ -37063,19 +37063,19 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4824</v>
+        <v>0.5138</v>
       </c>
       <c r="C155" t="n">
         <v>0.0039</v>
       </c>
       <c r="D155" t="n">
-        <v>0.1119</v>
+        <v>0.2689</v>
       </c>
       <c r="E155" t="n">
         <v>0.575</v>
       </c>
       <c r="F155" t="n">
-        <v>0.1119</v>
+        <v>0.2689</v>
       </c>
       <c r="G155" t="n">
         <v>0.7146</v>
@@ -37097,19 +37097,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4658</v>
+        <v>0.5806</v>
       </c>
       <c r="C156" t="n">
         <v>0.0403</v>
       </c>
       <c r="D156" t="n">
-        <v>0.1753</v>
+        <v>0.749</v>
       </c>
       <c r="E156" t="n">
         <v>0.5385</v>
       </c>
       <c r="F156" t="n">
-        <v>0.1753</v>
+        <v>0.749</v>
       </c>
       <c r="G156" t="n">
         <v>0.6449</v>
@@ -37131,19 +37131,19 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.4676</v>
+        <v>0.6353</v>
       </c>
       <c r="C157" t="n">
         <v>0.0832</v>
       </c>
       <c r="D157" t="n">
-        <v>0.0535</v>
+        <v>0.892</v>
       </c>
       <c r="E157" t="n">
         <v>0.5711000000000001</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0535</v>
+        <v>0.892</v>
       </c>
       <c r="G157" t="n">
         <v>0.7252999999999999</v>
@@ -37165,19 +37165,19 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.5081</v>
+        <v>0.6395</v>
       </c>
       <c r="C158" t="n">
         <v>0.0692</v>
       </c>
       <c r="D158" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="E158" t="n">
         <v>0.6163</v>
       </c>
       <c r="F158" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.732</v>
       </c>
       <c r="G158" t="n">
         <v>0.6758999999999999</v>
@@ -37199,19 +37199,19 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.4806</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="C159" t="n">
         <v>0.06859999999999999</v>
       </c>
       <c r="D159" t="n">
-        <v>0.0877</v>
+        <v>0.7368</v>
       </c>
       <c r="E159" t="n">
         <v>0.5788</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0877</v>
+        <v>0.7368</v>
       </c>
       <c r="G159" t="n">
         <v>0.6565</v>
@@ -37233,19 +37233,19 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.5108</v>
+        <v>0.6413</v>
       </c>
       <c r="C160" t="n">
         <v>0.0706</v>
       </c>
       <c r="D160" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.7411</v>
       </c>
       <c r="E160" t="n">
         <v>0.6163</v>
       </c>
       <c r="F160" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.7411</v>
       </c>
       <c r="G160" t="n">
         <v>0.6683</v>
@@ -37267,19 +37267,19 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.5138</v>
+        <v>0.6437</v>
       </c>
       <c r="C161" t="n">
         <v>0.0267</v>
       </c>
       <c r="D161" t="n">
-        <v>0.0887</v>
+        <v>0.7383</v>
       </c>
       <c r="E161" t="n">
         <v>0.6201</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0887</v>
+        <v>0.7383</v>
       </c>
       <c r="G161" t="n">
         <v>0.6515</v>
@@ -37301,19 +37301,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.5311</v>
+        <v>0.6655</v>
       </c>
       <c r="C162" t="n">
         <v>0.0395</v>
       </c>
       <c r="D162" t="n">
-        <v>0.0641</v>
+        <v>0.7363</v>
       </c>
       <c r="E162" t="n">
         <v>0.6478</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0641</v>
+        <v>0.7363</v>
       </c>
       <c r="G162" t="n">
         <v>0.6607</v>
@@ -37335,19 +37335,19 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.5456</v>
+        <v>0.6855</v>
       </c>
       <c r="C163" t="n">
         <v>0.0508</v>
       </c>
       <c r="D163" t="n">
-        <v>0.036</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="E163" t="n">
         <v>0.673</v>
       </c>
       <c r="F163" t="n">
-        <v>0.036</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="G163" t="n">
         <v>0.6604</v>
@@ -37369,19 +37369,19 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.5429</v>
+        <v>0.6847</v>
       </c>
       <c r="C164" t="n">
         <v>0.0608</v>
       </c>
       <c r="D164" t="n">
-        <v>0.0241</v>
+        <v>0.7333</v>
       </c>
       <c r="E164" t="n">
         <v>0.6726</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0241</v>
+        <v>0.7333</v>
       </c>
       <c r="G164" t="n">
         <v>0.6538</v>
@@ -37403,19 +37403,19 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.5616</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="C165" t="n">
         <v>0.0791</v>
       </c>
       <c r="D165" t="n">
-        <v>0.0174</v>
+        <v>0.7249</v>
       </c>
       <c r="E165" t="n">
         <v>0.6976</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0174</v>
+        <v>0.7249</v>
       </c>
       <c r="G165" t="n">
         <v>0.644</v>
@@ -37437,19 +37437,19 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.5599</v>
+        <v>0.7068</v>
       </c>
       <c r="C166" t="n">
         <v>0.0968</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.0123</v>
+        <v>0.7225</v>
       </c>
       <c r="E166" t="n">
         <v>0.7029</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.0123</v>
+        <v>0.7225</v>
       </c>
       <c r="G166" t="n">
         <v>0.6281</v>
@@ -37471,19 +37471,19 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.5789</v>
+        <v>0.7208</v>
       </c>
       <c r="C167" t="n">
         <v>0.0367</v>
       </c>
       <c r="D167" t="n">
-        <v>0.0156</v>
+        <v>0.7251</v>
       </c>
       <c r="E167" t="n">
         <v>0.7197</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0156</v>
+        <v>0.7251</v>
       </c>
       <c r="G167" t="n">
         <v>0.6152</v>
@@ -37505,19 +37505,19 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.599</v>
+        <v>0.6392</v>
       </c>
       <c r="C168" t="n">
         <v>0.0575</v>
       </c>
       <c r="D168" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="E168" t="n">
         <v>0.7325</v>
       </c>
       <c r="F168" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="G168" t="n">
         <v>0.6413</v>
@@ -37539,19 +37539,19 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.5724</v>
+        <v>0.8257</v>
       </c>
       <c r="C169" t="n">
         <v>0.0494</v>
       </c>
       <c r="D169" t="n">
-        <v>0.07340000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="E169" t="n">
         <v>0.6972</v>
       </c>
       <c r="F169" t="n">
-        <v>0.07340000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="G169" t="n">
         <v>0.5735</v>
@@ -37573,19 +37573,19 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.605</v>
+        <v>0.9275</v>
       </c>
       <c r="C170" t="n">
         <v>0.0779</v>
       </c>
       <c r="D170" t="n">
-        <v>0.09080000000000001</v>
+        <v>1.7034</v>
       </c>
       <c r="E170" t="n">
         <v>0.7335</v>
       </c>
       <c r="F170" t="n">
-        <v>0.09080000000000001</v>
+        <v>1.7034</v>
       </c>
       <c r="G170" t="n">
         <v>0.63</v>
@@ -37607,19 +37607,19 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.5897</v>
+        <v>0.916</v>
       </c>
       <c r="C171" t="n">
         <v>0.1262</v>
       </c>
       <c r="D171" t="n">
-        <v>0.07779999999999999</v>
+        <v>1.7091</v>
       </c>
       <c r="E171" t="n">
         <v>0.7177</v>
       </c>
       <c r="F171" t="n">
-        <v>0.07779999999999999</v>
+        <v>1.7091</v>
       </c>
       <c r="G171" t="n">
         <v>0.5918</v>
@@ -37641,19 +37641,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.9529</v>
       </c>
       <c r="C172" t="n">
         <v>0.0791</v>
       </c>
       <c r="D172" t="n">
-        <v>0.1045</v>
+        <v>1.7061</v>
       </c>
       <c r="E172" t="n">
         <v>0.7645999999999999</v>
       </c>
       <c r="F172" t="n">
-        <v>0.1045</v>
+        <v>1.7061</v>
       </c>
       <c r="G172" t="n">
         <v>0.575</v>
@@ -37675,19 +37675,19 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.6088</v>
+        <v>0.9424</v>
       </c>
       <c r="C173" t="n">
         <v>0.1374</v>
       </c>
       <c r="D173" t="n">
-        <v>0.0385</v>
+        <v>1.7062</v>
       </c>
       <c r="E173" t="n">
         <v>0.7514</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0385</v>
+        <v>1.7062</v>
       </c>
       <c r="G173" t="n">
         <v>0.571</v>
@@ -37709,19 +37709,19 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.6277</v>
+        <v>0.9591</v>
       </c>
       <c r="C174" t="n">
         <v>0.143</v>
       </c>
       <c r="D174" t="n">
-        <v>0.0511</v>
+        <v>1.7076</v>
       </c>
       <c r="E174" t="n">
         <v>0.7719</v>
       </c>
       <c r="F174" t="n">
-        <v>0.0511</v>
+        <v>1.7076</v>
       </c>
       <c r="G174" t="n">
         <v>0.602</v>
@@ -37743,19 +37743,19 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.6462</v>
+        <v>0.9705</v>
       </c>
       <c r="C175" t="n">
         <v>0.1453</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1043</v>
+        <v>1.7257</v>
       </c>
       <c r="E175" t="n">
         <v>0.7817</v>
       </c>
       <c r="F175" t="n">
-        <v>0.1043</v>
+        <v>1.7257</v>
       </c>
       <c r="G175" t="n">
         <v>0.5315</v>
@@ -37777,19 +37777,19 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.6613</v>
+        <v>0.9832</v>
       </c>
       <c r="C176" t="n">
         <v>0.1387</v>
       </c>
       <c r="D176" t="n">
-        <v>0.1169</v>
+        <v>1.7265</v>
       </c>
       <c r="E176" t="n">
         <v>0.7973</v>
       </c>
       <c r="F176" t="n">
-        <v>0.1169</v>
+        <v>1.7265</v>
       </c>
       <c r="G176" t="n">
         <v>0.6004</v>
@@ -37811,19 +37811,19 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.9727</v>
       </c>
       <c r="C177" t="n">
         <v>0.077</v>
       </c>
       <c r="D177" t="n">
-        <v>0.2673</v>
+        <v>1.7513</v>
       </c>
       <c r="E177" t="n">
         <v>0.778</v>
       </c>
       <c r="F177" t="n">
-        <v>0.2673</v>
+        <v>1.7513</v>
       </c>
       <c r="G177" t="n">
         <v>0.5423</v>
@@ -37845,19 +37845,19 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.5881</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="C178" t="n">
         <v>0.1453</v>
       </c>
       <c r="D178" t="n">
-        <v>0.242</v>
+        <v>1.7593</v>
       </c>
       <c r="E178" t="n">
         <v>0.6747</v>
       </c>
       <c r="F178" t="n">
-        <v>0.242</v>
+        <v>1.7593</v>
       </c>
       <c r="G178" t="n">
         <v>0.5137</v>
@@ -37879,19 +37879,19 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.6005</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="C179" t="n">
         <v>0.0901</v>
       </c>
       <c r="D179" t="n">
-        <v>0.2574</v>
+        <v>1.7488</v>
       </c>
       <c r="E179" t="n">
         <v>0.6862</v>
       </c>
       <c r="F179" t="n">
-        <v>0.2574</v>
+        <v>1.7488</v>
       </c>
       <c r="G179" t="n">
         <v>0.5649</v>
@@ -37913,19 +37913,19 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.5421</v>
+        <v>0.8724</v>
       </c>
       <c r="C180" t="n">
         <v>0.1644</v>
       </c>
       <c r="D180" t="n">
-        <v>0.0689</v>
+        <v>1.7201</v>
       </c>
       <c r="E180" t="n">
         <v>0.6604</v>
       </c>
       <c r="F180" t="n">
-        <v>0.0689</v>
+        <v>1.7201</v>
       </c>
       <c r="G180" t="n">
         <v>0.493</v>
@@ -37947,19 +37947,19 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.4649</v>
+        <v>0.5235</v>
       </c>
       <c r="C181" t="n">
         <v>0.1263</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.0198</v>
+        <v>0.2734</v>
       </c>
       <c r="E181" t="n">
         <v>0.5861</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.0198</v>
+        <v>0.2734</v>
       </c>
       <c r="G181" t="n">
         <v>0.5058</v>
@@ -37981,19 +37981,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.484</v>
+        <v>0.5381</v>
       </c>
       <c r="C182" t="n">
         <v>0.1088</v>
       </c>
       <c r="D182" t="n">
-        <v>0.0031</v>
+        <v>0.2734</v>
       </c>
       <c r="E182" t="n">
         <v>0.6042999999999999</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0031</v>
+        <v>0.2734</v>
       </c>
       <c r="G182" t="n">
         <v>0.5013</v>
@@ -38015,19 +38015,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.5117</v>
+        <v>0.5604</v>
       </c>
       <c r="C183" t="n">
         <v>0.1094</v>
       </c>
       <c r="D183" t="n">
-        <v>0.0433</v>
+        <v>0.2868</v>
       </c>
       <c r="E183" t="n">
         <v>0.6288</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0433</v>
+        <v>0.2868</v>
       </c>
       <c r="G183" t="n">
         <v>0.5104</v>
@@ -38049,19 +38049,19 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.3779</v>
+        <v>0.4191</v>
       </c>
       <c r="C184" t="n">
         <v>0.1333</v>
       </c>
       <c r="D184" t="n">
-        <v>0.0936</v>
+        <v>0.2994</v>
       </c>
       <c r="E184" t="n">
         <v>0.449</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0936</v>
+        <v>0.2994</v>
       </c>
       <c r="G184" t="n">
         <v>0.4914</v>
@@ -38083,19 +38083,19 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.3685</v>
+        <v>0.4283</v>
       </c>
       <c r="C185" t="n">
         <v>0.1307</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.0196</v>
+        <v>0.2795</v>
       </c>
       <c r="E185" t="n">
         <v>0.4655</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.0196</v>
+        <v>0.2795</v>
       </c>
       <c r="G185" t="n">
         <v>0.502</v>
@@ -38117,19 +38117,19 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.3866</v>
+        <v>0.4513</v>
       </c>
       <c r="C186" t="n">
         <v>0.1936</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.0406</v>
+        <v>0.2826</v>
       </c>
       <c r="E186" t="n">
         <v>0.4934</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.0406</v>
+        <v>0.2826</v>
       </c>
       <c r="G186" t="n">
         <v>0.4752</v>
@@ -38151,19 +38151,19 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.3567</v>
+        <v>0.4099</v>
       </c>
       <c r="C187" t="n">
         <v>0.1223</v>
       </c>
       <c r="D187" t="n">
-        <v>0.0125</v>
+        <v>0.278</v>
       </c>
       <c r="E187" t="n">
         <v>0.4428</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0125</v>
+        <v>0.278</v>
       </c>
       <c r="G187" t="n">
         <v>0.5037</v>
@@ -38185,19 +38185,19 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.3252</v>
+        <v>0.3682</v>
       </c>
       <c r="C188" t="n">
         <v>0.09</v>
       </c>
       <c r="D188" t="n">
-        <v>0.0614</v>
+        <v>0.2764</v>
       </c>
       <c r="E188" t="n">
         <v>0.3912</v>
       </c>
       <c r="F188" t="n">
-        <v>0.0614</v>
+        <v>0.2764</v>
       </c>
       <c r="G188" t="n">
         <v>0.4843</v>
@@ -38219,19 +38219,19 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.2822</v>
+        <v>0.3332</v>
       </c>
       <c r="C189" t="n">
         <v>0.0852</v>
       </c>
       <c r="D189" t="n">
-        <v>0.0117</v>
+        <v>0.2668</v>
       </c>
       <c r="E189" t="n">
         <v>0.3498</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0117</v>
+        <v>0.2668</v>
       </c>
       <c r="G189" t="n">
         <v>0.5167</v>
@@ -38253,19 +38253,19 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.3077</v>
+        <v>0.3325</v>
       </c>
       <c r="C190" t="n">
         <v>-0.0179</v>
       </c>
       <c r="D190" t="n">
-        <v>0.1474</v>
+        <v>0.2712</v>
       </c>
       <c r="E190" t="n">
         <v>0.3478</v>
       </c>
       <c r="F190" t="n">
-        <v>0.1474</v>
+        <v>0.2712</v>
       </c>
       <c r="G190" t="n">
         <v>0.5373</v>
@@ -38287,19 +38287,19 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.2939</v>
+        <v>0.3092</v>
       </c>
       <c r="C191" t="n">
         <v>-0.0464</v>
       </c>
       <c r="D191" t="n">
-        <v>0.1937</v>
+        <v>0.2705</v>
       </c>
       <c r="E191" t="n">
         <v>0.3189</v>
       </c>
       <c r="F191" t="n">
-        <v>0.1937</v>
+        <v>0.2705</v>
       </c>
       <c r="G191" t="n">
         <v>0.5974</v>
@@ -38321,19 +38321,19 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.2709</v>
+        <v>0.28</v>
       </c>
       <c r="C192" t="n">
         <v>-0.1013</v>
       </c>
       <c r="D192" t="n">
-        <v>0.2267</v>
+        <v>0.2725</v>
       </c>
       <c r="E192" t="n">
         <v>0.2819</v>
       </c>
       <c r="F192" t="n">
-        <v>0.2267</v>
+        <v>0.2725</v>
       </c>
       <c r="G192" t="n">
         <v>0.6135</v>
@@ -38355,19 +38355,19 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2891</v>
+        <v>0.5341</v>
       </c>
       <c r="C193" t="n">
         <v>-0.1619</v>
       </c>
       <c r="D193" t="n">
-        <v>0.2657</v>
+        <v>1.4907</v>
       </c>
       <c r="E193" t="n">
         <v>0.295</v>
       </c>
       <c r="F193" t="n">
-        <v>0.2657</v>
+        <v>1.4907</v>
       </c>
       <c r="G193" t="n">
         <v>0.576</v>
@@ -38389,19 +38389,19 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.2537</v>
+        <v>0.2507</v>
       </c>
       <c r="C194" t="n">
         <v>-0.181</v>
       </c>
       <c r="D194" t="n">
-        <v>0.2828</v>
+        <v>0.2676</v>
       </c>
       <c r="E194" t="n">
         <v>0.2465</v>
       </c>
       <c r="F194" t="n">
-        <v>0.2828</v>
+        <v>0.2676</v>
       </c>
       <c r="G194" t="n">
         <v>0.611</v>
@@ -38423,19 +38423,19 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.2245</v>
+        <v>0.2179</v>
       </c>
       <c r="C195" t="n">
         <v>-0.2154</v>
       </c>
       <c r="D195" t="n">
-        <v>0.2943</v>
+        <v>0.2613</v>
       </c>
       <c r="E195" t="n">
         <v>0.207</v>
       </c>
       <c r="F195" t="n">
-        <v>0.2943</v>
+        <v>0.2613</v>
       </c>
       <c r="G195" t="n">
         <v>0.6015</v>
@@ -38457,19 +38457,19 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.2455</v>
+        <v>0.2229</v>
       </c>
       <c r="C196" t="n">
         <v>-0.3056</v>
       </c>
       <c r="D196" t="n">
-        <v>0.3739</v>
+        <v>0.2608</v>
       </c>
       <c r="E196" t="n">
         <v>0.2134</v>
       </c>
       <c r="F196" t="n">
-        <v>0.3739</v>
+        <v>0.2608</v>
       </c>
       <c r="G196" t="n">
         <v>0.6501</v>
@@ -38491,19 +38491,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.2551</v>
+        <v>0.2123</v>
       </c>
       <c r="C197" t="n">
         <v>-0.3788</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4765</v>
+        <v>0.2628</v>
       </c>
       <c r="E197" t="n">
         <v>0.1997</v>
       </c>
       <c r="F197" t="n">
-        <v>0.4765</v>
+        <v>0.2628</v>
       </c>
       <c r="G197" t="n">
         <v>0.7177</v>
@@ -38525,19 +38525,19 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.1969</v>
+        <v>0.1451</v>
       </c>
       <c r="C198" t="n">
         <v>-0.4015</v>
       </c>
       <c r="D198" t="n">
-        <v>0.5223</v>
+        <v>0.2634</v>
       </c>
       <c r="E198" t="n">
         <v>0.1155</v>
       </c>
       <c r="F198" t="n">
-        <v>0.5223</v>
+        <v>0.2634</v>
       </c>
       <c r="G198" t="n">
         <v>0.681</v>
@@ -38559,19 +38559,19 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.1878</v>
+        <v>0.1335</v>
       </c>
       <c r="C199" t="n">
         <v>-0.4651</v>
       </c>
       <c r="D199" t="n">
-        <v>0.5347</v>
+        <v>0.2634</v>
       </c>
       <c r="E199" t="n">
         <v>0.1011</v>
       </c>
       <c r="F199" t="n">
-        <v>0.5347</v>
+        <v>0.2634</v>
       </c>
       <c r="G199" t="n">
         <v>0.6879999999999999</v>
@@ -38593,19 +38593,19 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.2208</v>
+        <v>0.4672</v>
       </c>
       <c r="C200" t="n">
         <v>-0.5458</v>
       </c>
       <c r="D200" t="n">
-        <v>0.6271</v>
+        <v>1.8588</v>
       </c>
       <c r="E200" t="n">
         <v>0.1193</v>
       </c>
       <c r="F200" t="n">
-        <v>0.6271</v>
+        <v>1.8588</v>
       </c>
       <c r="G200" t="n">
         <v>0.7059</v>
@@ -38627,19 +38627,19 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.2643</v>
+        <v>0.4879</v>
       </c>
       <c r="C201" t="n">
         <v>-0.6249</v>
       </c>
       <c r="D201" t="n">
-        <v>0.744</v>
+        <v>1.8623</v>
       </c>
       <c r="E201" t="n">
         <v>0.1443</v>
       </c>
       <c r="F201" t="n">
-        <v>0.744</v>
+        <v>1.8623</v>
       </c>
       <c r="G201" t="n">
         <v>0.7361</v>
@@ -38661,19 +38661,19 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.3739</v>
+        <v>0.5971</v>
       </c>
       <c r="C202" t="n">
         <v>-0.6512</v>
       </c>
       <c r="D202" t="n">
-        <v>0.7395</v>
+        <v>1.8556</v>
       </c>
       <c r="E202" t="n">
         <v>0.2825</v>
       </c>
       <c r="F202" t="n">
-        <v>0.7395</v>
+        <v>1.8556</v>
       </c>
       <c r="G202" t="n">
         <v>0.7568</v>
@@ -38695,19 +38695,19 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.344</v>
+        <v>0.5603</v>
       </c>
       <c r="C203" t="n">
         <v>-0.6737</v>
       </c>
       <c r="D203" t="n">
-        <v>0.7685999999999999</v>
+        <v>1.8501</v>
       </c>
       <c r="E203" t="n">
         <v>0.2378</v>
       </c>
       <c r="F203" t="n">
-        <v>0.7685999999999999</v>
+        <v>1.8501</v>
       </c>
       <c r="G203" t="n">
         <v>0.6739000000000001</v>
@@ -38729,19 +38729,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3969</v>
+        <v>0.6026</v>
       </c>
       <c r="C204" t="n">
         <v>-0.7195</v>
       </c>
       <c r="D204" t="n">
-        <v>0.8247</v>
+        <v>1.8529</v>
       </c>
       <c r="E204" t="n">
         <v>0.29</v>
       </c>
       <c r="F204" t="n">
-        <v>0.8247</v>
+        <v>1.8529</v>
       </c>
       <c r="G204" t="n">
         <v>0.7415</v>
@@ -38763,19 +38763,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.4468</v>
+        <v>0.3971</v>
       </c>
       <c r="C205" t="n">
         <v>-0.8053</v>
       </c>
       <c r="D205" t="n">
-        <v>0.868</v>
+        <v>0.619</v>
       </c>
       <c r="E205" t="n">
         <v>0.3416</v>
       </c>
       <c r="F205" t="n">
-        <v>0.868</v>
+        <v>0.619</v>
       </c>
       <c r="G205" t="n">
         <v>0.7791</v>
@@ -38797,19 +38797,19 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.4767</v>
+        <v>0.664</v>
       </c>
       <c r="C206" t="n">
         <v>-0.8897</v>
       </c>
       <c r="D206" t="n">
-        <v>0.9009</v>
+        <v>1.8374</v>
       </c>
       <c r="E206" t="n">
         <v>0.3707</v>
       </c>
       <c r="F206" t="n">
-        <v>0.9009</v>
+        <v>1.8374</v>
       </c>
       <c r="G206" t="n">
         <v>0.7759</v>
@@ -38831,19 +38831,19 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.4742</v>
+        <v>0.669</v>
       </c>
       <c r="C207" t="n">
         <v>-0.9205</v>
       </c>
       <c r="D207" t="n">
-        <v>0.8477</v>
+        <v>1.8218</v>
       </c>
       <c r="E207" t="n">
         <v>0.3808</v>
       </c>
       <c r="F207" t="n">
-        <v>0.8477</v>
+        <v>1.8218</v>
       </c>
       <c r="G207" t="n">
         <v>0.8046</v>
@@ -38865,19 +38865,19 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.5149</v>
+        <v>0.7047</v>
       </c>
       <c r="C208" t="n">
         <v>-0.9116</v>
       </c>
       <c r="D208" t="n">
-        <v>0.8717</v>
+        <v>1.8206</v>
       </c>
       <c r="E208" t="n">
         <v>0.4257</v>
       </c>
       <c r="F208" t="n">
-        <v>0.8717</v>
+        <v>1.8206</v>
       </c>
       <c r="G208" t="n">
         <v>0.7591</v>
@@ -38899,19 +38899,19 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.7456</v>
       </c>
       <c r="C209" t="n">
         <v>-0.9821</v>
       </c>
       <c r="D209" t="n">
-        <v>0.9457</v>
+        <v>1.8232</v>
       </c>
       <c r="E209" t="n">
         <v>0.4762</v>
       </c>
       <c r="F209" t="n">
-        <v>0.9457</v>
+        <v>1.8232</v>
       </c>
       <c r="G209" t="n">
         <v>0.8551</v>
@@ -38933,19 +38933,19 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.5812</v>
+        <v>0.7395</v>
       </c>
       <c r="C210" t="n">
         <v>-1.0519</v>
       </c>
       <c r="D210" t="n">
-        <v>1.0316</v>
+        <v>1.8235</v>
       </c>
       <c r="E210" t="n">
         <v>0.4686</v>
       </c>
       <c r="F210" t="n">
-        <v>1.0316</v>
+        <v>1.8235</v>
       </c>
       <c r="G210" t="n">
         <v>0.7999000000000001</v>
@@ -38967,19 +38967,19 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.6523</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="C211" t="n">
         <v>-1.1482</v>
       </c>
       <c r="D211" t="n">
-        <v>1.0913</v>
+        <v>1.8244</v>
       </c>
       <c r="E211" t="n">
         <v>0.5426</v>
       </c>
       <c r="F211" t="n">
-        <v>1.0913</v>
+        <v>1.8244</v>
       </c>
       <c r="G211" t="n">
         <v>0.8531</v>
@@ -39001,19 +39001,19 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.6642</v>
+        <v>0.4745</v>
       </c>
       <c r="C212" t="n">
         <v>-1.183</v>
       </c>
       <c r="D212" t="n">
-        <v>1.1891</v>
+        <v>0.2407</v>
       </c>
       <c r="E212" t="n">
         <v>0.533</v>
       </c>
       <c r="F212" t="n">
-        <v>1.1891</v>
+        <v>0.2407</v>
       </c>
       <c r="G212" t="n">
         <v>0.8335</v>
@@ -39035,19 +39035,19 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.6992</v>
+        <v>0.5017</v>
       </c>
       <c r="C213" t="n">
         <v>-1.1636</v>
       </c>
       <c r="D213" t="n">
-        <v>1.2344</v>
+        <v>0.2468</v>
       </c>
       <c r="E213" t="n">
         <v>0.5654</v>
       </c>
       <c r="F213" t="n">
-        <v>1.2344</v>
+        <v>0.2468</v>
       </c>
       <c r="G213" t="n">
         <v>0.8457</v>
@@ -39069,19 +39069,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.5566</v>
       </c>
       <c r="C214" t="n">
         <v>-1.2622</v>
       </c>
       <c r="D214" t="n">
-        <v>1.2519</v>
+        <v>0.2368</v>
       </c>
       <c r="E214" t="n">
         <v>0.6366000000000001</v>
       </c>
       <c r="F214" t="n">
-        <v>1.2519</v>
+        <v>0.2368</v>
       </c>
       <c r="G214" t="n">
         <v>0.8861</v>
@@ -39103,19 +39103,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.7688</v>
+        <v>0.5542</v>
       </c>
       <c r="C215" t="n">
         <v>-1.3419</v>
       </c>
       <c r="D215" t="n">
-        <v>1.3042</v>
+        <v>0.2311</v>
       </c>
       <c r="E215" t="n">
         <v>0.6349</v>
       </c>
       <c r="F215" t="n">
-        <v>1.3042</v>
+        <v>0.2311</v>
       </c>
       <c r="G215" t="n">
         <v>0.9217</v>
@@ -39137,19 +39137,19 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.7638</v>
+        <v>0.5416</v>
       </c>
       <c r="C216" t="n">
         <v>-1.4045</v>
       </c>
       <c r="D216" t="n">
-        <v>1.3379</v>
+        <v>0.2272</v>
       </c>
       <c r="E216" t="n">
         <v>0.6202</v>
       </c>
       <c r="F216" t="n">
-        <v>1.3379</v>
+        <v>0.2272</v>
       </c>
       <c r="G216" t="n">
         <v>0.8875999999999999</v>
@@ -39171,19 +39171,19 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.7983</v>
+        <v>1.1129</v>
       </c>
       <c r="C217" t="n">
         <v>-1.4378</v>
       </c>
       <c r="D217" t="n">
-        <v>1.2936</v>
+        <v>2.8667</v>
       </c>
       <c r="E217" t="n">
         <v>0.6744</v>
       </c>
       <c r="F217" t="n">
-        <v>1.2936</v>
+        <v>2.8667</v>
       </c>
       <c r="G217" t="n">
         <v>0.8515</v>
@@ -39205,19 +39205,19 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.7962</v>
+        <v>0.5685</v>
       </c>
       <c r="C218" t="n">
         <v>-1.5256</v>
       </c>
       <c r="D218" t="n">
-        <v>1.3264</v>
+        <v>0.1879</v>
       </c>
       <c r="E218" t="n">
         <v>0.6636</v>
       </c>
       <c r="F218" t="n">
-        <v>1.3264</v>
+        <v>0.1879</v>
       </c>
       <c r="G218" t="n">
         <v>0.8427</v>
@@ -39239,19 +39239,19 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8734</v>
+        <v>0.6099</v>
       </c>
       <c r="C219" t="n">
         <v>-1.6152</v>
       </c>
       <c r="D219" t="n">
-        <v>1.5172</v>
+        <v>0.1996</v>
       </c>
       <c r="E219" t="n">
         <v>0.7125</v>
       </c>
       <c r="F219" t="n">
-        <v>1.5172</v>
+        <v>0.1996</v>
       </c>
       <c r="G219" t="n">
         <v>0.8703</v>
@@ -39273,19 +39273,19 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.9449</v>
+        <v>0.6502</v>
       </c>
       <c r="C220" t="n">
         <v>-1.7821</v>
       </c>
       <c r="D220" t="n">
-        <v>1.6893</v>
+        <v>0.2157</v>
       </c>
       <c r="E220" t="n">
         <v>0.7588</v>
       </c>
       <c r="F220" t="n">
-        <v>1.6893</v>
+        <v>0.2157</v>
       </c>
       <c r="G220" t="n">
         <v>0.8859</v>
@@ -39307,19 +39307,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.9714</v>
+        <v>0.6563</v>
       </c>
       <c r="C221" t="n">
         <v>-1.8481</v>
       </c>
       <c r="D221" t="n">
-        <v>1.7852</v>
+        <v>0.2098</v>
       </c>
       <c r="E221" t="n">
         <v>0.768</v>
       </c>
       <c r="F221" t="n">
-        <v>1.7852</v>
+        <v>0.2098</v>
       </c>
       <c r="G221" t="n">
         <v>0.8721</v>
@@ -39341,19 +39341,19 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1.0038</v>
+        <v>0.9575</v>
       </c>
       <c r="C222" t="n">
         <v>-1.9645</v>
       </c>
       <c r="D222" t="n">
-        <v>1.9403</v>
+        <v>1.7086</v>
       </c>
       <c r="E222" t="n">
         <v>0.7697000000000001</v>
       </c>
       <c r="F222" t="n">
-        <v>1.9403</v>
+        <v>1.7086</v>
       </c>
       <c r="G222" t="n">
         <v>0.8974</v>
@@ -39375,19 +39375,19 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1.0645</v>
+        <v>1.1487</v>
       </c>
       <c r="C223" t="n">
         <v>-2.078</v>
       </c>
       <c r="D223" t="n">
-        <v>2.0727</v>
+        <v>2.4933</v>
       </c>
       <c r="E223" t="n">
         <v>0.8125</v>
       </c>
       <c r="F223" t="n">
-        <v>2.0727</v>
+        <v>2.4933</v>
       </c>
       <c r="G223" t="n">
         <v>0.886</v>
@@ -39409,19 +39409,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>1.071</v>
+        <v>1.3289</v>
       </c>
       <c r="C224" t="n">
         <v>-2.0636</v>
       </c>
       <c r="D224" t="n">
-        <v>2.0444</v>
+        <v>3.3341</v>
       </c>
       <c r="E224" t="n">
         <v>0.8276</v>
       </c>
       <c r="F224" t="n">
-        <v>2.0444</v>
+        <v>3.3341</v>
       </c>
       <c r="G224" t="n">
         <v>0.8925</v>
@@ -39443,19 +39443,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1.0637</v>
+        <v>1.3271</v>
       </c>
       <c r="C225" t="n">
         <v>-2.0644</v>
       </c>
       <c r="D225" t="n">
-        <v>1.9872</v>
+        <v>3.3043</v>
       </c>
       <c r="E225" t="n">
         <v>0.8328</v>
       </c>
       <c r="F225" t="n">
-        <v>1.9872</v>
+        <v>3.3043</v>
       </c>
       <c r="G225" t="n">
         <v>0.8887</v>
@@ -39477,19 +39477,19 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1.0596</v>
+        <v>1.3431</v>
       </c>
       <c r="C226" t="n">
         <v>-2.0119</v>
       </c>
       <c r="D226" t="n">
-        <v>1.874</v>
+        <v>3.2917</v>
       </c>
       <c r="E226" t="n">
         <v>0.856</v>
       </c>
       <c r="F226" t="n">
-        <v>1.874</v>
+        <v>3.2917</v>
       </c>
       <c r="G226" t="n">
         <v>0.8778</v>
@@ -39511,19 +39511,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1.0445</v>
+        <v>1.3297</v>
       </c>
       <c r="C227" t="n">
         <v>-2.0449</v>
       </c>
       <c r="D227" t="n">
-        <v>1.8476</v>
+        <v>3.274</v>
       </c>
       <c r="E227" t="n">
         <v>0.8437</v>
       </c>
       <c r="F227" t="n">
-        <v>1.8476</v>
+        <v>3.274</v>
       </c>
       <c r="G227" t="n">
         <v>0.8428</v>
@@ -39545,19 +39545,19 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1.0547</v>
+        <v>1.3432</v>
       </c>
       <c r="C228" t="n">
         <v>-1.9835</v>
       </c>
       <c r="D228" t="n">
-        <v>1.8298</v>
+        <v>3.2723</v>
       </c>
       <c r="E228" t="n">
         <v>0.8609</v>
       </c>
       <c r="F228" t="n">
-        <v>1.8298</v>
+        <v>3.2723</v>
       </c>
       <c r="G228" t="n">
         <v>0.8121</v>
@@ -39579,19 +39579,19 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1.1002</v>
+        <v>0.923</v>
       </c>
       <c r="C229" t="n">
         <v>-1.9719</v>
       </c>
       <c r="D229" t="n">
-        <v>1.8793</v>
+        <v>0.9935</v>
       </c>
       <c r="E229" t="n">
         <v>0.9054</v>
       </c>
       <c r="F229" t="n">
-        <v>1.8793</v>
+        <v>0.9935</v>
       </c>
       <c r="G229" t="n">
         <v>0.8365</v>
@@ -39613,19 +39613,19 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1.1574</v>
+        <v>1.4267</v>
       </c>
       <c r="C230" t="n">
         <v>-2.0048</v>
       </c>
       <c r="D230" t="n">
-        <v>1.9493</v>
+        <v>3.2956</v>
       </c>
       <c r="E230" t="n">
         <v>0.9595</v>
       </c>
       <c r="F230" t="n">
-        <v>1.9493</v>
+        <v>3.2956</v>
       </c>
       <c r="G230" t="n">
         <v>0.8534</v>
@@ -39647,19 +39647,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.1381</v>
+        <v>1.4217</v>
       </c>
       <c r="C231" t="n">
         <v>-2.0089</v>
       </c>
       <c r="D231" t="n">
-        <v>1.8502</v>
+        <v>3.2679</v>
       </c>
       <c r="E231" t="n">
         <v>0.9601</v>
       </c>
       <c r="F231" t="n">
-        <v>1.8502</v>
+        <v>3.2679</v>
       </c>
       <c r="G231" t="n">
         <v>0.8335</v>
@@ -39681,19 +39681,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.1787</v>
+        <v>1.4617</v>
       </c>
       <c r="C232" t="n">
         <v>-1.885</v>
       </c>
       <c r="D232" t="n">
-        <v>1.8359</v>
+        <v>3.251</v>
       </c>
       <c r="E232" t="n">
         <v>1.0144</v>
       </c>
       <c r="F232" t="n">
-        <v>1.8359</v>
+        <v>3.251</v>
       </c>
       <c r="G232" t="n">
         <v>0.8222</v>
@@ -39715,19 +39715,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.1512</v>
+        <v>1.4531</v>
       </c>
       <c r="C233" t="n">
         <v>-1.8162</v>
       </c>
       <c r="D233" t="n">
-        <v>1.7223</v>
+        <v>3.2317</v>
       </c>
       <c r="E233" t="n">
         <v>1.0085</v>
       </c>
       <c r="F233" t="n">
-        <v>1.7223</v>
+        <v>3.2317</v>
       </c>
       <c r="G233" t="n">
         <v>0.7627</v>
@@ -39749,19 +39749,19 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.12</v>
+        <v>1.1287</v>
       </c>
       <c r="C234" t="n">
         <v>-1.821</v>
       </c>
       <c r="D234" t="n">
-        <v>1.5993</v>
+        <v>1.6425</v>
       </c>
       <c r="E234" t="n">
         <v>1.0002</v>
       </c>
       <c r="F234" t="n">
-        <v>1.5993</v>
+        <v>1.6425</v>
       </c>
       <c r="G234" t="n">
         <v>0.712</v>
@@ -39783,19 +39783,19 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.1304</v>
+        <v>0.9908</v>
       </c>
       <c r="C235" t="n">
         <v>-1.8192</v>
       </c>
       <c r="D235" t="n">
-        <v>1.57</v>
+        <v>0.8717</v>
       </c>
       <c r="E235" t="n">
         <v>1.0205</v>
       </c>
       <c r="F235" t="n">
-        <v>1.57</v>
+        <v>0.8717</v>
       </c>
       <c r="G235" t="n">
         <v>0.6616</v>
@@ -39817,19 +39817,19 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.1187</v>
+        <v>0.8213</v>
       </c>
       <c r="C236" t="n">
         <v>-1.6004</v>
       </c>
       <c r="D236" t="n">
-        <v>1.5495</v>
+        <v>0.0623</v>
       </c>
       <c r="E236" t="n">
         <v>1.011</v>
       </c>
       <c r="F236" t="n">
-        <v>1.5495</v>
+        <v>0.0623</v>
       </c>
       <c r="G236" t="n">
         <v>0.5582</v>
@@ -39851,19 +39851,19 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0962</v>
+        <v>0.7895</v>
       </c>
       <c r="C237" t="n">
         <v>-1.6349</v>
       </c>
       <c r="D237" t="n">
-        <v>1.6065</v>
+        <v>0.0727</v>
       </c>
       <c r="E237" t="n">
         <v>0.9687</v>
       </c>
       <c r="F237" t="n">
-        <v>1.6065</v>
+        <v>0.0727</v>
       </c>
       <c r="G237" t="n">
         <v>0.4647</v>
@@ -39885,19 +39885,19 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1.0905</v>
+        <v>0.7903</v>
       </c>
       <c r="C238" t="n">
         <v>-1.6448</v>
       </c>
       <c r="D238" t="n">
-        <v>1.5698</v>
+        <v>0.0689</v>
       </c>
       <c r="E238" t="n">
         <v>0.9707</v>
       </c>
       <c r="F238" t="n">
-        <v>1.5698</v>
+        <v>0.0689</v>
       </c>
       <c r="G238" t="n">
         <v>0.4631</v>
@@ -39919,19 +39919,19 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.085</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="C239" t="n">
         <v>-1.5616</v>
       </c>
       <c r="D239" t="n">
-        <v>1.4782</v>
+        <v>0.0527</v>
       </c>
       <c r="E239" t="n">
         <v>0.9867</v>
       </c>
       <c r="F239" t="n">
-        <v>1.4782</v>
+        <v>0.0527</v>
       </c>
       <c r="G239" t="n">
         <v>0.3839</v>
@@ -39953,19 +39953,19 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0352</v>
+        <v>0.7769</v>
       </c>
       <c r="C240" t="n">
         <v>-1.5767</v>
       </c>
       <c r="D240" t="n">
-        <v>1.2971</v>
+        <v>0.0058</v>
       </c>
       <c r="E240" t="n">
         <v>0.9697</v>
       </c>
       <c r="F240" t="n">
-        <v>1.2971</v>
+        <v>0.0058</v>
       </c>
       <c r="G240" t="n">
         <v>0.3216</v>
@@ -39987,19 +39987,19 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0232</v>
+        <v>1.0045</v>
       </c>
       <c r="C241" t="n">
         <v>-1.6109</v>
       </c>
       <c r="D241" t="n">
-        <v>1.2521</v>
+        <v>1.1588</v>
       </c>
       <c r="E241" t="n">
         <v>0.966</v>
       </c>
       <c r="F241" t="n">
-        <v>1.2521</v>
+        <v>1.1588</v>
       </c>
       <c r="G241" t="n">
         <v>0.2499</v>
@@ -40021,19 +40021,19 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.9676</v>
+        <v>1.0537</v>
       </c>
       <c r="C242" t="n">
         <v>-1.3626</v>
       </c>
       <c r="D242" t="n">
-        <v>1.0963</v>
+        <v>1.5271</v>
       </c>
       <c r="E242" t="n">
         <v>0.9354</v>
       </c>
       <c r="F242" t="n">
-        <v>1.0963</v>
+        <v>1.5271</v>
       </c>
       <c r="G242" t="n">
         <v>0.1222</v>
@@ -40055,19 +40055,19 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9199000000000001</v>
+        <v>1.0388</v>
       </c>
       <c r="C243" t="n">
         <v>-1.2948</v>
       </c>
       <c r="D243" t="n">
-        <v>0.891</v>
+        <v>1.4852</v>
       </c>
       <c r="E243" t="n">
         <v>0.9272</v>
       </c>
       <c r="F243" t="n">
-        <v>0.891</v>
+        <v>1.4852</v>
       </c>
       <c r="G243" t="n">
         <v>0.09279999999999999</v>
@@ -40089,19 +40089,19 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.9303</v>
+        <v>1.0637</v>
       </c>
       <c r="C244" t="n">
         <v>-1.2666</v>
       </c>
       <c r="D244" t="n">
-        <v>0.7887</v>
+        <v>1.4554</v>
       </c>
       <c r="E244" t="n">
         <v>0.9657</v>
       </c>
       <c r="F244" t="n">
-        <v>0.7887</v>
+        <v>1.4554</v>
       </c>
       <c r="G244" t="n">
         <v>0.1019</v>
@@ -40123,19 +40123,19 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.9239000000000001</v>
+        <v>1.0231</v>
       </c>
       <c r="C245" t="n">
         <v>-1.2917</v>
       </c>
       <c r="D245" t="n">
-        <v>1.0174</v>
+        <v>1.5134</v>
       </c>
       <c r="E245" t="n">
         <v>0.9005</v>
       </c>
       <c r="F245" t="n">
-        <v>1.0174</v>
+        <v>1.5134</v>
       </c>
       <c r="G245" t="n">
         <v>-0.023</v>
@@ -40157,19 +40157,19 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.9455</v>
+        <v>1.0464</v>
       </c>
       <c r="C246" t="n">
         <v>-1.3073</v>
       </c>
       <c r="D246" t="n">
-        <v>0.9883</v>
+        <v>1.4929</v>
       </c>
       <c r="E246" t="n">
         <v>0.9348</v>
       </c>
       <c r="F246" t="n">
-        <v>0.9883</v>
+        <v>1.4929</v>
       </c>
       <c r="G246" t="n">
         <v>-0.0741</v>
@@ -40191,19 +40191,19 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.8919</v>
+        <v>1.0101</v>
       </c>
       <c r="C247" t="n">
         <v>-1.2459</v>
       </c>
       <c r="D247" t="n">
-        <v>0.8928</v>
+        <v>1.4838</v>
       </c>
       <c r="E247" t="n">
         <v>0.8917</v>
       </c>
       <c r="F247" t="n">
-        <v>0.8928</v>
+        <v>1.4838</v>
       </c>
       <c r="G247" t="n">
         <v>-0.0824</v>
@@ -40225,19 +40225,19 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.8786</v>
+        <v>1.0033</v>
       </c>
       <c r="C248" t="n">
         <v>-1.2832</v>
       </c>
       <c r="D248" t="n">
-        <v>0.8425</v>
+        <v>1.4658</v>
       </c>
       <c r="E248" t="n">
         <v>0.8875999999999999</v>
       </c>
       <c r="F248" t="n">
-        <v>0.8425</v>
+        <v>1.4658</v>
       </c>
       <c r="G248" t="n">
         <v>-0.2093</v>
@@ -40259,19 +40259,19 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.8914</v>
+        <v>1.0206</v>
       </c>
       <c r="C249" t="n">
         <v>-1.3149</v>
       </c>
       <c r="D249" t="n">
-        <v>0.8038999999999999</v>
+        <v>1.4498</v>
       </c>
       <c r="E249" t="n">
         <v>0.9133</v>
       </c>
       <c r="F249" t="n">
-        <v>0.8038999999999999</v>
+        <v>1.4498</v>
       </c>
       <c r="G249" t="n">
         <v>-0.2236</v>
@@ -40293,19 +40293,19 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.8727</v>
+        <v>1.0131</v>
       </c>
       <c r="C250" t="n">
         <v>-1.3282</v>
       </c>
       <c r="D250" t="n">
-        <v>0.7248</v>
+        <v>1.4267</v>
       </c>
       <c r="E250" t="n">
         <v>0.9096</v>
       </c>
       <c r="F250" t="n">
-        <v>0.7248</v>
+        <v>1.4267</v>
       </c>
       <c r="G250" t="n">
         <v>-0.2918</v>
@@ -40327,19 +40327,19 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.8774999999999999</v>
+        <v>1.0323</v>
       </c>
       <c r="C251" t="n">
         <v>-1.3331</v>
       </c>
       <c r="D251" t="n">
-        <v>0.6391</v>
+        <v>1.4131</v>
       </c>
       <c r="E251" t="n">
         <v>0.9371</v>
       </c>
       <c r="F251" t="n">
-        <v>0.6391</v>
+        <v>1.4131</v>
       </c>
       <c r="G251" t="n">
         <v>-0.2946</v>
@@ -40361,19 +40361,19 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.8681</v>
+        <v>1.0371</v>
       </c>
       <c r="C252" t="n">
         <v>-1.272</v>
       </c>
       <c r="D252" t="n">
-        <v>0.5569</v>
+        <v>1.4021</v>
       </c>
       <c r="E252" t="n">
         <v>0.9459</v>
       </c>
       <c r="F252" t="n">
-        <v>0.5569</v>
+        <v>1.4021</v>
       </c>
       <c r="G252" t="n">
         <v>-0.3493</v>
@@ -40395,19 +40395,19 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.8252</v>
+        <v>0.7009</v>
       </c>
       <c r="C253" t="n">
         <v>-1.124</v>
       </c>
       <c r="D253" t="n">
-        <v>0.4006</v>
+        <v>-0.2209</v>
       </c>
       <c r="E253" t="n">
         <v>0.9313</v>
       </c>
       <c r="F253" t="n">
-        <v>0.4006</v>
+        <v>-0.2209</v>
       </c>
       <c r="G253" t="n">
         <v>-0.4167</v>
@@ -40429,19 +40429,19 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.7859</v>
+        <v>0.6983</v>
       </c>
       <c r="C254" t="n">
         <v>-1.0902</v>
       </c>
       <c r="D254" t="n">
-        <v>0.1618</v>
+        <v>-0.2764</v>
       </c>
       <c r="E254" t="n">
         <v>0.9419999999999999</v>
       </c>
       <c r="F254" t="n">
-        <v>0.1618</v>
+        <v>-0.2764</v>
       </c>
       <c r="G254" t="n">
         <v>-0.4704</v>
@@ -40463,19 +40463,19 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.7823</v>
+        <v>0.708</v>
       </c>
       <c r="C255" t="n">
         <v>-1.0808</v>
       </c>
       <c r="D255" t="n">
-        <v>0.0788</v>
+        <v>-0.2927</v>
       </c>
       <c r="E255" t="n">
         <v>0.9582000000000001</v>
       </c>
       <c r="F255" t="n">
-        <v>0.0788</v>
+        <v>-0.2927</v>
       </c>
       <c r="G255" t="n">
         <v>-0.5066000000000001</v>
@@ -40497,19 +40497,19 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.7357</v>
+        <v>0.6602</v>
       </c>
       <c r="C256" t="n">
         <v>-1.126</v>
       </c>
       <c r="D256" t="n">
-        <v>0.0776</v>
+        <v>-0.3</v>
       </c>
       <c r="E256" t="n">
         <v>0.9002</v>
       </c>
       <c r="F256" t="n">
-        <v>0.0776</v>
+        <v>-0.3</v>
       </c>
       <c r="G256" t="n">
         <v>-0.6055</v>
@@ -40531,19 +40531,19 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.6555</v>
+        <v>0.619</v>
       </c>
       <c r="C257" t="n">
         <v>-1.0548</v>
       </c>
       <c r="D257" t="n">
-        <v>-0.1579</v>
+        <v>-0.34</v>
       </c>
       <c r="E257" t="n">
         <v>0.8588</v>
       </c>
       <c r="F257" t="n">
-        <v>-0.1579</v>
+        <v>-0.34</v>
       </c>
       <c r="G257" t="n">
         <v>-0.7845</v>
@@ -40565,19 +40565,19 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.6972</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="C258" t="n">
         <v>-1.1339</v>
       </c>
       <c r="D258" t="n">
-        <v>-0.2125</v>
+        <v>-0.3692</v>
       </c>
       <c r="E258" t="n">
         <v>0.9246</v>
       </c>
       <c r="F258" t="n">
-        <v>-0.2125</v>
+        <v>-0.3692</v>
       </c>
       <c r="G258" t="n">
         <v>-0.7927999999999999</v>
@@ -40599,19 +40599,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.7059</v>
+        <v>0.7954</v>
       </c>
       <c r="C259" t="n">
         <v>-0.8293</v>
       </c>
       <c r="D259" t="n">
-        <v>-0.2619</v>
+        <v>0.1856</v>
       </c>
       <c r="E259" t="n">
         <v>0.9478</v>
       </c>
       <c r="F259" t="n">
-        <v>-0.2619</v>
+        <v>0.1856</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8917</v>
@@ -41297,7 +41297,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Real Interest Rate 1-Year</t>
+          <t>Real Interest Rate 1-Year (ex-ante)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -41307,7 +41307,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>real_rate</t>
+          <t>real_rate_exante</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -41344,7 +41344,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Nominal 1y minus 1y expected inflation. Short real rate: high impact on activity.</t>
+          <t>Nominal 1y minus 1y expected inflation. 2005+ reference (ex-ante).</t>
         </is>
       </c>
     </row>
@@ -41356,7 +41356,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Real Interest Rate 3-Year</t>
+          <t>Real Interest Rate 3-Year (ex-ante)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>real_rate</t>
+          <t>real_rate_exante</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -41403,7 +41403,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Medium real rate (3y interpolated). High impact on activity.</t>
+          <t>Medium real rate (3y interpolated). 2005+ reference (ex-ante).</t>
         </is>
       </c>
     </row>
@@ -41415,7 +41415,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Real Interest Rate 10-Year</t>
+          <t>Real Interest Rate 10-Year (ex-ante)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -41425,7 +41425,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>real_rate</t>
+          <t>real_rate_exante</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -41462,7 +41462,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Long real rate. Lower direct impact on activity.</t>
+          <t>Long real rate. 2005+ reference (ex-ante).</t>
         </is>
       </c>
     </row>
@@ -41533,17 +41533,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Real Interest Rate 1-Year (ex-post vs realized core CPI)</t>
+          <t>Real Interest Rate 1-Year (ex-post)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>stage1_interest_rates</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>real_rate_xp</t>
+          <t>real_rate</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -41562,10 +41562,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Ex-post real 1y: nominal minus realized core CPI y/y. Long history (1974+) for horizon analysis.</t>
+          <t>Headline real 1y: nominal minus realized core CPI. Scored over longest history (1974+).</t>
         </is>
       </c>
     </row>
@@ -41592,17 +41592,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Real Interest Rate 3-Year (ex-post vs realized core CPI)</t>
+          <t>Real Interest Rate 3-Year (ex-post)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>stage1_interest_rates</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>real_rate_xp</t>
+          <t>real_rate</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -41621,10 +41621,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Ex-post real 3y (2y-5y interp minus realized core CPI). Long history for horizon analysis.</t>
+          <t>Headline real 3y (2y-5y interp minus realized core CPI). Scored over longest history (1974+).</t>
         </is>
       </c>
     </row>
@@ -41651,17 +41651,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Real Interest Rate 10-Year (ex-post vs realized core CPI)</t>
+          <t>Real Interest Rate 10-Year (ex-post)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>stage1_interest_rates</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>real_rate_xp</t>
+          <t>real_rate</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -41680,10 +41680,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Ex-post real 10y: nominal minus realized core CPI y/y. Long history (1986+) for horizon analysis.</t>
+          <t>Headline real 10y: nominal minus realized core CPI. Scored over longest history (1986+).</t>
         </is>
       </c>
     </row>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -804,12 +804,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-0.83pp</t>
+          <t>-0.62pp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.80 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.83pp below the midpoint natural-rate estimate (-0.15%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.85% to +0.55%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.80 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4749,13 +4749,13 @@
         <v>1.4047</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1</v>
+        <v>-0.278</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.1</v>
+        <v>0.291</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.8</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -4855,13 +4855,13 @@
         <v>1.4047</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1</v>
+        <v>-0.278</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.1</v>
+        <v>0.291</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.8</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4961,13 +4961,13 @@
         <v>1.4047</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1</v>
+        <v>-0.278</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.1</v>
+        <v>0.291</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.8</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -5067,13 +5067,13 @@
         <v>1.3922</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1.0091</v>
+        <v>-0.317</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.1121</v>
+        <v>0.292</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.7849</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="8">
@@ -5173,13 +5173,13 @@
         <v>1.3922</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.0091</v>
+        <v>-0.317</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.1121</v>
+        <v>0.292</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.7849</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="9">
@@ -5279,13 +5279,13 @@
         <v>1.3922</v>
       </c>
       <c r="AF9" t="n">
-        <v>-1.0091</v>
+        <v>-0.317</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.1121</v>
+        <v>0.292</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.7849</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="10">
@@ -5385,13 +5385,13 @@
         <v>1.3493</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1.0182</v>
+        <v>-0.335</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.1243</v>
+        <v>0.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.7696</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="11">
@@ -5491,13 +5491,13 @@
         <v>1.3493</v>
       </c>
       <c r="AF11" t="n">
-        <v>-1.0182</v>
+        <v>-0.335</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.1243</v>
+        <v>0.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.7696</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="12">
@@ -5597,13 +5597,13 @@
         <v>1.3493</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.0182</v>
+        <v>-0.335</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.1243</v>
+        <v>0.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.7696</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="13">
@@ -5703,13 +5703,13 @@
         <v>1.345</v>
       </c>
       <c r="AF13" t="n">
-        <v>-1.0274</v>
+        <v>-0.337</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.1365</v>
+        <v>0.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.7544</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="14">
@@ -5809,13 +5809,13 @@
         <v>1.345</v>
       </c>
       <c r="AF14" t="n">
-        <v>-1.0274</v>
+        <v>-0.337</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.1365</v>
+        <v>0.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.7544</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="15">
@@ -5915,13 +5915,13 @@
         <v>1.345</v>
       </c>
       <c r="AF15" t="n">
-        <v>-1.0274</v>
+        <v>-0.337</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.1365</v>
+        <v>0.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.7544</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="16">
@@ -6021,13 +6021,13 @@
         <v>1.3676</v>
       </c>
       <c r="AF16" t="n">
-        <v>-1.0363</v>
+        <v>-0.331</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.1485</v>
+        <v>0.295</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="17">
@@ -6127,13 +6127,13 @@
         <v>1.3676</v>
       </c>
       <c r="AF17" t="n">
-        <v>-1.0363</v>
+        <v>-0.331</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.1485</v>
+        <v>0.295</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="18">
@@ -6233,13 +6233,13 @@
         <v>1.3676</v>
       </c>
       <c r="AF18" t="n">
-        <v>-1.0363</v>
+        <v>-0.331</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.1485</v>
+        <v>0.295</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="19">
@@ -6339,13 +6339,13 @@
         <v>1.3038</v>
       </c>
       <c r="AF19" t="n">
-        <v>-1.0454</v>
+        <v>-0.313</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.1605</v>
+        <v>0.267</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="20">
@@ -6445,13 +6445,13 @@
         <v>1.3038</v>
       </c>
       <c r="AF20" t="n">
-        <v>-1.0454</v>
+        <v>-0.313</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.1605</v>
+        <v>0.267</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="21">
@@ -6551,13 +6551,13 @@
         <v>1.3038</v>
       </c>
       <c r="AF21" t="n">
-        <v>-1.0454</v>
+        <v>-0.313</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.1605</v>
+        <v>0.267</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="22">
@@ -6657,13 +6657,13 @@
         <v>1.3185</v>
       </c>
       <c r="AF22" t="n">
-        <v>-1.0546</v>
+        <v>-0.282</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.1728</v>
+        <v>0.236</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.7091</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="23">
@@ -6763,13 +6763,13 @@
         <v>1.3185</v>
       </c>
       <c r="AF23" t="n">
-        <v>-1.0546</v>
+        <v>-0.282</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.1728</v>
+        <v>0.236</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.7091</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="24">
@@ -6869,13 +6869,13 @@
         <v>1.3185</v>
       </c>
       <c r="AF24" t="n">
-        <v>-1.0546</v>
+        <v>-0.282</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.1728</v>
+        <v>0.236</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.7091</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="25">
@@ -6975,13 +6975,13 @@
         <v>1.2761</v>
       </c>
       <c r="AF25" t="n">
-        <v>-1.0637</v>
+        <v>-0.239</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.185</v>
+        <v>0.147</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.6938</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="26">
@@ -7081,13 +7081,13 @@
         <v>1.2761</v>
       </c>
       <c r="AF26" t="n">
-        <v>-1.0637</v>
+        <v>-0.239</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.185</v>
+        <v>0.147</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.6938</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="27">
@@ -7187,13 +7187,13 @@
         <v>1.2761</v>
       </c>
       <c r="AF27" t="n">
-        <v>-1.0637</v>
+        <v>-0.239</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.185</v>
+        <v>0.147</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.6938</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="28">
@@ -7293,13 +7293,13 @@
         <v>1.2935</v>
       </c>
       <c r="AF28" t="n">
-        <v>-1.0727</v>
+        <v>-0.202</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.1969</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="29">
@@ -7399,13 +7399,13 @@
         <v>1.2935</v>
       </c>
       <c r="AF29" t="n">
-        <v>-1.0727</v>
+        <v>-0.202</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.1969</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="30">
@@ -7505,13 +7505,13 @@
         <v>1.2935</v>
       </c>
       <c r="AF30" t="n">
-        <v>-1.0727</v>
+        <v>-0.202</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.1969</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="31">
@@ -7611,13 +7611,13 @@
         <v>1.2782</v>
       </c>
       <c r="AF31" t="n">
-        <v>-1.0817</v>
+        <v>-0.215</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.209</v>
+        <v>0.104</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="32">
@@ -7717,13 +7717,13 @@
         <v>1.2782</v>
       </c>
       <c r="AF32" t="n">
-        <v>-1.0817</v>
+        <v>-0.215</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.209</v>
+        <v>0.104</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="33">
@@ -7823,13 +7823,13 @@
         <v>1.2782</v>
       </c>
       <c r="AF33" t="n">
-        <v>-1.0817</v>
+        <v>-0.215</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.209</v>
+        <v>0.104</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="34">
@@ -7929,13 +7929,13 @@
         <v>1.2546</v>
       </c>
       <c r="AF34" t="n">
-        <v>-1.0909</v>
+        <v>-0.308</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.2212</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.6485</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="35">
@@ -8035,13 +8035,13 @@
         <v>1.2546</v>
       </c>
       <c r="AF35" t="n">
-        <v>-1.0909</v>
+        <v>-0.308</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.2212</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.6485</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="36">
@@ -8141,13 +8141,13 @@
         <v>1.2546</v>
       </c>
       <c r="AF36" t="n">
-        <v>-1.0909</v>
+        <v>-0.308</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.2212</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.6485</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="37">
@@ -8247,13 +8247,13 @@
         <v>1.2412</v>
       </c>
       <c r="AF37" t="n">
-        <v>-1.1001</v>
+        <v>-0.428</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.2334</v>
+        <v>0.024</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.6332</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="38">
@@ -8353,13 +8353,13 @@
         <v>1.2412</v>
       </c>
       <c r="AF38" t="n">
-        <v>-1.1001</v>
+        <v>-0.428</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.2334</v>
+        <v>0.024</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.6332</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="39">
@@ -8459,13 +8459,13 @@
         <v>1.2412</v>
       </c>
       <c r="AF39" t="n">
-        <v>-1.1001</v>
+        <v>-0.428</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.2334</v>
+        <v>0.024</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.6332</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="40">
@@ -8565,13 +8565,13 @@
         <v>1.1885</v>
       </c>
       <c r="AF40" t="n">
-        <v>-1.1091</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.2455</v>
+        <v>-0.055</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.6181</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="41">
@@ -8671,13 +8671,13 @@
         <v>1.1885</v>
       </c>
       <c r="AF41" t="n">
-        <v>-1.1091</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.2455</v>
+        <v>-0.055</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.6181</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="42">
@@ -8777,13 +8777,13 @@
         <v>1.1885</v>
       </c>
       <c r="AF42" t="n">
-        <v>-1.1091</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="AG42" t="n">
-        <v>-0.2455</v>
+        <v>-0.055</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.6181</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="43">
@@ -8883,13 +8883,13 @@
         <v>1.1972</v>
       </c>
       <c r="AF43" t="n">
-        <v>-1.1182</v>
+        <v>-0.681</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.2576</v>
+        <v>-0.063</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.603</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="44">
@@ -8989,13 +8989,13 @@
         <v>1.1972</v>
       </c>
       <c r="AF44" t="n">
-        <v>-1.1182</v>
+        <v>-0.681</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.2576</v>
+        <v>-0.063</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.603</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="45">
@@ -9095,13 +9095,13 @@
         <v>1.1972</v>
       </c>
       <c r="AF45" t="n">
-        <v>-1.1182</v>
+        <v>-0.681</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.2576</v>
+        <v>-0.063</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.603</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="46">
@@ -9201,13 +9201,13 @@
         <v>0.9696</v>
       </c>
       <c r="AF46" t="n">
-        <v>-1.1273</v>
+        <v>-0.762</v>
       </c>
       <c r="AG46" t="n">
-        <v>-0.2698</v>
+        <v>-0.11</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.5878</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="47">
@@ -9307,13 +9307,13 @@
         <v>0.9696</v>
       </c>
       <c r="AF47" t="n">
-        <v>-1.1273</v>
+        <v>-0.762</v>
       </c>
       <c r="AG47" t="n">
-        <v>-0.2698</v>
+        <v>-0.11</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.5878</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="48">
@@ -9413,13 +9413,13 @@
         <v>0.9696</v>
       </c>
       <c r="AF48" t="n">
-        <v>-1.1273</v>
+        <v>-0.762</v>
       </c>
       <c r="AG48" t="n">
-        <v>-0.2698</v>
+        <v>-0.11</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.5878</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="49">
@@ -9519,13 +9519,13 @@
         <v>0.8003</v>
       </c>
       <c r="AF49" t="n">
-        <v>-1.1365</v>
+        <v>-0.731</v>
       </c>
       <c r="AG49" t="n">
-        <v>-0.282</v>
+        <v>-0.157</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.5725</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="50">
@@ -9625,13 +9625,13 @@
         <v>0.8003</v>
       </c>
       <c r="AF50" t="n">
-        <v>-1.1365</v>
+        <v>-0.731</v>
       </c>
       <c r="AG50" t="n">
-        <v>-0.282</v>
+        <v>-0.157</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.5725</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="51">
@@ -9731,13 +9731,13 @@
         <v>0.8003</v>
       </c>
       <c r="AF51" t="n">
-        <v>-1.1365</v>
+        <v>-0.731</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.282</v>
+        <v>-0.157</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.5725</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="52">
@@ -9837,13 +9837,13 @@
         <v>0.584</v>
       </c>
       <c r="AF52" t="n">
-        <v>-1.1455</v>
+        <v>-0.536</v>
       </c>
       <c r="AG52" t="n">
-        <v>-0.294</v>
+        <v>-0.177</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.5576</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="53">
@@ -9943,13 +9943,13 @@
         <v>0.584</v>
       </c>
       <c r="AF53" t="n">
-        <v>-1.1455</v>
+        <v>-0.536</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.294</v>
+        <v>-0.177</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.5576</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="54">
@@ -10049,13 +10049,13 @@
         <v>0.584</v>
       </c>
       <c r="AF54" t="n">
-        <v>-1.1455</v>
+        <v>-0.536</v>
       </c>
       <c r="AG54" t="n">
-        <v>-0.294</v>
+        <v>-0.177</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.5576</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="55">
@@ -10155,13 +10155,13 @@
         <v>0.4235</v>
       </c>
       <c r="AF55" t="n">
-        <v>-1.1545</v>
+        <v>-0.382</v>
       </c>
       <c r="AG55" t="n">
-        <v>-0.306</v>
+        <v>-0.194</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.5424</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="56">
@@ -10261,13 +10261,13 @@
         <v>0.4235</v>
       </c>
       <c r="AF56" t="n">
-        <v>-1.1545</v>
+        <v>-0.382</v>
       </c>
       <c r="AG56" t="n">
-        <v>-0.306</v>
+        <v>-0.194</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.5424</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="57">
@@ -10367,13 +10367,13 @@
         <v>0.4235</v>
       </c>
       <c r="AF57" t="n">
-        <v>-1.1545</v>
+        <v>-0.382</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.306</v>
+        <v>-0.194</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.5424</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="58">
@@ -10473,13 +10473,13 @@
         <v>0.1783</v>
       </c>
       <c r="AF58" t="n">
-        <v>-1.1637</v>
+        <v>-0.26</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.3183</v>
+        <v>-0.171</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.5272</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -10579,13 +10579,13 @@
         <v>0.1783</v>
       </c>
       <c r="AF59" t="n">
-        <v>-1.1637</v>
+        <v>-0.26</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.3183</v>
+        <v>-0.171</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.5272</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -10685,13 +10685,13 @@
         <v>0.1783</v>
       </c>
       <c r="AF60" t="n">
-        <v>-1.1637</v>
+        <v>-0.26</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.3183</v>
+        <v>-0.171</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.5272</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -10791,13 +10791,13 @@
         <v>0.2701</v>
       </c>
       <c r="AF61" t="n">
-        <v>-1.1729</v>
+        <v>-0.323</v>
       </c>
       <c r="AG61" t="n">
-        <v>-0.3305</v>
+        <v>-0.124</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.5119</v>
+        <v>-0.076</v>
       </c>
     </row>
     <row r="62">
@@ -10897,13 +10897,13 @@
         <v>0.2701</v>
       </c>
       <c r="AF62" t="n">
-        <v>-1.1729</v>
+        <v>-0.323</v>
       </c>
       <c r="AG62" t="n">
-        <v>-0.3305</v>
+        <v>-0.124</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.5119</v>
+        <v>-0.076</v>
       </c>
     </row>
     <row r="63">
@@ -11003,13 +11003,13 @@
         <v>0.2701</v>
       </c>
       <c r="AF63" t="n">
-        <v>-1.1729</v>
+        <v>-0.323</v>
       </c>
       <c r="AG63" t="n">
-        <v>-0.3305</v>
+        <v>-0.124</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.5119</v>
+        <v>-0.076</v>
       </c>
     </row>
     <row r="64">
@@ -11109,13 +11109,13 @@
         <v>0.2948</v>
       </c>
       <c r="AF64" t="n">
-        <v>-1.1818</v>
+        <v>-0.369</v>
       </c>
       <c r="AG64" t="n">
-        <v>-0.3424</v>
+        <v>-0.11</v>
       </c>
       <c r="AH64" t="n">
-        <v>0.497</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="65">
@@ -11215,13 +11215,13 @@
         <v>0.2948</v>
       </c>
       <c r="AF65" t="n">
-        <v>-1.1818</v>
+        <v>-0.369</v>
       </c>
       <c r="AG65" t="n">
-        <v>-0.3424</v>
+        <v>-0.11</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.497</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="66">
@@ -11321,13 +11321,13 @@
         <v>0.2948</v>
       </c>
       <c r="AF66" t="n">
-        <v>-1.1818</v>
+        <v>-0.369</v>
       </c>
       <c r="AG66" t="n">
-        <v>-0.3424</v>
+        <v>-0.11</v>
       </c>
       <c r="AH66" t="n">
-        <v>0.497</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="67">
@@ -11427,13 +11427,13 @@
         <v>0.3485</v>
       </c>
       <c r="AF67" t="n">
-        <v>-1.1909</v>
+        <v>-0.371</v>
       </c>
       <c r="AG67" t="n">
-        <v>-0.3545</v>
+        <v>-0.169</v>
       </c>
       <c r="AH67" t="n">
-        <v>0.4819</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="68">
@@ -11533,13 +11533,13 @@
         <v>0.3485</v>
       </c>
       <c r="AF68" t="n">
-        <v>-1.1909</v>
+        <v>-0.371</v>
       </c>
       <c r="AG68" t="n">
-        <v>-0.3545</v>
+        <v>-0.169</v>
       </c>
       <c r="AH68" t="n">
-        <v>0.4819</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="69">
@@ -11639,13 +11639,13 @@
         <v>0.3485</v>
       </c>
       <c r="AF69" t="n">
-        <v>-1.1909</v>
+        <v>-0.371</v>
       </c>
       <c r="AG69" t="n">
-        <v>-0.3545</v>
+        <v>-0.169</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.4819</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="70">
@@ -11745,13 +11745,13 @@
         <v>0.3674</v>
       </c>
       <c r="AF70" t="n">
-        <v>-1.2</v>
+        <v>-0.357</v>
       </c>
       <c r="AG70" t="n">
-        <v>-0.3667</v>
+        <v>-0.178</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.4666</v>
+        <v>-0.027</v>
       </c>
     </row>
     <row r="71">
@@ -11851,13 +11851,13 @@
         <v>0.3674</v>
       </c>
       <c r="AF71" t="n">
-        <v>-1.2</v>
+        <v>-0.357</v>
       </c>
       <c r="AG71" t="n">
-        <v>-0.3667</v>
+        <v>-0.178</v>
       </c>
       <c r="AH71" t="n">
-        <v>0.4666</v>
+        <v>-0.027</v>
       </c>
     </row>
     <row r="72">
@@ -11957,13 +11957,13 @@
         <v>0.3674</v>
       </c>
       <c r="AF72" t="n">
-        <v>-1.2</v>
+        <v>-0.357</v>
       </c>
       <c r="AG72" t="n">
-        <v>-0.3667</v>
+        <v>-0.178</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.4666</v>
+        <v>-0.027</v>
       </c>
     </row>
     <row r="73">
@@ -12063,13 +12063,13 @@
         <v>0.4</v>
       </c>
       <c r="AF73" t="n">
-        <v>-1.2092</v>
+        <v>-0.328</v>
       </c>
       <c r="AG73" t="n">
-        <v>-0.3789</v>
+        <v>-0.204</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.4513</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="74">
@@ -12169,13 +12169,13 @@
         <v>0.4</v>
       </c>
       <c r="AF74" t="n">
-        <v>-1.2092</v>
+        <v>-0.328</v>
       </c>
       <c r="AG74" t="n">
-        <v>-0.3789</v>
+        <v>-0.204</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.4513</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="75">
@@ -12275,13 +12275,13 @@
         <v>0.4</v>
       </c>
       <c r="AF75" t="n">
-        <v>-1.2092</v>
+        <v>-0.328</v>
       </c>
       <c r="AG75" t="n">
-        <v>-0.3789</v>
+        <v>-0.204</v>
       </c>
       <c r="AH75" t="n">
-        <v>0.4513</v>
+        <v>-0.015</v>
       </c>
     </row>
     <row r="76">
@@ -12381,13 +12381,13 @@
         <v>0.4988</v>
       </c>
       <c r="AF76" t="n">
-        <v>-1.2182</v>
+        <v>-0.316</v>
       </c>
       <c r="AG76" t="n">
-        <v>-0.3909</v>
+        <v>-0.166</v>
       </c>
       <c r="AH76" t="n">
-        <v>0.4364</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="77">
@@ -12487,13 +12487,13 @@
         <v>0.4988</v>
       </c>
       <c r="AF77" t="n">
-        <v>-1.2182</v>
+        <v>-0.316</v>
       </c>
       <c r="AG77" t="n">
-        <v>-0.3909</v>
+        <v>-0.166</v>
       </c>
       <c r="AH77" t="n">
-        <v>0.4364</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="78">
@@ -12593,13 +12593,13 @@
         <v>0.4988</v>
       </c>
       <c r="AF78" t="n">
-        <v>-1.2182</v>
+        <v>-0.316</v>
       </c>
       <c r="AG78" t="n">
-        <v>-0.3909</v>
+        <v>-0.166</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.4364</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="79">
@@ -12699,13 +12699,13 @@
         <v>0.4974</v>
       </c>
       <c r="AF79" t="n">
-        <v>-1.2272</v>
+        <v>-0.383</v>
       </c>
       <c r="AG79" t="n">
-        <v>-0.403</v>
+        <v>-0.156</v>
       </c>
       <c r="AH79" t="n">
-        <v>0.4213</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="80">
@@ -12805,13 +12805,13 @@
         <v>0.4974</v>
       </c>
       <c r="AF80" t="n">
-        <v>-1.2272</v>
+        <v>-0.383</v>
       </c>
       <c r="AG80" t="n">
-        <v>-0.403</v>
+        <v>-0.156</v>
       </c>
       <c r="AH80" t="n">
-        <v>0.4213</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="81">
@@ -12911,13 +12911,13 @@
         <v>0.4974</v>
       </c>
       <c r="AF81" t="n">
-        <v>-1.2272</v>
+        <v>-0.383</v>
       </c>
       <c r="AG81" t="n">
-        <v>-0.403</v>
+        <v>-0.156</v>
       </c>
       <c r="AH81" t="n">
-        <v>0.4213</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="82">
@@ -13017,13 +13017,13 @@
         <v>0.5896</v>
       </c>
       <c r="AF82" t="n">
-        <v>-1.2364</v>
+        <v>-0.383</v>
       </c>
       <c r="AG82" t="n">
-        <v>-0.4152</v>
+        <v>-0.201</v>
       </c>
       <c r="AH82" t="n">
-        <v>0.406</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="83">
@@ -13123,13 +13123,13 @@
         <v>0.5896</v>
       </c>
       <c r="AF83" t="n">
-        <v>-1.2364</v>
+        <v>-0.383</v>
       </c>
       <c r="AG83" t="n">
-        <v>-0.4152</v>
+        <v>-0.201</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.406</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="84">
@@ -13229,13 +13229,13 @@
         <v>0.5896</v>
       </c>
       <c r="AF84" t="n">
-        <v>-1.2364</v>
+        <v>-0.383</v>
       </c>
       <c r="AG84" t="n">
-        <v>-0.4152</v>
+        <v>-0.201</v>
       </c>
       <c r="AH84" t="n">
-        <v>0.406</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="85">
@@ -13335,13 +13335,13 @@
         <v>0.6029</v>
       </c>
       <c r="AF85" t="n">
-        <v>-1.2455</v>
+        <v>-0.398</v>
       </c>
       <c r="AG85" t="n">
-        <v>-0.4274</v>
+        <v>-0.22</v>
       </c>
       <c r="AH85" t="n">
-        <v>0.3908</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="86">
@@ -13441,13 +13441,13 @@
         <v>0.6029</v>
       </c>
       <c r="AF86" t="n">
-        <v>-1.2455</v>
+        <v>-0.398</v>
       </c>
       <c r="AG86" t="n">
-        <v>-0.4274</v>
+        <v>-0.22</v>
       </c>
       <c r="AH86" t="n">
-        <v>0.3908</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="87">
@@ -13547,13 +13547,13 @@
         <v>0.6029</v>
       </c>
       <c r="AF87" t="n">
-        <v>-1.2455</v>
+        <v>-0.398</v>
       </c>
       <c r="AG87" t="n">
-        <v>-0.4274</v>
+        <v>-0.22</v>
       </c>
       <c r="AH87" t="n">
-        <v>0.3908</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="88">
@@ -13653,13 +13653,13 @@
         <v>0.6332</v>
       </c>
       <c r="AF88" t="n">
-        <v>-1.2546</v>
+        <v>-0.426</v>
       </c>
       <c r="AG88" t="n">
-        <v>-0.4395</v>
+        <v>-0.232</v>
       </c>
       <c r="AH88" t="n">
-        <v>0.3757</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="89">
@@ -13759,13 +13759,13 @@
         <v>0.6332</v>
       </c>
       <c r="AF89" t="n">
-        <v>-1.2546</v>
+        <v>-0.426</v>
       </c>
       <c r="AG89" t="n">
-        <v>-0.4395</v>
+        <v>-0.232</v>
       </c>
       <c r="AH89" t="n">
-        <v>0.3757</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="90">
@@ -13865,13 +13865,13 @@
         <v>0.6332</v>
       </c>
       <c r="AF90" t="n">
-        <v>-1.2546</v>
+        <v>-0.426</v>
       </c>
       <c r="AG90" t="n">
-        <v>-0.4395</v>
+        <v>-0.232</v>
       </c>
       <c r="AH90" t="n">
-        <v>0.3757</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="91">
@@ -13971,13 +13971,13 @@
         <v>0.7039</v>
       </c>
       <c r="AF91" t="n">
-        <v>-1.2637</v>
+        <v>-0.45</v>
       </c>
       <c r="AG91" t="n">
-        <v>-0.4515</v>
+        <v>-0.179</v>
       </c>
       <c r="AH91" t="n">
-        <v>0.3606</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="92">
@@ -14077,13 +14077,13 @@
         <v>0.7039</v>
       </c>
       <c r="AF92" t="n">
-        <v>-1.2637</v>
+        <v>-0.45</v>
       </c>
       <c r="AG92" t="n">
-        <v>-0.4515</v>
+        <v>-0.179</v>
       </c>
       <c r="AH92" t="n">
-        <v>0.3606</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="93">
@@ -14183,13 +14183,13 @@
         <v>0.7039</v>
       </c>
       <c r="AF93" t="n">
-        <v>-1.2637</v>
+        <v>-0.45</v>
       </c>
       <c r="AG93" t="n">
-        <v>-0.4515</v>
+        <v>-0.179</v>
       </c>
       <c r="AH93" t="n">
-        <v>0.3606</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="94">
@@ -14289,13 +14289,13 @@
         <v>0.6829</v>
       </c>
       <c r="AF94" t="n">
-        <v>-1.2728</v>
+        <v>-0.461</v>
       </c>
       <c r="AG94" t="n">
-        <v>-0.4638</v>
+        <v>-0.172</v>
       </c>
       <c r="AH94" t="n">
-        <v>0.3453</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="95">
@@ -14395,13 +14395,13 @@
         <v>0.6829</v>
       </c>
       <c r="AF95" t="n">
-        <v>-1.2728</v>
+        <v>-0.461</v>
       </c>
       <c r="AG95" t="n">
-        <v>-0.4638</v>
+        <v>-0.172</v>
       </c>
       <c r="AH95" t="n">
-        <v>0.3453</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="96">
@@ -14501,13 +14501,13 @@
         <v>0.6829</v>
       </c>
       <c r="AF96" t="n">
-        <v>-1.2728</v>
+        <v>-0.461</v>
       </c>
       <c r="AG96" t="n">
-        <v>-0.4638</v>
+        <v>-0.172</v>
       </c>
       <c r="AH96" t="n">
-        <v>0.3453</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="97">
@@ -14607,13 +14607,13 @@
         <v>0.6928</v>
       </c>
       <c r="AF97" t="n">
-        <v>-1.282</v>
+        <v>-0.476</v>
       </c>
       <c r="AG97" t="n">
-        <v>-0.476</v>
+        <v>-0.181</v>
       </c>
       <c r="AH97" t="n">
-        <v>0.33</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="98">
@@ -14713,13 +14713,13 @@
         <v>0.6928</v>
       </c>
       <c r="AF98" t="n">
-        <v>-1.282</v>
+        <v>-0.476</v>
       </c>
       <c r="AG98" t="n">
-        <v>-0.476</v>
+        <v>-0.181</v>
       </c>
       <c r="AH98" t="n">
-        <v>0.33</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="99">
@@ -14819,13 +14819,13 @@
         <v>0.6928</v>
       </c>
       <c r="AF99" t="n">
-        <v>-1.282</v>
+        <v>-0.476</v>
       </c>
       <c r="AG99" t="n">
-        <v>-0.476</v>
+        <v>-0.181</v>
       </c>
       <c r="AH99" t="n">
-        <v>0.33</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="100">
@@ -14925,13 +14925,13 @@
         <v>0.6798</v>
       </c>
       <c r="AF100" t="n">
-        <v>-1.2909</v>
+        <v>-0.503</v>
       </c>
       <c r="AG100" t="n">
-        <v>-0.4879</v>
+        <v>-0.217</v>
       </c>
       <c r="AH100" t="n">
-        <v>0.3151</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="101">
@@ -15031,13 +15031,13 @@
         <v>0.6798</v>
       </c>
       <c r="AF101" t="n">
-        <v>-1.2909</v>
+        <v>-0.503</v>
       </c>
       <c r="AG101" t="n">
-        <v>-0.4879</v>
+        <v>-0.217</v>
       </c>
       <c r="AH101" t="n">
-        <v>0.3151</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="102">
@@ -15137,13 +15137,13 @@
         <v>0.6798</v>
       </c>
       <c r="AF102" t="n">
-        <v>-1.2909</v>
+        <v>-0.503</v>
       </c>
       <c r="AG102" t="n">
-        <v>-0.4879</v>
+        <v>-0.217</v>
       </c>
       <c r="AH102" t="n">
-        <v>0.3151</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="103">
@@ -15243,13 +15243,13 @@
         <v>0.6641</v>
       </c>
       <c r="AF103" t="n">
-        <v>-1.3</v>
+        <v>-0.537</v>
       </c>
       <c r="AG103" t="n">
-        <v>-0.5</v>
+        <v>-0.264</v>
       </c>
       <c r="AH103" t="n">
-        <v>0.3</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="104">
@@ -15349,13 +15349,13 @@
         <v>0.6641</v>
       </c>
       <c r="AF104" t="n">
-        <v>-1.3</v>
+        <v>-0.537</v>
       </c>
       <c r="AG104" t="n">
-        <v>-0.5</v>
+        <v>-0.264</v>
       </c>
       <c r="AH104" t="n">
-        <v>0.3</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="105">
@@ -15455,13 +15455,13 @@
         <v>0.6641</v>
       </c>
       <c r="AF105" t="n">
-        <v>-1.3</v>
+        <v>-0.537</v>
       </c>
       <c r="AG105" t="n">
-        <v>-0.5</v>
+        <v>-0.264</v>
       </c>
       <c r="AH105" t="n">
-        <v>0.3</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="106">
@@ -15561,13 +15561,13 @@
         <v>0.6577</v>
       </c>
       <c r="AF106" t="n">
-        <v>-1.2964</v>
+        <v>-0.612</v>
       </c>
       <c r="AG106" t="n">
-        <v>-0.4982</v>
+        <v>-0.305</v>
       </c>
       <c r="AH106" t="n">
-        <v>0.3018</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="107">
@@ -15667,13 +15667,13 @@
         <v>0.6577</v>
       </c>
       <c r="AF107" t="n">
-        <v>-1.2964</v>
+        <v>-0.612</v>
       </c>
       <c r="AG107" t="n">
-        <v>-0.4982</v>
+        <v>-0.305</v>
       </c>
       <c r="AH107" t="n">
-        <v>0.3018</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="108">
@@ -15773,13 +15773,13 @@
         <v>0.6577</v>
       </c>
       <c r="AF108" t="n">
-        <v>-1.2964</v>
+        <v>-0.612</v>
       </c>
       <c r="AG108" t="n">
-        <v>-0.4982</v>
+        <v>-0.305</v>
       </c>
       <c r="AH108" t="n">
-        <v>0.3018</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="109">
@@ -15879,13 +15879,13 @@
         <v>0.6385999999999999</v>
       </c>
       <c r="AF109" t="n">
-        <v>-1.2928</v>
+        <v>-0.681</v>
       </c>
       <c r="AG109" t="n">
-        <v>-0.4964</v>
+        <v>-0.346</v>
       </c>
       <c r="AH109" t="n">
-        <v>0.3036</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="110">
@@ -15985,13 +15985,13 @@
         <v>0.6385999999999999</v>
       </c>
       <c r="AF110" t="n">
-        <v>-1.2928</v>
+        <v>-0.681</v>
       </c>
       <c r="AG110" t="n">
-        <v>-0.4964</v>
+        <v>-0.346</v>
       </c>
       <c r="AH110" t="n">
-        <v>0.3036</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="111">
@@ -16091,13 +16091,13 @@
         <v>0.6385999999999999</v>
       </c>
       <c r="AF111" t="n">
-        <v>-1.2928</v>
+        <v>-0.681</v>
       </c>
       <c r="AG111" t="n">
-        <v>-0.4964</v>
+        <v>-0.346</v>
       </c>
       <c r="AH111" t="n">
-        <v>0.3036</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="112">
@@ -16197,13 +16197,13 @@
         <v>0.5942</v>
       </c>
       <c r="AF112" t="n">
-        <v>-1.2893</v>
+        <v>-0.746</v>
       </c>
       <c r="AG112" t="n">
-        <v>-0.4946</v>
+        <v>-0.391</v>
       </c>
       <c r="AH112" t="n">
-        <v>0.3054</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="113">
@@ -16303,13 +16303,13 @@
         <v>0.5942</v>
       </c>
       <c r="AF113" t="n">
-        <v>-1.2893</v>
+        <v>-0.746</v>
       </c>
       <c r="AG113" t="n">
-        <v>-0.4946</v>
+        <v>-0.391</v>
       </c>
       <c r="AH113" t="n">
-        <v>0.3054</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="114">
@@ -16409,13 +16409,13 @@
         <v>0.5942</v>
       </c>
       <c r="AF114" t="n">
-        <v>-1.2893</v>
+        <v>-0.746</v>
       </c>
       <c r="AG114" t="n">
-        <v>-0.4946</v>
+        <v>-0.391</v>
       </c>
       <c r="AH114" t="n">
-        <v>0.3054</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="115">
@@ -16515,13 +16515,13 @@
         <v>0.5928</v>
       </c>
       <c r="AF115" t="n">
-        <v>-1.2857</v>
+        <v>-0.801</v>
       </c>
       <c r="AG115" t="n">
-        <v>-0.4929</v>
+        <v>-0.361</v>
       </c>
       <c r="AH115" t="n">
-        <v>0.3071</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="116">
@@ -16621,13 +16621,13 @@
         <v>0.5928</v>
       </c>
       <c r="AF116" t="n">
-        <v>-1.2857</v>
+        <v>-0.801</v>
       </c>
       <c r="AG116" t="n">
-        <v>-0.4929</v>
+        <v>-0.361</v>
       </c>
       <c r="AH116" t="n">
-        <v>0.3071</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="117">
@@ -16727,13 +16727,13 @@
         <v>0.5928</v>
       </c>
       <c r="AF117" t="n">
-        <v>-1.2857</v>
+        <v>-0.801</v>
       </c>
       <c r="AG117" t="n">
-        <v>-0.4929</v>
+        <v>-0.361</v>
       </c>
       <c r="AH117" t="n">
-        <v>0.3071</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="118">
@@ -16833,13 +16833,13 @@
         <v>0.5985</v>
       </c>
       <c r="AF118" t="n">
-        <v>-1.2821</v>
+        <v>-0.843</v>
       </c>
       <c r="AG118" t="n">
-        <v>-0.4911</v>
+        <v>-0.341</v>
       </c>
       <c r="AH118" t="n">
-        <v>0.3089</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="119">
@@ -16939,13 +16939,13 @@
         <v>0.5985</v>
       </c>
       <c r="AF119" t="n">
-        <v>-1.2821</v>
+        <v>-0.843</v>
       </c>
       <c r="AG119" t="n">
-        <v>-0.4911</v>
+        <v>-0.341</v>
       </c>
       <c r="AH119" t="n">
-        <v>0.3089</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="120">
@@ -17045,13 +17045,13 @@
         <v>0.5985</v>
       </c>
       <c r="AF120" t="n">
-        <v>-1.2821</v>
+        <v>-0.843</v>
       </c>
       <c r="AG120" t="n">
-        <v>-0.4911</v>
+        <v>-0.341</v>
       </c>
       <c r="AH120" t="n">
-        <v>0.3089</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="121">
@@ -17151,13 +17151,13 @@
         <v>0.5954</v>
       </c>
       <c r="AF121" t="n">
-        <v>-1.2785</v>
+        <v>-0.878</v>
       </c>
       <c r="AG121" t="n">
-        <v>-0.4893</v>
+        <v>-0.332</v>
       </c>
       <c r="AH121" t="n">
-        <v>0.3107</v>
+        <v>0.661</v>
       </c>
     </row>
     <row r="122">
@@ -17257,13 +17257,13 @@
         <v>0.5954</v>
       </c>
       <c r="AF122" t="n">
-        <v>-1.2785</v>
+        <v>-0.878</v>
       </c>
       <c r="AG122" t="n">
-        <v>-0.4893</v>
+        <v>-0.332</v>
       </c>
       <c r="AH122" t="n">
-        <v>0.3107</v>
+        <v>0.661</v>
       </c>
     </row>
     <row r="123">
@@ -17363,13 +17363,13 @@
         <v>0.5954</v>
       </c>
       <c r="AF123" t="n">
-        <v>-1.2785</v>
+        <v>-0.878</v>
       </c>
       <c r="AG123" t="n">
-        <v>-0.4893</v>
+        <v>-0.332</v>
       </c>
       <c r="AH123" t="n">
-        <v>0.3107</v>
+        <v>0.661</v>
       </c>
     </row>
     <row r="124">
@@ -17469,13 +17469,13 @@
         <v>0.5616</v>
       </c>
       <c r="AF124" t="n">
-        <v>-1.275</v>
+        <v>-0.902</v>
       </c>
       <c r="AG124" t="n">
-        <v>-0.4875</v>
+        <v>-0.388</v>
       </c>
       <c r="AH124" t="n">
-        <v>0.3125</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="125">
@@ -17575,13 +17575,13 @@
         <v>0.5616</v>
       </c>
       <c r="AF125" t="n">
-        <v>-1.275</v>
+        <v>-0.902</v>
       </c>
       <c r="AG125" t="n">
-        <v>-0.4875</v>
+        <v>-0.388</v>
       </c>
       <c r="AH125" t="n">
-        <v>0.3125</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="126">
@@ -17681,13 +17681,13 @@
         <v>0.5616</v>
       </c>
       <c r="AF126" t="n">
-        <v>-1.275</v>
+        <v>-0.902</v>
       </c>
       <c r="AG126" t="n">
-        <v>-0.4875</v>
+        <v>-0.388</v>
       </c>
       <c r="AH126" t="n">
-        <v>0.3125</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="127">
@@ -17787,13 +17787,13 @@
         <v>0.578</v>
       </c>
       <c r="AF127" t="n">
-        <v>-1.2715</v>
+        <v>-0.915</v>
       </c>
       <c r="AG127" t="n">
-        <v>-0.4857</v>
+        <v>-0.389</v>
       </c>
       <c r="AH127" t="n">
-        <v>0.3143</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="128">
@@ -17893,13 +17893,13 @@
         <v>0.578</v>
       </c>
       <c r="AF128" t="n">
-        <v>-1.2715</v>
+        <v>-0.915</v>
       </c>
       <c r="AG128" t="n">
-        <v>-0.4857</v>
+        <v>-0.389</v>
       </c>
       <c r="AH128" t="n">
-        <v>0.3143</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="129">
@@ -17999,13 +17999,13 @@
         <v>0.578</v>
       </c>
       <c r="AF129" t="n">
-        <v>-1.2715</v>
+        <v>-0.915</v>
       </c>
       <c r="AG129" t="n">
-        <v>-0.4857</v>
+        <v>-0.389</v>
       </c>
       <c r="AH129" t="n">
-        <v>0.3143</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="130">
@@ -18105,13 +18105,13 @@
         <v>0.5145999999999999</v>
       </c>
       <c r="AF130" t="n">
-        <v>-1.2679</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="AG130" t="n">
-        <v>-0.4839</v>
+        <v>-0.341</v>
       </c>
       <c r="AH130" t="n">
-        <v>0.3161</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -18211,13 +18211,13 @@
         <v>0.5145999999999999</v>
       </c>
       <c r="AF131" t="n">
-        <v>-1.2679</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="AG131" t="n">
-        <v>-0.4839</v>
+        <v>-0.341</v>
       </c>
       <c r="AH131" t="n">
-        <v>0.3161</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -18317,13 +18317,13 @@
         <v>0.5145999999999999</v>
       </c>
       <c r="AF132" t="n">
-        <v>-1.2679</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="AG132" t="n">
-        <v>-0.4839</v>
+        <v>-0.341</v>
       </c>
       <c r="AH132" t="n">
-        <v>0.3161</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -18423,13 +18423,13 @@
         <v>0.5435</v>
       </c>
       <c r="AF133" t="n">
-        <v>-1.2643</v>
+        <v>-0.97</v>
       </c>
       <c r="AG133" t="n">
-        <v>-0.4821</v>
+        <v>-0.305</v>
       </c>
       <c r="AH133" t="n">
-        <v>0.3179</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="134">
@@ -18529,13 +18529,13 @@
         <v>0.5435</v>
       </c>
       <c r="AF134" t="n">
-        <v>-1.2643</v>
+        <v>-0.97</v>
       </c>
       <c r="AG134" t="n">
-        <v>-0.4821</v>
+        <v>-0.305</v>
       </c>
       <c r="AH134" t="n">
-        <v>0.3179</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="135">
@@ -18635,13 +18635,13 @@
         <v>0.5435</v>
       </c>
       <c r="AF135" t="n">
-        <v>-1.2643</v>
+        <v>-0.97</v>
       </c>
       <c r="AG135" t="n">
-        <v>-0.4821</v>
+        <v>-0.305</v>
       </c>
       <c r="AH135" t="n">
-        <v>0.3179</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="136">
@@ -18741,13 +18741,13 @@
         <v>0.5258</v>
       </c>
       <c r="AF136" t="n">
-        <v>-1.2607</v>
+        <v>-1.029</v>
       </c>
       <c r="AG136" t="n">
-        <v>-0.4803</v>
+        <v>-0.3</v>
       </c>
       <c r="AH136" t="n">
-        <v>0.3197</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="137">
@@ -18847,13 +18847,13 @@
         <v>0.5258</v>
       </c>
       <c r="AF137" t="n">
-        <v>-1.2607</v>
+        <v>-1.029</v>
       </c>
       <c r="AG137" t="n">
-        <v>-0.4803</v>
+        <v>-0.3</v>
       </c>
       <c r="AH137" t="n">
-        <v>0.3197</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="138">
@@ -18953,13 +18953,13 @@
         <v>0.5258</v>
       </c>
       <c r="AF138" t="n">
-        <v>-1.2607</v>
+        <v>-1.029</v>
       </c>
       <c r="AG138" t="n">
-        <v>-0.4803</v>
+        <v>-0.3</v>
       </c>
       <c r="AH138" t="n">
-        <v>0.3197</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="139">
@@ -19059,13 +19059,13 @@
         <v>0.5296</v>
       </c>
       <c r="AF139" t="n">
-        <v>-1.2571</v>
+        <v>-1.065</v>
       </c>
       <c r="AG139" t="n">
-        <v>-0.4786</v>
+        <v>-0.334</v>
       </c>
       <c r="AH139" t="n">
-        <v>0.3214</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="140">
@@ -19165,13 +19165,13 @@
         <v>0.5296</v>
       </c>
       <c r="AF140" t="n">
-        <v>-1.2571</v>
+        <v>-1.065</v>
       </c>
       <c r="AG140" t="n">
-        <v>-0.4786</v>
+        <v>-0.334</v>
       </c>
       <c r="AH140" t="n">
-        <v>0.3214</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="141">
@@ -19271,13 +19271,13 @@
         <v>0.5296</v>
       </c>
       <c r="AF141" t="n">
-        <v>-1.2571</v>
+        <v>-1.065</v>
       </c>
       <c r="AG141" t="n">
-        <v>-0.4786</v>
+        <v>-0.334</v>
       </c>
       <c r="AH141" t="n">
-        <v>0.3214</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="142">
@@ -19377,13 +19377,13 @@
         <v>0.5544</v>
       </c>
       <c r="AF142" t="n">
-        <v>-1.2535</v>
+        <v>-1.074</v>
       </c>
       <c r="AG142" t="n">
-        <v>-0.4768</v>
+        <v>-0.29</v>
       </c>
       <c r="AH142" t="n">
-        <v>0.3232</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="143">
@@ -19483,13 +19483,13 @@
         <v>0.5544</v>
       </c>
       <c r="AF143" t="n">
-        <v>-1.2535</v>
+        <v>-1.074</v>
       </c>
       <c r="AG143" t="n">
-        <v>-0.4768</v>
+        <v>-0.29</v>
       </c>
       <c r="AH143" t="n">
-        <v>0.3232</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="144">
@@ -19589,13 +19589,13 @@
         <v>0.5544</v>
       </c>
       <c r="AF144" t="n">
-        <v>-1.2535</v>
+        <v>-1.074</v>
       </c>
       <c r="AG144" t="n">
-        <v>-0.4768</v>
+        <v>-0.29</v>
       </c>
       <c r="AH144" t="n">
-        <v>0.3232</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="145">
@@ -19695,13 +19695,13 @@
         <v>0.554</v>
       </c>
       <c r="AF145" t="n">
-        <v>-1.2499</v>
+        <v>-1.07</v>
       </c>
       <c r="AG145" t="n">
-        <v>-0.475</v>
+        <v>-0.306</v>
       </c>
       <c r="AH145" t="n">
-        <v>0.325</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="146">
@@ -19801,13 +19801,13 @@
         <v>0.554</v>
       </c>
       <c r="AF146" t="n">
-        <v>-1.2499</v>
+        <v>-1.07</v>
       </c>
       <c r="AG146" t="n">
-        <v>-0.475</v>
+        <v>-0.306</v>
       </c>
       <c r="AH146" t="n">
-        <v>0.325</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="147">
@@ -19907,13 +19907,13 @@
         <v>0.554</v>
       </c>
       <c r="AF147" t="n">
-        <v>-1.2499</v>
+        <v>-1.07</v>
       </c>
       <c r="AG147" t="n">
-        <v>-0.475</v>
+        <v>-0.306</v>
       </c>
       <c r="AH147" t="n">
-        <v>0.325</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="148">
@@ -20013,13 +20013,13 @@
         <v>0.5637</v>
       </c>
       <c r="AF148" t="n">
-        <v>-1.2464</v>
+        <v>-1.065</v>
       </c>
       <c r="AG148" t="n">
-        <v>-0.4732</v>
+        <v>-0.286</v>
       </c>
       <c r="AH148" t="n">
-        <v>0.3268</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="149">
@@ -20119,13 +20119,13 @@
         <v>0.5637</v>
       </c>
       <c r="AF149" t="n">
-        <v>-1.2464</v>
+        <v>-1.065</v>
       </c>
       <c r="AG149" t="n">
-        <v>-0.4732</v>
+        <v>-0.286</v>
       </c>
       <c r="AH149" t="n">
-        <v>0.3268</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="150">
@@ -20225,13 +20225,13 @@
         <v>0.5637</v>
       </c>
       <c r="AF150" t="n">
-        <v>-1.2464</v>
+        <v>-1.065</v>
       </c>
       <c r="AG150" t="n">
-        <v>-0.4732</v>
+        <v>-0.286</v>
       </c>
       <c r="AH150" t="n">
-        <v>0.3268</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="151">
@@ -20331,13 +20331,13 @@
         <v>0.605</v>
       </c>
       <c r="AF151" t="n">
-        <v>-1.2429</v>
+        <v>-1.058</v>
       </c>
       <c r="AG151" t="n">
-        <v>-0.4714</v>
+        <v>-0.309</v>
       </c>
       <c r="AH151" t="n">
-        <v>0.3286</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="152">
@@ -20437,13 +20437,13 @@
         <v>0.605</v>
       </c>
       <c r="AF152" t="n">
-        <v>-1.2429</v>
+        <v>-1.058</v>
       </c>
       <c r="AG152" t="n">
-        <v>-0.4714</v>
+        <v>-0.309</v>
       </c>
       <c r="AH152" t="n">
-        <v>0.3286</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="153">
@@ -20543,13 +20543,13 @@
         <v>0.605</v>
       </c>
       <c r="AF153" t="n">
-        <v>-1.2429</v>
+        <v>-1.058</v>
       </c>
       <c r="AG153" t="n">
-        <v>-0.4714</v>
+        <v>-0.309</v>
       </c>
       <c r="AH153" t="n">
-        <v>0.3286</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="154">
@@ -20649,13 +20649,13 @@
         <v>0.6524</v>
       </c>
       <c r="AF154" t="n">
-        <v>-1.2393</v>
+        <v>-1.049</v>
       </c>
       <c r="AG154" t="n">
-        <v>-0.4696</v>
+        <v>-0.329</v>
       </c>
       <c r="AH154" t="n">
-        <v>0.3304</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="155">
@@ -20755,13 +20755,13 @@
         <v>0.6524</v>
       </c>
       <c r="AF155" t="n">
-        <v>-1.2393</v>
+        <v>-1.049</v>
       </c>
       <c r="AG155" t="n">
-        <v>-0.4696</v>
+        <v>-0.329</v>
       </c>
       <c r="AH155" t="n">
-        <v>0.3304</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="156">
@@ -20861,13 +20861,13 @@
         <v>0.6524</v>
       </c>
       <c r="AF156" t="n">
-        <v>-1.2393</v>
+        <v>-1.049</v>
       </c>
       <c r="AG156" t="n">
-        <v>-0.4696</v>
+        <v>-0.329</v>
       </c>
       <c r="AH156" t="n">
-        <v>0.3304</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="157">
@@ -20967,13 +20967,13 @@
         <v>0.6642</v>
       </c>
       <c r="AF157" t="n">
-        <v>-1.2357</v>
+        <v>-1.038</v>
       </c>
       <c r="AG157" t="n">
-        <v>-0.4678</v>
+        <v>-0.315</v>
       </c>
       <c r="AH157" t="n">
-        <v>0.3322</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="158">
@@ -21073,13 +21073,13 @@
         <v>0.6642</v>
       </c>
       <c r="AF158" t="n">
-        <v>-1.2357</v>
+        <v>-1.038</v>
       </c>
       <c r="AG158" t="n">
-        <v>-0.4678</v>
+        <v>-0.315</v>
       </c>
       <c r="AH158" t="n">
-        <v>0.3322</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="159">
@@ -21179,13 +21179,13 @@
         <v>0.6642</v>
       </c>
       <c r="AF159" t="n">
-        <v>-1.2357</v>
+        <v>-1.038</v>
       </c>
       <c r="AG159" t="n">
-        <v>-0.4678</v>
+        <v>-0.315</v>
       </c>
       <c r="AH159" t="n">
-        <v>0.3322</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="160">
@@ -21285,13 +21285,13 @@
         <v>0.6751</v>
       </c>
       <c r="AF160" t="n">
-        <v>-1.2321</v>
+        <v>-1.021</v>
       </c>
       <c r="AG160" t="n">
-        <v>-0.4661</v>
+        <v>-0.295</v>
       </c>
       <c r="AH160" t="n">
-        <v>0.3339</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="161">
@@ -21391,13 +21391,13 @@
         <v>0.6751</v>
       </c>
       <c r="AF161" t="n">
-        <v>-1.2321</v>
+        <v>-1.021</v>
       </c>
       <c r="AG161" t="n">
-        <v>-0.4661</v>
+        <v>-0.295</v>
       </c>
       <c r="AH161" t="n">
-        <v>0.3339</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="162">
@@ -21497,13 +21497,13 @@
         <v>0.6751</v>
       </c>
       <c r="AF162" t="n">
-        <v>-1.2321</v>
+        <v>-1.021</v>
       </c>
       <c r="AG162" t="n">
-        <v>-0.4661</v>
+        <v>-0.295</v>
       </c>
       <c r="AH162" t="n">
-        <v>0.3339</v>
+        <v>0.464</v>
       </c>
     </row>
     <row r="163">
@@ -21603,13 +21603,13 @@
         <v>0.6768999999999999</v>
       </c>
       <c r="AF163" t="n">
-        <v>-1.2286</v>
+        <v>-1.003</v>
       </c>
       <c r="AG163" t="n">
-        <v>-0.4643</v>
+        <v>-0.356</v>
       </c>
       <c r="AH163" t="n">
-        <v>0.3357</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="164">
@@ -21709,13 +21709,13 @@
         <v>0.6768999999999999</v>
       </c>
       <c r="AF164" t="n">
-        <v>-1.2286</v>
+        <v>-1.003</v>
       </c>
       <c r="AG164" t="n">
-        <v>-0.4643</v>
+        <v>-0.356</v>
       </c>
       <c r="AH164" t="n">
-        <v>0.3357</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="165">
@@ -21815,13 +21815,13 @@
         <v>0.6768999999999999</v>
       </c>
       <c r="AF165" t="n">
-        <v>-1.2286</v>
+        <v>-1.003</v>
       </c>
       <c r="AG165" t="n">
-        <v>-0.4643</v>
+        <v>-0.356</v>
       </c>
       <c r="AH165" t="n">
-        <v>0.3357</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="166">
@@ -21921,13 +21921,13 @@
         <v>0.7045</v>
       </c>
       <c r="AF166" t="n">
-        <v>-1.225</v>
+        <v>-0.988</v>
       </c>
       <c r="AG166" t="n">
-        <v>-0.4625</v>
+        <v>-0.387</v>
       </c>
       <c r="AH166" t="n">
-        <v>0.3375</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="167">
@@ -22027,13 +22027,13 @@
         <v>0.7045</v>
       </c>
       <c r="AF167" t="n">
-        <v>-1.225</v>
+        <v>-0.988</v>
       </c>
       <c r="AG167" t="n">
-        <v>-0.4625</v>
+        <v>-0.387</v>
       </c>
       <c r="AH167" t="n">
-        <v>0.3375</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="168">
@@ -22133,13 +22133,13 @@
         <v>0.7045</v>
       </c>
       <c r="AF168" t="n">
-        <v>-1.225</v>
+        <v>-0.988</v>
       </c>
       <c r="AG168" t="n">
-        <v>-0.4625</v>
+        <v>-0.387</v>
       </c>
       <c r="AH168" t="n">
-        <v>0.3375</v>
+        <v>0.336</v>
       </c>
     </row>
     <row r="169">
@@ -22239,13 +22239,13 @@
         <v>0.7396</v>
       </c>
       <c r="AF169" t="n">
-        <v>-1.2214</v>
+        <v>-0.982</v>
       </c>
       <c r="AG169" t="n">
-        <v>-0.4607</v>
+        <v>-0.437</v>
       </c>
       <c r="AH169" t="n">
-        <v>0.3393</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="170">
@@ -22345,13 +22345,13 @@
         <v>0.7396</v>
       </c>
       <c r="AF170" t="n">
-        <v>-1.2214</v>
+        <v>-0.982</v>
       </c>
       <c r="AG170" t="n">
-        <v>-0.4607</v>
+        <v>-0.437</v>
       </c>
       <c r="AH170" t="n">
-        <v>0.3393</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="171">
@@ -22451,13 +22451,13 @@
         <v>0.7396</v>
       </c>
       <c r="AF171" t="n">
-        <v>-1.2214</v>
+        <v>-0.982</v>
       </c>
       <c r="AG171" t="n">
-        <v>-0.4607</v>
+        <v>-0.437</v>
       </c>
       <c r="AH171" t="n">
-        <v>0.3393</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="172">
@@ -22557,13 +22557,13 @@
         <v>0.7796999999999999</v>
       </c>
       <c r="AF172" t="n">
-        <v>-1.2179</v>
+        <v>-0.974</v>
       </c>
       <c r="AG172" t="n">
-        <v>-0.4589</v>
+        <v>-0.481</v>
       </c>
       <c r="AH172" t="n">
-        <v>0.3411</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="173">
@@ -22663,13 +22663,13 @@
         <v>0.7796999999999999</v>
       </c>
       <c r="AF173" t="n">
-        <v>-1.2179</v>
+        <v>-0.974</v>
       </c>
       <c r="AG173" t="n">
-        <v>-0.4589</v>
+        <v>-0.481</v>
       </c>
       <c r="AH173" t="n">
-        <v>0.3411</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="174">
@@ -22769,13 +22769,13 @@
         <v>0.7796999999999999</v>
       </c>
       <c r="AF174" t="n">
-        <v>-1.2179</v>
+        <v>-0.974</v>
       </c>
       <c r="AG174" t="n">
-        <v>-0.4589</v>
+        <v>-0.481</v>
       </c>
       <c r="AH174" t="n">
-        <v>0.3411</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="175">
@@ -22875,13 +22875,13 @@
         <v>0.7991</v>
       </c>
       <c r="AF175" t="n">
-        <v>-1.2143</v>
+        <v>-0.959</v>
       </c>
       <c r="AG175" t="n">
-        <v>-0.4572</v>
+        <v>-0.526</v>
       </c>
       <c r="AH175" t="n">
-        <v>0.3428</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="176">
@@ -22981,13 +22981,13 @@
         <v>0.7991</v>
       </c>
       <c r="AF176" t="n">
-        <v>-1.2143</v>
+        <v>-0.959</v>
       </c>
       <c r="AG176" t="n">
-        <v>-0.4572</v>
+        <v>-0.526</v>
       </c>
       <c r="AH176" t="n">
-        <v>0.3428</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -23087,13 +23087,13 @@
         <v>0.7991</v>
       </c>
       <c r="AF177" t="n">
-        <v>-1.2143</v>
+        <v>-0.959</v>
       </c>
       <c r="AG177" t="n">
-        <v>-0.4572</v>
+        <v>-0.526</v>
       </c>
       <c r="AH177" t="n">
-        <v>0.3428</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="178">
@@ -23193,13 +23193,13 @@
         <v>0.6589</v>
       </c>
       <c r="AF178" t="n">
-        <v>-1.2107</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="AG178" t="n">
-        <v>-0.4554</v>
+        <v>-0.576</v>
       </c>
       <c r="AH178" t="n">
-        <v>0.3446</v>
+        <v>-0.102</v>
       </c>
     </row>
     <row r="179">
@@ -23299,13 +23299,13 @@
         <v>0.6589</v>
       </c>
       <c r="AF179" t="n">
-        <v>-1.2107</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="AG179" t="n">
-        <v>-0.4554</v>
+        <v>-0.576</v>
       </c>
       <c r="AH179" t="n">
-        <v>0.3446</v>
+        <v>-0.102</v>
       </c>
     </row>
     <row r="180">
@@ -23405,13 +23405,13 @@
         <v>0.6589</v>
       </c>
       <c r="AF180" t="n">
-        <v>-1.2107</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="AG180" t="n">
-        <v>-0.4554</v>
+        <v>-0.576</v>
       </c>
       <c r="AH180" t="n">
-        <v>0.3446</v>
+        <v>-0.102</v>
       </c>
     </row>
     <row r="181">
@@ -23511,13 +23511,13 @@
         <v>0.4732</v>
       </c>
       <c r="AF181" t="n">
-        <v>-1.2071</v>
+        <v>-0.894</v>
       </c>
       <c r="AG181" t="n">
-        <v>-0.4536</v>
+        <v>-0.531</v>
       </c>
       <c r="AH181" t="n">
-        <v>0.3464</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="182">
@@ -23617,13 +23617,13 @@
         <v>0.4732</v>
       </c>
       <c r="AF182" t="n">
-        <v>-1.2071</v>
+        <v>-0.894</v>
       </c>
       <c r="AG182" t="n">
-        <v>-0.4536</v>
+        <v>-0.531</v>
       </c>
       <c r="AH182" t="n">
-        <v>0.3464</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="183">
@@ -23723,13 +23723,13 @@
         <v>0.4732</v>
       </c>
       <c r="AF183" t="n">
-        <v>-1.2071</v>
+        <v>-0.894</v>
       </c>
       <c r="AG183" t="n">
-        <v>-0.4536</v>
+        <v>-0.531</v>
       </c>
       <c r="AH183" t="n">
-        <v>0.3464</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="184">
@@ -23829,13 +23829,13 @@
         <v>0.3311</v>
       </c>
       <c r="AF184" t="n">
-        <v>-1.2036</v>
+        <v>-0.859</v>
       </c>
       <c r="AG184" t="n">
-        <v>-0.4518</v>
+        <v>-0.492</v>
       </c>
       <c r="AH184" t="n">
-        <v>0.3482</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="185">
@@ -23935,13 +23935,13 @@
         <v>0.3311</v>
       </c>
       <c r="AF185" t="n">
-        <v>-1.2036</v>
+        <v>-0.859</v>
       </c>
       <c r="AG185" t="n">
-        <v>-0.4518</v>
+        <v>-0.492</v>
       </c>
       <c r="AH185" t="n">
-        <v>0.3482</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="186">
@@ -24041,13 +24041,13 @@
         <v>0.3311</v>
       </c>
       <c r="AF186" t="n">
-        <v>-1.2036</v>
+        <v>-0.859</v>
       </c>
       <c r="AG186" t="n">
-        <v>-0.4518</v>
+        <v>-0.492</v>
       </c>
       <c r="AH186" t="n">
-        <v>0.3482</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="187">
@@ -24147,13 +24147,13 @@
         <v>0.2213</v>
       </c>
       <c r="AF187" t="n">
-        <v>-1.2</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="AG187" t="n">
-        <v>-0.45</v>
+        <v>-0.467</v>
       </c>
       <c r="AH187" t="n">
-        <v>0.35</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="188">
@@ -24253,13 +24253,13 @@
         <v>0.2213</v>
       </c>
       <c r="AF188" t="n">
-        <v>-1.2</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="AG188" t="n">
-        <v>-0.45</v>
+        <v>-0.467</v>
       </c>
       <c r="AH188" t="n">
-        <v>0.35</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="189">
@@ -24359,13 +24359,13 @@
         <v>0.2213</v>
       </c>
       <c r="AF189" t="n">
-        <v>-1.2</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="AG189" t="n">
-        <v>-0.45</v>
+        <v>-0.467</v>
       </c>
       <c r="AH189" t="n">
-        <v>0.35</v>
+        <v>-0.026</v>
       </c>
     </row>
     <row r="190">
@@ -24465,13 +24465,13 @@
         <v>0.08</v>
       </c>
       <c r="AF190" t="n">
-        <v>-1.1817</v>
+        <v>-0.778</v>
       </c>
       <c r="AG190" t="n">
-        <v>-0.4317</v>
+        <v>-0.421</v>
       </c>
       <c r="AH190" t="n">
-        <v>0.3637</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="191">
@@ -24571,13 +24571,13 @@
         <v>0.08</v>
       </c>
       <c r="AF191" t="n">
-        <v>-1.1817</v>
+        <v>-0.778</v>
       </c>
       <c r="AG191" t="n">
-        <v>-0.4317</v>
+        <v>-0.421</v>
       </c>
       <c r="AH191" t="n">
-        <v>0.3637</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="192">
@@ -24677,13 +24677,13 @@
         <v>0.08</v>
       </c>
       <c r="AF192" t="n">
-        <v>-1.1817</v>
+        <v>-0.778</v>
       </c>
       <c r="AG192" t="n">
-        <v>-0.4317</v>
+        <v>-0.421</v>
       </c>
       <c r="AH192" t="n">
-        <v>0.3637</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="193">
@@ -24783,13 +24783,13 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="AF193" t="n">
-        <v>-1.1633</v>
+        <v>-0.751</v>
       </c>
       <c r="AG193" t="n">
-        <v>-0.4133</v>
+        <v>-0.41</v>
       </c>
       <c r="AH193" t="n">
-        <v>0.3775</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="194">
@@ -24889,13 +24889,13 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="AF194" t="n">
-        <v>-1.1633</v>
+        <v>-0.751</v>
       </c>
       <c r="AG194" t="n">
-        <v>-0.4133</v>
+        <v>-0.41</v>
       </c>
       <c r="AH194" t="n">
-        <v>0.3775</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="195">
@@ -24995,13 +24995,13 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="AF195" t="n">
-        <v>-1.1633</v>
+        <v>-0.751</v>
       </c>
       <c r="AG195" t="n">
-        <v>-0.4133</v>
+        <v>-0.41</v>
       </c>
       <c r="AH195" t="n">
-        <v>0.3775</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="196">
@@ -25101,13 +25101,13 @@
         <v>0.1371</v>
       </c>
       <c r="AF196" t="n">
-        <v>-1.1454</v>
+        <v>-0.737</v>
       </c>
       <c r="AG196" t="n">
-        <v>-0.3954</v>
+        <v>-0.332</v>
       </c>
       <c r="AH196" t="n">
-        <v>0.3909</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="197">
@@ -25207,13 +25207,13 @@
         <v>0.1371</v>
       </c>
       <c r="AF197" t="n">
-        <v>-1.1454</v>
+        <v>-0.737</v>
       </c>
       <c r="AG197" t="n">
-        <v>-0.3954</v>
+        <v>-0.332</v>
       </c>
       <c r="AH197" t="n">
-        <v>0.3909</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="198">
@@ -25313,13 +25313,13 @@
         <v>0.1371</v>
       </c>
       <c r="AF198" t="n">
-        <v>-1.1454</v>
+        <v>-0.737</v>
       </c>
       <c r="AG198" t="n">
-        <v>-0.3954</v>
+        <v>-0.332</v>
       </c>
       <c r="AH198" t="n">
-        <v>0.3909</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="199">
@@ -25419,13 +25419,13 @@
         <v>0.2511</v>
       </c>
       <c r="AF199" t="n">
-        <v>-1.1273</v>
+        <v>-0.73</v>
       </c>
       <c r="AG199" t="n">
-        <v>-0.3773</v>
+        <v>-0.346</v>
       </c>
       <c r="AH199" t="n">
-        <v>0.4045</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="200">
@@ -25525,13 +25525,13 @@
         <v>0.2511</v>
       </c>
       <c r="AF200" t="n">
-        <v>-1.1273</v>
+        <v>-0.73</v>
       </c>
       <c r="AG200" t="n">
-        <v>-0.3773</v>
+        <v>-0.346</v>
       </c>
       <c r="AH200" t="n">
-        <v>0.4045</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="201">
@@ -25631,13 +25631,13 @@
         <v>0.2511</v>
       </c>
       <c r="AF201" t="n">
-        <v>-1.1273</v>
+        <v>-0.73</v>
       </c>
       <c r="AG201" t="n">
-        <v>-0.3773</v>
+        <v>-0.346</v>
       </c>
       <c r="AH201" t="n">
-        <v>0.4045</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="202">
@@ -25737,13 +25737,13 @@
         <v>0.3019</v>
       </c>
       <c r="AF202" t="n">
-        <v>-1.109</v>
+        <v>-0.741</v>
       </c>
       <c r="AG202" t="n">
-        <v>-0.359</v>
+        <v>-0.334</v>
       </c>
       <c r="AH202" t="n">
-        <v>0.4183</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="203">
@@ -25843,13 +25843,13 @@
         <v>0.3019</v>
       </c>
       <c r="AF203" t="n">
-        <v>-1.109</v>
+        <v>-0.741</v>
       </c>
       <c r="AG203" t="n">
-        <v>-0.359</v>
+        <v>-0.334</v>
       </c>
       <c r="AH203" t="n">
-        <v>0.4183</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="204">
@@ -25949,13 +25949,13 @@
         <v>0.3019</v>
       </c>
       <c r="AF204" t="n">
-        <v>-1.109</v>
+        <v>-0.741</v>
       </c>
       <c r="AG204" t="n">
-        <v>-0.359</v>
+        <v>-0.334</v>
       </c>
       <c r="AH204" t="n">
-        <v>0.4183</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="205">
@@ -26055,13 +26055,13 @@
         <v>0.3322</v>
       </c>
       <c r="AF205" t="n">
-        <v>-1.0906</v>
+        <v>-0.753</v>
       </c>
       <c r="AG205" t="n">
-        <v>-0.3406</v>
+        <v>-0.31</v>
       </c>
       <c r="AH205" t="n">
-        <v>0.432</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="206">
@@ -26161,13 +26161,13 @@
         <v>0.3322</v>
       </c>
       <c r="AF206" t="n">
-        <v>-1.0906</v>
+        <v>-0.753</v>
       </c>
       <c r="AG206" t="n">
-        <v>-0.3406</v>
+        <v>-0.31</v>
       </c>
       <c r="AH206" t="n">
-        <v>0.432</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="207">
@@ -26267,13 +26267,13 @@
         <v>0.3322</v>
       </c>
       <c r="AF207" t="n">
-        <v>-1.0906</v>
+        <v>-0.753</v>
       </c>
       <c r="AG207" t="n">
-        <v>-0.3406</v>
+        <v>-0.31</v>
       </c>
       <c r="AH207" t="n">
-        <v>0.432</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="208">
@@ -26373,13 +26373,13 @@
         <v>0.3687</v>
       </c>
       <c r="AF208" t="n">
-        <v>-1.0727</v>
+        <v>-0.767</v>
       </c>
       <c r="AG208" t="n">
-        <v>-0.3227</v>
+        <v>-0.329</v>
       </c>
       <c r="AH208" t="n">
-        <v>0.4455</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="209">
@@ -26479,13 +26479,13 @@
         <v>0.3687</v>
       </c>
       <c r="AF209" t="n">
-        <v>-1.0727</v>
+        <v>-0.767</v>
       </c>
       <c r="AG209" t="n">
-        <v>-0.3227</v>
+        <v>-0.329</v>
       </c>
       <c r="AH209" t="n">
-        <v>0.4455</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="210">
@@ -26585,13 +26585,13 @@
         <v>0.3687</v>
       </c>
       <c r="AF210" t="n">
-        <v>-1.0727</v>
+        <v>-0.767</v>
       </c>
       <c r="AG210" t="n">
-        <v>-0.3227</v>
+        <v>-0.329</v>
       </c>
       <c r="AH210" t="n">
-        <v>0.4455</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="211">
@@ -26691,13 +26691,13 @@
         <v>0.4269</v>
       </c>
       <c r="AF211" t="n">
-        <v>-1.0546</v>
+        <v>-0.789</v>
       </c>
       <c r="AG211" t="n">
-        <v>-0.3046</v>
+        <v>-0.348</v>
       </c>
       <c r="AH211" t="n">
-        <v>0.4591</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="212">
@@ -26797,13 +26797,13 @@
         <v>0.4269</v>
       </c>
       <c r="AF212" t="n">
-        <v>-1.0546</v>
+        <v>-0.789</v>
       </c>
       <c r="AG212" t="n">
-        <v>-0.3046</v>
+        <v>-0.348</v>
       </c>
       <c r="AH212" t="n">
-        <v>0.4591</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="213">
@@ -26903,13 +26903,13 @@
         <v>0.4269</v>
       </c>
       <c r="AF213" t="n">
-        <v>-1.0546</v>
+        <v>-0.789</v>
       </c>
       <c r="AG213" t="n">
-        <v>-0.3046</v>
+        <v>-0.348</v>
       </c>
       <c r="AH213" t="n">
-        <v>0.4591</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="214">
@@ -27009,13 +27009,13 @@
         <v>0.4919</v>
       </c>
       <c r="AF214" t="n">
-        <v>-1.0363</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="AG214" t="n">
-        <v>-0.2863</v>
+        <v>-0.365</v>
       </c>
       <c r="AH214" t="n">
-        <v>0.4728</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="215">
@@ -27115,13 +27115,13 @@
         <v>0.4919</v>
       </c>
       <c r="AF215" t="n">
-        <v>-1.0363</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="AG215" t="n">
-        <v>-0.2863</v>
+        <v>-0.365</v>
       </c>
       <c r="AH215" t="n">
-        <v>0.4728</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="216">
@@ -27221,13 +27221,13 @@
         <v>0.4919</v>
       </c>
       <c r="AF216" t="n">
-        <v>-1.0363</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="AG216" t="n">
-        <v>-0.2863</v>
+        <v>-0.365</v>
       </c>
       <c r="AH216" t="n">
-        <v>0.4728</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="217">
@@ -27327,13 +27327,13 @@
         <v>0.4908</v>
       </c>
       <c r="AF217" t="n">
-        <v>-1.0179</v>
+        <v>-0.841</v>
       </c>
       <c r="AG217" t="n">
-        <v>-0.2679</v>
+        <v>-0.387</v>
       </c>
       <c r="AH217" t="n">
-        <v>0.4866</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="218">
@@ -27433,13 +27433,13 @@
         <v>0.4908</v>
       </c>
       <c r="AF218" t="n">
-        <v>-1.0179</v>
+        <v>-0.841</v>
       </c>
       <c r="AG218" t="n">
-        <v>-0.2679</v>
+        <v>-0.387</v>
       </c>
       <c r="AH218" t="n">
-        <v>0.4866</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="219">
@@ -27539,13 +27539,13 @@
         <v>0.4908</v>
       </c>
       <c r="AF219" t="n">
-        <v>-1.0179</v>
+        <v>-0.841</v>
       </c>
       <c r="AG219" t="n">
-        <v>-0.2679</v>
+        <v>-0.387</v>
       </c>
       <c r="AH219" t="n">
-        <v>0.4866</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="220">
@@ -27645,13 +27645,13 @@
         <v>0.4919</v>
       </c>
       <c r="AF220" t="n">
-        <v>-1</v>
+        <v>-0.877</v>
       </c>
       <c r="AG220" t="n">
-        <v>-0.25</v>
+        <v>-0.412</v>
       </c>
       <c r="AH220" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="221">
@@ -27751,13 +27751,13 @@
         <v>0.4919</v>
       </c>
       <c r="AF221" t="n">
-        <v>-1</v>
+        <v>-0.877</v>
       </c>
       <c r="AG221" t="n">
-        <v>-0.25</v>
+        <v>-0.412</v>
       </c>
       <c r="AH221" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="222">
@@ -27857,13 +27857,13 @@
         <v>0.4919</v>
       </c>
       <c r="AF222" t="n">
-        <v>-1</v>
+        <v>-0.877</v>
       </c>
       <c r="AG222" t="n">
-        <v>-0.25</v>
+        <v>-0.412</v>
       </c>
       <c r="AH222" t="n">
-        <v>0.5</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="223">
@@ -27963,13 +27963,13 @@
         <v>0.5234</v>
       </c>
       <c r="AF223" t="n">
-        <v>-0.99</v>
+        <v>-0.929</v>
       </c>
       <c r="AG223" t="n">
-        <v>-0.245</v>
+        <v>-0.511</v>
       </c>
       <c r="AH223" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="224">
@@ -28069,13 +28069,13 @@
         <v>0.5234</v>
       </c>
       <c r="AF224" t="n">
-        <v>-0.99</v>
+        <v>-0.929</v>
       </c>
       <c r="AG224" t="n">
-        <v>-0.245</v>
+        <v>-0.511</v>
       </c>
       <c r="AH224" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="225">
@@ -28175,13 +28175,13 @@
         <v>0.5234</v>
       </c>
       <c r="AF225" t="n">
-        <v>-0.99</v>
+        <v>-0.929</v>
       </c>
       <c r="AG225" t="n">
-        <v>-0.245</v>
+        <v>-0.511</v>
       </c>
       <c r="AH225" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="226">
@@ -28281,13 +28281,13 @@
         <v>0.5189</v>
       </c>
       <c r="AF226" t="n">
-        <v>-0.98</v>
+        <v>-0.975</v>
       </c>
       <c r="AG226" t="n">
-        <v>-0.24</v>
+        <v>-0.466</v>
       </c>
       <c r="AH226" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="227">
@@ -28387,13 +28387,13 @@
         <v>0.5189</v>
       </c>
       <c r="AF227" t="n">
-        <v>-0.98</v>
+        <v>-0.975</v>
       </c>
       <c r="AG227" t="n">
-        <v>-0.24</v>
+        <v>-0.466</v>
       </c>
       <c r="AH227" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="228">
@@ -28493,13 +28493,13 @@
         <v>0.5189</v>
       </c>
       <c r="AF228" t="n">
-        <v>-0.98</v>
+        <v>-0.975</v>
       </c>
       <c r="AG228" t="n">
-        <v>-0.24</v>
+        <v>-0.466</v>
       </c>
       <c r="AH228" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="229">
@@ -28599,13 +28599,13 @@
         <v>0.5456</v>
       </c>
       <c r="AF229" t="n">
-        <v>-0.9699</v>
+        <v>-1.005</v>
       </c>
       <c r="AG229" t="n">
-        <v>-0.235</v>
+        <v>-0.423</v>
       </c>
       <c r="AH229" t="n">
-        <v>0.5</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="230">
@@ -28705,13 +28705,13 @@
         <v>0.5456</v>
       </c>
       <c r="AF230" t="n">
-        <v>-0.9699</v>
+        <v>-1.005</v>
       </c>
       <c r="AG230" t="n">
-        <v>-0.235</v>
+        <v>-0.423</v>
       </c>
       <c r="AH230" t="n">
-        <v>0.5</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="231">
@@ -28811,13 +28811,13 @@
         <v>0.5456</v>
       </c>
       <c r="AF231" t="n">
-        <v>-0.9699</v>
+        <v>-1.005</v>
       </c>
       <c r="AG231" t="n">
-        <v>-0.235</v>
+        <v>-0.423</v>
       </c>
       <c r="AH231" t="n">
-        <v>0.5</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="232">
@@ -28917,13 +28917,13 @@
         <v>0.5908</v>
       </c>
       <c r="AF232" t="n">
-        <v>-0.96</v>
+        <v>-1.009</v>
       </c>
       <c r="AG232" t="n">
-        <v>-0.23</v>
+        <v>-0.402</v>
       </c>
       <c r="AH232" t="n">
-        <v>0.5</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="233">
@@ -29023,13 +29023,13 @@
         <v>0.5908</v>
       </c>
       <c r="AF233" t="n">
-        <v>-0.96</v>
+        <v>-1.009</v>
       </c>
       <c r="AG233" t="n">
-        <v>-0.23</v>
+        <v>-0.402</v>
       </c>
       <c r="AH233" t="n">
-        <v>0.5</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="234">
@@ -29129,13 +29129,13 @@
         <v>0.5908</v>
       </c>
       <c r="AF234" t="n">
-        <v>-0.96</v>
+        <v>-1.009</v>
       </c>
       <c r="AG234" t="n">
-        <v>-0.23</v>
+        <v>-0.402</v>
       </c>
       <c r="AH234" t="n">
-        <v>0.5</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="235">
@@ -29235,13 +29235,13 @@
         <v>0.6291</v>
       </c>
       <c r="AF235" t="n">
-        <v>-0.95</v>
+        <v>-1.001</v>
       </c>
       <c r="AG235" t="n">
-        <v>-0.225</v>
+        <v>-0.388</v>
       </c>
       <c r="AH235" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="236">
@@ -29341,13 +29341,13 @@
         <v>0.6291</v>
       </c>
       <c r="AF236" t="n">
-        <v>-0.95</v>
+        <v>-1.001</v>
       </c>
       <c r="AG236" t="n">
-        <v>-0.225</v>
+        <v>-0.388</v>
       </c>
       <c r="AH236" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="237">
@@ -29447,13 +29447,13 @@
         <v>0.6291</v>
       </c>
       <c r="AF237" t="n">
-        <v>-0.95</v>
+        <v>-1.001</v>
       </c>
       <c r="AG237" t="n">
-        <v>-0.225</v>
+        <v>-0.388</v>
       </c>
       <c r="AH237" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="238">
@@ -29553,13 +29553,13 @@
         <v>0.631</v>
       </c>
       <c r="AF238" t="n">
-        <v>-0.9399</v>
+        <v>-0.989</v>
       </c>
       <c r="AG238" t="n">
-        <v>-0.22</v>
+        <v>-0.378</v>
       </c>
       <c r="AH238" t="n">
-        <v>0.5</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="239">
@@ -29659,13 +29659,13 @@
         <v>0.631</v>
       </c>
       <c r="AF239" t="n">
-        <v>-0.9399</v>
+        <v>-0.989</v>
       </c>
       <c r="AG239" t="n">
-        <v>-0.22</v>
+        <v>-0.378</v>
       </c>
       <c r="AH239" t="n">
-        <v>0.5</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="240">
@@ -29765,13 +29765,13 @@
         <v>0.631</v>
       </c>
       <c r="AF240" t="n">
-        <v>-0.9399</v>
+        <v>-0.989</v>
       </c>
       <c r="AG240" t="n">
-        <v>-0.22</v>
+        <v>-0.378</v>
       </c>
       <c r="AH240" t="n">
-        <v>0.5</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="241">
@@ -29871,13 +29871,13 @@
         <v>0.6032999999999999</v>
       </c>
       <c r="AF241" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.972</v>
       </c>
       <c r="AG241" t="n">
-        <v>-0.2149</v>
+        <v>-0.381</v>
       </c>
       <c r="AH241" t="n">
-        <v>0.5</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="242">
@@ -29977,13 +29977,13 @@
         <v>0.6032999999999999</v>
       </c>
       <c r="AF242" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.972</v>
       </c>
       <c r="AG242" t="n">
-        <v>-0.2149</v>
+        <v>-0.381</v>
       </c>
       <c r="AH242" t="n">
-        <v>0.5</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="243">
@@ -30083,13 +30083,13 @@
         <v>0.6032999999999999</v>
       </c>
       <c r="AF243" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.972</v>
       </c>
       <c r="AG243" t="n">
-        <v>-0.2149</v>
+        <v>-0.381</v>
       </c>
       <c r="AH243" t="n">
-        <v>0.5</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="244">
@@ -30189,13 +30189,13 @@
         <v>0.6354</v>
       </c>
       <c r="AF244" t="n">
-        <v>-0.92</v>
+        <v>-0.96</v>
       </c>
       <c r="AG244" t="n">
-        <v>-0.21</v>
+        <v>-0.378</v>
       </c>
       <c r="AH244" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="245">
@@ -30295,13 +30295,13 @@
         <v>0.6354</v>
       </c>
       <c r="AF245" t="n">
-        <v>-0.92</v>
+        <v>-0.96</v>
       </c>
       <c r="AG245" t="n">
-        <v>-0.21</v>
+        <v>-0.378</v>
       </c>
       <c r="AH245" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="246">
@@ -30401,13 +30401,13 @@
         <v>0.6354</v>
       </c>
       <c r="AF246" t="n">
-        <v>-0.92</v>
+        <v>-0.96</v>
       </c>
       <c r="AG246" t="n">
-        <v>-0.21</v>
+        <v>-0.378</v>
       </c>
       <c r="AH246" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="247">
@@ -30507,13 +30507,13 @@
         <v>0.6381</v>
       </c>
       <c r="AF247" t="n">
-        <v>-0.9101</v>
+        <v>-0.952</v>
       </c>
       <c r="AG247" t="n">
-        <v>-0.205</v>
+        <v>-0.371</v>
       </c>
       <c r="AH247" t="n">
-        <v>0.5</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="248">
@@ -30613,13 +30613,13 @@
         <v>0.6381</v>
       </c>
       <c r="AF248" t="n">
-        <v>-0.9101</v>
+        <v>-0.952</v>
       </c>
       <c r="AG248" t="n">
-        <v>-0.205</v>
+        <v>-0.371</v>
       </c>
       <c r="AH248" t="n">
-        <v>0.5</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="249">
@@ -30719,13 +30719,13 @@
         <v>0.6381</v>
       </c>
       <c r="AF249" t="n">
-        <v>-0.9101</v>
+        <v>-0.952</v>
       </c>
       <c r="AG249" t="n">
-        <v>-0.205</v>
+        <v>-0.371</v>
       </c>
       <c r="AH249" t="n">
-        <v>0.5</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="250">
@@ -30825,13 +30825,13 @@
         <v>0.6496</v>
       </c>
       <c r="AF250" t="n">
-        <v>-0.9</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG250" t="n">
-        <v>-0.2</v>
+        <v>-0.356</v>
       </c>
       <c r="AH250" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="251">
@@ -30931,13 +30931,13 @@
         <v>0.6496</v>
       </c>
       <c r="AF251" t="n">
-        <v>-0.9</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG251" t="n">
-        <v>-0.2</v>
+        <v>-0.356</v>
       </c>
       <c r="AH251" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="252">
@@ -31037,13 +31037,13 @@
         <v>0.6496</v>
       </c>
       <c r="AF252" t="n">
-        <v>-0.9</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG252" t="n">
-        <v>-0.2</v>
+        <v>-0.356</v>
       </c>
       <c r="AH252" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="253">
@@ -31143,13 +31143,13 @@
         <v>0.7155</v>
       </c>
       <c r="AF253" t="n">
-        <v>-0.8747</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG253" t="n">
-        <v>-0.1747</v>
+        <v>-0.356</v>
       </c>
       <c r="AH253" t="n">
-        <v>0.5253</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="254">
@@ -31249,13 +31249,13 @@
         <v>0.7155</v>
       </c>
       <c r="AF254" t="n">
-        <v>-0.8747</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG254" t="n">
-        <v>-0.1747</v>
+        <v>-0.356</v>
       </c>
       <c r="AH254" t="n">
-        <v>0.5253</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="255">
@@ -31355,13 +31355,13 @@
         <v>0.7155</v>
       </c>
       <c r="AF255" t="n">
-        <v>-0.8747</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG255" t="n">
-        <v>-0.1747</v>
+        <v>-0.356</v>
       </c>
       <c r="AH255" t="n">
-        <v>0.5253</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="256">
@@ -31461,13 +31461,13 @@
         <v>0.6982</v>
       </c>
       <c r="AF256" t="n">
-        <v>-0.85</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG256" t="n">
-        <v>-0.15</v>
+        <v>-0.356</v>
       </c>
       <c r="AH256" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="257">
@@ -31567,13 +31567,13 @@
         <v>0.6982</v>
       </c>
       <c r="AF257" t="n">
-        <v>-0.85</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG257" t="n">
-        <v>-0.15</v>
+        <v>-0.356</v>
       </c>
       <c r="AH257" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="258">
@@ -31673,13 +31673,13 @@
         <v>0.6982</v>
       </c>
       <c r="AF258" t="n">
-        <v>-0.85</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG258" t="n">
-        <v>-0.15</v>
+        <v>-0.356</v>
       </c>
       <c r="AH258" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="259">
@@ -31779,13 +31779,13 @@
         <v>0.7099</v>
       </c>
       <c r="AF259" t="n">
-        <v>-0.85</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="AG259" t="n">
-        <v>-0.15</v>
+        <v>-0.356</v>
       </c>
       <c r="AH259" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -31932,7 +31932,7 @@
         <v>-0.5926</v>
       </c>
       <c r="C4" t="n">
-        <v>0.223</v>
+        <v>-0.168</v>
       </c>
       <c r="D4" t="n">
         <v>0.0762</v>
@@ -31966,7 +31966,7 @@
         <v>-0.5737</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2218</v>
+        <v>-0.1692</v>
       </c>
       <c r="D5" t="n">
         <v>0.0949</v>
@@ -32000,7 +32000,7 @@
         <v>-0.5546</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1995</v>
+        <v>-0.1915</v>
       </c>
       <c r="D6" t="n">
         <v>0.09959999999999999</v>
@@ -32034,7 +32034,7 @@
         <v>-0.5615</v>
       </c>
       <c r="C7" t="n">
-        <v>0.191</v>
+        <v>-0.2131</v>
       </c>
       <c r="D7" t="n">
         <v>0.1047</v>
@@ -32068,7 +32068,7 @@
         <v>-0.5412</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0866</v>
+        <v>-0.3175</v>
       </c>
       <c r="D8" t="n">
         <v>0.1012</v>
@@ -32102,7 +32102,7 @@
         <v>-0.5626</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0555</v>
+        <v>-0.3486</v>
       </c>
       <c r="D9" t="n">
         <v>0.0737</v>
@@ -32136,7 +32136,7 @@
         <v>-0.5044999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.3832</v>
       </c>
       <c r="D10" t="n">
         <v>0.0743</v>
@@ -32170,7 +32170,7 @@
         <v>-0.5384</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0111</v>
+        <v>-0.4532</v>
       </c>
       <c r="D11" t="n">
         <v>0.0372</v>
@@ -32204,7 +32204,7 @@
         <v>-0.5231</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0322</v>
+        <v>-0.4965</v>
       </c>
       <c r="D12" t="n">
         <v>0.0303</v>
@@ -32238,7 +32238,7 @@
         <v>-0.5079</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0309</v>
+        <v>-0.4974</v>
       </c>
       <c r="D13" t="n">
         <v>0.0331</v>
@@ -32272,7 +32272,7 @@
         <v>-0.5006</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0001</v>
+        <v>-0.4666</v>
       </c>
       <c r="D14" t="n">
         <v>0.0395</v>
@@ -32306,7 +32306,7 @@
         <v>-0.5027</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.043</v>
+        <v>-0.5095</v>
       </c>
       <c r="D15" t="n">
         <v>0.0044</v>
@@ -32340,7 +32340,7 @@
         <v>-0.4803</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1073</v>
+        <v>-0.5508</v>
       </c>
       <c r="D16" t="n">
         <v>-0.0435</v>
@@ -32374,7 +32374,7 @@
         <v>-0.485</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1318</v>
+        <v>-0.5753</v>
       </c>
       <c r="D17" t="n">
         <v>-0.091</v>
@@ -32408,7 +32408,7 @@
         <v>-0.4955</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1566</v>
+        <v>-0.6001</v>
       </c>
       <c r="D18" t="n">
         <v>-0.121</v>
@@ -32442,7 +32442,7 @@
         <v>-0.4833</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1514</v>
+        <v>-0.5789</v>
       </c>
       <c r="D19" t="n">
         <v>-0.1324</v>
@@ -32476,7 +32476,7 @@
         <v>-0.4921</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0052</v>
+        <v>-0.4327</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1538</v>
@@ -32510,7 +32510,7 @@
         <v>-0.479</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.038</v>
+        <v>-0.4655</v>
       </c>
       <c r="D21" t="n">
         <v>-0.1254</v>
@@ -32544,7 +32544,7 @@
         <v>-0.4119</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0047</v>
+        <v>-0.4135</v>
       </c>
       <c r="D22" t="n">
         <v>-0.0771</v>
@@ -32578,7 +32578,7 @@
         <v>-0.432</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0412</v>
+        <v>-0.45</v>
       </c>
       <c r="D23" t="n">
         <v>-0.111</v>
@@ -32612,7 +32612,7 @@
         <v>-0.4049</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.043</v>
+        <v>-0.4518</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1243</v>
@@ -32646,7 +32646,7 @@
         <v>-0.3856</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0643</v>
+        <v>-0.3963</v>
       </c>
       <c r="D25" t="n">
         <v>-0.1218</v>
@@ -32680,7 +32680,7 @@
         <v>-0.3758</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1258</v>
+        <v>-0.4578</v>
       </c>
       <c r="D26" t="n">
         <v>-0.124</v>
@@ -32714,7 +32714,7 @@
         <v>-0.4024</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0572</v>
+        <v>-0.2748</v>
       </c>
       <c r="D27" t="n">
         <v>-0.1244</v>
@@ -32748,7 +32748,7 @@
         <v>-0.3921</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0645</v>
+        <v>-0.2194</v>
       </c>
       <c r="D28" t="n">
         <v>-0.1217</v>
@@ -32782,7 +32782,7 @@
         <v>-0.4002</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002</v>
+        <v>-0.2819</v>
       </c>
       <c r="D29" t="n">
         <v>-0.1317</v>
@@ -32816,7 +32816,7 @@
         <v>-0.3948</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0314</v>
+        <v>-0.3153</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1482</v>
@@ -32850,7 +32850,7 @@
         <v>-0.3819</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0235</v>
+        <v>-0.3365</v>
       </c>
       <c r="D31" t="n">
         <v>-0.2063</v>
@@ -32884,7 +32884,7 @@
         <v>-0.3685</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0077</v>
+        <v>-0.3207</v>
       </c>
       <c r="D32" t="n">
         <v>-0.2085</v>
@@ -32918,7 +32918,7 @@
         <v>-0.3647</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1114</v>
+        <v>-0.4244</v>
       </c>
       <c r="D33" t="n">
         <v>-0.1551</v>
@@ -32952,7 +32952,7 @@
         <v>-0.4359</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1253</v>
+        <v>-0.4155</v>
       </c>
       <c r="D34" t="n">
         <v>-0.1294</v>
@@ -32986,7 +32986,7 @@
         <v>-0.4447</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1221</v>
+        <v>-0.4123</v>
       </c>
       <c r="D35" t="n">
         <v>-0.1354</v>
@@ -33020,7 +33020,7 @@
         <v>-0.4332</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2038</v>
+        <v>-0.494</v>
       </c>
       <c r="D36" t="n">
         <v>-0.1064</v>
@@ -33054,7 +33054,7 @@
         <v>-0.4982</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1892</v>
+        <v>-0.4466</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0963</v>
@@ -33088,7 +33088,7 @@
         <v>-0.5091</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1758</v>
+        <v>-0.4332</v>
       </c>
       <c r="D38" t="n">
         <v>-0.0568</v>
@@ -33122,7 +33122,7 @@
         <v>-0.5078</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2892</v>
+        <v>-0.5466</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0597</v>
@@ -33156,7 +33156,7 @@
         <v>-0.5872000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2515</v>
+        <v>-0.442</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0387</v>
@@ -33190,7 +33190,7 @@
         <v>-0.5968</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3416</v>
+        <v>-0.5321</v>
       </c>
       <c r="D41" t="n">
         <v>-0.0679</v>
@@ -33224,7 +33224,7 @@
         <v>-0.5969</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.294</v>
+        <v>-0.4845</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1367</v>
@@ -33258,7 +33258,7 @@
         <v>-0.6729000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.3262</v>
+        <v>-0.5208</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1625</v>
@@ -33292,7 +33292,7 @@
         <v>-0.652</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.3489</v>
+        <v>-0.5435</v>
       </c>
       <c r="D44" t="n">
         <v>-0.126</v>
@@ -33326,7 +33326,7 @@
         <v>-0.644</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.3811</v>
+        <v>-0.5757</v>
       </c>
       <c r="D45" t="n">
         <v>-0.08989999999999999</v>
@@ -33360,7 +33360,7 @@
         <v>-0.7097</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.3936</v>
+        <v>-0.5534</v>
       </c>
       <c r="D46" t="n">
         <v>-0.09959999999999999</v>
@@ -33394,7 +33394,7 @@
         <v>-0.7362</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.3888</v>
+        <v>-0.5486</v>
       </c>
       <c r="D47" t="n">
         <v>-0.1036</v>
@@ -33428,7 +33428,7 @@
         <v>-0.7168</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2461</v>
+        <v>-0.4059</v>
       </c>
       <c r="D48" t="n">
         <v>-0.055</v>
@@ -33462,7 +33462,7 @@
         <v>-0.768</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.2033</v>
+        <v>-0.3283</v>
       </c>
       <c r="D49" t="n">
         <v>-0.0243</v>
@@ -33496,7 +33496,7 @@
         <v>-0.7941</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0545</v>
+        <v>-0.1795</v>
       </c>
       <c r="D50" t="n">
         <v>0.0226</v>
@@ -33530,7 +33530,7 @@
         <v>-0.8284</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2167</v>
+        <v>0.0917</v>
       </c>
       <c r="D51" t="n">
         <v>0.0066</v>
@@ -33564,7 +33564,7 @@
         <v>-0.9377</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3527</v>
+        <v>0.2357</v>
       </c>
       <c r="D52" t="n">
         <v>0.0086</v>
@@ -33598,7 +33598,7 @@
         <v>-0.9875</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5456</v>
+        <v>0.4286</v>
       </c>
       <c r="D53" t="n">
         <v>-0.002</v>
@@ -33632,7 +33632,7 @@
         <v>-0.9837</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8093</v>
+        <v>0.6923</v>
       </c>
       <c r="D54" t="n">
         <v>0.0091</v>
@@ -33666,7 +33666,7 @@
         <v>-1.0384</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.8633</v>
       </c>
       <c r="D55" t="n">
         <v>0.0157</v>
@@ -33700,7 +33700,7 @@
         <v>-1.0652</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9336</v>
+        <v>0.8216</v>
       </c>
       <c r="D56" t="n">
         <v>0.0414</v>
@@ -33734,7 +33734,7 @@
         <v>-1.102</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9248</v>
+        <v>0.8128</v>
       </c>
       <c r="D57" t="n">
         <v>0.0388</v>
@@ -33768,7 +33768,7 @@
         <v>-1.0559</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9406</v>
+        <v>0.7933</v>
       </c>
       <c r="D58" t="n">
         <v>0.054</v>
@@ -33802,7 +33802,7 @@
         <v>-1.0969</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9092</v>
+        <v>0.7619</v>
       </c>
       <c r="D59" t="n">
         <v>0.0474</v>
@@ -33836,7 +33836,7 @@
         <v>-1.1172</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8671</v>
+        <v>0.7198</v>
       </c>
       <c r="D60" t="n">
         <v>0.0426</v>
@@ -33870,7 +33870,7 @@
         <v>-1.0924</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8462</v>
+        <v>0.6397</v>
       </c>
       <c r="D61" t="n">
         <v>0.0735</v>
@@ -33904,7 +33904,7 @@
         <v>-1.1161</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8189</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="D62" t="n">
         <v>0.0683</v>
@@ -33938,7 +33938,7 @@
         <v>-1.1305</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7642</v>
+        <v>0.5577</v>
       </c>
       <c r="D63" t="n">
         <v>0.06809999999999999</v>
@@ -33972,7 +33972,7 @@
         <v>-1.0983</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7181</v>
+        <v>0.4857</v>
       </c>
       <c r="D64" t="n">
         <v>0.0696</v>
@@ -34006,7 +34006,7 @@
         <v>-1.1179</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7288</v>
+        <v>0.4964</v>
       </c>
       <c r="D65" t="n">
         <v>0.0658</v>
@@ -34040,7 +34040,7 @@
         <v>-1.1365</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.385</v>
       </c>
       <c r="D66" t="n">
         <v>0.0732</v>
@@ -34074,7 +34074,7 @@
         <v>-1.0987</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6747</v>
+        <v>0.4892</v>
       </c>
       <c r="D67" t="n">
         <v>0.0835</v>
@@ -34108,7 +34108,7 @@
         <v>-1.0951</v>
       </c>
       <c r="C68" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.4511</v>
       </c>
       <c r="D68" t="n">
         <v>0.0954</v>
@@ -34142,7 +34142,7 @@
         <v>-1.0713</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5488</v>
+        <v>0.3633</v>
       </c>
       <c r="D69" t="n">
         <v>0.1094</v>
@@ -34176,7 +34176,7 @@
         <v>-0.9788</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5564</v>
+        <v>0.3677</v>
       </c>
       <c r="D70" t="n">
         <v>0.1048</v>
@@ -34210,7 +34210,7 @@
         <v>-0.9614</v>
       </c>
       <c r="C71" t="n">
-        <v>0.4596</v>
+        <v>0.2709</v>
       </c>
       <c r="D71" t="n">
         <v>0.1217</v>
@@ -34244,7 +34244,7 @@
         <v>-0.9629</v>
       </c>
       <c r="C72" t="n">
-        <v>0.4581</v>
+        <v>0.2694</v>
       </c>
       <c r="D72" t="n">
         <v>0.0979</v>
@@ -34278,7 +34278,7 @@
         <v>-0.9134</v>
       </c>
       <c r="C73" t="n">
-        <v>0.366</v>
+        <v>0.1911</v>
       </c>
       <c r="D73" t="n">
         <v>0.0737</v>
@@ -34312,7 +34312,7 @@
         <v>-0.9112</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3275</v>
+        <v>0.1526</v>
       </c>
       <c r="D74" t="n">
         <v>0.0747</v>
@@ -34346,7 +34346,7 @@
         <v>-0.8949</v>
       </c>
       <c r="C75" t="n">
-        <v>0.3123</v>
+        <v>0.1374</v>
       </c>
       <c r="D75" t="n">
         <v>0.0577</v>
@@ -34380,7 +34380,7 @@
         <v>-0.7965</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2727</v>
+        <v>0.0478</v>
       </c>
       <c r="D76" t="n">
         <v>0.0643</v>
@@ -34414,7 +34414,7 @@
         <v>-0.7561</v>
       </c>
       <c r="C77" t="n">
-        <v>0.318</v>
+        <v>0.0931</v>
       </c>
       <c r="D77" t="n">
         <v>0.0658</v>
@@ -34448,7 +34448,7 @@
         <v>-0.7647</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2156</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="D78" t="n">
         <v>0.0806</v>
@@ -34482,7 +34482,7 @@
         <v>-0.7344000000000001</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1924</v>
+        <v>-0.0546</v>
       </c>
       <c r="D79" t="n">
         <v>0.08790000000000001</v>
@@ -34516,7 +34516,7 @@
         <v>-0.7269</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1889</v>
+        <v>-0.0581</v>
       </c>
       <c r="D80" t="n">
         <v>0.0917</v>
@@ -34550,7 +34550,7 @@
         <v>-0.7073</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1998</v>
+        <v>-0.0472</v>
       </c>
       <c r="D81" t="n">
         <v>0.103</v>
@@ -34584,7 +34584,7 @@
         <v>-0.6696</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1773</v>
+        <v>-0.0369</v>
       </c>
       <c r="D82" t="n">
         <v>0.1073</v>
@@ -34618,7 +34618,7 @@
         <v>-0.68</v>
       </c>
       <c r="C83" t="n">
-        <v>0.057</v>
+        <v>-0.1572</v>
       </c>
       <c r="D83" t="n">
         <v>0.1051</v>
@@ -34652,7 +34652,7 @@
         <v>-0.6629</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0735</v>
+        <v>-0.1407</v>
       </c>
       <c r="D84" t="n">
         <v>0.1069</v>
@@ -34686,7 +34686,7 @@
         <v>-0.6377</v>
       </c>
       <c r="C85" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.1975</v>
       </c>
       <c r="D85" t="n">
         <v>0.1065</v>
@@ -34720,7 +34720,7 @@
         <v>-0.6048</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.0169</v>
+        <v>-0.2243</v>
       </c>
       <c r="D86" t="n">
         <v>0.1089</v>
@@ -34754,7 +34754,7 @@
         <v>-0.5842000000000001</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0158</v>
+        <v>-0.1916</v>
       </c>
       <c r="D87" t="n">
         <v>0.112</v>
@@ -34788,7 +34788,7 @@
         <v>-0.5570000000000001</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.0888</v>
+        <v>-0.2963</v>
       </c>
       <c r="D88" t="n">
         <v>0.1119</v>
@@ -34822,7 +34822,7 @@
         <v>-0.5429</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.094</v>
+        <v>-0.3015</v>
       </c>
       <c r="D89" t="n">
         <v>0.1161</v>
@@ -34856,7 +34856,7 @@
         <v>-0.5137</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.0761</v>
+        <v>-0.2836</v>
       </c>
       <c r="D90" t="n">
         <v>0.1266</v>
@@ -34890,7 +34890,7 @@
         <v>-0.4755</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.1451</v>
+        <v>-0.4176</v>
       </c>
       <c r="D91" t="n">
         <v>0.1315</v>
@@ -34924,7 +34924,7 @@
         <v>-0.4499</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.2106</v>
+        <v>-0.4831</v>
       </c>
       <c r="D92" t="n">
         <v>0.138</v>
@@ -34958,7 +34958,7 @@
         <v>-0.4452</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.2003</v>
+        <v>-0.4728</v>
       </c>
       <c r="D93" t="n">
         <v>0.135</v>
@@ -34992,7 +34992,7 @@
         <v>-0.3953</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.2764</v>
+        <v>-0.5682</v>
       </c>
       <c r="D94" t="n">
         <v>0.1365</v>
@@ -35026,7 +35026,7 @@
         <v>-0.3826</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.2267</v>
+        <v>-0.5185</v>
       </c>
       <c r="D95" t="n">
         <v>0.1387</v>
@@ -35060,7 +35060,7 @@
         <v>-0.335</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.2546</v>
+        <v>-0.5464</v>
       </c>
       <c r="D96" t="n">
         <v>0.1408</v>
@@ -35094,7 +35094,7 @@
         <v>-0.2991</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.2788</v>
+        <v>-0.5738</v>
       </c>
       <c r="D97" t="n">
         <v>0.143</v>
@@ -35128,7 +35128,7 @@
         <v>-0.2988</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.3255</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="D98" t="n">
         <v>0.1433</v>
@@ -35162,7 +35162,7 @@
         <v>-0.2616</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.3433</v>
+        <v>-0.6383</v>
       </c>
       <c r="D99" t="n">
         <v>0.1533</v>
@@ -35196,7 +35196,7 @@
         <v>-0.2291</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.369</v>
+        <v>-0.6399</v>
       </c>
       <c r="D100" t="n">
         <v>0.1696</v>
@@ -35230,7 +35230,7 @@
         <v>-0.205</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.3658</v>
+        <v>-0.6367</v>
       </c>
       <c r="D101" t="n">
         <v>0.1535</v>
@@ -35264,7 +35264,7 @@
         <v>-0.1845</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.4643</v>
+        <v>-0.7352</v>
       </c>
       <c r="D102" t="n">
         <v>0.1264</v>
@@ -35298,7 +35298,7 @@
         <v>-0.1571</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.4159</v>
+        <v>-0.6519</v>
       </c>
       <c r="D103" t="n">
         <v>0.1238</v>
@@ -35332,7 +35332,7 @@
         <v>-0.1159</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.5068</v>
+        <v>-0.7428</v>
       </c>
       <c r="D104" t="n">
         <v>0.1256</v>
@@ -35366,7 +35366,7 @@
         <v>-0.1111</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.5272</v>
+        <v>-0.7632</v>
       </c>
       <c r="D105" t="n">
         <v>0.1344</v>
@@ -35400,7 +35400,7 @@
         <v>-0.1165</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.5202</v>
+        <v>-0.7134</v>
       </c>
       <c r="D106" t="n">
         <v>0.1391</v>
@@ -35434,7 +35434,7 @@
         <v>-0.0871</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.5985</v>
+        <v>-0.7917</v>
       </c>
       <c r="D107" t="n">
         <v>0.1517</v>
@@ -35468,7 +35468,7 @@
         <v>-0.0789</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.6315</v>
+        <v>-0.8247</v>
       </c>
       <c r="D108" t="n">
         <v>0.1536</v>
@@ -35502,7 +35502,7 @@
         <v>0.176</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.6771</v>
+        <v>-0.8275</v>
       </c>
       <c r="D109" t="n">
         <v>1.2316</v>
@@ -35536,7 +35536,7 @@
         <v>-0.0238</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.7478</v>
+        <v>-0.8982</v>
       </c>
       <c r="D110" t="n">
         <v>0.1502</v>
@@ -35570,7 +35570,7 @@
         <v>-0.0191</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.7503</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="D111" t="n">
         <v>0.1583</v>
@@ -35604,7 +35604,7 @@
         <v>0.009599999999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.7319</v>
+        <v>-0.8355</v>
       </c>
       <c r="D112" t="n">
         <v>0.16</v>
@@ -35638,7 +35638,7 @@
         <v>0.2343</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.7782</v>
+        <v>-0.8818</v>
       </c>
       <c r="D113" t="n">
         <v>1.2372</v>
@@ -35672,7 +35672,7 @@
         <v>0.2583</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.7962</v>
+        <v>-0.8998</v>
       </c>
       <c r="D114" t="n">
         <v>1.2383</v>
@@ -35706,7 +35706,7 @@
         <v>0.2538</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.7749</v>
+        <v>-0.9068000000000001</v>
       </c>
       <c r="D115" t="n">
         <v>1.2403</v>
@@ -35740,7 +35740,7 @@
         <v>0.2956</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.7304</v>
+        <v>-0.8623</v>
       </c>
       <c r="D116" t="n">
         <v>1.2498</v>
@@ -35774,7 +35774,7 @@
         <v>0.296</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.6811</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="D117" t="n">
         <v>1.2518</v>
@@ -35808,7 +35808,7 @@
         <v>0.3215</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.6401</v>
+        <v>-0.7902</v>
       </c>
       <c r="D118" t="n">
         <v>1.2507</v>
@@ -35842,7 +35842,7 @@
         <v>0.3483</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.5545</v>
+        <v>-0.7046</v>
       </c>
       <c r="D119" t="n">
         <v>1.2624</v>
@@ -35876,7 +35876,7 @@
         <v>0.3646</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.5393</v>
+        <v>-0.6894</v>
       </c>
       <c r="D120" t="n">
         <v>1.268</v>
@@ -35910,7 +35910,7 @@
         <v>0.1758</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.5256</v>
+        <v>-0.6829</v>
       </c>
       <c r="D121" t="n">
         <v>0.2039</v>
@@ -35944,7 +35944,7 @@
         <v>0.3876</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.4633</v>
+        <v>-0.6206</v>
       </c>
       <c r="D122" t="n">
         <v>1.297</v>
@@ -35978,7 +35978,7 @@
         <v>0.3985</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.3805</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="D123" t="n">
         <v>1.2755</v>
@@ -36012,7 +36012,7 @@
         <v>0.4715</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.4008</v>
+        <v>-0.5003</v>
       </c>
       <c r="D124" t="n">
         <v>1.2773</v>
@@ -36046,7 +36046,7 @@
         <v>0.2439</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.3135</v>
+        <v>-0.413</v>
       </c>
       <c r="D125" t="n">
         <v>0.2026</v>
@@ -36080,7 +36080,7 @@
         <v>0.2703</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.3233</v>
+        <v>-0.4228</v>
       </c>
       <c r="D126" t="n">
         <v>0.1965</v>
@@ -36114,7 +36114,7 @@
         <v>0.2812</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.3127</v>
+        <v>-0.4094</v>
       </c>
       <c r="D127" t="n">
         <v>0.1923</v>
@@ -36148,7 +36148,7 @@
         <v>0.2757</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.2012</v>
+        <v>-0.2979</v>
       </c>
       <c r="D128" t="n">
         <v>0.1933</v>
@@ -36182,7 +36182,7 @@
         <v>0.2667</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.2455</v>
+        <v>-0.3422</v>
       </c>
       <c r="D129" t="n">
         <v>0.1981</v>
@@ -36216,7 +36216,7 @@
         <v>0.2875</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.1268</v>
+        <v>-0.2697</v>
       </c>
       <c r="D130" t="n">
         <v>0.2012</v>
@@ -36250,7 +36250,7 @@
         <v>0.2822</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.1192</v>
+        <v>-0.2621</v>
       </c>
       <c r="D131" t="n">
         <v>0.2062</v>
@@ -36284,7 +36284,7 @@
         <v>0.2811</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.0614</v>
+        <v>-0.2043</v>
       </c>
       <c r="D132" t="n">
         <v>0.2087</v>
@@ -36318,7 +36318,7 @@
         <v>0.3175</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.2626</v>
       </c>
       <c r="D133" t="n">
         <v>0.2175</v>
@@ -36352,7 +36352,7 @@
         <v>0.2962</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.0362</v>
+        <v>-0.2133</v>
       </c>
       <c r="D134" t="n">
         <v>0.2247</v>
@@ -36386,7 +36386,7 @@
         <v>0.3194</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.1889</v>
+        <v>-0.366</v>
       </c>
       <c r="D135" t="n">
         <v>0.2864</v>
@@ -36420,7 +36420,7 @@
         <v>0.3323</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.1694</v>
+        <v>-0.3497</v>
       </c>
       <c r="D136" t="n">
         <v>0.2926</v>
@@ -36454,7 +36454,7 @@
         <v>0.3217</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.13</v>
+        <v>-0.3103</v>
       </c>
       <c r="D137" t="n">
         <v>0.3076</v>
@@ -36488,7 +36488,7 @@
         <v>0.3342</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.092</v>
+        <v>-0.2723</v>
       </c>
       <c r="D138" t="n">
         <v>0.3166</v>
@@ -36522,7 +36522,7 @@
         <v>0.3763</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0015</v>
+        <v>-0.1431</v>
       </c>
       <c r="D139" t="n">
         <v>0.3268</v>
@@ -36556,7 +36556,7 @@
         <v>0.3737</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.0521</v>
+        <v>-0.1967</v>
       </c>
       <c r="D140" t="n">
         <v>0.3549</v>
@@ -36590,7 +36590,7 @@
         <v>0.3454</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.0198</v>
+        <v>-0.1644</v>
       </c>
       <c r="D141" t="n">
         <v>0.3006</v>
@@ -36624,7 +36624,7 @@
         <v>0.3605</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.0544</v>
+        <v>-0.2412</v>
       </c>
       <c r="D142" t="n">
         <v>0.3097</v>
@@ -36658,7 +36658,7 @@
         <v>0.3864</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.0471</v>
+        <v>-0.2339</v>
       </c>
       <c r="D143" t="n">
         <v>0.321</v>
@@ -36692,7 +36692,7 @@
         <v>0.4018</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0078</v>
+        <v>-0.179</v>
       </c>
       <c r="D144" t="n">
         <v>0.3052</v>
@@ -36726,7 +36726,7 @@
         <v>0.4666</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0054</v>
+        <v>-0.1636</v>
       </c>
       <c r="D145" t="n">
         <v>0.4904</v>
@@ -36760,7 +36760,7 @@
         <v>0.4271</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0278</v>
+        <v>-0.1412</v>
       </c>
       <c r="D146" t="n">
         <v>0.3023</v>
@@ -36794,7 +36794,7 @@
         <v>0.4283</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0566</v>
+        <v>-0.1124</v>
       </c>
       <c r="D147" t="n">
         <v>0.2953</v>
@@ -36828,7 +36828,7 @@
         <v>0.4202</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.0332</v>
+        <v>-0.2204</v>
       </c>
       <c r="D148" t="n">
         <v>0.3065</v>
@@ -36862,7 +36862,7 @@
         <v>0.4553</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0354</v>
+        <v>-0.1518</v>
       </c>
       <c r="D149" t="n">
         <v>0.2918</v>
@@ -36896,7 +36896,7 @@
         <v>0.4579</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0617</v>
+        <v>-0.1255</v>
       </c>
       <c r="D150" t="n">
         <v>0.2799</v>
@@ -36930,7 +36930,7 @@
         <v>0.4557</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0464</v>
+        <v>-0.116</v>
       </c>
       <c r="D151" t="n">
         <v>0.2655</v>
@@ -36964,7 +36964,7 @@
         <v>0.4758</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0346</v>
+        <v>-0.1278</v>
       </c>
       <c r="D152" t="n">
         <v>0.258</v>
@@ -36998,7 +36998,7 @@
         <v>0.4721</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.0031</v>
+        <v>-0.1655</v>
       </c>
       <c r="D153" t="n">
         <v>0.266</v>
@@ -37032,7 +37032,7 @@
         <v>0.4911</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.0027</v>
+        <v>-0.1433</v>
       </c>
       <c r="D154" t="n">
         <v>0.2741</v>
@@ -37066,7 +37066,7 @@
         <v>0.5138</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0039</v>
+        <v>-0.1367</v>
       </c>
       <c r="D155" t="n">
         <v>0.2689</v>
@@ -37100,7 +37100,7 @@
         <v>0.5806</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0403</v>
+        <v>-0.1003</v>
       </c>
       <c r="D156" t="n">
         <v>0.749</v>
@@ -37134,7 +37134,7 @@
         <v>0.6353</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0832</v>
+        <v>-0.0696</v>
       </c>
       <c r="D157" t="n">
         <v>0.892</v>
@@ -37168,7 +37168,7 @@
         <v>0.6395</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0692</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="D158" t="n">
         <v>0.732</v>
@@ -37202,7 +37202,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="C159" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.0842</v>
       </c>
       <c r="D159" t="n">
         <v>0.7368</v>
@@ -37236,7 +37236,7 @@
         <v>0.6413</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0706</v>
+        <v>-0.1005</v>
       </c>
       <c r="D160" t="n">
         <v>0.7411</v>
@@ -37270,7 +37270,7 @@
         <v>0.6437</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0267</v>
+        <v>-0.1444</v>
       </c>
       <c r="D161" t="n">
         <v>0.7383</v>
@@ -37304,7 +37304,7 @@
         <v>0.6655</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0395</v>
+        <v>-0.1316</v>
       </c>
       <c r="D162" t="n">
         <v>0.7363</v>
@@ -37338,7 +37338,7 @@
         <v>0.6855</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0508</v>
+        <v>-0.0575</v>
       </c>
       <c r="D163" t="n">
         <v>0.7354000000000001</v>
@@ -37372,7 +37372,7 @@
         <v>0.6847</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0608</v>
+        <v>-0.0475</v>
       </c>
       <c r="D164" t="n">
         <v>0.7333</v>
@@ -37406,7 +37406,7 @@
         <v>0.7030999999999999</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0791</v>
+        <v>-0.0292</v>
       </c>
       <c r="D165" t="n">
         <v>0.7249</v>
@@ -37440,7 +37440,7 @@
         <v>0.7068</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0968</v>
+        <v>0.0213</v>
       </c>
       <c r="D166" t="n">
         <v>0.7225</v>
@@ -37474,7 +37474,7 @@
         <v>0.7208</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0367</v>
+        <v>-0.0388</v>
       </c>
       <c r="D167" t="n">
         <v>0.7251</v>
@@ -37508,7 +37508,7 @@
         <v>0.6392</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0575</v>
+        <v>-0.018</v>
       </c>
       <c r="D168" t="n">
         <v>0.266</v>
@@ -37542,7 +37542,7 @@
         <v>0.8257</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0494</v>
+        <v>0.0257</v>
       </c>
       <c r="D169" t="n">
         <v>1.34</v>
@@ -37576,7 +37576,7 @@
         <v>0.9275</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0779</v>
+        <v>0.0542</v>
       </c>
       <c r="D170" t="n">
         <v>1.7034</v>
@@ -37610,7 +37610,7 @@
         <v>0.916</v>
       </c>
       <c r="C171" t="n">
-        <v>0.1262</v>
+        <v>0.1025</v>
       </c>
       <c r="D171" t="n">
         <v>1.7091</v>
@@ -37644,7 +37644,7 @@
         <v>0.9529</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0791</v>
+        <v>0.1012</v>
       </c>
       <c r="D172" t="n">
         <v>1.7061</v>
@@ -37678,7 +37678,7 @@
         <v>0.9424</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1374</v>
+        <v>0.1595</v>
       </c>
       <c r="D173" t="n">
         <v>1.7062</v>
@@ -37712,7 +37712,7 @@
         <v>0.9591</v>
       </c>
       <c r="C174" t="n">
-        <v>0.143</v>
+        <v>0.1651</v>
       </c>
       <c r="D174" t="n">
         <v>1.7076</v>
@@ -37746,7 +37746,7 @@
         <v>0.9705</v>
       </c>
       <c r="C175" t="n">
-        <v>0.1453</v>
+        <v>0.2141</v>
       </c>
       <c r="D175" t="n">
         <v>1.7257</v>
@@ -37780,7 +37780,7 @@
         <v>0.9832</v>
       </c>
       <c r="C176" t="n">
-        <v>0.1387</v>
+        <v>0.2075</v>
       </c>
       <c r="D176" t="n">
         <v>1.7265</v>
@@ -37814,7 +37814,7 @@
         <v>0.9727</v>
       </c>
       <c r="C177" t="n">
-        <v>0.077</v>
+        <v>0.1458</v>
       </c>
       <c r="D177" t="n">
         <v>1.7513</v>
@@ -37848,7 +37848,7 @@
         <v>0.8915999999999999</v>
       </c>
       <c r="C178" t="n">
-        <v>0.1453</v>
+        <v>0.2659</v>
       </c>
       <c r="D178" t="n">
         <v>1.7593</v>
@@ -37882,7 +37882,7 @@
         <v>0.8987000000000001</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0901</v>
+        <v>0.2107</v>
       </c>
       <c r="D179" t="n">
         <v>1.7488</v>
@@ -37916,7 +37916,7 @@
         <v>0.8724</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1644</v>
+        <v>0.285</v>
       </c>
       <c r="D180" t="n">
         <v>1.7201</v>
@@ -37950,7 +37950,7 @@
         <v>0.5235</v>
       </c>
       <c r="C181" t="n">
-        <v>0.1263</v>
+        <v>0.2037</v>
       </c>
       <c r="D181" t="n">
         <v>0.2734</v>
@@ -37984,7 +37984,7 @@
         <v>0.5381</v>
       </c>
       <c r="C182" t="n">
-        <v>0.1088</v>
+        <v>0.1862</v>
       </c>
       <c r="D182" t="n">
         <v>0.2734</v>
@@ -38018,7 +38018,7 @@
         <v>0.5604</v>
       </c>
       <c r="C183" t="n">
-        <v>0.1094</v>
+        <v>0.1868</v>
       </c>
       <c r="D183" t="n">
         <v>0.2868</v>
@@ -38052,7 +38052,7 @@
         <v>0.4191</v>
       </c>
       <c r="C184" t="n">
-        <v>0.1333</v>
+        <v>0.1735</v>
       </c>
       <c r="D184" t="n">
         <v>0.2994</v>
@@ -38086,7 +38086,7 @@
         <v>0.4283</v>
       </c>
       <c r="C185" t="n">
-        <v>0.1307</v>
+        <v>0.1709</v>
       </c>
       <c r="D185" t="n">
         <v>0.2795</v>
@@ -38120,7 +38120,7 @@
         <v>0.4513</v>
       </c>
       <c r="C186" t="n">
-        <v>0.1936</v>
+        <v>0.2338</v>
       </c>
       <c r="D186" t="n">
         <v>0.2826</v>
@@ -38154,7 +38154,7 @@
         <v>0.4099</v>
       </c>
       <c r="C187" t="n">
-        <v>0.1223</v>
+        <v>0.1393</v>
       </c>
       <c r="D187" t="n">
         <v>0.278</v>
@@ -38188,7 +38188,7 @@
         <v>0.3682</v>
       </c>
       <c r="C188" t="n">
-        <v>0.09</v>
+        <v>0.107</v>
       </c>
       <c r="D188" t="n">
         <v>0.2764</v>
@@ -38222,7 +38222,7 @@
         <v>0.3332</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0852</v>
+        <v>0.1022</v>
       </c>
       <c r="D189" t="n">
         <v>0.2668</v>
@@ -38256,7 +38256,7 @@
         <v>0.3325</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.0179</v>
+        <v>-0.0286</v>
       </c>
       <c r="D190" t="n">
         <v>0.2712</v>
@@ -38290,7 +38290,7 @@
         <v>0.3092</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.0464</v>
+        <v>-0.0571</v>
       </c>
       <c r="D191" t="n">
         <v>0.2705</v>
@@ -38324,7 +38324,7 @@
         <v>0.28</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.1013</v>
+        <v>-0.112</v>
       </c>
       <c r="D192" t="n">
         <v>0.2725</v>
@@ -38358,7 +38358,7 @@
         <v>0.5341</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.1619</v>
+        <v>-0.1652</v>
       </c>
       <c r="D193" t="n">
         <v>1.4907</v>
@@ -38392,7 +38392,7 @@
         <v>0.2507</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.181</v>
+        <v>-0.1843</v>
       </c>
       <c r="D194" t="n">
         <v>0.2676</v>
@@ -38426,7 +38426,7 @@
         <v>0.2179</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.2154</v>
+        <v>-0.2187</v>
       </c>
       <c r="D195" t="n">
         <v>0.2613</v>
@@ -38460,7 +38460,7 @@
         <v>0.2229</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.3056</v>
+        <v>-0.369</v>
       </c>
       <c r="D196" t="n">
         <v>0.2608</v>
@@ -38494,7 +38494,7 @@
         <v>0.2123</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.3788</v>
+        <v>-0.4422</v>
       </c>
       <c r="D197" t="n">
         <v>0.2628</v>
@@ -38528,7 +38528,7 @@
         <v>0.1451</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.4015</v>
+        <v>-0.4649</v>
       </c>
       <c r="D198" t="n">
         <v>0.2634</v>
@@ -38562,7 +38562,7 @@
         <v>0.1335</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.4651</v>
+        <v>-0.4964</v>
       </c>
       <c r="D199" t="n">
         <v>0.2634</v>
@@ -38596,7 +38596,7 @@
         <v>0.4672</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.5458</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="D200" t="n">
         <v>1.8588</v>
@@ -38630,7 +38630,7 @@
         <v>0.4879</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.6249</v>
+        <v>-0.6562</v>
       </c>
       <c r="D201" t="n">
         <v>1.8623</v>
@@ -38664,7 +38664,7 @@
         <v>0.5971</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.6512</v>
+        <v>-0.6762</v>
       </c>
       <c r="D202" t="n">
         <v>1.8556</v>
@@ -38698,7 +38698,7 @@
         <v>0.5603</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.6737</v>
+        <v>-0.6987</v>
       </c>
       <c r="D203" t="n">
         <v>1.8501</v>
@@ -38732,7 +38732,7 @@
         <v>0.6026</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.7195</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="D204" t="n">
         <v>1.8529</v>
@@ -38766,7 +38766,7 @@
         <v>0.3971</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.8053</v>
+        <v>-0.8359</v>
       </c>
       <c r="D205" t="n">
         <v>0.619</v>
@@ -38800,7 +38800,7 @@
         <v>0.664</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.8897</v>
+        <v>-0.9203</v>
       </c>
       <c r="D206" t="n">
         <v>1.8374</v>
@@ -38834,7 +38834,7 @@
         <v>0.669</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.9205</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="D207" t="n">
         <v>1.8218</v>
@@ -38868,7 +38868,7 @@
         <v>0.7047</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.9116</v>
+        <v>-0.9053</v>
       </c>
       <c r="D208" t="n">
         <v>1.8206</v>
@@ -38902,7 +38902,7 @@
         <v>0.7456</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.9821</v>
+        <v>-0.9758</v>
       </c>
       <c r="D209" t="n">
         <v>1.8232</v>
@@ -38936,7 +38936,7 @@
         <v>0.7395</v>
       </c>
       <c r="C210" t="n">
-        <v>-1.0519</v>
+        <v>-1.0456</v>
       </c>
       <c r="D210" t="n">
         <v>1.8235</v>
@@ -38970,7 +38970,7 @@
         <v>0.7989000000000001</v>
       </c>
       <c r="C211" t="n">
-        <v>-1.1482</v>
+        <v>-1.1048</v>
       </c>
       <c r="D211" t="n">
         <v>1.8244</v>
@@ -39004,7 +39004,7 @@
         <v>0.4745</v>
       </c>
       <c r="C212" t="n">
-        <v>-1.183</v>
+        <v>-1.1396</v>
       </c>
       <c r="D212" t="n">
         <v>0.2407</v>
@@ -39038,7 +39038,7 @@
         <v>0.5017</v>
       </c>
       <c r="C213" t="n">
-        <v>-1.1636</v>
+        <v>-1.1202</v>
       </c>
       <c r="D213" t="n">
         <v>0.2468</v>
@@ -39072,7 +39072,7 @@
         <v>0.5566</v>
       </c>
       <c r="C214" t="n">
-        <v>-1.2622</v>
+        <v>-1.1835</v>
       </c>
       <c r="D214" t="n">
         <v>0.2368</v>
@@ -39106,7 +39106,7 @@
         <v>0.5542</v>
       </c>
       <c r="C215" t="n">
-        <v>-1.3419</v>
+        <v>-1.2632</v>
       </c>
       <c r="D215" t="n">
         <v>0.2311</v>
@@ -39140,7 +39140,7 @@
         <v>0.5416</v>
       </c>
       <c r="C216" t="n">
-        <v>-1.4045</v>
+        <v>-1.3258</v>
       </c>
       <c r="D216" t="n">
         <v>0.2272</v>
@@ -39174,7 +39174,7 @@
         <v>1.1129</v>
       </c>
       <c r="C217" t="n">
-        <v>-1.4378</v>
+        <v>-1.3187</v>
       </c>
       <c r="D217" t="n">
         <v>2.8667</v>
@@ -39208,7 +39208,7 @@
         <v>0.5685</v>
       </c>
       <c r="C218" t="n">
-        <v>-1.5256</v>
+        <v>-1.4065</v>
       </c>
       <c r="D218" t="n">
         <v>0.1879</v>
@@ -39242,7 +39242,7 @@
         <v>0.6099</v>
       </c>
       <c r="C219" t="n">
-        <v>-1.6152</v>
+        <v>-1.4961</v>
       </c>
       <c r="D219" t="n">
         <v>0.1996</v>
@@ -39276,7 +39276,7 @@
         <v>0.6502</v>
       </c>
       <c r="C220" t="n">
-        <v>-1.7821</v>
+        <v>-1.6201</v>
       </c>
       <c r="D220" t="n">
         <v>0.2157</v>
@@ -39310,7 +39310,7 @@
         <v>0.6563</v>
       </c>
       <c r="C221" t="n">
-        <v>-1.8481</v>
+        <v>-1.6861</v>
       </c>
       <c r="D221" t="n">
         <v>0.2098</v>
@@ -39344,7 +39344,7 @@
         <v>0.9575</v>
       </c>
       <c r="C222" t="n">
-        <v>-1.9645</v>
+        <v>-1.8025</v>
       </c>
       <c r="D222" t="n">
         <v>1.7086</v>
@@ -39378,7 +39378,7 @@
         <v>1.1487</v>
       </c>
       <c r="C223" t="n">
-        <v>-2.078</v>
+        <v>-1.812</v>
       </c>
       <c r="D223" t="n">
         <v>2.4933</v>
@@ -39412,7 +39412,7 @@
         <v>1.3289</v>
       </c>
       <c r="C224" t="n">
-        <v>-2.0636</v>
+        <v>-1.7976</v>
       </c>
       <c r="D224" t="n">
         <v>3.3341</v>
@@ -39446,7 +39446,7 @@
         <v>1.3271</v>
       </c>
       <c r="C225" t="n">
-        <v>-2.0644</v>
+        <v>-1.7984</v>
       </c>
       <c r="D225" t="n">
         <v>3.3043</v>
@@ -39480,7 +39480,7 @@
         <v>1.3431</v>
       </c>
       <c r="C226" t="n">
-        <v>-2.0119</v>
+        <v>-1.7859</v>
       </c>
       <c r="D226" t="n">
         <v>3.2917</v>
@@ -39514,7 +39514,7 @@
         <v>1.3297</v>
       </c>
       <c r="C227" t="n">
-        <v>-2.0449</v>
+        <v>-1.8189</v>
       </c>
       <c r="D227" t="n">
         <v>3.274</v>
@@ -39548,7 +39548,7 @@
         <v>1.3432</v>
       </c>
       <c r="C228" t="n">
-        <v>-1.9835</v>
+        <v>-1.7575</v>
       </c>
       <c r="D228" t="n">
         <v>3.2723</v>
@@ -39582,7 +39582,7 @@
         <v>0.923</v>
       </c>
       <c r="C229" t="n">
-        <v>-1.9719</v>
+        <v>-1.7839</v>
       </c>
       <c r="D229" t="n">
         <v>0.9935</v>
@@ -39616,7 +39616,7 @@
         <v>1.4267</v>
       </c>
       <c r="C230" t="n">
-        <v>-2.0048</v>
+        <v>-1.8168</v>
       </c>
       <c r="D230" t="n">
         <v>3.2956</v>
@@ -39650,7 +39650,7 @@
         <v>1.4217</v>
       </c>
       <c r="C231" t="n">
-        <v>-2.0089</v>
+        <v>-1.8209</v>
       </c>
       <c r="D231" t="n">
         <v>3.2679</v>
@@ -39684,7 +39684,7 @@
         <v>1.4617</v>
       </c>
       <c r="C232" t="n">
-        <v>-1.885</v>
+        <v>-1.713</v>
       </c>
       <c r="D232" t="n">
         <v>3.251</v>
@@ -39718,7 +39718,7 @@
         <v>1.4531</v>
       </c>
       <c r="C233" t="n">
-        <v>-1.8162</v>
+        <v>-1.6442</v>
       </c>
       <c r="D233" t="n">
         <v>3.2317</v>
@@ -39752,7 +39752,7 @@
         <v>1.1287</v>
       </c>
       <c r="C234" t="n">
-        <v>-1.821</v>
+        <v>-1.649</v>
       </c>
       <c r="D234" t="n">
         <v>1.6425</v>
@@ -39786,7 +39786,7 @@
         <v>0.9908</v>
       </c>
       <c r="C235" t="n">
-        <v>-1.8192</v>
+        <v>-1.6562</v>
       </c>
       <c r="D235" t="n">
         <v>0.8717</v>
@@ -39820,7 +39820,7 @@
         <v>0.8213</v>
       </c>
       <c r="C236" t="n">
-        <v>-1.6004</v>
+        <v>-1.4374</v>
       </c>
       <c r="D236" t="n">
         <v>0.0623</v>
@@ -39854,7 +39854,7 @@
         <v>0.7895</v>
       </c>
       <c r="C237" t="n">
-        <v>-1.6349</v>
+        <v>-1.4719</v>
       </c>
       <c r="D237" t="n">
         <v>0.0727</v>
@@ -39888,7 +39888,7 @@
         <v>0.7903</v>
       </c>
       <c r="C238" t="n">
-        <v>-1.6448</v>
+        <v>-1.4868</v>
       </c>
       <c r="D238" t="n">
         <v>0.0689</v>
@@ -39922,7 +39922,7 @@
         <v>0.7999000000000001</v>
       </c>
       <c r="C239" t="n">
-        <v>-1.5616</v>
+        <v>-1.4036</v>
       </c>
       <c r="D239" t="n">
         <v>0.0527</v>
@@ -39956,7 +39956,7 @@
         <v>0.7769</v>
       </c>
       <c r="C240" t="n">
-        <v>-1.5767</v>
+        <v>-1.4187</v>
       </c>
       <c r="D240" t="n">
         <v>0.0058</v>
@@ -39990,7 +39990,7 @@
         <v>1.0045</v>
       </c>
       <c r="C241" t="n">
-        <v>-1.6109</v>
+        <v>-1.4448</v>
       </c>
       <c r="D241" t="n">
         <v>1.1588</v>
@@ -40024,7 +40024,7 @@
         <v>1.0537</v>
       </c>
       <c r="C242" t="n">
-        <v>-1.3626</v>
+        <v>-1.1965</v>
       </c>
       <c r="D242" t="n">
         <v>1.5271</v>
@@ -40058,7 +40058,7 @@
         <v>1.0388</v>
       </c>
       <c r="C243" t="n">
-        <v>-1.2948</v>
+        <v>-1.1287</v>
       </c>
       <c r="D243" t="n">
         <v>1.4852</v>
@@ -40092,7 +40092,7 @@
         <v>1.0637</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.2666</v>
+        <v>-1.0986</v>
       </c>
       <c r="D244" t="n">
         <v>1.4554</v>
@@ -40126,7 +40126,7 @@
         <v>1.0231</v>
       </c>
       <c r="C245" t="n">
-        <v>-1.2917</v>
+        <v>-1.1237</v>
       </c>
       <c r="D245" t="n">
         <v>1.5134</v>
@@ -40160,7 +40160,7 @@
         <v>1.0464</v>
       </c>
       <c r="C246" t="n">
-        <v>-1.3073</v>
+        <v>-1.1393</v>
       </c>
       <c r="D246" t="n">
         <v>1.4929</v>
@@ -40194,7 +40194,7 @@
         <v>1.0101</v>
       </c>
       <c r="C247" t="n">
-        <v>-1.2459</v>
+        <v>-1.0799</v>
       </c>
       <c r="D247" t="n">
         <v>1.4838</v>
@@ -40228,7 +40228,7 @@
         <v>1.0033</v>
       </c>
       <c r="C248" t="n">
-        <v>-1.2832</v>
+        <v>-1.1172</v>
       </c>
       <c r="D248" t="n">
         <v>1.4658</v>
@@ -40262,7 +40262,7 @@
         <v>1.0206</v>
       </c>
       <c r="C249" t="n">
-        <v>-1.3149</v>
+        <v>-1.1489</v>
       </c>
       <c r="D249" t="n">
         <v>1.4498</v>
@@ -40296,7 +40296,7 @@
         <v>1.0131</v>
       </c>
       <c r="C250" t="n">
-        <v>-1.3282</v>
+        <v>-1.1722</v>
       </c>
       <c r="D250" t="n">
         <v>1.4267</v>
@@ -40330,7 +40330,7 @@
         <v>1.0323</v>
       </c>
       <c r="C251" t="n">
-        <v>-1.3331</v>
+        <v>-1.1771</v>
       </c>
       <c r="D251" t="n">
         <v>1.4131</v>
@@ -40364,7 +40364,7 @@
         <v>1.0371</v>
       </c>
       <c r="C252" t="n">
-        <v>-1.272</v>
+        <v>-1.116</v>
       </c>
       <c r="D252" t="n">
         <v>1.4021</v>
@@ -40398,7 +40398,7 @@
         <v>0.7009</v>
       </c>
       <c r="C253" t="n">
-        <v>-1.124</v>
+        <v>-0.9427</v>
       </c>
       <c r="D253" t="n">
         <v>-0.2209</v>
@@ -40432,7 +40432,7 @@
         <v>0.6983</v>
       </c>
       <c r="C254" t="n">
-        <v>-1.0902</v>
+        <v>-0.9089</v>
       </c>
       <c r="D254" t="n">
         <v>-0.2764</v>
@@ -40466,7 +40466,7 @@
         <v>0.708</v>
       </c>
       <c r="C255" t="n">
-        <v>-1.0808</v>
+        <v>-0.8995</v>
       </c>
       <c r="D255" t="n">
         <v>-0.2927</v>
@@ -40500,7 +40500,7 @@
         <v>0.6602</v>
       </c>
       <c r="C256" t="n">
-        <v>-1.126</v>
+        <v>-0.92</v>
       </c>
       <c r="D256" t="n">
         <v>-0.3</v>
@@ -40534,7 +40534,7 @@
         <v>0.619</v>
       </c>
       <c r="C257" t="n">
-        <v>-1.0548</v>
+        <v>-0.8488</v>
       </c>
       <c r="D257" t="n">
         <v>-0.34</v>
@@ -40568,7 +40568,7 @@
         <v>0.6657999999999999</v>
       </c>
       <c r="C258" t="n">
-        <v>-1.1339</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="D258" t="n">
         <v>-0.3692</v>
@@ -40602,7 +40602,7 @@
         <v>0.7954</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.8293</v>
+        <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
         <v>0.1856</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="228">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.141</v>
+        <v>1.143</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.652</v>
+        <v>2.653</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.838</v>
+        <v>-0.837</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.853</v>
+        <v>0.854</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67704.318</v>
+        <v>67826.909</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31692,19 +31692,19 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>1.1409</v>
+        <v>1.1426</v>
       </c>
       <c r="D259" t="n">
-        <v>1.41</v>
+        <v>1.4103</v>
       </c>
       <c r="E259" t="n">
-        <v>1.9388</v>
+        <v>1.9392</v>
       </c>
       <c r="F259" t="n">
-        <v>2.6517</v>
+        <v>2.6532</v>
       </c>
       <c r="G259" t="n">
-        <v>3.7979</v>
+        <v>3.7978</v>
       </c>
       <c r="H259" t="n">
         <v>1.9793</v>
@@ -31716,25 +31716,25 @@
         <v>1.7988</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.8384</v>
+        <v>-0.8367</v>
       </c>
       <c r="L259" t="n">
-        <v>-0.2742</v>
+        <v>-0.2739</v>
       </c>
       <c r="M259" t="n">
-        <v>0.8529</v>
+        <v>0.8544</v>
       </c>
       <c r="N259" t="n">
         <v>-0.9792999999999999</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.3686</v>
+        <v>-0.3669</v>
       </c>
       <c r="P259" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0771</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.1422</v>
+        <v>1.1437</v>
       </c>
       <c r="R259" t="n">
         <v>1.1708</v>
@@ -31761,7 +31761,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z259" t="n">
-        <v>67704.3175</v>
+        <v>67826.9094</v>
       </c>
       <c r="AA259" t="n">
         <v>161.498</v>
@@ -31997,7 +31997,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5062</v>
+        <v>-0.5061</v>
       </c>
       <c r="C6" t="n">
         <v>-0.0915</v>
@@ -32086,7 +32086,7 @@
         <v>-0.334</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4034</v>
+        <v>-0.4033</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3545</v>
@@ -32346,7 +32346,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5591</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="F16" t="n">
         <v>0.09089999999999999</v>
@@ -32584,7 +32584,7 @@
         <v>0.025</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4958</v>
+        <v>-0.4957</v>
       </c>
       <c r="F23" t="n">
         <v>0.025</v>
@@ -32618,7 +32618,7 @@
         <v>0.0534</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4607</v>
+        <v>-0.4606</v>
       </c>
       <c r="F24" t="n">
         <v>0.0534</v>
@@ -32630,7 +32630,7 @@
         <v>0.1042</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0346</v>
+        <v>-0.0345</v>
       </c>
       <c r="J24" t="n">
         <v>-0.5577</v>
@@ -32677,7 +32677,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3454</v>
+        <v>-0.3453</v>
       </c>
       <c r="C26" t="n">
         <v>-0.3078</v>
@@ -32800,7 +32800,7 @@
         <v>0.1443</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0878</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>-0.4567</v>
@@ -32970,7 +32970,7 @@
         <v>-0.2168</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0689</v>
       </c>
       <c r="J34" t="n">
         <v>-0.0348</v>
@@ -33174,7 +33174,7 @@
         <v>-1.0493</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5582</v>
+        <v>-0.5581</v>
       </c>
       <c r="J40" t="n">
         <v>0.3645</v>
@@ -33323,7 +33323,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4104</v>
+        <v>-0.4103</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3257</v>
@@ -33363,13 +33363,13 @@
         <v>-0.3034</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9775</v>
+        <v>0.9776</v>
       </c>
       <c r="E46" t="n">
         <v>-0.8575</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9775</v>
+        <v>0.9776</v>
       </c>
       <c r="G46" t="n">
         <v>-1.7931</v>
@@ -33434,7 +33434,7 @@
         <v>0.4548</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.9124</v>
+        <v>-0.9123</v>
       </c>
       <c r="F48" t="n">
         <v>0.4548</v>
@@ -33514,7 +33514,7 @@
         <v>-2.2435</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1133</v>
+        <v>-1.1132</v>
       </c>
       <c r="J50" t="n">
         <v>0.7669</v>
@@ -33536,7 +33536,7 @@
         <v>0.1178</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0742</v>
+        <v>-1.0741</v>
       </c>
       <c r="F51" t="n">
         <v>0.1178</v>
@@ -33548,7 +33548,7 @@
         <v>-2.2435</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1265</v>
+        <v>-1.1264</v>
       </c>
       <c r="J51" t="n">
         <v>0.6102</v>
@@ -33595,7 +33595,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9765</v>
+        <v>-0.9764</v>
       </c>
       <c r="C53" t="n">
         <v>0.6286</v>
@@ -33956,7 +33956,7 @@
         <v>-2.4338</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.1063</v>
+        <v>-1.1062</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4515</v>
@@ -34250,7 +34250,7 @@
         <v>-0.1495</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2351</v>
+        <v>-1.235</v>
       </c>
       <c r="F72" t="n">
         <v>-0.1495</v>
@@ -34296,7 +34296,7 @@
         <v>-1.1721</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2103</v>
+        <v>-1.2102</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8474</v>
@@ -34330,7 +34330,7 @@
         <v>-1.1721</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2366</v>
+        <v>-1.2365</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8237</v>
@@ -34364,7 +34364,7 @@
         <v>-1.1721</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2264</v>
+        <v>-1.2263</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8019</v>
@@ -34466,7 +34466,7 @@
         <v>-0.7467</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2645</v>
+        <v>-1.2644</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6214</v>
@@ -34615,7 +34615,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6617</v>
       </c>
       <c r="C83" t="n">
         <v>0.09279999999999999</v>
@@ -34624,7 +34624,7 @@
         <v>0.1823</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.8728</v>
+        <v>-0.8727</v>
       </c>
       <c r="F83" t="n">
         <v>0.1823</v>
@@ -34704,7 +34704,7 @@
         <v>-0.569</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3407</v>
+        <v>-1.3406</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2711</v>
@@ -34726,7 +34726,7 @@
         <v>0.2368</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7914</v>
+        <v>-0.7913</v>
       </c>
       <c r="F86" t="n">
         <v>0.2368</v>
@@ -34874,7 +34874,7 @@
         <v>-0.5154</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.3071</v>
+        <v>-1.307</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9081</v>
@@ -34908,7 +34908,7 @@
         <v>-0.3809</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.3093</v>
+        <v>-1.3092</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9362</v>
@@ -34976,7 +34976,7 @@
         <v>-0.3809</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3109</v>
+        <v>-1.3108</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8108</v>
@@ -34998,7 +34998,7 @@
         <v>0.2719</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.572</v>
       </c>
       <c r="F94" t="n">
         <v>0.2719</v>
@@ -35010,7 +35010,7 @@
         <v>-0.2429</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3207</v>
+        <v>-1.3206</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7756999999999999</v>
@@ -35044,7 +35044,7 @@
         <v>-0.2429</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.3076</v>
+        <v>-1.3075</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7816</v>
@@ -35329,7 +35329,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.0397</v>
+        <v>-0.0396</v>
       </c>
       <c r="C104" t="n">
         <v>-0.5427999999999999</v>
@@ -35384,7 +35384,7 @@
         <v>-0.0924</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7679</v>
+        <v>-0.7678</v>
       </c>
       <c r="J105" t="n">
         <v>-0.241</v>
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
       <c r="C108" t="n">
         <v>-0.6247</v>
@@ -35486,7 +35486,7 @@
         <v>-0.0349</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6495</v>
+        <v>-0.6494</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2862</v>
@@ -36018,7 +36018,7 @@
         <v>1.2797</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2838</v>
+        <v>0.2837</v>
       </c>
       <c r="F124" t="n">
         <v>1.2797</v>
@@ -36540,7 +36540,7 @@
         <v>0.7845</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1773</v>
+        <v>-0.1772</v>
       </c>
       <c r="J139" t="n">
         <v>0.1242</v>
@@ -37186,7 +37186,7 @@
         <v>0.8008999999999999</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1189</v>
+        <v>0.1188</v>
       </c>
       <c r="J158" t="n">
         <v>1.0065</v>
@@ -37424,7 +37424,7 @@
         <v>0.8361</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1176</v>
+        <v>0.1175</v>
       </c>
       <c r="J165" t="n">
         <v>1.3217</v>
@@ -37492,7 +37492,7 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="I167" t="n">
-        <v>0.128</v>
+        <v>0.1279</v>
       </c>
       <c r="J167" t="n">
         <v>1.39</v>
@@ -37545,13 +37545,13 @@
         <v>0.4257</v>
       </c>
       <c r="D169" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.6982</v>
       </c>
       <c r="E169" t="n">
         <v>0.7329</v>
       </c>
       <c r="F169" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.6982</v>
       </c>
       <c r="G169" t="n">
         <v>0.5735</v>
@@ -37560,7 +37560,7 @@
         <v>0.879</v>
       </c>
       <c r="I169" t="n">
-        <v>0.059</v>
+        <v>0.0589</v>
       </c>
       <c r="J169" t="n">
         <v>1.4199</v>
@@ -37922,7 +37922,7 @@
         <v>0.6763</v>
       </c>
       <c r="E180" t="n">
-        <v>0.6796</v>
+        <v>0.6795</v>
       </c>
       <c r="F180" t="n">
         <v>0.6763</v>
@@ -38126,7 +38126,7 @@
         <v>0.399</v>
       </c>
       <c r="E186" t="n">
-        <v>0.4933</v>
+        <v>0.4932</v>
       </c>
       <c r="F186" t="n">
         <v>0.399</v>
@@ -38376,7 +38376,7 @@
         <v>-0.4872</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0155</v>
+        <v>0.0154</v>
       </c>
       <c r="J193" t="n">
         <v>0.8569</v>
@@ -38410,7 +38410,7 @@
         <v>-0.4872</v>
       </c>
       <c r="I194" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J194" t="n">
         <v>0.5568</v>
@@ -38478,7 +38478,7 @@
         <v>-0.2759</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2185</v>
+        <v>0.2184</v>
       </c>
       <c r="J196" t="n">
         <v>0.0843</v>
@@ -38512,7 +38512,7 @@
         <v>-0.2759</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2635</v>
+        <v>0.2634</v>
       </c>
       <c r="J197" t="n">
         <v>-0.0983</v>
@@ -38546,7 +38546,7 @@
         <v>-0.2759</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2704</v>
+        <v>0.2703</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4217</v>
@@ -38614,7 +38614,7 @@
         <v>-0.1601</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3246</v>
+        <v>0.3245</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6143</v>
@@ -38648,7 +38648,7 @@
         <v>-0.1601</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3384</v>
+        <v>0.3383</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5955</v>
@@ -38750,7 +38750,7 @@
         <v>0.0994</v>
       </c>
       <c r="I204" t="n">
-        <v>0.474</v>
+        <v>0.4739</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4212</v>
@@ -38784,7 +38784,7 @@
         <v>0.2221</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4794</v>
+        <v>0.4793</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3821</v>
@@ -38886,7 +38886,7 @@
         <v>0.4073</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5145</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2458</v>
@@ -38908,7 +38908,7 @@
         <v>1.2979</v>
       </c>
       <c r="E209" t="n">
-        <v>0.439</v>
+        <v>0.4389</v>
       </c>
       <c r="F209" t="n">
         <v>1.2979</v>
@@ -38988,7 +38988,7 @@
         <v>0.5412</v>
       </c>
       <c r="I211" t="n">
-        <v>0.8032</v>
+        <v>0.8031</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1077</v>
@@ -39022,7 +39022,7 @@
         <v>0.5412</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8405</v>
+        <v>0.8404</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1226</v>
@@ -39090,7 +39090,7 @@
         <v>0.6193</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9686</v>
+        <v>0.9685</v>
       </c>
       <c r="J214" t="n">
         <v>0.0835</v>
@@ -39124,7 +39124,7 @@
         <v>0.6193</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0395</v>
+        <v>1.0394</v>
       </c>
       <c r="J215" t="n">
         <v>0.033</v>
@@ -39192,7 +39192,7 @@
         <v>0.7063</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8474</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="J217" t="n">
         <v>0.1713</v>
@@ -39226,7 +39226,7 @@
         <v>0.7063</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7759</v>
+        <v>0.7758</v>
       </c>
       <c r="J218" t="n">
         <v>0.142</v>
@@ -39239,7 +39239,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8698</v>
+        <v>0.8697</v>
       </c>
       <c r="C219" t="n">
         <v>-1.0961</v>
@@ -39328,7 +39328,7 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8719</v>
+        <v>0.8718</v>
       </c>
       <c r="J221" t="n">
         <v>0.3133</v>
@@ -39384,7 +39384,7 @@
         <v>1.7742</v>
       </c>
       <c r="E223" t="n">
-        <v>0.8032</v>
+        <v>0.8031</v>
       </c>
       <c r="F223" t="n">
         <v>1.7742</v>
@@ -39396,7 +39396,7 @@
         <v>0.8531</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1037</v>
+        <v>1.1036</v>
       </c>
       <c r="J223" t="n">
         <v>0.3699</v>
@@ -39430,7 +39430,7 @@
         <v>0.8531</v>
       </c>
       <c r="I224" t="n">
-        <v>1.1228</v>
+        <v>1.1227</v>
       </c>
       <c r="J224" t="n">
         <v>0.3796</v>
@@ -39464,7 +39464,7 @@
         <v>0.8531</v>
       </c>
       <c r="I225" t="n">
-        <v>1.2126</v>
+        <v>1.2125</v>
       </c>
       <c r="J225" t="n">
         <v>0.3975</v>
@@ -39498,7 +39498,7 @@
         <v>0.9577</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2832</v>
+        <v>1.2831</v>
       </c>
       <c r="J226" t="n">
         <v>0.3603</v>
@@ -39520,7 +39520,7 @@
         <v>1.5257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.868</v>
+        <v>0.8679</v>
       </c>
       <c r="F227" t="n">
         <v>1.5257</v>
@@ -39532,7 +39532,7 @@
         <v>0.9577</v>
       </c>
       <c r="I227" t="n">
-        <v>1.313</v>
+        <v>1.3129</v>
       </c>
       <c r="J227" t="n">
         <v>0.3583</v>
@@ -39545,7 +39545,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9801</v>
+        <v>0.98</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39600,7 +39600,7 @@
         <v>1.0556</v>
       </c>
       <c r="I229" t="n">
-        <v>1.3153</v>
+        <v>1.3152</v>
       </c>
       <c r="J229" t="n">
         <v>0.3868</v>
@@ -39634,7 +39634,7 @@
         <v>1.0556</v>
       </c>
       <c r="I230" t="n">
-        <v>1.4218</v>
+        <v>1.4217</v>
       </c>
       <c r="J230" t="n">
         <v>0.4868</v>
@@ -39647,7 +39647,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0741</v>
+        <v>1.074</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -39668,7 +39668,7 @@
         <v>1.0556</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5679</v>
+        <v>1.5678</v>
       </c>
       <c r="J231" t="n">
         <v>0.4234</v>
@@ -39681,7 +39681,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0963</v>
+        <v>1.0962</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39702,7 +39702,7 @@
         <v>1.1556</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6359</v>
+        <v>1.6358</v>
       </c>
       <c r="J232" t="n">
         <v>0.4843</v>
@@ -39715,7 +39715,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0553</v>
+        <v>1.0552</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -39736,7 +39736,7 @@
         <v>1.1556</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6989</v>
+        <v>1.6988</v>
       </c>
       <c r="J233" t="n">
         <v>0.4768</v>
@@ -39770,7 +39770,7 @@
         <v>1.1556</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7461</v>
+        <v>1.746</v>
       </c>
       <c r="J234" t="n">
         <v>0.4773</v>
@@ -39804,7 +39804,7 @@
         <v>1.1507</v>
       </c>
       <c r="I235" t="n">
-        <v>1.8306</v>
+        <v>1.8305</v>
       </c>
       <c r="J235" t="n">
         <v>0.5446</v>
@@ -39838,7 +39838,7 @@
         <v>1.1507</v>
       </c>
       <c r="I236" t="n">
-        <v>1.868</v>
+        <v>1.8679</v>
       </c>
       <c r="J236" t="n">
         <v>0.5608</v>
@@ -39851,7 +39851,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0389</v>
+        <v>1.0388</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -39872,7 +39872,7 @@
         <v>1.1507</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6362</v>
+        <v>1.6361</v>
       </c>
       <c r="J237" t="n">
         <v>0.5223</v>
@@ -39885,7 +39885,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9923</v>
+        <v>0.9922</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -39906,7 +39906,7 @@
         <v>1.1335</v>
       </c>
       <c r="I238" t="n">
-        <v>1.6227</v>
+        <v>1.6226</v>
       </c>
       <c r="J238" t="n">
         <v>0.5275</v>
@@ -39962,7 +39962,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9791</v>
+        <v>0.979</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40008,7 +40008,7 @@
         <v>1.1206</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8887</v>
+        <v>1.8886</v>
       </c>
       <c r="J241" t="n">
         <v>0.6456</v>
@@ -40030,7 +40030,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9534</v>
+        <v>0.9533</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40042,7 +40042,7 @@
         <v>1.1206</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9633</v>
+        <v>1.9632</v>
       </c>
       <c r="J242" t="n">
         <v>0.6073</v>
@@ -40055,7 +40055,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>1.0008</v>
+        <v>1.0007</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40076,7 +40076,7 @@
         <v>1.1206</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8957</v>
+        <v>1.8956</v>
       </c>
       <c r="J243" t="n">
         <v>0.5889</v>
@@ -40110,7 +40110,7 @@
         <v>1.1837</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8485</v>
+        <v>1.8484</v>
       </c>
       <c r="J244" t="n">
         <v>0.7049</v>
@@ -40166,7 +40166,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.9052</v>
+        <v>0.9051</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40178,7 +40178,7 @@
         <v>1.1837</v>
       </c>
       <c r="I246" t="n">
-        <v>1.8193</v>
+        <v>1.8192</v>
       </c>
       <c r="J246" t="n">
         <v>0.6918</v>
@@ -40212,7 +40212,7 @@
         <v>1.0856</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8504</v>
+        <v>1.8503</v>
       </c>
       <c r="J247" t="n">
         <v>0.6142</v>
@@ -40225,7 +40225,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9558</v>
+        <v>0.9557</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40246,7 +40246,7 @@
         <v>1.0856</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9701</v>
+        <v>1.97</v>
       </c>
       <c r="J248" t="n">
         <v>0.6325</v>
@@ -40280,7 +40280,7 @@
         <v>1.0856</v>
       </c>
       <c r="I249" t="n">
-        <v>2.0403</v>
+        <v>2.0402</v>
       </c>
       <c r="J249" t="n">
         <v>0.6929999999999999</v>
@@ -40314,7 +40314,7 @@
         <v>1.1121</v>
       </c>
       <c r="I250" t="n">
-        <v>2.1094</v>
+        <v>2.1093</v>
       </c>
       <c r="J250" t="n">
         <v>0.6269</v>
@@ -40336,7 +40336,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9375</v>
+        <v>0.9374</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40348,7 +40348,7 @@
         <v>1.1121</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2913</v>
+        <v>2.2912</v>
       </c>
       <c r="J251" t="n">
         <v>0.6411</v>
@@ -40382,7 +40382,7 @@
         <v>1.1121</v>
       </c>
       <c r="I252" t="n">
-        <v>2.4221</v>
+        <v>2.422</v>
       </c>
       <c r="J252" t="n">
         <v>0.6234</v>
@@ -40404,7 +40404,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40416,7 +40416,7 @@
         <v>1.1399</v>
       </c>
       <c r="I253" t="n">
-        <v>2.4479</v>
+        <v>2.4477</v>
       </c>
       <c r="J253" t="n">
         <v>0.6173</v>
@@ -40429,7 +40429,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8943</v>
+        <v>0.8942</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40450,7 +40450,7 @@
         <v>1.1399</v>
       </c>
       <c r="I254" t="n">
-        <v>2.5591</v>
+        <v>2.559</v>
       </c>
       <c r="J254" t="n">
         <v>0.5982</v>
@@ -40484,7 +40484,7 @@
         <v>1.1399</v>
       </c>
       <c r="I255" t="n">
-        <v>2.641</v>
+        <v>2.6409</v>
       </c>
       <c r="J255" t="n">
         <v>0.5657</v>
@@ -40506,7 +40506,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9205</v>
+        <v>0.9204</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40518,7 +40518,7 @@
         <v>1.0108</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6628</v>
+        <v>2.6627</v>
       </c>
       <c r="J256" t="n">
         <v>0.6137</v>
@@ -40552,7 +40552,7 @@
         <v>1.0108</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7953</v>
+        <v>2.7951</v>
       </c>
       <c r="J257" t="n">
         <v>0.4797</v>
@@ -40586,7 +40586,7 @@
         <v>1.0108</v>
       </c>
       <c r="I258" t="n">
-        <v>2.9537</v>
+        <v>2.9535</v>
       </c>
       <c r="J258" t="n">
         <v>0.5727</v>
@@ -40599,19 +40599,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8437</v>
+        <v>0.844</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
-        <v>0.3206</v>
+        <v>0.3201</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9745</v>
+        <v>0.975</v>
       </c>
       <c r="F259" t="n">
-        <v>0.3206</v>
+        <v>0.3201</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8917</v>
@@ -40620,7 +40620,7 @@
         <v>1.0864</v>
       </c>
       <c r="I259" t="n">
-        <v>3.1524</v>
+        <v>3.1547</v>
       </c>
       <c r="J259" t="n">
         <v>0.5507</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>1.04</v>
+        <v>1.039</v>
       </c>
     </row>
     <row r="242">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>0.857</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="256">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.143</v>
+        <v>1.144</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.41</v>
+        <v>1.411</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.939</v>
+        <v>1.94</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.653</v>
+        <v>2.655</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.798</v>
+        <v>3.797</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.837</v>
+        <v>-0.835</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.274</v>
+        <v>-0.273</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.854</v>
+        <v>0.856</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.06</v>
+        <v>-1.07</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67826.909</v>
+        <v>67901.802</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31692,19 +31692,19 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>1.1426</v>
+        <v>1.1442</v>
       </c>
       <c r="D259" t="n">
-        <v>1.4103</v>
+        <v>1.4112</v>
       </c>
       <c r="E259" t="n">
-        <v>1.9392</v>
+        <v>1.9403</v>
       </c>
       <c r="F259" t="n">
-        <v>2.6532</v>
+        <v>2.655</v>
       </c>
       <c r="G259" t="n">
-        <v>3.7978</v>
+        <v>3.7974</v>
       </c>
       <c r="H259" t="n">
         <v>1.9793</v>
@@ -31716,25 +31716,25 @@
         <v>1.7988</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.8367</v>
+        <v>-0.8351</v>
       </c>
       <c r="L259" t="n">
-        <v>-0.2739</v>
+        <v>-0.2729</v>
       </c>
       <c r="M259" t="n">
-        <v>0.8544</v>
+        <v>0.8562</v>
       </c>
       <c r="N259" t="n">
         <v>-0.9792999999999999</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.3669</v>
+        <v>-0.3653</v>
       </c>
       <c r="P259" t="n">
-        <v>0.0771</v>
+        <v>0.0781</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.1437</v>
+        <v>1.1455</v>
       </c>
       <c r="R259" t="n">
         <v>1.1708</v>
@@ -31761,7 +31761,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z259" t="n">
-        <v>67826.9094</v>
+        <v>67901.8017</v>
       </c>
       <c r="AA259" t="n">
         <v>161.498</v>
@@ -31969,13 +31969,13 @@
         <v>-0.0692</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2212</v>
+        <v>0.2213</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7226</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2212</v>
+        <v>0.2213</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4712</v>
@@ -32120,7 +32120,7 @@
         <v>-0.334</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4062</v>
+        <v>-0.4061</v>
       </c>
       <c r="J9" t="n">
         <v>-1.386</v>
@@ -32154,7 +32154,7 @@
         <v>-0.2117</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.38</v>
+        <v>-0.3799</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2409</v>
@@ -33208,7 +33208,7 @@
         <v>-1.0493</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5548</v>
+        <v>-0.5547</v>
       </c>
       <c r="J41" t="n">
         <v>0.3797</v>
@@ -33357,7 +33357,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4905</v>
+        <v>-0.4904</v>
       </c>
       <c r="C46" t="n">
         <v>-0.3034</v>
@@ -33366,7 +33366,7 @@
         <v>0.9776</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.8575</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="F46" t="n">
         <v>0.9776</v>
@@ -33480,7 +33480,7 @@
         <v>-2.2435</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0655</v>
+        <v>-1.0654</v>
       </c>
       <c r="J49" t="n">
         <v>0.9847</v>
@@ -33502,7 +33502,7 @@
         <v>0.132</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.0535</v>
+        <v>-1.0534</v>
       </c>
       <c r="F50" t="n">
         <v>0.132</v>
@@ -33567,13 +33567,13 @@
         <v>0.4357</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0701</v>
+        <v>0.0702</v>
       </c>
       <c r="E52" t="n">
         <v>-1.1885</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0701</v>
+        <v>0.0702</v>
       </c>
       <c r="G52" t="n">
         <v>-1.4913</v>
@@ -33582,7 +33582,7 @@
         <v>-2.7071</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0325</v>
+        <v>-1.0324</v>
       </c>
       <c r="J52" t="n">
         <v>0.4767</v>
@@ -33616,7 +33616,7 @@
         <v>-2.7071</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.0049</v>
+        <v>-1.0048</v>
       </c>
       <c r="J53" t="n">
         <v>0.1941</v>
@@ -33638,7 +33638,7 @@
         <v>-0.3292</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2426</v>
+        <v>-1.2425</v>
       </c>
       <c r="F54" t="n">
         <v>-0.3292</v>
@@ -33650,7 +33650,7 @@
         <v>-2.7071</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0308</v>
+        <v>-1.0307</v>
       </c>
       <c r="J54" t="n">
         <v>0.1116</v>
@@ -33684,7 +33684,7 @@
         <v>-2.9667</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.0043</v>
+        <v>-1.0042</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0176</v>
@@ -33718,7 +33718,7 @@
         <v>-2.9667</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0613</v>
+        <v>-1.0612</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2401</v>
@@ -33854,7 +33854,7 @@
         <v>-2.664</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1326</v>
+        <v>-1.1325</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9772999999999999</v>
@@ -33876,7 +33876,7 @@
         <v>-0.3869</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.397</v>
+        <v>-1.3969</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3869</v>
@@ -33888,7 +33888,7 @@
         <v>-2.4338</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1126</v>
+        <v>-1.1125</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1594</v>
@@ -33922,7 +33922,7 @@
         <v>-2.4338</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0759</v>
+        <v>-1.0758</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3285</v>
@@ -34058,7 +34058,7 @@
         <v>-2.1135</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0855</v>
+        <v>-1.0854</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9565</v>
@@ -34092,7 +34092,7 @@
         <v>-1.7802</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.1074</v>
+        <v>-1.1073</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1247</v>
@@ -34126,7 +34126,7 @@
         <v>-1.7802</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1759</v>
+        <v>-1.1758</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0981</v>
@@ -34160,7 +34160,7 @@
         <v>-1.7802</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2112</v>
+        <v>-1.2111</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0494</v>
@@ -34568,7 +34568,7 @@
         <v>-0.681</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3356</v>
+        <v>-1.3355</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4695</v>
@@ -34636,7 +34636,7 @@
         <v>-0.5931999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3488</v>
+        <v>-1.3487</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3522</v>
@@ -34670,7 +34670,7 @@
         <v>-0.5931999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3355</v>
+        <v>-1.3354</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3144</v>
@@ -34772,7 +34772,7 @@
         <v>-0.569</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3106</v>
+        <v>-1.3105</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1242</v>
@@ -34806,7 +34806,7 @@
         <v>-0.5154</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2281</v>
+        <v>-1.228</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0494</v>
@@ -34840,7 +34840,7 @@
         <v>-0.5154</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.252</v>
+        <v>-1.2519</v>
       </c>
       <c r="J89" t="n">
         <v>-1.083</v>
@@ -34896,7 +34896,7 @@
         <v>0.1763</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6513</v>
+        <v>-0.6512</v>
       </c>
       <c r="F91" t="n">
         <v>0.1763</v>
@@ -35146,7 +35146,7 @@
         <v>-0.1969</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0696</v>
+        <v>-1.0695</v>
       </c>
       <c r="J98" t="n">
         <v>-0.6121</v>
@@ -35542,7 +35542,7 @@
         <v>0.8838</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.0788</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="F110" t="n">
         <v>0.8838</v>
@@ -35644,7 +35644,7 @@
         <v>1.6983</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.037</v>
+        <v>-0.0369</v>
       </c>
       <c r="F113" t="n">
         <v>1.6983</v>
@@ -35826,7 +35826,7 @@
         <v>0.2604</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3354</v>
+        <v>-0.3353</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1561</v>
@@ -35860,7 +35860,7 @@
         <v>0.2604</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3213</v>
+        <v>-0.3212</v>
       </c>
       <c r="J119" t="n">
         <v>-0.07290000000000001</v>
@@ -36117,13 +36117,13 @@
         <v>-0.2094</v>
       </c>
       <c r="D127" t="n">
-        <v>0.379</v>
+        <v>0.3791</v>
       </c>
       <c r="E127" t="n">
         <v>0.3191</v>
       </c>
       <c r="F127" t="n">
-        <v>0.379</v>
+        <v>0.3791</v>
       </c>
       <c r="G127" t="n">
         <v>0.6489</v>
@@ -36200,7 +36200,7 @@
         <v>0.4803</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1576</v>
+        <v>0.1575</v>
       </c>
       <c r="J129" t="n">
         <v>-0.0684</v>
@@ -36553,7 +36553,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.3743</v>
+        <v>0.3744</v>
       </c>
       <c r="C140" t="n">
         <v>0.2033</v>
@@ -36982,7 +36982,7 @@
         <v>0.8181</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0551</v>
+        <v>0.055</v>
       </c>
       <c r="J152" t="n">
         <v>0.7085</v>
@@ -37131,7 +37131,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.6515</v>
+        <v>0.6514</v>
       </c>
       <c r="C157" t="n">
         <v>0.3304</v>
@@ -37174,7 +37174,7 @@
         <v>0.7731</v>
       </c>
       <c r="E158" t="n">
-        <v>0.6506</v>
+        <v>0.6505</v>
       </c>
       <c r="F158" t="n">
         <v>0.7731</v>
@@ -37267,7 +37267,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.6599</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="C161" t="n">
         <v>0.2556</v>
@@ -37322,7 +37322,7 @@
         <v>0.8396</v>
       </c>
       <c r="I162" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0994</v>
       </c>
       <c r="J162" t="n">
         <v>1.108</v>
@@ -37390,7 +37390,7 @@
         <v>0.8361</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1282</v>
+        <v>0.1281</v>
       </c>
       <c r="J164" t="n">
         <v>1.2112</v>
@@ -37526,7 +37526,7 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1165</v>
+        <v>0.1164</v>
       </c>
       <c r="J168" t="n">
         <v>1.4436</v>
@@ -38172,7 +38172,7 @@
         <v>-0.8447</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.177</v>
+        <v>-0.1771</v>
       </c>
       <c r="J187" t="n">
         <v>2.267</v>
@@ -38206,7 +38206,7 @@
         <v>-0.8447</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1579</v>
+        <v>-0.158</v>
       </c>
       <c r="J188" t="n">
         <v>2.0119</v>
@@ -38308,7 +38308,7 @@
         <v>-0.6925</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0706</v>
+        <v>-0.0707</v>
       </c>
       <c r="J191" t="n">
         <v>1.3074</v>
@@ -38342,7 +38342,7 @@
         <v>-0.6925</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0231</v>
+        <v>-0.0232</v>
       </c>
       <c r="J192" t="n">
         <v>1.0417</v>
@@ -38444,7 +38444,7 @@
         <v>-0.4872</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1459</v>
+        <v>0.1458</v>
       </c>
       <c r="J195" t="n">
         <v>0.3586</v>
@@ -38716,7 +38716,7 @@
         <v>0.0994</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4388</v>
+        <v>0.4387</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5009</v>
@@ -38874,7 +38874,7 @@
         <v>0.7245</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3588</v>
+        <v>0.3587</v>
       </c>
       <c r="F208" t="n">
         <v>0.7245</v>
@@ -38920,7 +38920,7 @@
         <v>0.4073</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6586</v>
+        <v>0.6585</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1652</v>
@@ -38954,7 +38954,7 @@
         <v>0.4073</v>
       </c>
       <c r="I210" t="n">
-        <v>0.7063</v>
+        <v>0.7062</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1629</v>
@@ -39146,7 +39146,7 @@
         <v>1.9735</v>
       </c>
       <c r="E216" t="n">
-        <v>0.618</v>
+        <v>0.6179</v>
       </c>
       <c r="F216" t="n">
         <v>1.9735</v>
@@ -39260,7 +39260,7 @@
         <v>0.7063</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8494</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J219" t="n">
         <v>0.2466</v>
@@ -39294,7 +39294,7 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8515</v>
+        <v>0.8514</v>
       </c>
       <c r="J220" t="n">
         <v>0.272</v>
@@ -39362,7 +39362,7 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9742</v>
       </c>
       <c r="J222" t="n">
         <v>0.2526</v>
@@ -39566,7 +39566,7 @@
         <v>0.9577</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3877</v>
+        <v>1.3876</v>
       </c>
       <c r="J228" t="n">
         <v>0.3614</v>
@@ -39690,7 +39690,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0245</v>
+        <v>1.0244</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39736,7 +39736,7 @@
         <v>1.1556</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6988</v>
+        <v>1.6987</v>
       </c>
       <c r="J233" t="n">
         <v>0.4768</v>
@@ -39770,7 +39770,7 @@
         <v>1.1556</v>
       </c>
       <c r="I234" t="n">
-        <v>1.746</v>
+        <v>1.7459</v>
       </c>
       <c r="J234" t="n">
         <v>0.4773</v>
@@ -39860,7 +39860,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9435</v>
+        <v>0.9434</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -39940,7 +39940,7 @@
         <v>1.1335</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7907</v>
+        <v>1.7906</v>
       </c>
       <c r="J239" t="n">
         <v>0.622</v>
@@ -39974,7 +39974,7 @@
         <v>1.1335</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8683</v>
+        <v>1.8682</v>
       </c>
       <c r="J240" t="n">
         <v>0.5928</v>
@@ -40076,7 +40076,7 @@
         <v>1.1206</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8956</v>
+        <v>1.8955</v>
       </c>
       <c r="J243" t="n">
         <v>0.5889</v>
@@ -40110,7 +40110,7 @@
         <v>1.1837</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8484</v>
+        <v>1.8483</v>
       </c>
       <c r="J244" t="n">
         <v>0.7049</v>
@@ -40144,7 +40144,7 @@
         <v>1.1837</v>
       </c>
       <c r="I245" t="n">
-        <v>1.7187</v>
+        <v>1.7186</v>
       </c>
       <c r="J245" t="n">
         <v>0.6133999999999999</v>
@@ -40280,7 +40280,7 @@
         <v>1.0856</v>
       </c>
       <c r="I249" t="n">
-        <v>2.0402</v>
+        <v>2.0401</v>
       </c>
       <c r="J249" t="n">
         <v>0.6929999999999999</v>
@@ -40314,7 +40314,7 @@
         <v>1.1121</v>
       </c>
       <c r="I250" t="n">
-        <v>2.1093</v>
+        <v>2.1092</v>
       </c>
       <c r="J250" t="n">
         <v>0.6269</v>
@@ -40348,7 +40348,7 @@
         <v>1.1121</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2912</v>
+        <v>2.2911</v>
       </c>
       <c r="J251" t="n">
         <v>0.6411</v>
@@ -40361,7 +40361,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>1.0037</v>
+        <v>1.0036</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40370,7 +40370,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.952</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40382,7 +40382,7 @@
         <v>1.1121</v>
       </c>
       <c r="I252" t="n">
-        <v>2.422</v>
+        <v>2.4219</v>
       </c>
       <c r="J252" t="n">
         <v>0.6234</v>
@@ -40438,7 +40438,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9567</v>
+        <v>0.9566</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40450,7 +40450,7 @@
         <v>1.1399</v>
       </c>
       <c r="I254" t="n">
-        <v>2.559</v>
+        <v>2.5589</v>
       </c>
       <c r="J254" t="n">
         <v>0.5982</v>
@@ -40472,7 +40472,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.96</v>
+        <v>0.9599</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40484,7 +40484,7 @@
         <v>1.1399</v>
       </c>
       <c r="I255" t="n">
-        <v>2.6409</v>
+        <v>2.6408</v>
       </c>
       <c r="J255" t="n">
         <v>0.5657</v>
@@ -40518,7 +40518,7 @@
         <v>1.0108</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6627</v>
+        <v>2.6626</v>
       </c>
       <c r="J256" t="n">
         <v>0.6137</v>
@@ -40574,7 +40574,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9361</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40586,7 +40586,7 @@
         <v>1.0108</v>
       </c>
       <c r="I258" t="n">
-        <v>2.9535</v>
+        <v>2.9534</v>
       </c>
       <c r="J258" t="n">
         <v>0.5727</v>
@@ -40599,19 +40599,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.844</v>
+        <v>0.8442</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
-        <v>0.3201</v>
+        <v>0.3195</v>
       </c>
       <c r="E259" t="n">
-        <v>0.975</v>
+        <v>0.9754</v>
       </c>
       <c r="F259" t="n">
-        <v>0.3201</v>
+        <v>0.3195</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8917</v>
@@ -40620,7 +40620,7 @@
         <v>1.0864</v>
       </c>
       <c r="I259" t="n">
-        <v>3.1547</v>
+        <v>3.1561</v>
       </c>
       <c r="J259" t="n">
         <v>0.5507</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-0.608</v>
+        <v>-0.607</v>
       </c>
     </row>
     <row r="4">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>-1.251</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="61">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="223">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
     </row>
   </sheetData>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.144</v>
+        <v>1.146</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.411</v>
+        <v>1.412</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.94</v>
+        <v>1.941</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.655</v>
+        <v>2.656</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.797</v>
+        <v>3.798</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.835</v>
+        <v>-0.834</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.273</v>
+        <v>-0.272</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.856</v>
+        <v>0.857</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67901.802</v>
+        <v>68136.777</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31692,19 +31692,19 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>1.1442</v>
+        <v>1.1457</v>
       </c>
       <c r="D259" t="n">
-        <v>1.4112</v>
+        <v>1.4124</v>
       </c>
       <c r="E259" t="n">
-        <v>1.9403</v>
+        <v>1.9408</v>
       </c>
       <c r="F259" t="n">
-        <v>2.655</v>
+        <v>2.6561</v>
       </c>
       <c r="G259" t="n">
-        <v>3.7974</v>
+        <v>3.7979</v>
       </c>
       <c r="H259" t="n">
         <v>1.9793</v>
@@ -31716,25 +31716,25 @@
         <v>1.7988</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.8351</v>
+        <v>-0.8336</v>
       </c>
       <c r="L259" t="n">
-        <v>-0.2729</v>
+        <v>-0.272</v>
       </c>
       <c r="M259" t="n">
-        <v>0.8562</v>
+        <v>0.8573</v>
       </c>
       <c r="N259" t="n">
         <v>-0.9792999999999999</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.3653</v>
+        <v>-0.3638</v>
       </c>
       <c r="P259" t="n">
-        <v>0.0781</v>
+        <v>0.079</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.1455</v>
+        <v>1.1466</v>
       </c>
       <c r="R259" t="n">
         <v>1.1708</v>
@@ -31761,7 +31761,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z259" t="n">
-        <v>67901.8017</v>
+        <v>68136.77740000001</v>
       </c>
       <c r="AA259" t="n">
         <v>161.498</v>
@@ -31879,7 +31879,7 @@
         <v>0.2573</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8978</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>0.2573</v>
@@ -31888,7 +31888,7 @@
         <v>-0.3402</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6434</v>
+        <v>-0.6433</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7097</v>
@@ -31950,7 +31950,7 @@
         <v>-0.3686</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5649</v>
+        <v>-0.5648</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6405</v>
@@ -31963,7 +31963,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5339</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="C5" t="n">
         <v>-0.0692</v>
@@ -31984,7 +31984,7 @@
         <v>-0.3686</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5435</v>
+        <v>-0.5434</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5072</v>
@@ -32018,7 +32018,7 @@
         <v>-0.3686</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5326</v>
+        <v>-0.5325</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4141</v>
@@ -32052,7 +32052,7 @@
         <v>-0.334</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.485</v>
+        <v>-0.4849</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5044</v>
@@ -32176,7 +32176,7 @@
         <v>0.1045</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.644</v>
+        <v>-0.6439</v>
       </c>
       <c r="F11" t="n">
         <v>0.1045</v>
@@ -32188,7 +32188,7 @@
         <v>-0.2117</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2933</v>
+        <v>-0.2932</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2781</v>
@@ -32290,7 +32290,7 @@
         <v>-0.1746</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2002</v>
+        <v>-0.2001</v>
       </c>
       <c r="J14" t="n">
         <v>-1.1456</v>
@@ -32324,7 +32324,7 @@
         <v>-0.1746</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1377</v>
+        <v>-0.1376</v>
       </c>
       <c r="J15" t="n">
         <v>-1.1222</v>
@@ -32596,7 +32596,7 @@
         <v>0.1042</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0288</v>
+        <v>-0.0287</v>
       </c>
       <c r="J23" t="n">
         <v>-0.7117</v>
@@ -33004,7 +33004,7 @@
         <v>-0.2168</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0767</v>
+        <v>-0.0766</v>
       </c>
       <c r="J35" t="n">
         <v>0.0255</v>
@@ -33072,7 +33072,7 @@
         <v>-0.5995</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2245</v>
+        <v>-0.2244</v>
       </c>
       <c r="J37" t="n">
         <v>0.1612</v>
@@ -33140,7 +33140,7 @@
         <v>-0.5995</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4131</v>
+        <v>-0.413</v>
       </c>
       <c r="J39" t="n">
         <v>0.2421</v>
@@ -33242,7 +33242,7 @@
         <v>-1.0493</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5272</v>
+        <v>-0.5271</v>
       </c>
       <c r="J42" t="n">
         <v>0.4891</v>
@@ -33344,7 +33344,7 @@
         <v>-1.4139</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5568</v>
+        <v>-0.5567</v>
       </c>
       <c r="J45" t="n">
         <v>0.744</v>
@@ -33378,7 +33378,7 @@
         <v>-1.7775</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6512</v>
+        <v>-0.6511</v>
       </c>
       <c r="J46" t="n">
         <v>0.7919</v>
@@ -33412,7 +33412,7 @@
         <v>-1.7775</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-0.8593</v>
       </c>
       <c r="J47" t="n">
         <v>0.7432</v>
@@ -33446,7 +33446,7 @@
         <v>-1.7775</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9428</v>
+        <v>-0.9427</v>
       </c>
       <c r="J48" t="n">
         <v>0.7851</v>
@@ -33459,7 +33459,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8176</v>
+        <v>-0.8175</v>
       </c>
       <c r="C49" t="n">
         <v>-0.1283</v>
@@ -33493,7 +33493,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8164</v>
+        <v>-0.8163</v>
       </c>
       <c r="C50" t="n">
         <v>0.0205</v>
@@ -33514,7 +33514,7 @@
         <v>-2.2435</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1132</v>
+        <v>-1.1131</v>
       </c>
       <c r="J50" t="n">
         <v>0.7669</v>
@@ -33527,7 +33527,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.8358</v>
+        <v>-0.8357</v>
       </c>
       <c r="C51" t="n">
         <v>0.2917</v>
@@ -33548,7 +33548,7 @@
         <v>-2.2435</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1264</v>
+        <v>-1.1263</v>
       </c>
       <c r="J51" t="n">
         <v>0.6102</v>
@@ -33752,7 +33752,7 @@
         <v>-2.9667</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0219</v>
+        <v>-1.0218</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4343</v>
@@ -33786,7 +33786,7 @@
         <v>-2.664</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.1016</v>
+        <v>-1.1015</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5717</v>
@@ -33820,7 +33820,7 @@
         <v>-2.664</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.117</v>
+        <v>-1.1169</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8103</v>
@@ -33910,7 +33910,7 @@
         <v>-0.2593</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.4187</v>
+        <v>-1.4186</v>
       </c>
       <c r="F62" t="n">
         <v>-0.2593</v>
@@ -33944,7 +33944,7 @@
         <v>-0.2126</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.439</v>
+        <v>-1.4389</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2126</v>
@@ -33956,7 +33956,7 @@
         <v>-2.4338</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.1062</v>
+        <v>-1.1061</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4515</v>
@@ -33969,7 +33969,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1633</v>
+        <v>-1.1632</v>
       </c>
       <c r="C64" t="n">
         <v>0.6857</v>
@@ -33990,7 +33990,7 @@
         <v>-2.1135</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0844</v>
+        <v>-1.0843</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6859</v>
@@ -34024,7 +34024,7 @@
         <v>-2.1135</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0425</v>
+        <v>-1.0424</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8083</v>
@@ -34114,7 +34114,7 @@
         <v>-0.2725</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.3933</v>
+        <v>-1.3932</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2725</v>
@@ -34194,7 +34194,7 @@
         <v>-1.4153</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2292</v>
+        <v>-1.2291</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9543</v>
@@ -34228,7 +34228,7 @@
         <v>-1.4153</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2628</v>
+        <v>-1.2627</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9157</v>
@@ -34262,7 +34262,7 @@
         <v>-1.4153</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2495</v>
+        <v>-1.2494</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8851</v>
@@ -34352,7 +34352,7 @@
         <v>-0.1831</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1319</v>
+        <v>-1.1318</v>
       </c>
       <c r="F75" t="n">
         <v>-0.1831</v>
@@ -34377,7 +34377,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8254</v>
+        <v>-0.8253</v>
       </c>
       <c r="C76" t="n">
         <v>0.2978</v>
@@ -34386,7 +34386,7 @@
         <v>-0.0857</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0103</v>
+        <v>-1.0102</v>
       </c>
       <c r="F76" t="n">
         <v>-0.0857</v>
@@ -34398,7 +34398,7 @@
         <v>-0.7467</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2579</v>
+        <v>-1.2578</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6932</v>
@@ -34420,7 +34420,7 @@
         <v>0.0533</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.949</v>
       </c>
       <c r="F77" t="n">
         <v>0.0533</v>
@@ -34432,7 +34432,7 @@
         <v>-0.7467</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2246</v>
+        <v>-1.2245</v>
       </c>
       <c r="J77" t="n">
         <v>-1.5888</v>
@@ -34445,7 +34445,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7524</v>
+        <v>-0.7523</v>
       </c>
       <c r="C78" t="n">
         <v>0.2407</v>
@@ -34500,7 +34500,7 @@
         <v>-0.681</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2871</v>
+        <v>-1.287</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5238</v>
@@ -34522,7 +34522,7 @@
         <v>0.2639</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.9226</v>
+        <v>-0.9225</v>
       </c>
       <c r="F80" t="n">
         <v>0.2639</v>
@@ -34534,7 +34534,7 @@
         <v>-0.681</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2874</v>
+        <v>-1.2873</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5062</v>
@@ -34602,7 +34602,7 @@
         <v>-0.5931999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3521</v>
+        <v>-1.352</v>
       </c>
       <c r="J82" t="n">
         <v>-1.338</v>
@@ -34649,7 +34649,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.6536</v>
       </c>
       <c r="C84" t="n">
         <v>0.1093</v>
@@ -34704,7 +34704,7 @@
         <v>-0.569</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3406</v>
+        <v>-1.3405</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2711</v>
@@ -34738,7 +34738,7 @@
         <v>-0.569</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3634</v>
+        <v>-1.3633</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1157</v>
@@ -34874,7 +34874,7 @@
         <v>-0.5154</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.307</v>
+        <v>-1.3069</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9081</v>
@@ -34908,7 +34908,7 @@
         <v>-0.3809</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.3092</v>
+        <v>-1.3091</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9362</v>
@@ -34942,7 +34942,7 @@
         <v>-0.3809</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3131</v>
+        <v>-1.313</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8218</v>
@@ -34955,7 +34955,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4654</v>
+        <v>-0.4653</v>
       </c>
       <c r="C93" t="n">
         <v>-0.2228</v>
@@ -34976,7 +34976,7 @@
         <v>-0.3809</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3108</v>
+        <v>-1.3107</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8108</v>
@@ -34989,7 +34989,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4033</v>
+        <v>-0.4032</v>
       </c>
       <c r="C94" t="n">
         <v>-0.3182</v>
@@ -35010,7 +35010,7 @@
         <v>-0.2429</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3206</v>
+        <v>-1.3205</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7756999999999999</v>
@@ -35044,7 +35044,7 @@
         <v>-0.2429</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.3075</v>
+        <v>-1.3074</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7816</v>
@@ -35078,7 +35078,7 @@
         <v>-0.2429</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2757</v>
+        <v>-1.2756</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5809</v>
@@ -35100,7 +35100,7 @@
         <v>0.589</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.4432</v>
+        <v>-0.4431</v>
       </c>
       <c r="F97" t="n">
         <v>0.589</v>
@@ -35112,7 +35112,7 @@
         <v>-0.1969</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.21</v>
+        <v>-1.2099</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5599</v>
@@ -35180,7 +35180,7 @@
         <v>-0.1969</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9806</v>
+        <v>-0.9805</v>
       </c>
       <c r="J99" t="n">
         <v>-0.4994</v>
@@ -35214,7 +35214,7 @@
         <v>-0.1572</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9304</v>
+        <v>-0.9303</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4959</v>
@@ -35248,7 +35248,7 @@
         <v>-0.1572</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8421</v>
+        <v>-0.842</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4095</v>
@@ -35372,7 +35372,7 @@
         <v>0.5889</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.1913</v>
+        <v>-0.1912</v>
       </c>
       <c r="F105" t="n">
         <v>0.5889</v>
@@ -35962,7 +35962,7 @@
         <v>0.3415</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0701</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J122" t="n">
         <v>-0.1447</v>
@@ -36015,13 +36015,13 @@
         <v>-0.3003</v>
       </c>
       <c r="D124" t="n">
-        <v>1.2797</v>
+        <v>1.2798</v>
       </c>
       <c r="E124" t="n">
         <v>0.2837</v>
       </c>
       <c r="F124" t="n">
-        <v>1.2797</v>
+        <v>1.2798</v>
       </c>
       <c r="G124" t="n">
         <v>0.6389</v>
@@ -36132,7 +36132,7 @@
         <v>0.4803</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1639</v>
+        <v>0.1638</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0168</v>
@@ -36166,7 +36166,7 @@
         <v>0.4803</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1667</v>
+        <v>0.1666</v>
       </c>
       <c r="J128" t="n">
         <v>-0.0354</v>
@@ -36302,7 +36302,7 @@
         <v>0.5567</v>
       </c>
       <c r="I132" t="n">
-        <v>0.143</v>
+        <v>0.1429</v>
       </c>
       <c r="J132" t="n">
         <v>-0.0172</v>
@@ -36642,7 +36642,7 @@
         <v>0.7886</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2246</v>
+        <v>-0.2245</v>
       </c>
       <c r="J142" t="n">
         <v>0.1775</v>
@@ -36778,7 +36778,7 @@
         <v>0.7784</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0541</v>
+        <v>0.054</v>
       </c>
       <c r="J146" t="n">
         <v>0.4397</v>
@@ -37165,7 +37165,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.6751</v>
+        <v>0.675</v>
       </c>
       <c r="C158" t="n">
         <v>0.3164</v>
@@ -37220,7 +37220,7 @@
         <v>0.8008999999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>0.052</v>
+        <v>0.0519</v>
       </c>
       <c r="J159" t="n">
         <v>0.9173</v>
@@ -37254,7 +37254,7 @@
         <v>0.8396</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0074</v>
+        <v>0.0073</v>
       </c>
       <c r="J160" t="n">
         <v>1.0239</v>
@@ -37310,7 +37310,7 @@
         <v>0.7343</v>
       </c>
       <c r="E162" t="n">
-        <v>0.677</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="F162" t="n">
         <v>0.7343</v>
@@ -37356,7 +37356,7 @@
         <v>0.8361</v>
       </c>
       <c r="I163" t="n">
-        <v>0.102</v>
+        <v>0.1019</v>
       </c>
       <c r="J163" t="n">
         <v>1.2083</v>
@@ -37458,7 +37458,7 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="I166" t="n">
-        <v>0.159</v>
+        <v>0.1589</v>
       </c>
       <c r="J166" t="n">
         <v>1.2732</v>
@@ -37616,7 +37616,7 @@
         <v>0.7526</v>
       </c>
       <c r="E171" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7423</v>
       </c>
       <c r="F171" t="n">
         <v>0.7526</v>
@@ -37696,7 +37696,7 @@
         <v>0.9641</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0014</v>
+        <v>-0.0015</v>
       </c>
       <c r="J173" t="n">
         <v>1.6146</v>
@@ -37718,7 +37718,7 @@
         <v>0.7543</v>
       </c>
       <c r="E174" t="n">
-        <v>0.7941</v>
+        <v>0.794</v>
       </c>
       <c r="F174" t="n">
         <v>0.7543</v>
@@ -37730,7 +37730,7 @@
         <v>0.9641</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0659</v>
+        <v>-0.066</v>
       </c>
       <c r="J174" t="n">
         <v>1.6761</v>
@@ -37764,7 +37764,7 @@
         <v>0.9605</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.112</v>
+        <v>-0.1121</v>
       </c>
       <c r="J175" t="n">
         <v>1.8102</v>
@@ -37798,7 +37798,7 @@
         <v>0.9605</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1203</v>
+        <v>-0.1204</v>
       </c>
       <c r="J176" t="n">
         <v>1.823</v>
@@ -37832,7 +37832,7 @@
         <v>0.9605</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1756</v>
+        <v>-0.1757</v>
       </c>
       <c r="J177" t="n">
         <v>1.8033</v>
@@ -37900,7 +37900,7 @@
         <v>0.4597</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1569</v>
+        <v>-0.157</v>
       </c>
       <c r="J179" t="n">
         <v>1.9398</v>
@@ -37968,7 +37968,7 @@
         <v>0.0944</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1366</v>
+        <v>-0.1367</v>
       </c>
       <c r="J181" t="n">
         <v>1.9519</v>
@@ -38002,7 +38002,7 @@
         <v>0.0944</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1649</v>
+        <v>-0.165</v>
       </c>
       <c r="J182" t="n">
         <v>2.048</v>
@@ -38036,7 +38036,7 @@
         <v>0.0944</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.181</v>
+        <v>-0.1811</v>
       </c>
       <c r="J183" t="n">
         <v>2.1726</v>
@@ -38138,7 +38138,7 @@
         <v>-0.4382</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2466</v>
+        <v>-0.2467</v>
       </c>
       <c r="J186" t="n">
         <v>2.1826</v>
@@ -38262,7 +38262,7 @@
         <v>0.2578</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3163</v>
+        <v>0.3162</v>
       </c>
       <c r="F190" t="n">
         <v>0.2578</v>
@@ -38274,7 +38274,7 @@
         <v>-0.6925</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.112</v>
+        <v>-0.1121</v>
       </c>
       <c r="J190" t="n">
         <v>1.5323</v>
@@ -38398,7 +38398,7 @@
         <v>0.1218</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1906</v>
+        <v>0.1905</v>
       </c>
       <c r="F194" t="n">
         <v>0.1218</v>
@@ -38410,7 +38410,7 @@
         <v>-0.4872</v>
       </c>
       <c r="I194" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0815</v>
       </c>
       <c r="J194" t="n">
         <v>0.5568</v>
@@ -38444,7 +38444,7 @@
         <v>-0.4872</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1458</v>
+        <v>0.1457</v>
       </c>
       <c r="J195" t="n">
         <v>0.3586</v>
@@ -38478,7 +38478,7 @@
         <v>-0.2759</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2184</v>
+        <v>0.2183</v>
       </c>
       <c r="J196" t="n">
         <v>0.0843</v>
@@ -38512,7 +38512,7 @@
         <v>-0.2759</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2634</v>
+        <v>0.2633</v>
       </c>
       <c r="J197" t="n">
         <v>-0.0983</v>
@@ -38546,7 +38546,7 @@
         <v>-0.2759</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2703</v>
+        <v>0.2702</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4217</v>
@@ -38580,7 +38580,7 @@
         <v>-0.1601</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3183</v>
+        <v>0.3182</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6627999999999999</v>
@@ -38614,7 +38614,7 @@
         <v>-0.1601</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3245</v>
+        <v>0.3244</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6143</v>
@@ -38648,7 +38648,7 @@
         <v>-0.1601</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3383</v>
+        <v>0.3382</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5955</v>
@@ -38670,7 +38670,7 @@
         <v>0.4635</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2182</v>
+        <v>0.2181</v>
       </c>
       <c r="F202" t="n">
         <v>0.4635</v>
@@ -38682,7 +38682,7 @@
         <v>0.0994</v>
       </c>
       <c r="I202" t="n">
-        <v>0.427</v>
+        <v>0.4269</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4106</v>
@@ -38750,7 +38750,7 @@
         <v>0.0994</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4739</v>
+        <v>0.4738</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4212</v>
@@ -38784,7 +38784,7 @@
         <v>0.2221</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4793</v>
+        <v>0.4792</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3821</v>
@@ -38818,7 +38818,7 @@
         <v>0.2221</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4694</v>
+        <v>0.4693</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2481</v>
@@ -38831,7 +38831,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3735</v>
+        <v>0.3734</v>
       </c>
       <c r="C207" t="n">
         <v>-0.5511</v>
@@ -38852,7 +38852,7 @@
         <v>0.2221</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4845</v>
+        <v>0.4844</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2872</v>
@@ -38886,7 +38886,7 @@
         <v>0.4073</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5145</v>
+        <v>0.5144</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2458</v>
@@ -39022,7 +39022,7 @@
         <v>0.5412</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8404</v>
+        <v>0.8403</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1226</v>
@@ -39056,7 +39056,7 @@
         <v>0.5412</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8647</v>
+        <v>0.8646</v>
       </c>
       <c r="J213" t="n">
         <v>-0.0765</v>
@@ -39078,7 +39078,7 @@
         <v>1.7312</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6394</v>
+        <v>0.6393</v>
       </c>
       <c r="F214" t="n">
         <v>1.7312</v>
@@ -39112,7 +39112,7 @@
         <v>1.8946</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6534</v>
+        <v>0.6533</v>
       </c>
       <c r="F215" t="n">
         <v>1.8946</v>
@@ -39137,7 +39137,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8891</v>
+        <v>0.889</v>
       </c>
       <c r="C216" t="n">
         <v>-0.9258</v>
@@ -39158,7 +39158,7 @@
         <v>0.6193</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9792</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0144</v>
@@ -39226,7 +39226,7 @@
         <v>0.7063</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7758</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="J218" t="n">
         <v>0.142</v>
@@ -39248,7 +39248,7 @@
         <v>1.6761</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6682</v>
+        <v>0.6681</v>
       </c>
       <c r="F219" t="n">
         <v>1.6761</v>
@@ -39316,7 +39316,7 @@
         <v>1.8104</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7279</v>
+        <v>0.7278</v>
       </c>
       <c r="F221" t="n">
         <v>1.8104</v>
@@ -39328,7 +39328,7 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8718</v>
+        <v>0.8717</v>
       </c>
       <c r="J221" t="n">
         <v>0.3133</v>
@@ -39362,7 +39362,7 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9742</v>
+        <v>0.9741</v>
       </c>
       <c r="J222" t="n">
         <v>0.2526</v>
@@ -39375,7 +39375,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.9974</v>
+        <v>0.9973</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39396,7 +39396,7 @@
         <v>0.8531</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1036</v>
+        <v>1.1035</v>
       </c>
       <c r="J223" t="n">
         <v>0.3699</v>
@@ -39418,7 +39418,7 @@
         <v>1.6966</v>
       </c>
       <c r="E224" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8119</v>
       </c>
       <c r="F224" t="n">
         <v>1.6966</v>
@@ -39430,7 +39430,7 @@
         <v>0.8531</v>
       </c>
       <c r="I224" t="n">
-        <v>1.1227</v>
+        <v>1.1226</v>
       </c>
       <c r="J224" t="n">
         <v>0.3796</v>
@@ -39452,7 +39452,7 @@
         <v>1.6703</v>
       </c>
       <c r="E225" t="n">
-        <v>0.838</v>
+        <v>0.8379</v>
       </c>
       <c r="F225" t="n">
         <v>1.6703</v>
@@ -39464,7 +39464,7 @@
         <v>0.8531</v>
       </c>
       <c r="I225" t="n">
-        <v>1.2125</v>
+        <v>1.2124</v>
       </c>
       <c r="J225" t="n">
         <v>0.3975</v>
@@ -39498,7 +39498,7 @@
         <v>0.9577</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2831</v>
+        <v>1.283</v>
       </c>
       <c r="J226" t="n">
         <v>0.3603</v>
@@ -39532,7 +39532,7 @@
         <v>0.9577</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3129</v>
+        <v>1.3128</v>
       </c>
       <c r="J227" t="n">
         <v>0.3583</v>
@@ -39566,7 +39566,7 @@
         <v>0.9577</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3876</v>
+        <v>1.3875</v>
       </c>
       <c r="J228" t="n">
         <v>0.3614</v>
@@ -39600,7 +39600,7 @@
         <v>1.0556</v>
       </c>
       <c r="I229" t="n">
-        <v>1.3152</v>
+        <v>1.315</v>
       </c>
       <c r="J229" t="n">
         <v>0.3868</v>
@@ -39622,7 +39622,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9544</v>
+        <v>0.9543</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39634,7 +39634,7 @@
         <v>1.0556</v>
       </c>
       <c r="I230" t="n">
-        <v>1.4217</v>
+        <v>1.4215</v>
       </c>
       <c r="J230" t="n">
         <v>0.4868</v>
@@ -39656,7 +39656,7 @@
         <v>1.4899</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9701</v>
+        <v>0.97</v>
       </c>
       <c r="F231" t="n">
         <v>1.4899</v>
@@ -39668,7 +39668,7 @@
         <v>1.0556</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5678</v>
+        <v>1.5676</v>
       </c>
       <c r="J231" t="n">
         <v>0.4234</v>
@@ -39702,7 +39702,7 @@
         <v>1.1556</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6358</v>
+        <v>1.6356</v>
       </c>
       <c r="J232" t="n">
         <v>0.4843</v>
@@ -39724,7 +39724,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0235</v>
+        <v>1.0234</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39736,7 +39736,7 @@
         <v>1.1556</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6987</v>
+        <v>1.6986</v>
       </c>
       <c r="J233" t="n">
         <v>0.4768</v>
@@ -39770,7 +39770,7 @@
         <v>1.1556</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7459</v>
+        <v>1.7458</v>
       </c>
       <c r="J234" t="n">
         <v>0.4773</v>
@@ -39792,7 +39792,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0469</v>
+        <v>1.0468</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -39804,7 +39804,7 @@
         <v>1.1507</v>
       </c>
       <c r="I235" t="n">
-        <v>1.8305</v>
+        <v>1.8303</v>
       </c>
       <c r="J235" t="n">
         <v>0.5446</v>
@@ -39817,7 +39817,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.1017</v>
+        <v>1.1016</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -39826,7 +39826,7 @@
         <v>1.3709</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0344</v>
+        <v>1.0343</v>
       </c>
       <c r="F236" t="n">
         <v>1.3709</v>
@@ -39838,7 +39838,7 @@
         <v>1.1507</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8679</v>
+        <v>1.8677</v>
       </c>
       <c r="J236" t="n">
         <v>0.5608</v>
@@ -39872,7 +39872,7 @@
         <v>1.1507</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6361</v>
+        <v>1.6359</v>
       </c>
       <c r="J237" t="n">
         <v>0.5223</v>
@@ -39906,7 +39906,7 @@
         <v>1.1335</v>
       </c>
       <c r="I238" t="n">
-        <v>1.6226</v>
+        <v>1.6224</v>
       </c>
       <c r="J238" t="n">
         <v>0.5275</v>
@@ -39940,7 +39940,7 @@
         <v>1.1335</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7906</v>
+        <v>1.7905</v>
       </c>
       <c r="J239" t="n">
         <v>0.622</v>
@@ -39974,7 +39974,7 @@
         <v>1.1335</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8682</v>
+        <v>1.8681</v>
       </c>
       <c r="J240" t="n">
         <v>0.5928</v>
@@ -39996,7 +39996,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9762</v>
+        <v>0.9761</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40008,7 +40008,7 @@
         <v>1.1206</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8886</v>
+        <v>1.8884</v>
       </c>
       <c r="J241" t="n">
         <v>0.6456</v>
@@ -40042,7 +40042,7 @@
         <v>1.1206</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9632</v>
+        <v>1.963</v>
       </c>
       <c r="J242" t="n">
         <v>0.6073</v>
@@ -40064,7 +40064,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9245</v>
+        <v>0.9244</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40076,7 +40076,7 @@
         <v>1.1206</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8955</v>
+        <v>1.8954</v>
       </c>
       <c r="J243" t="n">
         <v>0.5889</v>
@@ -40089,7 +40089,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.0383</v>
+        <v>1.0382</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40110,7 +40110,7 @@
         <v>1.1837</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8483</v>
+        <v>1.8482</v>
       </c>
       <c r="J244" t="n">
         <v>0.7049</v>
@@ -40123,7 +40123,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.0138</v>
+        <v>1.0137</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40132,7 +40132,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8732</v>
+        <v>0.8731</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40144,7 +40144,7 @@
         <v>1.1837</v>
       </c>
       <c r="I245" t="n">
-        <v>1.7186</v>
+        <v>1.7185</v>
       </c>
       <c r="J245" t="n">
         <v>0.6133999999999999</v>
@@ -40157,7 +40157,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0401</v>
+        <v>1.04</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40178,7 +40178,7 @@
         <v>1.1837</v>
       </c>
       <c r="I246" t="n">
-        <v>1.8192</v>
+        <v>1.819</v>
       </c>
       <c r="J246" t="n">
         <v>0.6918</v>
@@ -40191,7 +40191,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9843</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40212,7 +40212,7 @@
         <v>1.0856</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8503</v>
+        <v>1.8501</v>
       </c>
       <c r="J247" t="n">
         <v>0.6142</v>
@@ -40234,7 +40234,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8697</v>
+        <v>0.8696</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40246,7 +40246,7 @@
         <v>1.0856</v>
       </c>
       <c r="I248" t="n">
-        <v>1.97</v>
+        <v>1.9698</v>
       </c>
       <c r="J248" t="n">
         <v>0.6325</v>
@@ -40268,7 +40268,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8988</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40280,7 +40280,7 @@
         <v>1.0856</v>
       </c>
       <c r="I249" t="n">
-        <v>2.0401</v>
+        <v>2.0399</v>
       </c>
       <c r="J249" t="n">
         <v>0.6929999999999999</v>
@@ -40314,7 +40314,7 @@
         <v>1.1121</v>
       </c>
       <c r="I250" t="n">
-        <v>2.1092</v>
+        <v>2.109</v>
       </c>
       <c r="J250" t="n">
         <v>0.6269</v>
@@ -40348,7 +40348,7 @@
         <v>1.1121</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2911</v>
+        <v>2.2909</v>
       </c>
       <c r="J251" t="n">
         <v>0.6411</v>
@@ -40367,13 +40367,13 @@
         <v>-1.116</v>
       </c>
       <c r="D252" t="n">
-        <v>1.21</v>
+        <v>1.2101</v>
       </c>
       <c r="E252" t="n">
         <v>0.952</v>
       </c>
       <c r="F252" t="n">
-        <v>1.21</v>
+        <v>1.2101</v>
       </c>
       <c r="G252" t="n">
         <v>-0.3493</v>
@@ -40382,7 +40382,7 @@
         <v>1.1121</v>
       </c>
       <c r="I252" t="n">
-        <v>2.4219</v>
+        <v>2.4217</v>
       </c>
       <c r="J252" t="n">
         <v>0.6234</v>
@@ -40395,7 +40395,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7644</v>
+        <v>0.7643</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40416,7 +40416,7 @@
         <v>1.1399</v>
       </c>
       <c r="I253" t="n">
-        <v>2.4477</v>
+        <v>2.4474</v>
       </c>
       <c r="J253" t="n">
         <v>0.6173</v>
@@ -40450,7 +40450,7 @@
         <v>1.1399</v>
       </c>
       <c r="I254" t="n">
-        <v>2.5589</v>
+        <v>2.5586</v>
       </c>
       <c r="J254" t="n">
         <v>0.5982</v>
@@ -40463,7 +40463,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8565</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40484,7 +40484,7 @@
         <v>1.1399</v>
       </c>
       <c r="I255" t="n">
-        <v>2.6408</v>
+        <v>2.6405</v>
       </c>
       <c r="J255" t="n">
         <v>0.5657</v>
@@ -40497,7 +40497,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8343</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40506,7 +40506,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9204</v>
+        <v>0.9203</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40518,7 +40518,7 @@
         <v>1.0108</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6626</v>
+        <v>2.6623</v>
       </c>
       <c r="J256" t="n">
         <v>0.6137</v>
@@ -40531,7 +40531,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7645</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40540,7 +40540,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8753</v>
+        <v>0.8752</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40552,7 +40552,7 @@
         <v>1.0108</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7951</v>
+        <v>2.7948</v>
       </c>
       <c r="J257" t="n">
         <v>0.4797</v>
@@ -40565,7 +40565,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.8075</v>
+        <v>0.8074</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40586,7 +40586,7 @@
         <v>1.0108</v>
       </c>
       <c r="I258" t="n">
-        <v>2.9534</v>
+        <v>2.9531</v>
       </c>
       <c r="J258" t="n">
         <v>0.5727</v>
@@ -40599,19 +40599,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8442</v>
+        <v>0.845</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
-        <v>0.3195</v>
+        <v>0.319</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9754</v>
+        <v>0.9765</v>
       </c>
       <c r="F259" t="n">
-        <v>0.3195</v>
+        <v>0.319</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8917</v>
@@ -40620,7 +40620,7 @@
         <v>1.0864</v>
       </c>
       <c r="I259" t="n">
-        <v>3.1561</v>
+        <v>3.1605</v>
       </c>
       <c r="J259" t="n">
         <v>0.5507</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.84</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.84 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.85 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.146</v>
+        <v>1.147</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.412</v>
+        <v>1.413</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.941</v>
+        <v>1.94</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.656</v>
+        <v>2.655</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.798</v>
+        <v>3.797</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.834</v>
+        <v>-0.832</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.857</v>
+        <v>0.856</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68136.777</v>
+        <v>68197.982</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.37</v>
+        <v>4.38</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31692,19 +31692,19 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>1.1457</v>
+        <v>1.1473</v>
       </c>
       <c r="D259" t="n">
-        <v>1.4124</v>
+        <v>1.4128</v>
       </c>
       <c r="E259" t="n">
-        <v>1.9408</v>
+        <v>1.9399</v>
       </c>
       <c r="F259" t="n">
-        <v>2.6561</v>
+        <v>2.6551</v>
       </c>
       <c r="G259" t="n">
-        <v>3.7979</v>
+        <v>3.7971</v>
       </c>
       <c r="H259" t="n">
         <v>1.9793</v>
@@ -31716,25 +31716,25 @@
         <v>1.7988</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.8336</v>
+        <v>-0.832</v>
       </c>
       <c r="L259" t="n">
         <v>-0.272</v>
       </c>
       <c r="M259" t="n">
-        <v>0.8573</v>
+        <v>0.8563</v>
       </c>
       <c r="N259" t="n">
         <v>-0.9792999999999999</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.3638</v>
+        <v>-0.3622</v>
       </c>
       <c r="P259" t="n">
         <v>0.079</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.1466</v>
+        <v>1.1456</v>
       </c>
       <c r="R259" t="n">
         <v>1.1708</v>
@@ -31761,7 +31761,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z259" t="n">
-        <v>68136.77740000001</v>
+        <v>68197.9825</v>
       </c>
       <c r="AA259" t="n">
         <v>161.498</v>
@@ -31916,7 +31916,7 @@
         <v>-0.3175</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5888</v>
+        <v>-0.5887</v>
       </c>
       <c r="J3" t="n">
         <v>-1.6316</v>
@@ -32031,7 +32031,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.5407</v>
+        <v>-0.5406</v>
       </c>
       <c r="C7" t="n">
         <v>-0.1131</v>
@@ -32448,7 +32448,7 @@
         <v>0.0366</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5597</v>
+        <v>-0.5596</v>
       </c>
       <c r="F19" t="n">
         <v>0.0366</v>
@@ -32494,7 +32494,7 @@
         <v>-0.1078</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1262</v>
+        <v>-0.1261</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8205</v>
@@ -33310,7 +33310,7 @@
         <v>-1.4139</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5607</v>
+        <v>-0.5606</v>
       </c>
       <c r="J44" t="n">
         <v>0.5851</v>
@@ -33400,7 +33400,7 @@
         <v>0.7934</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.9194</v>
+        <v>-0.9193</v>
       </c>
       <c r="F47" t="n">
         <v>0.7934</v>
@@ -33480,7 +33480,7 @@
         <v>-2.2435</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0654</v>
+        <v>-1.0653</v>
       </c>
       <c r="J49" t="n">
         <v>0.9847</v>
@@ -33582,7 +33582,7 @@
         <v>-2.7071</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0324</v>
+        <v>-1.0323</v>
       </c>
       <c r="J52" t="n">
         <v>0.4767</v>
@@ -33799,7 +33799,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.2852</v>
+        <v>-1.2851</v>
       </c>
       <c r="C59" t="n">
         <v>0.9619</v>
@@ -34126,7 +34126,7 @@
         <v>-1.7802</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1758</v>
+        <v>-1.1757</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0981</v>
@@ -34296,7 +34296,7 @@
         <v>-1.1721</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2102</v>
+        <v>-1.2101</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8474</v>
@@ -34330,7 +34330,7 @@
         <v>-1.1721</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2365</v>
+        <v>-1.2364</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8237</v>
@@ -34466,7 +34466,7 @@
         <v>-0.7467</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2644</v>
+        <v>-1.2643</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6214</v>
@@ -34568,7 +34568,7 @@
         <v>-0.681</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3355</v>
+        <v>-1.3354</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4695</v>
@@ -34636,7 +34636,7 @@
         <v>-0.5931999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3487</v>
+        <v>-1.3486</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3522</v>
@@ -34670,7 +34670,7 @@
         <v>-0.5931999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3354</v>
+        <v>-1.3353</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3144</v>
@@ -35350,7 +35350,7 @@
         <v>-0.0924</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7267</v>
+        <v>-0.7266</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2289</v>
@@ -35588,7 +35588,7 @@
         <v>0.1515</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5635</v>
+        <v>-0.5634</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2337</v>
@@ -35669,7 +35669,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.334</v>
+        <v>0.3341</v>
       </c>
       <c r="C114" t="n">
         <v>-0.6998</v>
@@ -35758,7 +35758,7 @@
         <v>0.2018</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4718</v>
+        <v>-0.4717</v>
       </c>
       <c r="J116" t="n">
         <v>-0.1305</v>
@@ -36111,7 +36111,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3311</v>
+        <v>0.331</v>
       </c>
       <c r="C127" t="n">
         <v>-0.2094</v>
@@ -36120,7 +36120,7 @@
         <v>0.3791</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3191</v>
+        <v>0.319</v>
       </c>
       <c r="F127" t="n">
         <v>0.3791</v>
@@ -36664,7 +36664,7 @@
         <v>0.354</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4248</v>
+        <v>0.4249</v>
       </c>
       <c r="F143" t="n">
         <v>0.354</v>
@@ -37103,13 +37103,13 @@
         <v>0.2997</v>
       </c>
       <c r="D156" t="n">
-        <v>0.8369</v>
+        <v>0.837</v>
       </c>
       <c r="E156" t="n">
         <v>0.5889</v>
       </c>
       <c r="F156" t="n">
-        <v>0.8369</v>
+        <v>0.837</v>
       </c>
       <c r="G156" t="n">
         <v>0.6449</v>
@@ -37152,7 +37152,7 @@
         <v>0.8008999999999999</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1392</v>
+        <v>0.1391</v>
       </c>
       <c r="J157" t="n">
         <v>0.8122</v>
@@ -37514,7 +37514,7 @@
         <v>0.8165</v>
       </c>
       <c r="E168" t="n">
-        <v>0.7748</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="F168" t="n">
         <v>0.8165</v>
@@ -38376,7 +38376,7 @@
         <v>-0.4872</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0154</v>
+        <v>0.0153</v>
       </c>
       <c r="J193" t="n">
         <v>0.8569</v>
@@ -38593,7 +38593,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.1192</v>
+        <v>0.1191</v>
       </c>
       <c r="C200" t="n">
         <v>-0.1771</v>
@@ -38716,7 +38716,7 @@
         <v>0.0994</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4387</v>
+        <v>0.4386</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5009</v>
@@ -38988,7 +38988,7 @@
         <v>0.5412</v>
       </c>
       <c r="I211" t="n">
-        <v>0.8031</v>
+        <v>0.803</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1077</v>
@@ -39035,7 +39035,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.7482</v>
+        <v>0.7481</v>
       </c>
       <c r="C213" t="n">
         <v>-0.7202</v>
@@ -39090,7 +39090,7 @@
         <v>0.6193</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9685</v>
+        <v>0.9684</v>
       </c>
       <c r="J214" t="n">
         <v>0.0835</v>
@@ -39124,7 +39124,7 @@
         <v>0.6193</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0394</v>
+        <v>1.0393</v>
       </c>
       <c r="J215" t="n">
         <v>0.033</v>
@@ -39192,7 +39192,7 @@
         <v>0.7063</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8472</v>
       </c>
       <c r="J217" t="n">
         <v>0.1713</v>
@@ -39294,7 +39294,7 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8514</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="J220" t="n">
         <v>0.272</v>
@@ -39307,7 +39307,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.9444</v>
+        <v>0.9443</v>
       </c>
       <c r="C221" t="n">
         <v>-1.2861</v>
@@ -39396,7 +39396,7 @@
         <v>0.8531</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1035</v>
+        <v>1.1034</v>
       </c>
       <c r="J223" t="n">
         <v>0.3699</v>
@@ -39430,7 +39430,7 @@
         <v>0.8531</v>
       </c>
       <c r="I224" t="n">
-        <v>1.1226</v>
+        <v>1.1225</v>
       </c>
       <c r="J224" t="n">
         <v>0.3796</v>
@@ -39736,7 +39736,7 @@
         <v>1.1556</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6986</v>
+        <v>1.6985</v>
       </c>
       <c r="J233" t="n">
         <v>0.4768</v>
@@ -39838,7 +39838,7 @@
         <v>1.1507</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8677</v>
+        <v>1.8676</v>
       </c>
       <c r="J236" t="n">
         <v>0.5608</v>
@@ -39894,7 +39894,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9367</v>
+        <v>0.9366</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -39940,7 +39940,7 @@
         <v>1.1335</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7905</v>
+        <v>1.7904</v>
       </c>
       <c r="J239" t="n">
         <v>0.622</v>
@@ -39974,7 +39974,7 @@
         <v>1.1335</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8681</v>
+        <v>1.868</v>
       </c>
       <c r="J240" t="n">
         <v>0.5928</v>
@@ -40098,7 +40098,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9597</v>
+        <v>0.9596</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40302,7 +40302,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8891</v>
+        <v>0.889</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40327,7 +40327,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9971</v>
+        <v>0.997</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40348,7 +40348,7 @@
         <v>1.1121</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2909</v>
+        <v>2.2908</v>
       </c>
       <c r="J251" t="n">
         <v>0.6411</v>
@@ -40382,7 +40382,7 @@
         <v>1.1121</v>
       </c>
       <c r="I252" t="n">
-        <v>2.4217</v>
+        <v>2.4216</v>
       </c>
       <c r="J252" t="n">
         <v>0.6234</v>
@@ -40429,7 +40429,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8942</v>
+        <v>0.8941</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40450,7 +40450,7 @@
         <v>1.1399</v>
       </c>
       <c r="I254" t="n">
-        <v>2.5586</v>
+        <v>2.5585</v>
       </c>
       <c r="J254" t="n">
         <v>0.5982</v>
@@ -40484,7 +40484,7 @@
         <v>1.1399</v>
       </c>
       <c r="I255" t="n">
-        <v>2.6405</v>
+        <v>2.6404</v>
       </c>
       <c r="J255" t="n">
         <v>0.5657</v>
@@ -40518,7 +40518,7 @@
         <v>1.0108</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6623</v>
+        <v>2.6622</v>
       </c>
       <c r="J256" t="n">
         <v>0.6137</v>
@@ -40552,7 +40552,7 @@
         <v>1.0108</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7948</v>
+        <v>2.7947</v>
       </c>
       <c r="J257" t="n">
         <v>0.4797</v>
@@ -40574,7 +40574,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9359</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40586,7 +40586,7 @@
         <v>1.0108</v>
       </c>
       <c r="I258" t="n">
-        <v>2.9531</v>
+        <v>2.953</v>
       </c>
       <c r="J258" t="n">
         <v>0.5727</v>
@@ -40599,19 +40599,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.845</v>
+        <v>0.8452</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
-        <v>0.319</v>
+        <v>0.3188</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9765</v>
+        <v>0.9768</v>
       </c>
       <c r="F259" t="n">
-        <v>0.319</v>
+        <v>0.3188</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8917</v>
@@ -40620,7 +40620,7 @@
         <v>1.0864</v>
       </c>
       <c r="I259" t="n">
-        <v>3.1605</v>
+        <v>3.1617</v>
       </c>
       <c r="J259" t="n">
         <v>0.5507</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="258">
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.147</v>
+        <v>1.149</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.94</v>
+        <v>1.939</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.655</v>
+        <v>2.653</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.797</v>
+        <v>3.795</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.832</v>
+        <v>-0.831</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.272</v>
+        <v>-0.273</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.856</v>
+        <v>0.854</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.07</v>
+        <v>-1.06</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68197.982</v>
+        <v>68258.465</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31692,19 +31692,19 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>1.1473</v>
+        <v>1.1486</v>
       </c>
       <c r="D259" t="n">
-        <v>1.4128</v>
+        <v>1.4126</v>
       </c>
       <c r="E259" t="n">
-        <v>1.9399</v>
+        <v>1.9387</v>
       </c>
       <c r="F259" t="n">
-        <v>2.6551</v>
+        <v>2.6528</v>
       </c>
       <c r="G259" t="n">
-        <v>3.7971</v>
+        <v>3.7952</v>
       </c>
       <c r="H259" t="n">
         <v>1.9793</v>
@@ -31716,25 +31716,25 @@
         <v>1.7988</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.832</v>
+        <v>-0.8307</v>
       </c>
       <c r="L259" t="n">
-        <v>-0.272</v>
+        <v>-0.2725</v>
       </c>
       <c r="M259" t="n">
-        <v>0.8563</v>
+        <v>0.854</v>
       </c>
       <c r="N259" t="n">
         <v>-0.9792999999999999</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.3622</v>
+        <v>-0.3609</v>
       </c>
       <c r="P259" t="n">
-        <v>0.079</v>
+        <v>0.0785</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.1456</v>
+        <v>1.1433</v>
       </c>
       <c r="R259" t="n">
         <v>1.1708</v>
@@ -31761,7 +31761,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z259" t="n">
-        <v>68197.9825</v>
+        <v>68258.4648</v>
       </c>
       <c r="AA259" t="n">
         <v>161.498</v>
@@ -32086,7 +32086,7 @@
         <v>-0.334</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4033</v>
+        <v>-0.4032</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3545</v>
@@ -33276,7 +33276,7 @@
         <v>-1.4139</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5193</v>
+        <v>-0.5192</v>
       </c>
       <c r="J43" t="n">
         <v>0.5463</v>
@@ -33616,7 +33616,7 @@
         <v>-2.7071</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.0048</v>
+        <v>-1.0047</v>
       </c>
       <c r="J53" t="n">
         <v>0.1941</v>
@@ -33650,7 +33650,7 @@
         <v>-2.7071</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0307</v>
+        <v>-1.0306</v>
       </c>
       <c r="J54" t="n">
         <v>0.1116</v>
@@ -33684,7 +33684,7 @@
         <v>-2.9667</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.0042</v>
+        <v>-1.0041</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0176</v>
@@ -33718,7 +33718,7 @@
         <v>-2.9667</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0612</v>
+        <v>-1.0611</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2401</v>
@@ -34046,7 +34046,7 @@
         <v>-0.2077</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.4319</v>
+        <v>-1.4318</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2077</v>
@@ -34092,7 +34092,7 @@
         <v>-1.7802</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.1073</v>
+        <v>-1.1072</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1247</v>
@@ -34160,7 +34160,7 @@
         <v>-1.7802</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2111</v>
+        <v>-1.211</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0494</v>
@@ -34364,7 +34364,7 @@
         <v>-1.1721</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2263</v>
+        <v>-1.2262</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8019</v>
@@ -34581,7 +34581,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.6266</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="C82" t="n">
         <v>0.2131</v>
@@ -34772,7 +34772,7 @@
         <v>-0.569</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3105</v>
+        <v>-1.3104</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1242</v>
@@ -34806,7 +34806,7 @@
         <v>-0.5154</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.228</v>
+        <v>-1.2279</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0494</v>
@@ -34840,7 +34840,7 @@
         <v>-0.5154</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2519</v>
+        <v>-1.2518</v>
       </c>
       <c r="J89" t="n">
         <v>-1.083</v>
@@ -35193,7 +35193,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2534</v>
+        <v>-0.2533</v>
       </c>
       <c r="C100" t="n">
         <v>-0.3899</v>
@@ -35418,7 +35418,7 @@
         <v>-0.0349</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.7151</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3586</v>
@@ -35656,7 +35656,7 @@
         <v>0.1783</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5427</v>
+        <v>-0.5426</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2307</v>
@@ -37628,7 +37628,7 @@
         <v>0.879</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J171" t="n">
         <v>1.5074</v>
@@ -38240,7 +38240,7 @@
         <v>-0.8447</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1207</v>
+        <v>-0.1208</v>
       </c>
       <c r="J189" t="n">
         <v>1.7733</v>
@@ -38580,7 +38580,7 @@
         <v>-0.1601</v>
       </c>
       <c r="I199" t="n">
-        <v>0.3182</v>
+        <v>0.3181</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6627999999999999</v>
@@ -38682,7 +38682,7 @@
         <v>0.0994</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4269</v>
+        <v>0.4268</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4106</v>
@@ -38920,7 +38920,7 @@
         <v>0.4073</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6585</v>
+        <v>0.6584</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1652</v>
@@ -38933,7 +38933,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.6091</v>
+        <v>0.609</v>
       </c>
       <c r="C210" t="n">
         <v>-0.6456</v>
@@ -38954,7 +38954,7 @@
         <v>0.4073</v>
       </c>
       <c r="I210" t="n">
-        <v>0.7062</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1629</v>
@@ -38967,7 +38967,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.6862</v>
+        <v>0.6861</v>
       </c>
       <c r="C211" t="n">
         <v>-0.7048</v>
@@ -39056,7 +39056,7 @@
         <v>0.5412</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8646</v>
+        <v>0.8645</v>
       </c>
       <c r="J213" t="n">
         <v>-0.0765</v>
@@ -39260,7 +39260,7 @@
         <v>0.7063</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8492</v>
       </c>
       <c r="J219" t="n">
         <v>0.2466</v>
@@ -39477,7 +39477,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9912</v>
+        <v>0.9911</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
@@ -39498,7 +39498,7 @@
         <v>0.9577</v>
       </c>
       <c r="I226" t="n">
-        <v>1.283</v>
+        <v>1.2829</v>
       </c>
       <c r="J226" t="n">
         <v>0.3603</v>
@@ -39702,7 +39702,7 @@
         <v>1.1556</v>
       </c>
       <c r="I232" t="n">
-        <v>1.6356</v>
+        <v>1.6355</v>
       </c>
       <c r="J232" t="n">
         <v>0.4843</v>
@@ -39749,7 +39749,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.0777</v>
+        <v>1.0776</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -39758,7 +39758,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.0227</v>
+        <v>1.0226</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -39770,7 +39770,7 @@
         <v>1.1556</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7458</v>
+        <v>1.7457</v>
       </c>
       <c r="J234" t="n">
         <v>0.4773</v>
@@ -39783,7 +39783,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.1048</v>
+        <v>1.1047</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -39872,7 +39872,7 @@
         <v>1.1507</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6359</v>
+        <v>1.6358</v>
       </c>
       <c r="J237" t="n">
         <v>0.5223</v>
@@ -39987,7 +39987,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0395</v>
+        <v>1.0394</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40008,7 +40008,7 @@
         <v>1.1206</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8884</v>
+        <v>1.8883</v>
       </c>
       <c r="J241" t="n">
         <v>0.6456</v>
@@ -40042,7 +40042,7 @@
         <v>1.1206</v>
       </c>
       <c r="I242" t="n">
-        <v>1.963</v>
+        <v>1.9629</v>
       </c>
       <c r="J242" t="n">
         <v>0.6073</v>
@@ -40076,7 +40076,7 @@
         <v>1.1206</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8954</v>
+        <v>1.8953</v>
       </c>
       <c r="J243" t="n">
         <v>0.5889</v>
@@ -40110,7 +40110,7 @@
         <v>1.1837</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8482</v>
+        <v>1.8481</v>
       </c>
       <c r="J244" t="n">
         <v>0.7049</v>
@@ -40178,7 +40178,7 @@
         <v>1.1837</v>
       </c>
       <c r="I246" t="n">
-        <v>1.819</v>
+        <v>1.8189</v>
       </c>
       <c r="J246" t="n">
         <v>0.6918</v>
@@ -40246,7 +40246,7 @@
         <v>1.0856</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9698</v>
+        <v>1.9697</v>
       </c>
       <c r="J248" t="n">
         <v>0.6325</v>
@@ -40259,7 +40259,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9423</v>
+        <v>0.9422</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40280,7 +40280,7 @@
         <v>1.0856</v>
       </c>
       <c r="I249" t="n">
-        <v>2.0399</v>
+        <v>2.0398</v>
       </c>
       <c r="J249" t="n">
         <v>0.6929999999999999</v>
@@ -40293,7 +40293,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9544</v>
+        <v>0.9543</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40314,7 +40314,7 @@
         <v>1.1121</v>
       </c>
       <c r="I250" t="n">
-        <v>2.109</v>
+        <v>2.1089</v>
       </c>
       <c r="J250" t="n">
         <v>0.6269</v>
@@ -40336,7 +40336,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9374</v>
+        <v>0.9373</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40404,7 +40404,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.947</v>
+        <v>0.9469</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40416,7 +40416,7 @@
         <v>1.1399</v>
       </c>
       <c r="I253" t="n">
-        <v>2.4474</v>
+        <v>2.4473</v>
       </c>
       <c r="J253" t="n">
         <v>0.6173</v>
@@ -40438,7 +40438,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9566</v>
+        <v>0.9565</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40472,7 +40472,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9599</v>
+        <v>0.9598</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40552,7 +40552,7 @@
         <v>1.0108</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7947</v>
+        <v>2.7946</v>
       </c>
       <c r="J257" t="n">
         <v>0.4797</v>
@@ -40586,7 +40586,7 @@
         <v>1.0108</v>
       </c>
       <c r="I258" t="n">
-        <v>2.953</v>
+        <v>2.9529</v>
       </c>
       <c r="J258" t="n">
         <v>0.5727</v>
@@ -40599,19 +40599,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8452</v>
+        <v>0.8454</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
-        <v>0.3188</v>
+        <v>0.3189</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9768</v>
+        <v>0.9771</v>
       </c>
       <c r="F259" t="n">
-        <v>0.3188</v>
+        <v>0.3189</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8917</v>
@@ -40620,7 +40620,7 @@
         <v>1.0864</v>
       </c>
       <c r="I259" t="n">
-        <v>3.1617</v>
+        <v>3.1628</v>
       </c>
       <c r="J259" t="n">
         <v>0.5507</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>0.845</v>
+        <v>0.846</v>
       </c>
     </row>
   </sheetData>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.149</v>
+        <v>1.15</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.939</v>
+        <v>1.938</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.653</v>
+        <v>2.652</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.831</v>
+        <v>-0.829</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68258.465</v>
+        <v>68340.458</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31692,19 +31692,19 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>1.1486</v>
+        <v>1.1498</v>
       </c>
       <c r="D259" t="n">
         <v>1.4126</v>
       </c>
       <c r="E259" t="n">
-        <v>1.9387</v>
+        <v>1.9376</v>
       </c>
       <c r="F259" t="n">
-        <v>2.6528</v>
+        <v>2.6524</v>
       </c>
       <c r="G259" t="n">
-        <v>3.7952</v>
+        <v>3.7947</v>
       </c>
       <c r="H259" t="n">
         <v>1.9793</v>
@@ -31716,25 +31716,25 @@
         <v>1.7988</v>
       </c>
       <c r="K259" t="n">
-        <v>-0.8307</v>
+        <v>-0.8295</v>
       </c>
       <c r="L259" t="n">
-        <v>-0.2725</v>
+        <v>-0.2729</v>
       </c>
       <c r="M259" t="n">
-        <v>0.854</v>
+        <v>0.8536</v>
       </c>
       <c r="N259" t="n">
         <v>-0.9792999999999999</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.3609</v>
+        <v>-0.3597</v>
       </c>
       <c r="P259" t="n">
-        <v>0.0785</v>
+        <v>0.0781</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.1433</v>
+        <v>1.1429</v>
       </c>
       <c r="R259" t="n">
         <v>1.1708</v>
@@ -31761,7 +31761,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z259" t="n">
-        <v>68258.4648</v>
+        <v>68340.45819999999</v>
       </c>
       <c r="AA259" t="n">
         <v>161.498</v>
@@ -32108,7 +32108,7 @@
         <v>0.1057</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6958</v>
+        <v>-0.6957</v>
       </c>
       <c r="F9" t="n">
         <v>0.1057</v>
@@ -33038,7 +33038,7 @@
         <v>-0.2168</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2201</v>
+        <v>-0.22</v>
       </c>
       <c r="J36" t="n">
         <v>0.07290000000000001</v>
@@ -33106,7 +33106,7 @@
         <v>-0.5995</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3659</v>
+        <v>-0.3658</v>
       </c>
       <c r="J38" t="n">
         <v>0.2151</v>
@@ -33446,7 +33446,7 @@
         <v>-1.7775</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9427</v>
+        <v>-0.9426</v>
       </c>
       <c r="J48" t="n">
         <v>0.7851</v>
@@ -33629,7 +33629,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.0599</v>
+        <v>-1.0598</v>
       </c>
       <c r="C54" t="n">
         <v>0.8923</v>
@@ -33752,7 +33752,7 @@
         <v>-2.9667</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0218</v>
+        <v>-1.0217</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4343</v>
@@ -33854,7 +33854,7 @@
         <v>-2.664</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1325</v>
+        <v>-1.1324</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9772999999999999</v>
@@ -33888,7 +33888,7 @@
         <v>-2.4338</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1125</v>
+        <v>-1.1124</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1594</v>
@@ -33922,7 +33922,7 @@
         <v>-2.4338</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0758</v>
+        <v>-1.0757</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3285</v>
@@ -34058,7 +34058,7 @@
         <v>-2.1135</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0854</v>
+        <v>-1.0853</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9565</v>
@@ -34194,7 +34194,7 @@
         <v>-1.4153</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2291</v>
+        <v>-1.229</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9543</v>
@@ -34228,7 +34228,7 @@
         <v>-1.4153</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2627</v>
+        <v>-1.2626</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9157</v>
@@ -34262,7 +34262,7 @@
         <v>-1.4153</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2494</v>
+        <v>-1.2493</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8851</v>
@@ -34398,7 +34398,7 @@
         <v>-0.7467</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2578</v>
+        <v>-1.2577</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6932</v>
@@ -34432,7 +34432,7 @@
         <v>-0.7467</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2245</v>
+        <v>-1.2244</v>
       </c>
       <c r="J77" t="n">
         <v>-1.5888</v>
@@ -34602,7 +34602,7 @@
         <v>-0.5931999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.352</v>
+        <v>-1.3519</v>
       </c>
       <c r="J82" t="n">
         <v>-1.338</v>
@@ -34794,7 +34794,7 @@
         <v>0.332</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.7192</v>
       </c>
       <c r="F88" t="n">
         <v>0.332</v>
@@ -34853,7 +34853,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.5088</v>
+        <v>-0.5087</v>
       </c>
       <c r="C90" t="n">
         <v>-0.0336</v>
@@ -34964,7 +34964,7 @@
         <v>0.1767</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6259</v>
+        <v>-0.6258</v>
       </c>
       <c r="F93" t="n">
         <v>0.1767</v>
@@ -35078,7 +35078,7 @@
         <v>-0.2429</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2756</v>
+        <v>-1.2755</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5809</v>
@@ -35146,7 +35146,7 @@
         <v>-0.1969</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0695</v>
+        <v>-1.0694</v>
       </c>
       <c r="J98" t="n">
         <v>-0.6121</v>
@@ -35168,7 +35168,7 @@
         <v>0.1595</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.3735</v>
+        <v>-0.3734</v>
       </c>
       <c r="F99" t="n">
         <v>0.1595</v>
@@ -35316,7 +35316,7 @@
         <v>-0.0924</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8203</v>
+        <v>-0.8202</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3509</v>
@@ -35712,7 +35712,7 @@
         <v>1.7491</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.0194</v>
+        <v>-0.0193</v>
       </c>
       <c r="F115" t="n">
         <v>1.7491</v>
@@ -35724,7 +35724,7 @@
         <v>0.2018</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.5004</v>
       </c>
       <c r="J115" t="n">
         <v>-0.2451</v>
@@ -36404,7 +36404,7 @@
         <v>0.6357</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0404</v>
+        <v>-0.0403</v>
       </c>
       <c r="J135" t="n">
         <v>-0.0023</v>
@@ -36710,7 +36710,7 @@
         <v>0.7886</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0775</v>
+        <v>-0.0774</v>
       </c>
       <c r="J144" t="n">
         <v>0.3317</v>
@@ -37050,7 +37050,7 @@
         <v>0.8228</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0268</v>
+        <v>0.0267</v>
       </c>
       <c r="J154" t="n">
         <v>0.7334000000000001</v>
@@ -37186,7 +37186,7 @@
         <v>0.8008999999999999</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1188</v>
+        <v>0.1187</v>
       </c>
       <c r="J158" t="n">
         <v>1.0065</v>
@@ -37641,7 +37641,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.7984</v>
+        <v>0.7983</v>
       </c>
       <c r="C172" t="n">
         <v>0.5012</v>
@@ -37684,7 +37684,7 @@
         <v>0.8367</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7871</v>
+        <v>0.787</v>
       </c>
       <c r="F173" t="n">
         <v>0.8367</v>
@@ -37845,7 +37845,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.6856</v>
+        <v>0.6855</v>
       </c>
       <c r="C178" t="n">
         <v>0.6659</v>
@@ -37934,7 +37934,7 @@
         <v>0.4597</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1445</v>
+        <v>-0.1446</v>
       </c>
       <c r="J180" t="n">
         <v>1.9099</v>
@@ -38287,7 +38287,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.245</v>
+        <v>0.2449</v>
       </c>
       <c r="C191" t="n">
         <v>0.3429</v>
@@ -38342,7 +38342,7 @@
         <v>-0.6925</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0232</v>
+        <v>-0.0233</v>
       </c>
       <c r="J192" t="n">
         <v>1.0417</v>
@@ -38410,7 +38410,7 @@
         <v>-0.4872</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0815</v>
+        <v>0.0814</v>
       </c>
       <c r="J194" t="n">
         <v>0.5568</v>
@@ -38432,7 +38432,7 @@
         <v>0.1957</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1547</v>
+        <v>0.1546</v>
       </c>
       <c r="F195" t="n">
         <v>0.1957</v>
@@ -38478,7 +38478,7 @@
         <v>-0.2759</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2183</v>
+        <v>0.2182</v>
       </c>
       <c r="J196" t="n">
         <v>0.0843</v>
@@ -38546,7 +38546,7 @@
         <v>-0.2759</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2702</v>
+        <v>0.2701</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4217</v>
@@ -38818,7 +38818,7 @@
         <v>0.2221</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4693</v>
+        <v>0.4692</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2481</v>
@@ -39044,7 +39044,7 @@
         <v>1.5657</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5438</v>
+        <v>0.5437</v>
       </c>
       <c r="F213" t="n">
         <v>1.5657</v>
@@ -39464,7 +39464,7 @@
         <v>0.8531</v>
       </c>
       <c r="I225" t="n">
-        <v>1.2124</v>
+        <v>1.2123</v>
       </c>
       <c r="J225" t="n">
         <v>0.3975</v>
@@ -39511,7 +39511,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9994</v>
       </c>
       <c r="C227" t="n">
         <v>-1.4189</v>
@@ -39532,7 +39532,7 @@
         <v>0.9577</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3128</v>
+        <v>1.3127</v>
       </c>
       <c r="J227" t="n">
         <v>0.3583</v>
@@ -39566,7 +39566,7 @@
         <v>0.9577</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3875</v>
+        <v>1.3874</v>
       </c>
       <c r="J228" t="n">
         <v>0.3614</v>
@@ -39634,7 +39634,7 @@
         <v>1.0556</v>
       </c>
       <c r="I230" t="n">
-        <v>1.4215</v>
+        <v>1.4214</v>
       </c>
       <c r="J230" t="n">
         <v>0.4868</v>
@@ -39668,7 +39668,7 @@
         <v>1.0556</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5676</v>
+        <v>1.5675</v>
       </c>
       <c r="J231" t="n">
         <v>0.4234</v>
@@ -39804,7 +39804,7 @@
         <v>1.1507</v>
       </c>
       <c r="I235" t="n">
-        <v>1.8303</v>
+        <v>1.8302</v>
       </c>
       <c r="J235" t="n">
         <v>0.5446</v>
@@ -39838,7 +39838,7 @@
         <v>1.1507</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8676</v>
+        <v>1.8675</v>
       </c>
       <c r="J236" t="n">
         <v>0.5608</v>
@@ -39906,7 +39906,7 @@
         <v>1.1335</v>
       </c>
       <c r="I238" t="n">
-        <v>1.6224</v>
+        <v>1.6223</v>
       </c>
       <c r="J238" t="n">
         <v>0.5275</v>
@@ -39928,7 +39928,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9825</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -39940,7 +39940,7 @@
         <v>1.1335</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7904</v>
+        <v>1.7903</v>
       </c>
       <c r="J239" t="n">
         <v>0.622</v>
@@ -39974,7 +39974,7 @@
         <v>1.1335</v>
       </c>
       <c r="I240" t="n">
-        <v>1.868</v>
+        <v>1.8679</v>
       </c>
       <c r="J240" t="n">
         <v>0.5928</v>
@@ -40021,7 +40021,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0496</v>
+        <v>1.0495</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40144,7 +40144,7 @@
         <v>1.1837</v>
       </c>
       <c r="I245" t="n">
-        <v>1.7185</v>
+        <v>1.7184</v>
       </c>
       <c r="J245" t="n">
         <v>0.6133999999999999</v>
@@ -40200,7 +40200,7 @@
         <v>1.4542</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8669</v>
+        <v>0.8668</v>
       </c>
       <c r="F247" t="n">
         <v>1.4542</v>
@@ -40212,7 +40212,7 @@
         <v>1.0856</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8501</v>
+        <v>1.85</v>
       </c>
       <c r="J247" t="n">
         <v>0.6142</v>
@@ -40348,7 +40348,7 @@
         <v>1.1121</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2908</v>
+        <v>2.2907</v>
       </c>
       <c r="J251" t="n">
         <v>0.6411</v>
@@ -40370,7 +40370,7 @@
         <v>1.2101</v>
       </c>
       <c r="E252" t="n">
-        <v>0.952</v>
+        <v>0.9519</v>
       </c>
       <c r="F252" t="n">
         <v>1.2101</v>
@@ -40382,7 +40382,7 @@
         <v>1.1121</v>
       </c>
       <c r="I252" t="n">
-        <v>2.4216</v>
+        <v>2.4215</v>
       </c>
       <c r="J252" t="n">
         <v>0.6234</v>
@@ -40416,7 +40416,7 @@
         <v>1.1399</v>
       </c>
       <c r="I253" t="n">
-        <v>2.4473</v>
+        <v>2.4472</v>
       </c>
       <c r="J253" t="n">
         <v>0.6173</v>
@@ -40450,7 +40450,7 @@
         <v>1.1399</v>
       </c>
       <c r="I254" t="n">
-        <v>2.5585</v>
+        <v>2.5584</v>
       </c>
       <c r="J254" t="n">
         <v>0.5982</v>
@@ -40484,7 +40484,7 @@
         <v>1.1399</v>
       </c>
       <c r="I255" t="n">
-        <v>2.6404</v>
+        <v>2.6403</v>
       </c>
       <c r="J255" t="n">
         <v>0.5657</v>
@@ -40518,7 +40518,7 @@
         <v>1.0108</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6622</v>
+        <v>2.6621</v>
       </c>
       <c r="J256" t="n">
         <v>0.6137</v>
@@ -40540,7 +40540,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8752</v>
+        <v>0.8751</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40552,7 +40552,7 @@
         <v>1.0108</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7946</v>
+        <v>2.7945</v>
       </c>
       <c r="J257" t="n">
         <v>0.4797</v>
@@ -40565,7 +40565,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.8074</v>
+        <v>0.8073</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40586,7 +40586,7 @@
         <v>1.0108</v>
       </c>
       <c r="I258" t="n">
-        <v>2.9529</v>
+        <v>2.9528</v>
       </c>
       <c r="J258" t="n">
         <v>0.5727</v>
@@ -40599,19 +40599,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8454</v>
+        <v>0.8457</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
-        <v>0.3189</v>
+        <v>0.3188</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9771</v>
+        <v>0.9775</v>
       </c>
       <c r="F259" t="n">
-        <v>0.3189</v>
+        <v>0.3188</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8917</v>
@@ -40620,7 +40620,7 @@
         <v>1.0864</v>
       </c>
       <c r="I259" t="n">
-        <v>3.1628</v>
+        <v>3.1644</v>
       </c>
       <c r="J259" t="n">
         <v>0.5507</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>-0.445</v>
+        <v>-0.446</v>
       </c>
     </row>
     <row r="21">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>-0.428</v>
+        <v>-0.429</v>
       </c>
     </row>
     <row r="45">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>-1.186</v>
+        <v>-1.187</v>
       </c>
     </row>
     <row r="67">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>-1.15</v>
+        <v>-1.151</v>
       </c>
     </row>
     <row r="70">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.9419999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>-0.471</v>
+        <v>-0.472</v>
       </c>
     </row>
     <row r="93">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="109">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>0.66</v>
+        <v>0.661</v>
       </c>
     </row>
     <row r="161">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>0.241</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="192">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>0.882</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="217">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>0.821</v>
+        <v>0.822</v>
       </c>
     </row>
     <row r="218">
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>1.025</v>
+        <v>1.026</v>
       </c>
     </row>
     <row r="241">
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>1.031</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="242">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="250">
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>0.994</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="253">
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>0.846</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="256">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.971</v>
+        <v>0.967</v>
       </c>
     </row>
   </sheetData>
@@ -3563,11 +3563,11 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.15</v>
+        <v>1.164</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3589,11 +3589,11 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.411</v>
+        <v>1.4</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.938</v>
+        <v>1.959</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.654</v>
+        <v>2.711</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3667,11 +3667,11 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.798</v>
+        <v>3.883</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.829</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.855</v>
+        <v>0.912</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.06</v>
+        <v>-1.13</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>70474.96000000001</v>
+        <v>69604.05499999999</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1505</v>
+        <v>1.164</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4112</v>
+        <v>1.4</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9375</v>
+        <v>1.959</v>
       </c>
       <c r="F260" t="n">
-        <v>2.6541</v>
+        <v>2.711</v>
       </c>
       <c r="G260" t="n">
-        <v>3.7982</v>
+        <v>3.883</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8288</v>
+        <v>-0.8153</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2739</v>
+        <v>-0.2742</v>
       </c>
       <c r="M260" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.9122</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>70474.96000000001</v>
+        <v>69604.05499999999</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -31995,7 +31995,7 @@
         <v>0.2573</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8993</v>
+        <v>-0.8994</v>
       </c>
       <c r="F2" t="n">
         <v>0.2573</v>
@@ -32004,7 +32004,7 @@
         <v>-0.3417</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6421</v>
+        <v>-0.6423</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7141</v>
@@ -32017,7 +32017,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.6089</v>
+        <v>-0.609</v>
       </c>
       <c r="D3" t="n">
         <v>0.1079</v>
@@ -32032,7 +32032,7 @@
         <v>-0.3193</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5883</v>
+        <v>-0.5885</v>
       </c>
       <c r="J3" t="n">
         <v>-1.636</v>
@@ -32054,7 +32054,7 @@
         <v>0.1593</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.746</v>
+        <v>-0.7461</v>
       </c>
       <c r="F4" t="n">
         <v>0.1593</v>
@@ -32066,7 +32066,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5649</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6448</v>
@@ -32100,7 +32100,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5434</v>
+        <v>-0.5436</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5114</v>
@@ -32113,7 +32113,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5077</v>
+        <v>-0.5078</v>
       </c>
       <c r="C6" t="n">
         <v>-0.0915</v>
@@ -32134,7 +32134,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5326</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4181</v>
@@ -32168,7 +32168,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4857</v>
+        <v>-0.4858</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5085</v>
@@ -32190,7 +32190,7 @@
         <v>0.129</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6702</v>
+        <v>-0.6703</v>
       </c>
       <c r="F8" t="n">
         <v>0.129</v>
@@ -32202,7 +32202,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.405</v>
+        <v>-0.4052</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3584</v>
@@ -32236,7 +32236,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4082</v>
+        <v>-0.4083</v>
       </c>
       <c r="J9" t="n">
         <v>-1.39</v>
@@ -32258,7 +32258,7 @@
         <v>0.0931</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6329</v>
+        <v>-0.633</v>
       </c>
       <c r="F10" t="n">
         <v>0.0931</v>
@@ -32270,7 +32270,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3827</v>
+        <v>-0.3828</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2447</v>
@@ -32304,7 +32304,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2971</v>
+        <v>-0.2972</v>
       </c>
       <c r="J11" t="n">
         <v>-1.282</v>
@@ -32317,7 +32317,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.4697</v>
+        <v>-0.4698</v>
       </c>
       <c r="C12" t="n">
         <v>-0.3965</v>
@@ -32338,7 +32338,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1985</v>
+        <v>-0.1986</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2069</v>
@@ -32406,7 +32406,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2066</v>
+        <v>-0.2067</v>
       </c>
       <c r="J14" t="n">
         <v>-1.1493</v>
@@ -32508,7 +32508,7 @@
         <v>-0.0989</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1231</v>
+        <v>-0.1232</v>
       </c>
       <c r="J17" t="n">
         <v>-1.017</v>
@@ -32576,7 +32576,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1731</v>
+        <v>-0.1732</v>
       </c>
       <c r="J19" t="n">
         <v>-0.8567</v>
@@ -32598,7 +32598,7 @@
         <v>0.0143</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5604</v>
+        <v>-0.5605</v>
       </c>
       <c r="F20" t="n">
         <v>0.0143</v>
@@ -32610,7 +32610,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1334</v>
+        <v>-0.1335</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8238</v>
@@ -32644,7 +32644,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1037</v>
+        <v>-0.1038</v>
       </c>
       <c r="J21" t="n">
         <v>-0.7688</v>
@@ -32678,7 +32678,7 @@
         <v>0.0999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0827</v>
+        <v>-0.0828</v>
       </c>
       <c r="J22" t="n">
         <v>-0.7466</v>
@@ -32734,7 +32734,7 @@
         <v>0.0534</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4621</v>
+        <v>-0.4622</v>
       </c>
       <c r="F24" t="n">
         <v>0.0534</v>
@@ -33052,7 +33052,7 @@
         <v>0.2376</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0273</v>
+        <v>-0.0274</v>
       </c>
       <c r="J33" t="n">
         <v>-0.1775</v>
@@ -33099,7 +33099,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4145</v>
+        <v>-0.4146</v>
       </c>
       <c r="C35" t="n">
         <v>-0.1623</v>
@@ -33120,7 +33120,7 @@
         <v>-0.221</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0854</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0.0234</v>
@@ -33142,7 +33142,7 @@
         <v>0.1664</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5298</v>
       </c>
       <c r="F36" t="n">
         <v>0.1664</v>
@@ -33188,7 +33188,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2307</v>
+        <v>-0.2308</v>
       </c>
       <c r="J37" t="n">
         <v>0.1592</v>
@@ -33222,7 +33222,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3697</v>
+        <v>-0.3698</v>
       </c>
       <c r="J38" t="n">
         <v>0.2133</v>
@@ -33256,7 +33256,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.416</v>
+        <v>-0.4162</v>
       </c>
       <c r="J39" t="n">
         <v>0.2403</v>
@@ -33290,7 +33290,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5592</v>
+        <v>-0.5593</v>
       </c>
       <c r="J40" t="n">
         <v>0.3628</v>
@@ -33324,7 +33324,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.556</v>
       </c>
       <c r="J41" t="n">
         <v>0.3781</v>
@@ -33337,7 +33337,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.4717</v>
+        <v>-0.4718</v>
       </c>
       <c r="C42" t="n">
         <v>-0.2345</v>
@@ -33358,7 +33358,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5288</v>
+        <v>-0.5289</v>
       </c>
       <c r="J42" t="n">
         <v>0.4876</v>
@@ -33380,7 +33380,7 @@
         <v>0.7408</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.8077</v>
+        <v>-0.8078</v>
       </c>
       <c r="F43" t="n">
         <v>0.7408</v>
@@ -33392,7 +33392,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5208</v>
+        <v>-0.5209</v>
       </c>
       <c r="J43" t="n">
         <v>0.5449000000000001</v>
@@ -33426,7 +33426,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5611</v>
+        <v>-0.5612</v>
       </c>
       <c r="J44" t="n">
         <v>0.5838</v>
@@ -33439,7 +33439,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4097</v>
+        <v>-0.4098</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3257</v>
@@ -33460,7 +33460,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5568</v>
+        <v>-0.5569</v>
       </c>
       <c r="J45" t="n">
         <v>0.7429</v>
@@ -33473,7 +33473,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4896</v>
+        <v>-0.4897</v>
       </c>
       <c r="C46" t="n">
         <v>-0.3034</v>
@@ -33482,7 +33482,7 @@
         <v>0.9776</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.8565</v>
       </c>
       <c r="F46" t="n">
         <v>0.9776</v>
@@ -33494,7 +33494,7 @@
         <v>-1.781</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.6498</v>
       </c>
       <c r="J46" t="n">
         <v>0.7907999999999999</v>
@@ -33528,7 +33528,7 @@
         <v>-1.781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8541</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0.7421</v>
@@ -33541,7 +33541,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6372</v>
+        <v>-0.6373</v>
       </c>
       <c r="C48" t="n">
         <v>-0.2059</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9362</v>
+        <v>-0.9365</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33575,7 +33575,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8157</v>
+        <v>-0.8158</v>
       </c>
       <c r="C49" t="n">
         <v>-0.1283</v>
@@ -33584,7 +33584,7 @@
         <v>-0.08690000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.9979</v>
+        <v>-0.998</v>
       </c>
       <c r="F49" t="n">
         <v>-0.08690000000000001</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0576</v>
+        <v>-1.0579</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33609,7 +33609,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8145</v>
+        <v>-0.8146</v>
       </c>
       <c r="C50" t="n">
         <v>0.0205</v>
@@ -33618,7 +33618,7 @@
         <v>0.132</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.0511</v>
+        <v>-1.0512</v>
       </c>
       <c r="F50" t="n">
         <v>0.132</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1047</v>
+        <v>-1.1049</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.8337</v>
+        <v>-0.8338</v>
       </c>
       <c r="C51" t="n">
         <v>0.2917</v>
@@ -33652,7 +33652,7 @@
         <v>0.1178</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0716</v>
+        <v>-1.0717</v>
       </c>
       <c r="F51" t="n">
         <v>0.1178</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.117</v>
+        <v>-1.1173</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.024</v>
+        <v>-1.0242</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33720,7 +33720,7 @@
         <v>0.0622</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2343</v>
+        <v>-1.2344</v>
       </c>
       <c r="F53" t="n">
         <v>0.0622</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9971</v>
+        <v>-0.9973</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.0586</v>
+        <v>-1.0587</v>
       </c>
       <c r="C54" t="n">
         <v>0.8923</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0231</v>
+        <v>-1.0233</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9972</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33822,7 +33822,7 @@
         <v>-0.8145</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.3551</v>
+        <v>-1.3552</v>
       </c>
       <c r="F56" t="n">
         <v>-0.8145</v>
@@ -33834,7 +33834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0536</v>
+        <v>-1.0538</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2426</v>
@@ -33856,7 +33856,7 @@
         <v>-0.8924</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.399</v>
+        <v>-1.3991</v>
       </c>
       <c r="F57" t="n">
         <v>-0.8924</v>
@@ -33868,7 +33868,7 @@
         <v>-2.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0151</v>
+        <v>-1.0153</v>
       </c>
       <c r="J57" t="n">
         <v>-0.437</v>
@@ -33890,7 +33890,7 @@
         <v>-0.8324</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.3505</v>
+        <v>-1.3506</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8324</v>
@@ -33902,7 +33902,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0939</v>
+        <v>-1.0941</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5746</v>
@@ -33936,7 +33936,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1091</v>
+        <v>-1.1093</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8135</v>
@@ -33949,7 +33949,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.2495</v>
+        <v>-1.2496</v>
       </c>
       <c r="C60" t="n">
         <v>0.9198</v>
@@ -33958,7 +33958,7 @@
         <v>-0.5407999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.4267</v>
+        <v>-1.4268</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5407999999999999</v>
@@ -33970,7 +33970,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1244</v>
+        <v>-1.1246</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -33983,7 +33983,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.194</v>
+        <v>-1.1941</v>
       </c>
       <c r="C61" t="n">
         <v>0.8397</v>
@@ -33992,7 +33992,7 @@
         <v>-0.3869</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.3958</v>
+        <v>-1.3959</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3869</v>
@@ -34004,7 +34004,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1048</v>
+        <v>-1.105</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1631</v>
@@ -34038,7 +34038,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0688</v>
+        <v>-1.069</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3324</v>
@@ -34060,7 +34060,7 @@
         <v>-0.2126</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.4379</v>
+        <v>-1.438</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2126</v>
@@ -34072,7 +34072,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0986</v>
+        <v>-1.0988</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4556</v>
@@ -34094,7 +34094,7 @@
         <v>-0.2615</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3881</v>
+        <v>-1.3882</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2615</v>
@@ -34106,7 +34106,7 @@
         <v>-2.117</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0772</v>
+        <v>-1.0774</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6903</v>
@@ -34140,7 +34140,7 @@
         <v>-2.117</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0358</v>
+        <v>-1.036</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8128</v>
@@ -34174,7 +34174,7 @@
         <v>-2.117</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0779</v>
+        <v>-1.0781</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9613</v>
@@ -34187,7 +34187,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1444</v>
+        <v>-1.1445</v>
       </c>
       <c r="C67" t="n">
         <v>0.6892</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0994</v>
+        <v>-1.0996</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34221,7 +34221,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1683</v>
+        <v>-1.1684</v>
       </c>
       <c r="C68" t="n">
         <v>0.6511</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1671</v>
+        <v>-1.1673</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.202</v>
+        <v>-1.2023</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34298,7 +34298,7 @@
         <v>-0.2922</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2549</v>
+        <v>-1.255</v>
       </c>
       <c r="F70" t="n">
         <v>-0.2922</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2199</v>
+        <v>-1.2202</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34332,7 +34332,7 @@
         <v>-0.1096</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2462</v>
+        <v>-1.2463</v>
       </c>
       <c r="F71" t="n">
         <v>-0.1096</v>
@@ -34344,7 +34344,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2534</v>
+        <v>-1.2536</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9205</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2403</v>
+        <v>-1.2405</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34400,7 +34400,7 @@
         <v>-0.1169</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1621</v>
+        <v>-1.1622</v>
       </c>
       <c r="F73" t="n">
         <v>-0.1169</v>
@@ -34412,7 +34412,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2018</v>
+        <v>-1.202</v>
       </c>
       <c r="J73" t="n">
         <v>-1.852</v>
@@ -34425,7 +34425,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.9603</v>
+        <v>-0.9604</v>
       </c>
       <c r="C74" t="n">
         <v>0.4026</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2279</v>
+        <v>-1.2281</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34480,7 +34480,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2179</v>
+        <v>-1.2181</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8065</v>
@@ -34502,7 +34502,7 @@
         <v>-0.0857</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0095</v>
+        <v>-1.0096</v>
       </c>
       <c r="F76" t="n">
         <v>-0.0857</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2487</v>
+        <v>-1.2489</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34527,7 +34527,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7479</v>
+        <v>-0.748</v>
       </c>
       <c r="C77" t="n">
         <v>0.3431</v>
@@ -34536,7 +34536,7 @@
         <v>0.0533</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9482</v>
+        <v>-0.9483</v>
       </c>
       <c r="F77" t="n">
         <v>0.0533</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2157</v>
+        <v>-1.2159</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34561,7 +34561,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7517</v>
+        <v>-0.7518</v>
       </c>
       <c r="C78" t="n">
         <v>0.2407</v>
@@ -34582,7 +34582,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2552</v>
+        <v>-1.2554</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6257</v>
@@ -34595,7 +34595,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7216</v>
+        <v>-0.7217</v>
       </c>
       <c r="C79" t="n">
         <v>0.1954</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2775</v>
+        <v>-1.2777</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34650,7 +34650,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2782</v>
+        <v>-1.2784</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5104</v>
@@ -34672,7 +34672,7 @@
         <v>0.3202</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.9136</v>
+        <v>-0.9137</v>
       </c>
       <c r="F81" t="n">
         <v>0.3202</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3254</v>
+        <v>-1.3257</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34706,7 +34706,7 @@
         <v>0.3265</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8637</v>
+        <v>-0.8638</v>
       </c>
       <c r="F82" t="n">
         <v>0.3265</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3416</v>
+        <v>-1.3418</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34731,7 +34731,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6607</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="C83" t="n">
         <v>0.09279999999999999</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3383</v>
+        <v>-1.3386</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34774,7 +34774,7 @@
         <v>0.1353</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8497</v>
+        <v>-0.8498</v>
       </c>
       <c r="F84" t="n">
         <v>0.1353</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.325</v>
+        <v>-1.3253</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34799,7 +34799,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.6208</v>
+        <v>-0.6209</v>
       </c>
       <c r="C85" t="n">
         <v>0.0525</v>
@@ -34808,7 +34808,7 @@
         <v>0.1899</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.8235</v>
+        <v>-0.8236</v>
       </c>
       <c r="F85" t="n">
         <v>0.1899</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3301</v>
+        <v>-1.3303</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34854,7 +34854,7 @@
         <v>-0.573</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3526</v>
+        <v>-1.3529</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1193</v>
@@ -34876,7 +34876,7 @@
         <v>0.2856</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.7687</v>
+        <v>-0.7688</v>
       </c>
       <c r="F87" t="n">
         <v>0.2856</v>
@@ -34888,7 +34888,7 @@
         <v>-0.573</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3007</v>
+        <v>-1.3009</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1278</v>
@@ -34901,7 +34901,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.5084</v>
+        <v>-0.5085</v>
       </c>
       <c r="C88" t="n">
         <v>-0.0463</v>
@@ -34910,7 +34910,7 @@
         <v>0.332</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7185</v>
+        <v>-0.7186</v>
       </c>
       <c r="F88" t="n">
         <v>0.332</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2193</v>
+        <v>-1.2195</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -34956,7 +34956,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2429</v>
+        <v>-1.2431</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0865</v>
@@ -34969,7 +34969,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.5079</v>
+        <v>-0.508</v>
       </c>
       <c r="C90" t="n">
         <v>-0.0336</v>
@@ -34978,7 +34978,7 @@
         <v>0.2133</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.6882</v>
+        <v>-0.6883</v>
       </c>
       <c r="F90" t="n">
         <v>0.2133</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2969</v>
+        <v>-1.2972</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35003,7 +35003,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.4849</v>
+        <v>-0.485</v>
       </c>
       <c r="C91" t="n">
         <v>-0.1676</v>
@@ -35024,7 +35024,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.299</v>
+        <v>-1.2993</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9396</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3029</v>
+        <v>-1.3032</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35071,7 +35071,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4645</v>
+        <v>-0.4646</v>
       </c>
       <c r="C93" t="n">
         <v>-0.2228</v>
@@ -35080,7 +35080,7 @@
         <v>0.1767</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6248</v>
+        <v>-0.6249</v>
       </c>
       <c r="F93" t="n">
         <v>0.1767</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3008</v>
+        <v>-1.3011</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35105,7 +35105,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4025</v>
+        <v>-0.4026</v>
       </c>
       <c r="C94" t="n">
         <v>-0.3182</v>
@@ -35114,7 +35114,7 @@
         <v>0.2719</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.5712</v>
       </c>
       <c r="F94" t="n">
         <v>0.2719</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3105</v>
+        <v>-1.3108</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35148,7 +35148,7 @@
         <v>0.272</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5617</v>
+        <v>-0.5618</v>
       </c>
       <c r="F95" t="n">
         <v>0.272</v>
@@ -35160,7 +35160,7 @@
         <v>-0.247</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2975</v>
+        <v>-1.2977</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7848000000000001</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.266</v>
+        <v>-1.2662</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.2013</v>
+        <v>-1.2015</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35241,7 +35241,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.3179</v>
+        <v>-0.318</v>
       </c>
       <c r="C98" t="n">
         <v>-0.3705</v>
@@ -35250,7 +35250,7 @@
         <v>0.1393</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.4322</v>
+        <v>-0.4323</v>
       </c>
       <c r="F98" t="n">
         <v>0.1393</v>
@@ -35262,7 +35262,7 @@
         <v>-0.201</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0629</v>
+        <v>-1.0631</v>
       </c>
       <c r="J98" t="n">
         <v>-0.615</v>
@@ -35284,7 +35284,7 @@
         <v>0.1595</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.3737</v>
+        <v>-0.3738</v>
       </c>
       <c r="F99" t="n">
         <v>0.1595</v>
@@ -35296,7 +35296,7 @@
         <v>-0.201</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9751</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5022</v>
@@ -35318,7 +35318,7 @@
         <v>0.0925</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.3401</v>
+        <v>-0.3402</v>
       </c>
       <c r="F100" t="n">
         <v>0.0925</v>
@@ -35330,7 +35330,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.9261</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4986</v>
@@ -35364,7 +35364,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8391</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4122</v>
@@ -35398,7 +35398,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7406</v>
+        <v>-0.7407</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4036</v>
@@ -35411,7 +35411,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.1106</v>
+        <v>-0.1107</v>
       </c>
       <c r="C103" t="n">
         <v>-0.4519</v>
@@ -35420,7 +35420,7 @@
         <v>0.3913</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2361</v>
+        <v>-0.2362</v>
       </c>
       <c r="F103" t="n">
         <v>0.3913</v>
@@ -35432,7 +35432,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8177</v>
+        <v>-0.8178</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3535</v>
@@ -35466,7 +35466,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7258</v>
+        <v>-0.7259</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2313</v>
@@ -35500,7 +35500,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7663</v>
+        <v>-0.7664</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2434</v>
@@ -35534,7 +35534,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7146</v>
+        <v>-0.7147</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3611</v>
@@ -35568,7 +35568,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7106</v>
+        <v>-0.7107</v>
       </c>
       <c r="J107" t="n">
         <v>-0.2576</v>
@@ -35602,7 +35602,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.65</v>
+        <v>-0.6501</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2887</v>
@@ -35636,7 +35636,7 @@
         <v>0.1473</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5566</v>
+        <v>-0.5567</v>
       </c>
       <c r="J109" t="n">
         <v>-0.2918</v>
@@ -35658,7 +35658,7 @@
         <v>0.8838</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.0809</v>
+        <v>-0.081</v>
       </c>
       <c r="F110" t="n">
         <v>0.8838</v>
@@ -35670,7 +35670,7 @@
         <v>0.1473</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5415</v>
+        <v>-0.5416</v>
       </c>
       <c r="J110" t="n">
         <v>-0.3002</v>
@@ -35704,7 +35704,7 @@
         <v>0.1473</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5651</v>
+        <v>-0.5652</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2361</v>
@@ -35717,7 +35717,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.1357</v>
+        <v>0.1356</v>
       </c>
       <c r="C112" t="n">
         <v>-0.6355</v>
@@ -35738,7 +35738,7 @@
         <v>0.174</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5491</v>
+        <v>-0.5492</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2387</v>
@@ -35772,7 +35772,7 @@
         <v>0.174</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5445</v>
+        <v>-0.5446</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2332</v>
@@ -35806,7 +35806,7 @@
         <v>0.174</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5215</v>
+        <v>-0.5216</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2168</v>
@@ -35819,7 +35819,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3325</v>
+        <v>0.3324</v>
       </c>
       <c r="C115" t="n">
         <v>-0.7068</v>
@@ -35874,7 +35874,7 @@
         <v>0.1975</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4753</v>
+        <v>-0.4754</v>
       </c>
       <c r="J116" t="n">
         <v>-0.1328</v>
@@ -35908,7 +35908,7 @@
         <v>0.1975</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.449</v>
+        <v>-0.4491</v>
       </c>
       <c r="J117" t="n">
         <v>-0.1106</v>
@@ -35976,7 +35976,7 @@
         <v>0.2561</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3264</v>
+        <v>-0.3265</v>
       </c>
       <c r="J119" t="n">
         <v>-0.0751</v>
@@ -36010,7 +36010,7 @@
         <v>0.2561</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1504</v>
+        <v>-0.1505</v>
       </c>
       <c r="J120" t="n">
         <v>-0.0558</v>
@@ -36066,7 +36066,7 @@
         <v>1.3542</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1668</v>
+        <v>0.1667</v>
       </c>
       <c r="F122" t="n">
         <v>1.3542</v>
@@ -36261,7 +36261,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3117</v>
+        <v>0.3118</v>
       </c>
       <c r="C128" t="n">
         <v>-0.0979</v>
@@ -36282,7 +36282,7 @@
         <v>0.4759</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1534</v>
+        <v>0.1535</v>
       </c>
       <c r="J128" t="n">
         <v>-0.0375</v>
@@ -36295,7 +36295,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.2932</v>
+        <v>0.2933</v>
       </c>
       <c r="C129" t="n">
         <v>-0.1422</v>
@@ -36418,7 +36418,7 @@
         <v>0.5522</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1303</v>
+        <v>0.1304</v>
       </c>
       <c r="J132" t="n">
         <v>-0.0194</v>
@@ -36499,7 +36499,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.3696</v>
+        <v>0.3695</v>
       </c>
       <c r="C135" t="n">
         <v>0.034</v>
@@ -36520,7 +36520,7 @@
         <v>0.6312</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0497</v>
+        <v>-0.0498</v>
       </c>
       <c r="J135" t="n">
         <v>-0.0044</v>
@@ -36635,7 +36635,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.3848</v>
+        <v>0.3847</v>
       </c>
       <c r="C139" t="n">
         <v>0.2569</v>
@@ -36678,7 +36678,7 @@
         <v>0.3014</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3888</v>
+        <v>0.3887</v>
       </c>
       <c r="F140" t="n">
         <v>0.3014</v>
@@ -36724,7 +36724,7 @@
         <v>0.7799</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2419</v>
+        <v>-0.242</v>
       </c>
       <c r="J141" t="n">
         <v>0.1338</v>
@@ -36848,7 +36848,7 @@
         <v>0.6333</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5187</v>
       </c>
       <c r="F145" t="n">
         <v>0.6333</v>
@@ -36928,7 +36928,7 @@
         <v>0.7738</v>
       </c>
       <c r="I147" t="n">
-        <v>0.0199</v>
+        <v>0.02</v>
       </c>
       <c r="J147" t="n">
         <v>0.4469</v>
@@ -37030,7 +37030,7 @@
         <v>0.7911</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0256</v>
+        <v>0.0257</v>
       </c>
       <c r="J150" t="n">
         <v>0.5614</v>
@@ -37077,7 +37077,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5868</v>
+        <v>0.5869</v>
       </c>
       <c r="C152" t="n">
         <v>0.2722</v>
@@ -37200,7 +37200,7 @@
         <v>0.8182</v>
       </c>
       <c r="I155" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0871</v>
       </c>
       <c r="J155" t="n">
         <v>0.8493000000000001</v>
@@ -37234,7 +37234,7 @@
         <v>0.8182</v>
       </c>
       <c r="I156" t="n">
-        <v>0.099</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="J156" t="n">
         <v>0.7732</v>
@@ -37268,7 +37268,7 @@
         <v>0.7964</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1239</v>
+        <v>0.1241</v>
       </c>
       <c r="J157" t="n">
         <v>0.8111</v>
@@ -37302,7 +37302,7 @@
         <v>0.7964</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1032</v>
+        <v>0.1034</v>
       </c>
       <c r="J158" t="n">
         <v>1.0058</v>
@@ -37336,7 +37336,7 @@
         <v>0.7964</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0378</v>
+        <v>0.0379</v>
       </c>
       <c r="J159" t="n">
         <v>0.9164</v>
@@ -37370,7 +37370,7 @@
         <v>0.8351</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0061</v>
+        <v>-0.006</v>
       </c>
       <c r="J160" t="n">
         <v>1.0232</v>
@@ -37404,7 +37404,7 @@
         <v>0.8351</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0282</v>
+        <v>0.0283</v>
       </c>
       <c r="J161" t="n">
         <v>1.0307</v>
@@ -37438,7 +37438,7 @@
         <v>0.8351</v>
       </c>
       <c r="I162" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J162" t="n">
         <v>1.1074</v>
@@ -37460,7 +37460,7 @@
         <v>0.7772</v>
       </c>
       <c r="E163" t="n">
-        <v>0.6964</v>
+        <v>0.6965</v>
       </c>
       <c r="F163" t="n">
         <v>0.7772</v>
@@ -37472,7 +37472,7 @@
         <v>0.8315</v>
       </c>
       <c r="I163" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0871</v>
       </c>
       <c r="J163" t="n">
         <v>1.2078</v>
@@ -37506,7 +37506,7 @@
         <v>0.8315</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1131</v>
+        <v>0.1132</v>
       </c>
       <c r="J164" t="n">
         <v>1.2107</v>
@@ -37528,7 +37528,7 @@
         <v>0.8058999999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>0.7246</v>
+        <v>0.7247</v>
       </c>
       <c r="F165" t="n">
         <v>0.8058999999999999</v>
@@ -37540,7 +37540,7 @@
         <v>0.8315</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1025</v>
+        <v>0.1026</v>
       </c>
       <c r="J165" t="n">
         <v>1.3214</v>
@@ -37574,7 +37574,7 @@
         <v>0.8931</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1431</v>
+        <v>0.1432</v>
       </c>
       <c r="J166" t="n">
         <v>1.2728</v>
@@ -37596,7 +37596,7 @@
         <v>0.8496</v>
       </c>
       <c r="E167" t="n">
-        <v>0.7527</v>
+        <v>0.7528</v>
       </c>
       <c r="F167" t="n">
         <v>0.8496</v>
@@ -37608,7 +37608,7 @@
         <v>0.8931</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1129</v>
+        <v>0.113</v>
       </c>
       <c r="J167" t="n">
         <v>1.3898</v>
@@ -37642,7 +37642,7 @@
         <v>0.8931</v>
       </c>
       <c r="I168" t="n">
-        <v>0.102</v>
+        <v>0.1021</v>
       </c>
       <c r="J168" t="n">
         <v>1.4434</v>
@@ -37710,7 +37710,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0389</v>
+        <v>-0.0388</v>
       </c>
       <c r="J170" t="n">
         <v>1.5391</v>
@@ -37744,7 +37744,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0212</v>
+        <v>-0.0211</v>
       </c>
       <c r="J171" t="n">
         <v>1.5073</v>
@@ -37766,7 +37766,7 @@
         <v>0.7994</v>
       </c>
       <c r="E172" t="n">
-        <v>0.7937</v>
+        <v>0.7938</v>
       </c>
       <c r="F172" t="n">
         <v>0.7994</v>
@@ -37778,7 +37778,7 @@
         <v>0.9594</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.016</v>
+        <v>-0.0159</v>
       </c>
       <c r="J172" t="n">
         <v>1.6568</v>
@@ -37812,7 +37812,7 @@
         <v>0.9594</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0142</v>
+        <v>-0.0141</v>
       </c>
       <c r="J173" t="n">
         <v>1.6146</v>
@@ -37902,7 +37902,7 @@
         <v>0.7313</v>
       </c>
       <c r="E176" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8121</v>
       </c>
       <c r="F176" t="n">
         <v>0.7313</v>
@@ -37914,7 +37914,7 @@
         <v>0.9559</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1314</v>
+        <v>-0.1313</v>
       </c>
       <c r="J176" t="n">
         <v>1.8233</v>
@@ -37948,7 +37948,7 @@
         <v>0.9559</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1857</v>
+        <v>-0.1856</v>
       </c>
       <c r="J177" t="n">
         <v>1.8036</v>
@@ -37982,7 +37982,7 @@
         <v>0.4553</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1678</v>
+        <v>-0.1677</v>
       </c>
       <c r="J178" t="n">
         <v>1.9327</v>
@@ -38016,7 +38016,7 @@
         <v>0.4553</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1677</v>
+        <v>-0.1675</v>
       </c>
       <c r="J179" t="n">
         <v>1.9402</v>
@@ -38050,7 +38050,7 @@
         <v>0.4553</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1558</v>
+        <v>-0.1556</v>
       </c>
       <c r="J180" t="n">
         <v>1.9104</v>
@@ -38072,7 +38072,7 @@
         <v>0.5621</v>
       </c>
       <c r="E181" t="n">
-        <v>0.5999</v>
+        <v>0.6</v>
       </c>
       <c r="F181" t="n">
         <v>0.5621</v>
@@ -38084,7 +38084,7 @@
         <v>0.0902</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1482</v>
+        <v>-0.148</v>
       </c>
       <c r="J181" t="n">
         <v>1.9524</v>
@@ -38118,7 +38118,7 @@
         <v>0.0902</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.176</v>
+        <v>-0.1758</v>
       </c>
       <c r="J182" t="n">
         <v>2.0487</v>
@@ -38131,7 +38131,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.6599</v>
+        <v>0.66</v>
       </c>
       <c r="C183" t="n">
         <v>0.5868</v>
@@ -38152,7 +38152,7 @@
         <v>0.0902</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1915</v>
+        <v>-0.1914</v>
       </c>
       <c r="J183" t="n">
         <v>2.1734</v>
@@ -38220,7 +38220,7 @@
         <v>-0.4422</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2968</v>
+        <v>-0.2967</v>
       </c>
       <c r="J185" t="n">
         <v>2.1134</v>
@@ -38288,7 +38288,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1876</v>
+        <v>-0.1875</v>
       </c>
       <c r="J187" t="n">
         <v>2.2679</v>
@@ -38310,7 +38310,7 @@
         <v>0.4361</v>
       </c>
       <c r="E188" t="n">
-        <v>0.3699</v>
+        <v>0.37</v>
       </c>
       <c r="F188" t="n">
         <v>0.4361</v>
@@ -38322,7 +38322,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.169</v>
+        <v>-0.1689</v>
       </c>
       <c r="J188" t="n">
         <v>2.0124</v>
@@ -38356,7 +38356,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1326</v>
+        <v>-0.1325</v>
       </c>
       <c r="J189" t="n">
         <v>1.7736</v>
@@ -38390,7 +38390,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1243</v>
+        <v>-0.1242</v>
       </c>
       <c r="J190" t="n">
         <v>1.5322</v>
@@ -38424,7 +38424,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0838</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J191" t="n">
         <v>1.307</v>
@@ -38437,7 +38437,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.1843</v>
+        <v>0.1844</v>
       </c>
       <c r="C192" t="n">
         <v>0.288</v>
@@ -38446,7 +38446,7 @@
         <v>0.0009</v>
       </c>
       <c r="E192" t="n">
-        <v>0.2302</v>
+        <v>0.2303</v>
       </c>
       <c r="F192" t="n">
         <v>0.0009</v>
@@ -38458,7 +38458,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.038</v>
+        <v>-0.0378</v>
       </c>
       <c r="J192" t="n">
         <v>1.0409</v>
@@ -38480,7 +38480,7 @@
         <v>0.1272</v>
       </c>
       <c r="E193" t="n">
-        <v>0.2352</v>
+        <v>0.2353</v>
       </c>
       <c r="F193" t="n">
         <v>0.1272</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38505,7 +38505,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.1722</v>
+        <v>0.1723</v>
       </c>
       <c r="C194" t="n">
         <v>0.2157</v>
@@ -38514,7 +38514,7 @@
         <v>0.1218</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1848</v>
+        <v>0.1849</v>
       </c>
       <c r="F194" t="n">
         <v>0.1218</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0638</v>
+        <v>0.064</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38539,7 +38539,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.1579</v>
+        <v>0.158</v>
       </c>
       <c r="C195" t="n">
         <v>0.1813</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1266</v>
+        <v>0.1269</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38573,7 +38573,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.1788</v>
+        <v>0.1789</v>
       </c>
       <c r="C196" t="n">
         <v>0.031</v>
@@ -38582,7 +38582,7 @@
         <v>0.2432</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1627</v>
+        <v>0.1628</v>
       </c>
       <c r="F196" t="n">
         <v>0.2432</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1985</v>
+        <v>0.1988</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38616,7 +38616,7 @@
         <v>0.0738</v>
       </c>
       <c r="E197" t="n">
-        <v>0.145</v>
+        <v>0.1451</v>
       </c>
       <c r="F197" t="n">
         <v>0.0738</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2428</v>
+        <v>0.2431</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38641,7 +38641,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.0775</v>
+        <v>0.0776</v>
       </c>
       <c r="C198" t="n">
         <v>-0.0649</v>
@@ -38650,7 +38650,7 @@
         <v>0.1608</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0567</v>
+        <v>0.0568</v>
       </c>
       <c r="F198" t="n">
         <v>0.1608</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2499</v>
+        <v>0.2502</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2971</v>
+        <v>0.2973</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38718,7 +38718,7 @@
         <v>0.3398</v>
       </c>
       <c r="E200" t="n">
-        <v>0.057</v>
+        <v>0.0571</v>
       </c>
       <c r="F200" t="n">
         <v>0.3398</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3036</v>
+        <v>0.3038</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3173</v>
+        <v>0.3175</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2612</v>
+        <v>0.2613</v>
       </c>
       <c r="C202" t="n">
         <v>-0.2762</v>
@@ -38786,7 +38786,7 @@
         <v>0.4635</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2106</v>
+        <v>0.2107</v>
       </c>
       <c r="F202" t="n">
         <v>0.4635</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4036</v>
+        <v>0.4039</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38811,7 +38811,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.2365</v>
+        <v>0.2366</v>
       </c>
       <c r="C203" t="n">
         <v>-0.2987</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4161</v>
+        <v>0.4163</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38845,7 +38845,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3003</v>
+        <v>0.3004</v>
       </c>
       <c r="C204" t="n">
         <v>-0.3445</v>
@@ -38854,7 +38854,7 @@
         <v>0.6375</v>
       </c>
       <c r="E204" t="n">
-        <v>0.216</v>
+        <v>0.2161</v>
       </c>
       <c r="F204" t="n">
         <v>0.6375</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4505</v>
+        <v>0.4508</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4561</v>
+        <v>0.4564</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38913,7 +38913,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3433</v>
+        <v>0.3434</v>
       </c>
       <c r="C206" t="n">
         <v>-0.5203</v>
@@ -38922,7 +38922,7 @@
         <v>0.5264</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2976</v>
+        <v>0.2977</v>
       </c>
       <c r="F206" t="n">
         <v>0.5264</v>
@@ -38934,7 +38934,7 @@
         <v>0.2178</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4467</v>
+        <v>0.447</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2505</v>
@@ -38968,7 +38968,7 @@
         <v>0.2178</v>
       </c>
       <c r="I207" t="n">
-        <v>0.462</v>
+        <v>0.4622</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2897</v>
@@ -38990,7 +38990,7 @@
         <v>0.7245</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3517</v>
+        <v>0.3518</v>
       </c>
       <c r="F208" t="n">
         <v>0.7245</v>
@@ -39002,7 +39002,7 @@
         <v>0.4029</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4922</v>
+        <v>0.4924</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2483</v>
@@ -39024,7 +39024,7 @@
         <v>1.2979</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4316</v>
+        <v>0.4317</v>
       </c>
       <c r="F209" t="n">
         <v>1.2979</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6347</v>
+        <v>0.6349</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39049,7 +39049,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.6031</v>
+        <v>0.6032</v>
       </c>
       <c r="C210" t="n">
         <v>-0.6456</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6821</v>
+        <v>0.6823</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39092,7 +39092,7 @@
         <v>1.3412</v>
       </c>
       <c r="E211" t="n">
-        <v>0.5147</v>
+        <v>0.5148</v>
       </c>
       <c r="F211" t="n">
         <v>1.3412</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.778</v>
+        <v>0.7782</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39126,7 +39126,7 @@
         <v>1.4354</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5154</v>
+        <v>0.5155</v>
       </c>
       <c r="F212" t="n">
         <v>1.4354</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8152</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39151,7 +39151,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.7417</v>
+        <v>0.7418</v>
       </c>
       <c r="C213" t="n">
         <v>-0.7202</v>
@@ -39160,7 +39160,7 @@
         <v>1.5657</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5357</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="F213" t="n">
         <v>1.5657</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8381</v>
+        <v>0.8383</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9417</v>
+        <v>0.9419</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0121</v>
+        <v>1.0123</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39262,7 +39262,7 @@
         <v>1.9735</v>
       </c>
       <c r="E216" t="n">
-        <v>0.6097</v>
+        <v>0.6098</v>
       </c>
       <c r="F216" t="n">
         <v>1.9735</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.952</v>
+        <v>0.9522</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39296,7 +39296,7 @@
         <v>1.562</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6363</v>
+        <v>0.6364</v>
       </c>
       <c r="F217" t="n">
         <v>1.562</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8214</v>
+        <v>0.8217</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39321,7 +39321,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.9151</v>
+        <v>0.9152</v>
       </c>
       <c r="C218" t="n">
         <v>-1.0065</v>
@@ -39330,7 +39330,7 @@
         <v>2.1396</v>
       </c>
       <c r="E218" t="n">
-        <v>0.609</v>
+        <v>0.6091</v>
       </c>
       <c r="F218" t="n">
         <v>2.1396</v>
@@ -39342,7 +39342,7 @@
         <v>0.7019</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7508</v>
+        <v>0.751</v>
       </c>
       <c r="J218" t="n">
         <v>0.1401</v>
@@ -39355,7 +39355,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8635</v>
       </c>
       <c r="C219" t="n">
         <v>-1.0961</v>
@@ -39376,7 +39376,7 @@
         <v>0.7019</v>
       </c>
       <c r="I219" t="n">
-        <v>0.823</v>
+        <v>0.8233</v>
       </c>
       <c r="J219" t="n">
         <v>0.2448</v>
@@ -39398,7 +39398,7 @@
         <v>1.7394</v>
       </c>
       <c r="E220" t="n">
-        <v>0.708</v>
+        <v>0.7081</v>
       </c>
       <c r="F220" t="n">
         <v>1.7394</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8254</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39423,7 +39423,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.9379</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="C221" t="n">
         <v>-1.2861</v>
@@ -39432,7 +39432,7 @@
         <v>1.8104</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7198</v>
+        <v>0.7199</v>
       </c>
       <c r="F221" t="n">
         <v>1.8104</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8449</v>
+        <v>0.8451</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39457,7 +39457,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.9336</v>
+        <v>0.9337</v>
       </c>
       <c r="C222" t="n">
         <v>-1.4025</v>
@@ -39466,7 +39466,7 @@
         <v>1.724</v>
       </c>
       <c r="E222" t="n">
-        <v>0.736</v>
+        <v>0.7361</v>
       </c>
       <c r="F222" t="n">
         <v>1.724</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9453</v>
+        <v>0.9456</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.99</v>
+        <v>0.9901</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39500,7 +39500,7 @@
         <v>1.7742</v>
       </c>
       <c r="E223" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="F223" t="n">
         <v>1.7742</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.072</v>
+        <v>1.0724</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39525,7 +39525,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.9816</v>
+        <v>0.9817</v>
       </c>
       <c r="C224" t="n">
         <v>-1.3976</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0907</v>
+        <v>1.0911</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39559,7 +39559,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.9969</v>
+        <v>0.997</v>
       </c>
       <c r="C225" t="n">
         <v>-1.3984</v>
@@ -39568,7 +39568,7 @@
         <v>1.6703</v>
       </c>
       <c r="E225" t="n">
-        <v>0.8286</v>
+        <v>0.8287</v>
       </c>
       <c r="F225" t="n">
         <v>1.6703</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1798</v>
+        <v>1.1802</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39593,7 +39593,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9835</v>
+        <v>0.9836</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
@@ -39602,7 +39602,7 @@
         <v>1.477</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8601</v>
+        <v>0.8602</v>
       </c>
       <c r="F226" t="n">
         <v>1.477</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2494</v>
+        <v>1.2498</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39636,7 +39636,7 @@
         <v>1.5257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.8585</v>
       </c>
       <c r="F227" t="n">
         <v>1.5257</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2796</v>
+        <v>1.2799</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39661,7 +39661,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.972</v>
+        <v>0.9721</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39670,7 +39670,7 @@
         <v>1.3813</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8697</v>
+        <v>0.8698</v>
       </c>
       <c r="F228" t="n">
         <v>1.3813</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3524</v>
+        <v>1.3528</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39704,7 +39704,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8885</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2803</v>
+        <v>1.2806</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39729,7 +39729,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.9899</v>
+        <v>0.99</v>
       </c>
       <c r="C230" t="n">
         <v>-1.8168</v>
@@ -39738,7 +39738,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9438</v>
+        <v>0.944</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3843</v>
+        <v>1.3848</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39763,7 +39763,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.065</v>
+        <v>1.0651</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -39772,7 +39772,7 @@
         <v>1.4899</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9588</v>
+        <v>0.9589</v>
       </c>
       <c r="F231" t="n">
         <v>1.4899</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5275</v>
+        <v>1.528</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39797,7 +39797,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0869</v>
+        <v>1.087</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39806,7 +39806,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0128</v>
+        <v>1.0129</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5935</v>
+        <v>1.5941</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39831,7 +39831,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.046</v>
+        <v>1.0461</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -39840,7 +39840,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0119</v>
+        <v>1.0121</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6565</v>
+        <v>1.657</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.0687</v>
+        <v>1.0688</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -39874,7 +39874,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.0114</v>
+        <v>1.0116</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7032</v>
+        <v>1.7038</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39899,7 +39899,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.0958</v>
+        <v>1.0959</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -39908,7 +39908,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0356</v>
+        <v>1.0357</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7865</v>
+        <v>1.7871</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39933,7 +39933,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0925</v>
+        <v>1.0926</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -39942,7 +39942,7 @@
         <v>1.3709</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0229</v>
+        <v>1.0231</v>
       </c>
       <c r="F236" t="n">
         <v>1.3709</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8227</v>
+        <v>1.8233</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0306</v>
+        <v>1.0307</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -39976,7 +39976,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9332</v>
+        <v>0.9333</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5945</v>
+        <v>1.595</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40001,7 +40001,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9842</v>
+        <v>0.9843</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40010,7 +40010,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9266</v>
+        <v>0.9268</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5807</v>
+        <v>1.5812</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40035,7 +40035,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.0069</v>
+        <v>1.007</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40044,7 +40044,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9724</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7462</v>
+        <v>1.7467</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40069,7 +40069,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0254</v>
+        <v>1.0255</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40078,7 +40078,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9688</v>
+        <v>0.9689</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8231</v>
+        <v>1.8236</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40103,7 +40103,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0314</v>
+        <v>1.0315</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40112,7 +40112,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9661</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8429</v>
+        <v>1.8434</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40137,7 +40137,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0416</v>
+        <v>1.0417</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40146,7 +40146,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9434</v>
+        <v>0.9435</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9166</v>
+        <v>1.9172</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40171,7 +40171,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.993</v>
+        <v>0.9931</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40180,7 +40180,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.9149</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8497</v>
+        <v>1.8502</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40205,7 +40205,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.0307</v>
+        <v>1.0308</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40214,7 +40214,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9503</v>
+        <v>0.9504</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8035</v>
+        <v>1.804</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40239,7 +40239,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.007</v>
+        <v>1.0071</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40248,7 +40248,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8648</v>
+        <v>0.8649</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6765</v>
+        <v>1.6769</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40273,7 +40273,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0329</v>
+        <v>1.033</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40282,7 +40282,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8962</v>
+        <v>0.8964</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7741</v>
+        <v>1.7746</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40307,7 +40307,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9771</v>
+        <v>0.9772</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40316,7 +40316,7 @@
         <v>1.4542</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8578</v>
+        <v>0.858</v>
       </c>
       <c r="F247" t="n">
         <v>1.4542</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8043</v>
+        <v>1.8048</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9482</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40350,7 +40350,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8601</v>
+        <v>0.8603</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9216</v>
+        <v>1.9222</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9345</v>
+        <v>0.9346</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40384,7 +40384,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.889</v>
+        <v>0.8892</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9898</v>
+        <v>1.9904</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40409,7 +40409,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9462</v>
+        <v>0.9463</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40418,7 +40418,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8788</v>
+        <v>0.879</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.057</v>
+        <v>2.0576</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40443,7 +40443,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9881</v>
+        <v>0.9883</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40452,7 +40452,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9262</v>
+        <v>0.9264</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2345</v>
+        <v>2.2353</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9944</v>
+        <v>0.9946</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40486,7 +40486,7 @@
         <v>1.2101</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9405</v>
+        <v>0.9407</v>
       </c>
       <c r="F252" t="n">
         <v>1.2101</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.363</v>
+        <v>2.3638</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40511,7 +40511,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7553</v>
+        <v>0.7554</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40520,7 +40520,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9356</v>
+        <v>0.9358</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3884</v>
+        <v>2.3892</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8848</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9446</v>
+        <v>0.9448</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4966</v>
+        <v>2.4975</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40579,7 +40579,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8464</v>
+        <v>0.8466</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9473</v>
+        <v>0.9476</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5756</v>
+        <v>2.5765</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8247</v>
+        <v>0.8249</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9084</v>
+        <v>0.9086</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5985</v>
+        <v>2.5994</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7548</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40656,7 +40656,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8627</v>
+        <v>0.863</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7275</v>
+        <v>2.7285</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7965</v>
+        <v>0.7967</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9224</v>
+        <v>0.9226</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8807</v>
+        <v>2.8819</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8317</v>
+        <v>0.832</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3187</v>
       </c>
       <c r="E259" t="n">
-        <v>0.96</v>
+        <v>0.9603</v>
       </c>
       <c r="F259" t="n">
         <v>0.3187</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0753</v>
+        <v>3.0766</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9705</v>
+        <v>0.9666</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9705</v>
+        <v>0.9666</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.1174</v>
+        <v>3.1016</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.164</v>
+        <v>1.165</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.4</v>
+        <v>1.397</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.959</v>
+        <v>1.969</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.711</v>
+        <v>2.744</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.883</v>
+        <v>3.91</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.274</v>
+        <v>-0.272</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.912</v>
+        <v>0.946</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.13</v>
+        <v>-1.18</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69604.05499999999</v>
+        <v>69650.727</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.164</v>
+        <v>1.165</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4</v>
+        <v>1.3975</v>
       </c>
       <c r="E260" t="n">
-        <v>1.959</v>
+        <v>1.969</v>
       </c>
       <c r="F260" t="n">
-        <v>2.711</v>
+        <v>2.7445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.883</v>
+        <v>3.91</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8153</v>
+        <v>-0.8143</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2742</v>
+        <v>-0.2725</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9122</v>
+        <v>0.9457</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>69604.05499999999</v>
+        <v>69650.7267</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32258,7 +32258,7 @@
         <v>0.0931</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.633</v>
+        <v>-0.6329</v>
       </c>
       <c r="F10" t="n">
         <v>0.0931</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9365</v>
+        <v>-0.9364</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0579</v>
+        <v>-1.0578</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33720,7 +33720,7 @@
         <v>0.0622</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2344</v>
+        <v>-1.2343</v>
       </c>
       <c r="F53" t="n">
         <v>0.0622</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.9974</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33992,7 +33992,7 @@
         <v>-0.3869</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.3959</v>
+        <v>-1.3958</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3869</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2023</v>
+        <v>-1.2022</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2202</v>
+        <v>-1.2201</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2281</v>
+        <v>-1.228</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3257</v>
+        <v>-1.3256</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34706,7 +34706,7 @@
         <v>0.3265</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8638</v>
+        <v>-0.8637</v>
       </c>
       <c r="F82" t="n">
         <v>0.3265</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3386</v>
+        <v>-1.3385</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2972</v>
+        <v>-1.2971</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3011</v>
+        <v>-1.301</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35330,7 +35330,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9261</v>
+        <v>-0.926</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4986</v>
@@ -35420,7 +35420,7 @@
         <v>0.3913</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2362</v>
+        <v>-0.2361</v>
       </c>
       <c r="F103" t="n">
         <v>0.3913</v>
@@ -36282,7 +36282,7 @@
         <v>0.4759</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1535</v>
+        <v>0.1534</v>
       </c>
       <c r="J128" t="n">
         <v>-0.0375</v>
@@ -38016,7 +38016,7 @@
         <v>0.4553</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1675</v>
+        <v>-0.1676</v>
       </c>
       <c r="J179" t="n">
         <v>1.9402</v>
@@ -38446,7 +38446,7 @@
         <v>0.0009</v>
       </c>
       <c r="E192" t="n">
-        <v>0.2303</v>
+        <v>0.2302</v>
       </c>
       <c r="F192" t="n">
         <v>0.0009</v>
@@ -38480,7 +38480,7 @@
         <v>0.1272</v>
       </c>
       <c r="E193" t="n">
-        <v>0.2353</v>
+        <v>0.2352</v>
       </c>
       <c r="F193" t="n">
         <v>0.1272</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2431</v>
+        <v>0.243</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4039</v>
+        <v>0.4038</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4508</v>
+        <v>0.4507</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -39126,7 +39126,7 @@
         <v>1.4354</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5155</v>
+        <v>0.5154</v>
       </c>
       <c r="F212" t="n">
         <v>1.4354</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8254</v>
+        <v>0.8253</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.9901</v>
+        <v>0.99</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0724</v>
+        <v>1.0723</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39704,7 +39704,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8885</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5941</v>
+        <v>1.594</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7038</v>
+        <v>1.7037</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7871</v>
+        <v>1.787</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8233</v>
+        <v>1.8232</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5812</v>
+        <v>1.5811</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9172</v>
+        <v>1.9171</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40282,7 +40282,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8964</v>
+        <v>0.8963</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40384,7 +40384,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8892</v>
+        <v>0.8891</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8848</v>
+        <v>0.8847</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9476</v>
+        <v>0.9475</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8249</v>
+        <v>0.8248</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7548</v>
+        <v>0.7547</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7285</v>
+        <v>2.7284</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8819</v>
+        <v>2.8818</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9666</v>
+        <v>0.9668</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9666</v>
+        <v>0.9668</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.1016</v>
+        <v>3.1024</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.165</v>
+        <v>1.163</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.397</v>
+        <v>1.395</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.969</v>
+        <v>1.97</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.744</v>
+        <v>2.752</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.272</v>
+        <v>-0.274</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.946</v>
+        <v>0.954</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.18</v>
+        <v>-1.19</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69650.727</v>
+        <v>69672.467</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.165</v>
+        <v>1.163</v>
       </c>
       <c r="D260" t="n">
-        <v>1.3975</v>
+        <v>1.395</v>
       </c>
       <c r="E260" t="n">
-        <v>1.969</v>
+        <v>1.9697</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7445</v>
+        <v>2.7523</v>
       </c>
       <c r="G260" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8143</v>
+        <v>-0.8163</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2725</v>
+        <v>-0.2739</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9457</v>
+        <v>0.9535</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>69650.7267</v>
+        <v>69672.4675</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32406,7 +32406,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2067</v>
+        <v>-0.2066</v>
       </c>
       <c r="J14" t="n">
         <v>-1.1493</v>
@@ -32598,7 +32598,7 @@
         <v>0.0143</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5605</v>
+        <v>-0.5604</v>
       </c>
       <c r="F20" t="n">
         <v>0.0143</v>
@@ -33392,7 +33392,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5209</v>
+        <v>-0.5208</v>
       </c>
       <c r="J43" t="n">
         <v>0.5449000000000001</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3253</v>
+        <v>-1.3252</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3108</v>
+        <v>-1.3107</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -38050,7 +38050,7 @@
         <v>0.4553</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1556</v>
+        <v>-0.1557</v>
       </c>
       <c r="J180" t="n">
         <v>1.9104</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4564</v>
+        <v>0.4563</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3528</v>
+        <v>1.3527</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39738,7 +39738,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.944</v>
+        <v>0.9439</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3848</v>
+        <v>1.3847</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39840,7 +39840,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0121</v>
+        <v>1.012</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.804</v>
+        <v>1.8039</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40316,7 +40316,7 @@
         <v>1.4542</v>
       </c>
       <c r="E247" t="n">
-        <v>0.858</v>
+        <v>0.8579</v>
       </c>
       <c r="F247" t="n">
         <v>1.4542</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9904</v>
+        <v>1.9903</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0766</v>
+        <v>3.0765</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9668</v>
+        <v>0.9669</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9668</v>
+        <v>0.9669</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.1024</v>
+        <v>3.1028</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.967</v>
+        <v>0.966</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.163</v>
+        <v>1.164</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.97</v>
+        <v>1.976</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.752</v>
+        <v>2.77</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.92</v>
+        <v>3.934</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.274</v>
+        <v>-0.272</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.954</v>
+        <v>0.971</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.19</v>
+        <v>-1.21</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69672.467</v>
+        <v>69389.36599999999</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.163</v>
+        <v>1.1637</v>
       </c>
       <c r="D260" t="n">
-        <v>1.395</v>
+        <v>1.3952</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9697</v>
+        <v>1.9758</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7523</v>
+        <v>2.77</v>
       </c>
       <c r="G260" t="n">
-        <v>3.92</v>
+        <v>3.934</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8163</v>
+        <v>-0.8156</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2739</v>
+        <v>-0.2718</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9535</v>
+        <v>0.9712</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>69672.4675</v>
+        <v>69389.36599999999</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32066,7 +32066,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5651</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6448</v>
@@ -32168,7 +32168,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4858</v>
+        <v>-0.4859</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5085</v>
@@ -32236,7 +32236,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4083</v>
+        <v>-0.4084</v>
       </c>
       <c r="J9" t="n">
         <v>-1.39</v>
@@ -32249,7 +32249,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.4877</v>
+        <v>-0.4878</v>
       </c>
       <c r="C10" t="n">
         <v>-0.2832</v>
@@ -32258,7 +32258,7 @@
         <v>0.0931</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6329</v>
+        <v>-0.633</v>
       </c>
       <c r="F10" t="n">
         <v>0.0931</v>
@@ -32304,7 +32304,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2972</v>
+        <v>-0.2973</v>
       </c>
       <c r="J11" t="n">
         <v>-1.282</v>
@@ -32338,7 +32338,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1986</v>
+        <v>-0.1987</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2069</v>
@@ -32372,7 +32372,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1746</v>
+        <v>-0.1747</v>
       </c>
       <c r="J13" t="n">
         <v>-1.1973</v>
@@ -32406,7 +32406,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2066</v>
+        <v>-0.2067</v>
       </c>
       <c r="J14" t="n">
         <v>-1.1493</v>
@@ -32598,7 +32598,7 @@
         <v>0.0143</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5604</v>
+        <v>-0.5605</v>
       </c>
       <c r="F20" t="n">
         <v>0.0143</v>
@@ -32712,7 +32712,7 @@
         <v>0.0999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0378</v>
+        <v>-0.0379</v>
       </c>
       <c r="J23" t="n">
         <v>-0.7148</v>
@@ -32746,7 +32746,7 @@
         <v>0.0999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0435</v>
+        <v>-0.0436</v>
       </c>
       <c r="J24" t="n">
         <v>-0.5606</v>
@@ -33086,7 +33086,7 @@
         <v>-0.221</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>-0.037</v>
@@ -33154,7 +33154,7 @@
         <v>-0.221</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2266</v>
+        <v>-0.2267</v>
       </c>
       <c r="J36" t="n">
         <v>0.0709</v>
@@ -33167,7 +33167,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.385</v>
+        <v>-0.3851</v>
       </c>
       <c r="C37" t="n">
         <v>-0.1966</v>
@@ -33290,7 +33290,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5593</v>
+        <v>-0.5594</v>
       </c>
       <c r="J40" t="n">
         <v>0.3628</v>
@@ -33324,7 +33324,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.556</v>
+        <v>-0.5561</v>
       </c>
       <c r="J41" t="n">
         <v>0.3781</v>
@@ -33358,7 +33358,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5289</v>
+        <v>-0.529</v>
       </c>
       <c r="J42" t="n">
         <v>0.4876</v>
@@ -33392,7 +33392,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5208</v>
+        <v>-0.5209</v>
       </c>
       <c r="J43" t="n">
         <v>0.5449000000000001</v>
@@ -33426,7 +33426,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5612</v>
+        <v>-0.5613</v>
       </c>
       <c r="J44" t="n">
         <v>0.5838</v>
@@ -33460,7 +33460,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5569</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0.7429</v>
@@ -33494,7 +33494,7 @@
         <v>-1.781</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6498</v>
+        <v>-0.6499</v>
       </c>
       <c r="J46" t="n">
         <v>0.7907999999999999</v>
@@ -33516,7 +33516,7 @@
         <v>0.7934</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.9176</v>
+        <v>-0.9177</v>
       </c>
       <c r="F47" t="n">
         <v>0.7934</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9364</v>
+        <v>-0.9365</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0578</v>
+        <v>-1.0579</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1049</v>
+        <v>-1.105</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0242</v>
+        <v>-1.0243</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33711,7 +33711,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.975</v>
+        <v>-0.9751</v>
       </c>
       <c r="C53" t="n">
         <v>0.6286</v>
@@ -33720,7 +33720,7 @@
         <v>0.0622</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2343</v>
+        <v>-1.2344</v>
       </c>
       <c r="F53" t="n">
         <v>0.0622</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9973</v>
+        <v>-0.9974</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33754,7 +33754,7 @@
         <v>-0.3292</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.241</v>
+        <v>-1.2411</v>
       </c>
       <c r="F54" t="n">
         <v>-0.3292</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0233</v>
+        <v>-1.0234</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9974</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33902,7 +33902,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0941</v>
+        <v>-1.0942</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5746</v>
@@ -33992,7 +33992,7 @@
         <v>-0.3869</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.3958</v>
+        <v>-1.3959</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3869</v>
@@ -34004,7 +34004,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.105</v>
+        <v>-1.1051</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1631</v>
@@ -34026,7 +34026,7 @@
         <v>-0.2593</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.4179</v>
+        <v>-1.418</v>
       </c>
       <c r="F62" t="n">
         <v>-0.2593</v>
@@ -34106,7 +34106,7 @@
         <v>-2.117</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0774</v>
+        <v>-1.0775</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6903</v>
@@ -34128,7 +34128,7 @@
         <v>-0.3014</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.3981</v>
+        <v>-1.3982</v>
       </c>
       <c r="F65" t="n">
         <v>-0.3014</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0996</v>
+        <v>-1.0997</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34230,7 +34230,7 @@
         <v>-0.2725</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.3923</v>
+        <v>-1.3924</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2725</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1673</v>
+        <v>-1.1674</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2022</v>
+        <v>-1.2023</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34289,7 +34289,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0624</v>
+        <v>-1.0625</v>
       </c>
       <c r="C70" t="n">
         <v>0.5677</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2201</v>
+        <v>-1.2202</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34366,7 +34366,7 @@
         <v>-0.1495</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.234</v>
+        <v>-1.2341</v>
       </c>
       <c r="F72" t="n">
         <v>-0.1495</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2405</v>
+        <v>-1.2406</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34412,7 +34412,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.202</v>
+        <v>-1.2021</v>
       </c>
       <c r="J73" t="n">
         <v>-1.852</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.228</v>
+        <v>-1.2281</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34468,7 +34468,7 @@
         <v>-0.1831</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1311</v>
+        <v>-1.1312</v>
       </c>
       <c r="F75" t="n">
         <v>-0.1831</v>
@@ -34480,7 +34480,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2181</v>
+        <v>-1.2182</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8065</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2489</v>
+        <v>-1.249</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2159</v>
+        <v>-1.216</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34570,7 +34570,7 @@
         <v>0.1141</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.9683</v>
       </c>
       <c r="F78" t="n">
         <v>0.1141</v>
@@ -34604,7 +34604,7 @@
         <v>0.1235</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9329</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="F79" t="n">
         <v>0.1235</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2777</v>
+        <v>-1.2778</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3256</v>
+        <v>-1.3257</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34706,7 +34706,7 @@
         <v>0.3265</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8637</v>
+        <v>-0.8638</v>
       </c>
       <c r="F82" t="n">
         <v>0.3265</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3418</v>
+        <v>-1.3419</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34740,7 +34740,7 @@
         <v>0.1823</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.8716</v>
       </c>
       <c r="F83" t="n">
         <v>0.1823</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3385</v>
+        <v>-1.3386</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34765,7 +34765,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-0.6528</v>
       </c>
       <c r="C84" t="n">
         <v>0.1093</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3252</v>
+        <v>-1.3253</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3303</v>
+        <v>-1.3304</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34888,7 +34888,7 @@
         <v>-0.573</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3009</v>
+        <v>-1.301</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1278</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2195</v>
+        <v>-1.2196</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.5037</v>
+        <v>-0.5038</v>
       </c>
       <c r="C89" t="n">
         <v>-0.0515</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2971</v>
+        <v>-1.2972</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3032</v>
+        <v>-1.3033</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.301</v>
+        <v>-1.3011</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3107</v>
+        <v>-1.3108</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35160,7 +35160,7 @@
         <v>-0.247</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2977</v>
+        <v>-1.2978</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7848000000000001</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2662</v>
+        <v>-1.2663</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.2015</v>
+        <v>-1.2016</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35309,7 +35309,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2536</v>
+        <v>-0.2537</v>
       </c>
       <c r="C100" t="n">
         <v>-0.3899</v>
@@ -35330,7 +35330,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.926</v>
+        <v>-0.9261</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4986</v>
@@ -35420,7 +35420,7 @@
         <v>0.3913</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2361</v>
+        <v>-0.2362</v>
       </c>
       <c r="F103" t="n">
         <v>0.3913</v>
@@ -35556,7 +35556,7 @@
         <v>0.6536</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.1656</v>
+        <v>-0.1657</v>
       </c>
       <c r="F107" t="n">
         <v>0.6536</v>
@@ -35568,7 +35568,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7107</v>
+        <v>-0.7108</v>
       </c>
       <c r="J107" t="n">
         <v>-0.2576</v>
@@ -35772,7 +35772,7 @@
         <v>0.174</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5446</v>
+        <v>-0.5447</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2332</v>
@@ -35840,7 +35840,7 @@
         <v>0.1975</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5034</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="J115" t="n">
         <v>-0.2476</v>
@@ -35942,7 +35942,7 @@
         <v>0.2561</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3406</v>
+        <v>-0.3407</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1584</v>
@@ -36248,7 +36248,7 @@
         <v>0.4759</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1507</v>
+        <v>0.1508</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0189</v>
@@ -36282,7 +36282,7 @@
         <v>0.4759</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1534</v>
+        <v>0.1535</v>
       </c>
       <c r="J128" t="n">
         <v>-0.0375</v>
@@ -36508,7 +36508,7 @@
         <v>0.4551</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3482</v>
+        <v>0.3481</v>
       </c>
       <c r="F135" t="n">
         <v>0.4551</v>
@@ -36962,7 +36962,7 @@
         <v>0.7911</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0308</v>
+        <v>0.0309</v>
       </c>
       <c r="J148" t="n">
         <v>0.4423</v>
@@ -37145,7 +37145,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.6146</v>
+        <v>0.6147</v>
       </c>
       <c r="C154" t="n">
         <v>0.2567</v>
@@ -37213,7 +37213,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.6343</v>
+        <v>0.6344</v>
       </c>
       <c r="C156" t="n">
         <v>0.2997</v>
@@ -37404,7 +37404,7 @@
         <v>0.8351</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0283</v>
+        <v>0.0284</v>
       </c>
       <c r="J161" t="n">
         <v>1.0307</v>
@@ -37472,7 +37472,7 @@
         <v>0.8315</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0871</v>
+        <v>0.0872</v>
       </c>
       <c r="J163" t="n">
         <v>1.2078</v>
@@ -37553,7 +37553,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.7479</v>
+        <v>0.748</v>
       </c>
       <c r="C166" t="n">
         <v>0.4213</v>
@@ -37574,7 +37574,7 @@
         <v>0.8931</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1432</v>
+        <v>0.1433</v>
       </c>
       <c r="J166" t="n">
         <v>1.2728</v>
@@ -37630,7 +37630,7 @@
         <v>0.8165</v>
       </c>
       <c r="E168" t="n">
-        <v>0.7698</v>
+        <v>0.7699</v>
       </c>
       <c r="F168" t="n">
         <v>0.8165</v>
@@ -37846,7 +37846,7 @@
         <v>0.9594</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0775</v>
+        <v>-0.0774</v>
       </c>
       <c r="J174" t="n">
         <v>1.6762</v>
@@ -38016,7 +38016,7 @@
         <v>0.4553</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1676</v>
+        <v>-0.1675</v>
       </c>
       <c r="J179" t="n">
         <v>1.9402</v>
@@ -38050,7 +38050,7 @@
         <v>0.4553</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1557</v>
+        <v>-0.1556</v>
       </c>
       <c r="J180" t="n">
         <v>1.9104</v>
@@ -38233,7 +38233,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.4719</v>
+        <v>0.472</v>
       </c>
       <c r="C186" t="n">
         <v>0.6338</v>
@@ -38254,7 +38254,7 @@
         <v>-0.4422</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2553</v>
+        <v>-0.2552</v>
       </c>
       <c r="J186" t="n">
         <v>2.1834</v>
@@ -38378,7 +38378,7 @@
         <v>0.2578</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3121</v>
+        <v>0.3122</v>
       </c>
       <c r="F190" t="n">
         <v>0.2578</v>
@@ -38446,7 +38446,7 @@
         <v>0.0009</v>
       </c>
       <c r="E192" t="n">
-        <v>0.2302</v>
+        <v>0.2303</v>
       </c>
       <c r="F192" t="n">
         <v>0.0009</v>
@@ -38458,7 +38458,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0378</v>
+        <v>-0.0377</v>
       </c>
       <c r="J192" t="n">
         <v>1.0409</v>
@@ -38480,7 +38480,7 @@
         <v>0.1272</v>
       </c>
       <c r="E193" t="n">
-        <v>0.2352</v>
+        <v>0.2353</v>
       </c>
       <c r="F193" t="n">
         <v>0.1272</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0005</v>
+        <v>-0.0004</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.064</v>
+        <v>0.0641</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38548,7 +38548,7 @@
         <v>0.1957</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1485</v>
+        <v>0.1486</v>
       </c>
       <c r="F195" t="n">
         <v>0.1957</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1269</v>
+        <v>0.127</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1988</v>
+        <v>0.1989</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.243</v>
+        <v>0.2431</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2502</v>
+        <v>0.2503</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38684,7 +38684,7 @@
         <v>0.2053</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
       <c r="F199" t="n">
         <v>0.2053</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2973</v>
+        <v>0.2974</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38709,7 +38709,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.1136</v>
+        <v>0.1137</v>
       </c>
       <c r="C200" t="n">
         <v>-0.1771</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3038</v>
+        <v>0.3039</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38752,7 +38752,7 @@
         <v>0.4293</v>
       </c>
       <c r="E201" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="F201" t="n">
         <v>0.4293</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3175</v>
+        <v>0.3176</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4038</v>
+        <v>0.4039</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4163</v>
+        <v>0.4164</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4507</v>
+        <v>0.4508</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -38888,7 +38888,7 @@
         <v>1.7557</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2673</v>
+        <v>0.2674</v>
       </c>
       <c r="F205" t="n">
         <v>1.7557</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4563</v>
+        <v>0.4564</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38968,7 +38968,7 @@
         <v>0.2178</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4622</v>
+        <v>0.4623</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2897</v>
@@ -39015,7 +39015,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.6049</v>
+        <v>0.605</v>
       </c>
       <c r="C209" t="n">
         <v>-0.5758</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6349</v>
+        <v>0.635</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6823</v>
+        <v>0.6824</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39083,7 +39083,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.68</v>
+        <v>0.6801</v>
       </c>
       <c r="C211" t="n">
         <v>-0.7048</v>
@@ -39117,7 +39117,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.6994</v>
+        <v>0.6995</v>
       </c>
       <c r="C212" t="n">
         <v>-0.7396</v>
@@ -39126,7 +39126,7 @@
         <v>1.4354</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5154</v>
+        <v>0.5155</v>
       </c>
       <c r="F212" t="n">
         <v>1.4354</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8152</v>
+        <v>0.8153</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8383</v>
+        <v>0.8384</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39194,7 +39194,7 @@
         <v>1.7312</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6312</v>
+        <v>0.6313</v>
       </c>
       <c r="F214" t="n">
         <v>1.7312</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9419</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39228,7 +39228,7 @@
         <v>1.8946</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6451</v>
+        <v>0.6452</v>
       </c>
       <c r="F215" t="n">
         <v>1.8946</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0123</v>
+        <v>1.0124</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39253,7 +39253,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8825</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="C216" t="n">
         <v>-0.9258</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9522</v>
+        <v>0.9523</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8253</v>
+        <v>0.8254</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8451</v>
+        <v>0.8452</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9456</v>
+        <v>0.9457</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.99</v>
+        <v>0.9901</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0723</v>
+        <v>1.0724</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39534,7 +39534,7 @@
         <v>1.6966</v>
       </c>
       <c r="E224" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.803</v>
       </c>
       <c r="F224" t="n">
         <v>1.6966</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0911</v>
+        <v>1.0912</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1802</v>
+        <v>1.1803</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2498</v>
+        <v>1.2499</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39627,7 +39627,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.9919</v>
+        <v>0.992</v>
       </c>
       <c r="C227" t="n">
         <v>-1.4189</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2799</v>
+        <v>1.28</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3527</v>
+        <v>1.3529</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39695,7 +39695,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1.001</v>
+        <v>1.0011</v>
       </c>
       <c r="C229" t="n">
         <v>-1.3839</v>
@@ -39704,7 +39704,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8885</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2806</v>
+        <v>1.2807</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39738,7 +39738,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9439</v>
+        <v>0.944</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3847</v>
+        <v>1.3849</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.528</v>
+        <v>1.5281</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39806,7 +39806,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0129</v>
+        <v>1.013</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.594</v>
+        <v>1.5942</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39840,7 +39840,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.012</v>
+        <v>1.0121</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.657</v>
+        <v>1.6571</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7037</v>
+        <v>1.7039</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.787</v>
+        <v>1.7872</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39933,7 +39933,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0926</v>
+        <v>1.0927</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8232</v>
+        <v>1.8234</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0307</v>
+        <v>1.0308</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.595</v>
+        <v>1.5951</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5811</v>
+        <v>1.5813</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40035,7 +40035,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.007</v>
+        <v>1.0071</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7467</v>
+        <v>1.7469</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8236</v>
+        <v>1.8238</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40103,7 +40103,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0315</v>
+        <v>1.0316</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40112,7 +40112,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9663</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8434</v>
+        <v>1.8435</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40137,7 +40137,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0417</v>
+        <v>1.0418</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9171</v>
+        <v>1.9173</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8502</v>
+        <v>1.8503</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40205,7 +40205,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.0308</v>
+        <v>1.0309</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8039</v>
+        <v>1.8041</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6769</v>
+        <v>1.677</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40273,7 +40273,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.033</v>
+        <v>1.0331</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40282,7 +40282,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8963</v>
+        <v>0.8964</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7746</v>
+        <v>1.7748</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40316,7 +40316,7 @@
         <v>1.4542</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8579</v>
+        <v>0.858</v>
       </c>
       <c r="F247" t="n">
         <v>1.4542</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8048</v>
+        <v>1.8049</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9222</v>
+        <v>1.9223</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40384,7 +40384,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8891</v>
+        <v>0.8892</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9903</v>
+        <v>1.9905</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40409,7 +40409,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9463</v>
+        <v>0.9464</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40418,7 +40418,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.879</v>
+        <v>0.8791</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0576</v>
+        <v>2.0578</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40452,7 +40452,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9264</v>
+        <v>0.9265</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2353</v>
+        <v>2.2355</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3638</v>
+        <v>2.364</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40511,7 +40511,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7554</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40520,7 +40520,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9358</v>
+        <v>0.9359</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3892</v>
+        <v>2.3894</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8847</v>
+        <v>0.8848</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9448</v>
+        <v>0.9449</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4975</v>
+        <v>2.4978</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9475</v>
+        <v>0.9476</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5765</v>
+        <v>2.5768</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8248</v>
+        <v>0.8249</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9086</v>
+        <v>0.9087</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5994</v>
+        <v>2.5997</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7547</v>
+        <v>0.7548</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7284</v>
+        <v>2.7287</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7967</v>
+        <v>0.7968</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9226</v>
+        <v>0.9227</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8818</v>
+        <v>2.8822</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.832</v>
+        <v>0.8321</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3187</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9603</v>
+        <v>0.9604</v>
       </c>
       <c r="F259" t="n">
         <v>0.3187</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0765</v>
+        <v>3.0769</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9669</v>
+        <v>0.9656</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9669</v>
+        <v>0.9656</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.1028</v>
+        <v>3.0976</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.97</t>
+          <t>+0.96</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.97 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.96 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>-1.144</v>
+        <v>-1.145</v>
       </c>
     </row>
     <row r="68">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>0.863</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="220">
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="254">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.966</v>
+        <v>0.964</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.164</v>
+        <v>1.165</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.395</v>
+        <v>1.397</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.976</v>
+        <v>1.982</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.77</v>
+        <v>2.783</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.934</v>
+        <v>3.937</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.272</v>
+        <v>-0.269</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.971</v>
+        <v>0.984</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.21</v>
+        <v>-1.23</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69389.36599999999</v>
+        <v>68960.98</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1637</v>
+        <v>1.1646</v>
       </c>
       <c r="D260" t="n">
-        <v>1.3952</v>
+        <v>1.3966</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9758</v>
+        <v>1.982</v>
       </c>
       <c r="F260" t="n">
-        <v>2.77</v>
+        <v>2.7828</v>
       </c>
       <c r="G260" t="n">
-        <v>3.934</v>
+        <v>3.9374</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8156</v>
+        <v>-0.8147</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2718</v>
+        <v>-0.2688</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9712</v>
+        <v>0.984</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>69389.36599999999</v>
+        <v>68960.98</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32004,7 +32004,7 @@
         <v>-0.3417</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6423</v>
+        <v>-0.6424</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7141</v>
@@ -32023,7 +32023,7 @@
         <v>0.1079</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8479</v>
+        <v>-0.848</v>
       </c>
       <c r="F3" t="n">
         <v>0.1079</v>
@@ -32032,7 +32032,7 @@
         <v>-0.3193</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5885</v>
+        <v>-0.5886</v>
       </c>
       <c r="J3" t="n">
         <v>-1.636</v>
@@ -32066,7 +32066,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5651</v>
+        <v>-0.5652</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6448</v>
@@ -32088,7 +32088,7 @@
         <v>0.2213</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7248</v>
+        <v>-0.7249</v>
       </c>
       <c r="F5" t="n">
         <v>0.2213</v>
@@ -32100,7 +32100,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5436</v>
+        <v>-0.5437</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5114</v>
@@ -32122,7 +32122,7 @@
         <v>0.2701</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7022</v>
+        <v>-0.7023</v>
       </c>
       <c r="F6" t="n">
         <v>0.2701</v>
@@ -32134,7 +32134,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.5329</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4181</v>
@@ -32168,7 +32168,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4859</v>
+        <v>-0.486</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5085</v>
@@ -32202,7 +32202,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4052</v>
+        <v>-0.4053</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3584</v>
@@ -32236,7 +32236,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4084</v>
+        <v>-0.4085</v>
       </c>
       <c r="J9" t="n">
         <v>-1.39</v>
@@ -32270,7 +32270,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3828</v>
+        <v>-0.3829</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2447</v>
@@ -32292,7 +32292,7 @@
         <v>0.1045</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6462</v>
+        <v>-0.6463</v>
       </c>
       <c r="F11" t="n">
         <v>0.1045</v>
@@ -32419,7 +32419,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.4551</v>
+        <v>-0.4552</v>
       </c>
       <c r="C15" t="n">
         <v>-0.4095</v>
@@ -32428,7 +32428,7 @@
         <v>0.1065</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5955</v>
+        <v>-0.5956</v>
       </c>
       <c r="F15" t="n">
         <v>0.1065</v>
@@ -32474,7 +32474,7 @@
         <v>-0.0989</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1468</v>
+        <v>-0.1469</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0218</v>
@@ -32521,7 +32521,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.4752</v>
+        <v>-0.4753</v>
       </c>
       <c r="C18" t="n">
         <v>-0.5001</v>
@@ -32542,7 +32542,7 @@
         <v>-0.0989</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2054</v>
+        <v>-0.2055</v>
       </c>
       <c r="J18" t="n">
         <v>-0.9851</v>
@@ -32610,7 +32610,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1335</v>
+        <v>-0.1336</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8238</v>
@@ -32623,7 +32623,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.419</v>
+        <v>-0.4191</v>
       </c>
       <c r="C21" t="n">
         <v>-0.3155</v>
@@ -32666,7 +32666,7 @@
         <v>0.1099</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4846</v>
+        <v>-0.4847</v>
       </c>
       <c r="F22" t="n">
         <v>0.1099</v>
@@ -33176,7 +33176,7 @@
         <v>0.4873</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6031</v>
+        <v>-0.6032</v>
       </c>
       <c r="F37" t="n">
         <v>0.4873</v>
@@ -33210,7 +33210,7 @@
         <v>0.4015</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.6437</v>
       </c>
       <c r="F38" t="n">
         <v>0.4015</v>
@@ -33222,7 +33222,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3698</v>
+        <v>-0.3699</v>
       </c>
       <c r="J38" t="n">
         <v>0.2133</v>
@@ -33256,7 +33256,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4162</v>
+        <v>-0.4163</v>
       </c>
       <c r="J39" t="n">
         <v>0.2403</v>
@@ -33312,7 +33312,7 @@
         <v>0.4139</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7567</v>
       </c>
       <c r="F41" t="n">
         <v>0.4139</v>
@@ -33371,7 +33371,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.498</v>
+        <v>-0.4981</v>
       </c>
       <c r="C43" t="n">
         <v>-0.2708</v>
@@ -33507,7 +33507,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.5754</v>
+        <v>-0.5755</v>
       </c>
       <c r="C47" t="n">
         <v>-0.3486</v>
@@ -33528,7 +33528,7 @@
         <v>-1.781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.8545</v>
       </c>
       <c r="J47" t="n">
         <v>0.7421</v>
@@ -33550,7 +33550,7 @@
         <v>0.4548</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.9103</v>
+        <v>-0.9104</v>
       </c>
       <c r="F48" t="n">
         <v>0.4548</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9365</v>
+        <v>-0.9366</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0579</v>
+        <v>-1.058</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.105</v>
+        <v>-1.1051</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1173</v>
+        <v>-1.1175</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33677,7 +33677,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.9351</v>
       </c>
       <c r="C52" t="n">
         <v>0.4357</v>
@@ -33686,7 +33686,7 @@
         <v>0.0702</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1863</v>
+        <v>-1.1864</v>
       </c>
       <c r="F52" t="n">
         <v>0.0702</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0243</v>
+        <v>-1.0244</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9974</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0234</v>
+        <v>-1.0235</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -33779,7 +33779,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1591</v>
+        <v>-1.1592</v>
       </c>
       <c r="C55" t="n">
         <v>1.0633</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.9976</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33813,7 +33813,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.247</v>
+        <v>-1.2471</v>
       </c>
       <c r="C56" t="n">
         <v>1.0216</v>
@@ -33834,7 +33834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0538</v>
+        <v>-1.0539</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2426</v>
@@ -33847,7 +33847,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2977</v>
+        <v>-1.2978</v>
       </c>
       <c r="C57" t="n">
         <v>1.0128</v>
@@ -33868,7 +33868,7 @@
         <v>-2.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0153</v>
+        <v>-1.0154</v>
       </c>
       <c r="J57" t="n">
         <v>-0.437</v>
@@ -33881,7 +33881,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.2469</v>
+        <v>-1.247</v>
       </c>
       <c r="C58" t="n">
         <v>0.9933</v>
@@ -33902,7 +33902,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0942</v>
+        <v>-1.0943</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5746</v>
@@ -33915,7 +33915,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.2841</v>
+        <v>-1.2842</v>
       </c>
       <c r="C59" t="n">
         <v>0.9619</v>
@@ -33924,7 +33924,7 @@
         <v>-0.8113</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4023</v>
+        <v>-1.4024</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8113</v>
@@ -33936,7 +33936,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1093</v>
+        <v>-1.1094</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8135</v>
@@ -33970,7 +33970,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1246</v>
+        <v>-1.1247</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -34004,7 +34004,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1051</v>
+        <v>-1.1052</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1631</v>
@@ -34038,7 +34038,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.069</v>
+        <v>-1.0691</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3324</v>
@@ -34072,7 +34072,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0988</v>
+        <v>-1.0989</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4556</v>
@@ -34085,7 +34085,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1628</v>
+        <v>-1.1629</v>
       </c>
       <c r="C64" t="n">
         <v>0.6857</v>
@@ -34106,7 +34106,7 @@
         <v>-2.117</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0775</v>
+        <v>-1.0776</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6903</v>
@@ -34140,7 +34140,7 @@
         <v>-2.117</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.036</v>
+        <v>-1.0361</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8128</v>
@@ -34162,7 +34162,7 @@
         <v>-0.2077</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.4312</v>
+        <v>-1.4313</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2077</v>
@@ -34174,7 +34174,7 @@
         <v>-2.117</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0781</v>
+        <v>-1.0782</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9613</v>
@@ -34196,7 +34196,7 @@
         <v>-0.1867</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.3839</v>
+        <v>-1.384</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1867</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0997</v>
+        <v>-1.0998</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1674</v>
+        <v>-1.1675</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34255,7 +34255,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1505</v>
+        <v>-1.1506</v>
       </c>
       <c r="C69" t="n">
         <v>0.5633</v>
@@ -34264,7 +34264,7 @@
         <v>-0.261</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.3729</v>
+        <v>-1.373</v>
       </c>
       <c r="F69" t="n">
         <v>-0.261</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2023</v>
+        <v>-1.2024</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2202</v>
+        <v>-1.2203</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34323,7 +34323,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0189</v>
+        <v>-1.019</v>
       </c>
       <c r="C71" t="n">
         <v>0.5209</v>
@@ -34344,7 +34344,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2536</v>
+        <v>-1.2538</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9205</v>
@@ -34357,7 +34357,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0171</v>
+        <v>-1.0172</v>
       </c>
       <c r="C72" t="n">
         <v>0.5194</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2406</v>
+        <v>-1.2407</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34391,7 +34391,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.9532</v>
       </c>
       <c r="C73" t="n">
         <v>0.4411</v>
@@ -34412,7 +34412,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2021</v>
+        <v>-1.2022</v>
       </c>
       <c r="J73" t="n">
         <v>-1.852</v>
@@ -34434,7 +34434,7 @@
         <v>-0.1678</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1585</v>
+        <v>-1.1586</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1678</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2281</v>
+        <v>-1.2282</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34459,7 +34459,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9415</v>
+        <v>-0.9416</v>
       </c>
       <c r="C75" t="n">
         <v>0.3874</v>
@@ -34480,7 +34480,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2182</v>
+        <v>-1.2183</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8065</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.249</v>
+        <v>-1.2491</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.216</v>
+        <v>-1.2161</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34582,7 +34582,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2554</v>
+        <v>-1.2555</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6257</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2778</v>
+        <v>-1.2779</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34638,7 +34638,7 @@
         <v>0.2639</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.9217</v>
+        <v>-0.9218</v>
       </c>
       <c r="F80" t="n">
         <v>0.2639</v>
@@ -34650,7 +34650,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2784</v>
+        <v>-1.2785</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5104</v>
@@ -34663,7 +34663,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.6669</v>
+        <v>-0.667</v>
       </c>
       <c r="C81" t="n">
         <v>0.2028</v>
@@ -34672,7 +34672,7 @@
         <v>0.3202</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.9137</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="F81" t="n">
         <v>0.3202</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3257</v>
+        <v>-1.3258</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3419</v>
+        <v>-1.342</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3386</v>
+        <v>-1.3387</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3253</v>
+        <v>-1.3254</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3304</v>
+        <v>-1.3305</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34842,7 +34842,7 @@
         <v>0.2368</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7902</v>
+        <v>-0.7903</v>
       </c>
       <c r="F86" t="n">
         <v>0.2368</v>
@@ -34854,7 +34854,7 @@
         <v>-0.573</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3529</v>
+        <v>-1.3531</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1193</v>
@@ -34867,7 +34867,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5579</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="C87" t="n">
         <v>0.0584</v>
@@ -34888,7 +34888,7 @@
         <v>-0.573</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.301</v>
+        <v>-1.3011</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1278</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2196</v>
+        <v>-1.2197</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -34944,7 +34944,7 @@
         <v>0.3382</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7143</v>
       </c>
       <c r="F89" t="n">
         <v>0.3382</v>
@@ -34956,7 +34956,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2431</v>
+        <v>-1.2432</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0865</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2972</v>
+        <v>-1.2973</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35012,7 +35012,7 @@
         <v>0.1763</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6503</v>
+        <v>-0.6504</v>
       </c>
       <c r="F91" t="n">
         <v>0.1763</v>
@@ -35024,7 +35024,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2993</v>
+        <v>-1.2995</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9396</v>
@@ -35046,7 +35046,7 @@
         <v>0.1334</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.6227</v>
+        <v>-0.6228</v>
       </c>
       <c r="F92" t="n">
         <v>0.1334</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3033</v>
+        <v>-1.3034</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3011</v>
+        <v>-1.3012</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3108</v>
+        <v>-1.3109</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35160,7 +35160,7 @@
         <v>-0.247</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2978</v>
+        <v>-1.2979</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7848000000000001</v>
@@ -35182,7 +35182,7 @@
         <v>0.2773</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.4913</v>
+        <v>-0.4914</v>
       </c>
       <c r="F96" t="n">
         <v>0.2773</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2663</v>
+        <v>-1.2664</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35216,7 +35216,7 @@
         <v>0.589</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.4426</v>
+        <v>-0.4427</v>
       </c>
       <c r="F97" t="n">
         <v>0.589</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.2016</v>
+        <v>-1.2017</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35262,7 +35262,7 @@
         <v>-0.201</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0631</v>
+        <v>-1.0632</v>
       </c>
       <c r="J98" t="n">
         <v>-0.615</v>
@@ -35296,7 +35296,7 @@
         <v>-0.201</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9752999999999999</v>
+        <v>-0.9754</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5022</v>
@@ -35330,7 +35330,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9261</v>
+        <v>-0.9262</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4986</v>
@@ -35364,7 +35364,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.8393</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4122</v>
@@ -35432,7 +35432,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8178</v>
+        <v>-0.8179</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3535</v>
@@ -35466,7 +35466,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7259</v>
+        <v>-0.726</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2313</v>
@@ -35479,7 +35479,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0362</v>
+        <v>-0.0363</v>
       </c>
       <c r="C105" t="n">
         <v>-0.5632</v>
@@ -35500,7 +35500,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7664</v>
+        <v>-0.7665</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2434</v>
@@ -35602,7 +35602,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6501</v>
+        <v>-0.6502</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2887</v>
@@ -35683,7 +35683,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.115</v>
+        <v>0.1149</v>
       </c>
       <c r="C111" t="n">
         <v>-0.7007</v>
@@ -35738,7 +35738,7 @@
         <v>0.174</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5492</v>
+        <v>-0.5493</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2387</v>
@@ -35806,7 +35806,7 @@
         <v>0.174</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5216</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2168</v>
@@ -36270,7 +36270,7 @@
         <v>0.295</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3159</v>
+        <v>0.316</v>
       </c>
       <c r="F128" t="n">
         <v>0.295</v>
@@ -36316,7 +36316,7 @@
         <v>0.4759</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1446</v>
+        <v>0.1447</v>
       </c>
       <c r="J129" t="n">
         <v>-0.0706</v>
@@ -36372,7 +36372,7 @@
         <v>0.2226</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3264</v>
+        <v>0.3265</v>
       </c>
       <c r="F131" t="n">
         <v>0.2226</v>
@@ -36690,7 +36690,7 @@
         <v>0.7799</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1953</v>
+        <v>-0.1954</v>
       </c>
       <c r="J140" t="n">
         <v>0.1265</v>
@@ -36860,7 +36860,7 @@
         <v>0.7738</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0573</v>
+        <v>0.0574</v>
       </c>
       <c r="J145" t="n">
         <v>0.4385</v>
@@ -37064,7 +37064,7 @@
         <v>0.8136</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0045</v>
+        <v>0.0046</v>
       </c>
       <c r="J151" t="n">
         <v>0.5768</v>
@@ -37098,7 +37098,7 @@
         <v>0.8136</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0423</v>
+        <v>0.0424</v>
       </c>
       <c r="J152" t="n">
         <v>0.7073</v>
@@ -37166,7 +37166,7 @@
         <v>0.8182</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0143</v>
+        <v>0.0144</v>
       </c>
       <c r="J154" t="n">
         <v>0.7322</v>
@@ -37200,7 +37200,7 @@
         <v>0.8182</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0871</v>
+        <v>0.0872</v>
       </c>
       <c r="J155" t="n">
         <v>0.8493000000000001</v>
@@ -37234,7 +37234,7 @@
         <v>0.8182</v>
       </c>
       <c r="I156" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0992</v>
       </c>
       <c r="J156" t="n">
         <v>0.7732</v>
@@ -37268,7 +37268,7 @@
         <v>0.7964</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1241</v>
+        <v>0.1242</v>
       </c>
       <c r="J157" t="n">
         <v>0.8111</v>
@@ -37290,7 +37290,7 @@
         <v>0.7731</v>
       </c>
       <c r="E158" t="n">
-        <v>0.6452</v>
+        <v>0.6453</v>
       </c>
       <c r="F158" t="n">
         <v>0.7731</v>
@@ -37302,7 +37302,7 @@
         <v>0.7964</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1034</v>
+        <v>0.1035</v>
       </c>
       <c r="J158" t="n">
         <v>1.0058</v>
@@ -37324,7 +37324,7 @@
         <v>0.8692</v>
       </c>
       <c r="E159" t="n">
-        <v>0.6015</v>
+        <v>0.6016</v>
       </c>
       <c r="F159" t="n">
         <v>0.8692</v>
@@ -37336,7 +37336,7 @@
         <v>0.7964</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0379</v>
+        <v>0.038</v>
       </c>
       <c r="J159" t="n">
         <v>0.9164</v>
@@ -37370,7 +37370,7 @@
         <v>0.8351</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.006</v>
+        <v>-0.0059</v>
       </c>
       <c r="J160" t="n">
         <v>1.0232</v>
@@ -37438,7 +37438,7 @@
         <v>0.8351</v>
       </c>
       <c r="I162" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0847</v>
       </c>
       <c r="J162" t="n">
         <v>1.1074</v>
@@ -37494,7 +37494,7 @@
         <v>0.7725</v>
       </c>
       <c r="E164" t="n">
-        <v>0.7022</v>
+        <v>0.7023</v>
       </c>
       <c r="F164" t="n">
         <v>0.7725</v>
@@ -37506,7 +37506,7 @@
         <v>0.8315</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1132</v>
+        <v>0.1133</v>
       </c>
       <c r="J164" t="n">
         <v>1.2107</v>
@@ -37540,7 +37540,7 @@
         <v>0.8315</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1026</v>
+        <v>0.1027</v>
       </c>
       <c r="J165" t="n">
         <v>1.3214</v>
@@ -37608,7 +37608,7 @@
         <v>0.8931</v>
       </c>
       <c r="I167" t="n">
-        <v>0.113</v>
+        <v>0.1131</v>
       </c>
       <c r="J167" t="n">
         <v>1.3898</v>
@@ -37676,7 +37676,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0457</v>
+        <v>0.0458</v>
       </c>
       <c r="J169" t="n">
         <v>1.4197</v>
@@ -37732,7 +37732,7 @@
         <v>0.7526</v>
       </c>
       <c r="E171" t="n">
-        <v>0.7379</v>
+        <v>0.738</v>
       </c>
       <c r="F171" t="n">
         <v>0.7526</v>
@@ -37744,7 +37744,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0211</v>
+        <v>-0.021</v>
       </c>
       <c r="J171" t="n">
         <v>1.5073</v>
@@ -37812,7 +37812,7 @@
         <v>0.9594</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0141</v>
+        <v>-0.014</v>
       </c>
       <c r="J173" t="n">
         <v>1.6146</v>
@@ -37859,7 +37859,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.7813</v>
+        <v>0.7814</v>
       </c>
       <c r="C175" t="n">
         <v>0.6141</v>
@@ -37880,7 +37880,7 @@
         <v>0.9559</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.123</v>
+        <v>-0.1229</v>
       </c>
       <c r="J175" t="n">
         <v>1.8105</v>
@@ -37970,7 +37970,7 @@
         <v>0.6795</v>
       </c>
       <c r="E178" t="n">
-        <v>0.6835</v>
+        <v>0.6836</v>
       </c>
       <c r="F178" t="n">
         <v>0.6795</v>
@@ -38029,7 +38029,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="C180" t="n">
         <v>0.6850000000000001</v>
@@ -38038,7 +38038,7 @@
         <v>0.6763</v>
       </c>
       <c r="E180" t="n">
-        <v>0.6758</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="F180" t="n">
         <v>0.6763</v>
@@ -38050,7 +38050,7 @@
         <v>0.4553</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1556</v>
+        <v>-0.1555</v>
       </c>
       <c r="J180" t="n">
         <v>1.9104</v>
@@ -38084,7 +38084,7 @@
         <v>0.0902</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.148</v>
+        <v>-0.1479</v>
       </c>
       <c r="J181" t="n">
         <v>1.9524</v>
@@ -38106,7 +38106,7 @@
         <v>0.7829</v>
       </c>
       <c r="E182" t="n">
-        <v>0.616</v>
+        <v>0.6161</v>
       </c>
       <c r="F182" t="n">
         <v>0.7829</v>
@@ -38118,7 +38118,7 @@
         <v>0.0902</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1758</v>
+        <v>-0.1757</v>
       </c>
       <c r="J182" t="n">
         <v>2.0487</v>
@@ -38140,7 +38140,7 @@
         <v>0.7168</v>
       </c>
       <c r="E183" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.6458</v>
       </c>
       <c r="F183" t="n">
         <v>0.7168</v>
@@ -38152,7 +38152,7 @@
         <v>0.0902</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1914</v>
+        <v>-0.1913</v>
       </c>
       <c r="J183" t="n">
         <v>2.1734</v>
@@ -38322,7 +38322,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1689</v>
+        <v>-0.1688</v>
       </c>
       <c r="J188" t="n">
         <v>2.0124</v>
@@ -38356,7 +38356,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1325</v>
+        <v>-0.1324</v>
       </c>
       <c r="J189" t="n">
         <v>1.7736</v>
@@ -38390,7 +38390,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1242</v>
+        <v>-0.1241</v>
       </c>
       <c r="J190" t="n">
         <v>1.5322</v>
@@ -38424,7 +38424,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0835</v>
       </c>
       <c r="J191" t="n">
         <v>1.307</v>
@@ -38471,7 +38471,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2136</v>
+        <v>0.2137</v>
       </c>
       <c r="C193" t="n">
         <v>0.2348</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0004</v>
+        <v>-0.0003</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0641</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.127</v>
+        <v>0.1271</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38582,7 +38582,7 @@
         <v>0.2432</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1628</v>
+        <v>0.1629</v>
       </c>
       <c r="F196" t="n">
         <v>0.2432</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1989</v>
+        <v>0.199</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38607,7 +38607,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.1308</v>
+        <v>0.1309</v>
       </c>
       <c r="C197" t="n">
         <v>-0.0422</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2431</v>
+        <v>0.2433</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2503</v>
+        <v>0.2504</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38675,7 +38675,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0721</v>
+        <v>0.0722</v>
       </c>
       <c r="C199" t="n">
         <v>-0.0964</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2974</v>
+        <v>0.2975</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3039</v>
+        <v>0.304</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38743,7 +38743,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.1442</v>
+        <v>0.1443</v>
       </c>
       <c r="C201" t="n">
         <v>-0.2562</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3176</v>
+        <v>0.3177</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38786,7 +38786,7 @@
         <v>0.4635</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2107</v>
+        <v>0.2108</v>
       </c>
       <c r="F202" t="n">
         <v>0.4635</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4039</v>
+        <v>0.4041</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38820,7 +38820,7 @@
         <v>0.5004999999999999</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1706</v>
+        <v>0.1707</v>
       </c>
       <c r="F203" t="n">
         <v>0.5004999999999999</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4164</v>
+        <v>0.4165</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4508</v>
+        <v>0.451</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -38879,7 +38879,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5651</v>
       </c>
       <c r="C205" t="n">
         <v>-0.4359</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4564</v>
+        <v>0.4566</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38934,7 +38934,7 @@
         <v>0.2178</v>
       </c>
       <c r="I206" t="n">
-        <v>0.447</v>
+        <v>0.4472</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2505</v>
@@ -38956,7 +38956,7 @@
         <v>0.6433</v>
       </c>
       <c r="E207" t="n">
-        <v>0.2989</v>
+        <v>0.299</v>
       </c>
       <c r="F207" t="n">
         <v>0.6433</v>
@@ -38968,7 +38968,7 @@
         <v>0.2178</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4623</v>
+        <v>0.4624</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2897</v>
@@ -39002,7 +39002,7 @@
         <v>0.4029</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4924</v>
+        <v>0.4926</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2483</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.635</v>
+        <v>0.6351</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39058,7 +39058,7 @@
         <v>1.2949</v>
       </c>
       <c r="E210" t="n">
-        <v>0.4302</v>
+        <v>0.4303</v>
       </c>
       <c r="F210" t="n">
         <v>1.2949</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6824</v>
+        <v>0.6825</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7782</v>
+        <v>0.7783</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8153</v>
+        <v>0.8154</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8384</v>
+        <v>0.8385</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39185,7 +39185,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.8512</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="C214" t="n">
         <v>-0.7835</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9421</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39219,7 +39219,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.895</v>
+        <v>0.8951</v>
       </c>
       <c r="C215" t="n">
         <v>-0.8632</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0124</v>
+        <v>1.0125</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9523</v>
+        <v>0.9524</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39287,7 +39287,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.8215</v>
+        <v>0.8216</v>
       </c>
       <c r="C217" t="n">
         <v>-0.9187</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8217</v>
+        <v>0.8218</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39342,7 +39342,7 @@
         <v>0.7019</v>
       </c>
       <c r="I218" t="n">
-        <v>0.751</v>
+        <v>0.7511</v>
       </c>
       <c r="J218" t="n">
         <v>0.1401</v>
@@ -39364,7 +39364,7 @@
         <v>1.6761</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6603</v>
+        <v>0.6604</v>
       </c>
       <c r="F219" t="n">
         <v>1.6761</v>
@@ -39376,7 +39376,7 @@
         <v>0.7019</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8233</v>
+        <v>0.8235</v>
       </c>
       <c r="J219" t="n">
         <v>0.2448</v>
@@ -39389,7 +39389,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.9143</v>
+        <v>0.9144</v>
       </c>
       <c r="C220" t="n">
         <v>-1.2201</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8254</v>
+        <v>0.8255</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8452</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39466,7 +39466,7 @@
         <v>1.724</v>
       </c>
       <c r="E222" t="n">
-        <v>0.7361</v>
+        <v>0.7362</v>
       </c>
       <c r="F222" t="n">
         <v>1.724</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9457</v>
+        <v>0.9458</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39500,7 +39500,7 @@
         <v>1.7742</v>
       </c>
       <c r="E223" t="n">
-        <v>0.794</v>
+        <v>0.7941</v>
       </c>
       <c r="F223" t="n">
         <v>1.7742</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0724</v>
+        <v>1.0726</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0912</v>
+        <v>1.0914</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1803</v>
+        <v>1.1805</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39602,7 +39602,7 @@
         <v>1.477</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8602</v>
+        <v>0.8603</v>
       </c>
       <c r="F226" t="n">
         <v>1.477</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2499</v>
+        <v>1.2501</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39636,7 +39636,7 @@
         <v>1.5257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8585</v>
+        <v>0.8586</v>
       </c>
       <c r="F227" t="n">
         <v>1.5257</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.28</v>
+        <v>1.2801</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39661,7 +39661,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9721</v>
+        <v>0.9722</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39670,7 +39670,7 @@
         <v>1.3813</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8698</v>
+        <v>0.8699</v>
       </c>
       <c r="F228" t="n">
         <v>1.3813</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3529</v>
+        <v>1.353</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2807</v>
+        <v>1.2809</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39729,7 +39729,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.99</v>
+        <v>0.9901</v>
       </c>
       <c r="C230" t="n">
         <v>-1.8168</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3849</v>
+        <v>1.3851</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39763,7 +39763,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0651</v>
+        <v>1.0652</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -39772,7 +39772,7 @@
         <v>1.4899</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9589</v>
+        <v>0.959</v>
       </c>
       <c r="F231" t="n">
         <v>1.4899</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5281</v>
+        <v>1.5284</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39797,7 +39797,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.087</v>
+        <v>1.0871</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5942</v>
+        <v>1.5945</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39831,7 +39831,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0461</v>
+        <v>1.0462</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -39840,7 +39840,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0121</v>
+        <v>1.0122</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6571</v>
+        <v>1.6574</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.0688</v>
+        <v>1.0689</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -39874,7 +39874,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.0116</v>
+        <v>1.0117</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7039</v>
+        <v>1.7041</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39908,7 +39908,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0357</v>
+        <v>1.0358</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7872</v>
+        <v>1.7874</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39942,7 +39942,7 @@
         <v>1.3709</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0231</v>
+        <v>1.0232</v>
       </c>
       <c r="F236" t="n">
         <v>1.3709</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8234</v>
+        <v>1.8237</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39976,7 +39976,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9333</v>
+        <v>0.9334</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5951</v>
+        <v>1.5954</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40001,7 +40001,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9843</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40010,7 +40010,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9268</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5813</v>
+        <v>1.5815</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40044,7 +40044,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9724</v>
+        <v>0.9725</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7469</v>
+        <v>1.7471</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40069,7 +40069,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0255</v>
+        <v>1.0256</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40078,7 +40078,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9689</v>
+        <v>0.969</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8238</v>
+        <v>1.824</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8435</v>
+        <v>1.8438</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40146,7 +40146,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9435</v>
+        <v>0.9436</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9173</v>
+        <v>1.9176</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40171,7 +40171,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9931</v>
+        <v>0.9932</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40180,7 +40180,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9149</v>
+        <v>0.915</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8503</v>
+        <v>1.8506</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40214,7 +40214,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9504</v>
+        <v>0.9505</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8041</v>
+        <v>1.8043</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40239,7 +40239,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.0071</v>
+        <v>1.0072</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.677</v>
+        <v>1.6772</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7748</v>
+        <v>1.775</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40307,7 +40307,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9772</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40316,7 +40316,7 @@
         <v>1.4542</v>
       </c>
       <c r="E247" t="n">
-        <v>0.858</v>
+        <v>0.8581</v>
       </c>
       <c r="F247" t="n">
         <v>1.4542</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8049</v>
+        <v>1.8052</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9482</v>
+        <v>0.9483</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40350,7 +40350,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8603</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9223</v>
+        <v>1.9226</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9346</v>
+        <v>0.9347</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40384,7 +40384,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8892</v>
+        <v>0.8893</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9905</v>
+        <v>1.9908</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0578</v>
+        <v>2.0581</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40443,7 +40443,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9883</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40452,7 +40452,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9265</v>
+        <v>0.9266</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2355</v>
+        <v>2.2359</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9946</v>
+        <v>0.9947</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40486,7 +40486,7 @@
         <v>1.2101</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9407</v>
+        <v>0.9408</v>
       </c>
       <c r="F252" t="n">
         <v>1.2101</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.364</v>
+        <v>2.3644</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40511,7 +40511,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7556</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40520,7 +40520,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9359</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3894</v>
+        <v>2.3898</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8848</v>
+        <v>0.8849</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9449</v>
+        <v>0.945</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4978</v>
+        <v>2.4982</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40579,7 +40579,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8466</v>
+        <v>0.8467</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9476</v>
+        <v>0.9477</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5768</v>
+        <v>2.5773</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8249</v>
+        <v>0.825</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9087</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5997</v>
+        <v>2.6001</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7548</v>
+        <v>0.7549</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40656,7 +40656,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.863</v>
+        <v>0.8632</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7287</v>
+        <v>2.7292</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7968</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9227</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8822</v>
+        <v>2.8827</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8321</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3187</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9604</v>
+        <v>0.9606</v>
       </c>
       <c r="F259" t="n">
         <v>0.3187</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0769</v>
+        <v>3.0776</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9656</v>
+        <v>0.9636</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9656</v>
+        <v>0.9636</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0976</v>
+        <v>3.0898</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>-0.508</v>
+        <v>-0.509</v>
       </c>
     </row>
     <row r="89">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.964</v>
+        <v>0.963</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.165</v>
+        <v>1.167</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.397</v>
+        <v>1.403</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.982</v>
+        <v>1.992</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.783</v>
+        <v>2.795</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.937</v>
+        <v>3.948</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.269</v>
+        <v>-0.262</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.41</v>
+        <v>-0.43</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.984</v>
+        <v>0.996</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.23</v>
+        <v>-1.24</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68960.98</v>
+        <v>68787.10400000001</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1646</v>
+        <v>1.1672</v>
       </c>
       <c r="D260" t="n">
-        <v>1.3966</v>
+        <v>1.4027</v>
       </c>
       <c r="E260" t="n">
-        <v>1.982</v>
+        <v>1.9915</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7828</v>
+        <v>2.795</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9374</v>
+        <v>3.9475</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8147</v>
+        <v>-0.8121</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2688</v>
+        <v>-0.2616</v>
       </c>
       <c r="M260" t="n">
-        <v>0.984</v>
+        <v>0.9962</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>68960.98</v>
+        <v>68787.10430000001</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -31989,7 +31989,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6102</v>
+        <v>-0.6103</v>
       </c>
       <c r="D2" t="n">
         <v>0.2573</v>
@@ -32004,7 +32004,7 @@
         <v>-0.3417</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6424</v>
+        <v>-0.6425</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7141</v>
@@ -32202,7 +32202,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4053</v>
+        <v>-0.4054</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3584</v>
@@ -32440,7 +32440,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1449</v>
+        <v>-0.145</v>
       </c>
       <c r="J15" t="n">
         <v>-1.1259</v>
@@ -32678,7 +32678,7 @@
         <v>0.0999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0828</v>
+        <v>-0.0829</v>
       </c>
       <c r="J22" t="n">
         <v>-0.7466</v>
@@ -33290,7 +33290,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5594</v>
+        <v>-0.5595</v>
       </c>
       <c r="J40" t="n">
         <v>0.3628</v>
@@ -33303,7 +33303,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.5225</v>
+        <v>-0.5226</v>
       </c>
       <c r="C41" t="n">
         <v>-0.2821</v>
@@ -33392,7 +33392,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5209</v>
+        <v>-0.521</v>
       </c>
       <c r="J43" t="n">
         <v>0.5449000000000001</v>
@@ -33448,7 +33448,7 @@
         <v>1.038</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.7718</v>
       </c>
       <c r="F45" t="n">
         <v>1.038</v>
@@ -33460,7 +33460,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5571</v>
       </c>
       <c r="J45" t="n">
         <v>0.7429</v>
@@ -33494,7 +33494,7 @@
         <v>-1.781</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6499</v>
+        <v>-0.65</v>
       </c>
       <c r="J46" t="n">
         <v>0.7907999999999999</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9366</v>
+        <v>-0.9367</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.058</v>
+        <v>-1.0581</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33618,7 +33618,7 @@
         <v>0.132</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.0512</v>
+        <v>-1.0513</v>
       </c>
       <c r="F50" t="n">
         <v>0.132</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1051</v>
+        <v>-1.1052</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0244</v>
+        <v>-1.0245</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.9976</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33788,7 +33788,7 @@
         <v>-0.5705</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.3063</v>
+        <v>-1.3064</v>
       </c>
       <c r="F55" t="n">
         <v>-0.5705</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9976</v>
+        <v>-0.9977</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33834,7 +33834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0539</v>
+        <v>-1.054</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2426</v>
@@ -33868,7 +33868,7 @@
         <v>-2.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0154</v>
+        <v>-1.0155</v>
       </c>
       <c r="J57" t="n">
         <v>-0.437</v>
@@ -33936,7 +33936,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1094</v>
+        <v>-1.1095</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8135</v>
@@ -33970,7 +33970,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1247</v>
+        <v>-1.1248</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -34051,7 +34051,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.1929</v>
+        <v>-1.193</v>
       </c>
       <c r="C63" t="n">
         <v>0.7577</v>
@@ -34072,7 +34072,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0989</v>
+        <v>-1.099</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4556</v>
@@ -34140,7 +34140,7 @@
         <v>-2.117</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0361</v>
+        <v>-1.0362</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8128</v>
@@ -34153,7 +34153,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.1865</v>
+        <v>-1.1866</v>
       </c>
       <c r="C66" t="n">
         <v>0.585</v>
@@ -34174,7 +34174,7 @@
         <v>-2.117</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0782</v>
+        <v>-1.0783</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9613</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2024</v>
+        <v>-1.2025</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34298,7 +34298,7 @@
         <v>-0.2922</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.255</v>
+        <v>-1.2551</v>
       </c>
       <c r="F70" t="n">
         <v>-0.2922</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2203</v>
+        <v>-1.2204</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34493,7 +34493,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8248</v>
+        <v>-0.8249</v>
       </c>
       <c r="C76" t="n">
         <v>0.2978</v>
@@ -34582,7 +34582,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2555</v>
+        <v>-1.2556</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6257</v>
@@ -34650,7 +34650,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2785</v>
+        <v>-1.2786</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5104</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3258</v>
+        <v>-1.3259</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34697,7 +34697,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.6257</v>
+        <v>-0.6258</v>
       </c>
       <c r="C82" t="n">
         <v>0.2131</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3387</v>
+        <v>-1.3388</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3254</v>
+        <v>-1.3255</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34833,7 +34833,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5848</v>
+        <v>-0.5849</v>
       </c>
       <c r="C86" t="n">
         <v>0.0257</v>
@@ -34876,7 +34876,7 @@
         <v>0.2856</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.7688</v>
+        <v>-0.7689</v>
       </c>
       <c r="F87" t="n">
         <v>0.2856</v>
@@ -34888,7 +34888,7 @@
         <v>-0.573</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3011</v>
+        <v>-1.3012</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1278</v>
@@ -34956,7 +34956,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2432</v>
+        <v>-1.2433</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0865</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2973</v>
+        <v>-1.2974</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35037,7 +35037,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.4715</v>
+        <v>-0.4716</v>
       </c>
       <c r="C92" t="n">
         <v>-0.2331</v>
@@ -35080,7 +35080,7 @@
         <v>0.1767</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6249</v>
+        <v>-0.625</v>
       </c>
       <c r="F93" t="n">
         <v>0.1767</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3012</v>
+        <v>-1.3013</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3109</v>
+        <v>-1.311</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35139,7 +35139,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.395</v>
+        <v>-0.3951</v>
       </c>
       <c r="C95" t="n">
         <v>-0.2685</v>
@@ -35262,7 +35262,7 @@
         <v>-0.201</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0632</v>
+        <v>-1.0633</v>
       </c>
       <c r="J98" t="n">
         <v>-0.615</v>
@@ -35296,7 +35296,7 @@
         <v>-0.201</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9754</v>
+        <v>-0.9755</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5022</v>
@@ -35398,7 +35398,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7407</v>
+        <v>-0.7408</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4036</v>
@@ -35534,7 +35534,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7147</v>
+        <v>-0.7148</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3611</v>
@@ -35704,7 +35704,7 @@
         <v>0.1473</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5652</v>
+        <v>-0.5653</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2361</v>
@@ -35828,7 +35828,7 @@
         <v>1.7491</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.0217</v>
+        <v>-0.0218</v>
       </c>
       <c r="F115" t="n">
         <v>1.7491</v>
@@ -36656,7 +36656,7 @@
         <v>0.7799</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1855</v>
+        <v>-0.1856</v>
       </c>
       <c r="J139" t="n">
         <v>0.1223</v>
@@ -37052,7 +37052,7 @@
         <v>0.5953000000000001</v>
       </c>
       <c r="E151" t="n">
-        <v>0.5415</v>
+        <v>0.5416</v>
       </c>
       <c r="F151" t="n">
         <v>0.5953000000000001</v>
@@ -37383,7 +37383,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.6558</v>
+        <v>0.6559</v>
       </c>
       <c r="C161" t="n">
         <v>0.2556</v>
@@ -37472,7 +37472,7 @@
         <v>0.8315</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0872</v>
+        <v>0.0873</v>
       </c>
       <c r="J163" t="n">
         <v>1.2078</v>
@@ -37574,7 +37574,7 @@
         <v>0.8931</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1433</v>
+        <v>0.1434</v>
       </c>
       <c r="J166" t="n">
         <v>1.2728</v>
@@ -37587,7 +37587,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.7721</v>
+        <v>0.7722</v>
       </c>
       <c r="C167" t="n">
         <v>0.3612</v>
@@ -37642,7 +37642,7 @@
         <v>0.8931</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1021</v>
+        <v>0.1022</v>
       </c>
       <c r="J168" t="n">
         <v>1.4434</v>
@@ -37710,7 +37710,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0388</v>
+        <v>-0.0387</v>
       </c>
       <c r="J170" t="n">
         <v>1.5391</v>
@@ -37834,7 +37834,7 @@
         <v>0.7543</v>
       </c>
       <c r="E174" t="n">
-        <v>0.79</v>
+        <v>0.7901</v>
       </c>
       <c r="F174" t="n">
         <v>0.7543</v>
@@ -37914,7 +37914,7 @@
         <v>0.9559</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1313</v>
+        <v>-0.1312</v>
       </c>
       <c r="J176" t="n">
         <v>1.8233</v>
@@ -37961,7 +37961,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.6827</v>
+        <v>0.6828</v>
       </c>
       <c r="C178" t="n">
         <v>0.6659</v>
@@ -38288,7 +38288,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1875</v>
+        <v>-0.1874</v>
       </c>
       <c r="J187" t="n">
         <v>2.2679</v>
@@ -38458,7 +38458,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0377</v>
+        <v>-0.0376</v>
       </c>
       <c r="J192" t="n">
         <v>1.0409</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0643</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1271</v>
+        <v>0.1272</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.199</v>
+        <v>0.1991</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2975</v>
+        <v>0.2976</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38718,7 +38718,7 @@
         <v>0.3398</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0571</v>
+        <v>0.0572</v>
       </c>
       <c r="F200" t="n">
         <v>0.3398</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.304</v>
+        <v>0.3041</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4165</v>
+        <v>0.4166</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38854,7 +38854,7 @@
         <v>0.6375</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2161</v>
+        <v>0.2162</v>
       </c>
       <c r="F204" t="n">
         <v>0.6375</v>
@@ -38981,7 +38981,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.4263</v>
+        <v>0.4264</v>
       </c>
       <c r="C208" t="n">
         <v>-0.5053</v>
@@ -39024,7 +39024,7 @@
         <v>1.2979</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4317</v>
+        <v>0.4318</v>
       </c>
       <c r="F209" t="n">
         <v>1.2979</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7783</v>
+        <v>0.7784</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8385</v>
+        <v>0.8386</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9421</v>
+        <v>0.9422</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39262,7 +39262,7 @@
         <v>1.9735</v>
       </c>
       <c r="E216" t="n">
-        <v>0.6098</v>
+        <v>0.6099</v>
       </c>
       <c r="F216" t="n">
         <v>1.9735</v>
@@ -39296,7 +39296,7 @@
         <v>1.562</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6364</v>
+        <v>0.6365</v>
       </c>
       <c r="F217" t="n">
         <v>1.562</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8218</v>
+        <v>0.8219</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39342,7 +39342,7 @@
         <v>0.7019</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7511</v>
+        <v>0.7512</v>
       </c>
       <c r="J218" t="n">
         <v>0.1401</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8255</v>
+        <v>0.8256</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39432,7 +39432,7 @@
         <v>1.8104</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7199</v>
+        <v>0.72</v>
       </c>
       <c r="F221" t="n">
         <v>1.8104</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8454</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39457,7 +39457,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.9337</v>
+        <v>0.9338</v>
       </c>
       <c r="C222" t="n">
         <v>-1.4025</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9458</v>
+        <v>0.9459</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0726</v>
+        <v>1.0727</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39525,7 +39525,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.9817</v>
+        <v>0.9818</v>
       </c>
       <c r="C224" t="n">
         <v>-1.3976</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0914</v>
+        <v>1.0915</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39559,7 +39559,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.997</v>
+        <v>0.9971</v>
       </c>
       <c r="C225" t="n">
         <v>-1.3984</v>
@@ -39593,7 +39593,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9836</v>
+        <v>0.9837</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2801</v>
+        <v>1.2802</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.353</v>
+        <v>1.3531</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2809</v>
+        <v>1.281</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39738,7 +39738,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.944</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3851</v>
+        <v>1.3852</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5284</v>
+        <v>1.5285</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39806,7 +39806,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.013</v>
+        <v>1.0131</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5945</v>
+        <v>1.5946</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6574</v>
+        <v>1.6575</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7041</v>
+        <v>1.7042</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39899,7 +39899,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.0959</v>
+        <v>1.096</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7874</v>
+        <v>1.7875</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8237</v>
+        <v>1.8238</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5954</v>
+        <v>1.5955</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5815</v>
+        <v>1.5816</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7471</v>
+        <v>1.7472</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.824</v>
+        <v>1.8241</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40112,7 +40112,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9663</v>
+        <v>0.9664</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8438</v>
+        <v>1.8439</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9176</v>
+        <v>1.9177</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8506</v>
+        <v>1.8507</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8043</v>
+        <v>1.8044</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40248,7 +40248,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8649</v>
+        <v>0.865</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6772</v>
+        <v>1.6773</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40282,7 +40282,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8964</v>
+        <v>0.8965</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.775</v>
+        <v>1.7751</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8052</v>
+        <v>1.8053</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9226</v>
+        <v>1.9227</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9908</v>
+        <v>1.991</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40409,7 +40409,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9464</v>
+        <v>0.9465</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40418,7 +40418,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8791</v>
+        <v>0.8792</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0581</v>
+        <v>2.0583</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2359</v>
+        <v>2.236</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40486,7 +40486,7 @@
         <v>1.2101</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9408</v>
+        <v>0.9409</v>
       </c>
       <c r="F252" t="n">
         <v>1.2101</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3644</v>
+        <v>2.3646</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3898</v>
+        <v>2.39</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4982</v>
+        <v>2.4984</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40579,7 +40579,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8467</v>
+        <v>0.8468</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9477</v>
+        <v>0.9478</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5773</v>
+        <v>2.5775</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6001</v>
+        <v>2.6003</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7292</v>
+        <v>2.7294</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8827</v>
+        <v>2.8829</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0776</v>
+        <v>3.0778</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9636</v>
+        <v>0.9628</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9636</v>
+        <v>0.9628</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0898</v>
+        <v>3.0866</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.167</v>
+        <v>1.169</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.403</v>
+        <v>1.409</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.992</v>
+        <v>1.998</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.795</v>
+        <v>2.805</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.948</v>
+        <v>3.957</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.262</v>
+        <v>-0.255</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.996</v>
+        <v>1.006</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.24</v>
+        <v>-1.25</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68787.10400000001</v>
+        <v>68758.432</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1672</v>
+        <v>1.1694</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4027</v>
+        <v>1.4086</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9915</v>
+        <v>1.9983</v>
       </c>
       <c r="F260" t="n">
-        <v>2.795</v>
+        <v>2.8051</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9475</v>
+        <v>3.9569</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8121</v>
+        <v>-0.8099</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2616</v>
+        <v>-0.2554</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9962</v>
+        <v>1.0063</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>68787.10430000001</v>
+        <v>68758.4325</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32032,7 +32032,7 @@
         <v>-0.3193</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5886</v>
+        <v>-0.5887</v>
       </c>
       <c r="J3" t="n">
         <v>-1.636</v>
@@ -32725,7 +32725,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.359</v>
+        <v>-0.3591</v>
       </c>
       <c r="C24" t="n">
         <v>-0.3018</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0235</v>
+        <v>-1.0236</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -34038,7 +34038,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0691</v>
+        <v>-1.0692</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3324</v>
@@ -35160,7 +35160,7 @@
         <v>-0.247</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2979</v>
+        <v>-1.298</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7848000000000001</v>
@@ -37111,7 +37111,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5908</v>
+        <v>0.5909</v>
       </c>
       <c r="C153" t="n">
         <v>0.2345</v>
@@ -38968,7 +38968,7 @@
         <v>0.2178</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4624</v>
+        <v>0.4625</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2897</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0125</v>
+        <v>1.0126</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2501</v>
+        <v>1.2502</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7042</v>
+        <v>1.7043</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7875</v>
+        <v>1.7876</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8241</v>
+        <v>1.8242</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.236</v>
+        <v>2.2361</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8829</v>
+        <v>2.883</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0778</v>
+        <v>3.0779</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9628</v>
+        <v>0.9627</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9628</v>
+        <v>0.9627</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0866</v>
+        <v>3.0861</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.963</v>
+        <v>0.962</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.169</v>
+        <v>1.171</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.409</v>
+        <v>1.412</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.998</v>
+        <v>1.997</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.805</v>
+        <v>2.8</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.957</v>
+        <v>3.954</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.255</v>
+        <v>-0.254</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.006</v>
+        <v>1.001</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68758.432</v>
+        <v>68590.02099999999</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1694</v>
+        <v>1.1712</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4086</v>
+        <v>1.4117</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9983</v>
+        <v>1.9972</v>
       </c>
       <c r="F260" t="n">
-        <v>2.8051</v>
+        <v>2.7996</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9569</v>
+        <v>3.9545</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8099</v>
+        <v>-0.8081</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2554</v>
+        <v>-0.2536</v>
       </c>
       <c r="M260" t="n">
-        <v>1.0063</v>
+        <v>1.0008</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>68758.4325</v>
+        <v>68590.0211</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -31995,7 +31995,7 @@
         <v>0.2573</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8994</v>
+        <v>-0.8995</v>
       </c>
       <c r="F2" t="n">
         <v>0.2573</v>
@@ -32079,7 +32079,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5356</v>
+        <v>-0.5357</v>
       </c>
       <c r="C5" t="n">
         <v>-0.0692</v>
@@ -32100,7 +32100,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5437</v>
+        <v>-0.5438</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5114</v>
@@ -32134,7 +32134,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5329</v>
+        <v>-0.533</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4181</v>
@@ -32156,7 +32156,7 @@
         <v>0.1468</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7147</v>
+        <v>-0.7148</v>
       </c>
       <c r="F7" t="n">
         <v>0.1468</v>
@@ -32181,7 +32181,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.5104</v>
+        <v>-0.5105</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2175</v>
@@ -32270,7 +32270,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3829</v>
+        <v>-0.383</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2447</v>
@@ -32304,7 +32304,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2973</v>
+        <v>-0.2974</v>
       </c>
       <c r="J11" t="n">
         <v>-1.282</v>
@@ -32338,7 +32338,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1987</v>
+        <v>-0.1988</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2069</v>
@@ -32576,7 +32576,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1732</v>
+        <v>-0.1733</v>
       </c>
       <c r="J19" t="n">
         <v>-0.8567</v>
@@ -32780,7 +32780,7 @@
         <v>0.1817</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0228</v>
+        <v>-0.0229</v>
       </c>
       <c r="J25" t="n">
         <v>-0.5295</v>
@@ -33324,7 +33324,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5561</v>
+        <v>-0.5562</v>
       </c>
       <c r="J41" t="n">
         <v>0.3781</v>
@@ -33358,7 +33358,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.529</v>
+        <v>-0.5291</v>
       </c>
       <c r="J42" t="n">
         <v>0.4876</v>
@@ -33405,7 +33405,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.4285</v>
+        <v>-0.4286</v>
       </c>
       <c r="C44" t="n">
         <v>-0.2935</v>
@@ -33426,7 +33426,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5613</v>
+        <v>-0.5614</v>
       </c>
       <c r="J44" t="n">
         <v>0.5838</v>
@@ -33528,7 +33528,7 @@
         <v>-1.781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8545</v>
+        <v>-0.8546</v>
       </c>
       <c r="J47" t="n">
         <v>0.7421</v>
@@ -33541,7 +33541,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6373</v>
+        <v>-0.6374</v>
       </c>
       <c r="C48" t="n">
         <v>-0.2059</v>
@@ -33584,7 +33584,7 @@
         <v>-0.08690000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.998</v>
+        <v>-0.9981</v>
       </c>
       <c r="F49" t="n">
         <v>-0.08690000000000001</v>
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.8338</v>
+        <v>-0.8339</v>
       </c>
       <c r="C51" t="n">
         <v>0.2917</v>
@@ -33652,7 +33652,7 @@
         <v>0.1178</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0717</v>
+        <v>-1.0718</v>
       </c>
       <c r="F51" t="n">
         <v>0.1178</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1175</v>
+        <v>-1.1176</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33902,7 +33902,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0943</v>
+        <v>-1.0944</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5746</v>
@@ -34004,7 +34004,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1052</v>
+        <v>-1.1053</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1631</v>
@@ -34017,7 +34017,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.1862</v>
+        <v>-1.1863</v>
       </c>
       <c r="C62" t="n">
         <v>0.8124</v>
@@ -34106,7 +34106,7 @@
         <v>-2.117</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0776</v>
+        <v>-1.0777</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6903</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0998</v>
+        <v>-1.0999</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1675</v>
+        <v>-1.1676</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2407</v>
+        <v>-1.2408</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2282</v>
+        <v>-1.2283</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2491</v>
+        <v>-1.2492</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2161</v>
+        <v>-1.2162</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2779</v>
+        <v>-1.278</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34629,7 +34629,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.6846</v>
+        <v>-0.6847</v>
       </c>
       <c r="C80" t="n">
         <v>0.1919</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.342</v>
+        <v>-1.3421</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34808,7 +34808,7 @@
         <v>0.1899</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.8236</v>
+        <v>-0.8237</v>
       </c>
       <c r="F85" t="n">
         <v>0.1899</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3305</v>
+        <v>-1.3306</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34854,7 +34854,7 @@
         <v>-0.573</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3531</v>
+        <v>-1.3532</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1193</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2197</v>
+        <v>-1.2198</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -35003,7 +35003,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.485</v>
+        <v>-0.4851</v>
       </c>
       <c r="C91" t="n">
         <v>-0.1676</v>
@@ -35024,7 +35024,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2995</v>
+        <v>-1.2996</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9396</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3034</v>
+        <v>-1.3035</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35173,7 +35173,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3376</v>
+        <v>-0.3377</v>
       </c>
       <c r="C96" t="n">
         <v>-0.2964</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2664</v>
+        <v>-1.2665</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35207,7 +35207,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.2363</v>
+        <v>-0.2364</v>
       </c>
       <c r="C97" t="n">
         <v>-0.3238</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.2017</v>
+        <v>-1.2018</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35275,7 +35275,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.2671</v>
+        <v>-0.2672</v>
       </c>
       <c r="C99" t="n">
         <v>-0.3883</v>
@@ -35432,7 +35432,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8179</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3535</v>
@@ -35445,7 +35445,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.0406</v>
+        <v>-0.0407</v>
       </c>
       <c r="C104" t="n">
         <v>-0.5427999999999999</v>
@@ -35488,7 +35488,7 @@
         <v>0.5889</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.1925</v>
+        <v>-0.1926</v>
       </c>
       <c r="F105" t="n">
         <v>0.5889</v>
@@ -35568,7 +35568,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7108</v>
+        <v>-0.7109</v>
       </c>
       <c r="J107" t="n">
         <v>-0.2576</v>
@@ -35590,7 +35590,7 @@
         <v>0.79</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.1506</v>
+        <v>-0.1507</v>
       </c>
       <c r="F108" t="n">
         <v>0.79</v>
@@ -35908,7 +35908,7 @@
         <v>0.1975</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4491</v>
+        <v>-0.4492</v>
       </c>
       <c r="J117" t="n">
         <v>-0.1106</v>
@@ -35976,7 +35976,7 @@
         <v>0.2561</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3265</v>
+        <v>-0.3266</v>
       </c>
       <c r="J119" t="n">
         <v>-0.0751</v>
@@ -36588,7 +36588,7 @@
         <v>0.6814</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1266</v>
+        <v>-0.1267</v>
       </c>
       <c r="J137" t="n">
         <v>0.0472</v>
@@ -36622,7 +36622,7 @@
         <v>0.6814</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1275</v>
+        <v>-0.1276</v>
       </c>
       <c r="J138" t="n">
         <v>0.0449</v>
@@ -36792,7 +36792,7 @@
         <v>0.7841</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1704</v>
+        <v>-0.1705</v>
       </c>
       <c r="J143" t="n">
         <v>0.2682</v>
@@ -37778,7 +37778,7 @@
         <v>0.9594</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0159</v>
+        <v>-0.0158</v>
       </c>
       <c r="J172" t="n">
         <v>1.6568</v>
@@ -37948,7 +37948,7 @@
         <v>0.9559</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1856</v>
+        <v>-0.1855</v>
       </c>
       <c r="J177" t="n">
         <v>1.8036</v>
@@ -37982,7 +37982,7 @@
         <v>0.4553</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1677</v>
+        <v>-0.1676</v>
       </c>
       <c r="J178" t="n">
         <v>1.9327</v>
@@ -38016,7 +38016,7 @@
         <v>0.4553</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1675</v>
+        <v>-0.1674</v>
       </c>
       <c r="J179" t="n">
         <v>1.9402</v>
@@ -38152,7 +38152,7 @@
         <v>0.0902</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1913</v>
+        <v>-0.1912</v>
       </c>
       <c r="J183" t="n">
         <v>2.1734</v>
@@ -38208,7 +38208,7 @@
         <v>0.3993</v>
       </c>
       <c r="E185" t="n">
-        <v>0.469</v>
+        <v>0.4691</v>
       </c>
       <c r="F185" t="n">
         <v>0.3993</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0003</v>
+        <v>-0.0002</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1272</v>
+        <v>0.1273</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38573,7 +38573,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.1789</v>
+        <v>0.179</v>
       </c>
       <c r="C196" t="n">
         <v>0.031</v>
@@ -38616,7 +38616,7 @@
         <v>0.0738</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1451</v>
+        <v>0.1452</v>
       </c>
       <c r="F197" t="n">
         <v>0.0738</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2433</v>
+        <v>0.2434</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38650,7 +38650,7 @@
         <v>0.1608</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0568</v>
+        <v>0.0569</v>
       </c>
       <c r="F198" t="n">
         <v>0.1608</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2504</v>
+        <v>0.2505</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3177</v>
+        <v>0.3178</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4041</v>
+        <v>0.4042</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38811,7 +38811,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.2366</v>
+        <v>0.2367</v>
       </c>
       <c r="C203" t="n">
         <v>-0.2987</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4166</v>
+        <v>0.4167</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.451</v>
+        <v>0.4511</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4566</v>
+        <v>0.4567</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38913,7 +38913,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3434</v>
+        <v>0.3435</v>
       </c>
       <c r="C206" t="n">
         <v>-0.5203</v>
@@ -38934,7 +38934,7 @@
         <v>0.2178</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4472</v>
+        <v>0.4473</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2505</v>
@@ -38947,7 +38947,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3678</v>
+        <v>0.3679</v>
       </c>
       <c r="C207" t="n">
         <v>-0.5511</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6351</v>
+        <v>0.6352</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6825</v>
+        <v>0.6826</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8154</v>
+        <v>0.8155</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9524</v>
+        <v>0.9525</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39376,7 +39376,7 @@
         <v>0.7019</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8235</v>
+        <v>0.8236</v>
       </c>
       <c r="J219" t="n">
         <v>0.2448</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9459</v>
+        <v>0.946</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0727</v>
+        <v>1.0728</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39534,7 +39534,7 @@
         <v>1.6966</v>
       </c>
       <c r="E224" t="n">
-        <v>0.803</v>
+        <v>0.8031</v>
       </c>
       <c r="F224" t="n">
         <v>1.6966</v>
@@ -39568,7 +39568,7 @@
         <v>1.6703</v>
       </c>
       <c r="E225" t="n">
-        <v>0.8287</v>
+        <v>0.8288</v>
       </c>
       <c r="F225" t="n">
         <v>1.6703</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1805</v>
+        <v>1.1806</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2802</v>
+        <v>1.2803</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3531</v>
+        <v>1.3532</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39704,7 +39704,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8887</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.281</v>
+        <v>1.2811</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3852</v>
+        <v>1.3853</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5285</v>
+        <v>1.5286</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5946</v>
+        <v>1.5947</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6575</v>
+        <v>1.6576</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7043</v>
+        <v>1.7044</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39908,7 +39908,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0358</v>
+        <v>1.0359</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7876</v>
+        <v>1.7877</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39933,7 +39933,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0927</v>
+        <v>1.0928</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8238</v>
+        <v>1.8239</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39976,7 +39976,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9334</v>
+        <v>0.9335</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5955</v>
+        <v>1.5956</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5816</v>
+        <v>1.5817</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40044,7 +40044,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9725</v>
+        <v>0.9726</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7472</v>
+        <v>1.7473</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40078,7 +40078,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.969</v>
+        <v>0.9691</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8242</v>
+        <v>1.8243</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40103,7 +40103,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0316</v>
+        <v>1.0317</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8439</v>
+        <v>1.844</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40137,7 +40137,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0418</v>
+        <v>1.0419</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40146,7 +40146,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9436</v>
+        <v>0.9437</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9177</v>
+        <v>1.9178</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40180,7 +40180,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.915</v>
+        <v>0.9151</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8507</v>
+        <v>1.8508</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8044</v>
+        <v>1.8045</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6773</v>
+        <v>1.6774</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7751</v>
+        <v>1.7752</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8053</v>
+        <v>1.8054</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9227</v>
+        <v>1.9228</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9347</v>
+        <v>0.9348</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.991</v>
+        <v>1.9911</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0583</v>
+        <v>2.0584</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40443,7 +40443,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9885</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2361</v>
+        <v>2.2362</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9947</v>
+        <v>0.9948</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3646</v>
+        <v>2.3648</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40520,7 +40520,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9361</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.39</v>
+        <v>2.3902</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8849</v>
+        <v>0.885</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.945</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4984</v>
+        <v>2.4986</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5775</v>
+        <v>2.5777</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.825</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.9089</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6003</v>
+        <v>2.6005</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7549</v>
+        <v>0.755</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40656,7 +40656,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8632</v>
+        <v>0.8633</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7294</v>
+        <v>2.7296</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.883</v>
+        <v>2.8832</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8323</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3187</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9606</v>
+        <v>0.9607</v>
       </c>
       <c r="F259" t="n">
         <v>0.3187</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0779</v>
+        <v>3.0781</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9627</v>
+        <v>0.9619</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9627</v>
+        <v>0.9619</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0861</v>
+        <v>3.083</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.171</v>
+        <v>1.173</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.412</v>
+        <v>1.416</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.997</v>
+        <v>1.998</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.8</v>
+        <v>2.798</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.954</v>
+        <v>3.951</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.806</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.254</v>
+        <v>-0.25</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.001</v>
+        <v>0.999</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68590.02099999999</v>
+        <v>68505.36900000001</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1712</v>
+        <v>1.1734</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4117</v>
+        <v>1.4161</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9972</v>
+        <v>1.9982</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7996</v>
+        <v>2.7981</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9545</v>
+        <v>3.9509</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8081</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2536</v>
+        <v>-0.2504</v>
       </c>
       <c r="M260" t="n">
-        <v>1.0008</v>
+        <v>0.9993</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>68590.0211</v>
+        <v>68505.36900000001</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9367</v>
+        <v>-0.9368</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0581</v>
+        <v>-1.0582</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0245</v>
+        <v>-1.0246</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33834,7 +33834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.054</v>
+        <v>-1.0541</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2426</v>
@@ -33970,7 +33970,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1248</v>
+        <v>-1.1249</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -34060,7 +34060,7 @@
         <v>-0.2126</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.438</v>
+        <v>-1.4381</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2126</v>
@@ -34344,7 +34344,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2538</v>
+        <v>-1.2539</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9205</v>
@@ -34400,7 +34400,7 @@
         <v>-0.1169</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1622</v>
+        <v>-1.1623</v>
       </c>
       <c r="F73" t="n">
         <v>-0.1169</v>
@@ -34412,7 +34412,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2022</v>
+        <v>-1.2023</v>
       </c>
       <c r="J73" t="n">
         <v>-1.852</v>
@@ -34582,7 +34582,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2556</v>
+        <v>-1.2557</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6257</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3388</v>
+        <v>-1.3389</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3255</v>
+        <v>-1.3256</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34910,7 +34910,7 @@
         <v>0.332</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7186</v>
+        <v>-0.7187</v>
       </c>
       <c r="F88" t="n">
         <v>0.332</v>
@@ -34956,7 +34956,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2433</v>
+        <v>-1.2434</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0865</v>
@@ -34978,7 +34978,7 @@
         <v>0.2133</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.6883</v>
+        <v>-0.6884</v>
       </c>
       <c r="F90" t="n">
         <v>0.2133</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2974</v>
+        <v>-1.2975</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35114,7 +35114,7 @@
         <v>0.2719</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5712</v>
+        <v>-0.5713</v>
       </c>
       <c r="F94" t="n">
         <v>0.2719</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.311</v>
+        <v>-1.3111</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35636,7 +35636,7 @@
         <v>0.1473</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5567</v>
+        <v>-0.5568</v>
       </c>
       <c r="J109" t="n">
         <v>-0.2918</v>
@@ -35772,7 +35772,7 @@
         <v>0.174</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5447</v>
+        <v>-0.5448</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2332</v>
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.3228</v>
+        <v>0.3229</v>
       </c>
       <c r="C126" t="n">
         <v>-0.2228</v>
@@ -36214,7 +36214,7 @@
         <v>0.49</v>
       </c>
       <c r="I126" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="J126" t="n">
         <v>0.0233</v>
@@ -37664,7 +37664,7 @@
         <v>0.6982</v>
       </c>
       <c r="E169" t="n">
-        <v>0.7282</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="F169" t="n">
         <v>0.6982</v>
@@ -38335,7 +38335,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.3119</v>
+        <v>0.312</v>
       </c>
       <c r="C189" t="n">
         <v>0.5022</v>
@@ -38390,7 +38390,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1241</v>
+        <v>-0.124</v>
       </c>
       <c r="J190" t="n">
         <v>1.5322</v>
@@ -38412,7 +38412,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2811</v>
+        <v>0.2812</v>
       </c>
       <c r="F191" t="n">
         <v>0.08309999999999999</v>
@@ -38424,7 +38424,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0835</v>
+        <v>-0.0834</v>
       </c>
       <c r="J191" t="n">
         <v>1.307</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0643</v>
+        <v>0.0644</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2976</v>
+        <v>0.2977</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -39002,7 +39002,7 @@
         <v>0.4029</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4926</v>
+        <v>0.4927</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2483</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7784</v>
+        <v>0.7785</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39160,7 +39160,7 @@
         <v>1.5657</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5359</v>
       </c>
       <c r="F213" t="n">
         <v>1.5657</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8219</v>
+        <v>0.822</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8256</v>
+        <v>0.8257</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39423,7 +39423,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9381</v>
       </c>
       <c r="C221" t="n">
         <v>-1.2861</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8454</v>
+        <v>0.8455</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0915</v>
+        <v>1.0916</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2502</v>
+        <v>1.2503</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39797,7 +39797,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0871</v>
+        <v>1.0872</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5947</v>
+        <v>1.5948</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8239</v>
+        <v>1.824</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5817</v>
+        <v>1.5818</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40035,7 +40035,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.0071</v>
+        <v>1.0072</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7473</v>
+        <v>1.7474</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40069,7 +40069,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0256</v>
+        <v>1.0257</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.844</v>
+        <v>1.8441</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8508</v>
+        <v>1.8509</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40214,7 +40214,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9505</v>
+        <v>0.9506</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8045</v>
+        <v>1.8046</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40273,7 +40273,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0331</v>
+        <v>1.0332</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7752</v>
+        <v>1.7753</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8054</v>
+        <v>1.8055</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9228</v>
+        <v>1.9229</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9911</v>
+        <v>1.9912</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0584</v>
+        <v>2.0585</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40452,7 +40452,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9266</v>
+        <v>0.9267</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2362</v>
+        <v>2.2363</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40486,7 +40486,7 @@
         <v>1.2101</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9409</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F252" t="n">
         <v>1.2101</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3648</v>
+        <v>2.3649</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9478</v>
+        <v>0.9479</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5777</v>
+        <v>2.5778</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6005</v>
+        <v>2.6006</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7296</v>
+        <v>2.7297</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8832</v>
+        <v>2.8833</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0781</v>
+        <v>3.0782</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9619</v>
+        <v>0.9615</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9619</v>
+        <v>0.9615</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.083</v>
+        <v>3.0815</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>-0.575</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="48">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.961</v>
+        <v>0.959</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.177</v>
+        <v>1.179</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.42</v>
+        <v>1.421</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.99</v>
+        <v>1.988</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.781</v>
+        <v>2.776</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.922</v>
+        <v>3.917</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.802</v>
+        <v>-0.8</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.251</v>
+        <v>-0.25</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.982</v>
+        <v>0.977</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68386.728</v>
+        <v>68060.143</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1773</v>
+        <v>1.1793</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4196</v>
+        <v>1.4213</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9905</v>
+        <v>1.9882</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7812</v>
+        <v>2.776</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9225</v>
+        <v>3.9174</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.802</v>
+        <v>-0.8</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2506</v>
+        <v>-0.2502</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9772</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>68386.7283</v>
+        <v>68060.1431</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32004,7 +32004,7 @@
         <v>-0.3417</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6425</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7141</v>
@@ -32032,7 +32032,7 @@
         <v>-0.3193</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5887</v>
+        <v>-0.5888</v>
       </c>
       <c r="J3" t="n">
         <v>-1.636</v>
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5651</v>
       </c>
       <c r="C4" t="n">
         <v>-0.068</v>
@@ -32054,7 +32054,7 @@
         <v>0.1593</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7461</v>
+        <v>-0.7462</v>
       </c>
       <c r="F4" t="n">
         <v>0.1593</v>
@@ -32100,7 +32100,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5438</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5114</v>
@@ -32134,7 +32134,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.533</v>
+        <v>-0.5331</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4181</v>
@@ -32147,7 +32147,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.5424</v>
+        <v>-0.5425</v>
       </c>
       <c r="C7" t="n">
         <v>-0.1131</v>
@@ -32190,7 +32190,7 @@
         <v>0.129</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6703</v>
+        <v>-0.6704</v>
       </c>
       <c r="F8" t="n">
         <v>0.129</v>
@@ -32202,7 +32202,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4054</v>
+        <v>-0.4055</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3584</v>
@@ -32326,7 +32326,7 @@
         <v>0.1016</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6126</v>
+        <v>-0.6127</v>
       </c>
       <c r="F12" t="n">
         <v>0.1016</v>
@@ -32372,7 +32372,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1747</v>
+        <v>-0.1748</v>
       </c>
       <c r="J13" t="n">
         <v>-1.1973</v>
@@ -32644,7 +32644,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1038</v>
+        <v>-0.1039</v>
       </c>
       <c r="J21" t="n">
         <v>-0.7688</v>
@@ -32657,7 +32657,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3657</v>
+        <v>-0.3658</v>
       </c>
       <c r="C22" t="n">
         <v>-0.2635</v>
@@ -32882,7 +32882,7 @@
         <v>0.1401</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0268</v>
+        <v>0.0267</v>
       </c>
       <c r="J28" t="n">
         <v>-0.4227</v>
@@ -32950,7 +32950,7 @@
         <v>0.1401</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1077</v>
+        <v>0.1076</v>
       </c>
       <c r="J30" t="n">
         <v>-0.3352</v>
@@ -33052,7 +33052,7 @@
         <v>0.2376</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0274</v>
+        <v>-0.0275</v>
       </c>
       <c r="J33" t="n">
         <v>-0.1775</v>
@@ -33133,7 +33133,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3905</v>
+        <v>-0.3906</v>
       </c>
       <c r="C36" t="n">
         <v>-0.244</v>
@@ -33154,7 +33154,7 @@
         <v>-0.221</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2267</v>
+        <v>-0.2268</v>
       </c>
       <c r="J36" t="n">
         <v>0.0709</v>
@@ -33222,7 +33222,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3699</v>
+        <v>-0.37</v>
       </c>
       <c r="J38" t="n">
         <v>0.2133</v>
@@ -33256,7 +33256,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4163</v>
+        <v>-0.4164</v>
       </c>
       <c r="J39" t="n">
         <v>0.2403</v>
@@ -33290,7 +33290,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5595</v>
+        <v>-0.5596</v>
       </c>
       <c r="J40" t="n">
         <v>0.3628</v>
@@ -33460,7 +33460,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5571</v>
+        <v>-0.5572</v>
       </c>
       <c r="J45" t="n">
         <v>0.7429</v>
@@ -33494,7 +33494,7 @@
         <v>-1.781</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.65</v>
+        <v>-0.6501</v>
       </c>
       <c r="J46" t="n">
         <v>0.7907999999999999</v>
@@ -33528,7 +33528,7 @@
         <v>-1.781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8546</v>
+        <v>-0.8547</v>
       </c>
       <c r="J47" t="n">
         <v>0.7421</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9368</v>
+        <v>-0.9369</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33575,7 +33575,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8158</v>
+        <v>-0.8159</v>
       </c>
       <c r="C49" t="n">
         <v>-0.1283</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0582</v>
+        <v>-1.0583</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1053</v>
+        <v>-1.1054</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1176</v>
+        <v>-1.1177</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0246</v>
+        <v>-1.0247</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33720,7 +33720,7 @@
         <v>0.0622</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2344</v>
+        <v>-1.2345</v>
       </c>
       <c r="F53" t="n">
         <v>0.0622</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9977</v>
+        <v>-0.9978</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0236</v>
+        <v>-1.0237</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -33834,7 +33834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0541</v>
+        <v>-1.0542</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2426</v>
@@ -33856,7 +33856,7 @@
         <v>-0.8924</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.3991</v>
+        <v>-1.3992</v>
       </c>
       <c r="F57" t="n">
         <v>-0.8924</v>
@@ -33868,7 +33868,7 @@
         <v>-2.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0155</v>
+        <v>-1.0156</v>
       </c>
       <c r="J57" t="n">
         <v>-0.437</v>
@@ -33890,7 +33890,7 @@
         <v>-0.8324</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.3506</v>
+        <v>-1.3507</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8324</v>
@@ -33902,7 +33902,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0944</v>
+        <v>-1.0945</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5746</v>
@@ -33970,7 +33970,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1249</v>
+        <v>-1.125</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -34004,7 +34004,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1053</v>
+        <v>-1.1054</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1631</v>
@@ -34038,7 +34038,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0692</v>
+        <v>-1.0693</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3324</v>
@@ -34106,7 +34106,7 @@
         <v>-2.117</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0777</v>
+        <v>-1.0778</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6903</v>
@@ -34187,7 +34187,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1445</v>
+        <v>-1.1446</v>
       </c>
       <c r="C67" t="n">
         <v>0.6892</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0999</v>
+        <v>-1.1</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1676</v>
+        <v>-1.1677</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2026</v>
+        <v>-1.2027</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2205</v>
+        <v>-1.2206</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34332,7 +34332,7 @@
         <v>-0.1096</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2463</v>
+        <v>-1.2464</v>
       </c>
       <c r="F71" t="n">
         <v>-0.1096</v>
@@ -34344,7 +34344,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2539</v>
+        <v>-1.254</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9205</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2408</v>
+        <v>-1.2409</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34412,7 +34412,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2023</v>
+        <v>-1.2024</v>
       </c>
       <c r="J73" t="n">
         <v>-1.852</v>
@@ -34425,7 +34425,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.9604</v>
+        <v>-0.9605</v>
       </c>
       <c r="C74" t="n">
         <v>0.4026</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2283</v>
+        <v>-1.2284</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2492</v>
+        <v>-1.2493</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34536,7 +34536,7 @@
         <v>0.0533</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9483</v>
+        <v>-0.9484</v>
       </c>
       <c r="F77" t="n">
         <v>0.0533</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2162</v>
+        <v>-1.2163</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34582,7 +34582,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2557</v>
+        <v>-1.2558</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6257</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.278</v>
+        <v>-1.2781</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.326</v>
+        <v>-1.3261</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34706,7 +34706,7 @@
         <v>0.3265</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8638</v>
+        <v>-0.8639</v>
       </c>
       <c r="F82" t="n">
         <v>0.3265</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3421</v>
+        <v>-1.3422</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34740,7 +34740,7 @@
         <v>0.1823</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.8716</v>
+        <v>-0.8717</v>
       </c>
       <c r="F83" t="n">
         <v>0.1823</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3389</v>
+        <v>-1.339</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3256</v>
+        <v>-1.3257</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34799,7 +34799,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.6209</v>
+        <v>-0.621</v>
       </c>
       <c r="C85" t="n">
         <v>0.0525</v>
@@ -34854,7 +34854,7 @@
         <v>-0.573</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3532</v>
+        <v>-1.3533</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1193</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2198</v>
+        <v>-1.2199</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -34956,7 +34956,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2434</v>
+        <v>-1.2435</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0865</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2975</v>
+        <v>-1.2976</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35024,7 +35024,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2996</v>
+        <v>-1.2997</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9396</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3035</v>
+        <v>-1.3036</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35071,7 +35071,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4646</v>
+        <v>-0.4647</v>
       </c>
       <c r="C93" t="n">
         <v>-0.2228</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3014</v>
+        <v>-1.3015</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35105,7 +35105,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4026</v>
+        <v>-0.4027</v>
       </c>
       <c r="C94" t="n">
         <v>-0.3182</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3111</v>
+        <v>-1.3112</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35148,7 +35148,7 @@
         <v>0.272</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5618</v>
+        <v>-0.5619</v>
       </c>
       <c r="F95" t="n">
         <v>0.272</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2665</v>
+        <v>-1.2666</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.2018</v>
+        <v>-1.2019</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35250,7 +35250,7 @@
         <v>0.1393</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.4323</v>
+        <v>-0.4324</v>
       </c>
       <c r="F98" t="n">
         <v>0.1393</v>
@@ -35296,7 +35296,7 @@
         <v>-0.201</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9755</v>
+        <v>-0.9756</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5022</v>
@@ -35377,7 +35377,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.1581</v>
+        <v>-0.1582</v>
       </c>
       <c r="C102" t="n">
         <v>-0.5352</v>
@@ -35466,7 +35466,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.726</v>
+        <v>-0.7261</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2313</v>
@@ -35500,7 +35500,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7665</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2434</v>
@@ -35602,7 +35602,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6502</v>
+        <v>-0.6503</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2887</v>
@@ -35615,7 +35615,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.2272</v>
+        <v>0.2271</v>
       </c>
       <c r="C109" t="n">
         <v>-0.6274999999999999</v>
@@ -35692,7 +35692,7 @@
         <v>0.8897</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0788</v>
       </c>
       <c r="F111" t="n">
         <v>0.8897</v>
@@ -35738,7 +35738,7 @@
         <v>0.174</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5493</v>
+        <v>-0.5494</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2387</v>
@@ -35785,7 +35785,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.3323</v>
+        <v>0.3322</v>
       </c>
       <c r="C114" t="n">
         <v>-0.6998</v>
@@ -35806,7 +35806,7 @@
         <v>0.174</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5218</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2168</v>
@@ -35896,7 +35896,7 @@
         <v>1.6648</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0243</v>
+        <v>0.0242</v>
       </c>
       <c r="F117" t="n">
         <v>1.6648</v>
@@ -36146,7 +36146,7 @@
         <v>0.49</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0225</v>
+        <v>0.0226</v>
       </c>
       <c r="J124" t="n">
         <v>-0.0339</v>
@@ -36474,7 +36474,7 @@
         <v>0.3868</v>
       </c>
       <c r="E134" t="n">
-        <v>0.347</v>
+        <v>0.3469</v>
       </c>
       <c r="F134" t="n">
         <v>0.3868</v>
@@ -36486,7 +36486,7 @@
         <v>0.6312</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0366</v>
+        <v>0.0365</v>
       </c>
       <c r="J134" t="n">
         <v>-0.0473</v>
@@ -36669,7 +36669,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.3713</v>
+        <v>0.3712</v>
       </c>
       <c r="C140" t="n">
         <v>0.2033</v>
@@ -36724,7 +36724,7 @@
         <v>0.7799</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.242</v>
+        <v>-0.2421</v>
       </c>
       <c r="J141" t="n">
         <v>0.1338</v>
@@ -36758,7 +36758,7 @@
         <v>0.7841</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2328</v>
+        <v>-0.2329</v>
       </c>
       <c r="J142" t="n">
         <v>0.1756</v>
@@ -37132,7 +37132,7 @@
         <v>0.8136</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="J153" t="n">
         <v>0.6862</v>
@@ -37188,7 +37188,7 @@
         <v>0.7771</v>
       </c>
       <c r="E155" t="n">
-        <v>0.6171</v>
+        <v>0.6172</v>
       </c>
       <c r="F155" t="n">
         <v>0.7771</v>
@@ -37200,7 +37200,7 @@
         <v>0.8182</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0872</v>
+        <v>0.0873</v>
       </c>
       <c r="J155" t="n">
         <v>0.8493000000000001</v>
@@ -37268,7 +37268,7 @@
         <v>0.7964</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1242</v>
+        <v>0.1243</v>
       </c>
       <c r="J157" t="n">
         <v>0.8111</v>
@@ -37281,7 +37281,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.6708</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="C158" t="n">
         <v>0.3164</v>
@@ -37370,7 +37370,7 @@
         <v>0.8351</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0059</v>
+        <v>-0.0058</v>
       </c>
       <c r="J160" t="n">
         <v>1.0232</v>
@@ -37451,7 +37451,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.7126</v>
+        <v>0.7127</v>
       </c>
       <c r="C163" t="n">
         <v>0.3425</v>
@@ -37506,7 +37506,7 @@
         <v>0.8315</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1133</v>
+        <v>0.1134</v>
       </c>
       <c r="J164" t="n">
         <v>1.2107</v>
@@ -37519,7 +37519,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.7409</v>
+        <v>0.741</v>
       </c>
       <c r="C165" t="n">
         <v>0.3708</v>
@@ -37562,7 +37562,7 @@
         <v>0.8034</v>
       </c>
       <c r="E166" t="n">
-        <v>0.7341</v>
+        <v>0.7342</v>
       </c>
       <c r="F166" t="n">
         <v>0.8034</v>
@@ -37574,7 +37574,7 @@
         <v>0.8931</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1434</v>
+        <v>0.1435</v>
       </c>
       <c r="J166" t="n">
         <v>1.2728</v>
@@ -37608,7 +37608,7 @@
         <v>0.8931</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1131</v>
+        <v>0.1132</v>
       </c>
       <c r="J167" t="n">
         <v>1.3898</v>
@@ -37676,7 +37676,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0458</v>
+        <v>0.0459</v>
       </c>
       <c r="J169" t="n">
         <v>1.4197</v>
@@ -37744,7 +37744,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.021</v>
+        <v>-0.0209</v>
       </c>
       <c r="J171" t="n">
         <v>1.5073</v>
@@ -37880,7 +37880,7 @@
         <v>0.9559</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1229</v>
+        <v>-0.1228</v>
       </c>
       <c r="J175" t="n">
         <v>1.8105</v>
@@ -38050,7 +38050,7 @@
         <v>0.4553</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1555</v>
+        <v>-0.1554</v>
       </c>
       <c r="J180" t="n">
         <v>1.9104</v>
@@ -38063,7 +38063,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.5924</v>
+        <v>0.5925</v>
       </c>
       <c r="C181" t="n">
         <v>0.6037</v>
@@ -38097,7 +38097,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.6494</v>
+        <v>0.6495</v>
       </c>
       <c r="C182" t="n">
         <v>0.5862000000000001</v>
@@ -38254,7 +38254,7 @@
         <v>-0.4422</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2552</v>
+        <v>-0.2551</v>
       </c>
       <c r="J186" t="n">
         <v>2.1834</v>
@@ -38276,7 +38276,7 @@
         <v>0.3928</v>
       </c>
       <c r="E187" t="n">
-        <v>0.4339</v>
+        <v>0.434</v>
       </c>
       <c r="F187" t="n">
         <v>0.3928</v>
@@ -38288,7 +38288,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1874</v>
+        <v>-0.1873</v>
       </c>
       <c r="J187" t="n">
         <v>2.2679</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0002</v>
+        <v>-0.0001</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0644</v>
+        <v>0.0645</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38548,7 +38548,7 @@
         <v>0.1957</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1486</v>
+        <v>0.1487</v>
       </c>
       <c r="F195" t="n">
         <v>0.1957</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1273</v>
+        <v>0.1274</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1992</v>
+        <v>0.1993</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2435</v>
+        <v>0.2436</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2506</v>
+        <v>0.2507</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38684,7 +38684,7 @@
         <v>0.2053</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0389</v>
+        <v>0.039</v>
       </c>
       <c r="F199" t="n">
         <v>0.2053</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2977</v>
+        <v>0.2978</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3042</v>
+        <v>0.3043</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3178</v>
+        <v>0.3179</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2613</v>
+        <v>0.2614</v>
       </c>
       <c r="C202" t="n">
         <v>-0.2762</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4043</v>
+        <v>0.4044</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4167</v>
+        <v>0.4168</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38845,7 +38845,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3004</v>
+        <v>0.3005</v>
       </c>
       <c r="C204" t="n">
         <v>-0.3445</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4512</v>
+        <v>0.4513</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -38888,7 +38888,7 @@
         <v>1.7557</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2674</v>
+        <v>0.2675</v>
       </c>
       <c r="F205" t="n">
         <v>1.7557</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4567</v>
+        <v>0.4568</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38922,7 +38922,7 @@
         <v>0.5264</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2977</v>
+        <v>0.2978</v>
       </c>
       <c r="F206" t="n">
         <v>0.5264</v>
@@ -38934,7 +38934,7 @@
         <v>0.2178</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4473</v>
+        <v>0.4474</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2505</v>
@@ -38990,7 +38990,7 @@
         <v>0.7245</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3518</v>
+        <v>0.3519</v>
       </c>
       <c r="F208" t="n">
         <v>0.7245</v>
@@ -39002,7 +39002,7 @@
         <v>0.4029</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4927</v>
+        <v>0.4928</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2483</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6352</v>
+        <v>0.6353</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6826</v>
+        <v>0.6827</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39092,7 +39092,7 @@
         <v>1.3412</v>
       </c>
       <c r="E211" t="n">
-        <v>0.5148</v>
+        <v>0.5149</v>
       </c>
       <c r="F211" t="n">
         <v>1.3412</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7785</v>
+        <v>0.7786</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8155</v>
+        <v>0.8156</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39151,7 +39151,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.7418</v>
+        <v>0.7419</v>
       </c>
       <c r="C213" t="n">
         <v>-0.7202</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8387</v>
+        <v>0.8388</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39194,7 +39194,7 @@
         <v>1.7312</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6313</v>
+        <v>0.6314</v>
       </c>
       <c r="F214" t="n">
         <v>1.7312</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0126</v>
+        <v>1.0127</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.822</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39355,7 +39355,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8635</v>
+        <v>0.8636</v>
       </c>
       <c r="C219" t="n">
         <v>-1.0961</v>
@@ -39376,7 +39376,7 @@
         <v>0.7019</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8236</v>
+        <v>0.8237</v>
       </c>
       <c r="J219" t="n">
         <v>0.2448</v>
@@ -39398,7 +39398,7 @@
         <v>1.7394</v>
       </c>
       <c r="E220" t="n">
-        <v>0.7081</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="F220" t="n">
         <v>1.7394</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8257</v>
+        <v>0.8258</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8455</v>
+        <v>0.8456</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39466,7 +39466,7 @@
         <v>1.724</v>
       </c>
       <c r="E222" t="n">
-        <v>0.7362</v>
+        <v>0.7363</v>
       </c>
       <c r="F222" t="n">
         <v>1.724</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.946</v>
+        <v>0.9462</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39500,7 +39500,7 @@
         <v>1.7742</v>
       </c>
       <c r="E223" t="n">
-        <v>0.7941</v>
+        <v>0.7942</v>
       </c>
       <c r="F223" t="n">
         <v>1.7742</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0729</v>
+        <v>1.073</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0916</v>
+        <v>1.0918</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1807</v>
+        <v>1.1808</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2503</v>
+        <v>1.2505</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39627,7 +39627,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.992</v>
+        <v>0.9921</v>
       </c>
       <c r="C227" t="n">
         <v>-1.4189</v>
@@ -39636,7 +39636,7 @@
         <v>1.5257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8586</v>
+        <v>0.8587</v>
       </c>
       <c r="F227" t="n">
         <v>1.5257</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2804</v>
+        <v>1.2805</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39670,7 +39670,7 @@
         <v>1.3813</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8699</v>
+        <v>0.87</v>
       </c>
       <c r="F228" t="n">
         <v>1.3813</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3533</v>
+        <v>1.3534</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39695,7 +39695,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1.0011</v>
+        <v>1.0012</v>
       </c>
       <c r="C229" t="n">
         <v>-1.3839</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2812</v>
+        <v>1.2813</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39729,7 +39729,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.9901</v>
+        <v>0.9902</v>
       </c>
       <c r="C230" t="n">
         <v>-1.8168</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3854</v>
+        <v>1.3855</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39763,7 +39763,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0652</v>
+        <v>1.0653</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5287</v>
+        <v>1.5289</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39806,7 +39806,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0131</v>
+        <v>1.0132</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5948</v>
+        <v>1.595</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39840,7 +39840,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0122</v>
+        <v>1.0123</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6577</v>
+        <v>1.6579</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.0689</v>
+        <v>1.069</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7045</v>
+        <v>1.7047</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39899,7 +39899,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.096</v>
+        <v>1.0961</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7878</v>
+        <v>1.788</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.824</v>
+        <v>1.8242</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5957</v>
+        <v>1.5959</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40001,7 +40001,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9845</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40010,7 +40010,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.927</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5818</v>
+        <v>1.582</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7475</v>
+        <v>1.7477</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8244</v>
+        <v>1.8246</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40112,7 +40112,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9664</v>
+        <v>0.9665</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8442</v>
+        <v>1.8444</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9179</v>
+        <v>1.9181</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40171,7 +40171,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9932</v>
+        <v>0.9933</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8509</v>
+        <v>1.8511</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8047</v>
+        <v>1.8048</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40239,7 +40239,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.0072</v>
+        <v>1.0073</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6775</v>
+        <v>1.6777</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40282,7 +40282,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8965</v>
+        <v>0.8966</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7753</v>
+        <v>1.7755</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40307,7 +40307,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9774</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40316,7 +40316,7 @@
         <v>1.4542</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8581</v>
+        <v>0.8582</v>
       </c>
       <c r="F247" t="n">
         <v>1.4542</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8055</v>
+        <v>1.8057</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.923</v>
+        <v>1.9232</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9912</v>
+        <v>1.9915</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40409,7 +40409,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9465</v>
+        <v>0.9466</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40418,7 +40418,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8792</v>
+        <v>0.8793</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0586</v>
+        <v>2.0588</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40443,7 +40443,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9885</v>
+        <v>0.9886</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40452,7 +40452,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9267</v>
+        <v>0.9268</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2364</v>
+        <v>2.2367</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9948</v>
+        <v>0.9949</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40486,7 +40486,7 @@
         <v>1.2101</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9411</v>
       </c>
       <c r="F252" t="n">
         <v>1.2101</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.365</v>
+        <v>2.3653</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40520,7 +40520,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9361</v>
+        <v>0.9362</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3904</v>
+        <v>2.3906</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.885</v>
+        <v>0.8851</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9452</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4988</v>
+        <v>2.4991</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9479</v>
+        <v>0.948</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5779</v>
+        <v>2.5783</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8252</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9089</v>
+        <v>0.909</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6007</v>
+        <v>2.601</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.755</v>
+        <v>0.7551</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40656,7 +40656,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8633</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7299</v>
+        <v>2.7302</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.923</v>
+        <v>0.9231</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8835</v>
+        <v>2.8839</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.832</v>
+        <v>0.8321</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3171</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9608</v>
+        <v>0.9609</v>
       </c>
       <c r="F259" t="n">
         <v>0.3171</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0784</v>
+        <v>3.0789</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.961</v>
+        <v>0.9595</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.961</v>
+        <v>0.9595</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0793</v>
+        <v>3.0733</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.179</v>
+        <v>1.181</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.421</v>
+        <v>1.422</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.988</v>
+        <v>1.985</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.776</v>
+        <v>2.771</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.917</v>
+        <v>3.916</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.8</v>
+        <v>-0.798</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.25</v>
+        <v>-0.251</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.977</v>
+        <v>0.973</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.22</v>
+        <v>-1.21</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1793</v>
+        <v>1.1809</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4213</v>
+        <v>1.4225</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9882</v>
+        <v>1.9849</v>
       </c>
       <c r="F260" t="n">
-        <v>2.776</v>
+        <v>2.7713</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9174</v>
+        <v>3.9156</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.8</v>
+        <v>-0.7984</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2502</v>
+        <v>-0.2506</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9772</v>
+        <v>0.9725</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.959</v>
+        <v>0.958</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.181</v>
+        <v>1.182</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.422</v>
+        <v>1.424</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.985</v>
+        <v>1.983</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.771</v>
+        <v>2.768</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.916</v>
+        <v>3.915</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.798</v>
+        <v>-0.797</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.251</v>
+        <v>-0.25</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.973</v>
+        <v>0.97</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68060.143</v>
+        <v>67808.643</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1809</v>
+        <v>1.1825</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4225</v>
+        <v>1.4238</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9849</v>
+        <v>1.983</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7713</v>
+        <v>2.7684</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9156</v>
+        <v>3.9149</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.7984</v>
+        <v>-0.7968</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2506</v>
+        <v>-0.2503</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9725</v>
+        <v>0.9696</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>68060.1431</v>
+        <v>67808.6433</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32066,7 +32066,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5653</v>
+        <v>-0.5654</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6448</v>
@@ -32168,7 +32168,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4861</v>
+        <v>-0.4862</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5085</v>
@@ -32236,7 +32236,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4086</v>
+        <v>-0.4087</v>
       </c>
       <c r="J9" t="n">
         <v>-1.39</v>
@@ -32270,7 +32270,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.383</v>
+        <v>-0.3831</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2447</v>
@@ -32304,7 +32304,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2974</v>
+        <v>-0.2975</v>
       </c>
       <c r="J11" t="n">
         <v>-1.282</v>
@@ -32406,7 +32406,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2067</v>
+        <v>-0.2068</v>
       </c>
       <c r="J14" t="n">
         <v>-1.1493</v>
@@ -32610,7 +32610,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1336</v>
+        <v>-0.1337</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8238</v>
@@ -32746,7 +32746,7 @@
         <v>0.0999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0436</v>
+        <v>-0.0437</v>
       </c>
       <c r="J24" t="n">
         <v>-0.5606</v>
@@ -33065,7 +33065,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.431</v>
+        <v>-0.4311</v>
       </c>
       <c r="C34" t="n">
         <v>-0.1655</v>
@@ -33201,7 +33201,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.4346</v>
+        <v>-0.4347</v>
       </c>
       <c r="C38" t="n">
         <v>-0.1832</v>
@@ -33244,7 +33244,7 @@
         <v>0.4921</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.6365</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="F39" t="n">
         <v>0.4921</v>
@@ -33324,7 +33324,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5562</v>
+        <v>-0.5563</v>
       </c>
       <c r="J41" t="n">
         <v>0.3781</v>
@@ -33392,7 +33392,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.521</v>
+        <v>-0.5211</v>
       </c>
       <c r="J43" t="n">
         <v>0.5449000000000001</v>
@@ -33426,7 +33426,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5614</v>
+        <v>-0.5615</v>
       </c>
       <c r="J44" t="n">
         <v>0.5838</v>
@@ -33482,7 +33482,7 @@
         <v>0.9776</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.8565</v>
+        <v>-0.8566</v>
       </c>
       <c r="F46" t="n">
         <v>0.9776</v>
@@ -33516,7 +33516,7 @@
         <v>0.7934</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.9177</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="F47" t="n">
         <v>0.7934</v>
@@ -33528,7 +33528,7 @@
         <v>-1.781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8547</v>
+        <v>-0.8548</v>
       </c>
       <c r="J47" t="n">
         <v>0.7421</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9369</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0583</v>
+        <v>-1.0584</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33609,7 +33609,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8146</v>
+        <v>-0.8147</v>
       </c>
       <c r="C50" t="n">
         <v>0.0205</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1177</v>
+        <v>-1.1178</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33686,7 +33686,7 @@
         <v>0.0702</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1864</v>
+        <v>-1.1865</v>
       </c>
       <c r="F52" t="n">
         <v>0.0702</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0247</v>
+        <v>-1.0248</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.0587</v>
+        <v>-1.0588</v>
       </c>
       <c r="C54" t="n">
         <v>0.8923</v>
@@ -33754,7 +33754,7 @@
         <v>-0.3292</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2411</v>
+        <v>-1.2412</v>
       </c>
       <c r="F54" t="n">
         <v>-0.3292</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0237</v>
+        <v>-1.0238</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9978</v>
+        <v>-0.9979</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33868,7 +33868,7 @@
         <v>-2.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0156</v>
+        <v>-1.0157</v>
       </c>
       <c r="J57" t="n">
         <v>-0.437</v>
@@ -33936,7 +33936,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1096</v>
+        <v>-1.1097</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8135</v>
@@ -33949,7 +33949,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.2496</v>
+        <v>-1.2497</v>
       </c>
       <c r="C60" t="n">
         <v>0.9198</v>
@@ -33958,7 +33958,7 @@
         <v>-0.5407999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.4268</v>
+        <v>-1.4269</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5407999999999999</v>
@@ -33992,7 +33992,7 @@
         <v>-0.3869</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.3959</v>
+        <v>-1.396</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3869</v>
@@ -34038,7 +34038,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0693</v>
+        <v>-1.0694</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3324</v>
@@ -34072,7 +34072,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0991</v>
+        <v>-1.0992</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4556</v>
@@ -34094,7 +34094,7 @@
         <v>-0.2615</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3882</v>
+        <v>-1.3883</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2615</v>
@@ -34140,7 +34140,7 @@
         <v>-2.117</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0363</v>
+        <v>-1.0364</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8128</v>
@@ -34174,7 +34174,7 @@
         <v>-2.117</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0784</v>
+        <v>-1.0785</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9613</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.1</v>
+        <v>-1.1001</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34221,7 +34221,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1684</v>
+        <v>-1.1685</v>
       </c>
       <c r="C68" t="n">
         <v>0.6511</v>
@@ -34230,7 +34230,7 @@
         <v>-0.2725</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.3924</v>
+        <v>-1.3925</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2725</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1677</v>
+        <v>-1.1678</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34366,7 +34366,7 @@
         <v>-0.1495</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2341</v>
+        <v>-1.2342</v>
       </c>
       <c r="F72" t="n">
         <v>-0.1495</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2409</v>
+        <v>-1.241</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2284</v>
+        <v>-1.2285</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34480,7 +34480,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2184</v>
+        <v>-1.2185</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8065</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2493</v>
+        <v>-1.2494</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34561,7 +34561,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7518</v>
+        <v>-0.7519</v>
       </c>
       <c r="C78" t="n">
         <v>0.2407</v>
@@ -34604,7 +34604,7 @@
         <v>0.1235</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-0.9331</v>
       </c>
       <c r="F79" t="n">
         <v>0.1235</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2781</v>
+        <v>-1.2782</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34650,7 +34650,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2787</v>
+        <v>-1.2788</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5104</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3422</v>
+        <v>-1.3423</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3257</v>
+        <v>-1.3258</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3307</v>
+        <v>-1.3308</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34854,7 +34854,7 @@
         <v>-0.573</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3533</v>
+        <v>-1.3534</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1193</v>
@@ -34888,7 +34888,7 @@
         <v>-0.573</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3013</v>
+        <v>-1.3014</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1278</v>
@@ -34901,7 +34901,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.5085</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="C88" t="n">
         <v>-0.0463</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2199</v>
+        <v>-1.22</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -34969,7 +34969,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.508</v>
+        <v>-0.5081</v>
       </c>
       <c r="C90" t="n">
         <v>-0.0336</v>
@@ -35012,7 +35012,7 @@
         <v>0.1763</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6504</v>
+        <v>-0.6505</v>
       </c>
       <c r="F91" t="n">
         <v>0.1763</v>
@@ -35024,7 +35024,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2997</v>
+        <v>-1.2998</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9396</v>
@@ -35046,7 +35046,7 @@
         <v>0.1334</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.6228</v>
+        <v>-0.6229</v>
       </c>
       <c r="F92" t="n">
         <v>0.1334</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3036</v>
+        <v>-1.3037</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35160,7 +35160,7 @@
         <v>-0.247</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2981</v>
+        <v>-1.2982</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7848000000000001</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2666</v>
+        <v>-1.2667</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.2019</v>
+        <v>-1.202</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35262,7 +35262,7 @@
         <v>-0.201</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0634</v>
+        <v>-1.0635</v>
       </c>
       <c r="J98" t="n">
         <v>-0.615</v>
@@ -35330,7 +35330,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9263</v>
+        <v>-0.9264</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4986</v>
@@ -35352,7 +35352,7 @@
         <v>0.1072</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.2908</v>
+        <v>-0.2909</v>
       </c>
       <c r="F101" t="n">
         <v>0.1072</v>
@@ -35398,7 +35398,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7408</v>
+        <v>-0.7409</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4036</v>
@@ -35432,7 +35432,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.8181</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3535</v>
@@ -35522,7 +35522,7 @@
         <v>0.5485</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.1931</v>
+        <v>-0.1932</v>
       </c>
       <c r="F106" t="n">
         <v>0.5485</v>
@@ -35534,7 +35534,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7148</v>
+        <v>-0.7149</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3611</v>
@@ -35704,7 +35704,7 @@
         <v>0.1473</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5653</v>
+        <v>-0.5654</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2361</v>
@@ -35760,7 +35760,7 @@
         <v>1.6983</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.0392</v>
+        <v>-0.0393</v>
       </c>
       <c r="F113" t="n">
         <v>1.6983</v>
@@ -35942,7 +35942,7 @@
         <v>0.2561</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3407</v>
+        <v>-0.3408</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1584</v>
@@ -36248,7 +36248,7 @@
         <v>0.4759</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1508</v>
+        <v>0.1509</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0189</v>
@@ -36282,7 +36282,7 @@
         <v>0.4759</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1535</v>
+        <v>0.1536</v>
       </c>
       <c r="J128" t="n">
         <v>-0.0375</v>
@@ -36520,7 +36520,7 @@
         <v>0.6312</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0498</v>
+        <v>-0.0499</v>
       </c>
       <c r="J135" t="n">
         <v>-0.0044</v>
@@ -36554,7 +36554,7 @@
         <v>0.6814</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0597</v>
+        <v>-0.0598</v>
       </c>
       <c r="J136" t="n">
         <v>0.0368</v>
@@ -37030,7 +37030,7 @@
         <v>0.7911</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0257</v>
+        <v>0.0258</v>
       </c>
       <c r="J150" t="n">
         <v>0.5614</v>
@@ -37222,7 +37222,7 @@
         <v>0.837</v>
       </c>
       <c r="E156" t="n">
-        <v>0.5837</v>
+        <v>0.5838</v>
       </c>
       <c r="F156" t="n">
         <v>0.837</v>
@@ -37247,7 +37247,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.6472</v>
+        <v>0.6473</v>
       </c>
       <c r="C157" t="n">
         <v>0.3304</v>
@@ -37256,7 +37256,7 @@
         <v>0.7796999999999999</v>
       </c>
       <c r="E157" t="n">
-        <v>0.6141</v>
+        <v>0.6142</v>
       </c>
       <c r="F157" t="n">
         <v>0.7796999999999999</v>
@@ -37302,7 +37302,7 @@
         <v>0.7964</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1036</v>
+        <v>0.1037</v>
       </c>
       <c r="J158" t="n">
         <v>1.0058</v>
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.6842</v>
+        <v>0.6843</v>
       </c>
       <c r="C162" t="n">
         <v>0.2684</v>
@@ -37472,7 +37472,7 @@
         <v>0.8315</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0873</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J163" t="n">
         <v>1.2078</v>
@@ -37642,7 +37642,7 @@
         <v>0.8931</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1022</v>
+        <v>0.1023</v>
       </c>
       <c r="J168" t="n">
         <v>1.4434</v>
@@ -38016,7 +38016,7 @@
         <v>0.4553</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1674</v>
+        <v>-0.1673</v>
       </c>
       <c r="J179" t="n">
         <v>1.9402</v>
@@ -38072,7 +38072,7 @@
         <v>0.5621</v>
       </c>
       <c r="E181" t="n">
-        <v>0.6</v>
+        <v>0.6001</v>
       </c>
       <c r="F181" t="n">
         <v>0.5621</v>
@@ -38152,7 +38152,7 @@
         <v>0.0902</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1912</v>
+        <v>-0.1911</v>
       </c>
       <c r="J183" t="n">
         <v>2.1734</v>
@@ -38344,7 +38344,7 @@
         <v>0.2504</v>
       </c>
       <c r="E189" t="n">
-        <v>0.3273</v>
+        <v>0.3274</v>
       </c>
       <c r="F189" t="n">
         <v>0.2504</v>
@@ -38390,7 +38390,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.124</v>
+        <v>-0.1239</v>
       </c>
       <c r="J190" t="n">
         <v>1.5322</v>
@@ -38424,7 +38424,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0834</v>
+        <v>-0.0833</v>
       </c>
       <c r="J191" t="n">
         <v>1.307</v>
@@ -38458,7 +38458,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0375</v>
+        <v>-0.0374</v>
       </c>
       <c r="J192" t="n">
         <v>1.0409</v>
@@ -38480,7 +38480,7 @@
         <v>0.1272</v>
       </c>
       <c r="E193" t="n">
-        <v>0.2353</v>
+        <v>0.2354</v>
       </c>
       <c r="F193" t="n">
         <v>0.1272</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38505,7 +38505,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.1723</v>
+        <v>0.1724</v>
       </c>
       <c r="C194" t="n">
         <v>0.2157</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0645</v>
+        <v>0.0646</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1274</v>
+        <v>0.1275</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1993</v>
+        <v>0.1994</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2978</v>
+        <v>0.2979</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38752,7 +38752,7 @@
         <v>0.4293</v>
       </c>
       <c r="E201" t="n">
-        <v>0.073</v>
+        <v>0.0731</v>
       </c>
       <c r="F201" t="n">
         <v>0.4293</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3179</v>
+        <v>0.318</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38786,7 +38786,7 @@
         <v>0.4635</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2108</v>
+        <v>0.2109</v>
       </c>
       <c r="F202" t="n">
         <v>0.4635</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4044</v>
+        <v>0.4045</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38820,7 +38820,7 @@
         <v>0.5004999999999999</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1707</v>
+        <v>0.1708</v>
       </c>
       <c r="F203" t="n">
         <v>0.5004999999999999</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4168</v>
+        <v>0.4169</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4568</v>
+        <v>0.4569</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38934,7 +38934,7 @@
         <v>0.2178</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4474</v>
+        <v>0.4475</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2505</v>
@@ -38968,7 +38968,7 @@
         <v>0.2178</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4626</v>
+        <v>0.4627</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2897</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6353</v>
+        <v>0.6354</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6827</v>
+        <v>0.6828</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39126,7 +39126,7 @@
         <v>1.4354</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5155</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="F212" t="n">
         <v>1.4354</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8156</v>
+        <v>0.8157</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8388</v>
+        <v>0.8389</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9423</v>
+        <v>0.9424</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39228,7 +39228,7 @@
         <v>1.8946</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6452</v>
+        <v>0.6453</v>
       </c>
       <c r="F215" t="n">
         <v>1.8946</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0127</v>
+        <v>1.0128</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9526</v>
+        <v>0.9527</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39342,7 +39342,7 @@
         <v>0.7019</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7513</v>
+        <v>0.7514</v>
       </c>
       <c r="J218" t="n">
         <v>0.1401</v>
@@ -39376,7 +39376,7 @@
         <v>0.7019</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8237</v>
+        <v>0.8238</v>
       </c>
       <c r="J219" t="n">
         <v>0.2448</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8258</v>
+        <v>0.8259</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8456</v>
+        <v>0.8457</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.073</v>
+        <v>1.0731</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0918</v>
+        <v>1.0919</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1808</v>
+        <v>1.1809</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2505</v>
+        <v>1.2506</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2805</v>
+        <v>1.2806</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39661,7 +39661,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9722</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3534</v>
+        <v>1.3535</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2813</v>
+        <v>1.2814</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39738,7 +39738,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9442</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3855</v>
+        <v>1.3857</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5289</v>
+        <v>1.529</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.595</v>
+        <v>1.5952</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6579</v>
+        <v>1.6581</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7047</v>
+        <v>1.7048</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39908,7 +39908,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0359</v>
+        <v>1.036</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.788</v>
+        <v>1.7881</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39933,7 +39933,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0928</v>
+        <v>1.0929</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8242</v>
+        <v>1.8244</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39976,7 +39976,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9335</v>
+        <v>0.9336</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5959</v>
+        <v>1.596</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.582</v>
+        <v>1.5821</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40044,7 +40044,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9726</v>
+        <v>0.9727</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7477</v>
+        <v>1.7478</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40078,7 +40078,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9691</v>
+        <v>0.9692</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8246</v>
+        <v>1.8247</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40103,7 +40103,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0317</v>
+        <v>1.0318</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8444</v>
+        <v>1.8445</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40137,7 +40137,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0419</v>
+        <v>1.042</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40146,7 +40146,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9437</v>
+        <v>0.9438</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9181</v>
+        <v>1.9183</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40180,7 +40180,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9151</v>
+        <v>0.9152</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8511</v>
+        <v>1.8513</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40214,7 +40214,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9506</v>
+        <v>0.9507</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8048</v>
+        <v>1.805</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40248,7 +40248,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.865</v>
+        <v>0.8651</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6777</v>
+        <v>1.6778</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7755</v>
+        <v>1.7756</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8057</v>
+        <v>1.8059</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9232</v>
+        <v>1.9233</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9348</v>
+        <v>0.9349</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40384,7 +40384,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8894</v>
+        <v>0.8895</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9915</v>
+        <v>1.9916</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0588</v>
+        <v>2.059</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2367</v>
+        <v>2.2369</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3653</v>
+        <v>2.3655</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40511,7 +40511,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7557</v>
+        <v>0.7558</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40520,7 +40520,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9362</v>
+        <v>0.9363</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3906</v>
+        <v>2.3909</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9452</v>
+        <v>0.9453</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4991</v>
+        <v>2.4993</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40579,7 +40579,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8469</v>
+        <v>0.847</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.948</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5783</v>
+        <v>2.5785</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.909</v>
+        <v>0.9091</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.601</v>
+        <v>2.6013</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7551</v>
+        <v>0.7552</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40656,7 +40656,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8635</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7302</v>
+        <v>2.7305</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7971</v>
+        <v>0.7972</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9231</v>
+        <v>0.9232</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8839</v>
+        <v>2.8842</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8321</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3171</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9609</v>
+        <v>0.961</v>
       </c>
       <c r="F259" t="n">
         <v>0.3171</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0789</v>
+        <v>3.0792</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9595</v>
+        <v>0.9583</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9595</v>
+        <v>0.9583</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0733</v>
+        <v>3.0687</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>0.514</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="149">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="207">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.182</v>
+        <v>1.184</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.424</v>
+        <v>1.426</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.768</v>
+        <v>2.767</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.915</v>
+        <v>3.914</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.797</v>
+        <v>-0.796</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.25</v>
+        <v>-0.249</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.97</v>
+        <v>0.968</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67808.643</v>
+        <v>67722.016</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1825</v>
+        <v>1.1836</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4238</v>
+        <v>1.4255</v>
       </c>
       <c r="E260" t="n">
-        <v>1.983</v>
+        <v>1.9827</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7684</v>
+        <v>2.7669</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9149</v>
+        <v>3.9139</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.7968</v>
+        <v>-0.7957</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2503</v>
+        <v>-0.2493</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9696</v>
+        <v>0.9681</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>67808.6433</v>
+        <v>67722.0156</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32004,7 +32004,7 @@
         <v>-0.3417</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.6427</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7141</v>
@@ -32032,7 +32032,7 @@
         <v>-0.3193</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5888</v>
+        <v>-0.5889</v>
       </c>
       <c r="J3" t="n">
         <v>-1.636</v>
@@ -32134,7 +32134,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5331</v>
+        <v>-0.5332</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4181</v>
@@ -32202,7 +32202,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4055</v>
+        <v>-0.4056</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3584</v>
@@ -32215,7 +32215,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5372</v>
+        <v>-0.5373</v>
       </c>
       <c r="C9" t="n">
         <v>-0.2486</v>
@@ -32916,7 +32916,7 @@
         <v>0.1401</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0765</v>
+        <v>0.0764</v>
       </c>
       <c r="J29" t="n">
         <v>-0.4595</v>
@@ -33358,7 +33358,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5291</v>
+        <v>-0.5292</v>
       </c>
       <c r="J42" t="n">
         <v>0.4876</v>
@@ -33414,7 +33414,7 @@
         <v>1.0013</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.786</v>
+        <v>-0.7861</v>
       </c>
       <c r="F44" t="n">
         <v>1.0013</v>
@@ -33550,7 +33550,7 @@
         <v>0.4548</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.9104</v>
+        <v>-0.9105</v>
       </c>
       <c r="F48" t="n">
         <v>0.4548</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1054</v>
+        <v>-1.1055</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33902,7 +33902,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0945</v>
+        <v>-1.0946</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5746</v>
@@ -34004,7 +34004,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1054</v>
+        <v>-1.1055</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1631</v>
@@ -34344,7 +34344,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.254</v>
+        <v>-1.2541</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9205</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2163</v>
+        <v>-1.2164</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34570,7 +34570,7 @@
         <v>0.1141</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9683</v>
+        <v>-0.9684</v>
       </c>
       <c r="F78" t="n">
         <v>0.1141</v>
@@ -34582,7 +34582,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2558</v>
+        <v>-1.2559</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6257</v>
@@ -34595,7 +34595,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7217</v>
+        <v>-0.7218</v>
       </c>
       <c r="C79" t="n">
         <v>0.1954</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3261</v>
+        <v>-1.3262</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.339</v>
+        <v>-1.3391</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34765,7 +34765,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6528</v>
+        <v>-0.6529</v>
       </c>
       <c r="C84" t="n">
         <v>0.1093</v>
@@ -34956,7 +34956,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2435</v>
+        <v>-1.2436</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0865</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2976</v>
+        <v>-1.2977</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3015</v>
+        <v>-1.3016</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3112</v>
+        <v>-1.3113</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35241,7 +35241,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.318</v>
+        <v>-0.3181</v>
       </c>
       <c r="C98" t="n">
         <v>-0.3705</v>
@@ -35284,7 +35284,7 @@
         <v>0.1595</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.3738</v>
+        <v>-0.3739</v>
       </c>
       <c r="F99" t="n">
         <v>0.1595</v>
@@ -35296,7 +35296,7 @@
         <v>-0.201</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9756</v>
+        <v>-0.9757</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5022</v>
@@ -35318,7 +35318,7 @@
         <v>0.0925</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.3402</v>
+        <v>-0.3403</v>
       </c>
       <c r="F100" t="n">
         <v>0.0925</v>
@@ -35364,7 +35364,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8394</v>
+        <v>-0.8395</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4122</v>
@@ -35454,7 +35454,7 @@
         <v>0.5316</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.1837</v>
+        <v>-0.1838</v>
       </c>
       <c r="F104" t="n">
         <v>0.5316</v>
@@ -35568,7 +35568,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7109</v>
+        <v>-0.711</v>
       </c>
       <c r="J107" t="n">
         <v>-0.2576</v>
@@ -36078,7 +36078,7 @@
         <v>0.3371</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0788</v>
+        <v>-0.0789</v>
       </c>
       <c r="J122" t="n">
         <v>-0.147</v>
@@ -37009,7 +37009,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5576</v>
+        <v>0.5577</v>
       </c>
       <c r="C150" t="n">
         <v>0.2745</v>
@@ -37120,7 +37120,7 @@
         <v>0.7341</v>
       </c>
       <c r="E153" t="n">
-        <v>0.555</v>
+        <v>0.5551</v>
       </c>
       <c r="F153" t="n">
         <v>0.7341</v>
@@ -37868,7 +37868,7 @@
         <v>0.7323</v>
       </c>
       <c r="E175" t="n">
-        <v>0.7936</v>
+        <v>0.7937</v>
       </c>
       <c r="F175" t="n">
         <v>0.7323</v>
@@ -37914,7 +37914,7 @@
         <v>0.9559</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1312</v>
+        <v>-0.1311</v>
       </c>
       <c r="J176" t="n">
         <v>1.8233</v>
@@ -37995,7 +37995,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.6916</v>
+        <v>0.6917</v>
       </c>
       <c r="C179" t="n">
         <v>0.6107</v>
@@ -38084,7 +38084,7 @@
         <v>0.0902</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1478</v>
+        <v>-0.1477</v>
       </c>
       <c r="J181" t="n">
         <v>1.9524</v>
@@ -38118,7 +38118,7 @@
         <v>0.0902</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1756</v>
+        <v>-0.1755</v>
       </c>
       <c r="J182" t="n">
         <v>2.0487</v>
@@ -38356,7 +38356,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1323</v>
+        <v>-0.1322</v>
       </c>
       <c r="J189" t="n">
         <v>1.7736</v>
@@ -38437,7 +38437,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.1844</v>
+        <v>0.1845</v>
       </c>
       <c r="C192" t="n">
         <v>0.288</v>
@@ -38582,7 +38582,7 @@
         <v>0.2432</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1629</v>
+        <v>0.163</v>
       </c>
       <c r="F196" t="n">
         <v>0.2432</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2436</v>
+        <v>0.2437</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2507</v>
+        <v>0.2508</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38709,7 +38709,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.1137</v>
+        <v>0.1138</v>
       </c>
       <c r="C200" t="n">
         <v>-0.1771</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3043</v>
+        <v>0.3044</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4513</v>
+        <v>0.4514</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -38956,7 +38956,7 @@
         <v>0.6433</v>
       </c>
       <c r="E207" t="n">
-        <v>0.299</v>
+        <v>0.2991</v>
       </c>
       <c r="F207" t="n">
         <v>0.6433</v>
@@ -39002,7 +39002,7 @@
         <v>0.4029</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4928</v>
+        <v>0.4929</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2483</v>
@@ -39049,7 +39049,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.6032</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="C210" t="n">
         <v>-0.6456</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7786</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.8222</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9462</v>
+        <v>0.9463</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39568,7 +39568,7 @@
         <v>1.6703</v>
       </c>
       <c r="E225" t="n">
-        <v>0.8288</v>
+        <v>0.8289</v>
       </c>
       <c r="F225" t="n">
         <v>1.6703</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1809</v>
+        <v>1.181</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3535</v>
+        <v>1.3536</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39704,7 +39704,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8887</v>
+        <v>0.8888</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2814</v>
+        <v>1.2815</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39772,7 +39772,7 @@
         <v>1.4899</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9591</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="F231" t="n">
         <v>1.4899</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.529</v>
+        <v>1.5291</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39797,7 +39797,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0872</v>
+        <v>1.0873</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7048</v>
+        <v>1.7049</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7881</v>
+        <v>1.7882</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39942,7 +39942,7 @@
         <v>1.3709</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0233</v>
+        <v>1.0234</v>
       </c>
       <c r="F236" t="n">
         <v>1.3709</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5821</v>
+        <v>1.5822</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40035,7 +40035,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.0072</v>
+        <v>1.0073</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7478</v>
+        <v>1.7479</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8247</v>
+        <v>1.8248</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8445</v>
+        <v>1.8446</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7756</v>
+        <v>1.7757</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40350,7 +40350,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8605</v>
+        <v>0.8606</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9233</v>
+        <v>1.9234</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9916</v>
+        <v>1.9917</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40418,7 +40418,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8793</v>
+        <v>0.8794</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.059</v>
+        <v>2.0591</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2369</v>
+        <v>2.237</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3655</v>
+        <v>2.3656</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3909</v>
+        <v>2.391</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4993</v>
+        <v>2.4994</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5785</v>
+        <v>2.5786</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6013</v>
+        <v>2.6014</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7305</v>
+        <v>2.7306</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8842</v>
+        <v>2.8843</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0792</v>
+        <v>3.0793</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9583</v>
+        <v>0.9579</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9583</v>
+        <v>0.9579</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0687</v>
+        <v>3.0671</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>0.515</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="149">
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>0.984</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="239">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>0.832</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="260">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.958</v>
+        <v>0.957</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.184</v>
+        <v>1.187</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.426</v>
+        <v>1.43</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.983</v>
+        <v>1.985</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.914</v>
+        <v>3.915</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.796</v>
+        <v>-0.792</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.249</v>
+        <v>-0.246</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.968</v>
+        <v>0.969</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67722.016</v>
+        <v>67539.024</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31738,13 +31738,13 @@
         <v>-0.9792999999999999</v>
       </c>
       <c r="O259" t="n">
-        <v>-0.359</v>
+        <v>-0.3755</v>
       </c>
       <c r="P259" t="n">
-        <v>0.0771</v>
+        <v>0.0606</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.1605</v>
+        <v>1.144</v>
       </c>
       <c r="R259" t="n">
         <v>1.1708</v>
@@ -31783,7 +31783,7 @@
         <v>6.362</v>
       </c>
       <c r="AD259" t="n">
-        <v>1.5095</v>
+        <v>1.526</v>
       </c>
       <c r="AE259" t="n">
         <v>0.7099</v>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1836</v>
+        <v>1.1873</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4255</v>
+        <v>1.4301</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9827</v>
+        <v>1.9847</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7669</v>
+        <v>2.7674</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9139</v>
+        <v>3.9149</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,25 +31832,25 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.7957</v>
+        <v>-0.792</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2493</v>
+        <v>-0.2455</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9681</v>
+        <v>0.9686</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
       </c>
       <c r="O260" t="n">
-        <v>-0.359</v>
+        <v>-0.3755</v>
       </c>
       <c r="P260" t="n">
-        <v>0.0771</v>
+        <v>0.0606</v>
       </c>
       <c r="Q260" t="n">
-        <v>1.1605</v>
+        <v>1.144</v>
       </c>
       <c r="R260" t="n">
         <v>1.1708</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>67722.0156</v>
+        <v>67539.0235</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -31889,7 +31889,7 @@
         <v>6.362</v>
       </c>
       <c r="AD260" t="n">
-        <v>1.5095</v>
+        <v>1.526</v>
       </c>
       <c r="AE260" t="n">
         <v>0.7099</v>
@@ -32017,7 +32017,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.609</v>
+        <v>-0.6091</v>
       </c>
       <c r="D3" t="n">
         <v>0.1079</v>
@@ -32085,13 +32085,13 @@
         <v>-0.0692</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2213</v>
+        <v>0.2212</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7249</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2213</v>
+        <v>0.2212</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4717</v>
@@ -32100,7 +32100,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.544</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5114</v>
@@ -32113,7 +32113,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5078</v>
+        <v>-0.5079</v>
       </c>
       <c r="C6" t="n">
         <v>-0.0915</v>
@@ -32338,7 +32338,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1988</v>
+        <v>-0.1989</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2069</v>
@@ -32357,13 +32357,13 @@
         <v>-0.3974</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1015</v>
+        <v>0.1014</v>
       </c>
       <c r="E13" t="n">
         <v>-0.6041</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1015</v>
+        <v>0.1014</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8657</v>
@@ -32576,7 +32576,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1733</v>
+        <v>-0.1734</v>
       </c>
       <c r="J19" t="n">
         <v>-0.8567</v>
@@ -33086,7 +33086,7 @@
         <v>-0.221</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0779</v>
       </c>
       <c r="J34" t="n">
         <v>-0.037</v>
@@ -33120,7 +33120,7 @@
         <v>-0.221</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0856</v>
       </c>
       <c r="J35" t="n">
         <v>0.0234</v>
@@ -33290,7 +33290,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5596</v>
+        <v>-0.5597</v>
       </c>
       <c r="J40" t="n">
         <v>0.3628</v>
@@ -33479,13 +33479,13 @@
         <v>-0.3034</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9776</v>
+        <v>0.9775</v>
       </c>
       <c r="E46" t="n">
         <v>-0.8566</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9776</v>
+        <v>0.9775</v>
       </c>
       <c r="G46" t="n">
         <v>-1.7859</v>
@@ -33494,7 +33494,7 @@
         <v>-1.781</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6501</v>
+        <v>-0.6502</v>
       </c>
       <c r="J46" t="n">
         <v>0.7907999999999999</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1178</v>
+        <v>-1.1179</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33677,19 +33677,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9351</v>
+        <v>-0.9352</v>
       </c>
       <c r="C52" t="n">
         <v>0.4357</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0702</v>
+        <v>0.0701</v>
       </c>
       <c r="E52" t="n">
         <v>-1.1865</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0702</v>
+        <v>0.0701</v>
       </c>
       <c r="G52" t="n">
         <v>-1.486</v>
@@ -33711,7 +33711,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9751</v>
+        <v>-0.9752</v>
       </c>
       <c r="C53" t="n">
         <v>0.6286</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9978</v>
+        <v>-0.9979</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0238</v>
+        <v>-1.0239</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9979</v>
+        <v>-0.998</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33834,7 +33834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0542</v>
+        <v>-1.0543</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2426</v>
@@ -33924,7 +33924,7 @@
         <v>-0.8113</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4024</v>
+        <v>-1.4025</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8113</v>
@@ -33936,7 +33936,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1097</v>
+        <v>-1.1098</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8135</v>
@@ -33970,7 +33970,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.125</v>
+        <v>-1.1251</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -33983,7 +33983,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.1941</v>
+        <v>-1.1942</v>
       </c>
       <c r="C61" t="n">
         <v>0.8397</v>
@@ -34023,13 +34023,13 @@
         <v>0.8124</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.2592</v>
+        <v>-0.2593</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.418</v>
+        <v>-1.4181</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2592</v>
+        <v>-0.2593</v>
       </c>
       <c r="G62" t="n">
         <v>-0.8332000000000001</v>
@@ -34106,7 +34106,7 @@
         <v>-2.117</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0778</v>
+        <v>-1.0779</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6903</v>
@@ -34174,7 +34174,7 @@
         <v>-2.117</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0785</v>
+        <v>-1.0786</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9613</v>
@@ -34196,7 +34196,7 @@
         <v>-0.1867</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.384</v>
+        <v>-1.3841</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1867</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2027</v>
+        <v>-1.2028</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2206</v>
+        <v>-1.2207</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34412,7 +34412,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2024</v>
+        <v>-1.2025</v>
       </c>
       <c r="J73" t="n">
         <v>-1.852</v>
@@ -34431,13 +34431,13 @@
         <v>0.4026</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.1678</v>
+        <v>-0.1679</v>
       </c>
       <c r="E74" t="n">
         <v>-1.1586</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1678</v>
+        <v>-0.1679</v>
       </c>
       <c r="G74" t="n">
         <v>-0.4018</v>
@@ -34468,7 +34468,7 @@
         <v>-0.1831</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1312</v>
+        <v>-1.1313</v>
       </c>
       <c r="F75" t="n">
         <v>-0.1831</v>
@@ -34480,7 +34480,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2185</v>
+        <v>-1.2186</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8065</v>
@@ -34527,7 +34527,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.748</v>
+        <v>-0.7481</v>
       </c>
       <c r="C77" t="n">
         <v>0.3431</v>
@@ -34635,13 +34635,13 @@
         <v>0.1919</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2639</v>
+        <v>0.2638</v>
       </c>
       <c r="E80" t="n">
         <v>-0.9218</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2639</v>
+        <v>0.2638</v>
       </c>
       <c r="G80" t="n">
         <v>-0.2131</v>
@@ -34650,7 +34650,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2788</v>
+        <v>-1.2789</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5104</v>
@@ -34703,13 +34703,13 @@
         <v>0.2131</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3265</v>
+        <v>0.3264</v>
       </c>
       <c r="E82" t="n">
         <v>-0.8639</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3265</v>
+        <v>0.3264</v>
       </c>
       <c r="G82" t="n">
         <v>-0.1741</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3423</v>
+        <v>-1.3424</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34737,13 +34737,13 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1823</v>
+        <v>0.1822</v>
       </c>
       <c r="E83" t="n">
         <v>-0.8717</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1823</v>
+        <v>0.1822</v>
       </c>
       <c r="G83" t="n">
         <v>-0.1942</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3308</v>
+        <v>-1.3309</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34842,7 +34842,7 @@
         <v>0.2368</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7903</v>
+        <v>-0.7904</v>
       </c>
       <c r="F86" t="n">
         <v>0.2368</v>
@@ -34873,13 +34873,13 @@
         <v>0.0584</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2856</v>
+        <v>0.2855</v>
       </c>
       <c r="E87" t="n">
         <v>-0.7689</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2856</v>
+        <v>0.2855</v>
       </c>
       <c r="G87" t="n">
         <v>-0.07340000000000001</v>
@@ -34888,7 +34888,7 @@
         <v>-0.573</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3014</v>
+        <v>-1.3015</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1278</v>
@@ -34944,7 +34944,7 @@
         <v>0.3382</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.7143</v>
+        <v>-0.7144</v>
       </c>
       <c r="F89" t="n">
         <v>0.3382</v>
@@ -35024,7 +35024,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2998</v>
+        <v>-1.2999</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9396</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3037</v>
+        <v>-1.3038</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35111,13 +35111,13 @@
         <v>-0.3182</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2719</v>
+        <v>0.2718</v>
       </c>
       <c r="E94" t="n">
         <v>-0.5713</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2719</v>
+        <v>0.2718</v>
       </c>
       <c r="G94" t="n">
         <v>0.0519</v>
@@ -35160,7 +35160,7 @@
         <v>-0.247</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2982</v>
+        <v>-1.2983</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7848000000000001</v>
@@ -35182,7 +35182,7 @@
         <v>0.2773</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.4914</v>
+        <v>-0.4915</v>
       </c>
       <c r="F96" t="n">
         <v>0.2773</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2667</v>
+        <v>-1.2668</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35216,7 +35216,7 @@
         <v>0.589</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.4427</v>
+        <v>-0.4428</v>
       </c>
       <c r="F97" t="n">
         <v>0.589</v>
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.2112</v>
+        <v>-0.2113</v>
       </c>
       <c r="C101" t="n">
         <v>-0.4367</v>
@@ -35689,13 +35689,13 @@
         <v>-0.7007</v>
       </c>
       <c r="D111" t="n">
-        <v>0.8897</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="E111" t="n">
         <v>-0.0788</v>
       </c>
       <c r="F111" t="n">
-        <v>0.8897</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="G111" t="n">
         <v>0.3392</v>
@@ -35726,7 +35726,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.0526</v>
+        <v>-0.0527</v>
       </c>
       <c r="F112" t="n">
         <v>0.8885999999999999</v>
@@ -35772,7 +35772,7 @@
         <v>0.174</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5448</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2332</v>
@@ -35794,7 +35794,7 @@
         <v>1.7454</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.021</v>
+        <v>-0.0211</v>
       </c>
       <c r="F114" t="n">
         <v>1.7454</v>
@@ -35961,13 +35961,13 @@
         <v>-0.5046</v>
       </c>
       <c r="D119" t="n">
-        <v>1.5825</v>
+        <v>1.5824</v>
       </c>
       <c r="E119" t="n">
         <v>0.09329999999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>1.5825</v>
+        <v>1.5824</v>
       </c>
       <c r="G119" t="n">
         <v>0.5187</v>
@@ -36097,13 +36097,13 @@
         <v>-0.3378</v>
       </c>
       <c r="D123" t="n">
-        <v>1.2433</v>
+        <v>1.2432</v>
       </c>
       <c r="E123" t="n">
         <v>0.1869</v>
       </c>
       <c r="F123" t="n">
-        <v>1.2433</v>
+        <v>1.2432</v>
       </c>
       <c r="G123" t="n">
         <v>0.5772</v>
@@ -36131,13 +36131,13 @@
         <v>-0.3003</v>
       </c>
       <c r="D124" t="n">
-        <v>1.2798</v>
+        <v>1.2797</v>
       </c>
       <c r="E124" t="n">
         <v>0.2792</v>
       </c>
       <c r="F124" t="n">
-        <v>1.2798</v>
+        <v>1.2797</v>
       </c>
       <c r="G124" t="n">
         <v>0.6382</v>
@@ -36233,13 +36233,13 @@
         <v>-0.2094</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3791</v>
+        <v>0.379</v>
       </c>
       <c r="E127" t="n">
         <v>0.314</v>
       </c>
       <c r="F127" t="n">
-        <v>0.3791</v>
+        <v>0.379</v>
       </c>
       <c r="G127" t="n">
         <v>0.6482</v>
@@ -36338,7 +36338,7 @@
         <v>0.2588</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3232</v>
+        <v>0.3231</v>
       </c>
       <c r="F130" t="n">
         <v>0.2588</v>
@@ -36709,13 +36709,13 @@
         <v>0.2356</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2432</v>
+        <v>0.2431</v>
       </c>
       <c r="E141" t="n">
         <v>0.3621</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2432</v>
+        <v>0.2431</v>
       </c>
       <c r="G141" t="n">
         <v>0.7766</v>
@@ -36981,13 +36981,13 @@
         <v>0.2482</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5854</v>
+        <v>0.5853</v>
       </c>
       <c r="E149" t="n">
         <v>0.534</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5854</v>
+        <v>0.5853</v>
       </c>
       <c r="G149" t="n">
         <v>0.751</v>
@@ -37009,7 +37009,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5577</v>
+        <v>0.5576</v>
       </c>
       <c r="C150" t="n">
         <v>0.2745</v>
@@ -37185,13 +37185,13 @@
         <v>0.2633</v>
       </c>
       <c r="D155" t="n">
-        <v>0.7771</v>
+        <v>0.777</v>
       </c>
       <c r="E155" t="n">
         <v>0.6172</v>
       </c>
       <c r="F155" t="n">
-        <v>0.7771</v>
+        <v>0.777</v>
       </c>
       <c r="G155" t="n">
         <v>0.7138</v>
@@ -37219,13 +37219,13 @@
         <v>0.2997</v>
       </c>
       <c r="D156" t="n">
-        <v>0.837</v>
+        <v>0.8369</v>
       </c>
       <c r="E156" t="n">
         <v>0.5838</v>
       </c>
       <c r="F156" t="n">
-        <v>0.837</v>
+        <v>0.8369</v>
       </c>
       <c r="G156" t="n">
         <v>0.6442</v>
@@ -37234,7 +37234,7 @@
         <v>0.8182</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0993</v>
+        <v>0.0994</v>
       </c>
       <c r="J156" t="n">
         <v>0.7732</v>
@@ -37253,13 +37253,13 @@
         <v>0.3304</v>
       </c>
       <c r="D157" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7796</v>
       </c>
       <c r="E157" t="n">
         <v>0.6142</v>
       </c>
       <c r="F157" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7796</v>
       </c>
       <c r="G157" t="n">
         <v>0.7248</v>
@@ -37321,13 +37321,13 @@
         <v>0.3158</v>
       </c>
       <c r="D159" t="n">
-        <v>0.8693</v>
+        <v>0.8692</v>
       </c>
       <c r="E159" t="n">
         <v>0.6016</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8693</v>
+        <v>0.8692</v>
       </c>
       <c r="G159" t="n">
         <v>0.6554</v>
@@ -37404,7 +37404,7 @@
         <v>0.8351</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0285</v>
+        <v>0.0286</v>
       </c>
       <c r="J161" t="n">
         <v>1.0307</v>
@@ -37426,7 +37426,7 @@
         <v>0.7343</v>
       </c>
       <c r="E162" t="n">
-        <v>0.6717</v>
+        <v>0.6718</v>
       </c>
       <c r="F162" t="n">
         <v>0.7343</v>
@@ -37438,7 +37438,7 @@
         <v>0.8351</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0848</v>
+        <v>0.0849</v>
       </c>
       <c r="J162" t="n">
         <v>1.1074</v>
@@ -37540,7 +37540,7 @@
         <v>0.8315</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1028</v>
+        <v>0.1029</v>
       </c>
       <c r="J165" t="n">
         <v>1.3214</v>
@@ -37559,13 +37559,13 @@
         <v>0.4213</v>
       </c>
       <c r="D166" t="n">
-        <v>0.8034</v>
+        <v>0.8033</v>
       </c>
       <c r="E166" t="n">
         <v>0.7342</v>
       </c>
       <c r="F166" t="n">
-        <v>0.8034</v>
+        <v>0.8033</v>
       </c>
       <c r="G166" t="n">
         <v>0.6272</v>
@@ -37608,7 +37608,7 @@
         <v>0.8931</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1132</v>
+        <v>0.1133</v>
       </c>
       <c r="J167" t="n">
         <v>1.3898</v>
@@ -37661,13 +37661,13 @@
         <v>0.4257</v>
       </c>
       <c r="D169" t="n">
-        <v>0.6982</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="E169" t="n">
         <v>0.7282999999999999</v>
       </c>
       <c r="F169" t="n">
-        <v>0.6982</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="G169" t="n">
         <v>0.573</v>
@@ -37778,7 +37778,7 @@
         <v>0.9594</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0158</v>
+        <v>-0.0157</v>
       </c>
       <c r="J172" t="n">
         <v>1.6568</v>
@@ -37865,13 +37865,13 @@
         <v>0.6141</v>
       </c>
       <c r="D175" t="n">
-        <v>0.7323</v>
+        <v>0.7322</v>
       </c>
       <c r="E175" t="n">
         <v>0.7937</v>
       </c>
       <c r="F175" t="n">
-        <v>0.7323</v>
+        <v>0.7322</v>
       </c>
       <c r="G175" t="n">
         <v>0.531</v>
@@ -37982,7 +37982,7 @@
         <v>0.4553</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1676</v>
+        <v>-0.1675</v>
       </c>
       <c r="J178" t="n">
         <v>1.9327</v>
@@ -38050,7 +38050,7 @@
         <v>0.4553</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1554</v>
+        <v>-0.1553</v>
       </c>
       <c r="J180" t="n">
         <v>1.9104</v>
@@ -38307,13 +38307,13 @@
         <v>0.507</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4362</v>
+        <v>0.4361</v>
       </c>
       <c r="E188" t="n">
         <v>0.37</v>
       </c>
       <c r="F188" t="n">
-        <v>0.4362</v>
+        <v>0.4361</v>
       </c>
       <c r="G188" t="n">
         <v>0.4849</v>
@@ -38322,7 +38322,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1687</v>
+        <v>-0.1686</v>
       </c>
       <c r="J188" t="n">
         <v>2.0124</v>
@@ -38443,13 +38443,13 @@
         <v>0.288</v>
       </c>
       <c r="D192" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
       <c r="E192" t="n">
-        <v>0.2303</v>
+        <v>0.2304</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0009</v>
+        <v>0.0008</v>
       </c>
       <c r="G192" t="n">
         <v>0.6142</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1275</v>
+        <v>0.1276</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1994</v>
+        <v>0.1995</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38675,7 +38675,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0722</v>
+        <v>0.0723</v>
       </c>
       <c r="C199" t="n">
         <v>-0.0964</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2979</v>
+        <v>0.298</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.318</v>
+        <v>0.3181</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38783,13 +38783,13 @@
         <v>-0.2762</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4635</v>
+        <v>0.4634</v>
       </c>
       <c r="E202" t="n">
         <v>0.2109</v>
       </c>
       <c r="F202" t="n">
-        <v>0.4635</v>
+        <v>0.4634</v>
       </c>
       <c r="G202" t="n">
         <v>0.7571</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4045</v>
+        <v>0.4046</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4169</v>
+        <v>0.417</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38854,7 +38854,7 @@
         <v>0.6375</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2162</v>
+        <v>0.2163</v>
       </c>
       <c r="F204" t="n">
         <v>0.6375</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4569</v>
+        <v>0.457</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38919,13 +38919,13 @@
         <v>-0.5203</v>
       </c>
       <c r="D206" t="n">
-        <v>0.5264</v>
+        <v>0.5263</v>
       </c>
       <c r="E206" t="n">
         <v>0.2978</v>
       </c>
       <c r="F206" t="n">
-        <v>0.5264</v>
+        <v>0.5263</v>
       </c>
       <c r="G206" t="n">
         <v>0.7764</v>
@@ -38934,7 +38934,7 @@
         <v>0.2178</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4475</v>
+        <v>0.4476</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2505</v>
@@ -38968,7 +38968,7 @@
         <v>0.2178</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4627</v>
+        <v>0.4628</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2897</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6354</v>
+        <v>0.6355</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9424</v>
+        <v>0.9425</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0128</v>
+        <v>1.0129</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39253,7 +39253,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8827</v>
       </c>
       <c r="C216" t="n">
         <v>-0.9258</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9527</v>
+        <v>0.9528</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39327,13 +39327,13 @@
         <v>-1.0065</v>
       </c>
       <c r="D218" t="n">
-        <v>2.1397</v>
+        <v>2.1396</v>
       </c>
       <c r="E218" t="n">
         <v>0.6092</v>
       </c>
       <c r="F218" t="n">
-        <v>2.1397</v>
+        <v>2.1396</v>
       </c>
       <c r="G218" t="n">
         <v>0.8434</v>
@@ -39342,7 +39342,7 @@
         <v>0.7019</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7514</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J218" t="n">
         <v>0.1401</v>
@@ -39364,7 +39364,7 @@
         <v>1.6761</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6604</v>
+        <v>0.6605</v>
       </c>
       <c r="F219" t="n">
         <v>1.6761</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8457</v>
+        <v>0.8458</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0731</v>
+        <v>1.0732</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39525,7 +39525,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.9818</v>
+        <v>0.9819</v>
       </c>
       <c r="C224" t="n">
         <v>-1.3976</v>
@@ -39534,7 +39534,7 @@
         <v>1.6966</v>
       </c>
       <c r="E224" t="n">
-        <v>0.8031</v>
+        <v>0.8032</v>
       </c>
       <c r="F224" t="n">
         <v>1.6966</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0919</v>
+        <v>1.092</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39559,7 +39559,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.9971</v>
+        <v>0.9972</v>
       </c>
       <c r="C225" t="n">
         <v>-1.3984</v>
@@ -39593,7 +39593,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9837</v>
+        <v>0.9838</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2506</v>
+        <v>1.2507</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2806</v>
+        <v>1.2807</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3536</v>
+        <v>1.3537</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3857</v>
+        <v>1.3858</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5291</v>
+        <v>1.5292</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39806,7 +39806,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0132</v>
+        <v>1.0133</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5952</v>
+        <v>1.5954</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39840,7 +39840,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0123</v>
+        <v>1.0124</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6581</v>
+        <v>1.6582</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39874,7 +39874,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.0118</v>
+        <v>1.0119</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7049</v>
+        <v>1.705</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7882</v>
+        <v>1.7883</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39939,13 +39939,13 @@
         <v>-1.4374</v>
       </c>
       <c r="D236" t="n">
-        <v>1.3709</v>
+        <v>1.3708</v>
       </c>
       <c r="E236" t="n">
         <v>1.0234</v>
       </c>
       <c r="F236" t="n">
-        <v>1.3709</v>
+        <v>1.3708</v>
       </c>
       <c r="G236" t="n">
         <v>0.5635</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8244</v>
+        <v>1.8246</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.596</v>
+        <v>1.5961</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5822</v>
+        <v>1.5823</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7479</v>
+        <v>1.748</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40069,7 +40069,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0257</v>
+        <v>1.0258</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8248</v>
+        <v>1.8249</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8446</v>
+        <v>1.8447</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9183</v>
+        <v>1.9184</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8513</v>
+        <v>1.8514</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40205,7 +40205,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.031</v>
+        <v>1.0311</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.805</v>
+        <v>1.8051</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6778</v>
+        <v>1.6779</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40273,7 +40273,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0332</v>
+        <v>1.0333</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7757</v>
+        <v>1.7758</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40313,13 +40313,13 @@
         <v>-1.0799</v>
       </c>
       <c r="D247" t="n">
-        <v>1.4542</v>
+        <v>1.4541</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8582</v>
+        <v>0.8583</v>
       </c>
       <c r="F247" t="n">
-        <v>1.4542</v>
+        <v>1.4541</v>
       </c>
       <c r="G247" t="n">
         <v>-0.0668</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8059</v>
+        <v>1.806</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9484</v>
+        <v>0.9485</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9234</v>
+        <v>1.9235</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9917</v>
+        <v>1.9918</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0591</v>
+        <v>2.0592</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40452,7 +40452,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9268</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.237</v>
+        <v>2.2371</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40483,13 +40483,13 @@
         <v>-1.116</v>
       </c>
       <c r="D252" t="n">
-        <v>1.2101</v>
+        <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9411</v>
+        <v>0.9412</v>
       </c>
       <c r="F252" t="n">
-        <v>1.2101</v>
+        <v>1.21</v>
       </c>
       <c r="G252" t="n">
         <v>-0.3306</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3656</v>
+        <v>2.3657</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.391</v>
+        <v>2.3911</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8851</v>
+        <v>0.8852</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4994</v>
+        <v>2.4996</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5786</v>
+        <v>2.5788</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8252</v>
+        <v>0.8253</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6014</v>
+        <v>2.6016</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40656,7 +40656,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8635</v>
+        <v>0.8636</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7306</v>
+        <v>2.7308</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7972</v>
+        <v>0.7973</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9232</v>
+        <v>0.9233</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8843</v>
+        <v>2.8845</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,19 +40715,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8337</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
-        <v>0.3171</v>
+        <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.961</v>
+        <v>0.9611</v>
       </c>
       <c r="F259" t="n">
-        <v>0.3171</v>
+        <v>0.3242</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8665</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0793</v>
+        <v>3.0796</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9579</v>
+        <v>0.9571</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9579</v>
+        <v>0.9571</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0671</v>
+        <v>3.0637</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>0.3</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="205">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.957</v>
+        <v>0.956</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.187</v>
+        <v>1.192</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.43</v>
+        <v>1.436</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.985</v>
+        <v>1.989</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.767</v>
+        <v>2.77</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.915</v>
+        <v>3.919</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.792</v>
+        <v>-0.788</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.246</v>
+        <v>-0.24</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.969</v>
+        <v>0.971</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67539.024</v>
+        <v>67394.144</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1873</v>
+        <v>1.1916</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4301</v>
+        <v>1.4361</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9847</v>
+        <v>1.9891</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7674</v>
+        <v>2.7702</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9149</v>
+        <v>3.9187</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.792</v>
+        <v>-0.7877</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2455</v>
+        <v>-0.2401</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9686</v>
+        <v>0.9714</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>67539.0235</v>
+        <v>67394.1439</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32023,7 +32023,7 @@
         <v>0.1079</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.848</v>
+        <v>-0.8481</v>
       </c>
       <c r="F3" t="n">
         <v>0.1079</v>
@@ -32122,7 +32122,7 @@
         <v>0.2701</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7023</v>
+        <v>-0.7024</v>
       </c>
       <c r="F6" t="n">
         <v>0.2701</v>
@@ -32168,7 +32168,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4862</v>
+        <v>-0.4863</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5085</v>
@@ -32394,7 +32394,7 @@
         <v>0.0974</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6092</v>
+        <v>-0.6093</v>
       </c>
       <c r="F14" t="n">
         <v>0.0974</v>
@@ -32712,7 +32712,7 @@
         <v>0.0999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0379</v>
+        <v>-0.038</v>
       </c>
       <c r="J23" t="n">
         <v>-0.7148</v>
@@ -33256,7 +33256,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4164</v>
+        <v>-0.4165</v>
       </c>
       <c r="J39" t="n">
         <v>0.2403</v>
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.493</v>
+        <v>-0.4931</v>
       </c>
       <c r="C40" t="n">
         <v>-0.192</v>
@@ -33460,7 +33460,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5572</v>
+        <v>-0.5573</v>
       </c>
       <c r="J45" t="n">
         <v>0.7429</v>
@@ -33473,7 +33473,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4897</v>
+        <v>-0.4898</v>
       </c>
       <c r="C46" t="n">
         <v>-0.3034</v>
@@ -33528,7 +33528,7 @@
         <v>-1.781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8548</v>
+        <v>-0.8549</v>
       </c>
       <c r="J47" t="n">
         <v>0.7421</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.9371</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0584</v>
+        <v>-1.0585</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33618,7 +33618,7 @@
         <v>0.132</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.0513</v>
+        <v>-1.0514</v>
       </c>
       <c r="F50" t="n">
         <v>0.132</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0248</v>
+        <v>-1.0249</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33868,7 +33868,7 @@
         <v>-2.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0157</v>
+        <v>-1.0158</v>
       </c>
       <c r="J57" t="n">
         <v>-0.437</v>
@@ -34072,7 +34072,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0992</v>
+        <v>-1.0993</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4556</v>
@@ -34128,7 +34128,7 @@
         <v>-0.3014</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.3982</v>
+        <v>-1.3983</v>
       </c>
       <c r="F65" t="n">
         <v>-0.3014</v>
@@ -34140,7 +34140,7 @@
         <v>-2.117</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0364</v>
+        <v>-1.0365</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8128</v>
@@ -34162,7 +34162,7 @@
         <v>-0.2077</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.4313</v>
+        <v>-1.4314</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2077</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.1001</v>
+        <v>-1.1002</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1678</v>
+        <v>-1.1679</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34264,7 +34264,7 @@
         <v>-0.261</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.373</v>
+        <v>-1.3731</v>
       </c>
       <c r="F69" t="n">
         <v>-0.261</v>
@@ -34289,7 +34289,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0625</v>
+        <v>-1.0626</v>
       </c>
       <c r="C70" t="n">
         <v>0.5677</v>
@@ -34323,7 +34323,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.019</v>
+        <v>-1.0191</v>
       </c>
       <c r="C71" t="n">
         <v>0.5209</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.241</v>
+        <v>-1.2411</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2494</v>
+        <v>-1.2495</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2782</v>
+        <v>-1.2783</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34638,7 +34638,7 @@
         <v>0.2638</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.9218</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="F80" t="n">
         <v>0.2638</v>
@@ -34672,7 +34672,7 @@
         <v>0.3202</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.9139</v>
       </c>
       <c r="F81" t="n">
         <v>0.3202</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3391</v>
+        <v>-1.3392</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3258</v>
+        <v>-1.3259</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34854,7 +34854,7 @@
         <v>-0.573</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3534</v>
+        <v>-1.3535</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1193</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.22</v>
+        <v>-1.2201</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.5038</v>
+        <v>-0.5039</v>
       </c>
       <c r="C89" t="n">
         <v>-0.0515</v>
@@ -35080,7 +35080,7 @@
         <v>0.1767</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.625</v>
+        <v>-0.6251</v>
       </c>
       <c r="F93" t="n">
         <v>0.1767</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3113</v>
+        <v>-1.3114</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.202</v>
+        <v>-1.2021</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35262,7 +35262,7 @@
         <v>-0.201</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0635</v>
+        <v>-1.0636</v>
       </c>
       <c r="J98" t="n">
         <v>-0.615</v>
@@ -35500,7 +35500,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.7667</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2434</v>
@@ -35581,7 +35581,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0375</v>
+        <v>0.0374</v>
       </c>
       <c r="C108" t="n">
         <v>-0.6247</v>
@@ -35649,7 +35649,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.112</v>
+        <v>0.1119</v>
       </c>
       <c r="C110" t="n">
         <v>-0.6982</v>
@@ -35908,7 +35908,7 @@
         <v>0.1975</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4492</v>
+        <v>-0.4493</v>
       </c>
       <c r="J117" t="n">
         <v>-0.1106</v>
@@ -35976,7 +35976,7 @@
         <v>0.2561</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3266</v>
+        <v>-0.3267</v>
       </c>
       <c r="J119" t="n">
         <v>-0.0751</v>
@@ -36690,7 +36690,7 @@
         <v>0.7799</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1954</v>
+        <v>-0.1955</v>
       </c>
       <c r="J140" t="n">
         <v>0.1265</v>
@@ -37009,7 +37009,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5576</v>
+        <v>0.5577</v>
       </c>
       <c r="C150" t="n">
         <v>0.2745</v>
@@ -37268,7 +37268,7 @@
         <v>0.7964</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1243</v>
+        <v>0.1244</v>
       </c>
       <c r="J157" t="n">
         <v>0.8111</v>
@@ -37336,7 +37336,7 @@
         <v>0.7964</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0381</v>
+        <v>0.0382</v>
       </c>
       <c r="J159" t="n">
         <v>0.9164</v>
@@ -37574,7 +37574,7 @@
         <v>0.8931</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1435</v>
+        <v>0.1436</v>
       </c>
       <c r="J166" t="n">
         <v>1.2728</v>
@@ -37812,7 +37812,7 @@
         <v>0.9594</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0139</v>
+        <v>-0.0138</v>
       </c>
       <c r="J173" t="n">
         <v>1.6146</v>
@@ -38004,7 +38004,7 @@
         <v>0.6657</v>
       </c>
       <c r="E179" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.6982</v>
       </c>
       <c r="F179" t="n">
         <v>0.6657</v>
@@ -38301,7 +38301,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.3832</v>
+        <v>0.3833</v>
       </c>
       <c r="C188" t="n">
         <v>0.507</v>
@@ -38458,7 +38458,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0374</v>
+        <v>-0.0373</v>
       </c>
       <c r="J192" t="n">
         <v>1.0409</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0646</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38607,7 +38607,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.1309</v>
+        <v>0.131</v>
       </c>
       <c r="C197" t="n">
         <v>-0.0422</v>
@@ -38616,7 +38616,7 @@
         <v>0.0738</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1452</v>
+        <v>0.1453</v>
       </c>
       <c r="F197" t="n">
         <v>0.0738</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2437</v>
+        <v>0.2438</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2508</v>
+        <v>0.2509</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38718,7 +38718,7 @@
         <v>0.3398</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0572</v>
+        <v>0.0573</v>
       </c>
       <c r="F200" t="n">
         <v>0.3398</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3044</v>
+        <v>0.3045</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4514</v>
+        <v>0.4515</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -39058,7 +39058,7 @@
         <v>1.2949</v>
       </c>
       <c r="E210" t="n">
-        <v>0.4303</v>
+        <v>0.4304</v>
       </c>
       <c r="F210" t="n">
         <v>1.2949</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6828</v>
+        <v>0.6829</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39083,7 +39083,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.6801</v>
+        <v>0.6802</v>
       </c>
       <c r="C211" t="n">
         <v>-0.7048</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8157</v>
+        <v>0.8158</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8389</v>
+        <v>0.839</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39262,7 +39262,7 @@
         <v>1.9735</v>
       </c>
       <c r="E216" t="n">
-        <v>0.6099</v>
+        <v>0.61</v>
       </c>
       <c r="F216" t="n">
         <v>1.9735</v>
@@ -39376,7 +39376,7 @@
         <v>0.7019</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8238</v>
+        <v>0.8239</v>
       </c>
       <c r="J219" t="n">
         <v>0.2448</v>
@@ -39389,7 +39389,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.9144</v>
+        <v>0.9145</v>
       </c>
       <c r="C220" t="n">
         <v>-1.2201</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8259</v>
+        <v>0.826</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39432,7 +39432,7 @@
         <v>1.8104</v>
       </c>
       <c r="E221" t="n">
-        <v>0.72</v>
+        <v>0.7201</v>
       </c>
       <c r="F221" t="n">
         <v>1.8104</v>
@@ -39457,7 +39457,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.9338</v>
+        <v>0.9339</v>
       </c>
       <c r="C222" t="n">
         <v>-1.4025</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9463</v>
+        <v>0.9464</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0732</v>
+        <v>1.0733</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.181</v>
+        <v>1.1811</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39602,7 +39602,7 @@
         <v>1.477</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8605</v>
       </c>
       <c r="F226" t="n">
         <v>1.477</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2815</v>
+        <v>1.2816</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3858</v>
+        <v>1.3859</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5292</v>
+        <v>1.5293</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39831,7 +39831,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0463</v>
+        <v>1.0464</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6582</v>
+        <v>1.6583</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7883</v>
+        <v>1.7884</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0309</v>
+        <v>1.031</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5961</v>
+        <v>1.5962</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40010,7 +40010,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.927</v>
+        <v>0.9271</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5823</v>
+        <v>1.5824</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.748</v>
+        <v>1.7481</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8249</v>
+        <v>1.825</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40112,7 +40112,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9665</v>
+        <v>0.9666</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8447</v>
+        <v>1.8448</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9184</v>
+        <v>1.9185</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8514</v>
+        <v>1.8515</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8051</v>
+        <v>1.8052</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6779</v>
+        <v>1.678</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40282,7 +40282,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8966</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7758</v>
+        <v>1.7759</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40307,7 +40307,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9774</v>
+        <v>0.9775</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.806</v>
+        <v>1.8061</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9235</v>
+        <v>1.9236</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9918</v>
+        <v>1.9919</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40409,7 +40409,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9466</v>
+        <v>0.9467</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0592</v>
+        <v>2.0593</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40443,7 +40443,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9886</v>
+        <v>0.9887</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2371</v>
+        <v>2.2372</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9949</v>
+        <v>0.995</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3657</v>
+        <v>2.3659</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3911</v>
+        <v>2.3913</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9453</v>
+        <v>0.9454</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4996</v>
+        <v>2.4998</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40579,7 +40579,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.847</v>
+        <v>0.8471</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9482</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5788</v>
+        <v>2.579</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9091</v>
+        <v>0.9092</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6016</v>
+        <v>2.6017</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7308</v>
+        <v>2.731</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9233</v>
+        <v>0.9234</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8845</v>
+        <v>2.8847</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0796</v>
+        <v>3.0798</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9571</v>
+        <v>0.9564</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9571</v>
+        <v>0.9564</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0637</v>
+        <v>3.0611</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-0.51</v>
+        <v>-0.511</v>
       </c>
     </row>
     <row r="9">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>-0.96</v>
+        <v>-0.961</v>
       </c>
     </row>
     <row r="75">
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>0.514</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="149">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>0.948</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="249">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.956</v>
+        <v>0.955</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.192</v>
+        <v>1.195</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.436</v>
+        <v>1.44</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.989</v>
+        <v>1.991</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.77</v>
+        <v>2.771</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.919</v>
+        <v>3.921</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.788</v>
+        <v>-0.785</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.24</v>
+        <v>-0.236</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.971</v>
+        <v>0.972</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67394.144</v>
+        <v>67129.448</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1916</v>
+        <v>1.1948</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4361</v>
+        <v>1.4403</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9891</v>
+        <v>1.9915</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7702</v>
+        <v>2.7707</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9187</v>
+        <v>3.9215</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.7877</v>
+        <v>-0.7845</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2401</v>
+        <v>-0.2364</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9714</v>
+        <v>0.9719</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>67394.1439</v>
+        <v>67129.4479</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -31995,7 +31995,7 @@
         <v>0.2573</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8995</v>
+        <v>-0.8996</v>
       </c>
       <c r="F2" t="n">
         <v>0.2573</v>
@@ -32004,7 +32004,7 @@
         <v>-0.3417</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6427</v>
+        <v>-0.6428</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7141</v>
@@ -32032,7 +32032,7 @@
         <v>-0.3193</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5889</v>
+        <v>-0.589</v>
       </c>
       <c r="J3" t="n">
         <v>-1.636</v>
@@ -32066,7 +32066,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5654</v>
+        <v>-0.5655</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6448</v>
@@ -32088,7 +32088,7 @@
         <v>0.2212</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7249</v>
+        <v>-0.725</v>
       </c>
       <c r="F5" t="n">
         <v>0.2212</v>
@@ -32134,7 +32134,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5332</v>
+        <v>-0.5333</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4181</v>
@@ -32202,7 +32202,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4056</v>
+        <v>-0.4057</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3584</v>
@@ -32236,7 +32236,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4087</v>
+        <v>-0.4088</v>
       </c>
       <c r="J9" t="n">
         <v>-1.39</v>
@@ -32270,7 +32270,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3831</v>
+        <v>-0.3832</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2447</v>
@@ -32283,7 +32283,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.4961</v>
+        <v>-0.4962</v>
       </c>
       <c r="C11" t="n">
         <v>-0.3532</v>
@@ -32304,7 +32304,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2975</v>
+        <v>-0.2976</v>
       </c>
       <c r="J11" t="n">
         <v>-1.282</v>
@@ -32453,7 +32453,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.4309</v>
+        <v>-0.431</v>
       </c>
       <c r="C16" t="n">
         <v>-0.4508</v>
@@ -32474,7 +32474,7 @@
         <v>-0.0989</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1469</v>
+        <v>-0.147</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0218</v>
@@ -32542,7 +32542,7 @@
         <v>-0.0989</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2055</v>
+        <v>-0.2056</v>
       </c>
       <c r="J18" t="n">
         <v>-0.9851</v>
@@ -32678,7 +32678,7 @@
         <v>0.0999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0829</v>
+        <v>-0.083</v>
       </c>
       <c r="J22" t="n">
         <v>-0.7466</v>
@@ -32861,7 +32861,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4007</v>
+        <v>-0.4008</v>
       </c>
       <c r="C28" t="n">
         <v>0.0306</v>
@@ -33108,7 +33108,7 @@
         <v>-0.0015</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5178</v>
+        <v>-0.5179</v>
       </c>
       <c r="F35" t="n">
         <v>-0.0015</v>
@@ -33222,7 +33222,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.37</v>
+        <v>-0.3701</v>
       </c>
       <c r="J38" t="n">
         <v>0.2133</v>
@@ -33324,7 +33324,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5563</v>
+        <v>-0.5564</v>
       </c>
       <c r="J41" t="n">
         <v>0.3781</v>
@@ -33426,7 +33426,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5615</v>
+        <v>-0.5616</v>
       </c>
       <c r="J44" t="n">
         <v>0.5838</v>
@@ -33507,7 +33507,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.5755</v>
+        <v>-0.5756</v>
       </c>
       <c r="C47" t="n">
         <v>-0.3486</v>
@@ -33584,7 +33584,7 @@
         <v>-0.08690000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.9981</v>
+        <v>-0.9982</v>
       </c>
       <c r="F49" t="n">
         <v>-0.08690000000000001</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1055</v>
+        <v>-1.1056</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33652,7 +33652,7 @@
         <v>0.1178</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0718</v>
+        <v>-1.0719</v>
       </c>
       <c r="F51" t="n">
         <v>0.1178</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1179</v>
+        <v>-1.118</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0249</v>
+        <v>-1.025</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9979</v>
+        <v>-0.998</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0239</v>
+        <v>-1.024</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -33779,7 +33779,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1592</v>
+        <v>-1.1593</v>
       </c>
       <c r="C55" t="n">
         <v>1.0633</v>
@@ -33788,7 +33788,7 @@
         <v>-0.5705</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.3064</v>
+        <v>-1.3065</v>
       </c>
       <c r="F55" t="n">
         <v>-0.5705</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.998</v>
+        <v>-0.9981</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33813,7 +33813,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.2471</v>
+        <v>-1.2472</v>
       </c>
       <c r="C56" t="n">
         <v>1.0216</v>
@@ -33834,7 +33834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0543</v>
+        <v>-1.0544</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2426</v>
@@ -33902,7 +33902,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0946</v>
+        <v>-1.0947</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5746</v>
@@ -33970,7 +33970,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1251</v>
+        <v>-1.1252</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -34004,7 +34004,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1055</v>
+        <v>-1.1056</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1631</v>
@@ -34038,7 +34038,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0694</v>
+        <v>-1.0695</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3324</v>
@@ -34106,7 +34106,7 @@
         <v>-2.117</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0779</v>
+        <v>-1.078</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6903</v>
@@ -34255,7 +34255,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1506</v>
+        <v>-1.1507</v>
       </c>
       <c r="C69" t="n">
         <v>0.5633</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2028</v>
+        <v>-1.2029</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34298,7 +34298,7 @@
         <v>-0.2922</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2551</v>
+        <v>-1.2552</v>
       </c>
       <c r="F70" t="n">
         <v>-0.2922</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2207</v>
+        <v>-1.2208</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34344,7 +34344,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2541</v>
+        <v>-1.2542</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9205</v>
@@ -34357,7 +34357,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0172</v>
+        <v>-1.0173</v>
       </c>
       <c r="C72" t="n">
         <v>0.5194</v>
@@ -34412,7 +34412,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2025</v>
+        <v>-1.2026</v>
       </c>
       <c r="J73" t="n">
         <v>-1.852</v>
@@ -34434,7 +34434,7 @@
         <v>-0.1679</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1586</v>
+        <v>-1.1587</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1679</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2285</v>
+        <v>-1.2286</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2164</v>
+        <v>-1.2165</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34582,7 +34582,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2559</v>
+        <v>-1.256</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6257</v>
@@ -34650,7 +34650,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2789</v>
+        <v>-1.279</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5104</v>
@@ -34663,7 +34663,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.667</v>
+        <v>-0.6671</v>
       </c>
       <c r="C81" t="n">
         <v>0.2028</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3262</v>
+        <v>-1.3263</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3424</v>
+        <v>-1.3425</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3259</v>
+        <v>-1.326</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34808,7 +34808,7 @@
         <v>0.1899</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.8237</v>
+        <v>-0.8238</v>
       </c>
       <c r="F85" t="n">
         <v>0.1899</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3309</v>
+        <v>-1.331</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34867,7 +34867,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5581</v>
       </c>
       <c r="C87" t="n">
         <v>0.0584</v>
@@ -34876,7 +34876,7 @@
         <v>0.2855</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.7689</v>
+        <v>-0.769</v>
       </c>
       <c r="F87" t="n">
         <v>0.2855</v>
@@ -34888,7 +34888,7 @@
         <v>-0.573</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3015</v>
+        <v>-1.3016</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1278</v>
@@ -34956,7 +34956,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2436</v>
+        <v>-1.2437</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0865</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2977</v>
+        <v>-1.2978</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35024,7 +35024,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2999</v>
+        <v>-1.3</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9396</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3038</v>
+        <v>-1.3039</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3016</v>
+        <v>-1.3017</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35160,7 +35160,7 @@
         <v>-0.247</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2983</v>
+        <v>-1.2984</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7848000000000001</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2668</v>
+        <v>-1.2669</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35296,7 +35296,7 @@
         <v>-0.201</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9757</v>
+        <v>-0.9758</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5022</v>
@@ -35330,7 +35330,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9264</v>
+        <v>-0.9265</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4986</v>
@@ -35432,7 +35432,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8181</v>
+        <v>-0.8182</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3535</v>
@@ -35466,7 +35466,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7261</v>
+        <v>-0.7262</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2313</v>
@@ -35806,7 +35806,7 @@
         <v>0.174</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5218</v>
+        <v>-0.5219</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2168</v>
@@ -35840,7 +35840,7 @@
         <v>0.1975</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5036</v>
+        <v>-0.5037</v>
       </c>
       <c r="J115" t="n">
         <v>-0.2476</v>
@@ -35874,7 +35874,7 @@
         <v>0.1975</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4755</v>
+        <v>-0.4756</v>
       </c>
       <c r="J116" t="n">
         <v>-0.1328</v>
@@ -35887,7 +35887,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.3524</v>
+        <v>0.3523</v>
       </c>
       <c r="C117" t="n">
         <v>-0.613</v>
@@ -35930,7 +35930,7 @@
         <v>1.6174</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0643</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F118" t="n">
         <v>1.6174</v>
@@ -36202,7 +36202,7 @@
         <v>0.4301</v>
       </c>
       <c r="E126" t="n">
-        <v>0.296</v>
+        <v>0.2961</v>
       </c>
       <c r="F126" t="n">
         <v>0.4301</v>
@@ -36304,7 +36304,7 @@
         <v>0.2558</v>
       </c>
       <c r="E129" t="n">
-        <v>0.3026</v>
+        <v>0.3027</v>
       </c>
       <c r="F129" t="n">
         <v>0.2558</v>
@@ -36418,7 +36418,7 @@
         <v>0.5522</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1304</v>
+        <v>0.1305</v>
       </c>
       <c r="J132" t="n">
         <v>-0.0194</v>
@@ -36452,7 +36452,7 @@
         <v>0.6312</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1212</v>
+        <v>0.1213</v>
       </c>
       <c r="J133" t="n">
         <v>0.0065</v>
@@ -36656,7 +36656,7 @@
         <v>0.7799</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1856</v>
+        <v>-0.1857</v>
       </c>
       <c r="J139" t="n">
         <v>0.1223</v>
@@ -36771,7 +36771,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4074</v>
+        <v>0.4073</v>
       </c>
       <c r="C143" t="n">
         <v>0.1661</v>
@@ -37064,7 +37064,7 @@
         <v>0.8136</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0046</v>
+        <v>0.0047</v>
       </c>
       <c r="J151" t="n">
         <v>0.5768</v>
@@ -37098,7 +37098,7 @@
         <v>0.8136</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0424</v>
+        <v>0.0425</v>
       </c>
       <c r="J152" t="n">
         <v>0.7073</v>
@@ -37166,7 +37166,7 @@
         <v>0.8182</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0144</v>
+        <v>0.0145</v>
       </c>
       <c r="J154" t="n">
         <v>0.7322</v>
@@ -37302,7 +37302,7 @@
         <v>0.7964</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1037</v>
+        <v>0.1038</v>
       </c>
       <c r="J158" t="n">
         <v>1.0058</v>
@@ -37370,7 +37370,7 @@
         <v>0.8351</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0058</v>
+        <v>-0.0057</v>
       </c>
       <c r="J160" t="n">
         <v>1.0232</v>
@@ -37392,7 +37392,7 @@
         <v>0.7344000000000001</v>
       </c>
       <c r="E161" t="n">
-        <v>0.6362</v>
+        <v>0.6363</v>
       </c>
       <c r="F161" t="n">
         <v>0.7344000000000001</v>
@@ -37472,7 +37472,7 @@
         <v>0.8315</v>
       </c>
       <c r="I163" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J163" t="n">
         <v>1.2078</v>
@@ -37506,7 +37506,7 @@
         <v>0.8315</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1134</v>
+        <v>0.1135</v>
       </c>
       <c r="J164" t="n">
         <v>1.2107</v>
@@ -37655,7 +37655,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.7222</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="C169" t="n">
         <v>0.4257</v>
@@ -37710,7 +37710,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0387</v>
+        <v>-0.0386</v>
       </c>
       <c r="J170" t="n">
         <v>1.5391</v>
@@ -37791,7 +37791,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.7934</v>
+        <v>0.7935</v>
       </c>
       <c r="C173" t="n">
         <v>0.5595</v>
@@ -37846,7 +37846,7 @@
         <v>0.9594</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0772</v>
       </c>
       <c r="J174" t="n">
         <v>1.6762</v>
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="C176" t="n">
         <v>0.6075</v>
@@ -37948,7 +37948,7 @@
         <v>0.9559</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1855</v>
+        <v>-0.1854</v>
       </c>
       <c r="J177" t="n">
         <v>1.8036</v>
@@ -38084,7 +38084,7 @@
         <v>0.0902</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1477</v>
+        <v>-0.1476</v>
       </c>
       <c r="J181" t="n">
         <v>1.9524</v>
@@ -38118,7 +38118,7 @@
         <v>0.0902</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1755</v>
+        <v>-0.1754</v>
       </c>
       <c r="J182" t="n">
         <v>2.0487</v>
@@ -38152,7 +38152,7 @@
         <v>0.0902</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1911</v>
+        <v>-0.191</v>
       </c>
       <c r="J183" t="n">
         <v>2.1734</v>
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.4257</v>
+        <v>0.4258</v>
       </c>
       <c r="C187" t="n">
         <v>0.5393</v>
@@ -38288,7 +38288,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1873</v>
+        <v>-0.1872</v>
       </c>
       <c r="J187" t="n">
         <v>2.2679</v>
@@ -38369,7 +38369,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.3013</v>
+        <v>0.3014</v>
       </c>
       <c r="C190" t="n">
         <v>0.3714</v>
@@ -38390,7 +38390,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1239</v>
+        <v>-0.1238</v>
       </c>
       <c r="J190" t="n">
         <v>1.5322</v>
@@ -38424,7 +38424,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0833</v>
+        <v>-0.0832</v>
       </c>
       <c r="J191" t="n">
         <v>1.307</v>
@@ -38471,7 +38471,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2137</v>
+        <v>0.2138</v>
       </c>
       <c r="C193" t="n">
         <v>0.2348</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1276</v>
+        <v>0.1277</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1995</v>
+        <v>0.1996</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2438</v>
+        <v>0.2439</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38650,7 +38650,7 @@
         <v>0.1608</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0569</v>
+        <v>0.057</v>
       </c>
       <c r="F198" t="n">
         <v>0.1608</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.298</v>
+        <v>0.2981</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38743,7 +38743,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.1443</v>
+        <v>0.1444</v>
       </c>
       <c r="C201" t="n">
         <v>-0.2562</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3181</v>
+        <v>0.3182</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4046</v>
+        <v>0.4047</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.417</v>
+        <v>0.4171</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4515</v>
+        <v>0.4516</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -38879,7 +38879,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5651</v>
+        <v>0.5652</v>
       </c>
       <c r="C205" t="n">
         <v>-0.4359</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.457</v>
+        <v>0.4571</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38934,7 +38934,7 @@
         <v>0.2178</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4476</v>
+        <v>0.4477</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2505</v>
@@ -38968,7 +38968,7 @@
         <v>0.2178</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4628</v>
+        <v>0.4629</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2897</v>
@@ -39002,7 +39002,7 @@
         <v>0.4029</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4929</v>
+        <v>0.493</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2483</v>
@@ -39015,7 +39015,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.605</v>
+        <v>0.6051</v>
       </c>
       <c r="C209" t="n">
         <v>-0.5758</v>
@@ -39024,7 +39024,7 @@
         <v>1.2979</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4318</v>
+        <v>0.4319</v>
       </c>
       <c r="F209" t="n">
         <v>1.2979</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6355</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7788</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39117,7 +39117,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.6995</v>
+        <v>0.6996</v>
       </c>
       <c r="C212" t="n">
         <v>-0.7396</v>
@@ -39160,7 +39160,7 @@
         <v>1.5657</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5359</v>
+        <v>0.536</v>
       </c>
       <c r="F213" t="n">
         <v>1.5657</v>
@@ -39185,7 +39185,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8514</v>
       </c>
       <c r="C214" t="n">
         <v>-0.7835</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9425</v>
+        <v>0.9426</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.0129</v>
+        <v>1.013</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9528</v>
+        <v>0.9529</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39287,7 +39287,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.8216</v>
+        <v>0.8217</v>
       </c>
       <c r="C217" t="n">
         <v>-0.9187</v>
@@ -39296,7 +39296,7 @@
         <v>1.562</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6365</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="F217" t="n">
         <v>1.562</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8222</v>
+        <v>0.8223</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39342,7 +39342,7 @@
         <v>0.7019</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7516</v>
       </c>
       <c r="J218" t="n">
         <v>0.1401</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8458</v>
+        <v>0.8459</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9464</v>
+        <v>0.9465</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.9902</v>
+        <v>0.9903</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39500,7 +39500,7 @@
         <v>1.7742</v>
       </c>
       <c r="E223" t="n">
-        <v>0.7942</v>
+        <v>0.7943</v>
       </c>
       <c r="F223" t="n">
         <v>1.7742</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0733</v>
+        <v>1.0734</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.092</v>
+        <v>1.0921</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1811</v>
+        <v>1.1812</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2507</v>
+        <v>1.2508</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2807</v>
+        <v>1.2808</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39670,7 +39670,7 @@
         <v>1.3813</v>
       </c>
       <c r="E228" t="n">
-        <v>0.87</v>
+        <v>0.8701</v>
       </c>
       <c r="F228" t="n">
         <v>1.3813</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3537</v>
+        <v>1.3538</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2816</v>
+        <v>1.2817</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39729,7 +39729,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.9902</v>
+        <v>0.9903</v>
       </c>
       <c r="C230" t="n">
         <v>-1.8168</v>
@@ -39738,7 +39738,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9442</v>
+        <v>0.9443</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3859</v>
+        <v>1.386</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39763,7 +39763,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0653</v>
+        <v>1.0654</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5293</v>
+        <v>1.5294</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5954</v>
+        <v>1.5956</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6583</v>
+        <v>1.6585</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.069</v>
+        <v>1.0691</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.705</v>
+        <v>1.7052</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39899,7 +39899,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.0961</v>
+        <v>1.0962</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -39908,7 +39908,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.036</v>
+        <v>1.0361</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7884</v>
+        <v>1.7885</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39942,7 +39942,7 @@
         <v>1.3708</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0234</v>
+        <v>1.0235</v>
       </c>
       <c r="F236" t="n">
         <v>1.3708</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8246</v>
+        <v>1.8248</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5962</v>
+        <v>1.5964</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40001,7 +40001,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9845</v>
+        <v>0.9846</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5824</v>
+        <v>1.5825</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40044,7 +40044,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9727</v>
+        <v>0.9728</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7481</v>
+        <v>1.7482</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40078,7 +40078,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9692</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.825</v>
+        <v>1.8251</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8448</v>
+        <v>1.8449</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40146,7 +40146,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9438</v>
+        <v>0.9439</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9185</v>
+        <v>1.9187</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40171,7 +40171,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9933</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40180,7 +40180,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9152</v>
+        <v>0.9153</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8515</v>
+        <v>1.8517</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8052</v>
+        <v>1.8053</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40248,7 +40248,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8651</v>
+        <v>0.8652</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.678</v>
+        <v>1.6781</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7759</v>
+        <v>1.776</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8061</v>
+        <v>1.8063</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40350,7 +40350,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8606</v>
+        <v>0.8607</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9236</v>
+        <v>1.9238</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9349</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40384,7 +40384,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8895</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9919</v>
+        <v>1.9921</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40418,7 +40418,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8794</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0593</v>
+        <v>2.0595</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40452,7 +40452,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.927</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2372</v>
+        <v>2.2375</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40486,7 +40486,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9412</v>
+        <v>0.9413</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3659</v>
+        <v>2.3661</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40511,7 +40511,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7558</v>
+        <v>0.7559</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40520,7 +40520,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9363</v>
+        <v>0.9364</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3913</v>
+        <v>2.3915</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4998</v>
+        <v>2.5</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.579</v>
+        <v>2.5793</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8253</v>
+        <v>0.8254</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6017</v>
+        <v>2.602</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7552</v>
+        <v>0.7553</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40656,7 +40656,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8636</v>
+        <v>0.8637</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.731</v>
+        <v>2.7313</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7973</v>
+        <v>0.7974</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8847</v>
+        <v>2.8851</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8337</v>
+        <v>0.8338</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9611</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0798</v>
+        <v>3.0802</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9564</v>
+        <v>0.9552</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9564</v>
+        <v>0.9552</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0611</v>
+        <v>3.0562</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.96</t>
+          <t>+0.95</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-0.542</v>
+        <v>-0.543</v>
       </c>
     </row>
     <row r="8">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.96 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.95 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>-1.168</v>
+        <v>-1.169</v>
       </c>
     </row>
     <row r="69">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>0.977</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="248">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.955</v>
+        <v>0.954</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.195</v>
+        <v>1.197</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.44</v>
+        <v>1.444</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.991</v>
+        <v>1.993</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.921</v>
+        <v>3.925</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.785</v>
+        <v>-0.782</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.236</v>
+        <v>-0.234</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.972</v>
+        <v>0.973</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67129.448</v>
+        <v>66844.685</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1948</v>
+        <v>1.1972</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4403</v>
+        <v>1.4437</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9915</v>
+        <v>1.9932</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7707</v>
+        <v>2.7713</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9215</v>
+        <v>3.9246</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.7845</v>
+        <v>-0.7821</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2364</v>
+        <v>-0.2336</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9719</v>
+        <v>0.9725</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>67129.4479</v>
+        <v>66844.685</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32100,7 +32100,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.544</v>
+        <v>-0.5441</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5114</v>
@@ -32168,7 +32168,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4863</v>
+        <v>-0.4864</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5085</v>
@@ -32258,7 +32258,7 @@
         <v>0.0931</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.633</v>
+        <v>-0.6331</v>
       </c>
       <c r="F10" t="n">
         <v>0.0931</v>
@@ -32440,7 +32440,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.145</v>
+        <v>-0.1451</v>
       </c>
       <c r="J15" t="n">
         <v>-1.1259</v>
@@ -32589,7 +32589,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.4455</v>
+        <v>-0.4456</v>
       </c>
       <c r="C20" t="n">
         <v>-0.2827</v>
@@ -33188,7 +33188,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2309</v>
+        <v>-0.231</v>
       </c>
       <c r="J37" t="n">
         <v>0.1592</v>
@@ -33235,7 +33235,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.4108</v>
+        <v>-0.4109</v>
       </c>
       <c r="C39" t="n">
         <v>-0.2966</v>
@@ -33290,7 +33290,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5597</v>
+        <v>-0.5598</v>
       </c>
       <c r="J40" t="n">
         <v>0.3628</v>
@@ -33358,7 +33358,7 @@
         <v>-1.0531</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5292</v>
+        <v>-0.5293</v>
       </c>
       <c r="J42" t="n">
         <v>0.4876</v>
@@ -33392,7 +33392,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5211</v>
+        <v>-0.5212</v>
       </c>
       <c r="J43" t="n">
         <v>0.5449000000000001</v>
@@ -33439,7 +33439,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4098</v>
+        <v>-0.4099</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3257</v>
@@ -33494,7 +33494,7 @@
         <v>-1.781</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6502</v>
+        <v>-0.6503</v>
       </c>
       <c r="J46" t="n">
         <v>0.7907999999999999</v>
@@ -33528,7 +33528,7 @@
         <v>-1.781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8549</v>
+        <v>-0.855</v>
       </c>
       <c r="J47" t="n">
         <v>0.7421</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9371</v>
+        <v>-0.9372</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0585</v>
+        <v>-1.0586</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1056</v>
+        <v>-1.1057</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33643,7 +33643,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.8339</v>
+        <v>-0.834</v>
       </c>
       <c r="C51" t="n">
         <v>0.2917</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.118</v>
+        <v>-1.1181</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.998</v>
+        <v>-0.9981</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33834,7 +33834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0544</v>
+        <v>-1.0545</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2426</v>
@@ -33847,7 +33847,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2978</v>
+        <v>-1.2979</v>
       </c>
       <c r="C57" t="n">
         <v>1.0128</v>
@@ -33868,7 +33868,7 @@
         <v>-2.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0158</v>
+        <v>-1.0159</v>
       </c>
       <c r="J57" t="n">
         <v>-0.437</v>
@@ -33881,7 +33881,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.247</v>
+        <v>-1.2471</v>
       </c>
       <c r="C58" t="n">
         <v>0.9933</v>
@@ -33915,7 +33915,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.2842</v>
+        <v>-1.2843</v>
       </c>
       <c r="C59" t="n">
         <v>0.9619</v>
@@ -33936,7 +33936,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1098</v>
+        <v>-1.1099</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8135</v>
@@ -33970,7 +33970,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1252</v>
+        <v>-1.1253</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -34004,7 +34004,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1056</v>
+        <v>-1.1057</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1631</v>
@@ -34038,7 +34038,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0695</v>
+        <v>-1.0696</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3324</v>
@@ -34072,7 +34072,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0993</v>
+        <v>-1.0994</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4556</v>
@@ -34140,7 +34140,7 @@
         <v>-2.117</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0365</v>
+        <v>-1.0366</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8128</v>
@@ -34174,7 +34174,7 @@
         <v>-2.117</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0786</v>
+        <v>-1.0787</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9613</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.1002</v>
+        <v>-1.1003</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1679</v>
+        <v>-1.168</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34276,7 +34276,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2029</v>
+        <v>-1.203</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0543</v>
@@ -34310,7 +34310,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2208</v>
+        <v>-1.2209</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9591</v>
@@ -34344,7 +34344,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2542</v>
+        <v>-1.2543</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9205</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2411</v>
+        <v>-1.2412</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34391,7 +34391,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9532</v>
+        <v>-0.9533</v>
       </c>
       <c r="C73" t="n">
         <v>0.4411</v>
@@ -34446,7 +34446,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2286</v>
+        <v>-1.2287</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8283</v>
@@ -34459,7 +34459,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9416</v>
+        <v>-0.9417</v>
       </c>
       <c r="C75" t="n">
         <v>0.3874</v>
@@ -34480,7 +34480,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2186</v>
+        <v>-1.2187</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8065</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2495</v>
+        <v>-1.2496</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2165</v>
+        <v>-1.2166</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34582,7 +34582,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.256</v>
+        <v>-1.2561</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6257</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2783</v>
+        <v>-1.2784</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3263</v>
+        <v>-1.3264</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34697,7 +34697,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.6258</v>
+        <v>-0.6259</v>
       </c>
       <c r="C82" t="n">
         <v>0.2131</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3392</v>
+        <v>-1.3393</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34774,7 +34774,7 @@
         <v>0.1353</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8499</v>
+        <v>-0.85</v>
       </c>
       <c r="F84" t="n">
         <v>0.1353</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.331</v>
+        <v>-1.3311</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34833,7 +34833,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5849</v>
+        <v>-0.585</v>
       </c>
       <c r="C86" t="n">
         <v>0.0257</v>
@@ -34854,7 +34854,7 @@
         <v>-0.573</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3535</v>
+        <v>-1.3536</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1193</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2201</v>
+        <v>-1.2202</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -34956,7 +34956,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2437</v>
+        <v>-1.2438</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0865</v>
@@ -34978,7 +34978,7 @@
         <v>0.2133</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.6884</v>
+        <v>-0.6885</v>
       </c>
       <c r="F90" t="n">
         <v>0.2133</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2978</v>
+        <v>-1.2979</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35003,7 +35003,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.4851</v>
+        <v>-0.4852</v>
       </c>
       <c r="C91" t="n">
         <v>-0.1676</v>
@@ -35037,7 +35037,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.4716</v>
+        <v>-0.4717</v>
       </c>
       <c r="C92" t="n">
         <v>-0.2331</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3017</v>
+        <v>-1.3018</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35114,7 +35114,7 @@
         <v>0.2718</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5713</v>
+        <v>-0.5714</v>
       </c>
       <c r="F94" t="n">
         <v>0.2718</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3114</v>
+        <v>-1.3115</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35139,7 +35139,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.3951</v>
+        <v>-0.3952</v>
       </c>
       <c r="C95" t="n">
         <v>-0.2685</v>
@@ -35148,7 +35148,7 @@
         <v>0.272</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5619</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="F95" t="n">
         <v>0.272</v>
@@ -35160,7 +35160,7 @@
         <v>-0.247</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2984</v>
+        <v>-1.2985</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7848000000000001</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.2021</v>
+        <v>-1.2022</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35262,7 +35262,7 @@
         <v>-0.201</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0636</v>
+        <v>-1.0637</v>
       </c>
       <c r="J98" t="n">
         <v>-0.615</v>
@@ -35364,7 +35364,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8395</v>
+        <v>-0.8396</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4122</v>
@@ -35386,7 +35386,7 @@
         <v>0.2469</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.2594</v>
+        <v>-0.2595</v>
       </c>
       <c r="F102" t="n">
         <v>0.2469</v>
@@ -35398,7 +35398,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7409</v>
+        <v>-0.741</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4036</v>
@@ -35420,7 +35420,7 @@
         <v>0.3913</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2362</v>
+        <v>-0.2363</v>
       </c>
       <c r="F103" t="n">
         <v>0.3913</v>
@@ -35534,7 +35534,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7149</v>
+        <v>-0.715</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3611</v>
@@ -35547,7 +35547,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.0018</v>
+        <v>-0.0019</v>
       </c>
       <c r="C107" t="n">
         <v>-0.5917</v>
@@ -35602,7 +35602,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6503</v>
+        <v>-0.6504</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2887</v>
@@ -35636,7 +35636,7 @@
         <v>0.1473</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5568</v>
+        <v>-0.5569</v>
       </c>
       <c r="J109" t="n">
         <v>-0.2918</v>
@@ -35670,7 +35670,7 @@
         <v>0.1473</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5417</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J110" t="n">
         <v>-0.3002</v>
@@ -35704,7 +35704,7 @@
         <v>0.1473</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5654</v>
+        <v>-0.5655</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2361</v>
@@ -35738,7 +35738,7 @@
         <v>0.174</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5494</v>
+        <v>-0.5495</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2387</v>
@@ -35751,7 +35751,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.3083</v>
+        <v>0.3082</v>
       </c>
       <c r="C113" t="n">
         <v>-0.6818</v>
@@ -35964,7 +35964,7 @@
         <v>1.5824</v>
       </c>
       <c r="E119" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F119" t="n">
         <v>1.5824</v>
@@ -36316,7 +36316,7 @@
         <v>0.4759</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1447</v>
+        <v>0.1448</v>
       </c>
       <c r="J129" t="n">
         <v>-0.0706</v>
@@ -37200,7 +37200,7 @@
         <v>0.8182</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0873</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J155" t="n">
         <v>0.8493000000000001</v>
@@ -37349,7 +37349,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.6605</v>
+        <v>0.6606</v>
       </c>
       <c r="C160" t="n">
         <v>0.2995</v>
@@ -37460,7 +37460,7 @@
         <v>0.7772</v>
       </c>
       <c r="E163" t="n">
-        <v>0.6965</v>
+        <v>0.6966</v>
       </c>
       <c r="F163" t="n">
         <v>0.7772</v>
@@ -37485,7 +37485,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.7163</v>
+        <v>0.7164</v>
       </c>
       <c r="C164" t="n">
         <v>0.3525</v>
@@ -37528,7 +37528,7 @@
         <v>0.8058999999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>0.7247</v>
+        <v>0.7248</v>
       </c>
       <c r="F165" t="n">
         <v>0.8058999999999999</v>
@@ -37596,7 +37596,7 @@
         <v>0.8496</v>
       </c>
       <c r="E167" t="n">
-        <v>0.7528</v>
+        <v>0.7529</v>
       </c>
       <c r="F167" t="n">
         <v>0.8496</v>
@@ -37642,7 +37642,7 @@
         <v>0.8931</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1023</v>
+        <v>0.1024</v>
       </c>
       <c r="J168" t="n">
         <v>1.4434</v>
@@ -37676,7 +37676,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0459</v>
+        <v>0.046</v>
       </c>
       <c r="J169" t="n">
         <v>1.4197</v>
@@ -37744,7 +37744,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0209</v>
+        <v>-0.0208</v>
       </c>
       <c r="J171" t="n">
         <v>1.5073</v>
@@ -37800,7 +37800,7 @@
         <v>0.8367</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7826</v>
+        <v>0.7827</v>
       </c>
       <c r="F173" t="n">
         <v>0.8367</v>
@@ -37880,7 +37880,7 @@
         <v>0.9559</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1228</v>
+        <v>-0.1227</v>
       </c>
       <c r="J175" t="n">
         <v>1.8105</v>
@@ -38016,7 +38016,7 @@
         <v>0.4553</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1673</v>
+        <v>-0.1672</v>
       </c>
       <c r="J179" t="n">
         <v>1.9402</v>
@@ -38050,7 +38050,7 @@
         <v>0.4553</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1553</v>
+        <v>-0.1552</v>
       </c>
       <c r="J180" t="n">
         <v>1.9104</v>
@@ -38220,7 +38220,7 @@
         <v>-0.4422</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2967</v>
+        <v>-0.2966</v>
       </c>
       <c r="J185" t="n">
         <v>2.1134</v>
@@ -38322,7 +38322,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1686</v>
+        <v>-0.1685</v>
       </c>
       <c r="J188" t="n">
         <v>2.0124</v>
@@ -38356,7 +38356,7 @@
         <v>-0.8486</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1322</v>
+        <v>-0.1321</v>
       </c>
       <c r="J189" t="n">
         <v>1.7736</v>
@@ -38378,7 +38378,7 @@
         <v>0.2578</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3122</v>
+        <v>0.3123</v>
       </c>
       <c r="F190" t="n">
         <v>0.2578</v>
@@ -38458,7 +38458,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0373</v>
+        <v>-0.0372</v>
       </c>
       <c r="J192" t="n">
         <v>1.0409</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38514,7 +38514,7 @@
         <v>0.1218</v>
       </c>
       <c r="E194" t="n">
-        <v>0.185</v>
+        <v>0.1851</v>
       </c>
       <c r="F194" t="n">
         <v>0.1218</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0648</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38539,7 +38539,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.1581</v>
+        <v>0.1582</v>
       </c>
       <c r="C195" t="n">
         <v>0.1813</v>
@@ -38548,7 +38548,7 @@
         <v>0.1957</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1487</v>
+        <v>0.1488</v>
       </c>
       <c r="F195" t="n">
         <v>0.1957</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1277</v>
+        <v>0.1278</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38573,7 +38573,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.179</v>
+        <v>0.1791</v>
       </c>
       <c r="C196" t="n">
         <v>0.031</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1996</v>
+        <v>0.1997</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2439</v>
+        <v>0.244</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2509</v>
+        <v>0.251</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2981</v>
+        <v>0.2982</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3045</v>
+        <v>0.3046</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3182</v>
+        <v>0.3183</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4047</v>
+        <v>0.4048</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38811,7 +38811,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.2367</v>
+        <v>0.2368</v>
       </c>
       <c r="C203" t="n">
         <v>-0.2987</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4171</v>
+        <v>0.4172</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4571</v>
+        <v>0.4572</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38934,7 +38934,7 @@
         <v>0.2178</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4477</v>
+        <v>0.4478</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2505</v>
@@ -39002,7 +39002,7 @@
         <v>0.4029</v>
       </c>
       <c r="I208" t="n">
-        <v>0.493</v>
+        <v>0.4931</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2483</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6829</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7788</v>
+        <v>0.7789</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8158</v>
+        <v>0.8159</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.839</v>
+        <v>0.8391</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9426</v>
+        <v>0.9427</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39219,7 +39219,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.8951</v>
+        <v>0.8952</v>
       </c>
       <c r="C215" t="n">
         <v>-0.8632</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9529</v>
+        <v>0.953</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8223</v>
+        <v>0.8224</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39376,7 +39376,7 @@
         <v>0.7019</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8239</v>
+        <v>0.824</v>
       </c>
       <c r="J219" t="n">
         <v>0.2448</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.826</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39466,7 +39466,7 @@
         <v>1.724</v>
       </c>
       <c r="E222" t="n">
-        <v>0.7363</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="F222" t="n">
         <v>1.724</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9465</v>
+        <v>0.9466</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0734</v>
+        <v>1.0735</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0921</v>
+        <v>1.0923</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1812</v>
+        <v>1.1813</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2508</v>
+        <v>1.251</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39627,7 +39627,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.9921</v>
+        <v>0.9922</v>
       </c>
       <c r="C227" t="n">
         <v>-1.4189</v>
@@ -39636,7 +39636,7 @@
         <v>1.5257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8587</v>
+        <v>0.8588</v>
       </c>
       <c r="F227" t="n">
         <v>1.5257</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2808</v>
+        <v>1.2809</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3538</v>
+        <v>1.3539</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39695,7 +39695,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1.0012</v>
+        <v>1.0013</v>
       </c>
       <c r="C229" t="n">
         <v>-1.3839</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2817</v>
+        <v>1.2818</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.386</v>
+        <v>1.3861</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39772,7 +39772,7 @@
         <v>1.4899</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9593</v>
       </c>
       <c r="F231" t="n">
         <v>1.4899</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5294</v>
+        <v>1.5296</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39797,7 +39797,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0873</v>
+        <v>1.0874</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39806,7 +39806,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0133</v>
+        <v>1.0134</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5956</v>
+        <v>1.5958</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39840,7 +39840,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0124</v>
+        <v>1.0125</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6585</v>
+        <v>1.6586</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39874,7 +39874,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.0119</v>
+        <v>1.012</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7052</v>
+        <v>1.7054</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7885</v>
+        <v>1.7887</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39933,7 +39933,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0929</v>
+        <v>1.093</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8248</v>
+        <v>1.825</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39976,7 +39976,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9336</v>
+        <v>0.9337</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5964</v>
+        <v>1.5965</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5825</v>
+        <v>1.5827</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40035,7 +40035,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.0073</v>
+        <v>1.0074</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7482</v>
+        <v>1.7484</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8251</v>
+        <v>1.8253</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40103,7 +40103,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0318</v>
+        <v>1.0319</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8449</v>
+        <v>1.8451</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40137,7 +40137,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.042</v>
+        <v>1.0421</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9187</v>
+        <v>1.9188</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8517</v>
+        <v>1.8518</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40214,7 +40214,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9507</v>
+        <v>0.9508</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8053</v>
+        <v>1.8055</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40239,7 +40239,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.0073</v>
+        <v>1.0074</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6781</v>
+        <v>1.6782</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.776</v>
+        <v>1.7762</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40316,7 +40316,7 @@
         <v>1.4541</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8583</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="F247" t="n">
         <v>1.4541</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8063</v>
+        <v>1.8064</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9238</v>
+        <v>1.9239</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9921</v>
+        <v>1.9923</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0595</v>
+        <v>2.0597</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40443,7 +40443,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9887</v>
+        <v>0.9888</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2375</v>
+        <v>2.2377</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.995</v>
+        <v>0.9951</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3661</v>
+        <v>2.3664</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40520,7 +40520,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9364</v>
+        <v>0.9365</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3915</v>
+        <v>2.3918</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8852</v>
+        <v>0.8853</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9454</v>
+        <v>0.9455</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.5</v>
+        <v>2.5003</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40579,7 +40579,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8471</v>
+        <v>0.8472</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9482</v>
+        <v>0.9483</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5793</v>
+        <v>2.5796</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9092</v>
+        <v>0.9093</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.602</v>
+        <v>2.6023</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40647,7 +40647,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7553</v>
+        <v>0.7554</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7313</v>
+        <v>2.7316</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40681,7 +40681,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7974</v>
+        <v>0.7975</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9234</v>
+        <v>0.9235</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8851</v>
+        <v>2.8854</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8338</v>
+        <v>0.8339</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9613</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0802</v>
+        <v>3.0806</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9552</v>
+        <v>0.9539</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9552</v>
+        <v>0.9539</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0562</v>
+        <v>3.051</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>0.592</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="182">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="259">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.954</v>
+        <v>0.953</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.197</v>
+        <v>1.199</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.444</v>
+        <v>1.446</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.993</v>
+        <v>1.994</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.782</v>
+        <v>-0.78</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.234</v>
+        <v>-0.232</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.973</v>
+        <v>0.972</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66844.685</v>
+        <v>66607.673</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1972</v>
+        <v>1.1989</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4437</v>
+        <v>1.4459</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9932</v>
+        <v>1.9935</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7713</v>
+        <v>2.7706</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9246</v>
+        <v>3.9254</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.7821</v>
+        <v>-0.7804</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2336</v>
+        <v>-0.2321</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9725</v>
+        <v>0.9718</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>66844.685</v>
+        <v>66607.67290000001</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -31989,7 +31989,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6103</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="D2" t="n">
         <v>0.2573</v>
@@ -32004,7 +32004,7 @@
         <v>-0.3417</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6428</v>
+        <v>-0.6429</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7141</v>
@@ -32032,7 +32032,7 @@
         <v>-0.3193</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.589</v>
+        <v>-0.5891</v>
       </c>
       <c r="J3" t="n">
         <v>-1.636</v>
@@ -32066,7 +32066,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5655</v>
+        <v>-0.5656</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6448</v>
@@ -32134,7 +32134,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5333</v>
+        <v>-0.5334</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4181</v>
@@ -32202,7 +32202,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4057</v>
+        <v>-0.4058</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3584</v>
@@ -32236,7 +32236,7 @@
         <v>-0.3381</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4088</v>
+        <v>-0.4089</v>
       </c>
       <c r="J9" t="n">
         <v>-1.39</v>
@@ -32270,7 +32270,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3832</v>
+        <v>-0.3833</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2447</v>
@@ -32338,7 +32338,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1989</v>
+        <v>-0.199</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2069</v>
@@ -32372,7 +32372,7 @@
         <v>-0.1787</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1748</v>
+        <v>-0.1749</v>
       </c>
       <c r="J13" t="n">
         <v>-1.1973</v>
@@ -32555,7 +32555,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.4419</v>
+        <v>-0.442</v>
       </c>
       <c r="C19" t="n">
         <v>-0.4789</v>
@@ -32610,7 +32610,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1337</v>
+        <v>-0.1338</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8238</v>
@@ -32644,7 +32644,7 @@
         <v>-0.1119</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1039</v>
+        <v>-0.104</v>
       </c>
       <c r="J21" t="n">
         <v>-0.7688</v>
@@ -32814,7 +32814,7 @@
         <v>0.1817</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0447</v>
+        <v>0.0446</v>
       </c>
       <c r="J26" t="n">
         <v>-0.4886</v>
@@ -33154,7 +33154,7 @@
         <v>-0.221</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2268</v>
+        <v>-0.2269</v>
       </c>
       <c r="J36" t="n">
         <v>0.0709</v>
@@ -33256,7 +33256,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4165</v>
+        <v>-0.4166</v>
       </c>
       <c r="J39" t="n">
         <v>0.2403</v>
@@ -33380,7 +33380,7 @@
         <v>0.7408</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.8078</v>
+        <v>-0.8079</v>
       </c>
       <c r="F43" t="n">
         <v>0.7408</v>
@@ -33460,7 +33460,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5573</v>
+        <v>-0.5574</v>
       </c>
       <c r="J45" t="n">
         <v>0.7429</v>
@@ -33528,7 +33528,7 @@
         <v>-1.781</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.855</v>
+        <v>-0.8551</v>
       </c>
       <c r="J47" t="n">
         <v>0.7421</v>
@@ -33541,7 +33541,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6374</v>
+        <v>-0.6375</v>
       </c>
       <c r="C48" t="n">
         <v>-0.2059</v>
@@ -33562,7 +33562,7 @@
         <v>-1.781</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9372</v>
+        <v>-0.9373</v>
       </c>
       <c r="J48" t="n">
         <v>0.784</v>
@@ -33596,7 +33596,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0586</v>
+        <v>-1.0587</v>
       </c>
       <c r="J49" t="n">
         <v>0.9838</v>
@@ -33630,7 +33630,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1057</v>
+        <v>-1.1058</v>
       </c>
       <c r="J50" t="n">
         <v>0.7658</v>
@@ -33664,7 +33664,7 @@
         <v>-2.2469</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1181</v>
+        <v>-1.1182</v>
       </c>
       <c r="J51" t="n">
         <v>0.6089</v>
@@ -33698,7 +33698,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.025</v>
+        <v>-1.0251</v>
       </c>
       <c r="J52" t="n">
         <v>0.4752</v>
@@ -33720,7 +33720,7 @@
         <v>0.0622</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2345</v>
+        <v>-1.2346</v>
       </c>
       <c r="F53" t="n">
         <v>0.0622</v>
@@ -33766,7 +33766,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.024</v>
+        <v>-1.0241</v>
       </c>
       <c r="J54" t="n">
         <v>0.1097</v>
@@ -33800,7 +33800,7 @@
         <v>-2.97</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9981</v>
+        <v>-0.9982</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0197</v>
@@ -33822,7 +33822,7 @@
         <v>-0.8145</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.3553</v>
+        <v>-1.3554</v>
       </c>
       <c r="F56" t="n">
         <v>-0.8145</v>
@@ -33902,7 +33902,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0947</v>
+        <v>-1.0948</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5746</v>
@@ -33936,7 +33936,7 @@
         <v>-2.6673</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1099</v>
+        <v>-1.11</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8135</v>
@@ -34051,7 +34051,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.193</v>
+        <v>-1.1931</v>
       </c>
       <c r="C63" t="n">
         <v>0.7577</v>
@@ -34060,7 +34060,7 @@
         <v>-0.2126</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.4381</v>
+        <v>-1.4382</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2126</v>
@@ -34072,7 +34072,7 @@
         <v>-2.4372</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0994</v>
+        <v>-1.0995</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4556</v>
@@ -34085,7 +34085,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1629</v>
+        <v>-1.163</v>
       </c>
       <c r="C64" t="n">
         <v>0.6857</v>
@@ -34106,7 +34106,7 @@
         <v>-2.117</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.078</v>
+        <v>-1.0781</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6903</v>
@@ -34153,7 +34153,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.1866</v>
+        <v>-1.1867</v>
       </c>
       <c r="C66" t="n">
         <v>0.585</v>
@@ -34174,7 +34174,7 @@
         <v>-2.117</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0787</v>
+        <v>-1.0788</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9613</v>
@@ -34208,7 +34208,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.1003</v>
+        <v>-1.1004</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1297</v>
@@ -34242,7 +34242,7 @@
         <v>-1.7838</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.168</v>
+        <v>-1.1681</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1031</v>
@@ -34332,7 +34332,7 @@
         <v>-0.1096</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2464</v>
+        <v>-1.2465</v>
       </c>
       <c r="F71" t="n">
         <v>-0.1096</v>
@@ -34400,7 +34400,7 @@
         <v>-0.1169</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1623</v>
+        <v>-1.1624</v>
       </c>
       <c r="F73" t="n">
         <v>-0.1169</v>
@@ -34412,7 +34412,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2026</v>
+        <v>-1.2027</v>
       </c>
       <c r="J73" t="n">
         <v>-1.852</v>
@@ -34480,7 +34480,7 @@
         <v>-1.1759</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2187</v>
+        <v>-1.2188</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8065</v>
@@ -34493,7 +34493,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8249</v>
+        <v>-0.825</v>
       </c>
       <c r="C76" t="n">
         <v>0.2978</v>
@@ -34502,7 +34502,7 @@
         <v>-0.0857</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0097</v>
+        <v>-1.0098</v>
       </c>
       <c r="F76" t="n">
         <v>-0.0857</v>
@@ -34616,7 +34616,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2784</v>
+        <v>-1.2785</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5279</v>
@@ -34650,7 +34650,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.279</v>
+        <v>-1.2791</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5104</v>
@@ -34706,7 +34706,7 @@
         <v>0.3264</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8639</v>
+        <v>-0.864</v>
       </c>
       <c r="F82" t="n">
         <v>0.3264</v>
@@ -34718,7 +34718,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3425</v>
+        <v>-1.3426</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3419</v>
@@ -34752,7 +34752,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3393</v>
+        <v>-1.3394</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3561</v>
@@ -34786,7 +34786,7 @@
         <v>-0.5973000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.326</v>
+        <v>-1.3261</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3183</v>
@@ -34854,7 +34854,7 @@
         <v>-0.573</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3536</v>
+        <v>-1.3537</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1193</v>
@@ -34888,7 +34888,7 @@
         <v>-0.573</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.3016</v>
+        <v>-1.3017</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1278</v>
@@ -34910,7 +34910,7 @@
         <v>0.332</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7187</v>
+        <v>-0.7188</v>
       </c>
       <c r="F88" t="n">
         <v>0.332</v>
@@ -34990,7 +34990,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2979</v>
+        <v>-1.298</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9115</v>
@@ -35024,7 +35024,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.3</v>
+        <v>-1.3001</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9396</v>
@@ -35058,7 +35058,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3039</v>
+        <v>-1.304</v>
       </c>
       <c r="J92" t="n">
         <v>-0.825</v>
@@ -35126,7 +35126,7 @@
         <v>-0.247</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3115</v>
+        <v>-1.3116</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7788</v>
@@ -35173,7 +35173,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3377</v>
+        <v>-0.3378</v>
       </c>
       <c r="C96" t="n">
         <v>-0.2964</v>
@@ -35194,7 +35194,7 @@
         <v>-0.247</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2669</v>
+        <v>-1.267</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5838</v>
@@ -35228,7 +35228,7 @@
         <v>-0.201</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.2022</v>
+        <v>-1.2023</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5628</v>
@@ -35296,7 +35296,7 @@
         <v>-0.201</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9758</v>
+        <v>-0.9759</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5022</v>
@@ -35330,7 +35330,7 @@
         <v>-0.1613</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9265</v>
+        <v>-0.9266</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4986</v>
@@ -35500,7 +35500,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7667</v>
+        <v>-0.7668</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2434</v>
@@ -35568,7 +35568,7 @@
         <v>-0.0391</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.711</v>
+        <v>-0.7111</v>
       </c>
       <c r="J107" t="n">
         <v>-0.2576</v>
@@ -35624,7 +35624,7 @@
         <v>1.4998</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.091</v>
+        <v>-0.0911</v>
       </c>
       <c r="F109" t="n">
         <v>1.4998</v>
@@ -35772,7 +35772,7 @@
         <v>0.174</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.545</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2332</v>
@@ -36214,7 +36214,7 @@
         <v>0.49</v>
       </c>
       <c r="I126" t="n">
-        <v>0.0759</v>
+        <v>0.076</v>
       </c>
       <c r="J126" t="n">
         <v>0.0233</v>
@@ -36928,7 +36928,7 @@
         <v>0.7738</v>
       </c>
       <c r="I147" t="n">
-        <v>0.02</v>
+        <v>0.0201</v>
       </c>
       <c r="J147" t="n">
         <v>0.4469</v>
@@ -37179,7 +37179,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.6491</v>
+        <v>0.6492</v>
       </c>
       <c r="C155" t="n">
         <v>0.2633</v>
@@ -37234,7 +37234,7 @@
         <v>0.8182</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0994</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J156" t="n">
         <v>0.7732</v>
@@ -37268,7 +37268,7 @@
         <v>0.7964</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1244</v>
+        <v>0.1245</v>
       </c>
       <c r="J157" t="n">
         <v>0.8111</v>
@@ -37290,7 +37290,7 @@
         <v>0.7731</v>
       </c>
       <c r="E158" t="n">
-        <v>0.6453</v>
+        <v>0.6454</v>
       </c>
       <c r="F158" t="n">
         <v>0.7731</v>
@@ -37336,7 +37336,7 @@
         <v>0.7964</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0382</v>
+        <v>0.0383</v>
       </c>
       <c r="J159" t="n">
         <v>0.9164</v>
@@ -37404,7 +37404,7 @@
         <v>0.8351</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0286</v>
+        <v>0.0287</v>
       </c>
       <c r="J161" t="n">
         <v>1.0307</v>
@@ -37438,7 +37438,7 @@
         <v>0.8351</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0849</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J162" t="n">
         <v>1.1074</v>
@@ -37540,7 +37540,7 @@
         <v>0.8315</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1029</v>
+        <v>0.103</v>
       </c>
       <c r="J165" t="n">
         <v>1.3214</v>
@@ -37574,7 +37574,7 @@
         <v>0.8931</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1436</v>
+        <v>0.1437</v>
       </c>
       <c r="J166" t="n">
         <v>1.2728</v>
@@ -37608,7 +37608,7 @@
         <v>0.8931</v>
       </c>
       <c r="I167" t="n">
-        <v>0.1133</v>
+        <v>0.1134</v>
       </c>
       <c r="J167" t="n">
         <v>1.3898</v>
@@ -37914,7 +37914,7 @@
         <v>0.9559</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1311</v>
+        <v>-0.131</v>
       </c>
       <c r="J176" t="n">
         <v>1.8233</v>
@@ -37982,7 +37982,7 @@
         <v>0.4553</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1675</v>
+        <v>-0.1674</v>
       </c>
       <c r="J178" t="n">
         <v>1.9327</v>
@@ -38106,7 +38106,7 @@
         <v>0.7829</v>
       </c>
       <c r="E182" t="n">
-        <v>0.6161</v>
+        <v>0.6162</v>
       </c>
       <c r="F182" t="n">
         <v>0.7829</v>
@@ -38186,7 +38186,7 @@
         <v>-0.4422</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3325</v>
+        <v>-0.3324</v>
       </c>
       <c r="J184" t="n">
         <v>2.1142</v>
@@ -38254,7 +38254,7 @@
         <v>-0.4422</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2551</v>
+        <v>-0.255</v>
       </c>
       <c r="J186" t="n">
         <v>2.1834</v>
@@ -38310,7 +38310,7 @@
         <v>0.4361</v>
       </c>
       <c r="E188" t="n">
-        <v>0.37</v>
+        <v>0.3701</v>
       </c>
       <c r="F188" t="n">
         <v>0.4361</v>
@@ -38492,7 +38492,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0002</v>
+        <v>0.0003</v>
       </c>
       <c r="J193" t="n">
         <v>0.856</v>
@@ -38526,7 +38526,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0648</v>
+        <v>0.0649</v>
       </c>
       <c r="J194" t="n">
         <v>0.5555</v>
@@ -38560,7 +38560,7 @@
         <v>-0.4912</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1278</v>
+        <v>0.1279</v>
       </c>
       <c r="J195" t="n">
         <v>0.3569</v>
@@ -38594,7 +38594,7 @@
         <v>-0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1997</v>
+        <v>0.1998</v>
       </c>
       <c r="J196" t="n">
         <v>0.0823</v>
@@ -38641,7 +38641,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="C198" t="n">
         <v>-0.0649</v>
@@ -38662,7 +38662,7 @@
         <v>-0.28</v>
       </c>
       <c r="I198" t="n">
-        <v>0.251</v>
+        <v>0.2511</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4244</v>
@@ -38684,7 +38684,7 @@
         <v>0.2053</v>
       </c>
       <c r="E199" t="n">
-        <v>0.039</v>
+        <v>0.0391</v>
       </c>
       <c r="F199" t="n">
         <v>0.2053</v>
@@ -38696,7 +38696,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2982</v>
+        <v>0.2983</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6657999999999999</v>
@@ -38730,7 +38730,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3046</v>
+        <v>0.3047</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6173</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2614</v>
+        <v>0.2615</v>
       </c>
       <c r="C202" t="n">
         <v>-0.2762</v>
@@ -38786,7 +38786,7 @@
         <v>0.4634</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2109</v>
+        <v>0.211</v>
       </c>
       <c r="F202" t="n">
         <v>0.4634</v>
@@ -38798,7 +38798,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4048</v>
+        <v>0.4049</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4133</v>
@@ -38845,7 +38845,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3005</v>
+        <v>0.3006</v>
       </c>
       <c r="C204" t="n">
         <v>-0.3445</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4516</v>
+        <v>0.4517</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -38888,7 +38888,7 @@
         <v>1.7557</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2675</v>
+        <v>0.2676</v>
       </c>
       <c r="F205" t="n">
         <v>1.7557</v>
@@ -38900,7 +38900,7 @@
         <v>0.2178</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4572</v>
+        <v>0.4573</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3848</v>
@@ -38913,7 +38913,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3435</v>
+        <v>0.3436</v>
       </c>
       <c r="C206" t="n">
         <v>-0.5203</v>
@@ -38922,7 +38922,7 @@
         <v>0.5263</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2978</v>
+        <v>0.2979</v>
       </c>
       <c r="F206" t="n">
         <v>0.5263</v>
@@ -38947,7 +38947,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3679</v>
+        <v>0.368</v>
       </c>
       <c r="C207" t="n">
         <v>-0.5511</v>
@@ -38968,7 +38968,7 @@
         <v>0.2178</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4629</v>
+        <v>0.463</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2897</v>
@@ -38981,7 +38981,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.4264</v>
+        <v>0.4265</v>
       </c>
       <c r="C208" t="n">
         <v>-0.5053</v>
@@ -38990,7 +38990,7 @@
         <v>0.7245</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3519</v>
+        <v>0.352</v>
       </c>
       <c r="F208" t="n">
         <v>0.7245</v>
@@ -39036,7 +39036,7 @@
         <v>0.4029</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6357</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1675</v>
@@ -39070,7 +39070,7 @@
         <v>0.4029</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6831</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1653</v>
@@ -39092,7 +39092,7 @@
         <v>1.3412</v>
       </c>
       <c r="E211" t="n">
-        <v>0.5149</v>
+        <v>0.515</v>
       </c>
       <c r="F211" t="n">
         <v>1.3412</v>
@@ -39138,7 +39138,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8159</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1249</v>
@@ -39172,7 +39172,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8391</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07870000000000001</v>
@@ -39240,7 +39240,7 @@
         <v>0.6149</v>
       </c>
       <c r="I215" t="n">
-        <v>1.013</v>
+        <v>1.0131</v>
       </c>
       <c r="J215" t="n">
         <v>0.031</v>
@@ -39330,7 +39330,7 @@
         <v>2.1396</v>
       </c>
       <c r="E218" t="n">
-        <v>0.6092</v>
+        <v>0.6093</v>
       </c>
       <c r="F218" t="n">
         <v>2.1396</v>
@@ -39342,7 +39342,7 @@
         <v>0.7019</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7516</v>
+        <v>0.7517</v>
       </c>
       <c r="J218" t="n">
         <v>0.1401</v>
@@ -39376,7 +39376,7 @@
         <v>0.7019</v>
       </c>
       <c r="I219" t="n">
-        <v>0.824</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="J219" t="n">
         <v>0.2448</v>
@@ -39398,7 +39398,7 @@
         <v>1.7394</v>
       </c>
       <c r="E220" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.7083</v>
       </c>
       <c r="F220" t="n">
         <v>1.7394</v>
@@ -39410,7 +39410,7 @@
         <v>0.8497</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8262</v>
       </c>
       <c r="J220" t="n">
         <v>0.2702</v>
@@ -39423,7 +39423,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.9381</v>
+        <v>0.9382</v>
       </c>
       <c r="C221" t="n">
         <v>-1.2861</v>
@@ -39444,7 +39444,7 @@
         <v>0.8497</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8459</v>
+        <v>0.846</v>
       </c>
       <c r="J221" t="n">
         <v>0.3116</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0735</v>
+        <v>1.0736</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39534,7 +39534,7 @@
         <v>1.6966</v>
       </c>
       <c r="E224" t="n">
-        <v>0.8032</v>
+        <v>0.8033</v>
       </c>
       <c r="F224" t="n">
         <v>1.6966</v>
@@ -39546,7 +39546,7 @@
         <v>0.8486</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0923</v>
+        <v>1.0924</v>
       </c>
       <c r="J224" t="n">
         <v>0.378</v>
@@ -39568,7 +39568,7 @@
         <v>1.6703</v>
       </c>
       <c r="E225" t="n">
-        <v>0.8289</v>
+        <v>0.829</v>
       </c>
       <c r="F225" t="n">
         <v>1.6703</v>
@@ -39580,7 +39580,7 @@
         <v>0.8486</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1813</v>
+        <v>1.1814</v>
       </c>
       <c r="J225" t="n">
         <v>0.3959</v>
@@ -39614,7 +39614,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>1.251</v>
+        <v>1.2511</v>
       </c>
       <c r="J226" t="n">
         <v>0.3587</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2809</v>
+        <v>1.281</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39661,7 +39661,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9724</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3539</v>
+        <v>1.354</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39704,7 +39704,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8888</v>
+        <v>0.8889</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2818</v>
+        <v>1.2819</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39750,7 +39750,7 @@
         <v>1.051</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3861</v>
+        <v>1.3863</v>
       </c>
       <c r="J230" t="n">
         <v>0.4853</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5296</v>
+        <v>1.5297</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5958</v>
+        <v>1.5959</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39831,7 +39831,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0464</v>
+        <v>1.0465</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -39852,7 +39852,7 @@
         <v>1.1509</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6586</v>
+        <v>1.6588</v>
       </c>
       <c r="J233" t="n">
         <v>0.4754</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7054</v>
+        <v>1.7055</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39908,7 +39908,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0361</v>
+        <v>1.0362</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7887</v>
+        <v>1.7888</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.825</v>
+        <v>1.8251</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5965</v>
+        <v>1.5966</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40010,7 +40010,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9271</v>
+        <v>0.9272</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40022,7 +40022,7 @@
         <v>1.1289</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5827</v>
+        <v>1.5828</v>
       </c>
       <c r="J238" t="n">
         <v>0.5261</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7484</v>
+        <v>1.7485</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40069,7 +40069,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0258</v>
+        <v>1.0259</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8253</v>
+        <v>1.8254</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40112,7 +40112,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9666</v>
+        <v>0.9667</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8451</v>
+        <v>1.8452</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40146,7 +40146,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9439</v>
+        <v>0.944</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40158,7 +40158,7 @@
         <v>1.116</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9188</v>
+        <v>1.919</v>
       </c>
       <c r="J242" t="n">
         <v>0.606</v>
@@ -40192,7 +40192,7 @@
         <v>1.116</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8518</v>
+        <v>1.852</v>
       </c>
       <c r="J243" t="n">
         <v>0.5875</v>
@@ -40205,7 +40205,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.0311</v>
+        <v>1.0312</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8055</v>
+        <v>1.8056</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6782</v>
+        <v>1.6783</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40273,7 +40273,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0333</v>
+        <v>1.0334</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40282,7 +40282,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8968</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40294,7 +40294,7 @@
         <v>1.179</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7762</v>
+        <v>1.7763</v>
       </c>
       <c r="J246" t="n">
         <v>0.6906</v>
@@ -40328,7 +40328,7 @@
         <v>1.081</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8064</v>
+        <v>1.8066</v>
       </c>
       <c r="J247" t="n">
         <v>0.6129</v>
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9485</v>
+        <v>0.9486</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40362,7 +40362,7 @@
         <v>1.081</v>
       </c>
       <c r="I248" t="n">
-        <v>1.9239</v>
+        <v>1.9241</v>
       </c>
       <c r="J248" t="n">
         <v>0.6312</v>
@@ -40384,7 +40384,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8897</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40396,7 +40396,7 @@
         <v>1.081</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9923</v>
+        <v>1.9925</v>
       </c>
       <c r="J249" t="n">
         <v>0.6918</v>
@@ -40409,7 +40409,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9467</v>
+        <v>0.9468</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40418,7 +40418,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8796</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40430,7 +40430,7 @@
         <v>1.1074</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0597</v>
+        <v>2.0599</v>
       </c>
       <c r="J250" t="n">
         <v>0.6257</v>
@@ -40452,7 +40452,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.927</v>
+        <v>0.9271</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2377</v>
+        <v>2.2379</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40486,7 +40486,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9413</v>
+        <v>0.9414</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3664</v>
+        <v>2.3666</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40511,7 +40511,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7559</v>
+        <v>0.756</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3918</v>
+        <v>2.392</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40554,7 +40554,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9455</v>
+        <v>0.9456</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.5003</v>
+        <v>2.5005</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40588,7 +40588,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9483</v>
+        <v>0.9484</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5796</v>
+        <v>2.5798</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40613,7 +40613,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8254</v>
+        <v>0.8255</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40622,7 +40622,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9093</v>
+        <v>0.9094</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6023</v>
+        <v>2.6025</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40656,7 +40656,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8637</v>
+        <v>0.8638</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7316</v>
+        <v>2.7318</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40690,7 +40690,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9235</v>
+        <v>0.9236</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8854</v>
+        <v>2.8857</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8339</v>
+        <v>0.834</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40724,7 +40724,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9613</v>
+        <v>0.9614</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0806</v>
+        <v>3.0809</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9539</v>
+        <v>0.9528</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9539</v>
+        <v>0.9528</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.051</v>
+        <v>3.0466</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>0.649</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="183">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>0.914</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="221">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.953</v>
+        <v>0.952</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.199</v>
+        <v>1.201</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.446</v>
+        <v>1.448</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.994</v>
+        <v>1.995</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.771</v>
+        <v>2.772</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.925</v>
+        <v>3.928</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.78</v>
+        <v>-0.778</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.232</v>
+        <v>-0.23</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.972</v>
+        <v>0.973</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66607.673</v>
+        <v>66505.598</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31808,19 +31808,19 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>1.1989</v>
+        <v>1.201</v>
       </c>
       <c r="D260" t="n">
-        <v>1.4459</v>
+        <v>1.4483</v>
       </c>
       <c r="E260" t="n">
-        <v>1.9935</v>
+        <v>1.9954</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7706</v>
+        <v>2.772</v>
       </c>
       <c r="G260" t="n">
-        <v>3.9254</v>
+        <v>3.9276</v>
       </c>
       <c r="H260" t="n">
         <v>1.9793</v>
@@ -31832,13 +31832,13 @@
         <v>1.7988</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.7804</v>
+        <v>-0.7783</v>
       </c>
       <c r="L260" t="n">
-        <v>-0.2321</v>
+        <v>-0.2298</v>
       </c>
       <c r="M260" t="n">
-        <v>0.9718</v>
+        <v>0.9732</v>
       </c>
       <c r="N260" t="n">
         <v>-0.9792999999999999</v>
@@ -31877,7 +31877,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z260" t="n">
-        <v>66607.67290000001</v>
+        <v>66505.5977</v>
       </c>
       <c r="AA260" t="n">
         <v>160.77</v>
@@ -32100,7 +32100,7 @@
         <v>-0.3727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5441</v>
+        <v>-0.5442</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5114</v>
@@ -32156,7 +32156,7 @@
         <v>0.1468</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7148</v>
+        <v>-0.7149</v>
       </c>
       <c r="F7" t="n">
         <v>0.1468</v>
@@ -32304,7 +32304,7 @@
         <v>-0.2158</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2976</v>
+        <v>-0.2977</v>
       </c>
       <c r="J11" t="n">
         <v>-1.282</v>
@@ -33222,7 +33222,7 @@
         <v>-0.6035</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3701</v>
+        <v>-0.3702</v>
       </c>
       <c r="J38" t="n">
         <v>0.2133</v>
@@ -33426,7 +33426,7 @@
         <v>-1.4176</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5616</v>
+        <v>-0.5617</v>
       </c>
       <c r="J44" t="n">
         <v>0.5838</v>
@@ -33686,7 +33686,7 @@
         <v>0.0701</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1865</v>
+        <v>-1.1866</v>
       </c>
       <c r="F52" t="n">
         <v>0.0701</v>
@@ -33732,7 +33732,7 @@
         <v>-2.7104</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9981</v>
+        <v>-0.9982</v>
       </c>
       <c r="J53" t="n">
         <v>0.1923</v>
@@ -33868,7 +33868,7 @@
         <v>-2.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0159</v>
+        <v>-1.016</v>
       </c>
       <c r="J57" t="n">
         <v>-0.437</v>
@@ -34344,7 +34344,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2543</v>
+        <v>-1.2544</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9205</v>
@@ -34378,7 +34378,7 @@
         <v>-1.4191</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2412</v>
+        <v>-1.2413</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8898</v>
@@ -34514,7 +34514,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2496</v>
+        <v>-1.2497</v>
       </c>
       <c r="J76" t="n">
         <v>-1.6977</v>
@@ -34548,7 +34548,7 @@
         <v>-0.7507</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2166</v>
+        <v>-1.2167</v>
       </c>
       <c r="J77" t="n">
         <v>-1.593</v>
@@ -34629,7 +34629,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.6847</v>
+        <v>-0.6848</v>
       </c>
       <c r="C80" t="n">
         <v>0.1919</v>
@@ -34684,7 +34684,7 @@
         <v>-0.6850000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3264</v>
+        <v>-1.3265</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4736</v>
@@ -34731,7 +34731,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6609</v>
+        <v>-0.661</v>
       </c>
       <c r="C83" t="n">
         <v>0.09279999999999999</v>
@@ -34740,7 +34740,7 @@
         <v>0.1822</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.8717</v>
+        <v>-0.8718</v>
       </c>
       <c r="F83" t="n">
         <v>0.1822</v>
@@ -34799,7 +34799,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.621</v>
+        <v>-0.6211</v>
       </c>
       <c r="C85" t="n">
         <v>0.0525</v>
@@ -34820,7 +34820,7 @@
         <v>-0.573</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3311</v>
+        <v>-1.3312</v>
       </c>
       <c r="J85" t="n">
         <v>-1.275</v>
@@ -34922,7 +34922,7 @@
         <v>-0.5194</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2202</v>
+        <v>-1.2203</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0529</v>
@@ -35092,7 +35092,7 @@
         <v>-0.3849</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.3018</v>
+        <v>-1.3019</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8139999999999999</v>
@@ -35207,7 +35207,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.2364</v>
+        <v>-0.2365</v>
       </c>
       <c r="C97" t="n">
         <v>-0.3238</v>
@@ -35262,7 +35262,7 @@
         <v>-0.201</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0637</v>
+        <v>-1.0638</v>
       </c>
       <c r="J98" t="n">
         <v>-0.615</v>
@@ -35309,7 +35309,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2537</v>
+        <v>-0.2538</v>
       </c>
       <c r="C100" t="n">
         <v>-0.3899</v>
@@ -35432,7 +35432,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8182</v>
+        <v>-0.8183</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3535</v>
@@ -36962,7 +36962,7 @@
         <v>0.7911</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0309</v>
+        <v>0.031</v>
       </c>
       <c r="J148" t="n">
         <v>0.4423</v>
@@ -37302,7 +37302,7 @@
         <v>0.7964</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1038</v>
+        <v>0.1039</v>
       </c>
       <c r="J158" t="n">
         <v>1.0058</v>
@@ -37506,7 +37506,7 @@
         <v>0.8315</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1135</v>
+        <v>0.1136</v>
       </c>
       <c r="J164" t="n">
         <v>1.2107</v>
@@ -37778,7 +37778,7 @@
         <v>0.9594</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0157</v>
+        <v>-0.0156</v>
       </c>
       <c r="J172" t="n">
         <v>1.6568</v>
@@ -37812,7 +37812,7 @@
         <v>0.9594</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0138</v>
+        <v>-0.0137</v>
       </c>
       <c r="J173" t="n">
         <v>1.6146</v>
@@ -38038,7 +38038,7 @@
         <v>0.6763</v>
       </c>
       <c r="E180" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="F180" t="n">
         <v>0.6763</v>
@@ -38084,7 +38084,7 @@
         <v>0.0902</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1476</v>
+        <v>-0.1475</v>
       </c>
       <c r="J181" t="n">
         <v>1.9524</v>
@@ -38140,7 +38140,7 @@
         <v>0.7168</v>
       </c>
       <c r="E183" t="n">
-        <v>0.6458</v>
+        <v>0.6459</v>
       </c>
       <c r="F183" t="n">
         <v>0.7168</v>
@@ -38152,7 +38152,7 @@
         <v>0.0902</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.191</v>
+        <v>-0.1909</v>
       </c>
       <c r="J183" t="n">
         <v>2.1734</v>
@@ -38424,7 +38424,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0832</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J191" t="n">
         <v>1.307</v>
@@ -38458,7 +38458,7 @@
         <v>-0.6964</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0372</v>
+        <v>-0.0371</v>
       </c>
       <c r="J192" t="n">
         <v>1.0409</v>
@@ -38582,7 +38582,7 @@
         <v>0.2432</v>
       </c>
       <c r="E196" t="n">
-        <v>0.163</v>
+        <v>0.1631</v>
       </c>
       <c r="F196" t="n">
         <v>0.2432</v>
@@ -38628,7 +38628,7 @@
         <v>-0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.244</v>
+        <v>0.2441</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1006</v>
@@ -38752,7 +38752,7 @@
         <v>0.4293</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0731</v>
+        <v>0.0732</v>
       </c>
       <c r="F201" t="n">
         <v>0.4293</v>
@@ -38764,7 +38764,7 @@
         <v>-0.1642</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3183</v>
+        <v>0.3184</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5984</v>
@@ -38820,7 +38820,7 @@
         <v>0.5004999999999999</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1708</v>
+        <v>0.1709</v>
       </c>
       <c r="F203" t="n">
         <v>0.5004999999999999</v>
@@ -38832,7 +38832,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4172</v>
+        <v>0.4173</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5037</v>
@@ -38866,7 +38866,7 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4517</v>
+        <v>0.4518</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4239</v>
@@ -39104,7 +39104,7 @@
         <v>0.5368000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7789</v>
+        <v>0.779</v>
       </c>
       <c r="J211" t="n">
         <v>-0.11</v>
@@ -39194,7 +39194,7 @@
         <v>1.7312</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6314</v>
+        <v>0.6315</v>
       </c>
       <c r="F214" t="n">
         <v>1.7312</v>
@@ -39206,7 +39206,7 @@
         <v>0.6149</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9427</v>
+        <v>0.9428</v>
       </c>
       <c r="J214" t="n">
         <v>0.0815</v>
@@ -39274,7 +39274,7 @@
         <v>0.6149</v>
       </c>
       <c r="I216" t="n">
-        <v>0.953</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0166</v>
@@ -39308,7 +39308,7 @@
         <v>0.7019</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8224</v>
+        <v>0.8225</v>
       </c>
       <c r="J217" t="n">
         <v>0.1694</v>
@@ -39478,7 +39478,7 @@
         <v>0.8497</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9466</v>
+        <v>0.9467</v>
       </c>
       <c r="J222" t="n">
         <v>0.2508</v>
@@ -39512,7 +39512,7 @@
         <v>0.8486</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0736</v>
+        <v>1.0737</v>
       </c>
       <c r="J223" t="n">
         <v>0.3683</v>
@@ -39648,7 +39648,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I227" t="n">
-        <v>1.281</v>
+        <v>1.2811</v>
       </c>
       <c r="J227" t="n">
         <v>0.3567</v>
@@ -39682,7 +39682,7 @@
         <v>0.9530999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>1.354</v>
+        <v>1.3541</v>
       </c>
       <c r="J228" t="n">
         <v>0.3598</v>
@@ -39716,7 +39716,7 @@
         <v>1.051</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2819</v>
+        <v>1.282</v>
       </c>
       <c r="J229" t="n">
         <v>0.3852</v>
@@ -39784,7 +39784,7 @@
         <v>1.051</v>
       </c>
       <c r="I231" t="n">
-        <v>1.5297</v>
+        <v>1.5298</v>
       </c>
       <c r="J231" t="n">
         <v>0.4219</v>
@@ -39818,7 +39818,7 @@
         <v>1.1509</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5959</v>
+        <v>1.596</v>
       </c>
       <c r="J232" t="n">
         <v>0.4828</v>
@@ -39886,7 +39886,7 @@
         <v>1.1509</v>
       </c>
       <c r="I234" t="n">
-        <v>1.7055</v>
+        <v>1.7056</v>
       </c>
       <c r="J234" t="n">
         <v>0.4758</v>
@@ -39920,7 +39920,7 @@
         <v>1.1461</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7888</v>
+        <v>1.7889</v>
       </c>
       <c r="J235" t="n">
         <v>0.5432</v>
@@ -39954,7 +39954,7 @@
         <v>1.1461</v>
       </c>
       <c r="I236" t="n">
-        <v>1.8251</v>
+        <v>1.8252</v>
       </c>
       <c r="J236" t="n">
         <v>0.5594</v>
@@ -39967,7 +39967,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.031</v>
+        <v>1.0311</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -39988,7 +39988,7 @@
         <v>1.1461</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5966</v>
+        <v>1.5967</v>
       </c>
       <c r="J237" t="n">
         <v>0.5209</v>
@@ -40044,7 +40044,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9728</v>
+        <v>0.9729</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40056,7 +40056,7 @@
         <v>1.1289</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7485</v>
+        <v>1.7486</v>
       </c>
       <c r="J239" t="n">
         <v>0.6207</v>
@@ -40078,7 +40078,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9694</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40090,7 +40090,7 @@
         <v>1.1289</v>
       </c>
       <c r="I240" t="n">
-        <v>1.8254</v>
+        <v>1.8255</v>
       </c>
       <c r="J240" t="n">
         <v>0.5914</v>
@@ -40124,7 +40124,7 @@
         <v>1.116</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8452</v>
+        <v>1.8453</v>
       </c>
       <c r="J241" t="n">
         <v>0.6443</v>
@@ -40180,7 +40180,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9153</v>
+        <v>0.9154</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40226,7 +40226,7 @@
         <v>1.179</v>
       </c>
       <c r="I244" t="n">
-        <v>1.8056</v>
+        <v>1.8057</v>
       </c>
       <c r="J244" t="n">
         <v>0.7037</v>
@@ -40260,7 +40260,7 @@
         <v>1.179</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6783</v>
+        <v>1.6784</v>
       </c>
       <c r="J245" t="n">
         <v>0.6121</v>
@@ -40307,7 +40307,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9775</v>
+        <v>0.9776</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40464,7 +40464,7 @@
         <v>1.1074</v>
       </c>
       <c r="I251" t="n">
-        <v>2.2379</v>
+        <v>2.238</v>
       </c>
       <c r="J251" t="n">
         <v>0.6399</v>
@@ -40498,7 +40498,7 @@
         <v>1.1074</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3666</v>
+        <v>2.3667</v>
       </c>
       <c r="J252" t="n">
         <v>0.6221</v>
@@ -40532,7 +40532,7 @@
         <v>1.1352</v>
       </c>
       <c r="I253" t="n">
-        <v>2.392</v>
+        <v>2.3921</v>
       </c>
       <c r="J253" t="n">
         <v>0.616</v>
@@ -40545,7 +40545,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8853</v>
+        <v>0.8854</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40566,7 +40566,7 @@
         <v>1.1352</v>
       </c>
       <c r="I254" t="n">
-        <v>2.5005</v>
+        <v>2.5006</v>
       </c>
       <c r="J254" t="n">
         <v>0.5968</v>
@@ -40579,7 +40579,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8472</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40600,7 +40600,7 @@
         <v>1.1352</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5798</v>
+        <v>2.5799</v>
       </c>
       <c r="J255" t="n">
         <v>0.5644</v>
@@ -40634,7 +40634,7 @@
         <v>1.0062</v>
       </c>
       <c r="I256" t="n">
-        <v>2.6025</v>
+        <v>2.6026</v>
       </c>
       <c r="J256" t="n">
         <v>0.6124000000000001</v>
@@ -40668,7 +40668,7 @@
         <v>1.0062</v>
       </c>
       <c r="I257" t="n">
-        <v>2.7318</v>
+        <v>2.7319</v>
       </c>
       <c r="J257" t="n">
         <v>0.4782</v>
@@ -40702,7 +40702,7 @@
         <v>1.0062</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8857</v>
+        <v>2.8858</v>
       </c>
       <c r="J258" t="n">
         <v>0.5714</v>
@@ -40736,7 +40736,7 @@
         <v>1.0818</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0809</v>
+        <v>3.0811</v>
       </c>
       <c r="J259" t="n">
         <v>0.5494</v>
@@ -40749,13 +40749,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9528</v>
+        <v>0.9523</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9528</v>
+        <v>0.9523</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8665</v>
@@ -40764,7 +40764,7 @@
         <v>1.0818</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0466</v>
+        <v>3.0447</v>
       </c>
       <c r="J260" t="n">
         <v>0.5494</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -60,7 +60,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +97,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -149,6 +154,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2764,7 +2772,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>0.239</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="192">
@@ -3573,11 +3581,11 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.203</v>
+        <v>1.287</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3599,11 +3607,11 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.451</v>
+        <v>1.562</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3625,11 +3633,11 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.998</v>
+        <v>2.1</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3651,11 +3659,11 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.773</v>
+        <v>2.824</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3677,11 +3685,11 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.93</v>
+        <v>3.982</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3785,19 +3793,19 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.776</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>0.18</v>
+      <c r="E13" s="14" t="n">
+        <v>0.06</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Mildly accommodative</t>
+          <t>Broadly neutral</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.227</v>
+        <v>-0.119</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3821,11 +3829,11 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.48</v>
+        <v>-0.67</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Mildly restrictive</t>
+          <t>Restrictive</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.975</v>
+        <v>1.025</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.21</v>
+        <v>-1.27</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4183,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>63754.9</v>
+        <v>63856.215</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -4337,172 +4345,172 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>policy_rate</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>jgb_1y</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>jgb_2y</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>jgb_5y</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>jgb_10y</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>jgb_30y</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>infexp_1y</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>infexp_3y</t>
         </is>
       </c>
-      <c r="J1" s="14" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>infexp_10y</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>real_1y</t>
         </is>
       </c>
-      <c r="L1" s="14" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>real_3y</t>
         </is>
       </c>
-      <c r="M1" s="14" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>real_10y</t>
         </is>
       </c>
-      <c r="N1" s="14" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>real_policy_rate</t>
         </is>
       </c>
-      <c r="O1" s="14" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>real_1y_xp</t>
         </is>
       </c>
-      <c r="P1" s="14" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>real_3y_xp</t>
         </is>
       </c>
-      <c r="Q1" s="14" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>real_10y_xp</t>
         </is>
       </c>
-      <c r="R1" s="14" t="inlineStr">
+      <c r="R1" s="15" t="inlineStr">
         <is>
           <t>lending_rate</t>
         </is>
       </c>
-      <c r="S1" s="14" t="inlineStr">
+      <c r="S1" s="15" t="inlineStr">
         <is>
           <t>cp_rate</t>
         </is>
       </c>
-      <c r="T1" s="14" t="inlineStr">
+      <c r="T1" s="15" t="inlineStr">
         <is>
           <t>corp_bond_spread</t>
         </is>
       </c>
-      <c r="U1" s="14" t="inlineStr">
+      <c r="U1" s="15" t="inlineStr">
         <is>
           <t>tankan_lend_large</t>
         </is>
       </c>
-      <c r="V1" s="14" t="inlineStr">
+      <c r="V1" s="15" t="inlineStr">
         <is>
           <t>tankan_lend_small</t>
         </is>
       </c>
-      <c r="W1" s="14" t="inlineStr">
+      <c r="W1" s="15" t="inlineStr">
         <is>
           <t>tankan_finpos_large</t>
         </is>
       </c>
-      <c r="X1" s="14" t="inlineStr">
+      <c r="X1" s="15" t="inlineStr">
         <is>
           <t>tankan_finpos_small</t>
         </is>
       </c>
-      <c r="Y1" s="14" t="inlineStr">
+      <c r="Y1" s="15" t="inlineStr">
         <is>
           <t>topix</t>
         </is>
       </c>
-      <c r="Z1" s="14" t="inlineStr">
+      <c r="Z1" s="15" t="inlineStr">
         <is>
           <t>nikkei225</t>
         </is>
       </c>
-      <c r="AA1" s="14" t="inlineStr">
+      <c r="AA1" s="15" t="inlineStr">
         <is>
           <t>usdjpy</t>
         </is>
       </c>
-      <c r="AB1" s="14" t="inlineStr">
+      <c r="AB1" s="15" t="inlineStr">
         <is>
           <t>bank_lending_yoy</t>
         </is>
       </c>
-      <c r="AC1" s="14" t="inlineStr">
+      <c r="AC1" s="15" t="inlineStr">
         <is>
           <t>cp_corpbond_yoy</t>
         </is>
       </c>
-      <c r="AD1" s="14" t="inlineStr">
+      <c r="AD1" s="15" t="inlineStr">
         <is>
           <t>core_cpi_yoy</t>
         </is>
       </c>
-      <c r="AE1" s="14" t="inlineStr">
+      <c r="AE1" s="15" t="inlineStr">
         <is>
           <t>potential_growth</t>
         </is>
       </c>
-      <c r="AF1" s="14" t="inlineStr">
+      <c r="AF1" s="15" t="inlineStr">
         <is>
           <t>natural_rate_low</t>
         </is>
       </c>
-      <c r="AG1" s="14" t="inlineStr">
+      <c r="AG1" s="15" t="inlineStr">
         <is>
           <t>natural_rate_mid</t>
         </is>
       </c>
-      <c r="AH1" s="14" t="inlineStr">
+      <c r="AH1" s="15" t="inlineStr">
         <is>
           <t>natural_rate_high</t>
         </is>
@@ -31924,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.2035</v>
+        <v>1.287</v>
       </c>
       <c r="D261" t="n">
-        <v>1.451</v>
+        <v>1.562</v>
       </c>
       <c r="E261" t="n">
-        <v>1.9976</v>
+        <v>2.1</v>
       </c>
       <c r="F261" t="n">
-        <v>2.7734</v>
+        <v>2.824</v>
       </c>
       <c r="G261" t="n">
-        <v>3.93</v>
+        <v>3.982</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31948,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.7758</v>
+        <v>-0.6923</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.2273</v>
+        <v>-0.1192</v>
       </c>
       <c r="M261" t="n">
-        <v>0.9746</v>
+        <v>1.0252</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -31993,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>63754.9</v>
+        <v>63856.215</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32047,52 +32055,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>FCI</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>rate_gap</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>stage1</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>stage2</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>real_rate</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>funding_costs</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>asset_prices</t>
         </is>
       </c>
-      <c r="J1" s="14" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>funding_volumes</t>
         </is>
@@ -32105,7 +32113,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.612</v>
+        <v>-0.6119</v>
       </c>
       <c r="D2" t="n">
         <v>0.2573</v>
@@ -32216,7 +32224,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.5458</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5156</v>
@@ -32250,7 +32258,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5353</v>
+        <v>-0.5352</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4222</v>
@@ -33134,7 +33142,7 @@
         <v>0.2333</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="J32" t="n">
         <v>-0.2231</v>
@@ -33610,7 +33618,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6506</v>
+        <v>-0.6505</v>
       </c>
       <c r="J46" t="n">
         <v>0.7897999999999999</v>
@@ -33644,7 +33652,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8522</v>
+        <v>-0.8521</v>
       </c>
       <c r="J47" t="n">
         <v>0.741</v>
@@ -33780,7 +33788,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1116</v>
+        <v>-1.1115</v>
       </c>
       <c r="J51" t="n">
         <v>0.6076</v>
@@ -33904,7 +33912,7 @@
         <v>-0.5705</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.3059</v>
+        <v>-1.3058</v>
       </c>
       <c r="F55" t="n">
         <v>-0.5705</v>
@@ -33916,7 +33924,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9935</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0219</v>
@@ -34006,7 +34014,7 @@
         <v>-0.8324</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.3502</v>
+        <v>-1.3501</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8324</v>
@@ -34256,7 +34264,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0319</v>
+        <v>-1.0318</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8174</v>
@@ -34834,7 +34842,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3343</v>
+        <v>-1.3342</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3458</v>
@@ -34915,7 +34923,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.6206</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="C85" t="n">
         <v>0.0525</v>
@@ -35072,7 +35080,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2368</v>
+        <v>-1.2367</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0901</v>
@@ -35140,7 +35148,7 @@
         <v>-0.389</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2922</v>
+        <v>-1.2921</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9429999999999999</v>
@@ -35174,7 +35182,7 @@
         <v>-0.389</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2961</v>
+        <v>-1.296</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8282</v>
@@ -35650,7 +35658,7 @@
         <v>-0.0433</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7154</v>
+        <v>-0.7153</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3637</v>
@@ -35774,7 +35782,7 @@
         <v>0.8838</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.0834</v>
+        <v>-0.0833</v>
       </c>
       <c r="F110" t="n">
         <v>0.8838</v>
@@ -36556,7 +36564,7 @@
         <v>0.3672</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3743</v>
+        <v>0.3742</v>
       </c>
       <c r="F133" t="n">
         <v>0.3672</v>
@@ -37010,7 +37018,7 @@
         <v>0.7694</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0305</v>
+        <v>0.0304</v>
       </c>
       <c r="J146" t="n">
         <v>0.4366</v>
@@ -37384,7 +37392,7 @@
         <v>0.7919</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1107</v>
+        <v>0.1106</v>
       </c>
       <c r="J157" t="n">
         <v>0.8101</v>
@@ -37431,7 +37439,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.6514</v>
+        <v>0.6513</v>
       </c>
       <c r="C159" t="n">
         <v>0.3158</v>
@@ -37656,7 +37664,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0893</v>
       </c>
       <c r="J165" t="n">
         <v>1.321</v>
@@ -38030,7 +38038,7 @@
         <v>0.9513</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.141</v>
+        <v>-0.1411</v>
       </c>
       <c r="J176" t="n">
         <v>1.8237</v>
@@ -38052,7 +38060,7 @@
         <v>0.7199</v>
       </c>
       <c r="E177" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.7756</v>
       </c>
       <c r="F177" t="n">
         <v>0.7199</v>
@@ -38234,7 +38242,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1849</v>
+        <v>-0.185</v>
       </c>
       <c r="J182" t="n">
         <v>2.0493</v>
@@ -38587,7 +38595,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2103</v>
+        <v>0.2102</v>
       </c>
       <c r="C193" t="n">
         <v>0.2348</v>
@@ -38608,7 +38616,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0132</v>
+        <v>-0.0133</v>
       </c>
       <c r="J193" t="n">
         <v>0.855</v>
@@ -38757,7 +38765,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.0731</v>
+        <v>0.073</v>
       </c>
       <c r="C198" t="n">
         <v>-0.0649</v>
@@ -38800,7 +38808,7 @@
         <v>0.2053</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0329</v>
+        <v>0.0328</v>
       </c>
       <c r="F199" t="n">
         <v>0.2053</v>
@@ -38812,7 +38820,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2803</v>
+        <v>0.2802</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6688</v>
@@ -39084,7 +39092,7 @@
         <v>0.2135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4433</v>
+        <v>0.4432</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2922</v>
@@ -39152,7 +39160,7 @@
         <v>0.3986</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.6143</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1699</v>
@@ -39165,7 +39173,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.5979</v>
+        <v>0.5978</v>
       </c>
       <c r="C210" t="n">
         <v>-0.6456</v>
@@ -39390,7 +39398,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9282</v>
+        <v>0.9281</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0187</v>
@@ -39412,7 +39420,7 @@
         <v>1.562</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6294</v>
       </c>
       <c r="F217" t="n">
         <v>1.562</v>
@@ -39492,7 +39500,7 @@
         <v>0.6974</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8004</v>
+        <v>0.8003</v>
       </c>
       <c r="J219" t="n">
         <v>0.2431</v>
@@ -39526,7 +39534,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8025</v>
+        <v>0.8024</v>
       </c>
       <c r="J220" t="n">
         <v>0.2685</v>
@@ -39696,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1524</v>
+        <v>1.1523</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39752,7 +39760,7 @@
         <v>1.5257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8502</v>
+        <v>0.8501</v>
       </c>
       <c r="F227" t="n">
         <v>1.5257</v>
@@ -39777,7 +39785,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9651</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39879,7 +39887,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0575</v>
+        <v>1.0574</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -39900,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4946</v>
+        <v>1.4945</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39968,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6219</v>
+        <v>1.6218</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -39990,7 +39998,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.0021</v>
+        <v>1.002</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -40036,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7503</v>
+        <v>1.7502</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40058,7 +40066,7 @@
         <v>1.3708</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0135</v>
+        <v>1.0134</v>
       </c>
       <c r="F236" t="n">
         <v>1.3708</v>
@@ -40104,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5603</v>
+        <v>1.5602</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40126,7 +40134,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9184</v>
+        <v>0.9183</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40138,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5463</v>
+        <v>1.5462</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40172,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7098</v>
+        <v>1.7097</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40185,7 +40193,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0187</v>
+        <v>1.0186</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40206,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7859</v>
+        <v>1.7858</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40240,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8053</v>
+        <v>1.8052</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40296,7 +40304,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9069</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40308,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8118</v>
+        <v>1.8117</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40342,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7662</v>
+        <v>1.7661</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40466,7 +40474,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8525</v>
+        <v>0.8524</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40512,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.949</v>
+        <v>1.9489</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40546,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.015</v>
+        <v>2.0149</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40568,7 +40576,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9177</v>
+        <v>0.9176</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40580,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1898</v>
+        <v>2.1897</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40614,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3165</v>
+        <v>2.3164</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40627,7 +40635,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7484</v>
+        <v>0.7483</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40648,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3416</v>
+        <v>2.3415</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40670,7 +40678,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9356</v>
+        <v>0.9355</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40716,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5252</v>
+        <v>2.5251</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40784,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6751</v>
+        <v>2.675</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40806,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9126</v>
+        <v>0.9125</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40818,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8254</v>
+        <v>2.8253</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40831,7 +40839,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8246</v>
+        <v>0.8245</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40840,7 +40848,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9497</v>
+        <v>0.9496</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40852,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0168</v>
+        <v>3.0166</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40880,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0061</v>
+        <v>3.006</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40893,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9337</v>
+        <v>0.9342</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9337</v>
+        <v>0.9342</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40908,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9529</v>
+        <v>2.9548</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>
@@ -40944,67 +40952,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>series_id</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>polarity</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="J1" s="14" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>source_series_id</t>
         </is>
       </c>
-      <c r="L1" s="14" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="M1" s="14" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.93</t>
+          <t>+0.94</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.93 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.94 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>-0.429</v>
+        <v>-0.428</v>
       </c>
     </row>
     <row r="45">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>-0.038</v>
+        <v>-0.037</v>
       </c>
     </row>
     <row r="106">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="178">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>0.14</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="202">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="J211" t="n">
-        <v>0.675</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="212">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>0.978</v>
+        <v>0.977</v>
       </c>
     </row>
     <row r="239">
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="J244" t="n">
-        <v>1.025</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="245">
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>0.789</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="259">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>0.825</v>
+        <v>0.824</v>
       </c>
     </row>
     <row r="260">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.287</v>
+        <v>1.292</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.562</v>
+        <v>1.565</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.1</v>
+        <v>2.098</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.824</v>
+        <v>2.836</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.982</v>
+        <v>3.986</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.119</v>
+        <v>-0.118</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.025</v>
+        <v>1.037</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.27</v>
+        <v>-1.29</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>63856.215</v>
+        <v>64670.957</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.287</v>
+        <v>1.2925</v>
       </c>
       <c r="D261" t="n">
-        <v>1.562</v>
+        <v>1.565</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1</v>
+        <v>2.098</v>
       </c>
       <c r="F261" t="n">
-        <v>2.824</v>
+        <v>2.836</v>
       </c>
       <c r="G261" t="n">
-        <v>3.982</v>
+        <v>3.986</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6923</v>
+        <v>-0.6868</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.1192</v>
+        <v>-0.1178</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0252</v>
+        <v>1.0372</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>63856.215</v>
+        <v>64670.9567</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32128,7 +32128,7 @@
         <v>-0.3431</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6434</v>
+        <v>-0.6433</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7186</v>
@@ -32156,7 +32156,7 @@
         <v>-0.3209</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5903</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>-1.6403</v>
@@ -32190,7 +32190,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5672</v>
+        <v>-0.5671</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6492</v>
@@ -32212,7 +32212,7 @@
         <v>0.2212</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7276</v>
+        <v>-0.7275</v>
       </c>
       <c r="F5" t="n">
         <v>0.2212</v>
@@ -32224,7 +32224,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5458</v>
+        <v>-0.5457</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5156</v>
@@ -32258,7 +32258,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5352</v>
+        <v>-0.5351</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4222</v>
@@ -32271,7 +32271,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.5446</v>
+        <v>-0.5445</v>
       </c>
       <c r="C7" t="n">
         <v>-0.1131</v>
@@ -32292,7 +32292,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4889</v>
+        <v>-0.4887</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5127</v>
@@ -32326,7 +32326,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4092</v>
+        <v>-0.4091</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3624</v>
@@ -32360,7 +32360,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4125</v>
+        <v>-0.4124</v>
       </c>
       <c r="J9" t="n">
         <v>-1.394</v>
@@ -32394,7 +32394,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3874</v>
+        <v>-0.3873</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2486</v>
@@ -32416,7 +32416,7 @@
         <v>0.1045</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.649</v>
+        <v>-0.6489</v>
       </c>
       <c r="F11" t="n">
         <v>0.1045</v>
@@ -32428,7 +32428,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3028</v>
+        <v>-0.3027</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2859</v>
@@ -32496,7 +32496,7 @@
         <v>-0.1828</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1821</v>
+        <v>-0.182</v>
       </c>
       <c r="J13" t="n">
         <v>-1.201</v>
@@ -32598,7 +32598,7 @@
         <v>-0.1031</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1549</v>
+        <v>-0.1548</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0253</v>
@@ -32611,7 +32611,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.46</v>
+        <v>-0.4599</v>
       </c>
       <c r="C17" t="n">
         <v>-0.4753</v>
@@ -32734,7 +32734,7 @@
         <v>-0.116</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1418</v>
+        <v>-0.1417</v>
       </c>
       <c r="J20" t="n">
         <v>-0.827</v>
@@ -32768,7 +32768,7 @@
         <v>-0.116</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1126</v>
+        <v>-0.1125</v>
       </c>
       <c r="J21" t="n">
         <v>-0.772</v>
@@ -32904,7 +32904,7 @@
         <v>0.1774</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0329</v>
+        <v>-0.0328</v>
       </c>
       <c r="J25" t="n">
         <v>-0.5324</v>
@@ -33164,7 +33164,7 @@
         <v>-0.1085</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4217</v>
+        <v>-0.4216</v>
       </c>
       <c r="F33" t="n">
         <v>-0.1085</v>
@@ -33223,7 +33223,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4156</v>
+        <v>-0.4155</v>
       </c>
       <c r="C35" t="n">
         <v>-0.1623</v>
@@ -33278,7 +33278,7 @@
         <v>-0.225</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.234</v>
+        <v>-0.2339</v>
       </c>
       <c r="J36" t="n">
         <v>0.0688</v>
@@ -33312,7 +33312,7 @@
         <v>-0.6075</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2379</v>
+        <v>-0.2378</v>
       </c>
       <c r="J37" t="n">
         <v>0.1573</v>
@@ -33334,7 +33334,7 @@
         <v>0.4015</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.644</v>
+        <v>-0.6439</v>
       </c>
       <c r="F38" t="n">
         <v>0.4015</v>
@@ -33346,7 +33346,7 @@
         <v>-0.6075</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.375</v>
+        <v>-0.3749</v>
       </c>
       <c r="J38" t="n">
         <v>0.2114</v>
@@ -33368,7 +33368,7 @@
         <v>0.4921</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.6368</v>
+        <v>-0.6367</v>
       </c>
       <c r="F39" t="n">
         <v>0.4921</v>
@@ -33380,7 +33380,7 @@
         <v>-0.6075</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4207</v>
+        <v>-0.4206</v>
       </c>
       <c r="J39" t="n">
         <v>0.2385</v>
@@ -33414,7 +33414,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5621</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J40" t="n">
         <v>0.3612</v>
@@ -33448,7 +33448,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5588</v>
+        <v>-0.5587</v>
       </c>
       <c r="J41" t="n">
         <v>0.3765</v>
@@ -33482,7 +33482,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.532</v>
+        <v>-0.5319</v>
       </c>
       <c r="J42" t="n">
         <v>0.4861</v>
@@ -33516,7 +33516,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5238</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J43" t="n">
         <v>0.5435</v>
@@ -33538,7 +33538,7 @@
         <v>1.0013</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.786</v>
+        <v>-0.7859</v>
       </c>
       <c r="F44" t="n">
         <v>1.0013</v>
@@ -33550,7 +33550,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5634</v>
+        <v>-0.5633</v>
       </c>
       <c r="J44" t="n">
         <v>0.5824</v>
@@ -33584,7 +33584,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5589</v>
+        <v>-0.5588</v>
       </c>
       <c r="J45" t="n">
         <v>0.7418</v>
@@ -33618,7 +33618,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6505</v>
+        <v>-0.6504</v>
       </c>
       <c r="J46" t="n">
         <v>0.7897999999999999</v>
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.5748</v>
+        <v>-0.5747</v>
       </c>
       <c r="C47" t="n">
         <v>-0.3486</v>
@@ -33652,7 +33652,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8521</v>
+        <v>-0.852</v>
       </c>
       <c r="J47" t="n">
         <v>0.741</v>
@@ -33686,7 +33686,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9333</v>
+        <v>-0.9331</v>
       </c>
       <c r="J48" t="n">
         <v>0.7829</v>
@@ -33699,7 +33699,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8147</v>
+        <v>-0.8146</v>
       </c>
       <c r="C49" t="n">
         <v>-0.1283</v>
@@ -33720,7 +33720,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0533</v>
+        <v>-1.0531</v>
       </c>
       <c r="J49" t="n">
         <v>0.983</v>
@@ -33733,7 +33733,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8135</v>
+        <v>-0.8134</v>
       </c>
       <c r="C50" t="n">
         <v>0.0205</v>
@@ -33754,7 +33754,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0997</v>
+        <v>-1.0995</v>
       </c>
       <c r="J50" t="n">
         <v>0.7647</v>
@@ -33776,7 +33776,7 @@
         <v>0.1178</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0702</v>
+        <v>-1.0701</v>
       </c>
       <c r="F51" t="n">
         <v>0.1178</v>
@@ -33788,7 +33788,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1115</v>
+        <v>-1.1113</v>
       </c>
       <c r="J51" t="n">
         <v>0.6076</v>
@@ -33801,7 +33801,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9341</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="C52" t="n">
         <v>0.4357</v>
@@ -33822,7 +33822,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0195</v>
+        <v>-1.0193</v>
       </c>
       <c r="J52" t="n">
         <v>0.4738</v>
@@ -33835,7 +33835,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9744</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="C53" t="n">
         <v>0.6286</v>
@@ -33856,7 +33856,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.993</v>
+        <v>-0.9928</v>
       </c>
       <c r="J53" t="n">
         <v>0.1904</v>
@@ -33878,7 +33878,7 @@
         <v>-0.3292</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2404</v>
+        <v>-1.2403</v>
       </c>
       <c r="F54" t="n">
         <v>-0.3292</v>
@@ -33890,7 +33890,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0189</v>
+        <v>-1.0187</v>
       </c>
       <c r="J54" t="n">
         <v>0.1077</v>
@@ -33903,7 +33903,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1588</v>
+        <v>-1.1587</v>
       </c>
       <c r="C55" t="n">
         <v>1.0633</v>
@@ -33924,7 +33924,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.9933</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0219</v>
@@ -33958,7 +33958,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0491</v>
+        <v>-1.0489</v>
       </c>
       <c r="J56" t="n">
         <v>-0.245</v>
@@ -33980,7 +33980,7 @@
         <v>-0.8924</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.3986</v>
+        <v>-1.3985</v>
       </c>
       <c r="F57" t="n">
         <v>-0.8924</v>
@@ -33992,7 +33992,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0112</v>
+        <v>-1.0111</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4398</v>
@@ -34026,7 +34026,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0892</v>
+        <v>-1.089</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5775</v>
@@ -34039,7 +34039,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.2837</v>
+        <v>-1.2836</v>
       </c>
       <c r="C59" t="n">
         <v>0.9619</v>
@@ -34048,7 +34048,7 @@
         <v>-0.8113</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4018</v>
+        <v>-1.4017</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8113</v>
@@ -34060,7 +34060,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1042</v>
+        <v>-1.104</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8167</v>
@@ -34094,7 +34094,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1193</v>
+        <v>-1.1191</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9842</v>
@@ -34107,7 +34107,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.1938</v>
+        <v>-1.1937</v>
       </c>
       <c r="C61" t="n">
         <v>0.8397</v>
@@ -34116,7 +34116,7 @@
         <v>-0.3869</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.3955</v>
+        <v>-1.3954</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3869</v>
@@ -34128,7 +34128,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.1</v>
+        <v>-1.0999</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1668</v>
@@ -34141,7 +34141,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.1862</v>
+        <v>-1.1861</v>
       </c>
       <c r="C62" t="n">
         <v>0.8124</v>
@@ -34162,7 +34162,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0645</v>
+        <v>-1.0643</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3364</v>
@@ -34196,7 +34196,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0939</v>
+        <v>-1.0937</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4597</v>
@@ -34218,7 +34218,7 @@
         <v>-0.2615</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3883</v>
+        <v>-1.3882</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2615</v>
@@ -34230,7 +34230,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0729</v>
+        <v>-1.0727</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6947</v>
@@ -34264,7 +34264,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0318</v>
+        <v>-1.0317</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8174</v>
@@ -34277,7 +34277,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.1866</v>
+        <v>-1.1865</v>
       </c>
       <c r="C66" t="n">
         <v>0.585</v>
@@ -34286,7 +34286,7 @@
         <v>-0.2077</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.4313</v>
+        <v>-1.4312</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2077</v>
@@ -34298,7 +34298,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0733</v>
+        <v>-1.0731</v>
       </c>
       <c r="J66" t="n">
         <v>-1.966</v>
@@ -34332,7 +34332,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0946</v>
+        <v>-1.0944</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1347</v>
@@ -34354,7 +34354,7 @@
         <v>-0.2725</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.3922</v>
+        <v>-1.3921</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2725</v>
@@ -34366,7 +34366,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1615</v>
+        <v>-1.1613</v>
       </c>
       <c r="J68" t="n">
         <v>-2.108</v>
@@ -34388,7 +34388,7 @@
         <v>-0.261</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.3728</v>
+        <v>-1.3727</v>
       </c>
       <c r="F69" t="n">
         <v>-0.261</v>
@@ -34400,7 +34400,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1961</v>
+        <v>-1.1959</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0592</v>
@@ -34422,7 +34422,7 @@
         <v>-0.2922</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2549</v>
+        <v>-1.2548</v>
       </c>
       <c r="F70" t="n">
         <v>-0.2922</v>
@@ -34434,7 +34434,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2138</v>
+        <v>-1.2137</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9639</v>
@@ -34468,7 +34468,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.247</v>
+        <v>-1.2468</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9252</v>
@@ -34502,7 +34502,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2341</v>
+        <v>-1.2339</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8944</v>
@@ -34524,7 +34524,7 @@
         <v>-0.1169</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1621</v>
+        <v>-1.162</v>
       </c>
       <c r="F73" t="n">
         <v>-0.1169</v>
@@ -34536,7 +34536,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1962</v>
+        <v>-1.196</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8566</v>
@@ -34549,7 +34549,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.9603</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="C74" t="n">
         <v>0.4026</v>
@@ -34558,7 +34558,7 @@
         <v>-0.1679</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1584</v>
+        <v>-1.1583</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1679</v>
@@ -34570,7 +34570,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2219</v>
+        <v>-1.2217</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8329</v>
@@ -34604,7 +34604,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2121</v>
+        <v>-1.212</v>
       </c>
       <c r="J75" t="n">
         <v>-1.811</v>
@@ -34617,7 +34617,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8248</v>
+        <v>-0.8247</v>
       </c>
       <c r="C76" t="n">
         <v>0.2978</v>
@@ -34638,7 +34638,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2425</v>
+        <v>-1.2423</v>
       </c>
       <c r="J76" t="n">
         <v>-1.702</v>
@@ -34672,7 +34672,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2098</v>
+        <v>-1.2096</v>
       </c>
       <c r="J77" t="n">
         <v>-1.5973</v>
@@ -34706,7 +34706,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2489</v>
+        <v>-1.2487</v>
       </c>
       <c r="J78" t="n">
         <v>-1.63</v>
@@ -34740,7 +34740,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2709</v>
+        <v>-1.2707</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5321</v>
@@ -34774,7 +34774,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2717</v>
+        <v>-1.2715</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5145</v>
@@ -34796,7 +34796,7 @@
         <v>0.3202</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.9134</v>
+        <v>-0.9133</v>
       </c>
       <c r="F81" t="n">
         <v>0.3202</v>
@@ -34808,7 +34808,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3184</v>
+        <v>-1.3182</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4777</v>
@@ -34830,7 +34830,7 @@
         <v>0.3264</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8633999999999999</v>
+        <v>-0.8633</v>
       </c>
       <c r="F82" t="n">
         <v>0.3264</v>
@@ -34842,7 +34842,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3342</v>
+        <v>-1.3341</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3458</v>
@@ -34864,7 +34864,7 @@
         <v>0.1822</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.8711</v>
+        <v>-0.871</v>
       </c>
       <c r="F83" t="n">
         <v>0.1822</v>
@@ -34876,7 +34876,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3311</v>
+        <v>-1.3309</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3601</v>
@@ -34898,7 +34898,7 @@
         <v>0.1353</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8494</v>
+        <v>-0.8493000000000001</v>
       </c>
       <c r="F84" t="n">
         <v>0.1353</v>
@@ -34910,7 +34910,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3179</v>
+        <v>-1.3177</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3222</v>
@@ -34932,7 +34932,7 @@
         <v>0.1899</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.8232</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="F85" t="n">
         <v>0.1899</v>
@@ -34944,7 +34944,7 @@
         <v>-0.577</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3228</v>
+        <v>-1.3226</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2788</v>
@@ -34957,7 +34957,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5845</v>
+        <v>-0.5844</v>
       </c>
       <c r="C86" t="n">
         <v>0.0257</v>
@@ -34978,7 +34978,7 @@
         <v>-0.577</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3451</v>
+        <v>-1.3449</v>
       </c>
       <c r="J86" t="n">
         <v>-1.123</v>
@@ -34991,7 +34991,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5577</v>
+        <v>-0.5576</v>
       </c>
       <c r="C87" t="n">
         <v>0.0584</v>
@@ -35000,7 +35000,7 @@
         <v>0.2855</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.7685</v>
+        <v>-0.7684</v>
       </c>
       <c r="F87" t="n">
         <v>0.2855</v>
@@ -35012,7 +35012,7 @@
         <v>-0.577</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2939</v>
+        <v>-1.2937</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1315</v>
@@ -35046,7 +35046,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2135</v>
+        <v>-1.2133</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0564</v>
@@ -35068,7 +35068,7 @@
         <v>0.3382</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7141</v>
       </c>
       <c r="F89" t="n">
         <v>0.3382</v>
@@ -35080,7 +35080,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2367</v>
+        <v>-1.2366</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0901</v>
@@ -35114,7 +35114,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.29</v>
+        <v>-1.2898</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9147999999999999</v>
@@ -35148,7 +35148,7 @@
         <v>-0.389</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2921</v>
+        <v>-1.292</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9429999999999999</v>
@@ -35161,7 +35161,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.4713</v>
+        <v>-0.4712</v>
       </c>
       <c r="C92" t="n">
         <v>-0.2331</v>
@@ -35182,7 +35182,7 @@
         <v>-0.389</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.296</v>
+        <v>-1.2959</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8282</v>
@@ -35216,7 +35216,7 @@
         <v>-0.389</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.294</v>
+        <v>-1.2938</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8172</v>
@@ -35238,7 +35238,7 @@
         <v>0.2718</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.571</v>
+        <v>-0.5709</v>
       </c>
       <c r="F94" t="n">
         <v>0.2718</v>
@@ -35250,7 +35250,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3036</v>
+        <v>-1.3034</v>
       </c>
       <c r="J94" t="n">
         <v>-0.782</v>
@@ -35263,7 +35263,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.3949</v>
+        <v>-0.3948</v>
       </c>
       <c r="C95" t="n">
         <v>-0.2685</v>
@@ -35272,7 +35272,7 @@
         <v>0.272</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5616</v>
+        <v>-0.5615</v>
       </c>
       <c r="F95" t="n">
         <v>0.272</v>
@@ -35284,7 +35284,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2907</v>
+        <v>-1.2905</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7879</v>
@@ -35306,7 +35306,7 @@
         <v>0.2773</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.4912</v>
+        <v>-0.4911</v>
       </c>
       <c r="F96" t="n">
         <v>0.2773</v>
@@ -35318,7 +35318,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2595</v>
+        <v>-1.2593</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5867</v>
@@ -35331,7 +35331,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.2364</v>
+        <v>-0.2363</v>
       </c>
       <c r="C97" t="n">
         <v>-0.3238</v>
@@ -35352,7 +35352,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1956</v>
+        <v>-1.1954</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5657</v>
@@ -35386,7 +35386,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0589</v>
+        <v>-1.0588</v>
       </c>
       <c r="J98" t="n">
         <v>-0.618</v>
@@ -35399,7 +35399,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.2678</v>
+        <v>-0.2677</v>
       </c>
       <c r="C99" t="n">
         <v>-0.3883</v>
@@ -35408,7 +35408,7 @@
         <v>0.1595</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.3746</v>
+        <v>-0.3745</v>
       </c>
       <c r="F99" t="n">
         <v>0.1595</v>
@@ -35420,7 +35420,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9722</v>
+        <v>-0.972</v>
       </c>
       <c r="J99" t="n">
         <v>-0.505</v>
@@ -35454,7 +35454,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9236</v>
+        <v>-0.9235</v>
       </c>
       <c r="J100" t="n">
         <v>-0.5014</v>
@@ -35467,7 +35467,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.2122</v>
+        <v>-0.2121</v>
       </c>
       <c r="C101" t="n">
         <v>-0.4367</v>
@@ -35488,7 +35488,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8379</v>
+        <v>-0.8378</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4148</v>
@@ -35510,7 +35510,7 @@
         <v>0.2469</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.261</v>
+        <v>-0.2609</v>
       </c>
       <c r="F102" t="n">
         <v>0.2469</v>
@@ -35522,7 +35522,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7408</v>
+        <v>-0.7407</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4062</v>
@@ -35556,7 +35556,7 @@
         <v>-0.1008</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8169</v>
+        <v>-0.8168</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3561</v>
@@ -35624,7 +35624,7 @@
         <v>-0.1008</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7663</v>
+        <v>-0.7662</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2459</v>
@@ -35680,7 +35680,7 @@
         <v>0.6536</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.1674</v>
+        <v>-0.1673</v>
       </c>
       <c r="F107" t="n">
         <v>0.6536</v>
@@ -35692,7 +35692,7 @@
         <v>-0.0433</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7116</v>
+        <v>-0.7115</v>
       </c>
       <c r="J107" t="n">
         <v>-0.26</v>
@@ -35714,7 +35714,7 @@
         <v>0.79</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.1527</v>
+        <v>-0.1526</v>
       </c>
       <c r="F108" t="n">
         <v>0.79</v>
@@ -35726,7 +35726,7 @@
         <v>-0.0433</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6518</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2912</v>
@@ -35828,7 +35828,7 @@
         <v>0.143</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5679</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2386</v>
@@ -35896,7 +35896,7 @@
         <v>0.1698</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5477</v>
+        <v>-0.5476</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2356</v>
@@ -35930,7 +35930,7 @@
         <v>0.1698</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5251</v>
+        <v>-0.525</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2192</v>
@@ -35964,7 +35964,7 @@
         <v>0.1933</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5073</v>
+        <v>-0.5072</v>
       </c>
       <c r="J115" t="n">
         <v>-0.25</v>
@@ -35998,7 +35998,7 @@
         <v>0.1933</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4797</v>
+        <v>-0.4796</v>
       </c>
       <c r="J116" t="n">
         <v>-0.1351</v>
@@ -36032,7 +36032,7 @@
         <v>0.1933</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4537</v>
+        <v>-0.4536</v>
       </c>
       <c r="J117" t="n">
         <v>-0.1128</v>
@@ -36066,7 +36066,7 @@
         <v>0.2519</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3466</v>
+        <v>-0.3465</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1607</v>
@@ -36406,7 +36406,7 @@
         <v>0.4715</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1409</v>
+        <v>0.1408</v>
       </c>
       <c r="J128" t="n">
         <v>-0.0397</v>
@@ -36440,7 +36440,7 @@
         <v>0.4715</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1322</v>
+        <v>0.1321</v>
       </c>
       <c r="J129" t="n">
         <v>-0.0728</v>
@@ -36508,7 +36508,7 @@
         <v>0.5479000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0609</v>
+        <v>0.0608</v>
       </c>
       <c r="J131" t="n">
         <v>-0.0633</v>
@@ -36576,7 +36576,7 @@
         <v>0.6268</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1091</v>
+        <v>0.109</v>
       </c>
       <c r="J133" t="n">
         <v>0.0044</v>
@@ -36712,7 +36712,7 @@
         <v>0.677</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1358</v>
+        <v>-0.1357</v>
       </c>
       <c r="J137" t="n">
         <v>0.0452</v>
@@ -36904,7 +36904,7 @@
         <v>0.354</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4166</v>
+        <v>0.4167</v>
       </c>
       <c r="F143" t="n">
         <v>0.354</v>
@@ -36984,7 +36984,7 @@
         <v>0.7694</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="J145" t="n">
         <v>0.4369</v>
@@ -37188,7 +37188,7 @@
         <v>0.8091</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.0069</v>
+        <v>-0.007</v>
       </c>
       <c r="J151" t="n">
         <v>0.5754</v>
@@ -37303,7 +37303,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.6454</v>
+        <v>0.6453</v>
       </c>
       <c r="C155" t="n">
         <v>0.2633</v>
@@ -37358,7 +37358,7 @@
         <v>0.8138</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0861</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J156" t="n">
         <v>0.7721</v>
@@ -37371,7 +37371,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.6434</v>
+        <v>0.6433</v>
       </c>
       <c r="C157" t="n">
         <v>0.3304</v>
@@ -37392,7 +37392,7 @@
         <v>0.7919</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1106</v>
+        <v>0.1105</v>
       </c>
       <c r="J157" t="n">
         <v>0.8101</v>
@@ -37426,7 +37426,7 @@
         <v>0.7919</v>
       </c>
       <c r="I158" t="n">
-        <v>0.09</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J158" t="n">
         <v>1.005</v>
@@ -37494,7 +37494,7 @@
         <v>0.8306</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0179</v>
+        <v>-0.018</v>
       </c>
       <c r="J160" t="n">
         <v>1.0225</v>
@@ -37528,7 +37528,7 @@
         <v>0.8306</v>
       </c>
       <c r="I161" t="n">
-        <v>0.016</v>
+        <v>0.0159</v>
       </c>
       <c r="J161" t="n">
         <v>1.03</v>
@@ -37562,7 +37562,7 @@
         <v>0.8306</v>
       </c>
       <c r="I162" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J162" t="n">
         <v>1.1068</v>
@@ -37584,7 +37584,7 @@
         <v>0.7772</v>
       </c>
       <c r="E163" t="n">
-        <v>0.6918</v>
+        <v>0.6917</v>
       </c>
       <c r="F163" t="n">
         <v>0.7772</v>
@@ -37596,7 +37596,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>0.074</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J163" t="n">
         <v>1.2073</v>
@@ -37630,7 +37630,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0998</v>
+        <v>0.0997</v>
       </c>
       <c r="J164" t="n">
         <v>1.2102</v>
@@ -37677,7 +37677,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.7441</v>
+        <v>0.744</v>
       </c>
       <c r="C166" t="n">
         <v>0.4213</v>
@@ -37698,7 +37698,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1294</v>
+        <v>0.1293</v>
       </c>
       <c r="J166" t="n">
         <v>1.2724</v>
@@ -37732,7 +37732,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0997</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J167" t="n">
         <v>1.3895</v>
@@ -37754,7 +37754,7 @@
         <v>0.8165</v>
       </c>
       <c r="E168" t="n">
-        <v>0.7654</v>
+        <v>0.7653</v>
       </c>
       <c r="F168" t="n">
         <v>0.8165</v>
@@ -37766,7 +37766,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0891</v>
+        <v>0.089</v>
       </c>
       <c r="J168" t="n">
         <v>1.4432</v>
@@ -37834,7 +37834,7 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0498</v>
+        <v>-0.0499</v>
       </c>
       <c r="J170" t="n">
         <v>1.539</v>
@@ -37868,7 +37868,7 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0323</v>
+        <v>-0.0324</v>
       </c>
       <c r="J171" t="n">
         <v>1.5072</v>
@@ -37902,7 +37902,7 @@
         <v>0.9549</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0272</v>
+        <v>-0.0273</v>
       </c>
       <c r="J172" t="n">
         <v>1.657</v>
@@ -37958,7 +37958,7 @@
         <v>0.7543</v>
       </c>
       <c r="E174" t="n">
-        <v>0.7864</v>
+        <v>0.7863</v>
       </c>
       <c r="F174" t="n">
         <v>0.7543</v>
@@ -37970,7 +37970,7 @@
         <v>0.9549</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0878</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J174" t="n">
         <v>1.6763</v>
@@ -38004,7 +38004,7 @@
         <v>0.9513</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1328</v>
+        <v>-0.1329</v>
       </c>
       <c r="J175" t="n">
         <v>1.8108</v>
@@ -38072,7 +38072,7 @@
         <v>0.9513</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1946</v>
+        <v>-0.1947</v>
       </c>
       <c r="J177" t="n">
         <v>1.8039</v>
@@ -38140,7 +38140,7 @@
         <v>0.451</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1768</v>
+        <v>-0.1769</v>
       </c>
       <c r="J179" t="n">
         <v>1.9407</v>
@@ -38174,7 +38174,7 @@
         <v>0.451</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1651</v>
+        <v>-0.1652</v>
       </c>
       <c r="J180" t="n">
         <v>1.9108</v>
@@ -38208,7 +38208,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1576</v>
+        <v>-0.1577</v>
       </c>
       <c r="J181" t="n">
         <v>1.9529</v>
@@ -38230,7 +38230,7 @@
         <v>0.7829</v>
       </c>
       <c r="E182" t="n">
-        <v>0.6129</v>
+        <v>0.6128</v>
       </c>
       <c r="F182" t="n">
         <v>0.7829</v>
@@ -38242,7 +38242,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.185</v>
+        <v>-0.1851</v>
       </c>
       <c r="J182" t="n">
         <v>2.0493</v>
@@ -38276,7 +38276,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2001</v>
+        <v>-0.2002</v>
       </c>
       <c r="J183" t="n">
         <v>2.1742</v>
@@ -38298,7 +38298,7 @@
         <v>0.7181</v>
       </c>
       <c r="E184" t="n">
-        <v>0.4556</v>
+        <v>0.4555</v>
       </c>
       <c r="F184" t="n">
         <v>0.7181</v>
@@ -38310,7 +38310,7 @@
         <v>-0.4462</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3388</v>
+        <v>-0.3389</v>
       </c>
       <c r="J184" t="n">
         <v>2.1149</v>
@@ -38344,7 +38344,7 @@
         <v>-0.4462</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3036</v>
+        <v>-0.3037</v>
       </c>
       <c r="J185" t="n">
         <v>2.1141</v>
@@ -38378,7 +38378,7 @@
         <v>-0.4462</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.263</v>
+        <v>-0.2631</v>
       </c>
       <c r="J186" t="n">
         <v>2.1842</v>
@@ -38412,7 +38412,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1965</v>
+        <v>-0.1966</v>
       </c>
       <c r="J187" t="n">
         <v>2.2688</v>
@@ -38446,7 +38446,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1783</v>
+        <v>-0.1784</v>
       </c>
       <c r="J188" t="n">
         <v>2.013</v>
@@ -38480,7 +38480,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1426</v>
+        <v>-0.1427</v>
       </c>
       <c r="J189" t="n">
         <v>1.7738</v>
@@ -38502,7 +38502,7 @@
         <v>0.2578</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3086</v>
+        <v>0.3085</v>
       </c>
       <c r="F190" t="n">
         <v>0.2578</v>
@@ -38514,7 +38514,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1345</v>
+        <v>-0.1346</v>
       </c>
       <c r="J190" t="n">
         <v>1.5321</v>
@@ -38548,7 +38548,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0946</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J191" t="n">
         <v>1.3067</v>
@@ -38582,7 +38582,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0498</v>
+        <v>-0.0499</v>
       </c>
       <c r="J192" t="n">
         <v>1.0402</v>
@@ -38616,7 +38616,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0133</v>
+        <v>-0.0134</v>
       </c>
       <c r="J193" t="n">
         <v>0.855</v>
@@ -38629,7 +38629,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.1685</v>
+        <v>0.1684</v>
       </c>
       <c r="C194" t="n">
         <v>0.2157</v>
@@ -38650,7 +38650,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0501</v>
+        <v>0.0499</v>
       </c>
       <c r="J194" t="n">
         <v>0.5541</v>
@@ -38672,7 +38672,7 @@
         <v>0.1957</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1435</v>
+        <v>0.1434</v>
       </c>
       <c r="F195" t="n">
         <v>0.1957</v>
@@ -38684,7 +38684,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I195" t="n">
-        <v>0.112</v>
+        <v>0.1118</v>
       </c>
       <c r="J195" t="n">
         <v>0.3553</v>
@@ -38697,7 +38697,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.1746</v>
+        <v>0.1745</v>
       </c>
       <c r="C196" t="n">
         <v>0.031</v>
@@ -38718,7 +38718,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1831</v>
+        <v>0.1829</v>
       </c>
       <c r="J196" t="n">
         <v>0.0803</v>
@@ -38740,7 +38740,7 @@
         <v>0.0738</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1395</v>
+        <v>0.1394</v>
       </c>
       <c r="F197" t="n">
         <v>0.0738</v>
@@ -38752,7 +38752,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2267</v>
+        <v>0.2265</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1028</v>
@@ -38786,7 +38786,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2338</v>
+        <v>0.2336</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4271</v>
@@ -38820,7 +38820,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2802</v>
+        <v>0.28</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6688</v>
@@ -38833,7 +38833,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.1089</v>
+        <v>0.1088</v>
       </c>
       <c r="C200" t="n">
         <v>-0.1771</v>
@@ -38854,7 +38854,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2867</v>
+        <v>0.2865</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6202</v>
@@ -38876,7 +38876,7 @@
         <v>0.4293</v>
       </c>
       <c r="E201" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="F201" t="n">
         <v>0.4293</v>
@@ -38888,7 +38888,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3002</v>
+        <v>0.3</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6014</v>
@@ -38901,7 +38901,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2562</v>
+        <v>0.2561</v>
       </c>
       <c r="C202" t="n">
         <v>-0.2762</v>
@@ -38910,7 +38910,7 @@
         <v>0.4634</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2044</v>
+        <v>0.2043</v>
       </c>
       <c r="F202" t="n">
         <v>0.4634</v>
@@ -38922,7 +38922,7 @@
         <v>0.091</v>
       </c>
       <c r="I202" t="n">
-        <v>0.385</v>
+        <v>0.3847</v>
       </c>
       <c r="J202" t="n">
         <v>-0.416</v>
@@ -38956,7 +38956,7 @@
         <v>0.091</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3977</v>
+        <v>0.3975</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5065</v>
@@ -38978,7 +38978,7 @@
         <v>0.6375</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2098</v>
+        <v>0.2097</v>
       </c>
       <c r="F204" t="n">
         <v>0.6375</v>
@@ -38990,7 +38990,7 @@
         <v>0.091</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4316</v>
+        <v>0.4314</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4266</v>
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5599</v>
       </c>
       <c r="C205" t="n">
         <v>-0.4359</v>
@@ -39012,7 +39012,7 @@
         <v>1.7557</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2611</v>
+        <v>0.261</v>
       </c>
       <c r="F205" t="n">
         <v>1.7557</v>
@@ -39024,7 +39024,7 @@
         <v>0.2135</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4372</v>
+        <v>0.437</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3874</v>
@@ -39058,7 +39058,7 @@
         <v>0.2135</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4281</v>
+        <v>0.4279</v>
       </c>
       <c r="J206" t="n">
         <v>-0.253</v>
@@ -39092,7 +39092,7 @@
         <v>0.2135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4432</v>
+        <v>0.4431</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2922</v>
@@ -39105,7 +39105,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.4214</v>
+        <v>0.4213</v>
       </c>
       <c r="C208" t="n">
         <v>-0.5053</v>
@@ -39126,7 +39126,7 @@
         <v>0.3986</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4733</v>
+        <v>0.4731</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2508</v>
@@ -39139,7 +39139,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.5998</v>
+        <v>0.5997</v>
       </c>
       <c r="C209" t="n">
         <v>-0.5758</v>
@@ -39148,7 +39148,7 @@
         <v>1.2979</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4253</v>
+        <v>0.4252</v>
       </c>
       <c r="F209" t="n">
         <v>1.2979</v>
@@ -39160,7 +39160,7 @@
         <v>0.3986</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6143</v>
+        <v>0.6142</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1699</v>
@@ -39182,7 +39182,7 @@
         <v>1.2949</v>
       </c>
       <c r="E210" t="n">
-        <v>0.4236</v>
+        <v>0.4235</v>
       </c>
       <c r="F210" t="n">
         <v>1.2949</v>
@@ -39194,7 +39194,7 @@
         <v>0.3986</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6613</v>
+        <v>0.6611</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1676</v>
@@ -39216,7 +39216,7 @@
         <v>1.3412</v>
       </c>
       <c r="E211" t="n">
-        <v>0.5079</v>
+        <v>0.5078</v>
       </c>
       <c r="F211" t="n">
         <v>1.3412</v>
@@ -39228,7 +39228,7 @@
         <v>0.5324</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7561</v>
+        <v>0.7559</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1123</v>
@@ -39241,7 +39241,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.6939</v>
+        <v>0.6938</v>
       </c>
       <c r="C212" t="n">
         <v>-0.7396</v>
@@ -39262,7 +39262,7 @@
         <v>0.5324</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7926</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1272</v>
@@ -39296,7 +39296,7 @@
         <v>0.5324</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8153</v>
+        <v>0.8151</v>
       </c>
       <c r="J213" t="n">
         <v>-0.0809</v>
@@ -39318,7 +39318,7 @@
         <v>1.7312</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6239</v>
+        <v>0.6238</v>
       </c>
       <c r="F214" t="n">
         <v>1.7312</v>
@@ -39330,7 +39330,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9182</v>
+        <v>0.918</v>
       </c>
       <c r="J214" t="n">
         <v>0.0795</v>
@@ -39364,7 +39364,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9879</v>
+        <v>0.9877</v>
       </c>
       <c r="J215" t="n">
         <v>0.0289</v>
@@ -39377,7 +39377,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8767</v>
+        <v>0.8766</v>
       </c>
       <c r="C216" t="n">
         <v>-0.9258</v>
@@ -39398,7 +39398,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9281</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0187</v>
@@ -39411,7 +39411,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8159</v>
       </c>
       <c r="C217" t="n">
         <v>-0.9187</v>
@@ -39432,7 +39432,7 @@
         <v>0.6974</v>
       </c>
       <c r="I217" t="n">
-        <v>0.799</v>
+        <v>0.7988</v>
       </c>
       <c r="J217" t="n">
         <v>0.1675</v>
@@ -39466,7 +39466,7 @@
         <v>0.6974</v>
       </c>
       <c r="I218" t="n">
-        <v>0.729</v>
+        <v>0.7288</v>
       </c>
       <c r="J218" t="n">
         <v>0.1381</v>
@@ -39479,7 +39479,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8579</v>
+        <v>0.8578</v>
       </c>
       <c r="C219" t="n">
         <v>-1.0961</v>
@@ -39500,7 +39500,7 @@
         <v>0.6974</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8003</v>
+        <v>0.8002</v>
       </c>
       <c r="J219" t="n">
         <v>0.2431</v>
@@ -39534,7 +39534,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8024</v>
+        <v>0.8022</v>
       </c>
       <c r="J220" t="n">
         <v>0.2685</v>
@@ -39556,7 +39556,7 @@
         <v>1.8104</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7128</v>
+        <v>0.7127</v>
       </c>
       <c r="F221" t="n">
         <v>1.8104</v>
@@ -39568,7 +39568,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8218</v>
+        <v>0.8216</v>
       </c>
       <c r="J221" t="n">
         <v>0.3099</v>
@@ -39602,7 +39602,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9206</v>
       </c>
       <c r="J222" t="n">
         <v>0.249</v>
@@ -39615,7 +39615,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.9837</v>
+        <v>0.9836</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39624,7 +39624,7 @@
         <v>1.7742</v>
       </c>
       <c r="E223" t="n">
-        <v>0.7861</v>
+        <v>0.786</v>
       </c>
       <c r="F223" t="n">
         <v>1.7742</v>
@@ -39636,7 +39636,7 @@
         <v>0.8441</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0458</v>
+        <v>1.0455</v>
       </c>
       <c r="J223" t="n">
         <v>0.3667</v>
@@ -39658,7 +39658,7 @@
         <v>1.6966</v>
       </c>
       <c r="E224" t="n">
-        <v>0.7951</v>
+        <v>0.795</v>
       </c>
       <c r="F224" t="n">
         <v>1.6966</v>
@@ -39670,7 +39670,7 @@
         <v>0.8441</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0642</v>
+        <v>1.0639</v>
       </c>
       <c r="J224" t="n">
         <v>0.3764</v>
@@ -39683,7 +39683,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.9905</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="C225" t="n">
         <v>-1.3984</v>
@@ -39692,7 +39692,7 @@
         <v>1.6703</v>
       </c>
       <c r="E225" t="n">
-        <v>0.8205</v>
+        <v>0.8204</v>
       </c>
       <c r="F225" t="n">
         <v>1.6703</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1523</v>
+        <v>1.152</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39726,7 +39726,7 @@
         <v>1.477</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8519</v>
+        <v>0.8518</v>
       </c>
       <c r="F226" t="n">
         <v>1.477</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2211</v>
+        <v>1.2208</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -39751,7 +39751,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.9853</v>
+        <v>0.9852</v>
       </c>
       <c r="C227" t="n">
         <v>-1.4189</v>
@@ -39772,7 +39772,7 @@
         <v>0.9485</v>
       </c>
       <c r="I227" t="n">
-        <v>1.251</v>
+        <v>1.2507</v>
       </c>
       <c r="J227" t="n">
         <v>0.355</v>
@@ -39794,7 +39794,7 @@
         <v>1.3813</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8611</v>
+        <v>0.861</v>
       </c>
       <c r="F228" t="n">
         <v>1.3813</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3226</v>
+        <v>1.3223</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39819,7 +39819,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.9941</v>
+        <v>0.994</v>
       </c>
       <c r="C229" t="n">
         <v>-1.3839</v>
@@ -39828,7 +39828,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8799</v>
+        <v>0.8798</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.251</v>
+        <v>1.2507</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39862,7 +39862,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9349</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39874,7 +39874,7 @@
         <v>1.0464</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3535</v>
+        <v>1.3531</v>
       </c>
       <c r="J230" t="n">
         <v>0.4839</v>
@@ -39896,7 +39896,7 @@
         <v>1.4899</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9493</v>
+        <v>0.9492</v>
       </c>
       <c r="F231" t="n">
         <v>1.4899</v>
@@ -39908,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4945</v>
+        <v>1.4942</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39921,7 +39921,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0792</v>
+        <v>1.0791</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39930,7 +39930,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0032</v>
+        <v>1.0031</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5594</v>
+        <v>1.5589</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -39955,7 +39955,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0383</v>
+        <v>1.0382</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -39964,7 +39964,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0023</v>
+        <v>1.0022</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6218</v>
+        <v>1.6214</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -39989,7 +39989,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.0612</v>
+        <v>1.0611</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -39998,7 +39998,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.002</v>
+        <v>1.0019</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6681</v>
+        <v>1.6677</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40032,7 +40032,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0262</v>
+        <v>1.0261</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7502</v>
+        <v>1.7498</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40057,7 +40057,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0849</v>
+        <v>1.0848</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -40066,7 +40066,7 @@
         <v>1.3708</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0134</v>
+        <v>1.0133</v>
       </c>
       <c r="F236" t="n">
         <v>1.3708</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7857</v>
+        <v>1.7852</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40091,7 +40091,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0238</v>
+        <v>1.0237</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -40100,7 +40100,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9247</v>
+        <v>0.9246</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5602</v>
+        <v>1.5599</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40125,7 +40125,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9776</v>
+        <v>0.9775</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5462</v>
+        <v>1.5458</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40159,7 +40159,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.0002</v>
+        <v>1.0001</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40168,7 +40168,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9639</v>
+        <v>0.9638</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7097</v>
+        <v>1.7093</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40202,7 +40202,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9603</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7858</v>
+        <v>1.7854</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40236,7 +40236,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9579</v>
+        <v>0.9577</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8052</v>
+        <v>1.8048</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0351</v>
+        <v>1.035</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40270,7 +40270,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9352</v>
+        <v>0.9351</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8781</v>
+        <v>1.8776</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40304,7 +40304,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9067</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8117</v>
+        <v>1.8113</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40329,7 +40329,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.0245</v>
+        <v>1.0244</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40338,7 +40338,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9425</v>
+        <v>0.9424</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7661</v>
+        <v>1.7657</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40363,7 +40363,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.0014</v>
+        <v>1.0013</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40372,7 +40372,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8577</v>
+        <v>0.8576</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6409</v>
+        <v>1.6406</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40397,7 +40397,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0271</v>
+        <v>1.027</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40406,7 +40406,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.889</v>
+        <v>0.8889</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7368</v>
+        <v>1.7364</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40431,7 +40431,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9712</v>
+        <v>0.9711</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40440,7 +40440,7 @@
         <v>1.4541</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8505</v>
+        <v>0.8504</v>
       </c>
       <c r="F247" t="n">
         <v>1.4541</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7664</v>
+        <v>1.766</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40465,7 +40465,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9419</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40474,7 +40474,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8524</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.882</v>
+        <v>1.8815</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40499,7 +40499,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9283</v>
+        <v>0.9282</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40508,7 +40508,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8813</v>
+        <v>0.8812</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9489</v>
+        <v>1.9484</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40533,7 +40533,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9398</v>
+        <v>0.9397</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40542,7 +40542,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8708</v>
+        <v>0.8707</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0149</v>
+        <v>2.0144</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40567,7 +40567,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9813</v>
+        <v>0.9811</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40576,7 +40576,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9176</v>
+        <v>0.9175</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1897</v>
+        <v>2.1891</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40601,7 +40601,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9872</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40610,7 +40610,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9317</v>
+        <v>0.9315</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3164</v>
+        <v>2.3158</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40635,7 +40635,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7483</v>
+        <v>0.7482</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40644,7 +40644,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.927</v>
+        <v>0.9268</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3415</v>
+        <v>2.3408</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40669,7 +40669,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8773</v>
+        <v>0.8772</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40678,7 +40678,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9355</v>
+        <v>0.9354</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4479</v>
+        <v>2.4472</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8389</v>
+        <v>0.8388</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40712,7 +40712,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9378</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5251</v>
+        <v>2.5244</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40737,7 +40737,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8175</v>
+        <v>0.8173</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40746,7 +40746,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.8994</v>
+        <v>0.8992</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5483</v>
+        <v>2.5475</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40771,7 +40771,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7472</v>
+        <v>0.747</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40780,7 +40780,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8535</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.675</v>
+        <v>2.6742</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7887</v>
+        <v>0.7885</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40814,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9125</v>
+        <v>0.9123</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8253</v>
+        <v>2.8244</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8245</v>
+        <v>0.8243</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40848,7 +40848,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9496</v>
+        <v>0.9494</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0166</v>
+        <v>3.0156</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.947</v>
+        <v>0.9467</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.947</v>
+        <v>0.9467</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.006</v>
+        <v>3.005</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9342</v>
+        <v>0.9379</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9342</v>
+        <v>0.9379</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9548</v>
+        <v>2.9696</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.292</v>
+        <v>1.299</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.565</v>
+        <v>1.566</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.098</v>
+        <v>2.077</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.836</v>
+        <v>2.814</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.986</v>
+        <v>3.964</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.118</v>
+        <v>-0.124</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.037</v>
+        <v>1.016</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.29</v>
+        <v>-1.26</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>64670.957</v>
+        <v>64924.033</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.2925</v>
+        <v>1.2993</v>
       </c>
       <c r="D261" t="n">
-        <v>1.565</v>
+        <v>1.566</v>
       </c>
       <c r="E261" t="n">
-        <v>2.098</v>
+        <v>2.077</v>
       </c>
       <c r="F261" t="n">
-        <v>2.836</v>
+        <v>2.8145</v>
       </c>
       <c r="G261" t="n">
-        <v>3.986</v>
+        <v>3.9643</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6868</v>
+        <v>-0.6801</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.1178</v>
+        <v>-0.1242</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0372</v>
+        <v>1.0157</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>64670.9567</v>
+        <v>64924.0325</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32119,7 +32119,7 @@
         <v>0.2573</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.9016</v>
       </c>
       <c r="F2" t="n">
         <v>0.2573</v>
@@ -32128,7 +32128,7 @@
         <v>-0.3431</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6433</v>
+        <v>-0.6432</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7186</v>
@@ -32147,7 +32147,7 @@
         <v>0.1079</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8505</v>
+        <v>-0.8504</v>
       </c>
       <c r="F3" t="n">
         <v>0.1079</v>
@@ -32156,7 +32156,7 @@
         <v>-0.3209</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.5901</v>
       </c>
       <c r="J3" t="n">
         <v>-1.6403</v>
@@ -32190,7 +32190,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5671</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6492</v>
@@ -32394,7 +32394,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3873</v>
+        <v>-0.3872</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2486</v>
@@ -32462,7 +32462,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2055</v>
+        <v>-0.2054</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2107</v>
@@ -32530,7 +32530,7 @@
         <v>-0.1828</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2139</v>
+        <v>-0.2138</v>
       </c>
       <c r="J14" t="n">
         <v>-1.1529</v>
@@ -32700,7 +32700,7 @@
         <v>-0.116</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1809</v>
+        <v>-0.1808</v>
       </c>
       <c r="J19" t="n">
         <v>-0.86</v>
@@ -32870,7 +32870,7 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0532</v>
+        <v>-0.0531</v>
       </c>
       <c r="J24" t="n">
         <v>-0.5635</v>
@@ -33176,7 +33176,7 @@
         <v>0.2333</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0374</v>
+        <v>-0.0373</v>
       </c>
       <c r="J33" t="n">
         <v>-0.1799</v>
@@ -33325,7 +33325,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.4349</v>
+        <v>-0.4348</v>
       </c>
       <c r="C38" t="n">
         <v>-0.1832</v>
@@ -33393,7 +33393,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.493</v>
+        <v>-0.4929</v>
       </c>
       <c r="C40" t="n">
         <v>-0.192</v>
@@ -33448,7 +33448,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5587</v>
+        <v>-0.5586</v>
       </c>
       <c r="J41" t="n">
         <v>0.3765</v>
@@ -33640,7 +33640,7 @@
         <v>0.7934</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.9167</v>
       </c>
       <c r="F47" t="n">
         <v>0.7934</v>
@@ -33652,7 +33652,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.852</v>
+        <v>-0.8519</v>
       </c>
       <c r="J47" t="n">
         <v>0.741</v>
@@ -33686,7 +33686,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9331</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>0.7829</v>
@@ -33720,7 +33720,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0531</v>
+        <v>-1.053</v>
       </c>
       <c r="J49" t="n">
         <v>0.983</v>
@@ -33767,7 +33767,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.8326</v>
+        <v>-0.8325</v>
       </c>
       <c r="C51" t="n">
         <v>0.2917</v>
@@ -33810,7 +33810,7 @@
         <v>0.0701</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1851</v>
+        <v>-1.185</v>
       </c>
       <c r="F52" t="n">
         <v>0.0701</v>
@@ -33822,7 +33822,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0193</v>
+        <v>-1.0192</v>
       </c>
       <c r="J52" t="n">
         <v>0.4738</v>
@@ -33844,7 +33844,7 @@
         <v>0.0622</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2335</v>
+        <v>-1.2334</v>
       </c>
       <c r="F53" t="n">
         <v>0.0622</v>
@@ -33856,7 +33856,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9928</v>
+        <v>-0.9927</v>
       </c>
       <c r="J53" t="n">
         <v>0.1904</v>
@@ -33890,7 +33890,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0187</v>
+        <v>-1.0186</v>
       </c>
       <c r="J54" t="n">
         <v>0.1077</v>
@@ -33924,7 +33924,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9933</v>
+        <v>-0.9932</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0219</v>
@@ -33937,7 +33937,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.2466</v>
+        <v>-1.2465</v>
       </c>
       <c r="C56" t="n">
         <v>1.0216</v>
@@ -33992,7 +33992,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0111</v>
+        <v>-1.011</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4398</v>
@@ -34060,7 +34060,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.104</v>
+        <v>-1.1039</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8167</v>
@@ -34128,7 +34128,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0999</v>
+        <v>-1.0998</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1668</v>
@@ -34150,7 +34150,7 @@
         <v>-0.2593</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.4179</v>
+        <v>-1.4178</v>
       </c>
       <c r="F62" t="n">
         <v>-0.2593</v>
@@ -34252,7 +34252,7 @@
         <v>-0.3014</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.3983</v>
+        <v>-1.3982</v>
       </c>
       <c r="F65" t="n">
         <v>-0.3014</v>
@@ -34320,7 +34320,7 @@
         <v>-0.1867</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.3841</v>
+        <v>-1.384</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1867</v>
@@ -34434,7 +34434,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2137</v>
+        <v>-1.2136</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9639</v>
@@ -34481,7 +34481,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0169</v>
+        <v>-1.0168</v>
       </c>
       <c r="C72" t="n">
         <v>0.5194</v>
@@ -34604,7 +34604,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.212</v>
+        <v>-1.2119</v>
       </c>
       <c r="J75" t="n">
         <v>-1.811</v>
@@ -34685,7 +34685,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7517</v>
+        <v>-0.7516</v>
       </c>
       <c r="C78" t="n">
         <v>0.2407</v>
@@ -34706,7 +34706,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2487</v>
+        <v>-1.2486</v>
       </c>
       <c r="J78" t="n">
         <v>-1.63</v>
@@ -34762,7 +34762,7 @@
         <v>0.2638</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.9215</v>
+        <v>-0.9214</v>
       </c>
       <c r="F80" t="n">
         <v>0.2638</v>
@@ -34808,7 +34808,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3182</v>
+        <v>-1.3181</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4777</v>
@@ -34842,7 +34842,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3341</v>
+        <v>-1.334</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3458</v>
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6604</v>
+        <v>-0.6603</v>
       </c>
       <c r="C83" t="n">
         <v>0.09279999999999999</v>
@@ -34876,7 +34876,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3309</v>
+        <v>-1.3308</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3601</v>
@@ -34910,7 +34910,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3177</v>
+        <v>-1.3176</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3222</v>
@@ -34966,7 +34966,7 @@
         <v>0.2368</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.7897</v>
       </c>
       <c r="F86" t="n">
         <v>0.2368</v>
@@ -35059,7 +35059,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.5037</v>
+        <v>-0.5036</v>
       </c>
       <c r="C89" t="n">
         <v>-0.0515</v>
@@ -35080,7 +35080,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2366</v>
+        <v>-1.2365</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0901</v>
@@ -35093,7 +35093,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.5077</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="C90" t="n">
         <v>-0.0336</v>
@@ -35136,7 +35136,7 @@
         <v>0.1763</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6501</v>
+        <v>-0.65</v>
       </c>
       <c r="F91" t="n">
         <v>0.1763</v>
@@ -35148,7 +35148,7 @@
         <v>-0.389</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.292</v>
+        <v>-1.2919</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9429999999999999</v>
@@ -35182,7 +35182,7 @@
         <v>-0.389</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2959</v>
+        <v>-1.2958</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8282</v>
@@ -35204,7 +35204,7 @@
         <v>0.1767</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6246</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="F93" t="n">
         <v>0.1767</v>
@@ -35216,7 +35216,7 @@
         <v>-0.389</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2938</v>
+        <v>-1.2937</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8172</v>
@@ -35284,7 +35284,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2905</v>
+        <v>-1.2904</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7879</v>
@@ -35297,7 +35297,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3375</v>
+        <v>-0.3374</v>
       </c>
       <c r="C96" t="n">
         <v>-0.2964</v>
@@ -35318,7 +35318,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2593</v>
+        <v>-1.2592</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5867</v>
@@ -35386,7 +35386,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0588</v>
+        <v>-1.0587</v>
       </c>
       <c r="J98" t="n">
         <v>-0.618</v>
@@ -35442,7 +35442,7 @@
         <v>0.0925</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.341</v>
+        <v>-0.3409</v>
       </c>
       <c r="F100" t="n">
         <v>0.0925</v>
@@ -35590,7 +35590,7 @@
         <v>-0.1008</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.7262</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2338</v>
@@ -35658,7 +35658,7 @@
         <v>-0.0433</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7153</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3637</v>
@@ -35671,7 +35671,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.0032</v>
+        <v>-0.0031</v>
       </c>
       <c r="C107" t="n">
         <v>-0.5917</v>
@@ -35862,7 +35862,7 @@
         <v>0.1698</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5522</v>
+        <v>-0.5521</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2412</v>
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.3885</v>
+        <v>0.3886</v>
       </c>
       <c r="C119" t="n">
         <v>-0.5046</v>
@@ -36610,7 +36610,7 @@
         <v>0.6268</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0256</v>
+        <v>0.0257</v>
       </c>
       <c r="J134" t="n">
         <v>-0.0495</v>
@@ -37167,7 +37167,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5488</v>
+        <v>0.5487</v>
       </c>
       <c r="C151" t="n">
         <v>0.284</v>
@@ -37324,7 +37324,7 @@
         <v>0.8138</v>
       </c>
       <c r="I155" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0743</v>
       </c>
       <c r="J155" t="n">
         <v>0.8483000000000001</v>
@@ -37426,7 +37426,7 @@
         <v>0.7919</v>
       </c>
       <c r="I158" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0898</v>
       </c>
       <c r="J158" t="n">
         <v>1.005</v>
@@ -37460,7 +37460,7 @@
         <v>0.7919</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0254</v>
+        <v>0.0253</v>
       </c>
       <c r="J159" t="n">
         <v>0.9155</v>
@@ -37664,7 +37664,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0893</v>
+        <v>0.0892</v>
       </c>
       <c r="J165" t="n">
         <v>1.321</v>
@@ -37720,7 +37720,7 @@
         <v>0.8496</v>
       </c>
       <c r="E167" t="n">
-        <v>0.7483</v>
+        <v>0.7482</v>
       </c>
       <c r="F167" t="n">
         <v>0.8496</v>
@@ -37936,7 +37936,7 @@
         <v>0.9549</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0254</v>
+        <v>-0.0255</v>
       </c>
       <c r="J173" t="n">
         <v>1.6147</v>
@@ -38038,7 +38038,7 @@
         <v>0.9513</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1411</v>
+        <v>-0.1412</v>
       </c>
       <c r="J176" t="n">
         <v>1.8237</v>
@@ -38094,7 +38094,7 @@
         <v>0.6795</v>
       </c>
       <c r="E178" t="n">
-        <v>0.6804</v>
+        <v>0.6803</v>
       </c>
       <c r="F178" t="n">
         <v>0.6795</v>
@@ -38106,7 +38106,7 @@
         <v>0.451</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.177</v>
+        <v>-0.1771</v>
       </c>
       <c r="J178" t="n">
         <v>1.9331</v>
@@ -38208,7 +38208,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1577</v>
+        <v>-0.1578</v>
       </c>
       <c r="J181" t="n">
         <v>1.9529</v>
@@ -38221,7 +38221,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.6469</v>
+        <v>0.6468</v>
       </c>
       <c r="C182" t="n">
         <v>0.5862000000000001</v>
@@ -38276,7 +38276,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2002</v>
+        <v>-0.2003</v>
       </c>
       <c r="J183" t="n">
         <v>2.1742</v>
@@ -38412,7 +38412,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1966</v>
+        <v>-0.1967</v>
       </c>
       <c r="J187" t="n">
         <v>2.2688</v>
@@ -38434,7 +38434,7 @@
         <v>0.4361</v>
       </c>
       <c r="E188" t="n">
-        <v>0.367</v>
+        <v>0.3669</v>
       </c>
       <c r="F188" t="n">
         <v>0.4361</v>
@@ -38570,7 +38570,7 @@
         <v>0.0008</v>
       </c>
       <c r="E192" t="n">
-        <v>0.2263</v>
+        <v>0.2262</v>
       </c>
       <c r="F192" t="n">
         <v>0.0008</v>
@@ -38582,7 +38582,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0499</v>
+        <v>-0.05</v>
       </c>
       <c r="J192" t="n">
         <v>1.0402</v>
@@ -38616,7 +38616,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0134</v>
+        <v>-0.0135</v>
       </c>
       <c r="J193" t="n">
         <v>0.855</v>
@@ -38638,7 +38638,7 @@
         <v>0.1218</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1801</v>
+        <v>0.18</v>
       </c>
       <c r="F194" t="n">
         <v>0.1218</v>
@@ -38650,7 +38650,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0499</v>
+        <v>0.0498</v>
       </c>
       <c r="J194" t="n">
         <v>0.5541</v>
@@ -38663,7 +38663,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.1539</v>
+        <v>0.1538</v>
       </c>
       <c r="C195" t="n">
         <v>0.1813</v>
@@ -38684,7 +38684,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="J195" t="n">
         <v>0.3553</v>
@@ -38706,7 +38706,7 @@
         <v>0.2432</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1574</v>
+        <v>0.1573</v>
       </c>
       <c r="F196" t="n">
         <v>0.2432</v>
@@ -38718,7 +38718,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1829</v>
+        <v>0.1828</v>
       </c>
       <c r="J196" t="n">
         <v>0.0803</v>
@@ -38752,7 +38752,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2265</v>
+        <v>0.2264</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1028</v>
@@ -38774,7 +38774,7 @@
         <v>0.1608</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0511</v>
+        <v>0.051</v>
       </c>
       <c r="F198" t="n">
         <v>0.1608</v>
@@ -38786,7 +38786,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2336</v>
+        <v>0.2335</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4271</v>
@@ -38888,7 +38888,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3</v>
+        <v>0.2999</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6014</v>
@@ -38956,7 +38956,7 @@
         <v>0.091</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3975</v>
+        <v>0.3974</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5065</v>
@@ -38990,7 +38990,7 @@
         <v>0.091</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4314</v>
+        <v>0.4313</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4266</v>
@@ -39024,7 +39024,7 @@
         <v>0.2135</v>
       </c>
       <c r="I205" t="n">
-        <v>0.437</v>
+        <v>0.4369</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3874</v>
@@ -39058,7 +39058,7 @@
         <v>0.2135</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4279</v>
+        <v>0.4278</v>
       </c>
       <c r="J206" t="n">
         <v>-0.253</v>
@@ -39092,7 +39092,7 @@
         <v>0.2135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4431</v>
+        <v>0.443</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2922</v>
@@ -39114,7 +39114,7 @@
         <v>0.7245</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3456</v>
+        <v>0.3455</v>
       </c>
       <c r="F208" t="n">
         <v>0.7245</v>
@@ -39160,7 +39160,7 @@
         <v>0.3986</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6142</v>
+        <v>0.6141</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1699</v>
@@ -39250,7 +39250,7 @@
         <v>1.4354</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5085</v>
+        <v>0.5084</v>
       </c>
       <c r="F212" t="n">
         <v>1.4354</v>
@@ -39296,7 +39296,7 @@
         <v>0.5324</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8151</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J213" t="n">
         <v>-0.0809</v>
@@ -39330,7 +39330,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>0.918</v>
+        <v>0.9179</v>
       </c>
       <c r="J214" t="n">
         <v>0.0795</v>
@@ -39364,7 +39364,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9877</v>
+        <v>0.9876</v>
       </c>
       <c r="J215" t="n">
         <v>0.0289</v>
@@ -39432,7 +39432,7 @@
         <v>0.6974</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7988</v>
+        <v>0.7987</v>
       </c>
       <c r="J217" t="n">
         <v>0.1675</v>
@@ -39445,7 +39445,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.9097</v>
+        <v>0.9096</v>
       </c>
       <c r="C218" t="n">
         <v>-1.0065</v>
@@ -39454,7 +39454,7 @@
         <v>2.1396</v>
       </c>
       <c r="E218" t="n">
-        <v>0.6022</v>
+        <v>0.6021</v>
       </c>
       <c r="F218" t="n">
         <v>2.1396</v>
@@ -39488,7 +39488,7 @@
         <v>1.6761</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6533</v>
+        <v>0.6532</v>
       </c>
       <c r="F219" t="n">
         <v>1.6761</v>
@@ -39500,7 +39500,7 @@
         <v>0.6974</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8002</v>
+        <v>0.8001</v>
       </c>
       <c r="J219" t="n">
         <v>0.2431</v>
@@ -39581,7 +39581,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.9277</v>
+        <v>0.9276</v>
       </c>
       <c r="C222" t="n">
         <v>-1.4025</v>
@@ -39636,7 +39636,7 @@
         <v>0.8441</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0455</v>
+        <v>1.0454</v>
       </c>
       <c r="J223" t="n">
         <v>0.3667</v>
@@ -39649,7 +39649,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.9754</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="C224" t="n">
         <v>-1.3976</v>
@@ -39670,7 +39670,7 @@
         <v>0.8441</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0639</v>
+        <v>1.0638</v>
       </c>
       <c r="J224" t="n">
         <v>0.3764</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.152</v>
+        <v>1.1519</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39717,7 +39717,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9769</v>
+        <v>0.9768</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2208</v>
+        <v>1.2207</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3223</v>
+        <v>1.3222</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2507</v>
+        <v>1.2506</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.9828</v>
+        <v>0.9827</v>
       </c>
       <c r="C230" t="n">
         <v>-1.8168</v>
@@ -39874,7 +39874,7 @@
         <v>1.0464</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3531</v>
+        <v>1.353</v>
       </c>
       <c r="J230" t="n">
         <v>0.4839</v>
@@ -39887,7 +39887,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0574</v>
+        <v>1.0573</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -39908,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4942</v>
+        <v>1.494</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5589</v>
+        <v>1.5588</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6214</v>
+        <v>1.6213</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -39989,7 +39989,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.0611</v>
+        <v>1.061</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6677</v>
+        <v>1.6675</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40023,7 +40023,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.0882</v>
+        <v>1.0881</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -40032,7 +40032,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0261</v>
+        <v>1.026</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7498</v>
+        <v>1.7497</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7852</v>
+        <v>1.7851</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40100,7 +40100,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9246</v>
+        <v>0.9245</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5599</v>
+        <v>1.5597</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40134,7 +40134,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9183</v>
+        <v>0.9182</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5458</v>
+        <v>1.5457</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40168,7 +40168,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9638</v>
+        <v>0.9637</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7093</v>
+        <v>1.7092</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40193,7 +40193,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0186</v>
+        <v>1.0185</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7854</v>
+        <v>1.7853</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0248</v>
+        <v>1.0247</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8048</v>
+        <v>1.8047</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8776</v>
+        <v>1.8775</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40295,7 +40295,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9866</v>
+        <v>0.9865</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8113</v>
+        <v>1.8112</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7657</v>
+        <v>1.7656</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6406</v>
+        <v>1.6405</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40406,7 +40406,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8889</v>
+        <v>0.8888</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7364</v>
+        <v>1.7363</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.766</v>
+        <v>1.7658</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40465,7 +40465,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9419</v>
+        <v>0.9418</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8815</v>
+        <v>1.8814</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40508,7 +40508,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8812</v>
+        <v>0.8811</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9484</v>
+        <v>1.9483</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40533,7 +40533,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9397</v>
+        <v>0.9396</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0144</v>
+        <v>2.0143</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40576,7 +40576,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9175</v>
+        <v>0.9174</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1891</v>
+        <v>2.1889</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3158</v>
+        <v>2.3156</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3408</v>
+        <v>2.3406</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40669,7 +40669,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8772</v>
+        <v>0.8771</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40678,7 +40678,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9354</v>
+        <v>0.9353</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4472</v>
+        <v>2.4469</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8388</v>
+        <v>0.8387</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40712,7 +40712,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9378</v>
+        <v>0.9377</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5244</v>
+        <v>2.5241</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5475</v>
+        <v>2.5473</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40780,7 +40780,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8532</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6742</v>
+        <v>2.6739</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7885</v>
+        <v>0.7884</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40814,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9123</v>
+        <v>0.9122</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8244</v>
+        <v>2.8241</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40848,7 +40848,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9494</v>
+        <v>0.9493</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0156</v>
+        <v>3.0153</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.005</v>
+        <v>3.0047</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9379</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9379</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9696</v>
+        <v>2.9742</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>-0.523</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="42">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>-0.621</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="86">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>64924.033</v>
+        <v>65060.568</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>64924.0325</v>
+        <v>65060.568</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32141,7 +32141,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.6109</v>
+        <v>-0.6108</v>
       </c>
       <c r="D3" t="n">
         <v>0.1079</v>
@@ -32224,7 +32224,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5457</v>
+        <v>-0.5456</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5156</v>
@@ -32258,7 +32258,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5351</v>
+        <v>-0.535</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4222</v>
@@ -32326,7 +32326,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4091</v>
+        <v>-0.409</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3624</v>
@@ -32360,7 +32360,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4124</v>
+        <v>-0.4123</v>
       </c>
       <c r="J9" t="n">
         <v>-1.394</v>
@@ -32407,7 +32407,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.4983</v>
+        <v>-0.4982</v>
       </c>
       <c r="C11" t="n">
         <v>-0.3532</v>
@@ -32564,7 +32564,7 @@
         <v>-0.1828</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1529</v>
+        <v>-0.1528</v>
       </c>
       <c r="J15" t="n">
         <v>-1.1295</v>
@@ -32666,7 +32666,7 @@
         <v>-0.1031</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2131</v>
+        <v>-0.213</v>
       </c>
       <c r="J18" t="n">
         <v>-0.9886</v>
@@ -33210,7 +33210,7 @@
         <v>-0.225</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0871</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J34" t="n">
         <v>-0.0392</v>
@@ -33346,7 +33346,7 @@
         <v>-0.6075</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3749</v>
+        <v>-0.3748</v>
       </c>
       <c r="J38" t="n">
         <v>0.2114</v>
@@ -33754,7 +33754,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0995</v>
+        <v>-1.0994</v>
       </c>
       <c r="J50" t="n">
         <v>0.7647</v>
@@ -33788,7 +33788,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1113</v>
+        <v>-1.1112</v>
       </c>
       <c r="J51" t="n">
         <v>0.6076</v>
@@ -34094,7 +34094,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1191</v>
+        <v>-1.119</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9842</v>
@@ -34196,7 +34196,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0937</v>
+        <v>-1.0936</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4597</v>
@@ -34230,7 +34230,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0727</v>
+        <v>-1.0726</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6947</v>
@@ -34264,7 +34264,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0317</v>
+        <v>-1.0316</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8174</v>
@@ -34400,7 +34400,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1959</v>
+        <v>-1.1958</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0592</v>
@@ -34536,7 +34536,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.196</v>
+        <v>-1.1959</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8566</v>
@@ -34638,7 +34638,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2423</v>
+        <v>-1.2422</v>
       </c>
       <c r="J76" t="n">
         <v>-1.702</v>
@@ -34672,7 +34672,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2096</v>
+        <v>-1.2095</v>
       </c>
       <c r="J77" t="n">
         <v>-1.5973</v>
@@ -34740,7 +34740,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2707</v>
+        <v>-1.2706</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5321</v>
@@ -34944,7 +34944,7 @@
         <v>-0.577</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3226</v>
+        <v>-1.3225</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2788</v>
@@ -34978,7 +34978,7 @@
         <v>-0.577</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3449</v>
+        <v>-1.3448</v>
       </c>
       <c r="J86" t="n">
         <v>-1.123</v>
@@ -35046,7 +35046,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2133</v>
+        <v>-1.2132</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0564</v>
@@ -35170,7 +35170,7 @@
         <v>0.1334</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.6224</v>
+        <v>-0.6223</v>
       </c>
       <c r="F92" t="n">
         <v>0.1334</v>
@@ -35229,7 +35229,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4024</v>
+        <v>-0.4023</v>
       </c>
       <c r="C94" t="n">
         <v>-0.3182</v>
@@ -35250,7 +35250,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3034</v>
+        <v>-1.3033</v>
       </c>
       <c r="J94" t="n">
         <v>-0.782</v>
@@ -35340,7 +35340,7 @@
         <v>0.589</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.4427</v>
+        <v>-0.4426</v>
       </c>
       <c r="F97" t="n">
         <v>0.589</v>
@@ -35454,7 +35454,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9235</v>
+        <v>-0.9234</v>
       </c>
       <c r="J100" t="n">
         <v>-0.5014</v>
@@ -36100,7 +36100,7 @@
         <v>0.2519</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3325</v>
+        <v>-0.3324</v>
       </c>
       <c r="J119" t="n">
         <v>-0.07729999999999999</v>
@@ -36848,7 +36848,7 @@
         <v>0.7755</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2502</v>
+        <v>-0.2501</v>
       </c>
       <c r="J141" t="n">
         <v>0.1319</v>
@@ -37222,7 +37222,7 @@
         <v>0.8091</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0304</v>
+        <v>0.0303</v>
       </c>
       <c r="J152" t="n">
         <v>0.7060999999999999</v>
@@ -37358,7 +37358,7 @@
         <v>0.8138</v>
       </c>
       <c r="I156" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="J156" t="n">
         <v>0.7721</v>
@@ -37380,7 +37380,7 @@
         <v>0.7796</v>
       </c>
       <c r="E157" t="n">
-        <v>0.6093</v>
+        <v>0.6092</v>
       </c>
       <c r="F157" t="n">
         <v>0.7796</v>
@@ -37448,7 +37448,7 @@
         <v>0.8692</v>
       </c>
       <c r="E159" t="n">
-        <v>0.5969</v>
+        <v>0.5968</v>
       </c>
       <c r="F159" t="n">
         <v>0.8692</v>
@@ -37562,7 +37562,7 @@
         <v>0.8306</v>
       </c>
       <c r="I162" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="J162" t="n">
         <v>1.1068</v>
@@ -37698,7 +37698,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1293</v>
+        <v>0.1292</v>
       </c>
       <c r="J166" t="n">
         <v>1.2724</v>
@@ -37800,7 +37800,7 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0336</v>
+        <v>0.0335</v>
       </c>
       <c r="J169" t="n">
         <v>1.4195</v>
@@ -38174,7 +38174,7 @@
         <v>0.451</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1652</v>
+        <v>-0.1653</v>
       </c>
       <c r="J180" t="n">
         <v>1.9108</v>
@@ -38514,7 +38514,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1346</v>
+        <v>-0.1347</v>
       </c>
       <c r="J190" t="n">
         <v>1.5321</v>
@@ -38548,7 +38548,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0948</v>
       </c>
       <c r="J191" t="n">
         <v>1.3067</v>
@@ -38752,7 +38752,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2264</v>
+        <v>0.2263</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1028</v>
@@ -38820,7 +38820,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I199" t="n">
-        <v>0.28</v>
+        <v>0.2799</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6688</v>
@@ -38854,7 +38854,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2865</v>
+        <v>0.2864</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6202</v>
@@ -38922,7 +38922,7 @@
         <v>0.091</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3847</v>
+        <v>0.3846</v>
       </c>
       <c r="J202" t="n">
         <v>-0.416</v>
@@ -39037,7 +39037,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3384</v>
+        <v>0.3383</v>
       </c>
       <c r="C206" t="n">
         <v>-0.5203</v>
@@ -39046,7 +39046,7 @@
         <v>0.5263</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2914</v>
+        <v>0.2913</v>
       </c>
       <c r="F206" t="n">
         <v>0.5263</v>
@@ -39194,7 +39194,7 @@
         <v>0.3986</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6611</v>
+        <v>0.661</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1676</v>
@@ -39228,7 +39228,7 @@
         <v>0.5324</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7559</v>
+        <v>0.7558</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1123</v>
@@ -39284,7 +39284,7 @@
         <v>1.5657</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5286</v>
+        <v>0.5285</v>
       </c>
       <c r="F213" t="n">
         <v>1.5657</v>
@@ -39466,7 +39466,7 @@
         <v>0.6974</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7288</v>
+        <v>0.7287</v>
       </c>
       <c r="J218" t="n">
         <v>0.1381</v>
@@ -39534,7 +39534,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8022</v>
+        <v>0.8021</v>
       </c>
       <c r="J220" t="n">
         <v>0.2685</v>
@@ -39547,7 +39547,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.9323</v>
+        <v>0.9322</v>
       </c>
       <c r="C221" t="n">
         <v>-1.2861</v>
@@ -39568,7 +39568,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8216</v>
+        <v>0.8215</v>
       </c>
       <c r="J221" t="n">
         <v>0.3099</v>
@@ -39590,7 +39590,7 @@
         <v>1.724</v>
       </c>
       <c r="E222" t="n">
-        <v>0.7286</v>
+        <v>0.7285</v>
       </c>
       <c r="F222" t="n">
         <v>1.724</v>
@@ -39602,7 +39602,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9206</v>
+        <v>0.9205</v>
       </c>
       <c r="J222" t="n">
         <v>0.249</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2207</v>
+        <v>1.2206</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -39760,7 +39760,7 @@
         <v>1.5257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8501</v>
+        <v>0.85</v>
       </c>
       <c r="F227" t="n">
         <v>1.5257</v>
@@ -39772,7 +39772,7 @@
         <v>0.9485</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2507</v>
+        <v>1.2506</v>
       </c>
       <c r="J227" t="n">
         <v>0.355</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3222</v>
+        <v>1.3221</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39828,7 +39828,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8798</v>
+        <v>0.8797</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5588</v>
+        <v>1.5587</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6213</v>
+        <v>1.6212</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7497</v>
+        <v>1.7496</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7851</v>
+        <v>1.785</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40125,7 +40125,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9775</v>
+        <v>0.9774</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5457</v>
+        <v>1.5456</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7092</v>
+        <v>1.7091</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7853</v>
+        <v>1.7852</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8047</v>
+        <v>1.8046</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40270,7 +40270,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9351</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8775</v>
+        <v>1.8774</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8112</v>
+        <v>1.8111</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7656</v>
+        <v>1.7655</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6405</v>
+        <v>1.6404</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7363</v>
+        <v>1.7362</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40440,7 +40440,7 @@
         <v>1.4541</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8504</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="F247" t="n">
         <v>1.4541</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8814</v>
+        <v>1.8813</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9483</v>
+        <v>1.9482</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40542,7 +40542,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8707</v>
+        <v>0.8706</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0143</v>
+        <v>2.0142</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1889</v>
+        <v>2.1888</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3156</v>
+        <v>2.3155</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40644,7 +40644,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9268</v>
+        <v>0.9267</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3406</v>
+        <v>2.3405</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4469</v>
+        <v>2.4468</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5241</v>
+        <v>2.524</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40746,7 +40746,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.8992</v>
+        <v>0.8991</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5473</v>
+        <v>2.5472</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40771,7 +40771,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.747</v>
+        <v>0.7469</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6739</v>
+        <v>2.6738</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8241</v>
+        <v>2.824</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0153</v>
+        <v>3.0152</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9467</v>
+        <v>0.9466</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9467</v>
+        <v>0.9466</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0047</v>
+        <v>3.0045</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9396</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9396</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9742</v>
+        <v>2.9767</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-0.513</v>
+        <v>-0.512</v>
       </c>
     </row>
     <row r="9">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>0.631</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="157">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="197">
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>1.019</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="241">
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>0.987</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="244">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.299</v>
+        <v>1.31</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.566</v>
+        <v>1.575</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.077</v>
+        <v>2.08</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.814</v>
+        <v>2.812</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.964</v>
+        <v>3.956</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.68</v>
+        <v>-0.669</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.124</v>
+        <v>-0.117</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.66</v>
+        <v>-0.67</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.016</v>
+        <v>1.014</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>65060.568</v>
+        <v>65378.843</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.2993</v>
+        <v>1.3104</v>
       </c>
       <c r="D261" t="n">
-        <v>1.566</v>
+        <v>1.575</v>
       </c>
       <c r="E261" t="n">
-        <v>2.077</v>
+        <v>2.0798</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8145</v>
+        <v>2.8124</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9643</v>
+        <v>3.9564</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6801</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.1242</v>
+        <v>-0.1172</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0157</v>
+        <v>1.0136</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>65060.568</v>
+        <v>65378.8433</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32292,7 +32292,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4887</v>
+        <v>-0.4886</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5127</v>
@@ -32373,7 +32373,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.4898</v>
+        <v>-0.4897</v>
       </c>
       <c r="C10" t="n">
         <v>-0.2832</v>
@@ -32688,7 +32688,7 @@
         <v>0.0366</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5638</v>
+        <v>-0.5637</v>
       </c>
       <c r="F19" t="n">
         <v>0.0366</v>
@@ -32802,7 +32802,7 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0917</v>
       </c>
       <c r="J22" t="n">
         <v>-0.7498</v>
@@ -32836,7 +32836,7 @@
         <v>0.09569999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0475</v>
+        <v>-0.0474</v>
       </c>
       <c r="J23" t="n">
         <v>-0.7179</v>
@@ -33006,7 +33006,7 @@
         <v>0.1358</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0159</v>
+        <v>0.016</v>
       </c>
       <c r="J28" t="n">
         <v>-0.4254</v>
@@ -33244,7 +33244,7 @@
         <v>-0.225</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0946</v>
       </c>
       <c r="J35" t="n">
         <v>0.0213</v>
@@ -33359,7 +33359,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.411</v>
+        <v>-0.4109</v>
       </c>
       <c r="C39" t="n">
         <v>-0.2966</v>
@@ -33380,7 +33380,7 @@
         <v>-0.6075</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4206</v>
+        <v>-0.4205</v>
       </c>
       <c r="J39" t="n">
         <v>0.2385</v>
@@ -33402,7 +33402,7 @@
         <v>0.6107</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.7689</v>
+        <v>-0.7688</v>
       </c>
       <c r="F40" t="n">
         <v>0.6107</v>
@@ -33414,7 +33414,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5619</v>
       </c>
       <c r="J40" t="n">
         <v>0.3612</v>
@@ -33461,7 +33461,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.4719</v>
+        <v>-0.4718</v>
       </c>
       <c r="C42" t="n">
         <v>-0.2345</v>
@@ -33482,7 +33482,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5319</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>0.4861</v>
@@ -33516,7 +33516,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.5236</v>
       </c>
       <c r="J43" t="n">
         <v>0.5435</v>
@@ -33550,7 +33550,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5633</v>
+        <v>-0.5632</v>
       </c>
       <c r="J44" t="n">
         <v>0.5824</v>
@@ -33606,7 +33606,7 @@
         <v>0.9775</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.8562</v>
+        <v>-0.8561</v>
       </c>
       <c r="F46" t="n">
         <v>0.9775</v>
@@ -33618,7 +33618,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6504</v>
+        <v>-0.6503</v>
       </c>
       <c r="J46" t="n">
         <v>0.7897999999999999</v>
@@ -33652,7 +33652,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8519</v>
+        <v>-0.8518</v>
       </c>
       <c r="J47" t="n">
         <v>0.741</v>
@@ -33665,7 +33665,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6364</v>
+        <v>-0.6363</v>
       </c>
       <c r="C48" t="n">
         <v>-0.2059</v>
@@ -33674,7 +33674,7 @@
         <v>0.4548</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.9092</v>
+        <v>-0.9091</v>
       </c>
       <c r="F48" t="n">
         <v>0.4548</v>
@@ -33686,7 +33686,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-0.9329</v>
       </c>
       <c r="J48" t="n">
         <v>0.7829</v>
@@ -33708,7 +33708,7 @@
         <v>-0.08690000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.9966</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="F49" t="n">
         <v>-0.08690000000000001</v>
@@ -33720,7 +33720,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.053</v>
+        <v>-1.0529</v>
       </c>
       <c r="J49" t="n">
         <v>0.983</v>
@@ -33788,7 +33788,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1112</v>
+        <v>-1.1111</v>
       </c>
       <c r="J51" t="n">
         <v>0.6076</v>
@@ -33822,7 +33822,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0192</v>
+        <v>-1.0191</v>
       </c>
       <c r="J52" t="n">
         <v>0.4738</v>
@@ -33856,7 +33856,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9927</v>
+        <v>-0.9926</v>
       </c>
       <c r="J53" t="n">
         <v>0.1904</v>
@@ -33890,7 +33890,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0186</v>
+        <v>-1.0185</v>
       </c>
       <c r="J54" t="n">
         <v>0.1077</v>
@@ -33924,7 +33924,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9932</v>
+        <v>-0.9931</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0219</v>
@@ -33946,7 +33946,7 @@
         <v>-0.8145</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.3546</v>
+        <v>-1.3545</v>
       </c>
       <c r="F56" t="n">
         <v>-0.8145</v>
@@ -33958,7 +33958,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0489</v>
+        <v>-1.0488</v>
       </c>
       <c r="J56" t="n">
         <v>-0.245</v>
@@ -33992,7 +33992,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.011</v>
+        <v>-1.0109</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4398</v>
@@ -34005,7 +34005,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.2466</v>
+        <v>-1.2465</v>
       </c>
       <c r="C58" t="n">
         <v>0.9933</v>
@@ -34026,7 +34026,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.089</v>
+        <v>-1.0889</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5775</v>
@@ -34128,7 +34128,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0998</v>
+        <v>-1.0997</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1668</v>
@@ -34162,7 +34162,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0643</v>
+        <v>-1.0642</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3364</v>
@@ -34298,7 +34298,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0731</v>
+        <v>-1.073</v>
       </c>
       <c r="J66" t="n">
         <v>-1.966</v>
@@ -34332,7 +34332,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0944</v>
+        <v>-1.0943</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1347</v>
@@ -34366,7 +34366,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1613</v>
+        <v>-1.1612</v>
       </c>
       <c r="J68" t="n">
         <v>-2.108</v>
@@ -34434,7 +34434,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2136</v>
+        <v>-1.2135</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9639</v>
@@ -34456,7 +34456,7 @@
         <v>-0.1096</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.246</v>
+        <v>-1.2459</v>
       </c>
       <c r="F71" t="n">
         <v>-0.1096</v>
@@ -34468,7 +34468,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2468</v>
+        <v>-1.2467</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9252</v>
@@ -34490,7 +34490,7 @@
         <v>-0.1495</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2337</v>
+        <v>-1.2336</v>
       </c>
       <c r="F72" t="n">
         <v>-0.1495</v>
@@ -34502,7 +34502,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2339</v>
+        <v>-1.2338</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8944</v>
@@ -34570,7 +34570,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2217</v>
+        <v>-1.2216</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8329</v>
@@ -34604,7 +34604,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2119</v>
+        <v>-1.2118</v>
       </c>
       <c r="J75" t="n">
         <v>-1.811</v>
@@ -34660,7 +34660,7 @@
         <v>0.0533</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.948</v>
       </c>
       <c r="F77" t="n">
         <v>0.0533</v>
@@ -34706,7 +34706,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2486</v>
+        <v>-1.2485</v>
       </c>
       <c r="J78" t="n">
         <v>-1.63</v>
@@ -34774,7 +34774,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2715</v>
+        <v>-1.2714</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5145</v>
@@ -34808,7 +34808,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3181</v>
+        <v>-1.318</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4777</v>
@@ -34821,7 +34821,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.6254</v>
+        <v>-0.6253</v>
       </c>
       <c r="C82" t="n">
         <v>0.2131</v>
@@ -34842,7 +34842,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.334</v>
+        <v>-1.3339</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3458</v>
@@ -34876,7 +34876,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3308</v>
+        <v>-1.3307</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3601</v>
@@ -34910,7 +34910,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3176</v>
+        <v>-1.3175</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3222</v>
@@ -35012,7 +35012,7 @@
         <v>-0.577</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2937</v>
+        <v>-1.2936</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1315</v>
@@ -35034,7 +35034,7 @@
         <v>0.332</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7185</v>
+        <v>-0.7184</v>
       </c>
       <c r="F88" t="n">
         <v>0.332</v>
@@ -35080,7 +35080,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2365</v>
+        <v>-1.2364</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0901</v>
@@ -35114,7 +35114,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2898</v>
+        <v>-1.2897</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9147999999999999</v>
@@ -35148,7 +35148,7 @@
         <v>-0.389</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2919</v>
+        <v>-1.2918</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9429999999999999</v>
@@ -35182,7 +35182,7 @@
         <v>-0.389</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2958</v>
+        <v>-1.2957</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8282</v>
@@ -35216,7 +35216,7 @@
         <v>-0.389</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2937</v>
+        <v>-1.2936</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8172</v>
@@ -35284,7 +35284,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2904</v>
+        <v>-1.2903</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7879</v>
@@ -35318,7 +35318,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2592</v>
+        <v>-1.2591</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5867</v>
@@ -35352,7 +35352,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1954</v>
+        <v>-1.1953</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5657</v>
@@ -35386,7 +35386,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0587</v>
+        <v>-1.0586</v>
       </c>
       <c r="J98" t="n">
         <v>-0.618</v>
@@ -35420,7 +35420,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.972</v>
+        <v>-0.9719</v>
       </c>
       <c r="J99" t="n">
         <v>-0.505</v>
@@ -35476,7 +35476,7 @@
         <v>0.1072</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.292</v>
+        <v>-0.2919</v>
       </c>
       <c r="F101" t="n">
         <v>0.1072</v>
@@ -35488,7 +35488,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8378</v>
+        <v>-0.8377</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4148</v>
@@ -35522,7 +35522,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7407</v>
+        <v>-0.7406</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4062</v>
@@ -35556,7 +35556,7 @@
         <v>-0.1008</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8168</v>
+        <v>-0.8167</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3561</v>
@@ -35624,7 +35624,7 @@
         <v>-0.1008</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7662</v>
+        <v>-0.7661</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2459</v>
@@ -35646,7 +35646,7 @@
         <v>0.5485</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.1949</v>
+        <v>-0.1948</v>
       </c>
       <c r="F106" t="n">
         <v>0.5485</v>
@@ -35794,7 +35794,7 @@
         <v>0.143</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5446</v>
+        <v>-0.5445</v>
       </c>
       <c r="J110" t="n">
         <v>-0.3027</v>
@@ -35828,7 +35828,7 @@
         <v>0.143</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5679</v>
+        <v>-0.5678</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2386</v>
@@ -35884,7 +35884,7 @@
         <v>1.6983</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.0417</v>
+        <v>-0.0416</v>
       </c>
       <c r="F113" t="n">
         <v>1.6983</v>
@@ -35930,7 +35930,7 @@
         <v>0.1698</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.525</v>
+        <v>-0.5249</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2192</v>
@@ -35986,7 +35986,7 @@
         <v>1.7555</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0188</v>
+        <v>0.0189</v>
       </c>
       <c r="F116" t="n">
         <v>1.7555</v>
@@ -36045,7 +36045,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.3723</v>
+        <v>0.3724</v>
       </c>
       <c r="C118" t="n">
         <v>-0.5901999999999999</v>
@@ -36317,7 +36317,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.3192</v>
+        <v>0.3191</v>
       </c>
       <c r="C126" t="n">
         <v>-0.2228</v>
@@ -36338,7 +36338,7 @@
         <v>0.4856</v>
       </c>
       <c r="I126" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="J126" t="n">
         <v>0.0212</v>
@@ -36372,7 +36372,7 @@
         <v>0.4715</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1382</v>
+        <v>0.1381</v>
       </c>
       <c r="J127" t="n">
         <v>-0.021</v>
@@ -36394,7 +36394,7 @@
         <v>0.295</v>
       </c>
       <c r="E128" t="n">
-        <v>0.311</v>
+        <v>0.3109</v>
       </c>
       <c r="F128" t="n">
         <v>0.295</v>
@@ -36644,7 +36644,7 @@
         <v>0.6268</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0596</v>
+        <v>-0.0595</v>
       </c>
       <c r="J135" t="n">
         <v>-0.0066</v>
@@ -36882,7 +36882,7 @@
         <v>0.7796</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2411</v>
+        <v>-0.241</v>
       </c>
       <c r="J142" t="n">
         <v>0.1737</v>
@@ -37244,7 +37244,7 @@
         <v>0.7341</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5506</v>
+        <v>0.5505</v>
       </c>
       <c r="F153" t="n">
         <v>0.7341</v>
@@ -37290,7 +37290,7 @@
         <v>0.8138</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="J154" t="n">
         <v>0.7311</v>
@@ -37482,7 +37482,7 @@
         <v>0.7828000000000001</v>
       </c>
       <c r="E160" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6254</v>
       </c>
       <c r="F160" t="n">
         <v>0.7828000000000001</v>
@@ -37528,7 +37528,7 @@
         <v>0.8306</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0159</v>
+        <v>0.0158</v>
       </c>
       <c r="J161" t="n">
         <v>1.03</v>
@@ -37732,7 +37732,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J167" t="n">
         <v>1.3895</v>
@@ -37822,7 +37822,7 @@
         <v>0.7912</v>
       </c>
       <c r="E170" t="n">
-        <v>0.7474</v>
+        <v>0.7473</v>
       </c>
       <c r="F170" t="n">
         <v>0.7912</v>
@@ -38196,7 +38196,7 @@
         <v>0.5621</v>
       </c>
       <c r="E181" t="n">
-        <v>0.5966</v>
+        <v>0.5965</v>
       </c>
       <c r="F181" t="n">
         <v>0.5621</v>
@@ -38242,7 +38242,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1851</v>
+        <v>-0.1852</v>
       </c>
       <c r="J182" t="n">
         <v>2.0493</v>
@@ -38391,7 +38391,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.4234</v>
+        <v>0.4233</v>
       </c>
       <c r="C187" t="n">
         <v>0.5393</v>
@@ -38446,7 +38446,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1784</v>
+        <v>-0.1785</v>
       </c>
       <c r="J188" t="n">
         <v>2.013</v>
@@ -38480,7 +38480,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1427</v>
+        <v>-0.1428</v>
       </c>
       <c r="J189" t="n">
         <v>1.7738</v>
@@ -38582,7 +38582,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.05</v>
+        <v>-0.0501</v>
       </c>
       <c r="J192" t="n">
         <v>1.0402</v>
@@ -38604,7 +38604,7 @@
         <v>0.1272</v>
       </c>
       <c r="E193" t="n">
-        <v>0.231</v>
+        <v>0.2309</v>
       </c>
       <c r="F193" t="n">
         <v>0.1272</v>
@@ -38616,7 +38616,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0135</v>
+        <v>-0.0136</v>
       </c>
       <c r="J193" t="n">
         <v>0.855</v>
@@ -38650,7 +38650,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0498</v>
+        <v>0.0497</v>
       </c>
       <c r="J194" t="n">
         <v>0.5541</v>
@@ -38672,7 +38672,7 @@
         <v>0.1957</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1434</v>
+        <v>0.1433</v>
       </c>
       <c r="F195" t="n">
         <v>0.1957</v>
@@ -38684,7 +38684,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1117</v>
+        <v>0.1116</v>
       </c>
       <c r="J195" t="n">
         <v>0.3553</v>
@@ -38718,7 +38718,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1828</v>
+        <v>0.1827</v>
       </c>
       <c r="J196" t="n">
         <v>0.0803</v>
@@ -38731,7 +38731,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.1263</v>
+        <v>0.1262</v>
       </c>
       <c r="C197" t="n">
         <v>-0.0422</v>
@@ -38786,7 +38786,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2335</v>
+        <v>0.2334</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4271</v>
@@ -38808,7 +38808,7 @@
         <v>0.2053</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0328</v>
+        <v>0.0327</v>
       </c>
       <c r="F199" t="n">
         <v>0.2053</v>
@@ -38820,7 +38820,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2799</v>
+        <v>0.2798</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6688</v>
@@ -38842,7 +38842,7 @@
         <v>0.3398</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0511</v>
+        <v>0.051</v>
       </c>
       <c r="F200" t="n">
         <v>0.3398</v>
@@ -38854,7 +38854,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2864</v>
+        <v>0.2863</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6202</v>
@@ -38888,7 +38888,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2999</v>
+        <v>0.2998</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6014</v>
@@ -38922,7 +38922,7 @@
         <v>0.091</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3846</v>
+        <v>0.3845</v>
       </c>
       <c r="J202" t="n">
         <v>-0.416</v>
@@ -38944,7 +38944,7 @@
         <v>0.5004999999999999</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1644</v>
+        <v>0.1643</v>
       </c>
       <c r="F203" t="n">
         <v>0.5004999999999999</v>
@@ -38956,7 +38956,7 @@
         <v>0.091</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3974</v>
+        <v>0.3973</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5065</v>
@@ -38990,7 +38990,7 @@
         <v>0.091</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4313</v>
+        <v>0.4312</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4266</v>
@@ -39024,7 +39024,7 @@
         <v>0.2135</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4369</v>
+        <v>0.4368</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3874</v>
@@ -39058,7 +39058,7 @@
         <v>0.2135</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4278</v>
+        <v>0.4277</v>
       </c>
       <c r="J206" t="n">
         <v>-0.253</v>
@@ -39080,7 +39080,7 @@
         <v>0.6433</v>
       </c>
       <c r="E207" t="n">
-        <v>0.2927</v>
+        <v>0.2926</v>
       </c>
       <c r="F207" t="n">
         <v>0.6433</v>
@@ -39092,7 +39092,7 @@
         <v>0.2135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.443</v>
+        <v>0.4429</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2922</v>
@@ -39126,7 +39126,7 @@
         <v>0.3986</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4731</v>
+        <v>0.473</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2508</v>
@@ -39160,7 +39160,7 @@
         <v>0.3986</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6141</v>
+        <v>0.614</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1699</v>
@@ -39262,7 +39262,7 @@
         <v>0.5324</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7926</v>
+        <v>0.7925</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1272</v>
@@ -39296,7 +39296,7 @@
         <v>0.5324</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8149</v>
       </c>
       <c r="J213" t="n">
         <v>-0.0809</v>
@@ -39330,7 +39330,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9179</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="J214" t="n">
         <v>0.0795</v>
@@ -39343,7 +39343,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.889</v>
+        <v>0.8889</v>
       </c>
       <c r="C215" t="n">
         <v>-0.8632</v>
@@ -39352,7 +39352,7 @@
         <v>1.8946</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6375</v>
       </c>
       <c r="F215" t="n">
         <v>1.8946</v>
@@ -39364,7 +39364,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9876</v>
+        <v>0.9875</v>
       </c>
       <c r="J215" t="n">
         <v>0.0289</v>
@@ -39398,7 +39398,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9278</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0187</v>
@@ -39432,7 +39432,7 @@
         <v>0.6974</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7987</v>
+        <v>0.7986</v>
       </c>
       <c r="J217" t="n">
         <v>0.1675</v>
@@ -39500,7 +39500,7 @@
         <v>0.6974</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8001</v>
+        <v>0.8</v>
       </c>
       <c r="J219" t="n">
         <v>0.2431</v>
@@ -39513,7 +39513,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.9087</v>
+        <v>0.9086</v>
       </c>
       <c r="C220" t="n">
         <v>-1.2201</v>
@@ -39522,7 +39522,7 @@
         <v>1.7394</v>
       </c>
       <c r="E220" t="n">
-        <v>0.701</v>
+        <v>0.7009</v>
       </c>
       <c r="F220" t="n">
         <v>1.7394</v>
@@ -39568,7 +39568,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8215</v>
+        <v>0.8214</v>
       </c>
       <c r="J221" t="n">
         <v>0.3099</v>
@@ -39602,7 +39602,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9205</v>
+        <v>0.9204</v>
       </c>
       <c r="J222" t="n">
         <v>0.249</v>
@@ -39624,7 +39624,7 @@
         <v>1.7742</v>
       </c>
       <c r="E223" t="n">
-        <v>0.786</v>
+        <v>0.7859</v>
       </c>
       <c r="F223" t="n">
         <v>1.7742</v>
@@ -39636,7 +39636,7 @@
         <v>0.8441</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0454</v>
+        <v>1.0452</v>
       </c>
       <c r="J223" t="n">
         <v>0.3667</v>
@@ -39670,7 +39670,7 @@
         <v>0.8441</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0638</v>
+        <v>1.0637</v>
       </c>
       <c r="J224" t="n">
         <v>0.3764</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1519</v>
+        <v>1.1518</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2206</v>
+        <v>1.2205</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -39772,7 +39772,7 @@
         <v>0.9485</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2506</v>
+        <v>1.2505</v>
       </c>
       <c r="J227" t="n">
         <v>0.355</v>
@@ -39785,7 +39785,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9651</v>
+        <v>0.965</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3221</v>
+        <v>1.322</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2506</v>
+        <v>1.2504</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39862,7 +39862,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9349</v>
+        <v>0.9348</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39874,7 +39874,7 @@
         <v>1.0464</v>
       </c>
       <c r="I230" t="n">
-        <v>1.353</v>
+        <v>1.3528</v>
       </c>
       <c r="J230" t="n">
         <v>0.4839</v>
@@ -39896,7 +39896,7 @@
         <v>1.4899</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9492</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F231" t="n">
         <v>1.4899</v>
@@ -39908,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.494</v>
+        <v>1.4938</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39930,7 +39930,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0031</v>
+        <v>1.003</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5587</v>
+        <v>1.5586</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -39964,7 +39964,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0022</v>
+        <v>1.0021</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6212</v>
+        <v>1.621</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6675</v>
+        <v>1.6673</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7496</v>
+        <v>1.7494</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40066,7 +40066,7 @@
         <v>1.3708</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0133</v>
+        <v>1.0132</v>
       </c>
       <c r="F236" t="n">
         <v>1.3708</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.785</v>
+        <v>1.7849</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5597</v>
+        <v>1.5595</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5456</v>
+        <v>1.5455</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40159,7 +40159,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.0001</v>
+        <v>1</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7091</v>
+        <v>1.7089</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40202,7 +40202,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9601</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7852</v>
+        <v>1.785</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8046</v>
+        <v>1.8044</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.035</v>
+        <v>1.0349</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8774</v>
+        <v>1.8773</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40304,7 +40304,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9067</v>
+        <v>0.9066</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8111</v>
+        <v>1.8109</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7655</v>
+        <v>1.7654</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6404</v>
+        <v>1.6403</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7362</v>
+        <v>1.7361</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7658</v>
+        <v>1.7656</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40474,7 +40474,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8522</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8813</v>
+        <v>1.8812</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40499,7 +40499,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9282</v>
+        <v>0.9281</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9482</v>
+        <v>1.948</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0142</v>
+        <v>2.014</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40567,7 +40567,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9811</v>
+        <v>0.981</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40576,7 +40576,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9174</v>
+        <v>0.9173</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1888</v>
+        <v>2.1886</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40601,7 +40601,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9872</v>
+        <v>0.9871</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40610,7 +40610,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9315</v>
+        <v>0.9314</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3155</v>
+        <v>2.3152</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40635,7 +40635,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7482</v>
+        <v>0.7481</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3405</v>
+        <v>2.3403</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40678,7 +40678,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9353</v>
+        <v>0.9352</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4468</v>
+        <v>2.4466</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8387</v>
+        <v>0.8386</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40712,7 +40712,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9377</v>
+        <v>0.9376</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.524</v>
+        <v>2.5237</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40737,7 +40737,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8173</v>
+        <v>0.8172</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5472</v>
+        <v>2.5469</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40780,7 +40780,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8532</v>
+        <v>0.8531</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6738</v>
+        <v>2.6735</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7884</v>
+        <v>0.7883</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40814,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9122</v>
+        <v>0.9121</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.824</v>
+        <v>2.8236</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8243</v>
+        <v>0.8242</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40848,7 +40848,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9493</v>
+        <v>0.9492</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0152</v>
+        <v>3.0148</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9466</v>
+        <v>0.9465</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9466</v>
+        <v>0.9465</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0045</v>
+        <v>3.0042</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9396</v>
+        <v>0.9411</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9396</v>
+        <v>0.9411</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9767</v>
+        <v>2.9824</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>-1.187</v>
+        <v>-1.186</v>
       </c>
     </row>
     <row r="67">
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="168">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.947</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="261">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.31</v>
+        <v>1.319</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.575</v>
+        <v>1.582</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.08</v>
+        <v>2.083</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.812</v>
+        <v>2.813</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.956</v>
+        <v>3.957</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.669</v>
+        <v>-0.66</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.117</v>
+        <v>-0.111</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.67</v>
+        <v>-0.68</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>65378.843</v>
+        <v>65685.303</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3104</v>
+        <v>1.3192</v>
       </c>
       <c r="D261" t="n">
-        <v>1.575</v>
+        <v>1.5822</v>
       </c>
       <c r="E261" t="n">
-        <v>2.0798</v>
+        <v>2.0833</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8124</v>
+        <v>2.8128</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9564</v>
+        <v>3.9565</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.6601</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.1172</v>
+        <v>-0.1113</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0136</v>
+        <v>1.014</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>65378.8433</v>
+        <v>65685.3029</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32128,7 +32128,7 @@
         <v>-0.3431</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6432</v>
+        <v>-0.6431</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7186</v>
@@ -32156,7 +32156,7 @@
         <v>-0.3209</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5901</v>
+        <v>-0.59</v>
       </c>
       <c r="J3" t="n">
         <v>-1.6403</v>
@@ -32190,7 +32190,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5669</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6492</v>
@@ -32203,7 +32203,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.5377</v>
       </c>
       <c r="C5" t="n">
         <v>-0.0692</v>
@@ -32224,7 +32224,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5456</v>
+        <v>-0.5455</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5156</v>
@@ -32246,7 +32246,7 @@
         <v>0.2701</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7048</v>
+        <v>-0.7047</v>
       </c>
       <c r="F6" t="n">
         <v>0.2701</v>
@@ -32258,7 +32258,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.535</v>
+        <v>-0.5349</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4222</v>
@@ -32280,7 +32280,7 @@
         <v>0.1468</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7174</v>
+        <v>-0.7173</v>
       </c>
       <c r="F7" t="n">
         <v>0.1468</v>
@@ -32326,7 +32326,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.409</v>
+        <v>-0.4089</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3624</v>
@@ -32360,7 +32360,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4123</v>
+        <v>-0.4122</v>
       </c>
       <c r="J9" t="n">
         <v>-1.394</v>
@@ -32382,7 +32382,7 @@
         <v>0.0931</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6355</v>
+        <v>-0.6354</v>
       </c>
       <c r="F10" t="n">
         <v>0.0931</v>
@@ -32428,7 +32428,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3027</v>
+        <v>-0.3026</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2859</v>
@@ -32496,7 +32496,7 @@
         <v>-0.1828</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.182</v>
+        <v>-0.1819</v>
       </c>
       <c r="J13" t="n">
         <v>-1.201</v>
@@ -32632,7 +32632,7 @@
         <v>-0.1031</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1317</v>
+        <v>-0.1316</v>
       </c>
       <c r="J17" t="n">
         <v>-1.0205</v>
@@ -32790,7 +32790,7 @@
         <v>0.1099</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4868</v>
+        <v>-0.4867</v>
       </c>
       <c r="F22" t="n">
         <v>0.1099</v>
@@ -33448,7 +33448,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5586</v>
+        <v>-0.5585</v>
       </c>
       <c r="J41" t="n">
         <v>0.3765</v>
@@ -33584,7 +33584,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5588</v>
+        <v>-0.5587</v>
       </c>
       <c r="J45" t="n">
         <v>0.7418</v>
@@ -33652,7 +33652,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8518</v>
+        <v>-0.8517</v>
       </c>
       <c r="J47" t="n">
         <v>0.741</v>
@@ -33686,7 +33686,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9329</v>
+        <v>-0.9328</v>
       </c>
       <c r="J48" t="n">
         <v>0.7829</v>
@@ -33742,7 +33742,7 @@
         <v>0.132</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.0498</v>
+        <v>-1.0497</v>
       </c>
       <c r="F50" t="n">
         <v>0.132</v>
@@ -33754,7 +33754,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0994</v>
+        <v>-1.0993</v>
       </c>
       <c r="J50" t="n">
         <v>0.7647</v>
@@ -33822,7 +33822,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0191</v>
+        <v>-1.019</v>
       </c>
       <c r="J52" t="n">
         <v>0.4738</v>
@@ -33869,7 +33869,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.0581</v>
+        <v>-1.058</v>
       </c>
       <c r="C54" t="n">
         <v>0.8923</v>
@@ -33958,7 +33958,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0488</v>
+        <v>-1.0487</v>
       </c>
       <c r="J56" t="n">
         <v>-0.245</v>
@@ -34026,7 +34026,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0889</v>
+        <v>-1.0888</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5775</v>
@@ -34060,7 +34060,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1039</v>
+        <v>-1.1038</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8167</v>
@@ -34082,7 +34082,7 @@
         <v>-0.5407999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.4263</v>
+        <v>-1.4262</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5407999999999999</v>
@@ -34094,7 +34094,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.119</v>
+        <v>-1.1189</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9842</v>
@@ -34162,7 +34162,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3364</v>
@@ -34175,7 +34175,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.1927</v>
+        <v>-1.1926</v>
       </c>
       <c r="C63" t="n">
         <v>0.7577</v>
@@ -34184,7 +34184,7 @@
         <v>-0.2126</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.4377</v>
+        <v>-1.4376</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2126</v>
@@ -34196,7 +34196,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0936</v>
+        <v>-1.0935</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4597</v>
@@ -34209,7 +34209,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1629</v>
+        <v>-1.1628</v>
       </c>
       <c r="C64" t="n">
         <v>0.6857</v>
@@ -34230,7 +34230,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0726</v>
+        <v>-1.0725</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6947</v>
@@ -34264,7 +34264,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0316</v>
+        <v>-1.0315</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8174</v>
@@ -34298,7 +34298,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.073</v>
+        <v>-1.0729</v>
       </c>
       <c r="J66" t="n">
         <v>-1.966</v>
@@ -34311,7 +34311,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1446</v>
+        <v>-1.1445</v>
       </c>
       <c r="C67" t="n">
         <v>0.6892</v>
@@ -34332,7 +34332,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0943</v>
+        <v>-1.0942</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1347</v>
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1682</v>
+        <v>-1.1681</v>
       </c>
       <c r="C68" t="n">
         <v>0.6511</v>
@@ -34366,7 +34366,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1612</v>
+        <v>-1.1611</v>
       </c>
       <c r="J68" t="n">
         <v>-2.108</v>
@@ -34379,7 +34379,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1504</v>
+        <v>-1.1503</v>
       </c>
       <c r="C69" t="n">
         <v>0.5633</v>
@@ -34400,7 +34400,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1958</v>
+        <v>-1.1957</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0592</v>
@@ -34434,7 +34434,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2135</v>
+        <v>-1.2134</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9639</v>
@@ -34468,7 +34468,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2467</v>
+        <v>-1.2466</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9252</v>
@@ -34502,7 +34502,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2338</v>
+        <v>-1.2337</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8944</v>
@@ -34536,7 +34536,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1959</v>
+        <v>-1.1958</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8566</v>
@@ -34570,7 +34570,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2216</v>
+        <v>-1.2215</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8329</v>
@@ -34592,7 +34592,7 @@
         <v>-0.1831</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.131</v>
+        <v>-1.1309</v>
       </c>
       <c r="F75" t="n">
         <v>-0.1831</v>
@@ -34626,7 +34626,7 @@
         <v>-0.0857</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0095</v>
+        <v>-1.0094</v>
       </c>
       <c r="F76" t="n">
         <v>-0.0857</v>
@@ -34638,7 +34638,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2422</v>
+        <v>-1.2421</v>
       </c>
       <c r="J76" t="n">
         <v>-1.702</v>
@@ -34672,7 +34672,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2095</v>
+        <v>-1.2094</v>
       </c>
       <c r="J77" t="n">
         <v>-1.5973</v>
@@ -34719,7 +34719,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7214</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="C79" t="n">
         <v>0.1954</v>
@@ -34728,7 +34728,7 @@
         <v>0.1235</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9326</v>
+        <v>-0.9325</v>
       </c>
       <c r="F79" t="n">
         <v>0.1235</v>
@@ -34740,7 +34740,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2706</v>
+        <v>-1.2705</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5321</v>
@@ -34774,7 +34774,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2714</v>
+        <v>-1.2713</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5145</v>
@@ -34842,7 +34842,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3339</v>
+        <v>-1.3338</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3458</v>
@@ -34889,7 +34889,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6524</v>
+        <v>-0.6523</v>
       </c>
       <c r="C84" t="n">
         <v>0.1093</v>
@@ -34910,7 +34910,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3175</v>
+        <v>-1.3174</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3222</v>
@@ -34944,7 +34944,7 @@
         <v>-0.577</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3225</v>
+        <v>-1.3224</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2788</v>
@@ -34978,7 +34978,7 @@
         <v>-0.577</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3448</v>
+        <v>-1.3447</v>
       </c>
       <c r="J86" t="n">
         <v>-1.123</v>
@@ -35012,7 +35012,7 @@
         <v>-0.577</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2936</v>
+        <v>-1.2935</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1315</v>
@@ -35025,7 +35025,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.5084</v>
+        <v>-0.5083</v>
       </c>
       <c r="C88" t="n">
         <v>-0.0463</v>
@@ -35046,7 +35046,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2132</v>
+        <v>-1.2131</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0564</v>
@@ -35102,7 +35102,7 @@
         <v>0.2133</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.6879</v>
+        <v>-0.6878</v>
       </c>
       <c r="F90" t="n">
         <v>0.2133</v>
@@ -35114,7 +35114,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2897</v>
+        <v>-1.2896</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9147999999999999</v>
@@ -35127,7 +35127,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.4848</v>
+        <v>-0.4847</v>
       </c>
       <c r="C91" t="n">
         <v>-0.1676</v>
@@ -35148,7 +35148,7 @@
         <v>-0.389</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2918</v>
+        <v>-1.2917</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9429999999999999</v>
@@ -35182,7 +35182,7 @@
         <v>-0.389</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2957</v>
+        <v>-1.2956</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8282</v>
@@ -35250,7 +35250,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3033</v>
+        <v>-1.3032</v>
       </c>
       <c r="J94" t="n">
         <v>-0.782</v>
@@ -35284,7 +35284,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2903</v>
+        <v>-1.2902</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7879</v>
@@ -35352,7 +35352,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1953</v>
+        <v>-1.1952</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5657</v>
@@ -35365,7 +35365,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.3184</v>
+        <v>-0.3183</v>
       </c>
       <c r="C98" t="n">
         <v>-0.3705</v>
@@ -35374,7 +35374,7 @@
         <v>0.1393</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.4328</v>
+        <v>-0.4327</v>
       </c>
       <c r="F98" t="n">
         <v>0.1393</v>
@@ -35433,7 +35433,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2543</v>
+        <v>-0.2542</v>
       </c>
       <c r="C100" t="n">
         <v>-0.3899</v>
@@ -35544,7 +35544,7 @@
         <v>0.3913</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2375</v>
+        <v>-0.2374</v>
       </c>
       <c r="F103" t="n">
         <v>0.3913</v>
@@ -35726,7 +35726,7 @@
         <v>-0.0433</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6516</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2912</v>
@@ -35748,7 +35748,7 @@
         <v>1.4998</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.0934</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="F109" t="n">
         <v>1.4998</v>
@@ -35760,7 +35760,7 @@
         <v>0.143</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5595</v>
+        <v>-0.5594</v>
       </c>
       <c r="J109" t="n">
         <v>-0.2943</v>
@@ -35841,7 +35841,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.1337</v>
+        <v>0.1338</v>
       </c>
       <c r="C112" t="n">
         <v>-0.6355</v>
@@ -35875,7 +35875,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.3063</v>
+        <v>0.3064</v>
       </c>
       <c r="C113" t="n">
         <v>-0.6818</v>
@@ -35896,7 +35896,7 @@
         <v>0.1698</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5476</v>
+        <v>-0.5475</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2356</v>
@@ -35909,7 +35909,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.3303</v>
+        <v>0.3304</v>
       </c>
       <c r="C114" t="n">
         <v>-0.6998</v>
@@ -35952,7 +35952,7 @@
         <v>1.7491</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.0243</v>
+        <v>-0.0242</v>
       </c>
       <c r="F115" t="n">
         <v>1.7491</v>
@@ -35964,7 +35964,7 @@
         <v>0.1933</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5072</v>
+        <v>-0.5071</v>
       </c>
       <c r="J115" t="n">
         <v>-0.25</v>
@@ -36020,7 +36020,7 @@
         <v>1.6648</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0216</v>
+        <v>0.0217</v>
       </c>
       <c r="F117" t="n">
         <v>1.6648</v>
@@ -36780,7 +36780,7 @@
         <v>0.7755</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1941</v>
+        <v>-0.194</v>
       </c>
       <c r="J139" t="n">
         <v>0.1203</v>
@@ -36814,7 +36814,7 @@
         <v>0.7755</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2039</v>
+        <v>-0.2038</v>
       </c>
       <c r="J140" t="n">
         <v>0.1246</v>
@@ -36963,7 +36963,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5379</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="C145" t="n">
         <v>0.2364</v>
@@ -37278,7 +37278,7 @@
         <v>0.7361</v>
       </c>
       <c r="E154" t="n">
-        <v>0.5798</v>
+        <v>0.5797</v>
       </c>
       <c r="F154" t="n">
         <v>0.7361</v>
@@ -37392,7 +37392,7 @@
         <v>0.7919</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1105</v>
+        <v>0.1104</v>
       </c>
       <c r="J157" t="n">
         <v>0.8101</v>
@@ -37414,7 +37414,7 @@
         <v>0.7731</v>
       </c>
       <c r="E158" t="n">
-        <v>0.6405</v>
+        <v>0.6404</v>
       </c>
       <c r="F158" t="n">
         <v>0.7731</v>
@@ -37426,7 +37426,7 @@
         <v>0.7919</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0898</v>
+        <v>0.0897</v>
       </c>
       <c r="J158" t="n">
         <v>1.005</v>
@@ -37460,7 +37460,7 @@
         <v>0.7919</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0253</v>
+        <v>0.0252</v>
       </c>
       <c r="J159" t="n">
         <v>0.9155</v>
@@ -37494,7 +37494,7 @@
         <v>0.8306</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.018</v>
+        <v>-0.0181</v>
       </c>
       <c r="J160" t="n">
         <v>1.0225</v>
@@ -37507,7 +37507,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.6522</v>
+        <v>0.6521</v>
       </c>
       <c r="C161" t="n">
         <v>0.2556</v>
@@ -37596,7 +37596,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0738</v>
       </c>
       <c r="J163" t="n">
         <v>1.2073</v>
@@ -37630,7 +37630,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0997</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J164" t="n">
         <v>1.2102</v>
@@ -37643,7 +37643,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.7372</v>
+        <v>0.7371</v>
       </c>
       <c r="C165" t="n">
         <v>0.3708</v>
@@ -37664,7 +37664,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0892</v>
+        <v>0.0891</v>
       </c>
       <c r="J165" t="n">
         <v>1.321</v>
@@ -37766,7 +37766,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>0.089</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J168" t="n">
         <v>1.4432</v>
@@ -37856,7 +37856,7 @@
         <v>0.7526</v>
       </c>
       <c r="E171" t="n">
-        <v>0.7339</v>
+        <v>0.7338</v>
       </c>
       <c r="F171" t="n">
         <v>0.7526</v>
@@ -37890,7 +37890,7 @@
         <v>0.7994</v>
       </c>
       <c r="E172" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7897</v>
       </c>
       <c r="F172" t="n">
         <v>0.7994</v>
@@ -37970,7 +37970,7 @@
         <v>0.9549</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="J174" t="n">
         <v>1.6763</v>
@@ -37983,7 +37983,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.7785</v>
+        <v>0.7784</v>
       </c>
       <c r="C175" t="n">
         <v>0.6141</v>
@@ -38140,7 +38140,7 @@
         <v>0.451</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1769</v>
+        <v>-0.177</v>
       </c>
       <c r="J179" t="n">
         <v>1.9407</v>
@@ -38162,7 +38162,7 @@
         <v>0.6763</v>
       </c>
       <c r="E180" t="n">
-        <v>0.6726</v>
+        <v>0.6725</v>
       </c>
       <c r="F180" t="n">
         <v>0.6763</v>
@@ -38187,7 +38187,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.5897</v>
+        <v>0.5896</v>
       </c>
       <c r="C181" t="n">
         <v>0.6037</v>
@@ -38208,7 +38208,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1578</v>
+        <v>-0.1579</v>
       </c>
       <c r="J181" t="n">
         <v>1.9529</v>
@@ -38276,7 +38276,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2003</v>
+        <v>-0.2004</v>
       </c>
       <c r="J183" t="n">
         <v>2.1742</v>
@@ -38548,7 +38548,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0948</v>
+        <v>-0.0949</v>
       </c>
       <c r="J191" t="n">
         <v>1.3067</v>
@@ -38561,7 +38561,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.1812</v>
+        <v>0.1811</v>
       </c>
       <c r="C192" t="n">
         <v>0.288</v>
@@ -38616,7 +38616,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0136</v>
+        <v>-0.0137</v>
       </c>
       <c r="J193" t="n">
         <v>0.855</v>
@@ -38650,7 +38650,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0497</v>
+        <v>0.0496</v>
       </c>
       <c r="J194" t="n">
         <v>0.5541</v>
@@ -38684,7 +38684,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1116</v>
+        <v>0.1115</v>
       </c>
       <c r="J195" t="n">
         <v>0.3553</v>
@@ -38718,7 +38718,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1827</v>
+        <v>0.1826</v>
       </c>
       <c r="J196" t="n">
         <v>0.0803</v>
@@ -38740,7 +38740,7 @@
         <v>0.0738</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1394</v>
+        <v>0.1393</v>
       </c>
       <c r="F197" t="n">
         <v>0.0738</v>
@@ -38752,7 +38752,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2263</v>
+        <v>0.2262</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1028</v>
@@ -38786,7 +38786,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2334</v>
+        <v>0.2333</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4271</v>
@@ -38799,7 +38799,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0673</v>
+        <v>0.0672</v>
       </c>
       <c r="C199" t="n">
         <v>-0.0964</v>
@@ -38820,7 +38820,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2798</v>
+        <v>0.2797</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6688</v>
@@ -38867,7 +38867,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.1395</v>
+        <v>0.1394</v>
       </c>
       <c r="C201" t="n">
         <v>-0.2562</v>
@@ -38910,7 +38910,7 @@
         <v>0.4634</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2043</v>
+        <v>0.2042</v>
       </c>
       <c r="F202" t="n">
         <v>0.4634</v>
@@ -38935,7 +38935,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.2316</v>
+        <v>0.2315</v>
       </c>
       <c r="C203" t="n">
         <v>-0.2987</v>
@@ -38956,7 +38956,7 @@
         <v>0.091</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3973</v>
+        <v>0.3972</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5065</v>
@@ -38969,7 +38969,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.2953</v>
+        <v>0.2952</v>
       </c>
       <c r="C204" t="n">
         <v>-0.3445</v>
@@ -38990,7 +38990,7 @@
         <v>0.091</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4312</v>
+        <v>0.4311</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4266</v>
@@ -39012,7 +39012,7 @@
         <v>1.7557</v>
       </c>
       <c r="E205" t="n">
-        <v>0.261</v>
+        <v>0.2609</v>
       </c>
       <c r="F205" t="n">
         <v>1.7557</v>
@@ -39024,7 +39024,7 @@
         <v>0.2135</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4368</v>
+        <v>0.4367</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3874</v>
@@ -39092,7 +39092,7 @@
         <v>0.2135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4429</v>
+        <v>0.4428</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2922</v>
@@ -39126,7 +39126,7 @@
         <v>0.3986</v>
       </c>
       <c r="I208" t="n">
-        <v>0.473</v>
+        <v>0.4729</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2508</v>
@@ -39160,7 +39160,7 @@
         <v>0.3986</v>
       </c>
       <c r="I209" t="n">
-        <v>0.614</v>
+        <v>0.6139</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1699</v>
@@ -39194,7 +39194,7 @@
         <v>0.3986</v>
       </c>
       <c r="I210" t="n">
-        <v>0.661</v>
+        <v>0.6609</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1676</v>
@@ -39207,7 +39207,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.6745</v>
+        <v>0.6744</v>
       </c>
       <c r="C211" t="n">
         <v>-0.7048</v>
@@ -39228,7 +39228,7 @@
         <v>0.5324</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7558</v>
+        <v>0.7557</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1123</v>
@@ -39262,7 +39262,7 @@
         <v>0.5324</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7925</v>
+        <v>0.7924</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1272</v>
@@ -39275,7 +39275,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.736</v>
+        <v>0.7359</v>
       </c>
       <c r="C213" t="n">
         <v>-0.7202</v>
@@ -39296,7 +39296,7 @@
         <v>0.5324</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8149</v>
+        <v>0.8148</v>
       </c>
       <c r="J213" t="n">
         <v>-0.0809</v>
@@ -39330,7 +39330,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9177</v>
       </c>
       <c r="J214" t="n">
         <v>0.0795</v>
@@ -39386,7 +39386,7 @@
         <v>1.9735</v>
       </c>
       <c r="E216" t="n">
-        <v>0.6024</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="F216" t="n">
         <v>1.9735</v>
@@ -39398,7 +39398,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9278</v>
+        <v>0.9277</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0187</v>
@@ -39420,7 +39420,7 @@
         <v>1.562</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6294</v>
+        <v>0.6293</v>
       </c>
       <c r="F217" t="n">
         <v>1.562</v>
@@ -39466,7 +39466,7 @@
         <v>0.6974</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7287</v>
+        <v>0.7286</v>
       </c>
       <c r="J218" t="n">
         <v>0.1381</v>
@@ -39500,7 +39500,7 @@
         <v>0.6974</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J219" t="n">
         <v>0.2431</v>
@@ -39534,7 +39534,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8021</v>
+        <v>0.802</v>
       </c>
       <c r="J220" t="n">
         <v>0.2685</v>
@@ -39602,7 +39602,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9204</v>
+        <v>0.9203</v>
       </c>
       <c r="J222" t="n">
         <v>0.249</v>
@@ -39636,7 +39636,7 @@
         <v>0.8441</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0452</v>
+        <v>1.0451</v>
       </c>
       <c r="J223" t="n">
         <v>0.3667</v>
@@ -39670,7 +39670,7 @@
         <v>0.8441</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0637</v>
+        <v>1.0635</v>
       </c>
       <c r="J224" t="n">
         <v>0.3764</v>
@@ -39683,7 +39683,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9903</v>
       </c>
       <c r="C225" t="n">
         <v>-1.3984</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1518</v>
+        <v>1.1517</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39726,7 +39726,7 @@
         <v>1.477</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8518</v>
+        <v>0.8517</v>
       </c>
       <c r="F226" t="n">
         <v>1.477</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2205</v>
+        <v>1.2204</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -39751,7 +39751,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.9852</v>
+        <v>0.9851</v>
       </c>
       <c r="C227" t="n">
         <v>-1.4189</v>
@@ -39772,7 +39772,7 @@
         <v>0.9485</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2505</v>
+        <v>1.2504</v>
       </c>
       <c r="J227" t="n">
         <v>0.355</v>
@@ -39794,7 +39794,7 @@
         <v>1.3813</v>
       </c>
       <c r="E228" t="n">
-        <v>0.861</v>
+        <v>0.8609</v>
       </c>
       <c r="F228" t="n">
         <v>1.3813</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.322</v>
+        <v>1.3219</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39819,7 +39819,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.994</v>
+        <v>0.9939</v>
       </c>
       <c r="C229" t="n">
         <v>-1.3839</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2504</v>
+        <v>1.2503</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39874,7 +39874,7 @@
         <v>1.0464</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3528</v>
+        <v>1.3527</v>
       </c>
       <c r="J230" t="n">
         <v>0.4839</v>
@@ -39908,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4938</v>
+        <v>1.4937</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39921,7 +39921,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0791</v>
+        <v>1.079</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5586</v>
+        <v>1.5584</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -39955,7 +39955,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0382</v>
+        <v>1.0381</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.621</v>
+        <v>1.6209</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -39998,7 +39998,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.0019</v>
+        <v>1.0018</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6673</v>
+        <v>1.6671</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40023,7 +40023,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.0881</v>
+        <v>1.088</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -40032,7 +40032,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.026</v>
+        <v>1.0259</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7494</v>
+        <v>1.7493</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40057,7 +40057,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0848</v>
+        <v>1.0847</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7849</v>
+        <v>1.7847</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40091,7 +40091,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0237</v>
+        <v>1.0236</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5595</v>
+        <v>1.5594</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40134,7 +40134,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9182</v>
+        <v>0.9181</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5455</v>
+        <v>1.5453</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40168,7 +40168,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9637</v>
+        <v>0.9636</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7089</v>
+        <v>1.7088</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.785</v>
+        <v>1.7849</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0247</v>
+        <v>1.0246</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40236,7 +40236,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9577</v>
+        <v>0.9576</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8044</v>
+        <v>1.8043</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8773</v>
+        <v>1.8771</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40295,7 +40295,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9865</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8109</v>
+        <v>1.8108</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40338,7 +40338,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9424</v>
+        <v>0.9423</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7654</v>
+        <v>1.7653</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40372,7 +40372,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8576</v>
+        <v>0.8575</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6403</v>
+        <v>1.6401</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40397,7 +40397,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.027</v>
+        <v>1.0269</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40406,7 +40406,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8888</v>
+        <v>0.8887</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7361</v>
+        <v>1.7359</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40431,7 +40431,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9711</v>
+        <v>0.971</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7656</v>
+        <v>1.7654</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8812</v>
+        <v>1.881</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40508,7 +40508,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8811</v>
+        <v>0.881</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.948</v>
+        <v>1.9478</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40533,7 +40533,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9396</v>
+        <v>0.9395</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40542,7 +40542,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8706</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.014</v>
+        <v>2.0138</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1886</v>
+        <v>2.1883</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40610,7 +40610,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9314</v>
+        <v>0.9313</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3152</v>
+        <v>2.315</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40644,7 +40644,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9267</v>
+        <v>0.9266</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3403</v>
+        <v>2.34</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40669,7 +40669,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8771</v>
+        <v>0.877</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40678,7 +40678,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9352</v>
+        <v>0.9351</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4466</v>
+        <v>2.4463</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5237</v>
+        <v>2.5234</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40746,7 +40746,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.8991</v>
+        <v>0.899</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5469</v>
+        <v>2.5466</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40771,7 +40771,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7469</v>
+        <v>0.7468</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6735</v>
+        <v>2.6732</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7883</v>
+        <v>0.7882</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40814,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9121</v>
+        <v>0.912</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8236</v>
+        <v>2.8233</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8242</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40848,7 +40848,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9492</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0148</v>
+        <v>3.0144</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9465</v>
+        <v>0.9464</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9465</v>
+        <v>0.9464</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0042</v>
+        <v>3.0038</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9411</v>
+        <v>0.9425</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9411</v>
+        <v>0.9425</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9824</v>
+        <v>2.988</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>-0.833</v>
+        <v>-0.832</v>
       </c>
     </row>
     <row r="52">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.944</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.319</v>
+        <v>1.33</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.582</v>
+        <v>1.591</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.083</v>
+        <v>2.089</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.813</v>
+        <v>2.819</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.957</v>
+        <v>3.961</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.66</v>
+        <v>-0.649</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.111</v>
+        <v>-0.103</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.014</v>
+        <v>1.02</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.26</v>
+        <v>-1.27</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>65685.303</v>
+        <v>66013.21400000001</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3192</v>
+        <v>1.3304</v>
       </c>
       <c r="D261" t="n">
-        <v>1.5822</v>
+        <v>1.5913</v>
       </c>
       <c r="E261" t="n">
-        <v>2.0833</v>
+        <v>2.0886</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8128</v>
+        <v>2.819</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9565</v>
+        <v>3.9611</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6601</v>
+        <v>-0.6489</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.1113</v>
+        <v>-0.1035</v>
       </c>
       <c r="M261" t="n">
-        <v>1.014</v>
+        <v>1.0202</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>65685.3029</v>
+        <v>66013.2138</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32128,7 +32128,7 @@
         <v>-0.3431</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6431</v>
+        <v>-0.643</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7186</v>
@@ -32169,7 +32169,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.5672</v>
+        <v>-0.5671</v>
       </c>
       <c r="C4" t="n">
         <v>-0.068</v>
@@ -32292,7 +32292,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4886</v>
+        <v>-0.4885</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5127</v>
@@ -32339,7 +32339,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5393</v>
+        <v>-0.5392</v>
       </c>
       <c r="C9" t="n">
         <v>-0.2486</v>
@@ -32394,7 +32394,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3872</v>
+        <v>-0.3871</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2486</v>
@@ -32462,7 +32462,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2054</v>
+        <v>-0.2053</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2107</v>
@@ -32734,7 +32734,7 @@
         <v>-0.116</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1417</v>
+        <v>-0.1416</v>
       </c>
       <c r="J20" t="n">
         <v>-0.827</v>
@@ -32768,7 +32768,7 @@
         <v>-0.116</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1125</v>
+        <v>-0.1124</v>
       </c>
       <c r="J21" t="n">
         <v>-0.772</v>
@@ -33257,7 +33257,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3911</v>
+        <v>-0.391</v>
       </c>
       <c r="C36" t="n">
         <v>-0.244</v>
@@ -33278,7 +33278,7 @@
         <v>-0.225</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2339</v>
+        <v>-0.2338</v>
       </c>
       <c r="J36" t="n">
         <v>0.0688</v>
@@ -33312,7 +33312,7 @@
         <v>-0.6075</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2378</v>
+        <v>-0.2377</v>
       </c>
       <c r="J37" t="n">
         <v>0.1573</v>
@@ -33346,7 +33346,7 @@
         <v>-0.6075</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3748</v>
+        <v>-0.3747</v>
       </c>
       <c r="J38" t="n">
         <v>0.2114</v>
@@ -33414,7 +33414,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5619</v>
+        <v>-0.5618</v>
       </c>
       <c r="J40" t="n">
         <v>0.3612</v>
@@ -33618,7 +33618,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6503</v>
+        <v>-0.6502</v>
       </c>
       <c r="J46" t="n">
         <v>0.7897999999999999</v>
@@ -33720,7 +33720,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0529</v>
+        <v>-1.0528</v>
       </c>
       <c r="J49" t="n">
         <v>0.983</v>
@@ -33754,7 +33754,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0993</v>
+        <v>-1.0992</v>
       </c>
       <c r="J50" t="n">
         <v>0.7647</v>
@@ -33776,7 +33776,7 @@
         <v>0.1178</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0701</v>
+        <v>-1.07</v>
       </c>
       <c r="F51" t="n">
         <v>0.1178</v>
@@ -33788,7 +33788,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1111</v>
+        <v>-1.111</v>
       </c>
       <c r="J51" t="n">
         <v>0.6076</v>
@@ -33822,7 +33822,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.019</v>
+        <v>-1.0189</v>
       </c>
       <c r="J52" t="n">
         <v>0.4738</v>
@@ -33856,7 +33856,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9926</v>
+        <v>-0.9925</v>
       </c>
       <c r="J53" t="n">
         <v>0.1904</v>
@@ -33878,7 +33878,7 @@
         <v>-0.3292</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2403</v>
+        <v>-1.2402</v>
       </c>
       <c r="F54" t="n">
         <v>-0.3292</v>
@@ -33890,7 +33890,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0185</v>
+        <v>-1.0184</v>
       </c>
       <c r="J54" t="n">
         <v>0.1077</v>
@@ -33912,7 +33912,7 @@
         <v>-0.5705</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.3058</v>
+        <v>-1.3057</v>
       </c>
       <c r="F55" t="n">
         <v>-0.5705</v>
@@ -33924,7 +33924,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9931</v>
+        <v>-0.993</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0219</v>
@@ -33992,7 +33992,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0109</v>
+        <v>-1.0108</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4398</v>
@@ -34014,7 +34014,7 @@
         <v>-0.8324</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.3501</v>
+        <v>-1.35</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8324</v>
@@ -34060,7 +34060,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1038</v>
+        <v>-1.1037</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8167</v>
@@ -34073,7 +34073,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.2492</v>
+        <v>-1.2491</v>
       </c>
       <c r="C60" t="n">
         <v>0.9198</v>
@@ -34128,7 +34128,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0997</v>
+        <v>-1.0996</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1668</v>
@@ -34196,7 +34196,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0935</v>
+        <v>-1.0934</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4597</v>
@@ -34354,7 +34354,7 @@
         <v>-0.2725</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.3921</v>
+        <v>-1.392</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2725</v>
@@ -34400,7 +34400,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1957</v>
+        <v>-1.1956</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0592</v>
@@ -34447,7 +34447,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0187</v>
+        <v>-1.0186</v>
       </c>
       <c r="C71" t="n">
         <v>0.5209</v>
@@ -34536,7 +34536,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1958</v>
+        <v>-1.1957</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8566</v>
@@ -34604,7 +34604,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2118</v>
+        <v>-1.2117</v>
       </c>
       <c r="J75" t="n">
         <v>-1.811</v>
@@ -34638,7 +34638,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2421</v>
+        <v>-1.242</v>
       </c>
       <c r="J76" t="n">
         <v>-1.702</v>
@@ -34672,7 +34672,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2094</v>
+        <v>-1.2093</v>
       </c>
       <c r="J77" t="n">
         <v>-1.5973</v>
@@ -34694,7 +34694,7 @@
         <v>0.1141</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9681</v>
+        <v>-0.968</v>
       </c>
       <c r="F78" t="n">
         <v>0.1141</v>
@@ -34706,7 +34706,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2485</v>
+        <v>-1.2484</v>
       </c>
       <c r="J78" t="n">
         <v>-1.63</v>
@@ -34740,7 +34740,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2705</v>
+        <v>-1.2704</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5321</v>
@@ -34753,7 +34753,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.6844</v>
+        <v>-0.6843</v>
       </c>
       <c r="C80" t="n">
         <v>0.1919</v>
@@ -34787,7 +34787,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.6666</v>
+        <v>-0.6665</v>
       </c>
       <c r="C81" t="n">
         <v>0.2028</v>
@@ -34796,7 +34796,7 @@
         <v>0.3202</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.9133</v>
+        <v>-0.9132</v>
       </c>
       <c r="F81" t="n">
         <v>0.3202</v>
@@ -34808,7 +34808,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.318</v>
+        <v>-1.3179</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4777</v>
@@ -34842,7 +34842,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3338</v>
+        <v>-1.3337</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3458</v>
@@ -34864,7 +34864,7 @@
         <v>0.1822</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.871</v>
+        <v>-0.8709</v>
       </c>
       <c r="F83" t="n">
         <v>0.1822</v>
@@ -34876,7 +34876,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3307</v>
+        <v>-1.3306</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3601</v>
@@ -34898,7 +34898,7 @@
         <v>0.1353</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.8492</v>
       </c>
       <c r="F84" t="n">
         <v>0.1353</v>
@@ -34923,7 +34923,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6204</v>
       </c>
       <c r="C85" t="n">
         <v>0.0525</v>
@@ -34932,7 +34932,7 @@
         <v>0.1899</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.823</v>
       </c>
       <c r="F85" t="n">
         <v>0.1899</v>
@@ -34944,7 +34944,7 @@
         <v>-0.577</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3224</v>
+        <v>-1.3223</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2788</v>
@@ -34978,7 +34978,7 @@
         <v>-0.577</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3447</v>
+        <v>-1.3446</v>
       </c>
       <c r="J86" t="n">
         <v>-1.123</v>
@@ -35000,7 +35000,7 @@
         <v>0.2855</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.7684</v>
+        <v>-0.7683</v>
       </c>
       <c r="F87" t="n">
         <v>0.2855</v>
@@ -35080,7 +35080,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2364</v>
+        <v>-1.2363</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0901</v>
@@ -35114,7 +35114,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2896</v>
+        <v>-1.2895</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9147999999999999</v>
@@ -35148,7 +35148,7 @@
         <v>-0.389</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2917</v>
+        <v>-1.2916</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9429999999999999</v>
@@ -35182,7 +35182,7 @@
         <v>-0.389</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2956</v>
+        <v>-1.2955</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8282</v>
@@ -35195,7 +35195,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4643</v>
+        <v>-0.4642</v>
       </c>
       <c r="C93" t="n">
         <v>-0.2228</v>
@@ -35216,7 +35216,7 @@
         <v>-0.389</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2936</v>
+        <v>-1.2935</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8172</v>
@@ -35238,7 +35238,7 @@
         <v>0.2718</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5709</v>
+        <v>-0.5708</v>
       </c>
       <c r="F94" t="n">
         <v>0.2718</v>
@@ -35250,7 +35250,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3032</v>
+        <v>-1.3031</v>
       </c>
       <c r="J94" t="n">
         <v>-0.782</v>
@@ -35272,7 +35272,7 @@
         <v>0.272</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5615</v>
+        <v>-0.5614</v>
       </c>
       <c r="F95" t="n">
         <v>0.272</v>
@@ -35318,7 +35318,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2591</v>
+        <v>-1.259</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5867</v>
@@ -35386,7 +35386,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0586</v>
+        <v>-1.0585</v>
       </c>
       <c r="J98" t="n">
         <v>-0.618</v>
@@ -35420,7 +35420,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9719</v>
+        <v>-0.9718</v>
       </c>
       <c r="J99" t="n">
         <v>-0.505</v>
@@ -35454,7 +35454,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9234</v>
+        <v>-0.9233</v>
       </c>
       <c r="J100" t="n">
         <v>-0.5014</v>
@@ -35590,7 +35590,7 @@
         <v>-0.1008</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7262</v>
+        <v>-0.7261</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2338</v>
@@ -35612,7 +35612,7 @@
         <v>0.5889</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.1941</v>
+        <v>-0.194</v>
       </c>
       <c r="F105" t="n">
         <v>0.5889</v>
@@ -35692,7 +35692,7 @@
         <v>-0.0433</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7115</v>
+        <v>-0.7114</v>
       </c>
       <c r="J107" t="n">
         <v>-0.26</v>
@@ -35850,7 +35850,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.055</v>
+        <v>-0.0549</v>
       </c>
       <c r="F112" t="n">
         <v>0.8885999999999999</v>
@@ -35862,7 +35862,7 @@
         <v>0.1698</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5521</v>
+        <v>-0.552</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2412</v>
@@ -35998,7 +35998,7 @@
         <v>0.1933</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4796</v>
+        <v>-0.4795</v>
       </c>
       <c r="J116" t="n">
         <v>-0.1351</v>
@@ -36032,7 +36032,7 @@
         <v>0.1933</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4536</v>
+        <v>-0.4535</v>
       </c>
       <c r="J117" t="n">
         <v>-0.1128</v>
@@ -36304,7 +36304,7 @@
         <v>0.4856</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0254</v>
+        <v>0.0253</v>
       </c>
       <c r="J125" t="n">
         <v>-0.1084</v>
@@ -36385,7 +36385,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3078</v>
+        <v>0.3077</v>
       </c>
       <c r="C128" t="n">
         <v>-0.0979</v>
@@ -36406,7 +36406,7 @@
         <v>0.4715</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1408</v>
+        <v>0.1407</v>
       </c>
       <c r="J128" t="n">
         <v>-0.0397</v>
@@ -36487,7 +36487,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.302</v>
+        <v>0.3019</v>
       </c>
       <c r="C131" t="n">
         <v>-0.0621</v>
@@ -37120,7 +37120,7 @@
         <v>0.7867</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0396</v>
+        <v>-0.0397</v>
       </c>
       <c r="J149" t="n">
         <v>0.6211</v>
@@ -37154,7 +37154,7 @@
         <v>0.7867</v>
       </c>
       <c r="I150" t="n">
-        <v>0.014</v>
+        <v>0.0139</v>
       </c>
       <c r="J150" t="n">
         <v>0.5601</v>
@@ -37188,7 +37188,7 @@
         <v>0.8091</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.007</v>
+        <v>-0.0071</v>
       </c>
       <c r="J151" t="n">
         <v>0.5754</v>
@@ -37235,7 +37235,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5873</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="C153" t="n">
         <v>0.2345</v>
@@ -37256,7 +37256,7 @@
         <v>0.8091</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0117</v>
+        <v>-0.0118</v>
       </c>
       <c r="J153" t="n">
         <v>0.6850000000000001</v>
@@ -37324,7 +37324,7 @@
         <v>0.8138</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0743</v>
+        <v>0.0742</v>
       </c>
       <c r="J155" t="n">
         <v>0.8483000000000001</v>
@@ -37358,7 +37358,7 @@
         <v>0.8138</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0859</v>
+        <v>0.0858</v>
       </c>
       <c r="J156" t="n">
         <v>0.7721</v>
@@ -37562,7 +37562,7 @@
         <v>0.8306</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0713</v>
+        <v>0.0712</v>
       </c>
       <c r="J162" t="n">
         <v>1.1068</v>
@@ -37698,7 +37698,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1292</v>
+        <v>0.1291</v>
       </c>
       <c r="J166" t="n">
         <v>1.2724</v>
@@ -37745,7 +37745,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.7756</v>
+        <v>0.7755</v>
       </c>
       <c r="C168" t="n">
         <v>0.382</v>
@@ -37868,7 +37868,7 @@
         <v>0.87</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0324</v>
+        <v>-0.0325</v>
       </c>
       <c r="J171" t="n">
         <v>1.5072</v>
@@ -37902,7 +37902,7 @@
         <v>0.9549</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0273</v>
+        <v>-0.0274</v>
       </c>
       <c r="J172" t="n">
         <v>1.657</v>
@@ -37924,7 +37924,7 @@
         <v>0.8367</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7785</v>
+        <v>0.7784</v>
       </c>
       <c r="F173" t="n">
         <v>0.8367</v>
@@ -37936,7 +37936,7 @@
         <v>0.9549</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0255</v>
+        <v>-0.0256</v>
       </c>
       <c r="J173" t="n">
         <v>1.6147</v>
@@ -38004,7 +38004,7 @@
         <v>0.9513</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1329</v>
+        <v>-0.133</v>
       </c>
       <c r="J175" t="n">
         <v>1.8108</v>
@@ -38106,7 +38106,7 @@
         <v>0.451</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1771</v>
+        <v>-0.1772</v>
       </c>
       <c r="J178" t="n">
         <v>1.9331</v>
@@ -38174,7 +38174,7 @@
         <v>0.451</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1653</v>
+        <v>-0.1654</v>
       </c>
       <c r="J180" t="n">
         <v>1.9108</v>
@@ -38242,7 +38242,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1852</v>
+        <v>-0.1853</v>
       </c>
       <c r="J182" t="n">
         <v>2.0493</v>
@@ -38378,7 +38378,7 @@
         <v>-0.4462</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2631</v>
+        <v>-0.2632</v>
       </c>
       <c r="J186" t="n">
         <v>2.1842</v>
@@ -38412,7 +38412,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1967</v>
+        <v>-0.1968</v>
       </c>
       <c r="J187" t="n">
         <v>2.2688</v>
@@ -38514,7 +38514,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1347</v>
+        <v>-0.1348</v>
       </c>
       <c r="J190" t="n">
         <v>1.5321</v>
@@ -38527,7 +38527,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.2385</v>
+        <v>0.2384</v>
       </c>
       <c r="C191" t="n">
         <v>0.3429</v>
@@ -38582,7 +38582,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0501</v>
+        <v>-0.0502</v>
       </c>
       <c r="J192" t="n">
         <v>1.0402</v>
@@ -38629,7 +38629,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.1684</v>
+        <v>0.1683</v>
       </c>
       <c r="C194" t="n">
         <v>0.2157</v>
@@ -38650,7 +38650,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0496</v>
+        <v>0.0495</v>
       </c>
       <c r="J194" t="n">
         <v>0.5541</v>
@@ -38684,7 +38684,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1115</v>
+        <v>0.1114</v>
       </c>
       <c r="J195" t="n">
         <v>0.3553</v>
@@ -38697,7 +38697,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.1745</v>
+        <v>0.1744</v>
       </c>
       <c r="C196" t="n">
         <v>0.031</v>
@@ -38718,7 +38718,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1826</v>
+        <v>0.1825</v>
       </c>
       <c r="J196" t="n">
         <v>0.0803</v>
@@ -38752,7 +38752,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2262</v>
+        <v>0.2261</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1028</v>
@@ -38765,7 +38765,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.073</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="C198" t="n">
         <v>-0.0649</v>
@@ -38786,7 +38786,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2333</v>
+        <v>0.2332</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4271</v>
@@ -38854,7 +38854,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2863</v>
+        <v>0.2862</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6202</v>
@@ -38888,7 +38888,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2998</v>
+        <v>0.2997</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6014</v>
@@ -38922,7 +38922,7 @@
         <v>0.091</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3845</v>
+        <v>0.3844</v>
       </c>
       <c r="J202" t="n">
         <v>-0.416</v>
@@ -38990,7 +38990,7 @@
         <v>0.091</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4311</v>
+        <v>0.431</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4266</v>
@@ -39024,7 +39024,7 @@
         <v>0.2135</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4367</v>
+        <v>0.4366</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3874</v>
@@ -39058,7 +39058,7 @@
         <v>0.2135</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4277</v>
+        <v>0.4276</v>
       </c>
       <c r="J206" t="n">
         <v>-0.253</v>
@@ -39071,7 +39071,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3628</v>
+        <v>0.3627</v>
       </c>
       <c r="C207" t="n">
         <v>-0.5511</v>
@@ -39148,7 +39148,7 @@
         <v>1.2979</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4252</v>
+        <v>0.4251</v>
       </c>
       <c r="F209" t="n">
         <v>1.2979</v>
@@ -39194,7 +39194,7 @@
         <v>0.3986</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6609</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1676</v>
@@ -39216,7 +39216,7 @@
         <v>1.3412</v>
       </c>
       <c r="E211" t="n">
-        <v>0.5078</v>
+        <v>0.5077</v>
       </c>
       <c r="F211" t="n">
         <v>1.3412</v>
@@ -39228,7 +39228,7 @@
         <v>0.5324</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7557</v>
+        <v>0.7556</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1123</v>
@@ -39262,7 +39262,7 @@
         <v>0.5324</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7924</v>
+        <v>0.7923</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1272</v>
@@ -39296,7 +39296,7 @@
         <v>0.5324</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8148</v>
+        <v>0.8147</v>
       </c>
       <c r="J213" t="n">
         <v>-0.0809</v>
@@ -39309,7 +39309,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.8452</v>
       </c>
       <c r="C214" t="n">
         <v>-0.7835</v>
@@ -39364,7 +39364,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9875</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="J215" t="n">
         <v>0.0289</v>
@@ -39377,7 +39377,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8766</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="C216" t="n">
         <v>-0.9258</v>
@@ -39398,7 +39398,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9277</v>
+        <v>0.9276</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0187</v>
@@ -39432,7 +39432,7 @@
         <v>0.6974</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7986</v>
+        <v>0.7985</v>
       </c>
       <c r="J217" t="n">
         <v>0.1675</v>
@@ -39466,7 +39466,7 @@
         <v>0.6974</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7286</v>
+        <v>0.7285</v>
       </c>
       <c r="J218" t="n">
         <v>0.1381</v>
@@ -39500,7 +39500,7 @@
         <v>0.6974</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7998</v>
       </c>
       <c r="J219" t="n">
         <v>0.2431</v>
@@ -39534,7 +39534,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.802</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="J220" t="n">
         <v>0.2685</v>
@@ -39568,7 +39568,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8214</v>
+        <v>0.8213</v>
       </c>
       <c r="J221" t="n">
         <v>0.3099</v>
@@ -39602,7 +39602,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9203</v>
+        <v>0.9202</v>
       </c>
       <c r="J222" t="n">
         <v>0.249</v>
@@ -39615,7 +39615,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.9836</v>
+        <v>0.9835</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39636,7 +39636,7 @@
         <v>0.8441</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0451</v>
+        <v>1.045</v>
       </c>
       <c r="J223" t="n">
         <v>0.3667</v>
@@ -39658,7 +39658,7 @@
         <v>1.6966</v>
       </c>
       <c r="E224" t="n">
-        <v>0.795</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="F224" t="n">
         <v>1.6966</v>
@@ -39670,7 +39670,7 @@
         <v>0.8441</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0635</v>
+        <v>1.0634</v>
       </c>
       <c r="J224" t="n">
         <v>0.3764</v>
@@ -39692,7 +39692,7 @@
         <v>1.6703</v>
       </c>
       <c r="E225" t="n">
-        <v>0.8204</v>
+        <v>0.8203</v>
       </c>
       <c r="F225" t="n">
         <v>1.6703</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1517</v>
+        <v>1.1516</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2204</v>
+        <v>1.2203</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -39772,7 +39772,7 @@
         <v>0.9485</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2504</v>
+        <v>1.2503</v>
       </c>
       <c r="J227" t="n">
         <v>0.355</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3219</v>
+        <v>1.3218</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2503</v>
+        <v>1.2502</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39874,7 +39874,7 @@
         <v>1.0464</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3527</v>
+        <v>1.3525</v>
       </c>
       <c r="J230" t="n">
         <v>0.4839</v>
@@ -39887,7 +39887,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0573</v>
+        <v>1.0572</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -39908,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4937</v>
+        <v>1.4935</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39930,7 +39930,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.003</v>
+        <v>1.0029</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5584</v>
+        <v>1.5582</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -39964,7 +39964,7 @@
         <v>1.1823</v>
       </c>
       <c r="E233" t="n">
-        <v>1.0021</v>
+        <v>1.002</v>
       </c>
       <c r="F233" t="n">
         <v>1.1823</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6209</v>
+        <v>1.6207</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -39989,7 +39989,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.061</v>
+        <v>1.0609</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6671</v>
+        <v>1.667</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7493</v>
+        <v>1.7491</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7847</v>
+        <v>1.7845</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40100,7 +40100,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9245</v>
+        <v>0.9244</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5594</v>
+        <v>1.5592</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40125,7 +40125,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9774</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5453</v>
+        <v>1.5452</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7088</v>
+        <v>1.7086</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40193,7 +40193,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0185</v>
+        <v>1.0184</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40202,7 +40202,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9601</v>
+        <v>0.96</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7849</v>
+        <v>1.7847</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8043</v>
+        <v>1.8041</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40270,7 +40270,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9349</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8771</v>
+        <v>1.8769</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8108</v>
+        <v>1.8106</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40329,7 +40329,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.0244</v>
+        <v>1.0243</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7653</v>
+        <v>1.7651</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40363,7 +40363,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.0013</v>
+        <v>1.0012</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6401</v>
+        <v>1.64</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7359</v>
+        <v>1.7358</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40440,7 +40440,7 @@
         <v>1.4541</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8502</v>
       </c>
       <c r="F247" t="n">
         <v>1.4541</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7654</v>
+        <v>1.7653</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40465,7 +40465,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9418</v>
+        <v>0.9417</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.881</v>
+        <v>1.8808</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9478</v>
+        <v>1.9476</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0138</v>
+        <v>2.0135</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40567,7 +40567,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.981</v>
+        <v>0.9809</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40576,7 +40576,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9173</v>
+        <v>0.9172</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1883</v>
+        <v>2.1881</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40601,7 +40601,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9871</v>
+        <v>0.987</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.315</v>
+        <v>2.3147</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40635,7 +40635,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7481</v>
+        <v>0.748</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40644,7 +40644,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9266</v>
+        <v>0.9265</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.34</v>
+        <v>2.3398</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4463</v>
+        <v>2.446</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8386</v>
+        <v>0.8385</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40712,7 +40712,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9376</v>
+        <v>0.9375</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5234</v>
+        <v>2.5231</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40737,7 +40737,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8172</v>
+        <v>0.8171</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40746,7 +40746,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.899</v>
+        <v>0.8989</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5466</v>
+        <v>2.5464</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40780,7 +40780,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8531</v>
+        <v>0.853</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6732</v>
+        <v>2.6729</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40814,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.912</v>
+        <v>0.9119</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8233</v>
+        <v>2.8229</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.824</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40848,7 +40848,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.949</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0144</v>
+        <v>3.014</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9464</v>
+        <v>0.9463</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9464</v>
+        <v>0.9463</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0038</v>
+        <v>3.0034</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9425</v>
+        <v>0.944</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9425</v>
+        <v>0.944</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.988</v>
+        <v>2.9939</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.94</t>
+          <t>+0.95</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-0.545</v>
+        <v>-0.544</v>
       </c>
     </row>
     <row r="8">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.94 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.95 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>-1.247</v>
+        <v>-1.246</v>
       </c>
     </row>
     <row r="57">
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="251">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>0.839</v>
+        <v>0.838</v>
       </c>
     </row>
     <row r="256">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.944</v>
+        <v>0.945</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.33</v>
+        <v>1.339</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.591</v>
+        <v>1.599</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.089</v>
+        <v>2.094</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.819</v>
+        <v>2.826</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.961</v>
+        <v>3.966</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.649</v>
+        <v>-0.64</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.103</v>
+        <v>-0.097</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.02</v>
+        <v>1.027</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66013.21400000001</v>
+        <v>66313.27899999999</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3304</v>
+        <v>1.3391</v>
       </c>
       <c r="D261" t="n">
-        <v>1.5913</v>
+        <v>1.5987</v>
       </c>
       <c r="E261" t="n">
-        <v>2.0886</v>
+        <v>2.0943</v>
       </c>
       <c r="F261" t="n">
-        <v>2.819</v>
+        <v>2.8257</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9611</v>
+        <v>3.9663</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6489</v>
+        <v>-0.6402</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.1035</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0202</v>
+        <v>1.0269</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66013.2138</v>
+        <v>66313.2789</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32113,7 +32113,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6119</v>
+        <v>-0.6118</v>
       </c>
       <c r="D2" t="n">
         <v>0.2573</v>
@@ -32156,7 +32156,7 @@
         <v>-0.3209</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.59</v>
+        <v>-0.5899</v>
       </c>
       <c r="J3" t="n">
         <v>-1.6403</v>
@@ -32178,7 +32178,7 @@
         <v>0.1593</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7488</v>
+        <v>-0.7487</v>
       </c>
       <c r="F4" t="n">
         <v>0.1593</v>
@@ -32190,7 +32190,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5669</v>
+        <v>-0.5668</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6492</v>
@@ -32224,7 +32224,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5455</v>
+        <v>-0.5454</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5156</v>
@@ -32258,7 +32258,7 @@
         <v>-0.3767</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5349</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4222</v>
@@ -32314,7 +32314,7 @@
         <v>0.129</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6728</v>
       </c>
       <c r="F8" t="n">
         <v>0.129</v>
@@ -32326,7 +32326,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4089</v>
+        <v>-0.4088</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3624</v>
@@ -32428,7 +32428,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3026</v>
+        <v>-0.3025</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2859</v>
@@ -32700,7 +32700,7 @@
         <v>-0.116</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1808</v>
+        <v>-0.1807</v>
       </c>
       <c r="J19" t="n">
         <v>-0.86</v>
@@ -33074,7 +33074,7 @@
         <v>0.1358</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0958</v>
+        <v>0.0959</v>
       </c>
       <c r="J30" t="n">
         <v>-0.3377</v>
@@ -33142,7 +33142,7 @@
         <v>0.2333</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0907</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>-0.2231</v>
@@ -33300,7 +33300,7 @@
         <v>0.4873</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.604</v>
+        <v>-0.6039</v>
       </c>
       <c r="F37" t="n">
         <v>0.4873</v>
@@ -33380,7 +33380,7 @@
         <v>-0.6075</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4205</v>
+        <v>-0.4204</v>
       </c>
       <c r="J39" t="n">
         <v>0.2385</v>
@@ -33482,7 +33482,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.5317</v>
       </c>
       <c r="J42" t="n">
         <v>0.4861</v>
@@ -33550,7 +33550,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5632</v>
+        <v>-0.5631</v>
       </c>
       <c r="J44" t="n">
         <v>0.5824</v>
@@ -33563,7 +33563,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4097</v>
+        <v>-0.4096</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3257</v>
@@ -33584,7 +33584,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5587</v>
+        <v>-0.5586</v>
       </c>
       <c r="J45" t="n">
         <v>0.7418</v>
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.5747</v>
+        <v>-0.5746</v>
       </c>
       <c r="C47" t="n">
         <v>-0.3486</v>
@@ -33652,7 +33652,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8517</v>
+        <v>-0.8516</v>
       </c>
       <c r="J47" t="n">
         <v>0.741</v>
@@ -33686,7 +33686,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9328</v>
+        <v>-0.9327</v>
       </c>
       <c r="J48" t="n">
         <v>0.7829</v>
@@ -33720,7 +33720,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0528</v>
+        <v>-1.0527</v>
       </c>
       <c r="J49" t="n">
         <v>0.983</v>
@@ -33754,7 +33754,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0992</v>
+        <v>-1.0991</v>
       </c>
       <c r="J50" t="n">
         <v>0.7647</v>
@@ -33788,7 +33788,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.111</v>
+        <v>-1.1109</v>
       </c>
       <c r="J51" t="n">
         <v>0.6076</v>
@@ -33801,7 +33801,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9339</v>
       </c>
       <c r="C52" t="n">
         <v>0.4357</v>
@@ -33822,7 +33822,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0189</v>
+        <v>-1.0188</v>
       </c>
       <c r="J52" t="n">
         <v>0.4738</v>
@@ -33856,7 +33856,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9925</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0.1904</v>
@@ -33890,7 +33890,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0184</v>
+        <v>-1.0183</v>
       </c>
       <c r="J54" t="n">
         <v>0.1077</v>
@@ -33958,7 +33958,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0487</v>
+        <v>-1.0486</v>
       </c>
       <c r="J56" t="n">
         <v>-0.245</v>
@@ -34026,7 +34026,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0888</v>
+        <v>-1.0887</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5775</v>
@@ -34048,7 +34048,7 @@
         <v>-0.8113</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4017</v>
+        <v>-1.4016</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8113</v>
@@ -34094,7 +34094,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1189</v>
+        <v>-1.1188</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9842</v>
@@ -34116,7 +34116,7 @@
         <v>-0.3869</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.3954</v>
+        <v>-1.3953</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3869</v>
@@ -34162,7 +34162,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0641</v>
+        <v>-1.064</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3364</v>
@@ -34230,7 +34230,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0725</v>
+        <v>-1.0724</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6947</v>
@@ -34243,7 +34243,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1789</v>
+        <v>-1.1788</v>
       </c>
       <c r="C65" t="n">
         <v>0.6964</v>
@@ -34264,7 +34264,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0315</v>
+        <v>-1.0314</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8174</v>
@@ -34298,7 +34298,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0729</v>
+        <v>-1.0728</v>
       </c>
       <c r="J66" t="n">
         <v>-1.966</v>
@@ -34332,7 +34332,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0942</v>
+        <v>-1.0941</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1347</v>
@@ -34366,7 +34366,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1611</v>
+        <v>-1.161</v>
       </c>
       <c r="J68" t="n">
         <v>-2.108</v>
@@ -34388,7 +34388,7 @@
         <v>-0.261</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.3727</v>
+        <v>-1.3726</v>
       </c>
       <c r="F69" t="n">
         <v>-0.261</v>
@@ -34413,7 +34413,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0623</v>
+        <v>-1.0622</v>
       </c>
       <c r="C70" t="n">
         <v>0.5677</v>
@@ -34422,7 +34422,7 @@
         <v>-0.2922</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2548</v>
+        <v>-1.2547</v>
       </c>
       <c r="F70" t="n">
         <v>-0.2922</v>
@@ -34434,7 +34434,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2134</v>
+        <v>-1.2133</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9639</v>
@@ -34468,7 +34468,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2466</v>
+        <v>-1.2465</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9252</v>
@@ -34502,7 +34502,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2337</v>
+        <v>-1.2336</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8944</v>
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.953</v>
+        <v>-0.9529</v>
       </c>
       <c r="C73" t="n">
         <v>0.4411</v>
@@ -34570,7 +34570,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2215</v>
+        <v>-1.2214</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8329</v>
@@ -34651,7 +34651,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7478</v>
+        <v>-0.7477</v>
       </c>
       <c r="C77" t="n">
         <v>0.3431</v>
@@ -34774,7 +34774,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2713</v>
+        <v>-1.2712</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5145</v>
@@ -34808,7 +34808,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3179</v>
+        <v>-1.3178</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4777</v>
@@ -34830,7 +34830,7 @@
         <v>0.3264</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8633</v>
+        <v>-0.8632</v>
       </c>
       <c r="F82" t="n">
         <v>0.3264</v>
@@ -34876,7 +34876,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3306</v>
+        <v>-1.3305</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3601</v>
@@ -34910,7 +34910,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3174</v>
+        <v>-1.3173</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3222</v>
@@ -34944,7 +34944,7 @@
         <v>-0.577</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3223</v>
+        <v>-1.3222</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2788</v>
@@ -34978,7 +34978,7 @@
         <v>-0.577</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3446</v>
+        <v>-1.3445</v>
       </c>
       <c r="J86" t="n">
         <v>-1.123</v>
@@ -35012,7 +35012,7 @@
         <v>-0.577</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2935</v>
+        <v>-1.2934</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1315</v>
@@ -35046,7 +35046,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2131</v>
+        <v>-1.213</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0564</v>
@@ -35068,7 +35068,7 @@
         <v>0.3382</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.7141</v>
+        <v>-0.714</v>
       </c>
       <c r="F89" t="n">
         <v>0.3382</v>
@@ -35080,7 +35080,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2363</v>
+        <v>-1.2362</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0901</v>
@@ -35216,7 +35216,7 @@
         <v>-0.389</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2935</v>
+        <v>-1.2934</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8172</v>
@@ -35250,7 +35250,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.3031</v>
+        <v>-1.303</v>
       </c>
       <c r="J94" t="n">
         <v>-0.782</v>
@@ -35263,7 +35263,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.3948</v>
+        <v>-0.3947</v>
       </c>
       <c r="C95" t="n">
         <v>-0.2685</v>
@@ -35284,7 +35284,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2902</v>
+        <v>-1.2901</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7879</v>
@@ -35306,7 +35306,7 @@
         <v>0.2773</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.4911</v>
+        <v>-0.491</v>
       </c>
       <c r="F96" t="n">
         <v>0.2773</v>
@@ -35318,7 +35318,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.259</v>
+        <v>-1.2589</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5867</v>
@@ -35352,7 +35352,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1952</v>
+        <v>-1.1951</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5657</v>
@@ -35488,7 +35488,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8377</v>
+        <v>-0.8376</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4148</v>
@@ -35501,7 +35501,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.1594</v>
+        <v>-0.1593</v>
       </c>
       <c r="C102" t="n">
         <v>-0.5352</v>
@@ -35556,7 +35556,7 @@
         <v>-0.1008</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8167</v>
+        <v>-0.8166</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3561</v>
@@ -35624,7 +35624,7 @@
         <v>-0.1008</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7661</v>
+        <v>-0.766</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2459</v>
@@ -35658,7 +35658,7 @@
         <v>-0.0433</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.7151</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3637</v>
@@ -35807,7 +35807,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.1132</v>
+        <v>0.1133</v>
       </c>
       <c r="C111" t="n">
         <v>-0.7007</v>
@@ -35816,7 +35816,7 @@
         <v>0.8895999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.0809</v>
+        <v>-0.0808</v>
       </c>
       <c r="F111" t="n">
         <v>0.8895999999999999</v>
@@ -35930,7 +35930,7 @@
         <v>0.1698</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5249</v>
+        <v>-0.5248</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2192</v>
@@ -36066,7 +36066,7 @@
         <v>0.2519</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3465</v>
+        <v>-0.3464</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1607</v>
@@ -36270,7 +36270,7 @@
         <v>0.4856</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0118</v>
+        <v>0.0117</v>
       </c>
       <c r="J124" t="n">
         <v>-0.036</v>
@@ -36283,7 +36283,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.3034</v>
+        <v>0.3033</v>
       </c>
       <c r="C125" t="n">
         <v>-0.213</v>
@@ -36542,7 +36542,7 @@
         <v>0.5479000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1181</v>
+        <v>0.118</v>
       </c>
       <c r="J132" t="n">
         <v>-0.0215</v>
@@ -36678,7 +36678,7 @@
         <v>0.677</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0696</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J136" t="n">
         <v>0.0347</v>
@@ -36700,7 +36700,7 @@
         <v>0.2956</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3388</v>
+        <v>0.3389</v>
       </c>
       <c r="F137" t="n">
         <v>0.2956</v>
@@ -37392,7 +37392,7 @@
         <v>0.7919</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1104</v>
+        <v>0.1103</v>
       </c>
       <c r="J157" t="n">
         <v>0.8101</v>
@@ -37405,7 +37405,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.667</v>
+        <v>0.6669</v>
       </c>
       <c r="C158" t="n">
         <v>0.3164</v>
@@ -37426,7 +37426,7 @@
         <v>0.7919</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0897</v>
+        <v>0.0896</v>
       </c>
       <c r="J158" t="n">
         <v>1.005</v>
@@ -37528,7 +37528,7 @@
         <v>0.8306</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0158</v>
+        <v>0.0157</v>
       </c>
       <c r="J161" t="n">
         <v>1.03</v>
@@ -37541,7 +37541,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.6804</v>
+        <v>0.6803</v>
       </c>
       <c r="C162" t="n">
         <v>0.2684</v>
@@ -37652,7 +37652,7 @@
         <v>0.8058999999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>0.72</v>
+        <v>0.7199</v>
       </c>
       <c r="F165" t="n">
         <v>0.8058999999999999</v>
@@ -37732,7 +37732,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0994</v>
       </c>
       <c r="J167" t="n">
         <v>1.3895</v>
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.7188</v>
+        <v>0.7187</v>
       </c>
       <c r="C169" t="n">
         <v>0.4257</v>
@@ -37834,7 +37834,7 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0499</v>
+        <v>-0.05</v>
       </c>
       <c r="J170" t="n">
         <v>1.539</v>
@@ -38026,7 +38026,7 @@
         <v>0.7313</v>
       </c>
       <c r="E176" t="n">
-        <v>0.8086</v>
+        <v>0.8085</v>
       </c>
       <c r="F176" t="n">
         <v>0.7313</v>
@@ -38038,7 +38038,7 @@
         <v>0.9513</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1412</v>
+        <v>-0.1413</v>
       </c>
       <c r="J176" t="n">
         <v>1.8237</v>
@@ -38072,7 +38072,7 @@
         <v>0.9513</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.1947</v>
+        <v>-0.1948</v>
       </c>
       <c r="J177" t="n">
         <v>1.8039</v>
@@ -38208,7 +38208,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1579</v>
+        <v>-0.158</v>
       </c>
       <c r="J181" t="n">
         <v>1.9529</v>
@@ -38264,7 +38264,7 @@
         <v>0.7168</v>
       </c>
       <c r="E183" t="n">
-        <v>0.6428</v>
+        <v>0.6427</v>
       </c>
       <c r="F183" t="n">
         <v>0.7168</v>
@@ -38276,7 +38276,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2004</v>
+        <v>-0.2005</v>
       </c>
       <c r="J183" t="n">
         <v>2.1742</v>
@@ -38366,7 +38366,7 @@
         <v>0.399</v>
       </c>
       <c r="E186" t="n">
-        <v>0.4874</v>
+        <v>0.4873</v>
       </c>
       <c r="F186" t="n">
         <v>0.399</v>
@@ -38400,7 +38400,7 @@
         <v>0.3928</v>
       </c>
       <c r="E187" t="n">
-        <v>0.431</v>
+        <v>0.4309</v>
       </c>
       <c r="F187" t="n">
         <v>0.3928</v>
@@ -38446,7 +38446,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1785</v>
+        <v>-0.1786</v>
       </c>
       <c r="J188" t="n">
         <v>2.013</v>
@@ -38480,7 +38480,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1428</v>
+        <v>-0.1429</v>
       </c>
       <c r="J189" t="n">
         <v>1.7738</v>
@@ -38493,7 +38493,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.2984</v>
+        <v>0.2983</v>
       </c>
       <c r="C190" t="n">
         <v>0.3714</v>
@@ -38595,7 +38595,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2102</v>
+        <v>0.2101</v>
       </c>
       <c r="C193" t="n">
         <v>0.2348</v>
@@ -38616,7 +38616,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0137</v>
+        <v>-0.0138</v>
       </c>
       <c r="J193" t="n">
         <v>0.855</v>
@@ -38684,7 +38684,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1114</v>
+        <v>0.1113</v>
       </c>
       <c r="J195" t="n">
         <v>0.3553</v>
@@ -38706,7 +38706,7 @@
         <v>0.2432</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1573</v>
+        <v>0.1572</v>
       </c>
       <c r="F196" t="n">
         <v>0.2432</v>
@@ -38718,7 +38718,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1825</v>
+        <v>0.1824</v>
       </c>
       <c r="J196" t="n">
         <v>0.0803</v>
@@ -38752,7 +38752,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2261</v>
+        <v>0.226</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1028</v>
@@ -38820,7 +38820,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2797</v>
+        <v>0.2796</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6688</v>
@@ -38854,7 +38854,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2862</v>
+        <v>0.2861</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6202</v>
@@ -38876,7 +38876,7 @@
         <v>0.4293</v>
       </c>
       <c r="E201" t="n">
-        <v>0.067</v>
+        <v>0.0669</v>
       </c>
       <c r="F201" t="n">
         <v>0.4293</v>
@@ -38888,7 +38888,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2997</v>
+        <v>0.2996</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6014</v>
@@ -38901,7 +38901,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2561</v>
+        <v>0.256</v>
       </c>
       <c r="C202" t="n">
         <v>-0.2762</v>
@@ -38922,7 +38922,7 @@
         <v>0.091</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3844</v>
+        <v>0.3843</v>
       </c>
       <c r="J202" t="n">
         <v>-0.416</v>
@@ -38956,7 +38956,7 @@
         <v>0.091</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3972</v>
+        <v>0.3971</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5065</v>
@@ -38978,7 +38978,7 @@
         <v>0.6375</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2097</v>
+        <v>0.2096</v>
       </c>
       <c r="F204" t="n">
         <v>0.6375</v>
@@ -38990,7 +38990,7 @@
         <v>0.091</v>
       </c>
       <c r="I204" t="n">
-        <v>0.431</v>
+        <v>0.4309</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4266</v>
@@ -39024,7 +39024,7 @@
         <v>0.2135</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4366</v>
+        <v>0.4365</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3874</v>
@@ -39058,7 +39058,7 @@
         <v>0.2135</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4276</v>
+        <v>0.4275</v>
       </c>
       <c r="J206" t="n">
         <v>-0.253</v>
@@ -39092,7 +39092,7 @@
         <v>0.2135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4428</v>
+        <v>0.4427</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2922</v>
@@ -39126,7 +39126,7 @@
         <v>0.3986</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4729</v>
+        <v>0.4728</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2508</v>
@@ -39160,7 +39160,7 @@
         <v>0.3986</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6139</v>
+        <v>0.6138</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1699</v>
@@ -39173,7 +39173,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.5978</v>
+        <v>0.5977</v>
       </c>
       <c r="C210" t="n">
         <v>-0.6456</v>
@@ -39318,7 +39318,7 @@
         <v>1.7312</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6238</v>
+        <v>0.6237</v>
       </c>
       <c r="F214" t="n">
         <v>1.7312</v>
@@ -39330,7 +39330,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9177</v>
+        <v>0.9176</v>
       </c>
       <c r="J214" t="n">
         <v>0.0795</v>
@@ -39364,7 +39364,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9873</v>
       </c>
       <c r="J215" t="n">
         <v>0.0289</v>
@@ -39398,7 +39398,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9276</v>
+        <v>0.9275</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0187</v>
@@ -39432,7 +39432,7 @@
         <v>0.6974</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7985</v>
+        <v>0.7984</v>
       </c>
       <c r="J217" t="n">
         <v>0.1675</v>
@@ -39479,7 +39479,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8578</v>
+        <v>0.8577</v>
       </c>
       <c r="C219" t="n">
         <v>-1.0961</v>
@@ -39534,7 +39534,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8018</v>
       </c>
       <c r="J220" t="n">
         <v>0.2685</v>
@@ -39556,7 +39556,7 @@
         <v>1.8104</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7127</v>
+        <v>0.7126</v>
       </c>
       <c r="F221" t="n">
         <v>1.8104</v>
@@ -39568,7 +39568,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8213</v>
+        <v>0.8212</v>
       </c>
       <c r="J221" t="n">
         <v>0.3099</v>
@@ -39602,7 +39602,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9202</v>
+        <v>0.9201</v>
       </c>
       <c r="J222" t="n">
         <v>0.249</v>
@@ -39624,7 +39624,7 @@
         <v>1.7742</v>
       </c>
       <c r="E223" t="n">
-        <v>0.7859</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="F223" t="n">
         <v>1.7742</v>
@@ -39636,7 +39636,7 @@
         <v>0.8441</v>
       </c>
       <c r="I223" t="n">
-        <v>1.045</v>
+        <v>1.0449</v>
       </c>
       <c r="J223" t="n">
         <v>0.3667</v>
@@ -39649,7 +39649,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9752</v>
       </c>
       <c r="C224" t="n">
         <v>-1.3976</v>
@@ -39670,7 +39670,7 @@
         <v>0.8441</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0634</v>
+        <v>1.0633</v>
       </c>
       <c r="J224" t="n">
         <v>0.3764</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1516</v>
+        <v>1.1515</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39717,7 +39717,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9768</v>
+        <v>0.9767</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2203</v>
+        <v>1.2202</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -39760,7 +39760,7 @@
         <v>1.5257</v>
       </c>
       <c r="E227" t="n">
-        <v>0.85</v>
+        <v>0.8499</v>
       </c>
       <c r="F227" t="n">
         <v>1.5257</v>
@@ -39772,7 +39772,7 @@
         <v>0.9485</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2503</v>
+        <v>1.2502</v>
       </c>
       <c r="J227" t="n">
         <v>0.355</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3218</v>
+        <v>1.3217</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39828,7 +39828,7 @@
         <v>1.451</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8797</v>
+        <v>0.8796</v>
       </c>
       <c r="F229" t="n">
         <v>1.451</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2502</v>
+        <v>1.2501</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.9827</v>
+        <v>0.9826</v>
       </c>
       <c r="C230" t="n">
         <v>-1.8168</v>
@@ -39862,7 +39862,7 @@
         <v>1.1742</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9348</v>
+        <v>0.9347</v>
       </c>
       <c r="F230" t="n">
         <v>1.1742</v>
@@ -39874,7 +39874,7 @@
         <v>1.0464</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3525</v>
+        <v>1.3524</v>
       </c>
       <c r="J230" t="n">
         <v>0.4839</v>
@@ -39896,7 +39896,7 @@
         <v>1.4899</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.949</v>
       </c>
       <c r="F231" t="n">
         <v>1.4899</v>
@@ -39908,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4935</v>
+        <v>1.4933</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5582</v>
+        <v>1.558</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6207</v>
+        <v>1.6206</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -39998,7 +39998,7 @@
         <v>1.2976</v>
       </c>
       <c r="E234" t="n">
-        <v>1.0018</v>
+        <v>1.0017</v>
       </c>
       <c r="F234" t="n">
         <v>1.2976</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.667</v>
+        <v>1.6668</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7491</v>
+        <v>1.7489</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40066,7 +40066,7 @@
         <v>1.3708</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0132</v>
+        <v>1.0131</v>
       </c>
       <c r="F236" t="n">
         <v>1.3708</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7845</v>
+        <v>1.7843</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5592</v>
+        <v>1.5591</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5452</v>
+        <v>1.545</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40159,7 +40159,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7086</v>
+        <v>1.7085</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7847</v>
+        <v>1.7846</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40236,7 +40236,7 @@
         <v>1.2928</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9576</v>
+        <v>0.9575</v>
       </c>
       <c r="F241" t="n">
         <v>1.2928</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8041</v>
+        <v>1.8039</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0349</v>
+        <v>1.0348</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8769</v>
+        <v>1.8768</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40304,7 +40304,7 @@
         <v>1.3058</v>
       </c>
       <c r="E243" t="n">
-        <v>0.9066</v>
+        <v>0.9065</v>
       </c>
       <c r="F243" t="n">
         <v>1.3058</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8106</v>
+        <v>1.8105</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40338,7 +40338,7 @@
         <v>1.3525</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9423</v>
+        <v>0.9422</v>
       </c>
       <c r="F244" t="n">
         <v>1.3525</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7651</v>
+        <v>1.7649</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.64</v>
+        <v>1.6399</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7358</v>
+        <v>1.7356</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7653</v>
+        <v>1.7651</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40474,7 +40474,7 @@
         <v>1.3</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8522</v>
+        <v>0.8521</v>
       </c>
       <c r="F248" t="n">
         <v>1.3</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8808</v>
+        <v>1.8806</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40499,7 +40499,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9281</v>
+        <v>0.928</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40508,7 +40508,7 @@
         <v>1.1164</v>
       </c>
       <c r="E249" t="n">
-        <v>0.881</v>
+        <v>0.8809</v>
       </c>
       <c r="F249" t="n">
         <v>1.1164</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9476</v>
+        <v>1.9474</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40542,7 +40542,7 @@
         <v>1.2156</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8704</v>
       </c>
       <c r="F250" t="n">
         <v>1.2156</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0135</v>
+        <v>2.0133</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1881</v>
+        <v>2.1879</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40610,7 +40610,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9313</v>
+        <v>0.9312</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3147</v>
+        <v>2.3145</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3398</v>
+        <v>2.3395</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40669,7 +40669,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.877</v>
+        <v>0.8769</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40678,7 +40678,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9351</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.446</v>
+        <v>2.4457</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40712,7 +40712,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9375</v>
+        <v>0.9374</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5231</v>
+        <v>2.5228</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40737,7 +40737,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8171</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40746,7 +40746,7 @@
         <v>0.4899</v>
       </c>
       <c r="E256" t="n">
-        <v>0.8989</v>
+        <v>0.8988</v>
       </c>
       <c r="F256" t="n">
         <v>0.4899</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5464</v>
+        <v>2.5461</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40771,7 +40771,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7468</v>
+        <v>0.7467</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40780,7 +40780,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.853</v>
+        <v>0.8529</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6729</v>
+        <v>2.6726</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7882</v>
+        <v>0.7881</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40814,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9119</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8229</v>
+        <v>2.8226</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.824</v>
+        <v>0.8239</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40848,7 +40848,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.949</v>
+        <v>0.9489</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.014</v>
+        <v>3.0136</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9463</v>
+        <v>0.9462</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9463</v>
+        <v>0.9462</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0034</v>
+        <v>3.003</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.944</v>
+        <v>0.9453</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.944</v>
+        <v>0.9453</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9939</v>
+        <v>2.9993</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>-1.247</v>
+        <v>-1.246</v>
       </c>
     </row>
     <row r="59">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="204">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.945</v>
+        <v>0.947</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.339</v>
+        <v>1.347</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.599</v>
+        <v>1.605</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.094</v>
+        <v>2.101</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.826</v>
+        <v>2.832</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.966</v>
+        <v>3.97</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.64</v>
+        <v>-0.632</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.097</v>
+        <v>-0.09</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.71</v>
+        <v>-0.72</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.027</v>
+        <v>1.033</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.27</v>
+        <v>-1.28</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66313.27899999999</v>
+        <v>66603.976</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3391</v>
+        <v>1.3472</v>
       </c>
       <c r="D261" t="n">
-        <v>1.5987</v>
+        <v>1.6052</v>
       </c>
       <c r="E261" t="n">
-        <v>2.0943</v>
+        <v>2.1006</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8257</v>
+        <v>2.8316</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9663</v>
+        <v>3.9702</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6402</v>
+        <v>-0.6321</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.0902</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0269</v>
+        <v>1.0328</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66313.2789</v>
+        <v>66603.976</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32128,7 +32128,7 @@
         <v>-0.3431</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.643</v>
+        <v>-0.6429</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7186</v>
@@ -32237,7 +32237,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5098</v>
+        <v>-0.5097</v>
       </c>
       <c r="C6" t="n">
         <v>-0.0915</v>
@@ -32292,7 +32292,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4885</v>
+        <v>-0.4884</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5127</v>
@@ -32348,7 +32348,7 @@
         <v>0.1057</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7005</v>
+        <v>-0.7004</v>
       </c>
       <c r="F9" t="n">
         <v>0.1057</v>
@@ -32360,7 +32360,7 @@
         <v>-0.3422</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4122</v>
+        <v>-0.4121</v>
       </c>
       <c r="J9" t="n">
         <v>-1.394</v>
@@ -32394,7 +32394,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3871</v>
+        <v>-0.387</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2486</v>
@@ -32586,7 +32586,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5639</v>
       </c>
       <c r="F16" t="n">
         <v>0.09089999999999999</v>
@@ -32598,7 +32598,7 @@
         <v>-0.1031</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1548</v>
+        <v>-0.1547</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0253</v>
@@ -33028,7 +33028,7 @@
         <v>-0.0893</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4684</v>
+        <v>-0.4683</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0893</v>
@@ -33436,7 +33436,7 @@
         <v>0.4139</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7565</v>
       </c>
       <c r="F41" t="n">
         <v>0.4139</v>
@@ -33448,7 +33448,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5585</v>
+        <v>-0.5584</v>
       </c>
       <c r="J41" t="n">
         <v>0.3765</v>
@@ -33516,7 +33516,7 @@
         <v>-1.4213</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5236</v>
+        <v>-0.5235</v>
       </c>
       <c r="J43" t="n">
         <v>0.5435</v>
@@ -33529,7 +33529,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.4285</v>
+        <v>-0.4284</v>
       </c>
       <c r="C44" t="n">
         <v>-0.2935</v>
@@ -33572,7 +33572,7 @@
         <v>1.038</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.7716</v>
+        <v>-0.7715</v>
       </c>
       <c r="F45" t="n">
         <v>1.038</v>
@@ -33618,7 +33618,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6502</v>
+        <v>-0.6501</v>
       </c>
       <c r="J46" t="n">
         <v>0.7897999999999999</v>
@@ -33652,7 +33652,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8516</v>
+        <v>-0.8515</v>
       </c>
       <c r="J47" t="n">
         <v>0.741</v>
@@ -33686,7 +33686,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9327</v>
+        <v>-0.9326</v>
       </c>
       <c r="J48" t="n">
         <v>0.7829</v>
@@ -33720,7 +33720,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0527</v>
+        <v>-1.0526</v>
       </c>
       <c r="J49" t="n">
         <v>0.983</v>
@@ -33733,7 +33733,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8134</v>
+        <v>-0.8133</v>
       </c>
       <c r="C50" t="n">
         <v>0.0205</v>
@@ -33788,7 +33788,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1109</v>
+        <v>-1.1108</v>
       </c>
       <c r="J51" t="n">
         <v>0.6076</v>
@@ -33810,7 +33810,7 @@
         <v>0.0701</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.185</v>
+        <v>-1.1849</v>
       </c>
       <c r="F52" t="n">
         <v>0.0701</v>
@@ -33835,7 +33835,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9742</v>
       </c>
       <c r="C53" t="n">
         <v>0.6286</v>
@@ -33924,7 +33924,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.993</v>
+        <v>-0.9929</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0219</v>
@@ -33958,7 +33958,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0486</v>
+        <v>-1.0485</v>
       </c>
       <c r="J56" t="n">
         <v>-0.245</v>
@@ -33971,7 +33971,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2973</v>
+        <v>-1.2972</v>
       </c>
       <c r="C57" t="n">
         <v>1.0128</v>
@@ -33992,7 +33992,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0108</v>
+        <v>-1.0107</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4398</v>
@@ -34060,7 +34060,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1037</v>
+        <v>-1.1036</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8167</v>
@@ -34094,7 +34094,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1188</v>
+        <v>-1.1187</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9842</v>
@@ -34107,7 +34107,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.1937</v>
+        <v>-1.1936</v>
       </c>
       <c r="C61" t="n">
         <v>0.8397</v>
@@ -34128,7 +34128,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0996</v>
+        <v>-1.0995</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1668</v>
@@ -34196,7 +34196,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0934</v>
+        <v>-1.0933</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4597</v>
@@ -34218,7 +34218,7 @@
         <v>-0.2615</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3882</v>
+        <v>-1.3881</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2615</v>
@@ -34332,7 +34332,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0941</v>
+        <v>-1.094</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1347</v>
@@ -34366,7 +34366,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.161</v>
+        <v>-1.1609</v>
       </c>
       <c r="J68" t="n">
         <v>-2.108</v>
@@ -34400,7 +34400,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1956</v>
+        <v>-1.1955</v>
       </c>
       <c r="J69" t="n">
         <v>-2.0592</v>
@@ -34434,7 +34434,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2133</v>
+        <v>-1.2132</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9639</v>
@@ -34468,7 +34468,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2465</v>
+        <v>-1.2464</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9252</v>
@@ -34502,7 +34502,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2336</v>
+        <v>-1.2335</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8944</v>
@@ -34524,7 +34524,7 @@
         <v>-0.1169</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.162</v>
+        <v>-1.1619</v>
       </c>
       <c r="F73" t="n">
         <v>-0.1169</v>
@@ -34536,7 +34536,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1957</v>
+        <v>-1.1956</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8566</v>
@@ -34558,7 +34558,7 @@
         <v>-0.1679</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1583</v>
+        <v>-1.1582</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1679</v>
@@ -34583,7 +34583,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9414</v>
+        <v>-0.9413</v>
       </c>
       <c r="C75" t="n">
         <v>0.3874</v>
@@ -34604,7 +34604,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2117</v>
+        <v>-1.2116</v>
       </c>
       <c r="J75" t="n">
         <v>-1.811</v>
@@ -34638,7 +34638,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.242</v>
+        <v>-1.2419</v>
       </c>
       <c r="J76" t="n">
         <v>-1.702</v>
@@ -34672,7 +34672,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2093</v>
+        <v>-1.2092</v>
       </c>
       <c r="J77" t="n">
         <v>-1.5973</v>
@@ -34706,7 +34706,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2484</v>
+        <v>-1.2483</v>
       </c>
       <c r="J78" t="n">
         <v>-1.63</v>
@@ -34740,7 +34740,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2704</v>
+        <v>-1.2703</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5321</v>
@@ -34842,7 +34842,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3337</v>
+        <v>-1.3336</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3458</v>
@@ -34876,7 +34876,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3305</v>
+        <v>-1.3304</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3601</v>
@@ -34910,7 +34910,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3173</v>
+        <v>-1.3172</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3222</v>
@@ -34957,7 +34957,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5844</v>
+        <v>-0.5843</v>
       </c>
       <c r="C86" t="n">
         <v>0.0257</v>
@@ -34966,7 +34966,7 @@
         <v>0.2368</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7897</v>
+        <v>-0.7896</v>
       </c>
       <c r="F86" t="n">
         <v>0.2368</v>
@@ -34991,7 +34991,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5576</v>
+        <v>-0.5575</v>
       </c>
       <c r="C87" t="n">
         <v>0.0584</v>
@@ -35012,7 +35012,7 @@
         <v>-0.577</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2934</v>
+        <v>-1.2933</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1315</v>
@@ -35046,7 +35046,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.213</v>
+        <v>-1.2129</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0564</v>
@@ -35114,7 +35114,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2895</v>
+        <v>-1.2894</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9147999999999999</v>
@@ -35148,7 +35148,7 @@
         <v>-0.389</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2916</v>
+        <v>-1.2915</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9429999999999999</v>
@@ -35161,7 +35161,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.4712</v>
+        <v>-0.4711</v>
       </c>
       <c r="C92" t="n">
         <v>-0.2331</v>
@@ -35182,7 +35182,7 @@
         <v>-0.389</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2955</v>
+        <v>-1.2954</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8282</v>
@@ -35204,7 +35204,7 @@
         <v>0.1767</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.6244</v>
       </c>
       <c r="F93" t="n">
         <v>0.1767</v>
@@ -35284,7 +35284,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2901</v>
+        <v>-1.29</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7879</v>
@@ -35352,7 +35352,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1951</v>
+        <v>-1.195</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5657</v>
@@ -35386,7 +35386,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0585</v>
+        <v>-1.0584</v>
       </c>
       <c r="J98" t="n">
         <v>-0.618</v>
@@ -35408,7 +35408,7 @@
         <v>0.1595</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.3745</v>
+        <v>-0.3744</v>
       </c>
       <c r="F99" t="n">
         <v>0.1595</v>
@@ -35420,7 +35420,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9718</v>
+        <v>-0.9717</v>
       </c>
       <c r="J99" t="n">
         <v>-0.505</v>
@@ -35454,7 +35454,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9233</v>
+        <v>-0.9232</v>
       </c>
       <c r="J100" t="n">
         <v>-0.5014</v>
@@ -35522,7 +35522,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7406</v>
+        <v>-0.7405</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4062</v>
@@ -35603,7 +35603,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0375</v>
+        <v>-0.0374</v>
       </c>
       <c r="C105" t="n">
         <v>-0.5632</v>
@@ -35828,7 +35828,7 @@
         <v>0.143</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5678</v>
+        <v>-0.5677</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2386</v>
@@ -35896,7 +35896,7 @@
         <v>0.1698</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5475</v>
+        <v>-0.5474</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2356</v>
@@ -36100,7 +36100,7 @@
         <v>0.2519</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3324</v>
+        <v>-0.3323</v>
       </c>
       <c r="J119" t="n">
         <v>-0.07729999999999999</v>
@@ -36168,7 +36168,7 @@
         <v>0.3328</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0718</v>
+        <v>-0.0717</v>
       </c>
       <c r="J121" t="n">
         <v>-0.0892</v>
@@ -36190,7 +36190,7 @@
         <v>1.3542</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1628</v>
+        <v>0.1629</v>
       </c>
       <c r="F122" t="n">
         <v>1.3542</v>
@@ -36746,7 +36746,7 @@
         <v>0.677</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1367</v>
+        <v>-0.1366</v>
       </c>
       <c r="J138" t="n">
         <v>0.0428</v>
@@ -37086,7 +37086,7 @@
         <v>0.7867</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0192</v>
+        <v>0.0191</v>
       </c>
       <c r="J148" t="n">
         <v>0.4407</v>
@@ -37133,7 +37133,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5541</v>
+        <v>0.554</v>
       </c>
       <c r="C150" t="n">
         <v>0.2745</v>
@@ -37596,7 +37596,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="J163" t="n">
         <v>1.2073</v>
@@ -37609,7 +37609,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.7126</v>
+        <v>0.7125</v>
       </c>
       <c r="C164" t="n">
         <v>0.3525</v>
@@ -37630,7 +37630,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J164" t="n">
         <v>1.2102</v>
@@ -37664,7 +37664,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0891</v>
+        <v>0.089</v>
       </c>
       <c r="J165" t="n">
         <v>1.321</v>
@@ -37698,7 +37698,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1291</v>
+        <v>0.129</v>
       </c>
       <c r="J166" t="n">
         <v>1.2724</v>
@@ -37766,7 +37766,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0888</v>
       </c>
       <c r="J168" t="n">
         <v>1.4432</v>
@@ -37800,7 +37800,7 @@
         <v>0.87</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0335</v>
+        <v>0.0334</v>
       </c>
       <c r="J169" t="n">
         <v>1.4195</v>
@@ -38140,7 +38140,7 @@
         <v>0.451</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.177</v>
+        <v>-0.1771</v>
       </c>
       <c r="J179" t="n">
         <v>1.9407</v>
@@ -38174,7 +38174,7 @@
         <v>0.451</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1654</v>
+        <v>-0.1655</v>
       </c>
       <c r="J180" t="n">
         <v>1.9108</v>
@@ -38425,7 +38425,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.3808</v>
+        <v>0.3807</v>
       </c>
       <c r="C188" t="n">
         <v>0.507</v>
@@ -38468,7 +38468,7 @@
         <v>0.2504</v>
       </c>
       <c r="E189" t="n">
-        <v>0.3239</v>
+        <v>0.3238</v>
       </c>
       <c r="F189" t="n">
         <v>0.2504</v>
@@ -38514,7 +38514,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1348</v>
+        <v>-0.1349</v>
       </c>
       <c r="J190" t="n">
         <v>1.5321</v>
@@ -38536,7 +38536,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2773</v>
+        <v>0.2772</v>
       </c>
       <c r="F191" t="n">
         <v>0.08309999999999999</v>
@@ -38548,7 +38548,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.0949</v>
+        <v>-0.095</v>
       </c>
       <c r="J191" t="n">
         <v>1.3067</v>
@@ -38582,7 +38582,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0502</v>
+        <v>-0.0503</v>
       </c>
       <c r="J192" t="n">
         <v>1.0402</v>
@@ -38616,7 +38616,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0138</v>
+        <v>-0.0139</v>
       </c>
       <c r="J193" t="n">
         <v>0.855</v>
@@ -38638,7 +38638,7 @@
         <v>0.1218</v>
       </c>
       <c r="E194" t="n">
-        <v>0.18</v>
+        <v>0.1799</v>
       </c>
       <c r="F194" t="n">
         <v>0.1218</v>
@@ -38650,7 +38650,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0495</v>
+        <v>0.0494</v>
       </c>
       <c r="J194" t="n">
         <v>0.5541</v>
@@ -38663,7 +38663,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.1538</v>
+        <v>0.1537</v>
       </c>
       <c r="C195" t="n">
         <v>0.1813</v>
@@ -38684,7 +38684,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1113</v>
+        <v>0.1112</v>
       </c>
       <c r="J195" t="n">
         <v>0.3553</v>
@@ -38718,7 +38718,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1824</v>
+        <v>0.1823</v>
       </c>
       <c r="J196" t="n">
         <v>0.0803</v>
@@ -38752,7 +38752,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I197" t="n">
-        <v>0.226</v>
+        <v>0.2259</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1028</v>
@@ -38774,7 +38774,7 @@
         <v>0.1608</v>
       </c>
       <c r="E198" t="n">
-        <v>0.051</v>
+        <v>0.0509</v>
       </c>
       <c r="F198" t="n">
         <v>0.1608</v>
@@ -38786,7 +38786,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2332</v>
+        <v>0.2331</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4271</v>
@@ -38820,7 +38820,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2796</v>
+        <v>0.2795</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6688</v>
@@ -38833,7 +38833,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.1088</v>
+        <v>0.1087</v>
       </c>
       <c r="C200" t="n">
         <v>-0.1771</v>
@@ -38854,7 +38854,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2861</v>
+        <v>0.286</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6202</v>
@@ -38888,7 +38888,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2996</v>
+        <v>0.2995</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6014</v>
@@ -38922,7 +38922,7 @@
         <v>0.091</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3843</v>
+        <v>0.3842</v>
       </c>
       <c r="J202" t="n">
         <v>-0.416</v>
@@ -38944,7 +38944,7 @@
         <v>0.5004999999999999</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1643</v>
+        <v>0.1642</v>
       </c>
       <c r="F203" t="n">
         <v>0.5004999999999999</v>
@@ -38956,7 +38956,7 @@
         <v>0.091</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3971</v>
+        <v>0.397</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5065</v>
@@ -38990,7 +38990,7 @@
         <v>0.091</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4309</v>
+        <v>0.4308</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4266</v>
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5599</v>
+        <v>0.5598</v>
       </c>
       <c r="C205" t="n">
         <v>-0.4359</v>
@@ -39058,7 +39058,7 @@
         <v>0.2135</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4275</v>
+        <v>0.4274</v>
       </c>
       <c r="J206" t="n">
         <v>-0.253</v>
@@ -39092,7 +39092,7 @@
         <v>0.2135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4427</v>
+        <v>0.4426</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2922</v>
@@ -39126,7 +39126,7 @@
         <v>0.3986</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4728</v>
+        <v>0.4727</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2508</v>
@@ -39160,7 +39160,7 @@
         <v>0.3986</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6138</v>
+        <v>0.6137</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1699</v>
@@ -39182,7 +39182,7 @@
         <v>1.2949</v>
       </c>
       <c r="E210" t="n">
-        <v>0.4235</v>
+        <v>0.4234</v>
       </c>
       <c r="F210" t="n">
         <v>1.2949</v>
@@ -39194,7 +39194,7 @@
         <v>0.3986</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6607</v>
       </c>
       <c r="J210" t="n">
         <v>-0.1676</v>
@@ -39228,7 +39228,7 @@
         <v>0.5324</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7556</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1123</v>
@@ -39262,7 +39262,7 @@
         <v>0.5324</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7923</v>
+        <v>0.7922</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1272</v>
@@ -39284,7 +39284,7 @@
         <v>1.5657</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5285</v>
+        <v>0.5284</v>
       </c>
       <c r="F213" t="n">
         <v>1.5657</v>
@@ -39296,7 +39296,7 @@
         <v>0.5324</v>
       </c>
       <c r="I213" t="n">
-        <v>0.8147</v>
+        <v>0.8146</v>
       </c>
       <c r="J213" t="n">
         <v>-0.0809</v>
@@ -39330,7 +39330,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9176</v>
+        <v>0.9175</v>
       </c>
       <c r="J214" t="n">
         <v>0.0795</v>
@@ -39411,7 +39411,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.8159</v>
+        <v>0.8158</v>
       </c>
       <c r="C217" t="n">
         <v>-0.9187</v>
@@ -39432,7 +39432,7 @@
         <v>0.6974</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7984</v>
+        <v>0.7983</v>
       </c>
       <c r="J217" t="n">
         <v>0.1675</v>
@@ -39466,7 +39466,7 @@
         <v>0.6974</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7285</v>
+        <v>0.7284</v>
       </c>
       <c r="J218" t="n">
         <v>0.1381</v>
@@ -39488,7 +39488,7 @@
         <v>1.6761</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6532</v>
+        <v>0.6531</v>
       </c>
       <c r="F219" t="n">
         <v>1.6761</v>
@@ -39500,7 +39500,7 @@
         <v>0.6974</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7998</v>
+        <v>0.7997</v>
       </c>
       <c r="J219" t="n">
         <v>0.2431</v>
@@ -39568,7 +39568,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8212</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="J221" t="n">
         <v>0.3099</v>
@@ -39581,7 +39581,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.9276</v>
+        <v>0.9275</v>
       </c>
       <c r="C222" t="n">
         <v>-1.4025</v>
@@ -39590,7 +39590,7 @@
         <v>1.724</v>
       </c>
       <c r="E222" t="n">
-        <v>0.7285</v>
+        <v>0.7284</v>
       </c>
       <c r="F222" t="n">
         <v>1.724</v>
@@ -39636,7 +39636,7 @@
         <v>0.8441</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0449</v>
+        <v>1.0448</v>
       </c>
       <c r="J223" t="n">
         <v>0.3667</v>
@@ -39670,7 +39670,7 @@
         <v>0.8441</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0633</v>
+        <v>1.0632</v>
       </c>
       <c r="J224" t="n">
         <v>0.3764</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1515</v>
+        <v>1.1514</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39726,7 +39726,7 @@
         <v>1.477</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8517</v>
+        <v>0.8516</v>
       </c>
       <c r="F226" t="n">
         <v>1.477</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2202</v>
+        <v>1.2201</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -39772,7 +39772,7 @@
         <v>0.9485</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2502</v>
+        <v>1.2501</v>
       </c>
       <c r="J227" t="n">
         <v>0.355</v>
@@ -39785,7 +39785,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.965</v>
+        <v>0.9649</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39794,7 +39794,7 @@
         <v>1.3813</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8609</v>
+        <v>0.8608</v>
       </c>
       <c r="F228" t="n">
         <v>1.3813</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3217</v>
+        <v>1.3216</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2501</v>
+        <v>1.25</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39874,7 +39874,7 @@
         <v>1.0464</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3524</v>
+        <v>1.3523</v>
       </c>
       <c r="J230" t="n">
         <v>0.4839</v>
@@ -39908,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4933</v>
+        <v>1.4932</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39921,7 +39921,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.079</v>
+        <v>1.0789</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -39930,7 +39930,7 @@
         <v>1.3833</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0029</v>
+        <v>1.0028</v>
       </c>
       <c r="F232" t="n">
         <v>1.3833</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.558</v>
+        <v>1.5579</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -39955,7 +39955,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0381</v>
+        <v>1.038</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6206</v>
+        <v>1.6204</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6668</v>
+        <v>1.6667</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40032,7 +40032,7 @@
         <v>1.3365</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0259</v>
+        <v>1.0258</v>
       </c>
       <c r="F235" t="n">
         <v>1.3365</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7489</v>
+        <v>1.7488</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40057,7 +40057,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0847</v>
+        <v>1.0846</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7843</v>
+        <v>1.7842</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40100,7 +40100,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9244</v>
+        <v>0.9243</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5591</v>
+        <v>1.559</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40134,7 +40134,7 @@
         <v>1.2144</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9181</v>
+        <v>0.918</v>
       </c>
       <c r="F238" t="n">
         <v>1.2144</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.545</v>
+        <v>1.5449</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40168,7 +40168,7 @@
         <v>1.1455</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9636</v>
+        <v>0.9635</v>
       </c>
       <c r="F239" t="n">
         <v>1.1455</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7085</v>
+        <v>1.7083</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7846</v>
+        <v>1.7844</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0246</v>
+        <v>1.0245</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8039</v>
+        <v>1.8038</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40270,7 +40270,7 @@
         <v>1.4347</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9349</v>
+        <v>0.9348</v>
       </c>
       <c r="F242" t="n">
         <v>1.4347</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8768</v>
+        <v>1.8766</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8105</v>
+        <v>1.8103</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7649</v>
+        <v>1.7648</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40372,7 +40372,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8575</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6399</v>
+        <v>1.6398</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40406,7 +40406,7 @@
         <v>1.5797</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8887</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="F246" t="n">
         <v>1.5797</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7356</v>
+        <v>1.7355</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40431,7 +40431,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.971</v>
+        <v>0.9709</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40440,7 +40440,7 @@
         <v>1.4541</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8502</v>
+        <v>0.8501</v>
       </c>
       <c r="F247" t="n">
         <v>1.4541</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7651</v>
+        <v>1.765</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40465,7 +40465,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9417</v>
+        <v>0.9416</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8806</v>
+        <v>1.8805</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9474</v>
+        <v>1.9473</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40533,7 +40533,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9395</v>
+        <v>0.9394</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0133</v>
+        <v>2.0132</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40567,7 +40567,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9809</v>
+        <v>0.9808</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40576,7 +40576,7 @@
         <v>1.2358</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9172</v>
+        <v>0.9171</v>
       </c>
       <c r="F251" t="n">
         <v>1.2358</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1879</v>
+        <v>2.1876</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40601,7 +40601,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.987</v>
+        <v>0.9869</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40610,7 +40610,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9312</v>
+        <v>0.9311</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3145</v>
+        <v>2.3142</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40635,7 +40635,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.748</v>
+        <v>0.7479</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40644,7 +40644,7 @@
         <v>0.0338</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9265</v>
+        <v>0.9264</v>
       </c>
       <c r="F253" t="n">
         <v>0.0338</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3395</v>
+        <v>2.3393</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40678,7 +40678,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9349</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4457</v>
+        <v>2.4455</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8385</v>
+        <v>0.8384</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40712,7 +40712,7 @@
         <v>0.4427</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9374</v>
+        <v>0.9373</v>
       </c>
       <c r="F255" t="n">
         <v>0.4427</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5228</v>
+        <v>2.5225</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5461</v>
+        <v>2.5458</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40771,7 +40771,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7467</v>
+        <v>0.7466</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40780,7 +40780,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8529</v>
+        <v>0.8528</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6726</v>
+        <v>2.6723</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7881</v>
+        <v>0.788</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8226</v>
+        <v>2.8222</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40848,7 +40848,7 @@
         <v>0.3242</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9489</v>
+        <v>0.9488</v>
       </c>
       <c r="F259" t="n">
         <v>0.3242</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0136</v>
+        <v>3.0132</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9462</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9462</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.003</v>
+        <v>3.0027</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9453</v>
+        <v>0.9466</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9453</v>
+        <v>0.9466</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9993</v>
+        <v>3.0046</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>0.984</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="224">
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.347</v>
+        <v>1.356</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.605</v>
+        <v>1.614</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.101</v>
+        <v>2.108</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.832</v>
+        <v>2.84</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.97</v>
+        <v>3.978</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.632</v>
+        <v>-0.623</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.09</v>
+        <v>-0.082</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.033</v>
+        <v>1.042</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.28</v>
+        <v>-1.29</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66603.976</v>
+        <v>66681.863</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3472</v>
+        <v>1.3564</v>
       </c>
       <c r="D261" t="n">
-        <v>1.6052</v>
+        <v>1.6143</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1006</v>
+        <v>2.1082</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8316</v>
+        <v>2.8403</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9702</v>
+        <v>3.9782</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6321</v>
+        <v>-0.6229</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.0902</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0328</v>
+        <v>1.0415</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66603.976</v>
+        <v>66681.8627</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32156,7 +32156,7 @@
         <v>-0.3209</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5899</v>
+        <v>-0.5898</v>
       </c>
       <c r="J3" t="n">
         <v>-1.6403</v>
@@ -32212,7 +32212,7 @@
         <v>0.2212</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7275</v>
+        <v>-0.7274</v>
       </c>
       <c r="F5" t="n">
         <v>0.2212</v>
@@ -33640,7 +33640,7 @@
         <v>0.7934</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.9167</v>
+        <v>-0.9166</v>
       </c>
       <c r="F47" t="n">
         <v>0.7934</v>
@@ -33754,7 +33754,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0991</v>
+        <v>-1.099</v>
       </c>
       <c r="J50" t="n">
         <v>0.7647</v>
@@ -33822,7 +33822,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0188</v>
+        <v>-1.0187</v>
       </c>
       <c r="J52" t="n">
         <v>0.4738</v>
@@ -33844,7 +33844,7 @@
         <v>0.0622</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2334</v>
+        <v>-1.2333</v>
       </c>
       <c r="F53" t="n">
         <v>0.0622</v>
@@ -33856,7 +33856,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.9923</v>
       </c>
       <c r="J53" t="n">
         <v>0.1904</v>
@@ -33890,7 +33890,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0183</v>
+        <v>-1.0182</v>
       </c>
       <c r="J54" t="n">
         <v>0.1077</v>
@@ -33980,7 +33980,7 @@
         <v>-0.8924</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.3985</v>
+        <v>-1.3984</v>
       </c>
       <c r="F57" t="n">
         <v>-0.8924</v>
@@ -34026,7 +34026,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0887</v>
+        <v>-1.0886</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5775</v>
@@ -34230,7 +34230,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0724</v>
+        <v>-1.0723</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6947</v>
@@ -34286,7 +34286,7 @@
         <v>-0.2077</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.4312</v>
+        <v>-1.4311</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2077</v>
@@ -34298,7 +34298,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0728</v>
+        <v>-1.0727</v>
       </c>
       <c r="J66" t="n">
         <v>-1.966</v>
@@ -34320,7 +34320,7 @@
         <v>-0.1867</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.384</v>
+        <v>-1.3839</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1867</v>
@@ -34774,7 +34774,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2712</v>
+        <v>-1.2711</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5145</v>
@@ -35080,7 +35080,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2362</v>
+        <v>-1.2361</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0901</v>
@@ -35136,7 +35136,7 @@
         <v>0.1763</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.65</v>
+        <v>-0.6499</v>
       </c>
       <c r="F91" t="n">
         <v>0.1763</v>
@@ -35216,7 +35216,7 @@
         <v>-0.389</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2934</v>
+        <v>-1.2933</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8172</v>
@@ -35318,7 +35318,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2589</v>
+        <v>-1.2588</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5867</v>
@@ -37686,7 +37686,7 @@
         <v>0.8033</v>
       </c>
       <c r="E166" t="n">
-        <v>0.7292</v>
+        <v>0.7291</v>
       </c>
       <c r="F166" t="n">
         <v>0.8033</v>
@@ -37970,7 +37970,7 @@
         <v>0.9549</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.0881</v>
       </c>
       <c r="J174" t="n">
         <v>1.6763</v>
@@ -38085,7 +38085,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.6802</v>
+        <v>0.6801</v>
       </c>
       <c r="C178" t="n">
         <v>0.6659</v>
@@ -38128,7 +38128,7 @@
         <v>0.6657</v>
       </c>
       <c r="E179" t="n">
-        <v>0.6947</v>
+        <v>0.6946</v>
       </c>
       <c r="F179" t="n">
         <v>0.6657</v>
@@ -38242,7 +38242,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1853</v>
+        <v>-0.1854</v>
       </c>
       <c r="J182" t="n">
         <v>2.0493</v>
@@ -38412,7 +38412,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1968</v>
+        <v>-0.1969</v>
       </c>
       <c r="J187" t="n">
         <v>2.2688</v>
@@ -39024,7 +39024,7 @@
         <v>0.2135</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4365</v>
+        <v>0.4364</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3874</v>
@@ -39046,7 +39046,7 @@
         <v>0.5263</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2913</v>
+        <v>0.2912</v>
       </c>
       <c r="F206" t="n">
         <v>0.5263</v>
@@ -39114,7 +39114,7 @@
         <v>0.7245</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3455</v>
+        <v>0.3454</v>
       </c>
       <c r="F208" t="n">
         <v>0.7245</v>
@@ -39250,7 +39250,7 @@
         <v>1.4354</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5084</v>
+        <v>0.5083</v>
       </c>
       <c r="F212" t="n">
         <v>1.4354</v>
@@ -39534,7 +39534,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8018</v>
+        <v>0.8017</v>
       </c>
       <c r="J220" t="n">
         <v>0.2685</v>
@@ -39602,7 +39602,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9201</v>
+        <v>0.92</v>
       </c>
       <c r="J222" t="n">
         <v>0.249</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1514</v>
+        <v>1.1513</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3216</v>
+        <v>1.3215</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.25</v>
+        <v>1.2499</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5579</v>
+        <v>1.5578</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6667</v>
+        <v>1.6666</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40023,7 +40023,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.088</v>
+        <v>1.0879</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7842</v>
+        <v>1.7841</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40091,7 +40091,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0236</v>
+        <v>1.0235</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.559</v>
+        <v>1.5589</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40202,7 +40202,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.96</v>
+        <v>0.9599</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8038</v>
+        <v>1.8037</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40295,7 +40295,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9863</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6398</v>
+        <v>1.6397</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40397,7 +40397,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0269</v>
+        <v>1.0268</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7355</v>
+        <v>1.7354</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.765</v>
+        <v>1.7649</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8805</v>
+        <v>1.8804</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9473</v>
+        <v>1.9472</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0132</v>
+        <v>2.0131</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3393</v>
+        <v>2.3392</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40669,7 +40669,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8769</v>
+        <v>0.8768</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4455</v>
+        <v>2.4454</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5225</v>
+        <v>2.5224</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5458</v>
+        <v>2.5457</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6723</v>
+        <v>2.6722</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40814,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9117</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8239</v>
+        <v>0.8238</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0132</v>
+        <v>3.0131</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0027</v>
+        <v>3.0026</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9466</v>
+        <v>0.947</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9466</v>
+        <v>0.947</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.0046</v>
+        <v>3.006</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>0.983</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="224">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.947</v>
+        <v>0.946</v>
       </c>
     </row>
   </sheetData>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.356</v>
+        <v>1.363</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.614</v>
+        <v>1.621</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.108</v>
+        <v>2.114</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.84</v>
+        <v>2.849</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.978</v>
+        <v>3.989</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.623</v>
+        <v>-0.616</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.082</v>
+        <v>-0.075</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.73</v>
+        <v>-0.75</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.042</v>
+        <v>1.05</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.29</v>
+        <v>-1.3</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66681.863</v>
+        <v>66568.909</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3564</v>
+        <v>1.3632</v>
       </c>
       <c r="D261" t="n">
-        <v>1.6143</v>
+        <v>1.6213</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1082</v>
+        <v>2.1145</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8403</v>
+        <v>2.8488</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9782</v>
+        <v>3.9889</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6229</v>
+        <v>-0.6161</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0415</v>
+        <v>1.05</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66681.8627</v>
+        <v>66568.90919999999</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32128,7 +32128,7 @@
         <v>-0.3431</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6429</v>
+        <v>-0.643</v>
       </c>
       <c r="J2" t="n">
         <v>-1.7186</v>
@@ -32156,7 +32156,7 @@
         <v>-0.3209</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5898</v>
+        <v>-0.5899</v>
       </c>
       <c r="J3" t="n">
         <v>-1.6403</v>
@@ -32212,7 +32212,7 @@
         <v>0.2212</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7274</v>
+        <v>-0.7275</v>
       </c>
       <c r="F5" t="n">
         <v>0.2212</v>
@@ -32586,7 +32586,7 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5639</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="F16" t="n">
         <v>0.09089999999999999</v>
@@ -33640,7 +33640,7 @@
         <v>0.7934</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.9166</v>
+        <v>-0.9167</v>
       </c>
       <c r="F47" t="n">
         <v>0.7934</v>
@@ -33720,7 +33720,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0526</v>
+        <v>-1.0527</v>
       </c>
       <c r="J49" t="n">
         <v>0.983</v>
@@ -33754,7 +33754,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.099</v>
+        <v>-1.0991</v>
       </c>
       <c r="J50" t="n">
         <v>0.7647</v>
@@ -33822,7 +33822,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0187</v>
+        <v>-1.0188</v>
       </c>
       <c r="J52" t="n">
         <v>0.4738</v>
@@ -33835,7 +33835,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9742</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="C53" t="n">
         <v>0.6286</v>
@@ -33844,7 +33844,7 @@
         <v>0.0622</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2333</v>
+        <v>-1.2334</v>
       </c>
       <c r="F53" t="n">
         <v>0.0622</v>
@@ -33856,7 +33856,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9923</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0.1904</v>
@@ -33890,7 +33890,7 @@
         <v>-2.7137</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0182</v>
+        <v>-1.0183</v>
       </c>
       <c r="J54" t="n">
         <v>0.1077</v>
@@ -33980,7 +33980,7 @@
         <v>-0.8924</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.3984</v>
+        <v>-1.3985</v>
       </c>
       <c r="F57" t="n">
         <v>-0.8924</v>
@@ -34026,7 +34026,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0886</v>
+        <v>-1.0887</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5775</v>
@@ -34218,7 +34218,7 @@
         <v>-0.2615</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3881</v>
+        <v>-1.3882</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2615</v>
@@ -34230,7 +34230,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0723</v>
+        <v>-1.0724</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6947</v>
@@ -34286,7 +34286,7 @@
         <v>-0.2077</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.4311</v>
+        <v>-1.4312</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2077</v>
@@ -34298,7 +34298,7 @@
         <v>-2.1205</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0727</v>
+        <v>-1.0728</v>
       </c>
       <c r="J66" t="n">
         <v>-1.966</v>
@@ -34320,7 +34320,7 @@
         <v>-0.1867</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.3839</v>
+        <v>-1.384</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1867</v>
@@ -34502,7 +34502,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2335</v>
+        <v>-1.2336</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8944</v>
@@ -34774,7 +34774,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2711</v>
+        <v>-1.2712</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5145</v>
@@ -35080,7 +35080,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2361</v>
+        <v>-1.2362</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0901</v>
@@ -35136,7 +35136,7 @@
         <v>0.1763</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6499</v>
+        <v>-0.65</v>
       </c>
       <c r="F91" t="n">
         <v>0.1763</v>
@@ -35216,7 +35216,7 @@
         <v>-0.389</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2933</v>
+        <v>-1.2934</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8172</v>
@@ -35318,7 +35318,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2588</v>
+        <v>-1.2589</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5867</v>
@@ -35352,7 +35352,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.195</v>
+        <v>-1.1951</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5657</v>
@@ -35896,7 +35896,7 @@
         <v>0.1698</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5474</v>
+        <v>-0.5475</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2356</v>
@@ -37133,7 +37133,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.554</v>
+        <v>0.5541</v>
       </c>
       <c r="C150" t="n">
         <v>0.2745</v>
@@ -37686,7 +37686,7 @@
         <v>0.8033</v>
       </c>
       <c r="E166" t="n">
-        <v>0.7291</v>
+        <v>0.7292</v>
       </c>
       <c r="F166" t="n">
         <v>0.8033</v>
@@ -37970,7 +37970,7 @@
         <v>0.9549</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0881</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="J174" t="n">
         <v>1.6763</v>
@@ -38085,7 +38085,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.6801</v>
+        <v>0.6802</v>
       </c>
       <c r="C178" t="n">
         <v>0.6659</v>
@@ -38128,7 +38128,7 @@
         <v>0.6657</v>
       </c>
       <c r="E179" t="n">
-        <v>0.6946</v>
+        <v>0.6947</v>
       </c>
       <c r="F179" t="n">
         <v>0.6657</v>
@@ -38174,7 +38174,7 @@
         <v>0.451</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1655</v>
+        <v>-0.1654</v>
       </c>
       <c r="J180" t="n">
         <v>1.9108</v>
@@ -38242,7 +38242,7 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1854</v>
+        <v>-0.1853</v>
       </c>
       <c r="J182" t="n">
         <v>2.0493</v>
@@ -38412,7 +38412,7 @@
         <v>-0.8525</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1969</v>
+        <v>-0.1968</v>
       </c>
       <c r="J187" t="n">
         <v>2.2688</v>
@@ -38536,7 +38536,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2772</v>
+        <v>0.2773</v>
       </c>
       <c r="F191" t="n">
         <v>0.08309999999999999</v>
@@ -38944,7 +38944,7 @@
         <v>0.5004999999999999</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1642</v>
+        <v>0.1643</v>
       </c>
       <c r="F203" t="n">
         <v>0.5004999999999999</v>
@@ -39024,7 +39024,7 @@
         <v>0.2135</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4364</v>
+        <v>0.4365</v>
       </c>
       <c r="J205" t="n">
         <v>-0.3874</v>
@@ -39046,7 +39046,7 @@
         <v>0.5263</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2912</v>
+        <v>0.2913</v>
       </c>
       <c r="F206" t="n">
         <v>0.5263</v>
@@ -39114,7 +39114,7 @@
         <v>0.7245</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3454</v>
+        <v>0.3455</v>
       </c>
       <c r="F208" t="n">
         <v>0.7245</v>
@@ -39250,7 +39250,7 @@
         <v>1.4354</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5083</v>
+        <v>0.5084</v>
       </c>
       <c r="F212" t="n">
         <v>1.4354</v>
@@ -39432,7 +39432,7 @@
         <v>0.6974</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7983</v>
+        <v>0.7984</v>
       </c>
       <c r="J217" t="n">
         <v>0.1675</v>
@@ -39534,7 +39534,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8017</v>
+        <v>0.8018</v>
       </c>
       <c r="J220" t="n">
         <v>0.2685</v>
@@ -39602,7 +39602,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>0.92</v>
+        <v>0.9201</v>
       </c>
       <c r="J222" t="n">
         <v>0.249</v>
@@ -39704,7 +39704,7 @@
         <v>0.8441</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1513</v>
+        <v>1.1514</v>
       </c>
       <c r="J225" t="n">
         <v>0.3944</v>
@@ -39726,7 +39726,7 @@
         <v>1.477</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8516</v>
+        <v>0.8517</v>
       </c>
       <c r="F226" t="n">
         <v>1.477</v>
@@ -39794,7 +39794,7 @@
         <v>1.3813</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8608</v>
+        <v>0.8609</v>
       </c>
       <c r="F228" t="n">
         <v>1.3813</v>
@@ -39806,7 +39806,7 @@
         <v>0.9485</v>
       </c>
       <c r="I228" t="n">
-        <v>1.3215</v>
+        <v>1.3216</v>
       </c>
       <c r="J228" t="n">
         <v>0.3582</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2499</v>
+        <v>1.25</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5578</v>
+        <v>1.5579</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6666</v>
+        <v>1.6667</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40023,7 +40023,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.0879</v>
+        <v>1.088</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7841</v>
+        <v>1.7842</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40091,7 +40091,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0235</v>
+        <v>1.0236</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -40100,7 +40100,7 @@
         <v>1.4204</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9243</v>
+        <v>0.9244</v>
       </c>
       <c r="F237" t="n">
         <v>1.4204</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5589</v>
+        <v>1.559</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40202,7 +40202,7 @@
         <v>1.252</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9599</v>
+        <v>0.96</v>
       </c>
       <c r="F240" t="n">
         <v>1.252</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8037</v>
+        <v>1.8038</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40295,7 +40295,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9863</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6397</v>
+        <v>1.6398</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40397,7 +40397,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0268</v>
+        <v>1.0269</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7354</v>
+        <v>1.7355</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7649</v>
+        <v>1.765</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40465,7 +40465,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9416</v>
+        <v>0.9417</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8804</v>
+        <v>1.8805</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9472</v>
+        <v>1.9473</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0131</v>
+        <v>2.0132</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40567,7 +40567,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9808</v>
+        <v>0.9809</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1876</v>
+        <v>2.1877</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40610,7 +40610,7 @@
         <v>1.21</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9311</v>
+        <v>0.9312</v>
       </c>
       <c r="F252" t="n">
         <v>1.21</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3142</v>
+        <v>2.3143</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3392</v>
+        <v>2.3393</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40669,7 +40669,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8768</v>
+        <v>0.8769</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4454</v>
+        <v>2.4455</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5224</v>
+        <v>2.5225</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5457</v>
+        <v>2.5458</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6722</v>
+        <v>2.6723</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40805,7 +40805,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.788</v>
+        <v>0.7881</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40814,7 +40814,7 @@
         <v>0.2932</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9117</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="F258" t="n">
         <v>0.2932</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8222</v>
+        <v>2.8223</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8238</v>
+        <v>0.8239</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0131</v>
+        <v>3.0133</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40873,13 +40873,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9462</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9462</v>
       </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0026</v>
+        <v>3.0027</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.947</v>
+        <v>0.9465</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.947</v>
+        <v>0.9465</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.006</v>
+        <v>3.0039</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.363</v>
+        <v>1.368</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.621</v>
+        <v>1.626</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.114</v>
+        <v>2.117</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.849</v>
+        <v>2.853</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.989</v>
+        <v>3.994</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.616</v>
+        <v>-0.611</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.075</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.05</v>
+        <v>1.054</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.3</v>
+        <v>-1.31</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66568.909</v>
+        <v>66541.823</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3632</v>
+        <v>1.3682</v>
       </c>
       <c r="D261" t="n">
-        <v>1.6213</v>
+        <v>1.6262</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1145</v>
+        <v>2.1171</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8488</v>
+        <v>2.8526</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9889</v>
+        <v>3.9943</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6161</v>
+        <v>-0.6111</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.0706</v>
       </c>
       <c r="M261" t="n">
-        <v>1.05</v>
+        <v>1.0538</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66568.90919999999</v>
+        <v>66541.82309999999</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -33572,7 +33572,7 @@
         <v>1.038</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.7715</v>
+        <v>-0.7716</v>
       </c>
       <c r="F45" t="n">
         <v>1.038</v>
@@ -33652,7 +33652,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8515</v>
+        <v>-0.8516</v>
       </c>
       <c r="J47" t="n">
         <v>0.741</v>
@@ -34107,7 +34107,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.1936</v>
+        <v>-1.1937</v>
       </c>
       <c r="C61" t="n">
         <v>0.8397</v>
@@ -34332,7 +34332,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.094</v>
+        <v>-1.0941</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1347</v>
@@ -34876,7 +34876,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3304</v>
+        <v>-1.3305</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3601</v>
@@ -35204,7 +35204,7 @@
         <v>0.1767</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6244</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="F93" t="n">
         <v>0.1767</v>
@@ -35408,7 +35408,7 @@
         <v>0.1595</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.3744</v>
+        <v>-0.3745</v>
       </c>
       <c r="F99" t="n">
         <v>0.1595</v>
@@ -38616,7 +38616,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0139</v>
+        <v>-0.0138</v>
       </c>
       <c r="J193" t="n">
         <v>0.855</v>
@@ -38854,7 +38854,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I200" t="n">
-        <v>0.286</v>
+        <v>0.2861</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6202</v>
@@ -38888,7 +38888,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2995</v>
+        <v>0.2996</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6014</v>
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5598</v>
+        <v>0.5599</v>
       </c>
       <c r="C205" t="n">
         <v>-0.4359</v>
@@ -39284,7 +39284,7 @@
         <v>1.5657</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5284</v>
+        <v>0.5285</v>
       </c>
       <c r="F213" t="n">
         <v>1.5657</v>
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0245</v>
+        <v>1.0246</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40282,7 +40282,7 @@
         <v>1.1114</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8766</v>
+        <v>1.8767</v>
       </c>
       <c r="J242" t="n">
         <v>0.6047</v>
@@ -40372,7 +40372,7 @@
         <v>1.5761</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8575</v>
       </c>
       <c r="F245" t="n">
         <v>1.5761</v>
@@ -40678,7 +40678,7 @@
         <v>0.6445</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9349</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F254" t="n">
         <v>0.6445</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5225</v>
+        <v>2.5226</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5458</v>
+        <v>2.5459</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40780,7 +40780,7 @@
         <v>0.3218</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8528</v>
+        <v>0.8529</v>
       </c>
       <c r="F257" t="n">
         <v>0.3218</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6723</v>
+        <v>2.6724</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40888,7 +40888,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0027</v>
+        <v>3.0028</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40901,13 +40901,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9465</v>
+        <v>0.9463</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9465</v>
+        <v>0.9463</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40916,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.0039</v>
+        <v>3.0035</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-0.544</v>
+        <v>-0.545</v>
       </c>
     </row>
     <row r="8">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-0.512</v>
+        <v>-0.513</v>
       </c>
     </row>
     <row r="9">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-0.457</v>
+        <v>-0.458</v>
       </c>
     </row>
     <row r="16">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-0.367</v>
+        <v>-0.368</v>
       </c>
     </row>
     <row r="23">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>-0.365</v>
+        <v>-0.366</v>
       </c>
     </row>
     <row r="32">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>-0.522</v>
+        <v>-0.523</v>
       </c>
     </row>
     <row r="42">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>-0.832</v>
+        <v>-0.833</v>
       </c>
     </row>
     <row r="52">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>-1.246</v>
+        <v>-1.247</v>
       </c>
     </row>
     <row r="57">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>-1.297</v>
+        <v>-1.298</v>
       </c>
     </row>
     <row r="58">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>-1.246</v>
+        <v>-1.247</v>
       </c>
     </row>
     <row r="59">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>-1.186</v>
+        <v>-1.187</v>
       </c>
     </row>
     <row r="67">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.9419999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>-0.62</v>
+        <v>-0.621</v>
       </c>
     </row>
     <row r="86">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>-0.037</v>
+        <v>-0.038</v>
       </c>
     </row>
     <row r="106">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="116">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>0.406</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="121">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.946</v>
+        <v>0.839</v>
       </c>
     </row>
     <row r="261">
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.368</v>
+        <v>1.373</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.626</v>
+        <v>1.631</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.117</v>
+        <v>2.118</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.611</v>
+        <v>-0.606</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.068</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66541.823</v>
+        <v>66504.28999999999</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31862,13 +31862,13 @@
         <v>-0.9792999999999999</v>
       </c>
       <c r="O260" t="n">
-        <v>-0.3755</v>
+        <v>-0.5886</v>
       </c>
       <c r="P260" t="n">
-        <v>0.0606</v>
+        <v>-0.1589</v>
       </c>
       <c r="Q260" t="n">
-        <v>1.144</v>
+        <v>0.9812</v>
       </c>
       <c r="R260" t="n">
         <v>1.1708</v>
@@ -31907,7 +31907,7 @@
         <v>6.362</v>
       </c>
       <c r="AD260" t="n">
-        <v>1.526</v>
+        <v>1.7921</v>
       </c>
       <c r="AE260" t="n">
         <v>0.7099</v>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3682</v>
+        <v>1.3729</v>
       </c>
       <c r="D261" t="n">
-        <v>1.6262</v>
+        <v>1.6305</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1171</v>
+        <v>2.1178</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8526</v>
+        <v>2.8527</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9943</v>
+        <v>3.9944</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,25 +31956,25 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6111</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.0706</v>
+        <v>-0.0675</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0538</v>
+        <v>1.0539</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
       </c>
       <c r="O261" t="n">
-        <v>-0.3755</v>
+        <v>-0.5886</v>
       </c>
       <c r="P261" t="n">
-        <v>0.0606</v>
+        <v>-0.1589</v>
       </c>
       <c r="Q261" t="n">
-        <v>1.144</v>
+        <v>0.9812</v>
       </c>
       <c r="R261" t="n">
         <v>1.1708</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66541.82309999999</v>
+        <v>66504.28999999999</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32013,7 +32013,7 @@
         <v>6.362</v>
       </c>
       <c r="AD261" t="n">
-        <v>1.526</v>
+        <v>1.7921</v>
       </c>
       <c r="AE261" t="n">
         <v>0.7099</v>
@@ -32113,16 +32113,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6118</v>
+        <v>-0.612</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2573</v>
+        <v>0.2568</v>
       </c>
       <c r="E2" t="n">
         <v>-0.9016</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2573</v>
+        <v>0.2568</v>
       </c>
       <c r="G2" t="n">
         <v>-0.3431</v>
@@ -32141,16 +32141,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.6108</v>
+        <v>-0.6109</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1079</v>
+        <v>0.1073</v>
       </c>
       <c r="E3" t="n">
         <v>-0.8504</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1079</v>
+        <v>0.1073</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3209</v>
@@ -32169,19 +32169,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.5671</v>
+        <v>-0.5672</v>
       </c>
       <c r="C4" t="n">
         <v>-0.068</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1593</v>
+        <v>0.1587</v>
       </c>
       <c r="E4" t="n">
         <v>-0.7487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1593</v>
+        <v>0.1587</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4022</v>
@@ -32203,19 +32203,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5377</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="C5" t="n">
         <v>-0.0692</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2212</v>
+        <v>0.2207</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7275</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2212</v>
+        <v>0.2207</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4721</v>
@@ -32237,19 +32237,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5097</v>
+        <v>-0.5098</v>
       </c>
       <c r="C6" t="n">
         <v>-0.0915</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2701</v>
+        <v>0.2696</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7047</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2701</v>
+        <v>0.2696</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4851</v>
@@ -32271,19 +32271,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.5445</v>
+        <v>-0.5446</v>
       </c>
       <c r="C7" t="n">
         <v>-0.1131</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1468</v>
+        <v>0.1462</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7173</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1468</v>
+        <v>0.1462</v>
       </c>
       <c r="G7" t="n">
         <v>-0.526</v>
@@ -32305,19 +32305,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.5125</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2175</v>
       </c>
       <c r="D8" t="n">
-        <v>0.129</v>
+        <v>0.1284</v>
       </c>
       <c r="E8" t="n">
         <v>-0.6728</v>
       </c>
       <c r="F8" t="n">
-        <v>0.129</v>
+        <v>0.1284</v>
       </c>
       <c r="G8" t="n">
         <v>-0.578</v>
@@ -32339,19 +32339,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5392</v>
+        <v>-0.5394</v>
       </c>
       <c r="C9" t="n">
         <v>-0.2486</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1057</v>
+        <v>0.105</v>
       </c>
       <c r="E9" t="n">
         <v>-0.7004</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1057</v>
+        <v>0.105</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6535</v>
@@ -32373,19 +32373,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.4897</v>
+        <v>-0.4899</v>
       </c>
       <c r="C10" t="n">
         <v>-0.2832</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0931</v>
+        <v>0.0924</v>
       </c>
       <c r="E10" t="n">
         <v>-0.6354</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0931</v>
+        <v>0.0924</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6862</v>
@@ -32407,19 +32407,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.4982</v>
+        <v>-0.4983</v>
       </c>
       <c r="C11" t="n">
         <v>-0.3532</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1045</v>
+        <v>0.1039</v>
       </c>
       <c r="E11" t="n">
         <v>-0.6489</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1045</v>
+        <v>0.1039</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7873</v>
@@ -32441,19 +32441,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.472</v>
+        <v>-0.4721</v>
       </c>
       <c r="C12" t="n">
         <v>-0.3965</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1016</v>
+        <v>0.101</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6153999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1016</v>
+        <v>0.101</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8257</v>
@@ -32475,19 +32475,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.4652</v>
+        <v>-0.4653</v>
       </c>
       <c r="C13" t="n">
         <v>-0.3974</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1014</v>
+        <v>0.1008</v>
       </c>
       <c r="E13" t="n">
         <v>-0.6069</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1014</v>
+        <v>0.1008</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8617</v>
@@ -32509,19 +32509,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4701</v>
+        <v>-0.4702</v>
       </c>
       <c r="C14" t="n">
         <v>-0.3666</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0974</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>-0.612</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0974</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8984</v>
@@ -32543,19 +32543,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.4574</v>
+        <v>-0.4575</v>
       </c>
       <c r="C15" t="n">
         <v>-0.4095</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1065</v>
+        <v>0.1058</v>
       </c>
       <c r="E15" t="n">
         <v>-0.5984</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1065</v>
+        <v>0.1058</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9283</v>
@@ -32577,19 +32577,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.433</v>
+        <v>-0.4331</v>
       </c>
       <c r="C16" t="n">
         <v>-0.4508</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0902</v>
       </c>
       <c r="E16" t="n">
         <v>-0.5639999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0902</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9726</v>
@@ -32598,7 +32598,7 @@
         <v>-0.1031</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1547</v>
+        <v>-0.1548</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0253</v>
@@ -32611,19 +32611,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.4599</v>
+        <v>-0.4601</v>
       </c>
       <c r="C17" t="n">
         <v>-0.4753</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0533</v>
+        <v>-0.0541</v>
       </c>
       <c r="E17" t="n">
         <v>-0.5616</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0533</v>
+        <v>-0.0541</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9911</v>
@@ -32645,19 +32645,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.477</v>
+        <v>-0.4771</v>
       </c>
       <c r="C18" t="n">
         <v>-0.5001</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0302</v>
+        <v>-0.031</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5887</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0302</v>
+        <v>-0.031</v>
       </c>
       <c r="G18" t="n">
         <v>-1.05</v>
@@ -32679,19 +32679,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.4437</v>
+        <v>-0.4438</v>
       </c>
       <c r="C19" t="n">
         <v>-0.4789</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0366</v>
+        <v>0.0359</v>
       </c>
       <c r="E19" t="n">
         <v>-0.5637</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0366</v>
+        <v>0.0359</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0982</v>
@@ -32713,19 +32713,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.4472</v>
+        <v>-0.4473</v>
       </c>
       <c r="C20" t="n">
         <v>-0.2827</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0143</v>
+        <v>0.0136</v>
       </c>
       <c r="E20" t="n">
         <v>-0.5626</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0143</v>
+        <v>0.0136</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1656</v>
@@ -32747,19 +32747,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.4207</v>
+        <v>-0.4208</v>
       </c>
       <c r="C21" t="n">
         <v>-0.3155</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1095</v>
+        <v>0.1089</v>
       </c>
       <c r="E21" t="n">
         <v>-0.5533</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1095</v>
+        <v>0.1089</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2126</v>
@@ -32781,19 +32781,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3674</v>
+        <v>-0.3675</v>
       </c>
       <c r="C22" t="n">
         <v>-0.2635</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1099</v>
+        <v>0.1092</v>
       </c>
       <c r="E22" t="n">
         <v>-0.4867</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1099</v>
+        <v>0.1092</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2012</v>
@@ -32815,19 +32815,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3946</v>
+        <v>-0.3948</v>
       </c>
       <c r="C23" t="n">
         <v>-0.3</v>
       </c>
       <c r="D23" t="n">
-        <v>0.025</v>
+        <v>0.0243</v>
       </c>
       <c r="E23" t="n">
         <v>-0.4995</v>
       </c>
       <c r="F23" t="n">
-        <v>0.025</v>
+        <v>0.0243</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3285</v>
@@ -32849,19 +32849,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3605</v>
+        <v>-0.3606</v>
       </c>
       <c r="C24" t="n">
         <v>-0.3018</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0534</v>
+        <v>0.0527</v>
       </c>
       <c r="E24" t="n">
         <v>-0.464</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0534</v>
+        <v>0.0527</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3351</v>
@@ -32883,19 +32883,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3349</v>
+        <v>-0.335</v>
       </c>
       <c r="C25" t="n">
         <v>-0.2463</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0989</v>
+        <v>0.0983</v>
       </c>
       <c r="E25" t="n">
         <v>-0.4434</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0989</v>
+        <v>0.0983</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3858</v>
@@ -32917,19 +32917,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3483</v>
+        <v>-0.3484</v>
       </c>
       <c r="C26" t="n">
         <v>-0.3078</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0379</v>
+        <v>-0.0387</v>
       </c>
       <c r="E26" t="n">
         <v>-0.4259</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0379</v>
+        <v>-0.0387</v>
       </c>
       <c r="G26" t="n">
         <v>-1.4234</v>
@@ -32951,19 +32951,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3797</v>
+        <v>-0.3798</v>
       </c>
       <c r="C27" t="n">
         <v>-0.0248</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0766</v>
+        <v>-0.0774</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4554</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0766</v>
+        <v>-0.0774</v>
       </c>
       <c r="G27" t="n">
         <v>-1.5141</v>
@@ -32985,19 +32985,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4021</v>
+        <v>-0.4023</v>
       </c>
       <c r="C28" t="n">
         <v>0.0306</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1706</v>
+        <v>-0.1715</v>
       </c>
       <c r="E28" t="n">
         <v>-0.46</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1706</v>
+        <v>-0.1715</v>
       </c>
       <c r="G28" t="n">
         <v>-1.5664</v>
@@ -33019,19 +33019,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3925</v>
+        <v>-0.3927</v>
       </c>
       <c r="C29" t="n">
         <v>-0.0319</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0893</v>
+        <v>-0.0901</v>
       </c>
       <c r="E29" t="n">
         <v>-0.4683</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0893</v>
+        <v>-0.0901</v>
       </c>
       <c r="G29" t="n">
         <v>-1.612</v>
@@ -33053,19 +33053,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3792</v>
+        <v>-0.3794</v>
       </c>
       <c r="C30" t="n">
         <v>-0.0653</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1156</v>
+        <v>-0.1164</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4451</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1156</v>
+        <v>-0.1164</v>
       </c>
       <c r="G30" t="n">
         <v>-1.6744</v>
@@ -33087,19 +33087,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3654</v>
+        <v>-0.3656</v>
       </c>
       <c r="C31" t="n">
         <v>-0.08649999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1808</v>
+        <v>-0.1817</v>
       </c>
       <c r="E31" t="n">
         <v>-0.4116</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1808</v>
+        <v>-0.1817</v>
       </c>
       <c r="G31" t="n">
         <v>-1.6854</v>
@@ -33121,19 +33121,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3536</v>
+        <v>-0.3537</v>
       </c>
       <c r="C32" t="n">
         <v>-0.0707</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1734</v>
+        <v>-0.1743</v>
       </c>
       <c r="E32" t="n">
         <v>-0.3986</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1734</v>
+        <v>-0.1743</v>
       </c>
       <c r="G32" t="n">
         <v>-1.6954</v>
@@ -33155,19 +33155,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.359</v>
+        <v>-0.3592</v>
       </c>
       <c r="C33" t="n">
         <v>-0.1744</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1085</v>
+        <v>-0.1093</v>
       </c>
       <c r="E33" t="n">
         <v>-0.4216</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1085</v>
+        <v>-0.1093</v>
       </c>
       <c r="G33" t="n">
         <v>-1.7027</v>
@@ -33189,19 +33189,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.432</v>
+        <v>-0.4321</v>
       </c>
       <c r="C34" t="n">
         <v>-0.1655</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0979</v>
       </c>
       <c r="E34" t="n">
         <v>-0.5157</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0979</v>
       </c>
       <c r="G34" t="n">
         <v>-1.7114</v>
@@ -33223,19 +33223,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4155</v>
+        <v>-0.4157</v>
       </c>
       <c r="C35" t="n">
         <v>-0.1623</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0015</v>
+        <v>-0.0022</v>
       </c>
       <c r="E35" t="n">
         <v>-0.5191</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0015</v>
+        <v>-0.0022</v>
       </c>
       <c r="G35" t="n">
         <v>-1.7778</v>
@@ -33257,19 +33257,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.391</v>
+        <v>-0.3912</v>
       </c>
       <c r="C36" t="n">
         <v>-0.244</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1664</v>
+        <v>0.1658</v>
       </c>
       <c r="E36" t="n">
         <v>-0.5304</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1664</v>
+        <v>0.1658</v>
       </c>
       <c r="G36" t="n">
         <v>-1.7316</v>
@@ -33291,19 +33291,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.3857</v>
+        <v>-0.3858</v>
       </c>
       <c r="C37" t="n">
         <v>-0.1966</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4873</v>
+        <v>0.487</v>
       </c>
       <c r="E37" t="n">
         <v>-0.6039</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4873</v>
+        <v>0.487</v>
       </c>
       <c r="G37" t="n">
         <v>-1.7279</v>
@@ -33325,19 +33325,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.4348</v>
+        <v>-0.4349</v>
       </c>
       <c r="C38" t="n">
         <v>-0.1832</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4015</v>
+        <v>0.4011</v>
       </c>
       <c r="E38" t="n">
         <v>-0.6439</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4015</v>
+        <v>0.4011</v>
       </c>
       <c r="G38" t="n">
         <v>-1.8048</v>
@@ -33359,19 +33359,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.4109</v>
+        <v>-0.411</v>
       </c>
       <c r="C39" t="n">
         <v>-0.2966</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4921</v>
+        <v>0.4918</v>
       </c>
       <c r="E39" t="n">
         <v>-0.6367</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4921</v>
+        <v>0.4918</v>
       </c>
       <c r="G39" t="n">
         <v>-1.7573</v>
@@ -33393,19 +33393,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.4929</v>
+        <v>-0.493</v>
       </c>
       <c r="C40" t="n">
         <v>-0.192</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6107</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="E40" t="n">
         <v>-0.7688</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6107</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="G40" t="n">
         <v>-1.8177</v>
@@ -33433,13 +33433,13 @@
         <v>-0.2821</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4139</v>
+        <v>0.4135</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.7565</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4139</v>
+        <v>0.4135</v>
       </c>
       <c r="G41" t="n">
         <v>-1.7873</v>
@@ -33448,7 +33448,7 @@
         <v>-1.0569</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5584</v>
+        <v>-0.5585</v>
       </c>
       <c r="J41" t="n">
         <v>0.3765</v>
@@ -33461,19 +33461,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.4718</v>
+        <v>-0.4719</v>
       </c>
       <c r="C42" t="n">
         <v>-0.2345</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5656</v>
+        <v>0.5653</v>
       </c>
       <c r="E42" t="n">
         <v>-0.7312</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5656</v>
+        <v>0.5653</v>
       </c>
       <c r="G42" t="n">
         <v>-1.8222</v>
@@ -33501,13 +33501,13 @@
         <v>-0.2708</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7408</v>
+        <v>0.7407</v>
       </c>
       <c r="E43" t="n">
         <v>-0.8078</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7408</v>
+        <v>0.7407</v>
       </c>
       <c r="G43" t="n">
         <v>-1.8297</v>
@@ -33569,13 +33569,13 @@
         <v>-0.3257</v>
       </c>
       <c r="D45" t="n">
-        <v>1.038</v>
+        <v>1.0381</v>
       </c>
       <c r="E45" t="n">
         <v>-0.7716</v>
       </c>
       <c r="F45" t="n">
-        <v>1.038</v>
+        <v>1.0381</v>
       </c>
       <c r="G45" t="n">
         <v>-1.848</v>
@@ -33618,7 +33618,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6501</v>
+        <v>-0.6502</v>
       </c>
       <c r="J46" t="n">
         <v>0.7897999999999999</v>
@@ -33631,19 +33631,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.5746</v>
+        <v>-0.5747</v>
       </c>
       <c r="C47" t="n">
         <v>-0.3486</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7934</v>
+        <v>0.7933</v>
       </c>
       <c r="E47" t="n">
         <v>-0.9167</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7934</v>
+        <v>0.7933</v>
       </c>
       <c r="G47" t="n">
         <v>-1.7714</v>
@@ -33665,19 +33665,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6363</v>
+        <v>-0.6364</v>
       </c>
       <c r="C48" t="n">
         <v>-0.2059</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4548</v>
+        <v>0.4544</v>
       </c>
       <c r="E48" t="n">
         <v>-0.9091</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4548</v>
+        <v>0.4544</v>
       </c>
       <c r="G48" t="n">
         <v>-1.7019</v>
@@ -33699,19 +33699,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8146</v>
+        <v>-0.8147</v>
       </c>
       <c r="C49" t="n">
         <v>-0.1283</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0877</v>
       </c>
       <c r="E49" t="n">
         <v>-0.9965000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0877</v>
       </c>
       <c r="G49" t="n">
         <v>-1.666</v>
@@ -33733,19 +33733,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8133</v>
+        <v>-0.8135</v>
       </c>
       <c r="C50" t="n">
         <v>0.0205</v>
       </c>
       <c r="D50" t="n">
-        <v>0.132</v>
+        <v>0.1314</v>
       </c>
       <c r="E50" t="n">
         <v>-1.0497</v>
       </c>
       <c r="F50" t="n">
-        <v>0.132</v>
+        <v>0.1314</v>
       </c>
       <c r="G50" t="n">
         <v>-1.6141</v>
@@ -33767,19 +33767,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.8325</v>
+        <v>-0.8326</v>
       </c>
       <c r="C51" t="n">
         <v>0.2917</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1178</v>
+        <v>0.1171</v>
       </c>
       <c r="E51" t="n">
         <v>-1.07</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1178</v>
+        <v>0.1171</v>
       </c>
       <c r="G51" t="n">
         <v>-1.5265</v>
@@ -33788,7 +33788,7 @@
         <v>-2.2503</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1108</v>
+        <v>-1.1109</v>
       </c>
       <c r="J51" t="n">
         <v>0.6076</v>
@@ -33801,19 +33801,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9339</v>
+        <v>-0.9341</v>
       </c>
       <c r="C52" t="n">
         <v>0.4357</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0701</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E52" t="n">
         <v>-1.1849</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0701</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G52" t="n">
         <v>-1.4811</v>
@@ -33835,19 +33835,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9744</v>
       </c>
       <c r="C53" t="n">
         <v>0.6286</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0622</v>
+        <v>0.0615</v>
       </c>
       <c r="E53" t="n">
         <v>-1.2334</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0622</v>
+        <v>0.0615</v>
       </c>
       <c r="G53" t="n">
         <v>-1.4178</v>
@@ -33869,19 +33869,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.058</v>
+        <v>-1.0582</v>
       </c>
       <c r="C54" t="n">
         <v>0.8923</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3292</v>
+        <v>-0.3301</v>
       </c>
       <c r="E54" t="n">
         <v>-1.2402</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3292</v>
+        <v>-0.3301</v>
       </c>
       <c r="G54" t="n">
         <v>-1.3366</v>
@@ -33903,19 +33903,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1587</v>
+        <v>-1.1589</v>
       </c>
       <c r="C55" t="n">
         <v>1.0633</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5705</v>
+        <v>-0.5716</v>
       </c>
       <c r="E55" t="n">
         <v>-1.3057</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.5705</v>
+        <v>-0.5716</v>
       </c>
       <c r="G55" t="n">
         <v>-1.2349</v>
@@ -33937,19 +33937,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.2465</v>
+        <v>-1.2467</v>
       </c>
       <c r="C56" t="n">
         <v>1.0216</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.8145</v>
+        <v>-0.8158</v>
       </c>
       <c r="E56" t="n">
         <v>-1.3545</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.8145</v>
+        <v>-0.8158</v>
       </c>
       <c r="G56" t="n">
         <v>-1.1512</v>
@@ -33958,7 +33958,7 @@
         <v>-2.9732</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0485</v>
+        <v>-1.0486</v>
       </c>
       <c r="J56" t="n">
         <v>-0.245</v>
@@ -33971,19 +33971,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2972</v>
+        <v>-1.2975</v>
       </c>
       <c r="C57" t="n">
         <v>1.0128</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.8924</v>
+        <v>-0.8938</v>
       </c>
       <c r="E57" t="n">
         <v>-1.3985</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.8924</v>
+        <v>-0.8938</v>
       </c>
       <c r="G57" t="n">
         <v>-1.1701</v>
@@ -34005,19 +34005,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.2465</v>
+        <v>-1.2468</v>
       </c>
       <c r="C58" t="n">
         <v>0.9933</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.8324</v>
+        <v>-0.8337</v>
       </c>
       <c r="E58" t="n">
         <v>-1.35</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.8324</v>
+        <v>-0.8337</v>
       </c>
       <c r="G58" t="n">
         <v>-1.0633</v>
@@ -34039,19 +34039,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.2836</v>
+        <v>-1.2838</v>
       </c>
       <c r="C59" t="n">
         <v>0.9619</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.8113</v>
+        <v>-0.8126</v>
       </c>
       <c r="E59" t="n">
         <v>-1.4016</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.8113</v>
+        <v>-0.8126</v>
       </c>
       <c r="G59" t="n">
         <v>-1.0155</v>
@@ -34073,19 +34073,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.2491</v>
+        <v>-1.2493</v>
       </c>
       <c r="C60" t="n">
         <v>0.9198</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5419</v>
       </c>
       <c r="E60" t="n">
         <v>-1.4262</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5419</v>
       </c>
       <c r="G60" t="n">
         <v>-0.9312</v>
@@ -34107,19 +34107,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.1937</v>
+        <v>-1.1939</v>
       </c>
       <c r="C61" t="n">
         <v>0.8397</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.3869</v>
+        <v>-0.3879</v>
       </c>
       <c r="E61" t="n">
         <v>-1.3953</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3869</v>
+        <v>-0.3879</v>
       </c>
       <c r="G61" t="n">
         <v>-0.8745000000000001</v>
@@ -34141,19 +34141,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.1861</v>
+        <v>-1.1863</v>
       </c>
       <c r="C62" t="n">
         <v>0.8124</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.2593</v>
+        <v>-0.2602</v>
       </c>
       <c r="E62" t="n">
         <v>-1.4178</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2593</v>
+        <v>-0.2602</v>
       </c>
       <c r="G62" t="n">
         <v>-0.8302</v>
@@ -34175,19 +34175,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.1926</v>
+        <v>-1.1928</v>
       </c>
       <c r="C63" t="n">
         <v>0.7577</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.2126</v>
+        <v>-0.2135</v>
       </c>
       <c r="E63" t="n">
         <v>-1.4376</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2126</v>
+        <v>-0.2135</v>
       </c>
       <c r="G63" t="n">
         <v>-0.7568</v>
@@ -34209,19 +34209,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1628</v>
+        <v>-1.163</v>
       </c>
       <c r="C64" t="n">
         <v>0.6857</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.2615</v>
+        <v>-0.2624</v>
       </c>
       <c r="E64" t="n">
         <v>-1.3882</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2615</v>
+        <v>-0.2624</v>
       </c>
       <c r="G64" t="n">
         <v>-0.6651</v>
@@ -34243,19 +34243,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1788</v>
+        <v>-1.179</v>
       </c>
       <c r="C65" t="n">
         <v>0.6964</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.3014</v>
+        <v>-0.3024</v>
       </c>
       <c r="E65" t="n">
         <v>-1.3982</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3014</v>
+        <v>-0.3024</v>
       </c>
       <c r="G65" t="n">
         <v>-0.6235000000000001</v>
@@ -34277,19 +34277,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.1865</v>
+        <v>-1.1866</v>
       </c>
       <c r="C66" t="n">
         <v>0.585</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.2077</v>
+        <v>-0.2086</v>
       </c>
       <c r="E66" t="n">
         <v>-1.4312</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2077</v>
+        <v>-0.2086</v>
       </c>
       <c r="G66" t="n">
         <v>-0.5654</v>
@@ -34311,19 +34311,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1445</v>
+        <v>-1.1447</v>
       </c>
       <c r="C67" t="n">
         <v>0.6892</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.1867</v>
+        <v>-0.1876</v>
       </c>
       <c r="E67" t="n">
         <v>-1.384</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1867</v>
+        <v>-0.1876</v>
       </c>
       <c r="G67" t="n">
         <v>-0.5197000000000001</v>
@@ -34345,19 +34345,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1681</v>
+        <v>-1.1683</v>
       </c>
       <c r="C68" t="n">
         <v>0.6511</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2725</v>
+        <v>-0.2734</v>
       </c>
       <c r="E68" t="n">
         <v>-1.392</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.2725</v>
+        <v>-0.2734</v>
       </c>
       <c r="G68" t="n">
         <v>-0.5117</v>
@@ -34379,19 +34379,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1503</v>
+        <v>-1.1505</v>
       </c>
       <c r="C69" t="n">
         <v>0.5633</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.261</v>
+        <v>-0.2619</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3726</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.261</v>
+        <v>-0.2619</v>
       </c>
       <c r="G69" t="n">
         <v>-0.4484</v>
@@ -34413,19 +34413,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0622</v>
+        <v>-1.0624</v>
       </c>
       <c r="C70" t="n">
         <v>0.5677</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.2922</v>
+        <v>-0.2931</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2547</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.2922</v>
+        <v>-0.2931</v>
       </c>
       <c r="G70" t="n">
         <v>-0.419</v>
@@ -34434,7 +34434,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2132</v>
+        <v>-1.2133</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9639</v>
@@ -34447,19 +34447,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0186</v>
+        <v>-1.0188</v>
       </c>
       <c r="C71" t="n">
         <v>0.5209</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.1096</v>
+        <v>-0.1104</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2459</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1096</v>
+        <v>-0.1104</v>
       </c>
       <c r="G71" t="n">
         <v>-0.3891</v>
@@ -34481,19 +34481,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0168</v>
+        <v>-1.0169</v>
       </c>
       <c r="C72" t="n">
         <v>0.5194</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.1495</v>
+        <v>-0.1504</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2336</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1495</v>
+        <v>-0.1504</v>
       </c>
       <c r="G72" t="n">
         <v>-0.3835</v>
@@ -34515,19 +34515,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9529</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="C73" t="n">
         <v>0.4411</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1169</v>
+        <v>-0.1177</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1619</v>
+        <v>-1.162</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.1169</v>
+        <v>-0.1177</v>
       </c>
       <c r="G73" t="n">
         <v>-0.4158</v>
@@ -34536,7 +34536,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1956</v>
+        <v>-1.1957</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8566</v>
@@ -34549,19 +34549,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.9603</v>
       </c>
       <c r="C74" t="n">
         <v>0.4026</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.1679</v>
+        <v>-0.1687</v>
       </c>
       <c r="E74" t="n">
         <v>-1.1582</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1679</v>
+        <v>-0.1687</v>
       </c>
       <c r="G74" t="n">
         <v>-0.399</v>
@@ -34583,19 +34583,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9413</v>
+        <v>-0.9415</v>
       </c>
       <c r="C75" t="n">
         <v>0.3874</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.1831</v>
+        <v>-0.1839</v>
       </c>
       <c r="E75" t="n">
         <v>-1.1309</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.1831</v>
+        <v>-0.1839</v>
       </c>
       <c r="G75" t="n">
         <v>-0.3212</v>
@@ -34617,19 +34617,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8247</v>
+        <v>-0.8248</v>
       </c>
       <c r="C76" t="n">
         <v>0.2978</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.0857</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="E76" t="n">
         <v>-1.0094</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.0857</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="G76" t="n">
         <v>-0.339</v>
@@ -34651,19 +34651,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7477</v>
+        <v>-0.7479</v>
       </c>
       <c r="C77" t="n">
         <v>0.3431</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0533</v>
+        <v>0.0526</v>
       </c>
       <c r="E77" t="n">
         <v>-0.948</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0533</v>
+        <v>0.0526</v>
       </c>
       <c r="G77" t="n">
         <v>-0.2308</v>
@@ -34685,19 +34685,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7516</v>
+        <v>-0.7517</v>
       </c>
       <c r="C78" t="n">
         <v>0.2407</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1141</v>
+        <v>0.1135</v>
       </c>
       <c r="E78" t="n">
         <v>-0.968</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1141</v>
+        <v>0.1135</v>
       </c>
       <c r="G78" t="n">
         <v>-0.2391</v>
@@ -34719,19 +34719,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7214</v>
       </c>
       <c r="C79" t="n">
         <v>0.1954</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1235</v>
+        <v>0.1228</v>
       </c>
       <c r="E79" t="n">
         <v>-0.9325</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1235</v>
+        <v>0.1228</v>
       </c>
       <c r="G79" t="n">
         <v>-0.2385</v>
@@ -34753,19 +34753,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.6843</v>
+        <v>-0.6844</v>
       </c>
       <c r="C80" t="n">
         <v>0.1919</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2638</v>
+        <v>0.2633</v>
       </c>
       <c r="E80" t="n">
         <v>-0.9214</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2638</v>
+        <v>0.2633</v>
       </c>
       <c r="G80" t="n">
         <v>-0.2107</v>
@@ -34787,19 +34787,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.6665</v>
+        <v>-0.6666</v>
       </c>
       <c r="C81" t="n">
         <v>0.2028</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3202</v>
+        <v>0.3198</v>
       </c>
       <c r="E81" t="n">
         <v>-0.9132</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3202</v>
+        <v>0.3198</v>
       </c>
       <c r="G81" t="n">
         <v>-0.1683</v>
@@ -34821,19 +34821,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.6253</v>
+        <v>-0.6254</v>
       </c>
       <c r="C82" t="n">
         <v>0.2131</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3264</v>
+        <v>0.326</v>
       </c>
       <c r="E82" t="n">
         <v>-0.8632</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3264</v>
+        <v>0.326</v>
       </c>
       <c r="G82" t="n">
         <v>-0.1722</v>
@@ -34855,19 +34855,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6603</v>
+        <v>-0.6604</v>
       </c>
       <c r="C83" t="n">
         <v>0.09279999999999999</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1822</v>
+        <v>0.1817</v>
       </c>
       <c r="E83" t="n">
         <v>-0.8709</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1822</v>
+        <v>0.1817</v>
       </c>
       <c r="G83" t="n">
         <v>-0.1918</v>
@@ -34889,19 +34889,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6523</v>
+        <v>-0.6524</v>
       </c>
       <c r="C84" t="n">
         <v>0.1093</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1353</v>
+        <v>0.1347</v>
       </c>
       <c r="E84" t="n">
         <v>-0.8492</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1353</v>
+        <v>0.1347</v>
       </c>
       <c r="G84" t="n">
         <v>-0.1561</v>
@@ -34910,7 +34910,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3172</v>
+        <v>-1.3173</v>
       </c>
       <c r="J84" t="n">
         <v>-1.3222</v>
@@ -34923,19 +34923,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.6204</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="C85" t="n">
         <v>0.0525</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1899</v>
+        <v>0.1894</v>
       </c>
       <c r="E85" t="n">
         <v>-0.823</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1899</v>
+        <v>0.1894</v>
       </c>
       <c r="G85" t="n">
         <v>-0.1141</v>
@@ -34957,19 +34957,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5843</v>
+        <v>-0.5845</v>
       </c>
       <c r="C86" t="n">
         <v>0.0257</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2368</v>
+        <v>0.2363</v>
       </c>
       <c r="E86" t="n">
         <v>-0.7896</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2368</v>
+        <v>0.2363</v>
       </c>
       <c r="G86" t="n">
         <v>-0.1141</v>
@@ -34991,19 +34991,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5575</v>
+        <v>-0.5576</v>
       </c>
       <c r="C87" t="n">
         <v>0.0584</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2855</v>
+        <v>0.285</v>
       </c>
       <c r="E87" t="n">
         <v>-0.7683</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2855</v>
+        <v>0.285</v>
       </c>
       <c r="G87" t="n">
         <v>-0.07149999999999999</v>
@@ -35025,19 +35025,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.5083</v>
+        <v>-0.5084</v>
       </c>
       <c r="C88" t="n">
         <v>-0.0463</v>
       </c>
       <c r="D88" t="n">
-        <v>0.332</v>
+        <v>0.3315</v>
       </c>
       <c r="E88" t="n">
         <v>-0.7184</v>
       </c>
       <c r="F88" t="n">
-        <v>0.332</v>
+        <v>0.3315</v>
       </c>
       <c r="G88" t="n">
         <v>-0.08069999999999999</v>
@@ -35046,7 +35046,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2129</v>
+        <v>-1.213</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0564</v>
@@ -35059,19 +35059,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.5036</v>
+        <v>-0.5037</v>
       </c>
       <c r="C89" t="n">
         <v>-0.0515</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3382</v>
+        <v>0.3377</v>
       </c>
       <c r="E89" t="n">
         <v>-0.714</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3382</v>
+        <v>0.3377</v>
       </c>
       <c r="G89" t="n">
         <v>-0.0064</v>
@@ -35093,19 +35093,19 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5077</v>
       </c>
       <c r="C90" t="n">
         <v>-0.0336</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2133</v>
+        <v>0.2128</v>
       </c>
       <c r="E90" t="n">
         <v>-0.6878</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2133</v>
+        <v>0.2128</v>
       </c>
       <c r="G90" t="n">
         <v>-0.0235</v>
@@ -35127,19 +35127,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.4847</v>
+        <v>-0.4848</v>
       </c>
       <c r="C91" t="n">
         <v>-0.1676</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1763</v>
+        <v>0.1758</v>
       </c>
       <c r="E91" t="n">
         <v>-0.65</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1763</v>
+        <v>0.1758</v>
       </c>
       <c r="G91" t="n">
         <v>0.0236</v>
@@ -35161,19 +35161,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.4711</v>
+        <v>-0.4713</v>
       </c>
       <c r="C92" t="n">
         <v>-0.2331</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1334</v>
+        <v>0.1327</v>
       </c>
       <c r="E92" t="n">
         <v>-0.6223</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1334</v>
+        <v>0.1327</v>
       </c>
       <c r="G92" t="n">
         <v>0.0236</v>
@@ -35195,19 +35195,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4642</v>
+        <v>-0.4643</v>
       </c>
       <c r="C93" t="n">
         <v>-0.2228</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1767</v>
+        <v>0.1761</v>
       </c>
       <c r="E93" t="n">
         <v>-0.6245000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1767</v>
+        <v>0.1761</v>
       </c>
       <c r="G93" t="n">
         <v>0.0017</v>
@@ -35229,19 +35229,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4023</v>
+        <v>-0.4024</v>
       </c>
       <c r="C94" t="n">
         <v>-0.3182</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2718</v>
+        <v>0.2713</v>
       </c>
       <c r="E94" t="n">
         <v>-0.5708</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2718</v>
+        <v>0.2713</v>
       </c>
       <c r="G94" t="n">
         <v>0.0528</v>
@@ -35263,19 +35263,19 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.3947</v>
+        <v>-0.3948</v>
       </c>
       <c r="C95" t="n">
         <v>-0.2685</v>
       </c>
       <c r="D95" t="n">
-        <v>0.272</v>
+        <v>0.2715</v>
       </c>
       <c r="E95" t="n">
         <v>-0.5614</v>
       </c>
       <c r="F95" t="n">
-        <v>0.272</v>
+        <v>0.2715</v>
       </c>
       <c r="G95" t="n">
         <v>0.0834</v>
@@ -35284,7 +35284,7 @@
         <v>-0.2511</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.29</v>
+        <v>-1.2901</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7879</v>
@@ -35297,19 +35297,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3374</v>
+        <v>-0.3375</v>
       </c>
       <c r="C96" t="n">
         <v>-0.2964</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2773</v>
+        <v>0.2768</v>
       </c>
       <c r="E96" t="n">
         <v>-0.491</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2773</v>
+        <v>0.2768</v>
       </c>
       <c r="G96" t="n">
         <v>0.1326</v>
@@ -35337,13 +35337,13 @@
         <v>-0.3238</v>
       </c>
       <c r="D97" t="n">
-        <v>0.589</v>
+        <v>0.5887</v>
       </c>
       <c r="E97" t="n">
         <v>-0.4426</v>
       </c>
       <c r="F97" t="n">
-        <v>0.589</v>
+        <v>0.5887</v>
       </c>
       <c r="G97" t="n">
         <v>0.1956</v>
@@ -35365,19 +35365,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.3183</v>
+        <v>-0.3184</v>
       </c>
       <c r="C98" t="n">
         <v>-0.3705</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1393</v>
+        <v>0.1387</v>
       </c>
       <c r="E98" t="n">
         <v>-0.4327</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1393</v>
+        <v>0.1387</v>
       </c>
       <c r="G98" t="n">
         <v>0.1507</v>
@@ -35399,19 +35399,19 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.2677</v>
+        <v>-0.2678</v>
       </c>
       <c r="C99" t="n">
         <v>-0.3883</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1595</v>
+        <v>0.1589</v>
       </c>
       <c r="E99" t="n">
         <v>-0.3745</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1595</v>
+        <v>0.1589</v>
       </c>
       <c r="G99" t="n">
         <v>0.184</v>
@@ -35433,19 +35433,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2542</v>
+        <v>-0.2543</v>
       </c>
       <c r="C100" t="n">
         <v>-0.3899</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0925</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="E100" t="n">
         <v>-0.3409</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0925</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G100" t="n">
         <v>0.2266</v>
@@ -35467,19 +35467,19 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.2121</v>
+        <v>-0.2122</v>
       </c>
       <c r="C101" t="n">
         <v>-0.4367</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1072</v>
+        <v>0.1066</v>
       </c>
       <c r="E101" t="n">
         <v>-0.2919</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1072</v>
+        <v>0.1066</v>
       </c>
       <c r="G101" t="n">
         <v>0.2503</v>
@@ -35501,19 +35501,19 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.1593</v>
+        <v>-0.1594</v>
       </c>
       <c r="C102" t="n">
         <v>-0.5352</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2469</v>
+        <v>0.2464</v>
       </c>
       <c r="E102" t="n">
         <v>-0.2609</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2469</v>
+        <v>0.2464</v>
       </c>
       <c r="G102" t="n">
         <v>0.2686</v>
@@ -35535,19 +35535,19 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.1117</v>
+        <v>-0.1118</v>
       </c>
       <c r="C103" t="n">
         <v>-0.4519</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3913</v>
+        <v>0.3909</v>
       </c>
       <c r="E103" t="n">
         <v>-0.2374</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3913</v>
+        <v>0.3909</v>
       </c>
       <c r="G103" t="n">
         <v>0.3237</v>
@@ -35569,19 +35569,19 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.0418</v>
+        <v>-0.0419</v>
       </c>
       <c r="C104" t="n">
         <v>-0.5427999999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5316</v>
+        <v>0.5313</v>
       </c>
       <c r="E104" t="n">
         <v>-0.1852</v>
       </c>
       <c r="F104" t="n">
-        <v>0.5316</v>
+        <v>0.5313</v>
       </c>
       <c r="G104" t="n">
         <v>0.32</v>
@@ -35603,19 +35603,19 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0374</v>
+        <v>-0.0375</v>
       </c>
       <c r="C105" t="n">
         <v>-0.5632</v>
       </c>
       <c r="D105" t="n">
-        <v>0.5889</v>
+        <v>0.5886</v>
       </c>
       <c r="E105" t="n">
         <v>-0.194</v>
       </c>
       <c r="F105" t="n">
-        <v>0.5889</v>
+        <v>0.5886</v>
       </c>
       <c r="G105" t="n">
         <v>0.3365</v>
@@ -35643,13 +35643,13 @@
         <v>-0.5134</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5485</v>
+        <v>0.5482</v>
       </c>
       <c r="E106" t="n">
         <v>-0.1948</v>
       </c>
       <c r="F106" t="n">
-        <v>0.5485</v>
+        <v>0.5482</v>
       </c>
       <c r="G106" t="n">
         <v>0.3428</v>
@@ -35671,19 +35671,19 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.0031</v>
+        <v>-0.0032</v>
       </c>
       <c r="C107" t="n">
         <v>-0.5917</v>
       </c>
       <c r="D107" t="n">
-        <v>0.6536</v>
+        <v>0.6534</v>
       </c>
       <c r="E107" t="n">
         <v>-0.1673</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6536</v>
+        <v>0.6534</v>
       </c>
       <c r="G107" t="n">
         <v>0.3455</v>
@@ -35711,13 +35711,13 @@
         <v>-0.6247</v>
       </c>
       <c r="D108" t="n">
-        <v>0.79</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="E108" t="n">
         <v>-0.1526</v>
       </c>
       <c r="F108" t="n">
-        <v>0.79</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="G108" t="n">
         <v>0.3756</v>
@@ -35739,19 +35739,19 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.2253</v>
+        <v>0.2254</v>
       </c>
       <c r="C109" t="n">
         <v>-0.6274999999999999</v>
       </c>
       <c r="D109" t="n">
-        <v>1.4998</v>
+        <v>1.5002</v>
       </c>
       <c r="E109" t="n">
         <v>-0.09329999999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>1.4998</v>
+        <v>1.5002</v>
       </c>
       <c r="G109" t="n">
         <v>0.3373</v>
@@ -35779,13 +35779,13 @@
         <v>-0.6982</v>
       </c>
       <c r="D110" t="n">
-        <v>0.8838</v>
+        <v>0.8837</v>
       </c>
       <c r="E110" t="n">
         <v>-0.0833</v>
       </c>
       <c r="F110" t="n">
-        <v>0.8838</v>
+        <v>0.8837</v>
       </c>
       <c r="G110" t="n">
         <v>0.3709</v>
@@ -35807,7 +35807,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.1133</v>
+        <v>0.1132</v>
       </c>
       <c r="C111" t="n">
         <v>-0.7007</v>
@@ -35847,13 +35847,13 @@
         <v>-0.6355</v>
       </c>
       <c r="D112" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8885</v>
       </c>
       <c r="E112" t="n">
         <v>-0.0549</v>
       </c>
       <c r="F112" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8885</v>
       </c>
       <c r="G112" t="n">
         <v>0.4036</v>
@@ -35875,19 +35875,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.3064</v>
+        <v>0.3065</v>
       </c>
       <c r="C113" t="n">
         <v>-0.6818</v>
       </c>
       <c r="D113" t="n">
-        <v>1.6983</v>
+        <v>1.6989</v>
       </c>
       <c r="E113" t="n">
         <v>-0.0416</v>
       </c>
       <c r="F113" t="n">
-        <v>1.6983</v>
+        <v>1.6989</v>
       </c>
       <c r="G113" t="n">
         <v>0.4468</v>
@@ -35909,19 +35909,19 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.3304</v>
+        <v>0.3305</v>
       </c>
       <c r="C114" t="n">
         <v>-0.6998</v>
       </c>
       <c r="D114" t="n">
-        <v>1.7454</v>
+        <v>1.7459</v>
       </c>
       <c r="E114" t="n">
         <v>-0.0234</v>
       </c>
       <c r="F114" t="n">
-        <v>1.7454</v>
+        <v>1.7459</v>
       </c>
       <c r="G114" t="n">
         <v>0.4808</v>
@@ -35943,19 +35943,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3304</v>
+        <v>0.3306</v>
       </c>
       <c r="C115" t="n">
         <v>-0.7068</v>
       </c>
       <c r="D115" t="n">
-        <v>1.7491</v>
+        <v>1.7497</v>
       </c>
       <c r="E115" t="n">
         <v>-0.0242</v>
       </c>
       <c r="F115" t="n">
-        <v>1.7491</v>
+        <v>1.7497</v>
       </c>
       <c r="G115" t="n">
         <v>0.4669</v>
@@ -35977,19 +35977,19 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.3662</v>
+        <v>0.3663</v>
       </c>
       <c r="C116" t="n">
         <v>-0.6623</v>
       </c>
       <c r="D116" t="n">
-        <v>1.7555</v>
+        <v>1.7561</v>
       </c>
       <c r="E116" t="n">
         <v>0.0189</v>
       </c>
       <c r="F116" t="n">
-        <v>1.7555</v>
+        <v>1.7561</v>
       </c>
       <c r="G116" t="n">
         <v>0.4968</v>
@@ -36011,19 +36011,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.3503</v>
+        <v>0.3504</v>
       </c>
       <c r="C117" t="n">
         <v>-0.613</v>
       </c>
       <c r="D117" t="n">
-        <v>1.6648</v>
+        <v>1.6653</v>
       </c>
       <c r="E117" t="n">
         <v>0.0217</v>
       </c>
       <c r="F117" t="n">
-        <v>1.6648</v>
+        <v>1.6653</v>
       </c>
       <c r="G117" t="n">
         <v>0.4597</v>
@@ -36045,19 +36045,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.3724</v>
+        <v>0.3725</v>
       </c>
       <c r="C118" t="n">
         <v>-0.5901999999999999</v>
       </c>
       <c r="D118" t="n">
-        <v>1.6174</v>
+        <v>1.6179</v>
       </c>
       <c r="E118" t="n">
         <v>0.0611</v>
       </c>
       <c r="F118" t="n">
-        <v>1.6174</v>
+        <v>1.6179</v>
       </c>
       <c r="G118" t="n">
         <v>0.4997</v>
@@ -36079,19 +36079,19 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.3886</v>
+        <v>0.3887</v>
       </c>
       <c r="C119" t="n">
         <v>-0.5046</v>
       </c>
       <c r="D119" t="n">
-        <v>1.5824</v>
+        <v>1.5829</v>
       </c>
       <c r="E119" t="n">
         <v>0.0901</v>
       </c>
       <c r="F119" t="n">
-        <v>1.5824</v>
+        <v>1.5829</v>
       </c>
       <c r="G119" t="n">
         <v>0.5182</v>
@@ -36113,19 +36113,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4065</v>
+        <v>0.4066</v>
       </c>
       <c r="C120" t="n">
         <v>-0.4894</v>
       </c>
       <c r="D120" t="n">
-        <v>1.4572</v>
+        <v>1.4576</v>
       </c>
       <c r="E120" t="n">
         <v>0.1438</v>
       </c>
       <c r="F120" t="n">
-        <v>1.4572</v>
+        <v>1.4576</v>
       </c>
       <c r="G120" t="n">
         <v>0.54</v>
@@ -36147,19 +36147,19 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.2138</v>
+        <v>0.2137</v>
       </c>
       <c r="C121" t="n">
         <v>-0.4829</v>
       </c>
       <c r="D121" t="n">
-        <v>0.3535</v>
+        <v>0.353</v>
       </c>
       <c r="E121" t="n">
         <v>0.1788</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3535</v>
+        <v>0.353</v>
       </c>
       <c r="G121" t="n">
         <v>0.5434</v>
@@ -36181,19 +36181,19 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4011</v>
+        <v>0.4012</v>
       </c>
       <c r="C122" t="n">
         <v>-0.4206</v>
       </c>
       <c r="D122" t="n">
-        <v>1.3542</v>
+        <v>1.3545</v>
       </c>
       <c r="E122" t="n">
         <v>0.1629</v>
       </c>
       <c r="F122" t="n">
-        <v>1.3542</v>
+        <v>1.3545</v>
       </c>
       <c r="G122" t="n">
         <v>0.5557</v>
@@ -36221,13 +36221,13 @@
         <v>-0.3378</v>
       </c>
       <c r="D123" t="n">
-        <v>1.2432</v>
+        <v>1.2434</v>
       </c>
       <c r="E123" t="n">
         <v>0.1826</v>
       </c>
       <c r="F123" t="n">
-        <v>1.2432</v>
+        <v>1.2434</v>
       </c>
       <c r="G123" t="n">
         <v>0.5765</v>
@@ -36255,13 +36255,13 @@
         <v>-0.3003</v>
       </c>
       <c r="D124" t="n">
-        <v>1.2797</v>
+        <v>1.28</v>
       </c>
       <c r="E124" t="n">
         <v>0.2748</v>
       </c>
       <c r="F124" t="n">
-        <v>1.2797</v>
+        <v>1.28</v>
       </c>
       <c r="G124" t="n">
         <v>0.6377</v>
@@ -36289,13 +36289,13 @@
         <v>-0.213</v>
       </c>
       <c r="D125" t="n">
-        <v>0.5223</v>
+        <v>0.522</v>
       </c>
       <c r="E125" t="n">
         <v>0.2486</v>
       </c>
       <c r="F125" t="n">
-        <v>0.5223</v>
+        <v>0.522</v>
       </c>
       <c r="G125" t="n">
         <v>0.5918</v>
@@ -36323,13 +36323,13 @@
         <v>-0.2228</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4301</v>
+        <v>0.4297</v>
       </c>
       <c r="E126" t="n">
         <v>0.2914</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4301</v>
+        <v>0.4297</v>
       </c>
       <c r="G126" t="n">
         <v>0.5947</v>
@@ -36351,19 +36351,19 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3231</v>
+        <v>0.323</v>
       </c>
       <c r="C127" t="n">
         <v>-0.2094</v>
       </c>
       <c r="D127" t="n">
-        <v>0.379</v>
+        <v>0.3786</v>
       </c>
       <c r="E127" t="n">
         <v>0.3091</v>
       </c>
       <c r="F127" t="n">
-        <v>0.379</v>
+        <v>0.3786</v>
       </c>
       <c r="G127" t="n">
         <v>0.6478</v>
@@ -36385,19 +36385,19 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3077</v>
+        <v>0.3076</v>
       </c>
       <c r="C128" t="n">
         <v>-0.0979</v>
       </c>
       <c r="D128" t="n">
-        <v>0.295</v>
+        <v>0.2945</v>
       </c>
       <c r="E128" t="n">
         <v>0.3109</v>
       </c>
       <c r="F128" t="n">
-        <v>0.295</v>
+        <v>0.2945</v>
       </c>
       <c r="G128" t="n">
         <v>0.6712</v>
@@ -36419,19 +36419,19 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.2894</v>
+        <v>0.2893</v>
       </c>
       <c r="C129" t="n">
         <v>-0.1422</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2558</v>
+        <v>0.2553</v>
       </c>
       <c r="E129" t="n">
         <v>0.2978</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2558</v>
+        <v>0.2553</v>
       </c>
       <c r="G129" t="n">
         <v>0.6604</v>
@@ -36453,19 +36453,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.3066</v>
+        <v>0.3065</v>
       </c>
       <c r="C130" t="n">
         <v>-0.0697</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2588</v>
+        <v>0.2582</v>
       </c>
       <c r="E130" t="n">
         <v>0.3186</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2588</v>
+        <v>0.2582</v>
       </c>
       <c r="G130" t="n">
         <v>0.6974</v>
@@ -36487,19 +36487,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.3019</v>
+        <v>0.3018</v>
       </c>
       <c r="C131" t="n">
         <v>-0.0621</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2226</v>
+        <v>0.2221</v>
       </c>
       <c r="E131" t="n">
         <v>0.3218</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2226</v>
+        <v>0.2221</v>
       </c>
       <c r="G131" t="n">
         <v>0.7417</v>
@@ -36521,19 +36521,19 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.3374</v>
+        <v>0.3373</v>
       </c>
       <c r="C132" t="n">
         <v>-0.0043</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3565</v>
+        <v>0.3561</v>
       </c>
       <c r="E132" t="n">
         <v>0.3326</v>
       </c>
       <c r="F132" t="n">
-        <v>0.3565</v>
+        <v>0.3561</v>
       </c>
       <c r="G132" t="n">
         <v>0.6860000000000001</v>
@@ -36555,19 +36555,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3728</v>
+        <v>0.3727</v>
       </c>
       <c r="C133" t="n">
         <v>-0.0626</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3672</v>
+        <v>0.3667</v>
       </c>
       <c r="E133" t="n">
         <v>0.3742</v>
       </c>
       <c r="F133" t="n">
-        <v>0.3672</v>
+        <v>0.3667</v>
       </c>
       <c r="G133" t="n">
         <v>0.7568</v>
@@ -36589,19 +36589,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3513</v>
+        <v>0.3512</v>
       </c>
       <c r="C134" t="n">
         <v>-0.0133</v>
       </c>
       <c r="D134" t="n">
-        <v>0.3868</v>
+        <v>0.3864</v>
       </c>
       <c r="E134" t="n">
         <v>0.3424</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3868</v>
+        <v>0.3864</v>
       </c>
       <c r="G134" t="n">
         <v>0.7667</v>
@@ -36629,13 +36629,13 @@
         <v>0.034</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4551</v>
+        <v>0.4548</v>
       </c>
       <c r="E135" t="n">
         <v>0.3439</v>
       </c>
       <c r="F135" t="n">
-        <v>0.4551</v>
+        <v>0.4548</v>
       </c>
       <c r="G135" t="n">
         <v>0.8148</v>
@@ -36657,19 +36657,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3555</v>
+        <v>0.3554</v>
       </c>
       <c r="C136" t="n">
         <v>0.0503</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3208</v>
+        <v>0.3204</v>
       </c>
       <c r="E136" t="n">
         <v>0.3641</v>
       </c>
       <c r="F136" t="n">
-        <v>0.3208</v>
+        <v>0.3204</v>
       </c>
       <c r="G136" t="n">
         <v>0.8144</v>
@@ -36691,19 +36691,19 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.3302</v>
+        <v>0.3301</v>
       </c>
       <c r="C137" t="n">
         <v>0.0897</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2956</v>
+        <v>0.2951</v>
       </c>
       <c r="E137" t="n">
         <v>0.3389</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2956</v>
+        <v>0.2951</v>
       </c>
       <c r="G137" t="n">
         <v>0.769</v>
@@ -36725,19 +36725,19 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.3423</v>
+        <v>0.3422</v>
       </c>
       <c r="C138" t="n">
         <v>0.1277</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3085</v>
+        <v>0.308</v>
       </c>
       <c r="E138" t="n">
         <v>0.3508</v>
       </c>
       <c r="F138" t="n">
-        <v>0.3085</v>
+        <v>0.308</v>
       </c>
       <c r="G138" t="n">
         <v>0.8201000000000001</v>
@@ -36765,13 +36765,13 @@
         <v>0.2569</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3257</v>
+        <v>0.3253</v>
       </c>
       <c r="E139" t="n">
         <v>0.3956</v>
       </c>
       <c r="F139" t="n">
-        <v>0.3257</v>
+        <v>0.3253</v>
       </c>
       <c r="G139" t="n">
         <v>0.8807</v>
@@ -36793,19 +36793,19 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.3682</v>
+        <v>0.3681</v>
       </c>
       <c r="C140" t="n">
         <v>0.2033</v>
       </c>
       <c r="D140" t="n">
-        <v>0.3014</v>
+        <v>0.3009</v>
       </c>
       <c r="E140" t="n">
         <v>0.3849</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3014</v>
+        <v>0.3009</v>
       </c>
       <c r="G140" t="n">
         <v>0.8434</v>
@@ -36827,19 +36827,19 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3352</v>
+        <v>0.3351</v>
       </c>
       <c r="C141" t="n">
         <v>0.2356</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2431</v>
+        <v>0.2426</v>
       </c>
       <c r="E141" t="n">
         <v>0.3582</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2431</v>
+        <v>0.2426</v>
       </c>
       <c r="G141" t="n">
         <v>0.7754</v>
@@ -36861,19 +36861,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.3558</v>
+        <v>0.3557</v>
       </c>
       <c r="C142" t="n">
         <v>0.1588</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2582</v>
+        <v>0.2577</v>
       </c>
       <c r="E142" t="n">
         <v>0.3802</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2582</v>
+        <v>0.2577</v>
       </c>
       <c r="G142" t="n">
         <v>0.8086</v>
@@ -36895,19 +36895,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4041</v>
+        <v>0.404</v>
       </c>
       <c r="C143" t="n">
         <v>0.1661</v>
       </c>
       <c r="D143" t="n">
-        <v>0.354</v>
+        <v>0.3536</v>
       </c>
       <c r="E143" t="n">
         <v>0.4167</v>
       </c>
       <c r="F143" t="n">
-        <v>0.354</v>
+        <v>0.3536</v>
       </c>
       <c r="G143" t="n">
         <v>0.8001</v>
@@ -36929,19 +36929,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4281</v>
+        <v>0.428</v>
       </c>
       <c r="C144" t="n">
         <v>0.221</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3337</v>
+        <v>0.3332</v>
       </c>
       <c r="E144" t="n">
         <v>0.4517</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3337</v>
+        <v>0.3332</v>
       </c>
       <c r="G144" t="n">
         <v>0.7963</v>
@@ -36969,13 +36969,13 @@
         <v>0.2364</v>
       </c>
       <c r="D145" t="n">
-        <v>0.6333</v>
+        <v>0.633</v>
       </c>
       <c r="E145" t="n">
         <v>0.514</v>
       </c>
       <c r="F145" t="n">
-        <v>0.6333</v>
+        <v>0.633</v>
       </c>
       <c r="G145" t="n">
         <v>0.8041</v>
@@ -36997,19 +36997,19 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5099</v>
+        <v>0.5098</v>
       </c>
       <c r="C146" t="n">
         <v>0.2588</v>
       </c>
       <c r="D146" t="n">
-        <v>0.5056</v>
+        <v>0.5053</v>
       </c>
       <c r="E146" t="n">
         <v>0.5109</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5056</v>
+        <v>0.5053</v>
       </c>
       <c r="G146" t="n">
         <v>0.8073</v>
@@ -37031,19 +37031,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5144</v>
+        <v>0.5143</v>
       </c>
       <c r="C147" t="n">
         <v>0.2876</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5476</v>
       </c>
       <c r="E147" t="n">
         <v>0.506</v>
       </c>
       <c r="F147" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.5476</v>
       </c>
       <c r="G147" t="n">
         <v>0.8007</v>
@@ -37065,19 +37065,19 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5109</v>
+        <v>0.5108</v>
       </c>
       <c r="C148" t="n">
         <v>0.1796</v>
       </c>
       <c r="D148" t="n">
-        <v>0.6012</v>
+        <v>0.6009</v>
       </c>
       <c r="E148" t="n">
         <v>0.4883</v>
       </c>
       <c r="F148" t="n">
-        <v>0.6012</v>
+        <v>0.6009</v>
       </c>
       <c r="G148" t="n">
         <v>0.7067</v>
@@ -37086,7 +37086,7 @@
         <v>0.7867</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0191</v>
+        <v>0.0192</v>
       </c>
       <c r="J148" t="n">
         <v>0.4407</v>
@@ -37099,19 +37099,19 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5407</v>
       </c>
       <c r="C149" t="n">
         <v>0.2482</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5853</v>
+        <v>0.5851</v>
       </c>
       <c r="E149" t="n">
         <v>0.5296</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5853</v>
+        <v>0.5851</v>
       </c>
       <c r="G149" t="n">
         <v>0.7504</v>
@@ -37133,19 +37133,19 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5541</v>
+        <v>0.554</v>
       </c>
       <c r="C150" t="n">
         <v>0.2745</v>
       </c>
       <c r="D150" t="n">
-        <v>0.6142</v>
+        <v>0.614</v>
       </c>
       <c r="E150" t="n">
         <v>0.539</v>
       </c>
       <c r="F150" t="n">
-        <v>0.6142</v>
+        <v>0.614</v>
       </c>
       <c r="G150" t="n">
         <v>0.7954</v>
@@ -37173,13 +37173,13 @@
         <v>0.284</v>
       </c>
       <c r="D151" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5951</v>
       </c>
       <c r="E151" t="n">
         <v>0.5371</v>
       </c>
       <c r="F151" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5951</v>
       </c>
       <c r="G151" t="n">
         <v>0.7708</v>
@@ -37201,19 +37201,19 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5831</v>
       </c>
       <c r="C152" t="n">
         <v>0.2722</v>
       </c>
       <c r="D152" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6333</v>
       </c>
       <c r="E152" t="n">
         <v>0.5706</v>
       </c>
       <c r="F152" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6333</v>
       </c>
       <c r="G152" t="n">
         <v>0.7368</v>
@@ -37241,13 +37241,13 @@
         <v>0.2345</v>
       </c>
       <c r="D153" t="n">
-        <v>0.7341</v>
+        <v>0.7339</v>
       </c>
       <c r="E153" t="n">
         <v>0.5505</v>
       </c>
       <c r="F153" t="n">
-        <v>0.7341</v>
+        <v>0.7339</v>
       </c>
       <c r="G153" t="n">
         <v>0.7198</v>
@@ -37275,13 +37275,13 @@
         <v>0.2567</v>
       </c>
       <c r="D154" t="n">
-        <v>0.7361</v>
+        <v>0.7359</v>
       </c>
       <c r="E154" t="n">
         <v>0.5797</v>
       </c>
       <c r="F154" t="n">
-        <v>0.7361</v>
+        <v>0.7359</v>
       </c>
       <c r="G154" t="n">
         <v>0.7715</v>
@@ -37309,13 +37309,13 @@
         <v>0.2633</v>
       </c>
       <c r="D155" t="n">
-        <v>0.777</v>
+        <v>0.7769</v>
       </c>
       <c r="E155" t="n">
         <v>0.6124000000000001</v>
       </c>
       <c r="F155" t="n">
-        <v>0.777</v>
+        <v>0.7769</v>
       </c>
       <c r="G155" t="n">
         <v>0.7131999999999999</v>
@@ -37377,13 +37377,13 @@
         <v>0.3304</v>
       </c>
       <c r="D157" t="n">
-        <v>0.7796</v>
+        <v>0.7795</v>
       </c>
       <c r="E157" t="n">
         <v>0.6092</v>
       </c>
       <c r="F157" t="n">
-        <v>0.7796</v>
+        <v>0.7795</v>
       </c>
       <c r="G157" t="n">
         <v>0.7245</v>
@@ -37411,13 +37411,13 @@
         <v>0.3164</v>
       </c>
       <c r="D158" t="n">
-        <v>0.7731</v>
+        <v>0.7729</v>
       </c>
       <c r="E158" t="n">
         <v>0.6404</v>
       </c>
       <c r="F158" t="n">
-        <v>0.7731</v>
+        <v>0.7729</v>
       </c>
       <c r="G158" t="n">
         <v>0.6751</v>
@@ -37479,13 +37479,13 @@
         <v>0.2995</v>
       </c>
       <c r="D160" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7827</v>
       </c>
       <c r="E160" t="n">
         <v>0.6254</v>
       </c>
       <c r="F160" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7827</v>
       </c>
       <c r="G160" t="n">
         <v>0.6667999999999999</v>
@@ -37513,13 +37513,13 @@
         <v>0.2556</v>
       </c>
       <c r="D161" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7343</v>
       </c>
       <c r="E161" t="n">
         <v>0.6316000000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7343</v>
       </c>
       <c r="G161" t="n">
         <v>0.6499</v>
@@ -37547,13 +37547,13 @@
         <v>0.2684</v>
       </c>
       <c r="D162" t="n">
-        <v>0.7343</v>
+        <v>0.7341</v>
       </c>
       <c r="E162" t="n">
         <v>0.6669</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7343</v>
+        <v>0.7341</v>
       </c>
       <c r="G162" t="n">
         <v>0.6589</v>
@@ -37581,13 +37581,13 @@
         <v>0.3425</v>
       </c>
       <c r="D163" t="n">
-        <v>0.7772</v>
+        <v>0.777</v>
       </c>
       <c r="E163" t="n">
         <v>0.6917</v>
       </c>
       <c r="F163" t="n">
-        <v>0.7772</v>
+        <v>0.777</v>
       </c>
       <c r="G163" t="n">
         <v>0.6586</v>
@@ -37615,13 +37615,13 @@
         <v>0.3525</v>
       </c>
       <c r="D164" t="n">
-        <v>0.7725</v>
+        <v>0.7724</v>
       </c>
       <c r="E164" t="n">
         <v>0.6976</v>
       </c>
       <c r="F164" t="n">
-        <v>0.7725</v>
+        <v>0.7724</v>
       </c>
       <c r="G164" t="n">
         <v>0.6535</v>
@@ -37649,13 +37649,13 @@
         <v>0.3708</v>
       </c>
       <c r="D165" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.8058</v>
       </c>
       <c r="E165" t="n">
         <v>0.7199</v>
       </c>
       <c r="F165" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.8058</v>
       </c>
       <c r="G165" t="n">
         <v>0.6425999999999999</v>
@@ -37664,7 +37664,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>0.089</v>
+        <v>0.0891</v>
       </c>
       <c r="J165" t="n">
         <v>1.321</v>
@@ -37683,13 +37683,13 @@
         <v>0.4213</v>
       </c>
       <c r="D166" t="n">
-        <v>0.8033</v>
+        <v>0.8032</v>
       </c>
       <c r="E166" t="n">
         <v>0.7292</v>
       </c>
       <c r="F166" t="n">
-        <v>0.8033</v>
+        <v>0.8032</v>
       </c>
       <c r="G166" t="n">
         <v>0.6266</v>
@@ -37698,7 +37698,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>0.129</v>
+        <v>0.1291</v>
       </c>
       <c r="J166" t="n">
         <v>1.2724</v>
@@ -37717,13 +37717,13 @@
         <v>0.3612</v>
       </c>
       <c r="D167" t="n">
-        <v>0.8496</v>
+        <v>0.8495</v>
       </c>
       <c r="E167" t="n">
         <v>0.7482</v>
       </c>
       <c r="F167" t="n">
-        <v>0.8496</v>
+        <v>0.8495</v>
       </c>
       <c r="G167" t="n">
         <v>0.6153</v>
@@ -37751,13 +37751,13 @@
         <v>0.382</v>
       </c>
       <c r="D168" t="n">
-        <v>0.8165</v>
+        <v>0.8164</v>
       </c>
       <c r="E168" t="n">
         <v>0.7653</v>
       </c>
       <c r="F168" t="n">
-        <v>0.8165</v>
+        <v>0.8164</v>
       </c>
       <c r="G168" t="n">
         <v>0.6405</v>
@@ -37785,13 +37785,13 @@
         <v>0.4257</v>
       </c>
       <c r="D169" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="E169" t="n">
         <v>0.7239</v>
       </c>
       <c r="F169" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="G169" t="n">
         <v>0.5727</v>
@@ -37819,13 +37819,13 @@
         <v>0.4542</v>
       </c>
       <c r="D170" t="n">
-        <v>0.7912</v>
+        <v>0.7911</v>
       </c>
       <c r="E170" t="n">
         <v>0.7473</v>
       </c>
       <c r="F170" t="n">
-        <v>0.7912</v>
+        <v>0.7911</v>
       </c>
       <c r="G170" t="n">
         <v>0.6303</v>
@@ -37853,13 +37853,13 @@
         <v>0.5024999999999999</v>
       </c>
       <c r="D171" t="n">
-        <v>0.7526</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="E171" t="n">
         <v>0.7338</v>
       </c>
       <c r="F171" t="n">
-        <v>0.7526</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="G171" t="n">
         <v>0.5907</v>
@@ -37881,19 +37881,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.7917</v>
+        <v>0.7916</v>
       </c>
       <c r="C172" t="n">
         <v>0.5012</v>
       </c>
       <c r="D172" t="n">
-        <v>0.7994</v>
+        <v>0.7993</v>
       </c>
       <c r="E172" t="n">
         <v>0.7897</v>
       </c>
       <c r="F172" t="n">
-        <v>0.7994</v>
+        <v>0.7993</v>
       </c>
       <c r="G172" t="n">
         <v>0.5745</v>
@@ -37921,13 +37921,13 @@
         <v>0.5595</v>
       </c>
       <c r="D173" t="n">
-        <v>0.8367</v>
+        <v>0.8366</v>
       </c>
       <c r="E173" t="n">
         <v>0.7784</v>
       </c>
       <c r="F173" t="n">
-        <v>0.8367</v>
+        <v>0.8366</v>
       </c>
       <c r="G173" t="n">
         <v>0.5698</v>
@@ -37955,13 +37955,13 @@
         <v>0.5651</v>
       </c>
       <c r="D174" t="n">
-        <v>0.7543</v>
+        <v>0.7541</v>
       </c>
       <c r="E174" t="n">
         <v>0.7863</v>
       </c>
       <c r="F174" t="n">
-        <v>0.7543</v>
+        <v>0.7541</v>
       </c>
       <c r="G174" t="n">
         <v>0.602</v>
@@ -37989,13 +37989,13 @@
         <v>0.6141</v>
       </c>
       <c r="D175" t="n">
-        <v>0.7322</v>
+        <v>0.7321</v>
       </c>
       <c r="E175" t="n">
         <v>0.79</v>
       </c>
       <c r="F175" t="n">
-        <v>0.7322</v>
+        <v>0.7321</v>
       </c>
       <c r="G175" t="n">
         <v>0.5308</v>
@@ -38023,13 +38023,13 @@
         <v>0.6075</v>
       </c>
       <c r="D176" t="n">
-        <v>0.7313</v>
+        <v>0.7311</v>
       </c>
       <c r="E176" t="n">
         <v>0.8085</v>
       </c>
       <c r="F176" t="n">
-        <v>0.7313</v>
+        <v>0.7311</v>
       </c>
       <c r="G176" t="n">
         <v>0.6005</v>
@@ -38051,19 +38051,19 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.7645</v>
+        <v>0.7644</v>
       </c>
       <c r="C177" t="n">
         <v>0.5458</v>
       </c>
       <c r="D177" t="n">
-        <v>0.7199</v>
+        <v>0.7198</v>
       </c>
       <c r="E177" t="n">
         <v>0.7756</v>
       </c>
       <c r="F177" t="n">
-        <v>0.7199</v>
+        <v>0.7198</v>
       </c>
       <c r="G177" t="n">
         <v>0.5419</v>
@@ -38085,19 +38085,19 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.6802</v>
+        <v>0.6801</v>
       </c>
       <c r="C178" t="n">
         <v>0.6659</v>
       </c>
       <c r="D178" t="n">
-        <v>0.6795</v>
+        <v>0.6793</v>
       </c>
       <c r="E178" t="n">
         <v>0.6803</v>
       </c>
       <c r="F178" t="n">
-        <v>0.6795</v>
+        <v>0.6793</v>
       </c>
       <c r="G178" t="n">
         <v>0.5144</v>
@@ -38119,19 +38119,19 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.6889</v>
+        <v>0.6888</v>
       </c>
       <c r="C179" t="n">
         <v>0.6107</v>
       </c>
       <c r="D179" t="n">
-        <v>0.6657</v>
+        <v>0.6655</v>
       </c>
       <c r="E179" t="n">
         <v>0.6947</v>
       </c>
       <c r="F179" t="n">
-        <v>0.6657</v>
+        <v>0.6655</v>
       </c>
       <c r="G179" t="n">
         <v>0.5639999999999999</v>
@@ -38153,19 +38153,19 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.6733</v>
+        <v>0.6732</v>
       </c>
       <c r="C180" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="D180" t="n">
-        <v>0.6763</v>
+        <v>0.6761</v>
       </c>
       <c r="E180" t="n">
         <v>0.6725</v>
       </c>
       <c r="F180" t="n">
-        <v>0.6763</v>
+        <v>0.6761</v>
       </c>
       <c r="G180" t="n">
         <v>0.4937</v>
@@ -38193,13 +38193,13 @@
         <v>0.6037</v>
       </c>
       <c r="D181" t="n">
-        <v>0.5621</v>
+        <v>0.5618</v>
       </c>
       <c r="E181" t="n">
         <v>0.5965</v>
       </c>
       <c r="F181" t="n">
-        <v>0.5621</v>
+        <v>0.5618</v>
       </c>
       <c r="G181" t="n">
         <v>0.5051</v>
@@ -38227,13 +38227,13 @@
         <v>0.5862000000000001</v>
       </c>
       <c r="D182" t="n">
-        <v>0.7829</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="E182" t="n">
         <v>0.6128</v>
       </c>
       <c r="F182" t="n">
-        <v>0.7829</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="G182" t="n">
         <v>0.5012</v>
@@ -38255,19 +38255,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.6576</v>
+        <v>0.6575</v>
       </c>
       <c r="C183" t="n">
         <v>0.5868</v>
       </c>
       <c r="D183" t="n">
-        <v>0.7168</v>
+        <v>0.7167</v>
       </c>
       <c r="E183" t="n">
         <v>0.6427</v>
       </c>
       <c r="F183" t="n">
-        <v>0.7168</v>
+        <v>0.7167</v>
       </c>
       <c r="G183" t="n">
         <v>0.5113</v>
@@ -38289,19 +38289,19 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.5081</v>
+        <v>0.508</v>
       </c>
       <c r="C184" t="n">
         <v>0.5735</v>
       </c>
       <c r="D184" t="n">
-        <v>0.7181</v>
+        <v>0.718</v>
       </c>
       <c r="E184" t="n">
         <v>0.4555</v>
       </c>
       <c r="F184" t="n">
-        <v>0.7181</v>
+        <v>0.718</v>
       </c>
       <c r="G184" t="n">
         <v>0.4923</v>
@@ -38323,19 +38323,19 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.453</v>
+        <v>0.4529</v>
       </c>
       <c r="C185" t="n">
         <v>0.5709</v>
       </c>
       <c r="D185" t="n">
-        <v>0.3993</v>
+        <v>0.3989</v>
       </c>
       <c r="E185" t="n">
         <v>0.4665</v>
       </c>
       <c r="F185" t="n">
-        <v>0.3993</v>
+        <v>0.3989</v>
       </c>
       <c r="G185" t="n">
         <v>0.5016</v>
@@ -38357,19 +38357,19 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.4697</v>
+        <v>0.4696</v>
       </c>
       <c r="C186" t="n">
         <v>0.6338</v>
       </c>
       <c r="D186" t="n">
-        <v>0.399</v>
+        <v>0.3986</v>
       </c>
       <c r="E186" t="n">
         <v>0.4873</v>
       </c>
       <c r="F186" t="n">
-        <v>0.399</v>
+        <v>0.3986</v>
       </c>
       <c r="G186" t="n">
         <v>0.4745</v>
@@ -38391,19 +38391,19 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.4233</v>
+        <v>0.4232</v>
       </c>
       <c r="C187" t="n">
         <v>0.5393</v>
       </c>
       <c r="D187" t="n">
-        <v>0.3928</v>
+        <v>0.3924</v>
       </c>
       <c r="E187" t="n">
         <v>0.4309</v>
       </c>
       <c r="F187" t="n">
-        <v>0.3928</v>
+        <v>0.3924</v>
       </c>
       <c r="G187" t="n">
         <v>0.5042</v>
@@ -38431,13 +38431,13 @@
         <v>0.507</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4361</v>
+        <v>0.4358</v>
       </c>
       <c r="E188" t="n">
         <v>0.3669</v>
       </c>
       <c r="F188" t="n">
-        <v>0.4361</v>
+        <v>0.4358</v>
       </c>
       <c r="G188" t="n">
         <v>0.4856</v>
@@ -38459,19 +38459,19 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.3092</v>
+        <v>0.3091</v>
       </c>
       <c r="C189" t="n">
         <v>0.5022</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2504</v>
+        <v>0.2499</v>
       </c>
       <c r="E189" t="n">
         <v>0.3238</v>
       </c>
       <c r="F189" t="n">
-        <v>0.2504</v>
+        <v>0.2499</v>
       </c>
       <c r="G189" t="n">
         <v>0.5169</v>
@@ -38493,19 +38493,19 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.2983</v>
+        <v>0.2982</v>
       </c>
       <c r="C190" t="n">
         <v>0.3714</v>
       </c>
       <c r="D190" t="n">
-        <v>0.2578</v>
+        <v>0.2573</v>
       </c>
       <c r="E190" t="n">
         <v>0.3085</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2578</v>
+        <v>0.2573</v>
       </c>
       <c r="G190" t="n">
         <v>0.5368000000000001</v>
@@ -38514,7 +38514,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1349</v>
+        <v>-0.1348</v>
       </c>
       <c r="J190" t="n">
         <v>1.5321</v>
@@ -38527,19 +38527,19 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.2384</v>
+        <v>0.2383</v>
       </c>
       <c r="C191" t="n">
         <v>0.3429</v>
       </c>
       <c r="D191" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0825</v>
       </c>
       <c r="E191" t="n">
         <v>0.2773</v>
       </c>
       <c r="F191" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0825</v>
       </c>
       <c r="G191" t="n">
         <v>0.5975</v>
@@ -38561,19 +38561,19 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.1811</v>
+        <v>0.181</v>
       </c>
       <c r="C192" t="n">
         <v>0.288</v>
       </c>
       <c r="D192" t="n">
-        <v>0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="E192" t="n">
         <v>0.2262</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0008</v>
+        <v>0.0002</v>
       </c>
       <c r="G192" t="n">
         <v>0.615</v>
@@ -38595,19 +38595,19 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2101</v>
+        <v>0.21</v>
       </c>
       <c r="C193" t="n">
         <v>0.2348</v>
       </c>
       <c r="D193" t="n">
-        <v>0.1272</v>
+        <v>0.1266</v>
       </c>
       <c r="E193" t="n">
         <v>0.2309</v>
       </c>
       <c r="F193" t="n">
-        <v>0.1272</v>
+        <v>0.1266</v>
       </c>
       <c r="G193" t="n">
         <v>0.5775</v>
@@ -38629,19 +38629,19 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.1683</v>
+        <v>0.1682</v>
       </c>
       <c r="C194" t="n">
         <v>0.2157</v>
       </c>
       <c r="D194" t="n">
-        <v>0.1218</v>
+        <v>0.1212</v>
       </c>
       <c r="E194" t="n">
         <v>0.1799</v>
       </c>
       <c r="F194" t="n">
-        <v>0.1218</v>
+        <v>0.1212</v>
       </c>
       <c r="G194" t="n">
         <v>0.6114000000000001</v>
@@ -38663,19 +38663,19 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.1537</v>
+        <v>0.1536</v>
       </c>
       <c r="C195" t="n">
         <v>0.1813</v>
       </c>
       <c r="D195" t="n">
-        <v>0.1957</v>
+        <v>0.1951</v>
       </c>
       <c r="E195" t="n">
         <v>0.1433</v>
       </c>
       <c r="F195" t="n">
-        <v>0.1957</v>
+        <v>0.1951</v>
       </c>
       <c r="G195" t="n">
         <v>0.6017</v>
@@ -38684,7 +38684,7 @@
         <v>-0.4951</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1112</v>
+        <v>0.1113</v>
       </c>
       <c r="J195" t="n">
         <v>0.3553</v>
@@ -38697,19 +38697,19 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.1744</v>
+        <v>0.1743</v>
       </c>
       <c r="C196" t="n">
         <v>0.031</v>
       </c>
       <c r="D196" t="n">
-        <v>0.2432</v>
+        <v>0.2427</v>
       </c>
       <c r="E196" t="n">
         <v>0.1572</v>
       </c>
       <c r="F196" t="n">
-        <v>0.2432</v>
+        <v>0.2427</v>
       </c>
       <c r="G196" t="n">
         <v>0.6503</v>
@@ -38731,19 +38731,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.1262</v>
+        <v>0.1261</v>
       </c>
       <c r="C197" t="n">
         <v>-0.0422</v>
       </c>
       <c r="D197" t="n">
-        <v>0.0738</v>
+        <v>0.0731</v>
       </c>
       <c r="E197" t="n">
         <v>0.1393</v>
       </c>
       <c r="F197" t="n">
-        <v>0.0738</v>
+        <v>0.0731</v>
       </c>
       <c r="G197" t="n">
         <v>0.7181</v>
@@ -38765,19 +38765,19 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0728</v>
       </c>
       <c r="C198" t="n">
         <v>-0.0649</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1608</v>
+        <v>0.1602</v>
       </c>
       <c r="E198" t="n">
         <v>0.0509</v>
       </c>
       <c r="F198" t="n">
-        <v>0.1608</v>
+        <v>0.1602</v>
       </c>
       <c r="G198" t="n">
         <v>0.6818</v>
@@ -38799,19 +38799,19 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0672</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="C199" t="n">
         <v>-0.0964</v>
       </c>
       <c r="D199" t="n">
-        <v>0.2053</v>
+        <v>0.2048</v>
       </c>
       <c r="E199" t="n">
         <v>0.0327</v>
       </c>
       <c r="F199" t="n">
-        <v>0.2053</v>
+        <v>0.2048</v>
       </c>
       <c r="G199" t="n">
         <v>0.6883</v>
@@ -38839,13 +38839,13 @@
         <v>-0.1771</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3398</v>
+        <v>0.3394</v>
       </c>
       <c r="E200" t="n">
         <v>0.051</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3398</v>
+        <v>0.3394</v>
       </c>
       <c r="G200" t="n">
         <v>0.7064</v>
@@ -38867,19 +38867,19 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.1394</v>
+        <v>0.1393</v>
       </c>
       <c r="C201" t="n">
         <v>-0.2562</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4293</v>
+        <v>0.429</v>
       </c>
       <c r="E201" t="n">
         <v>0.0669</v>
       </c>
       <c r="F201" t="n">
-        <v>0.4293</v>
+        <v>0.429</v>
       </c>
       <c r="G201" t="n">
         <v>0.7378</v>
@@ -38907,13 +38907,13 @@
         <v>-0.2762</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4634</v>
+        <v>0.4631</v>
       </c>
       <c r="E202" t="n">
         <v>0.2042</v>
       </c>
       <c r="F202" t="n">
-        <v>0.4634</v>
+        <v>0.4631</v>
       </c>
       <c r="G202" t="n">
         <v>0.7575</v>
@@ -38935,19 +38935,19 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.2315</v>
+        <v>0.2314</v>
       </c>
       <c r="C203" t="n">
         <v>-0.2987</v>
       </c>
       <c r="D203" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5001</v>
       </c>
       <c r="E203" t="n">
         <v>0.1643</v>
       </c>
       <c r="F203" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5001</v>
       </c>
       <c r="G203" t="n">
         <v>0.6755</v>
@@ -38969,19 +38969,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.2952</v>
+        <v>0.2951</v>
       </c>
       <c r="C204" t="n">
         <v>-0.3445</v>
       </c>
       <c r="D204" t="n">
-        <v>0.6375</v>
+        <v>0.6373</v>
       </c>
       <c r="E204" t="n">
         <v>0.2096</v>
       </c>
       <c r="F204" t="n">
-        <v>0.6375</v>
+        <v>0.6373</v>
       </c>
       <c r="G204" t="n">
         <v>0.7432</v>
@@ -39003,19 +39003,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5599</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C205" t="n">
         <v>-0.4359</v>
       </c>
       <c r="D205" t="n">
-        <v>1.7557</v>
+        <v>1.7563</v>
       </c>
       <c r="E205" t="n">
         <v>0.2609</v>
       </c>
       <c r="F205" t="n">
-        <v>1.7557</v>
+        <v>1.7563</v>
       </c>
       <c r="G205" t="n">
         <v>0.7809</v>
@@ -39037,19 +39037,19 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3383</v>
+        <v>0.3382</v>
       </c>
       <c r="C206" t="n">
         <v>-0.5203</v>
       </c>
       <c r="D206" t="n">
-        <v>0.5263</v>
+        <v>0.526</v>
       </c>
       <c r="E206" t="n">
         <v>0.2913</v>
       </c>
       <c r="F206" t="n">
-        <v>0.5263</v>
+        <v>0.526</v>
       </c>
       <c r="G206" t="n">
         <v>0.777</v>
@@ -39058,7 +39058,7 @@
         <v>0.2135</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4274</v>
+        <v>0.4275</v>
       </c>
       <c r="J206" t="n">
         <v>-0.253</v>
@@ -39077,13 +39077,13 @@
         <v>-0.5511</v>
       </c>
       <c r="D207" t="n">
-        <v>0.6433</v>
+        <v>0.6431</v>
       </c>
       <c r="E207" t="n">
         <v>0.2926</v>
       </c>
       <c r="F207" t="n">
-        <v>0.6433</v>
+        <v>0.6431</v>
       </c>
       <c r="G207" t="n">
         <v>0.8064</v>
@@ -39092,7 +39092,7 @@
         <v>0.2135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4426</v>
+        <v>0.4427</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2922</v>
@@ -39105,19 +39105,19 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.4213</v>
+        <v>0.4212</v>
       </c>
       <c r="C208" t="n">
         <v>-0.5053</v>
       </c>
       <c r="D208" t="n">
-        <v>0.7245</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="E208" t="n">
         <v>0.3455</v>
       </c>
       <c r="F208" t="n">
-        <v>0.7245</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="G208" t="n">
         <v>0.7612</v>
@@ -39126,7 +39126,7 @@
         <v>0.3986</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4727</v>
+        <v>0.4728</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2508</v>
@@ -39145,13 +39145,13 @@
         <v>-0.5758</v>
       </c>
       <c r="D209" t="n">
-        <v>1.2979</v>
+        <v>1.2981</v>
       </c>
       <c r="E209" t="n">
         <v>0.4251</v>
       </c>
       <c r="F209" t="n">
-        <v>1.2979</v>
+        <v>1.2981</v>
       </c>
       <c r="G209" t="n">
         <v>0.8579</v>
@@ -39173,19 +39173,19 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.5977</v>
+        <v>0.5978</v>
       </c>
       <c r="C210" t="n">
         <v>-0.6456</v>
       </c>
       <c r="D210" t="n">
-        <v>1.2949</v>
+        <v>1.2952</v>
       </c>
       <c r="E210" t="n">
         <v>0.4234</v>
       </c>
       <c r="F210" t="n">
-        <v>1.2949</v>
+        <v>1.2952</v>
       </c>
       <c r="G210" t="n">
         <v>0.8021</v>
@@ -39207,19 +39207,19 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.6744</v>
+        <v>0.6745</v>
       </c>
       <c r="C211" t="n">
         <v>-0.7048</v>
       </c>
       <c r="D211" t="n">
-        <v>1.3412</v>
+        <v>1.3414</v>
       </c>
       <c r="E211" t="n">
         <v>0.5077</v>
       </c>
       <c r="F211" t="n">
-        <v>1.3412</v>
+        <v>1.3414</v>
       </c>
       <c r="G211" t="n">
         <v>0.8552</v>
@@ -39247,13 +39247,13 @@
         <v>-0.7396</v>
       </c>
       <c r="D212" t="n">
-        <v>1.4354</v>
+        <v>1.4357</v>
       </c>
       <c r="E212" t="n">
         <v>0.5084</v>
       </c>
       <c r="F212" t="n">
-        <v>1.4354</v>
+        <v>1.4357</v>
       </c>
       <c r="G212" t="n">
         <v>0.8359</v>
@@ -39275,19 +39275,19 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.7359</v>
+        <v>0.736</v>
       </c>
       <c r="C213" t="n">
         <v>-0.7202</v>
       </c>
       <c r="D213" t="n">
-        <v>1.5657</v>
+        <v>1.5661</v>
       </c>
       <c r="E213" t="n">
         <v>0.5285</v>
       </c>
       <c r="F213" t="n">
-        <v>1.5657</v>
+        <v>1.5661</v>
       </c>
       <c r="G213" t="n">
         <v>0.8477</v>
@@ -39309,19 +39309,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.8452</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="C214" t="n">
         <v>-0.7835</v>
       </c>
       <c r="D214" t="n">
-        <v>1.7312</v>
+        <v>1.7317</v>
       </c>
       <c r="E214" t="n">
         <v>0.6237</v>
       </c>
       <c r="F214" t="n">
-        <v>1.7312</v>
+        <v>1.7317</v>
       </c>
       <c r="G214" t="n">
         <v>0.8874</v>
@@ -39343,19 +39343,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.8889</v>
+        <v>0.889</v>
       </c>
       <c r="C215" t="n">
         <v>-0.8632</v>
       </c>
       <c r="D215" t="n">
-        <v>1.8946</v>
+        <v>1.8952</v>
       </c>
       <c r="E215" t="n">
         <v>0.6375</v>
       </c>
       <c r="F215" t="n">
-        <v>1.8946</v>
+        <v>1.8952</v>
       </c>
       <c r="G215" t="n">
         <v>0.9233</v>
@@ -39377,19 +39377,19 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8767</v>
       </c>
       <c r="C216" t="n">
         <v>-0.9258</v>
       </c>
       <c r="D216" t="n">
-        <v>1.9735</v>
+        <v>1.9742</v>
       </c>
       <c r="E216" t="n">
         <v>0.6022999999999999</v>
       </c>
       <c r="F216" t="n">
-        <v>1.9735</v>
+        <v>1.9742</v>
       </c>
       <c r="G216" t="n">
         <v>0.8899</v>
@@ -39411,19 +39411,19 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.8158</v>
+        <v>0.8159</v>
       </c>
       <c r="C217" t="n">
         <v>-0.9187</v>
       </c>
       <c r="D217" t="n">
-        <v>1.562</v>
+        <v>1.5625</v>
       </c>
       <c r="E217" t="n">
         <v>0.6293</v>
       </c>
       <c r="F217" t="n">
-        <v>1.562</v>
+        <v>1.5625</v>
       </c>
       <c r="G217" t="n">
         <v>0.8539</v>
@@ -39445,19 +39445,19 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.9096</v>
+        <v>0.9097</v>
       </c>
       <c r="C218" t="n">
         <v>-1.0065</v>
       </c>
       <c r="D218" t="n">
-        <v>2.1396</v>
+        <v>2.1405</v>
       </c>
       <c r="E218" t="n">
         <v>0.6021</v>
       </c>
       <c r="F218" t="n">
-        <v>2.1396</v>
+        <v>2.1405</v>
       </c>
       <c r="G218" t="n">
         <v>0.8443000000000001</v>
@@ -39479,19 +39479,19 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8577</v>
+        <v>0.8578</v>
       </c>
       <c r="C219" t="n">
         <v>-1.0961</v>
       </c>
       <c r="D219" t="n">
-        <v>1.6761</v>
+        <v>1.6766</v>
       </c>
       <c r="E219" t="n">
         <v>0.6531</v>
       </c>
       <c r="F219" t="n">
-        <v>1.6761</v>
+        <v>1.6766</v>
       </c>
       <c r="G219" t="n">
         <v>0.8724</v>
@@ -39513,19 +39513,19 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.9086</v>
+        <v>0.9087</v>
       </c>
       <c r="C220" t="n">
         <v>-1.2201</v>
       </c>
       <c r="D220" t="n">
-        <v>1.7394</v>
+        <v>1.74</v>
       </c>
       <c r="E220" t="n">
         <v>0.7009</v>
       </c>
       <c r="F220" t="n">
-        <v>1.7394</v>
+        <v>1.74</v>
       </c>
       <c r="G220" t="n">
         <v>0.888</v>
@@ -39547,19 +39547,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.9322</v>
+        <v>0.9323</v>
       </c>
       <c r="C221" t="n">
         <v>-1.2861</v>
       </c>
       <c r="D221" t="n">
-        <v>1.8104</v>
+        <v>1.811</v>
       </c>
       <c r="E221" t="n">
         <v>0.7126</v>
       </c>
       <c r="F221" t="n">
-        <v>1.8104</v>
+        <v>1.811</v>
       </c>
       <c r="G221" t="n">
         <v>0.8742</v>
@@ -39568,7 +39568,7 @@
         <v>0.8453000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8212</v>
       </c>
       <c r="J221" t="n">
         <v>0.3099</v>
@@ -39581,19 +39581,19 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.9275</v>
+        <v>0.9277</v>
       </c>
       <c r="C222" t="n">
         <v>-1.4025</v>
       </c>
       <c r="D222" t="n">
-        <v>1.724</v>
+        <v>1.7246</v>
       </c>
       <c r="E222" t="n">
         <v>0.7284</v>
       </c>
       <c r="F222" t="n">
-        <v>1.724</v>
+        <v>1.7246</v>
       </c>
       <c r="G222" t="n">
         <v>0.8994</v>
@@ -39615,19 +39615,19 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.9835</v>
+        <v>0.9836</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
       </c>
       <c r="D223" t="n">
-        <v>1.7742</v>
+        <v>1.7748</v>
       </c>
       <c r="E223" t="n">
         <v>0.7858000000000001</v>
       </c>
       <c r="F223" t="n">
-        <v>1.7742</v>
+        <v>1.7748</v>
       </c>
       <c r="G223" t="n">
         <v>0.8877</v>
@@ -39649,19 +39649,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.9752</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="C224" t="n">
         <v>-1.3976</v>
       </c>
       <c r="D224" t="n">
-        <v>1.6966</v>
+        <v>1.6971</v>
       </c>
       <c r="E224" t="n">
         <v>0.7949000000000001</v>
       </c>
       <c r="F224" t="n">
-        <v>1.6966</v>
+        <v>1.6971</v>
       </c>
       <c r="G224" t="n">
         <v>0.8958</v>
@@ -39683,19 +39683,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.9903</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="C225" t="n">
         <v>-1.3984</v>
       </c>
       <c r="D225" t="n">
-        <v>1.6703</v>
+        <v>1.6708</v>
       </c>
       <c r="E225" t="n">
         <v>0.8203</v>
       </c>
       <c r="F225" t="n">
-        <v>1.6703</v>
+        <v>1.6708</v>
       </c>
       <c r="G225" t="n">
         <v>0.8913</v>
@@ -39717,19 +39717,19 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9767</v>
+        <v>0.9768</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
       </c>
       <c r="D226" t="n">
-        <v>1.477</v>
+        <v>1.4774</v>
       </c>
       <c r="E226" t="n">
         <v>0.8517</v>
       </c>
       <c r="F226" t="n">
-        <v>1.477</v>
+        <v>1.4774</v>
       </c>
       <c r="G226" t="n">
         <v>0.8809</v>
@@ -39751,19 +39751,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.9851</v>
+        <v>0.9852</v>
       </c>
       <c r="C227" t="n">
         <v>-1.4189</v>
       </c>
       <c r="D227" t="n">
-        <v>1.5257</v>
+        <v>1.5261</v>
       </c>
       <c r="E227" t="n">
         <v>0.8499</v>
       </c>
       <c r="F227" t="n">
-        <v>1.5257</v>
+        <v>1.5261</v>
       </c>
       <c r="G227" t="n">
         <v>0.846</v>
@@ -39785,19 +39785,19 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9649</v>
+        <v>0.965</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
       </c>
       <c r="D228" t="n">
-        <v>1.3813</v>
+        <v>1.3816</v>
       </c>
       <c r="E228" t="n">
         <v>0.8609</v>
       </c>
       <c r="F228" t="n">
-        <v>1.3813</v>
+        <v>1.3816</v>
       </c>
       <c r="G228" t="n">
         <v>0.8151</v>
@@ -39819,19 +39819,19 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.9939</v>
+        <v>0.994</v>
       </c>
       <c r="C229" t="n">
         <v>-1.3839</v>
       </c>
       <c r="D229" t="n">
-        <v>1.451</v>
+        <v>1.4513</v>
       </c>
       <c r="E229" t="n">
         <v>0.8796</v>
       </c>
       <c r="F229" t="n">
-        <v>1.451</v>
+        <v>1.4513</v>
       </c>
       <c r="G229" t="n">
         <v>0.8384</v>
@@ -39859,13 +39859,13 @@
         <v>-1.8168</v>
       </c>
       <c r="D230" t="n">
-        <v>1.1742</v>
+        <v>1.1744</v>
       </c>
       <c r="E230" t="n">
         <v>0.9347</v>
       </c>
       <c r="F230" t="n">
-        <v>1.1742</v>
+        <v>1.1744</v>
       </c>
       <c r="G230" t="n">
         <v>0.8562</v>
@@ -39887,19 +39887,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0572</v>
+        <v>1.0573</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
       </c>
       <c r="D231" t="n">
-        <v>1.4899</v>
+        <v>1.4903</v>
       </c>
       <c r="E231" t="n">
         <v>0.949</v>
       </c>
       <c r="F231" t="n">
-        <v>1.4899</v>
+        <v>1.4903</v>
       </c>
       <c r="G231" t="n">
         <v>0.836</v>
@@ -39908,7 +39908,7 @@
         <v>1.0464</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4932</v>
+        <v>1.4933</v>
       </c>
       <c r="J231" t="n">
         <v>0.4203</v>
@@ -39921,19 +39921,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0789</v>
+        <v>1.079</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
       </c>
       <c r="D232" t="n">
-        <v>1.3833</v>
+        <v>1.3836</v>
       </c>
       <c r="E232" t="n">
-        <v>1.0028</v>
+        <v>1.0029</v>
       </c>
       <c r="F232" t="n">
-        <v>1.3833</v>
+        <v>1.3836</v>
       </c>
       <c r="G232" t="n">
         <v>0.8258</v>
@@ -39955,19 +39955,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.038</v>
+        <v>1.0381</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
       </c>
       <c r="D233" t="n">
-        <v>1.1823</v>
+        <v>1.1824</v>
       </c>
       <c r="E233" t="n">
         <v>1.002</v>
       </c>
       <c r="F233" t="n">
-        <v>1.1823</v>
+        <v>1.1824</v>
       </c>
       <c r="G233" t="n">
         <v>0.7672</v>
@@ -39976,7 +39976,7 @@
         <v>1.1463</v>
       </c>
       <c r="I233" t="n">
-        <v>1.6204</v>
+        <v>1.6205</v>
       </c>
       <c r="J233" t="n">
         <v>0.4739</v>
@@ -39995,13 +39995,13 @@
         <v>-1.649</v>
       </c>
       <c r="D234" t="n">
-        <v>1.2976</v>
+        <v>1.2978</v>
       </c>
       <c r="E234" t="n">
         <v>1.0017</v>
       </c>
       <c r="F234" t="n">
-        <v>1.2976</v>
+        <v>1.2978</v>
       </c>
       <c r="G234" t="n">
         <v>0.7194</v>
@@ -40029,13 +40029,13 @@
         <v>-1.6562</v>
       </c>
       <c r="D235" t="n">
-        <v>1.3365</v>
+        <v>1.3367</v>
       </c>
       <c r="E235" t="n">
         <v>1.0258</v>
       </c>
       <c r="F235" t="n">
-        <v>1.3365</v>
+        <v>1.3367</v>
       </c>
       <c r="G235" t="n">
         <v>0.6712</v>
@@ -40057,19 +40057,19 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0846</v>
+        <v>1.0847</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
       </c>
       <c r="D236" t="n">
-        <v>1.3708</v>
+        <v>1.3711</v>
       </c>
       <c r="E236" t="n">
         <v>1.0131</v>
       </c>
       <c r="F236" t="n">
-        <v>1.3708</v>
+        <v>1.3711</v>
       </c>
       <c r="G236" t="n">
         <v>0.5686</v>
@@ -40097,13 +40097,13 @@
         <v>-1.4719</v>
       </c>
       <c r="D237" t="n">
-        <v>1.4204</v>
+        <v>1.4207</v>
       </c>
       <c r="E237" t="n">
         <v>0.9244</v>
       </c>
       <c r="F237" t="n">
-        <v>1.4204</v>
+        <v>1.4207</v>
       </c>
       <c r="G237" t="n">
         <v>0.4775</v>
@@ -40131,13 +40131,13 @@
         <v>-1.4868</v>
       </c>
       <c r="D238" t="n">
-        <v>1.2144</v>
+        <v>1.2146</v>
       </c>
       <c r="E238" t="n">
         <v>0.918</v>
       </c>
       <c r="F238" t="n">
-        <v>1.2144</v>
+        <v>1.2146</v>
       </c>
       <c r="G238" t="n">
         <v>0.4782</v>
@@ -40159,19 +40159,19 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
       </c>
       <c r="D239" t="n">
-        <v>1.1455</v>
+        <v>1.1456</v>
       </c>
       <c r="E239" t="n">
         <v>0.9635</v>
       </c>
       <c r="F239" t="n">
-        <v>1.1455</v>
+        <v>1.1456</v>
       </c>
       <c r="G239" t="n">
         <v>0.4021</v>
@@ -40180,7 +40180,7 @@
         <v>1.1243</v>
       </c>
       <c r="I239" t="n">
-        <v>1.7083</v>
+        <v>1.7084</v>
       </c>
       <c r="J239" t="n">
         <v>0.6194</v>
@@ -40199,13 +40199,13 @@
         <v>-1.4187</v>
       </c>
       <c r="D240" t="n">
-        <v>1.252</v>
+        <v>1.2522</v>
       </c>
       <c r="E240" t="n">
         <v>0.96</v>
       </c>
       <c r="F240" t="n">
-        <v>1.252</v>
+        <v>1.2522</v>
       </c>
       <c r="G240" t="n">
         <v>0.341</v>
@@ -40214,7 +40214,7 @@
         <v>1.1243</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7844</v>
+        <v>1.7845</v>
       </c>
       <c r="J240" t="n">
         <v>0.5901</v>
@@ -40233,13 +40233,13 @@
         <v>-1.4448</v>
       </c>
       <c r="D241" t="n">
-        <v>1.2928</v>
+        <v>1.293</v>
       </c>
       <c r="E241" t="n">
         <v>0.9575</v>
       </c>
       <c r="F241" t="n">
-        <v>1.2928</v>
+        <v>1.293</v>
       </c>
       <c r="G241" t="n">
         <v>0.2718</v>
@@ -40261,19 +40261,19 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0348</v>
+        <v>1.0349</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
       </c>
       <c r="D242" t="n">
-        <v>1.4347</v>
+        <v>1.4351</v>
       </c>
       <c r="E242" t="n">
         <v>0.9348</v>
       </c>
       <c r="F242" t="n">
-        <v>1.4347</v>
+        <v>1.4351</v>
       </c>
       <c r="G242" t="n">
         <v>0.1467</v>
@@ -40301,13 +40301,13 @@
         <v>-1.1287</v>
       </c>
       <c r="D243" t="n">
-        <v>1.3058</v>
+        <v>1.3061</v>
       </c>
       <c r="E243" t="n">
         <v>0.9065</v>
       </c>
       <c r="F243" t="n">
-        <v>1.3058</v>
+        <v>1.3061</v>
       </c>
       <c r="G243" t="n">
         <v>0.1181</v>
@@ -40316,7 +40316,7 @@
         <v>1.1114</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8103</v>
+        <v>1.8104</v>
       </c>
       <c r="J243" t="n">
         <v>0.5862000000000001</v>
@@ -40335,13 +40335,13 @@
         <v>-1.0986</v>
       </c>
       <c r="D244" t="n">
-        <v>1.3525</v>
+        <v>1.3528</v>
       </c>
       <c r="E244" t="n">
         <v>0.9422</v>
       </c>
       <c r="F244" t="n">
-        <v>1.3525</v>
+        <v>1.3528</v>
       </c>
       <c r="G244" t="n">
         <v>0.1271</v>
@@ -40350,7 +40350,7 @@
         <v>1.1744</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7648</v>
+        <v>1.7649</v>
       </c>
       <c r="J244" t="n">
         <v>0.7025</v>
@@ -40363,19 +40363,19 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1.0012</v>
+        <v>1.0013</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
       </c>
       <c r="D245" t="n">
-        <v>1.5761</v>
+        <v>1.5766</v>
       </c>
       <c r="E245" t="n">
         <v>0.8575</v>
       </c>
       <c r="F245" t="n">
-        <v>1.5761</v>
+        <v>1.5766</v>
       </c>
       <c r="G245" t="n">
         <v>0.0048</v>
@@ -40397,19 +40397,19 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0269</v>
+        <v>1.027</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
       </c>
       <c r="D246" t="n">
-        <v>1.5797</v>
+        <v>1.5802</v>
       </c>
       <c r="E246" t="n">
         <v>0.8885999999999999</v>
       </c>
       <c r="F246" t="n">
-        <v>1.5797</v>
+        <v>1.5802</v>
       </c>
       <c r="G246" t="n">
         <v>-0.0447</v>
@@ -40431,19 +40431,19 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9709</v>
+        <v>0.971</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
       </c>
       <c r="D247" t="n">
-        <v>1.4541</v>
+        <v>1.4545</v>
       </c>
       <c r="E247" t="n">
         <v>0.8501</v>
       </c>
       <c r="F247" t="n">
-        <v>1.4541</v>
+        <v>1.4545</v>
       </c>
       <c r="G247" t="n">
         <v>-0.0524</v>
@@ -40471,13 +40471,13 @@
         <v>-1.1172</v>
       </c>
       <c r="D248" t="n">
-        <v>1.3</v>
+        <v>1.3002</v>
       </c>
       <c r="E248" t="n">
         <v>0.8521</v>
       </c>
       <c r="F248" t="n">
-        <v>1.3</v>
+        <v>1.3002</v>
       </c>
       <c r="G248" t="n">
         <v>-0.1785</v>
@@ -40505,13 +40505,13 @@
         <v>-1.1489</v>
       </c>
       <c r="D249" t="n">
-        <v>1.1164</v>
+        <v>1.1165</v>
       </c>
       <c r="E249" t="n">
         <v>0.8809</v>
       </c>
       <c r="F249" t="n">
-        <v>1.1164</v>
+        <v>1.1165</v>
       </c>
       <c r="G249" t="n">
         <v>-0.1907</v>
@@ -40533,19 +40533,19 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9394</v>
+        <v>0.9395</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
       </c>
       <c r="D250" t="n">
-        <v>1.2156</v>
+        <v>1.2158</v>
       </c>
       <c r="E250" t="n">
         <v>0.8704</v>
       </c>
       <c r="F250" t="n">
-        <v>1.2156</v>
+        <v>1.2158</v>
       </c>
       <c r="G250" t="n">
         <v>-0.2589</v>
@@ -40573,13 +40573,13 @@
         <v>-1.1771</v>
       </c>
       <c r="D251" t="n">
-        <v>1.2358</v>
+        <v>1.236</v>
       </c>
       <c r="E251" t="n">
         <v>0.9171</v>
       </c>
       <c r="F251" t="n">
-        <v>1.2358</v>
+        <v>1.236</v>
       </c>
       <c r="G251" t="n">
         <v>-0.2606</v>
@@ -40601,19 +40601,19 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9869</v>
+        <v>0.987</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
       </c>
       <c r="D252" t="n">
-        <v>1.21</v>
+        <v>1.2102</v>
       </c>
       <c r="E252" t="n">
         <v>0.9312</v>
       </c>
       <c r="F252" t="n">
-        <v>1.21</v>
+        <v>1.2102</v>
       </c>
       <c r="G252" t="n">
         <v>-0.3134</v>
@@ -40635,19 +40635,19 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7479</v>
+        <v>0.7478</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
       </c>
       <c r="D253" t="n">
-        <v>0.0338</v>
+        <v>0.0331</v>
       </c>
       <c r="E253" t="n">
         <v>0.9264</v>
       </c>
       <c r="F253" t="n">
-        <v>0.0338</v>
+        <v>0.0331</v>
       </c>
       <c r="G253" t="n">
         <v>-0.3789</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3393</v>
+        <v>2.3394</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40669,19 +40669,19 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8769</v>
+        <v>0.8768</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
       </c>
       <c r="D254" t="n">
-        <v>0.6445</v>
+        <v>0.6443</v>
       </c>
       <c r="E254" t="n">
         <v>0.9350000000000001</v>
       </c>
       <c r="F254" t="n">
-        <v>0.6445</v>
+        <v>0.6443</v>
       </c>
       <c r="G254" t="n">
         <v>-0.4319</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4455</v>
+        <v>2.4456</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40703,19 +40703,19 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8384</v>
+        <v>0.8383</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
       </c>
       <c r="D255" t="n">
-        <v>0.4427</v>
+        <v>0.4423</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9373</v>
+        <v>0.9374</v>
       </c>
       <c r="F255" t="n">
-        <v>0.4427</v>
+        <v>0.4423</v>
       </c>
       <c r="G255" t="n">
         <v>-0.4668</v>
@@ -40737,19 +40737,19 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8169</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
       </c>
       <c r="D256" t="n">
-        <v>0.4899</v>
+        <v>0.4895</v>
       </c>
       <c r="E256" t="n">
         <v>0.8988</v>
       </c>
       <c r="F256" t="n">
-        <v>0.4899</v>
+        <v>0.4895</v>
       </c>
       <c r="G256" t="n">
         <v>-0.5635</v>
@@ -40777,13 +40777,13 @@
         <v>-0.8488</v>
       </c>
       <c r="D257" t="n">
-        <v>0.3218</v>
+        <v>0.3213</v>
       </c>
       <c r="E257" t="n">
         <v>0.8529</v>
       </c>
       <c r="F257" t="n">
-        <v>0.3218</v>
+        <v>0.3213</v>
       </c>
       <c r="G257" t="n">
         <v>-0.7393</v>
@@ -40805,19 +40805,19 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7881</v>
+        <v>0.788</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
       </c>
       <c r="D258" t="n">
-        <v>0.2932</v>
+        <v>0.2926</v>
       </c>
       <c r="E258" t="n">
         <v>0.9118000000000001</v>
       </c>
       <c r="F258" t="n">
-        <v>0.2932</v>
+        <v>0.2926</v>
       </c>
       <c r="G258" t="n">
         <v>-0.7468</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8223</v>
+        <v>2.8224</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40839,19 +40839,19 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8239</v>
+        <v>0.8238</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
       </c>
       <c r="D259" t="n">
-        <v>0.3242</v>
+        <v>0.3237</v>
       </c>
       <c r="E259" t="n">
         <v>0.9488</v>
       </c>
       <c r="F259" t="n">
-        <v>0.3242</v>
+        <v>0.3237</v>
       </c>
       <c r="G259" t="n">
         <v>-0.8431999999999999</v>
@@ -40873,14 +40873,20 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.9462</v>
+        <v>0.8393</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
       </c>
+      <c r="D260" t="n">
+        <v>0.4117</v>
+      </c>
       <c r="E260" t="n">
         <v>0.9462</v>
       </c>
+      <c r="F260" t="n">
+        <v>0.4117</v>
+      </c>
       <c r="G260" t="n">
         <v>-0.8431999999999999</v>
       </c>
@@ -40901,13 +40907,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9463</v>
+        <v>0.9462</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9463</v>
+        <v>0.9462</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40916,7 +40922,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.0035</v>
+        <v>3.0028</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.373</v>
+        <v>1.378</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.631</v>
+        <v>1.634</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.118</v>
+        <v>2.12</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.853</v>
+        <v>2.855</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.994</v>
+        <v>3.998</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.606</v>
+        <v>-0.602</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.068</v>
+        <v>-0.064</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.054</v>
+        <v>1.056</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66504.28999999999</v>
+        <v>66439.21000000001</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3729</v>
+        <v>1.3776</v>
       </c>
       <c r="D261" t="n">
-        <v>1.6305</v>
+        <v>1.6342</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1178</v>
+        <v>2.1199</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8527</v>
+        <v>2.8548</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9944</v>
+        <v>3.9978</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.6017</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.0675</v>
+        <v>-0.0644</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0539</v>
+        <v>1.056</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66504.28999999999</v>
+        <v>66439.21000000001</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32141,7 +32141,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.6109</v>
+        <v>-0.611</v>
       </c>
       <c r="D3" t="n">
         <v>0.1073</v>
@@ -32237,7 +32237,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5098</v>
+        <v>-0.5099</v>
       </c>
       <c r="C6" t="n">
         <v>-0.0915</v>
@@ -32348,7 +32348,7 @@
         <v>0.105</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7004</v>
+        <v>-0.7005</v>
       </c>
       <c r="F9" t="n">
         <v>0.105</v>
@@ -32394,7 +32394,7 @@
         <v>-0.2198</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.387</v>
+        <v>-0.3871</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2486</v>
@@ -33686,7 +33686,7 @@
         <v>-1.7846</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9326</v>
+        <v>-0.9327</v>
       </c>
       <c r="J48" t="n">
         <v>0.7829</v>
@@ -34094,7 +34094,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1187</v>
+        <v>-1.1188</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9842</v>
@@ -34196,7 +34196,7 @@
         <v>-2.4406</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0933</v>
+        <v>-1.0934</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4597</v>
@@ -34366,7 +34366,7 @@
         <v>-1.7874</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1609</v>
+        <v>-1.161</v>
       </c>
       <c r="J68" t="n">
         <v>-2.108</v>
@@ -34468,7 +34468,7 @@
         <v>-1.4228</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2464</v>
+        <v>-1.2465</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9252</v>
@@ -34672,7 +34672,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2092</v>
+        <v>-1.2093</v>
       </c>
       <c r="J77" t="n">
         <v>-1.5973</v>
@@ -34966,7 +34966,7 @@
         <v>0.2363</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7896</v>
+        <v>-0.7897</v>
       </c>
       <c r="F86" t="n">
         <v>0.2363</v>
@@ -34991,7 +34991,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5576</v>
+        <v>-0.5577</v>
       </c>
       <c r="C87" t="n">
         <v>0.0584</v>
@@ -35012,7 +35012,7 @@
         <v>-0.577</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2933</v>
+        <v>-1.2934</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1315</v>
@@ -35386,7 +35386,7 @@
         <v>-0.2051</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0584</v>
+        <v>-1.0585</v>
       </c>
       <c r="J98" t="n">
         <v>-0.618</v>
@@ -35943,7 +35943,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3306</v>
+        <v>0.3305</v>
       </c>
       <c r="C115" t="n">
         <v>-0.7068</v>
@@ -36100,7 +36100,7 @@
         <v>0.2519</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3323</v>
+        <v>-0.3324</v>
       </c>
       <c r="J119" t="n">
         <v>-0.07729999999999999</v>
@@ -36190,7 +36190,7 @@
         <v>1.3545</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1629</v>
+        <v>0.1628</v>
       </c>
       <c r="F122" t="n">
         <v>1.3545</v>
@@ -36746,7 +36746,7 @@
         <v>0.677</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1366</v>
+        <v>-0.1367</v>
       </c>
       <c r="J138" t="n">
         <v>0.0428</v>
@@ -37630,7 +37630,7 @@
         <v>0.8270999999999999</v>
       </c>
       <c r="I164" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J164" t="n">
         <v>1.2102</v>
@@ -37766,7 +37766,7 @@
         <v>0.8885999999999999</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0888</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J168" t="n">
         <v>1.4432</v>
@@ -38140,7 +38140,7 @@
         <v>0.451</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1771</v>
+        <v>-0.177</v>
       </c>
       <c r="J179" t="n">
         <v>1.9407</v>
@@ -38718,7 +38718,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1823</v>
+        <v>0.1824</v>
       </c>
       <c r="J196" t="n">
         <v>0.0803</v>
@@ -38752,7 +38752,7 @@
         <v>-0.2841</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2259</v>
+        <v>0.226</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1028</v>
@@ -38990,7 +38990,7 @@
         <v>0.091</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4308</v>
+        <v>0.4309</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4266</v>
@@ -39160,7 +39160,7 @@
         <v>0.3986</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6137</v>
+        <v>0.6138</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1699</v>
@@ -39330,7 +39330,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9175</v>
+        <v>0.9176</v>
       </c>
       <c r="J214" t="n">
         <v>0.0795</v>
@@ -39445,7 +39445,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.9097</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="C218" t="n">
         <v>-1.0065</v>
@@ -39670,7 +39670,7 @@
         <v>0.8441</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0632</v>
+        <v>1.0633</v>
       </c>
       <c r="J224" t="n">
         <v>0.3764</v>
@@ -39772,7 +39772,7 @@
         <v>0.9485</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2501</v>
+        <v>1.2502</v>
       </c>
       <c r="J227" t="n">
         <v>0.355</v>
@@ -39874,7 +39874,7 @@
         <v>1.0464</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3523</v>
+        <v>1.3524</v>
       </c>
       <c r="J230" t="n">
         <v>0.4839</v>
@@ -39942,7 +39942,7 @@
         <v>1.1463</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5579</v>
+        <v>1.558</v>
       </c>
       <c r="J232" t="n">
         <v>0.4813</v>
@@ -40044,7 +40044,7 @@
         <v>1.1415</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7488</v>
+        <v>1.7489</v>
       </c>
       <c r="J235" t="n">
         <v>0.5417999999999999</v>
@@ -40078,7 +40078,7 @@
         <v>1.1415</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7842</v>
+        <v>1.7843</v>
       </c>
       <c r="J236" t="n">
         <v>0.5580000000000001</v>
@@ -40146,7 +40146,7 @@
         <v>1.1243</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5449</v>
+        <v>1.545</v>
       </c>
       <c r="J238" t="n">
         <v>0.5247000000000001</v>
@@ -40248,7 +40248,7 @@
         <v>1.1114</v>
       </c>
       <c r="I241" t="n">
-        <v>1.8038</v>
+        <v>1.8039</v>
       </c>
       <c r="J241" t="n">
         <v>0.6431</v>
@@ -40270,7 +40270,7 @@
         <v>1.4351</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9348</v>
+        <v>0.9349</v>
       </c>
       <c r="F242" t="n">
         <v>1.4351</v>
@@ -40406,7 +40406,7 @@
         <v>1.5802</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8887</v>
       </c>
       <c r="F246" t="n">
         <v>1.5802</v>
@@ -40440,7 +40440,7 @@
         <v>1.4545</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8501</v>
+        <v>0.8502</v>
       </c>
       <c r="F247" t="n">
         <v>1.4545</v>
@@ -40452,7 +40452,7 @@
         <v>1.0764</v>
       </c>
       <c r="I247" t="n">
-        <v>1.765</v>
+        <v>1.7651</v>
       </c>
       <c r="J247" t="n">
         <v>0.6116</v>
@@ -40486,7 +40486,7 @@
         <v>1.0764</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8805</v>
+        <v>1.8806</v>
       </c>
       <c r="J248" t="n">
         <v>0.6299</v>
@@ -40520,7 +40520,7 @@
         <v>1.0764</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9473</v>
+        <v>1.9474</v>
       </c>
       <c r="J249" t="n">
         <v>0.6906</v>
@@ -40554,7 +40554,7 @@
         <v>1.1028</v>
       </c>
       <c r="I250" t="n">
-        <v>2.0132</v>
+        <v>2.0133</v>
       </c>
       <c r="J250" t="n">
         <v>0.6244</v>
@@ -40588,7 +40588,7 @@
         <v>1.1028</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1877</v>
+        <v>2.1878</v>
       </c>
       <c r="J251" t="n">
         <v>0.6385999999999999</v>
@@ -40622,7 +40622,7 @@
         <v>1.1028</v>
       </c>
       <c r="I252" t="n">
-        <v>2.3143</v>
+        <v>2.3144</v>
       </c>
       <c r="J252" t="n">
         <v>0.6209</v>
@@ -40644,7 +40644,7 @@
         <v>0.0331</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9264</v>
+        <v>0.9265</v>
       </c>
       <c r="F253" t="n">
         <v>0.0331</v>
@@ -40703,7 +40703,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8383</v>
+        <v>0.8384</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40724,7 +40724,7 @@
         <v>1.1306</v>
       </c>
       <c r="I255" t="n">
-        <v>2.5226</v>
+        <v>2.5227</v>
       </c>
       <c r="J255" t="n">
         <v>0.5629999999999999</v>
@@ -40737,7 +40737,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8169</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40758,7 +40758,7 @@
         <v>1.0016</v>
       </c>
       <c r="I256" t="n">
-        <v>2.5459</v>
+        <v>2.546</v>
       </c>
       <c r="J256" t="n">
         <v>0.6111</v>
@@ -40792,7 +40792,7 @@
         <v>1.0016</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6724</v>
+        <v>2.6725</v>
       </c>
       <c r="J257" t="n">
         <v>0.4767</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0133</v>
+        <v>3.0134</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40894,7 +40894,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0028</v>
+        <v>3.0029</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40907,13 +40907,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9462</v>
+        <v>0.9459</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9462</v>
+        <v>0.9459</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40922,7 +40922,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.0028</v>
+        <v>3.0016</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.378</v>
+        <v>1.382</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.634</v>
+        <v>1.638</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.12</v>
+        <v>2.122</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.855</v>
+        <v>2.857</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.998</v>
+        <v>4</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.602</v>
+        <v>-0.598</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.064</v>
+        <v>-0.061</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.056</v>
+        <v>1.058</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66439.21000000001</v>
+        <v>66402.78599999999</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3776</v>
+        <v>1.3815</v>
       </c>
       <c r="D261" t="n">
-        <v>1.6342</v>
+        <v>1.6376</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1199</v>
+        <v>2.1222</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8548</v>
+        <v>2.8569</v>
       </c>
       <c r="G261" t="n">
-        <v>3.9978</v>
+        <v>4.0003</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.6017</v>
+        <v>-0.5978</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.0644</v>
+        <v>-0.0614</v>
       </c>
       <c r="M261" t="n">
-        <v>1.056</v>
+        <v>1.0581</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66439.21000000001</v>
+        <v>66402.78630000001</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -33937,7 +33937,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.2467</v>
+        <v>-1.2468</v>
       </c>
       <c r="C56" t="n">
         <v>1.0216</v>
@@ -34060,7 +34060,7 @@
         <v>-2.6707</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.1036</v>
+        <v>-1.1037</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8167</v>
@@ -34604,7 +34604,7 @@
         <v>-1.1798</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2116</v>
+        <v>-1.2117</v>
       </c>
       <c r="J75" t="n">
         <v>-1.811</v>
@@ -34638,7 +34638,7 @@
         <v>-0.7546</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2419</v>
+        <v>-1.242</v>
       </c>
       <c r="J76" t="n">
         <v>-1.702</v>
@@ -34740,7 +34740,7 @@
         <v>-0.6889999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2703</v>
+        <v>-1.2704</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5321</v>
@@ -34842,7 +34842,7 @@
         <v>-0.6012999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3336</v>
+        <v>-1.3337</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3458</v>
@@ -35114,7 +35114,7 @@
         <v>-0.5234</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2894</v>
+        <v>-1.2895</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9147999999999999</v>
@@ -35148,7 +35148,7 @@
         <v>-0.389</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2915</v>
+        <v>-1.2916</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9429999999999999</v>
@@ -35182,7 +35182,7 @@
         <v>-0.389</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2954</v>
+        <v>-1.2955</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8282</v>
@@ -38582,7 +38582,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0503</v>
+        <v>-0.0502</v>
       </c>
       <c r="J192" t="n">
         <v>1.0402</v>
@@ -38638,7 +38638,7 @@
         <v>0.1212</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1799</v>
+        <v>0.18</v>
       </c>
       <c r="F194" t="n">
         <v>0.1212</v>
@@ -38820,7 +38820,7 @@
         <v>-0.1683</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2795</v>
+        <v>0.2796</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6688</v>
@@ -38969,7 +38969,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.2951</v>
+        <v>0.2952</v>
       </c>
       <c r="C204" t="n">
         <v>-0.3445</v>
@@ -39262,7 +39262,7 @@
         <v>0.5324</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7922</v>
+        <v>0.7923</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1272</v>
@@ -39466,7 +39466,7 @@
         <v>0.6974</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7284</v>
+        <v>0.7285</v>
       </c>
       <c r="J218" t="n">
         <v>0.1381</v>
@@ -39488,7 +39488,7 @@
         <v>1.6766</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6531</v>
+        <v>0.6532</v>
       </c>
       <c r="F219" t="n">
         <v>1.6766</v>
@@ -39636,7 +39636,7 @@
         <v>0.8441</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0448</v>
+        <v>1.0449</v>
       </c>
       <c r="J223" t="n">
         <v>0.3667</v>
@@ -39738,7 +39738,7 @@
         <v>0.9485</v>
       </c>
       <c r="I226" t="n">
-        <v>1.2201</v>
+        <v>1.2202</v>
       </c>
       <c r="J226" t="n">
         <v>0.357</v>
@@ -40010,7 +40010,7 @@
         <v>1.1463</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6667</v>
+        <v>1.6668</v>
       </c>
       <c r="J234" t="n">
         <v>0.4744</v>
@@ -40032,7 +40032,7 @@
         <v>1.3367</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0258</v>
+        <v>1.0259</v>
       </c>
       <c r="F235" t="n">
         <v>1.3367</v>
@@ -40112,7 +40112,7 @@
         <v>1.1415</v>
       </c>
       <c r="I237" t="n">
-        <v>1.559</v>
+        <v>1.5591</v>
       </c>
       <c r="J237" t="n">
         <v>0.5194</v>
@@ -40384,7 +40384,7 @@
         <v>1.1744</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6398</v>
+        <v>1.6399</v>
       </c>
       <c r="J245" t="n">
         <v>0.6108</v>
@@ -40418,7 +40418,7 @@
         <v>1.1744</v>
       </c>
       <c r="I246" t="n">
-        <v>1.7355</v>
+        <v>1.7356</v>
       </c>
       <c r="J246" t="n">
         <v>0.6894</v>
@@ -40576,7 +40576,7 @@
         <v>1.236</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9171</v>
+        <v>0.9172</v>
       </c>
       <c r="F251" t="n">
         <v>1.236</v>
@@ -40656,7 +40656,7 @@
         <v>1.1306</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3394</v>
+        <v>2.3395</v>
       </c>
       <c r="J253" t="n">
         <v>0.6147</v>
@@ -40690,7 +40690,7 @@
         <v>1.1306</v>
       </c>
       <c r="I254" t="n">
-        <v>2.4456</v>
+        <v>2.4457</v>
       </c>
       <c r="J254" t="n">
         <v>0.5955</v>
@@ -40826,7 +40826,7 @@
         <v>1.0016</v>
       </c>
       <c r="I258" t="n">
-        <v>2.8224</v>
+        <v>2.8225</v>
       </c>
       <c r="J258" t="n">
         <v>0.57</v>
@@ -40860,7 +40860,7 @@
         <v>1.0772</v>
       </c>
       <c r="I259" t="n">
-        <v>3.0134</v>
+        <v>3.0135</v>
       </c>
       <c r="J259" t="n">
         <v>0.548</v>
@@ -40907,13 +40907,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9459</v>
+        <v>0.9457</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9459</v>
+        <v>0.9457</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40922,7 +40922,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.0016</v>
+        <v>3.0009</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.382</v>
+        <v>1.39</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.638</v>
+        <v>1.644</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.122</v>
+        <v>2.128</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.857</v>
+        <v>2.861</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4</v>
+        <v>4.005</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.598</v>
+        <v>-0.589</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.061</v>
+        <v>-0.055</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.058</v>
+        <v>1.063</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.31</v>
+        <v>-1.32</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66402.78599999999</v>
+        <v>66394.514</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3815</v>
+        <v>1.3901</v>
       </c>
       <c r="D261" t="n">
-        <v>1.6376</v>
+        <v>1.6438</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1222</v>
+        <v>2.1278</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8569</v>
+        <v>2.8614</v>
       </c>
       <c r="G261" t="n">
-        <v>4.0003</v>
+        <v>4.0049</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.5978</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.0614</v>
+        <v>-0.0554</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0581</v>
+        <v>1.0626</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66402.78630000001</v>
+        <v>66394.5141</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -35522,7 +35522,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7405</v>
+        <v>-0.7406</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4062</v>
@@ -36168,7 +36168,7 @@
         <v>0.3328</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0717</v>
+        <v>-0.0718</v>
       </c>
       <c r="J121" t="n">
         <v>-0.0892</v>
@@ -38548,7 +38548,7 @@
         <v>-0.7002</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.095</v>
+        <v>-0.0949</v>
       </c>
       <c r="J191" t="n">
         <v>1.3067</v>
@@ -39840,7 +39840,7 @@
         <v>1.0464</v>
       </c>
       <c r="I229" t="n">
-        <v>1.25</v>
+        <v>1.2501</v>
       </c>
       <c r="J229" t="n">
         <v>0.3836</v>
@@ -40848,7 +40848,7 @@
         <v>0.3237</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9488</v>
+        <v>0.9489</v>
       </c>
       <c r="F259" t="n">
         <v>0.3237</v>
@@ -40922,7 +40922,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.0009</v>
+        <v>3.0008</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.39</v>
+        <v>1.394</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.644</v>
+        <v>1.647</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.128</v>
+        <v>2.131</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.861</v>
+        <v>2.863</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.005</v>
+        <v>4.007</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.589</v>
+        <v>-0.585</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.055</v>
+        <v>-0.052</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.063</v>
+        <v>1.065</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66394.514</v>
+        <v>66379.929</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -31932,19 +31932,19 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>1.3901</v>
+        <v>1.394</v>
       </c>
       <c r="D261" t="n">
-        <v>1.6438</v>
+        <v>1.6467</v>
       </c>
       <c r="E261" t="n">
-        <v>2.1278</v>
+        <v>2.1308</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8614</v>
+        <v>2.8633</v>
       </c>
       <c r="G261" t="n">
-        <v>4.0049</v>
+        <v>4.0068</v>
       </c>
       <c r="H261" t="n">
         <v>1.9793</v>
@@ -31956,13 +31956,13 @@
         <v>1.7988</v>
       </c>
       <c r="K261" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.5853</v>
       </c>
       <c r="L261" t="n">
-        <v>-0.0554</v>
+        <v>-0.0524</v>
       </c>
       <c r="M261" t="n">
-        <v>1.0626</v>
+        <v>1.0645</v>
       </c>
       <c r="N261" t="n">
         <v>-0.9792999999999999</v>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66394.5141</v>
+        <v>66379.9289</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -32169,7 +32169,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.5672</v>
+        <v>-0.5673</v>
       </c>
       <c r="C4" t="n">
         <v>-0.068</v>
@@ -33427,7 +33427,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.5225</v>
+        <v>-0.5226</v>
       </c>
       <c r="C41" t="n">
         <v>-0.2821</v>
@@ -33810,7 +33810,7 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1849</v>
+        <v>-1.185</v>
       </c>
       <c r="F52" t="n">
         <v>0.06950000000000001</v>
@@ -35454,7 +35454,7 @@
         <v>-0.1655</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9232</v>
+        <v>-0.9233</v>
       </c>
       <c r="J100" t="n">
         <v>-0.5014</v>
@@ -38468,7 +38468,7 @@
         <v>0.2499</v>
       </c>
       <c r="E189" t="n">
-        <v>0.3238</v>
+        <v>0.3239</v>
       </c>
       <c r="F189" t="n">
         <v>0.2499</v>
@@ -38956,7 +38956,7 @@
         <v>0.091</v>
       </c>
       <c r="I203" t="n">
-        <v>0.397</v>
+        <v>0.3971</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5065</v>
@@ -40894,7 +40894,7 @@
         <v>1.0772</v>
       </c>
       <c r="I260" t="n">
-        <v>3.0029</v>
+        <v>3.003</v>
       </c>
       <c r="J260" t="n">
         <v>0.548</v>
@@ -40907,13 +40907,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9457</v>
+        <v>0.9456</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9457</v>
+        <v>0.9456</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8431999999999999</v>
@@ -40922,7 +40922,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.0008</v>
+        <v>3.0005</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66379.929</v>
+        <v>66381.27800000001</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z261" t="n">
-        <v>66379.9289</v>
+        <v>66381.2779</v>
       </c>
       <c r="AA261" t="n">
         <v>162.3295</v>
@@ -40922,7 +40922,7 @@
         <v>1.0772</v>
       </c>
       <c r="I261" t="n">
-        <v>3.0005</v>
+        <v>3.0006</v>
       </c>
       <c r="J261" t="n">
         <v>0.548</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.93</t>
+          <t>+0.92</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-0.515</v>
+        <v>-0.514</v>
       </c>
     </row>
     <row r="9">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-0.468</v>
+        <v>-0.467</v>
       </c>
     </row>
     <row r="14">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-0.446</v>
+        <v>-0.445</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>-0.423</v>
+        <v>-0.422</v>
       </c>
     </row>
     <row r="22">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.93 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.92 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.00%. The real policy rate is about -0.98%, roughly 0.62pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>-0.635</v>
+        <v>-0.636</v>
       </c>
     </row>
     <row r="49">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.8129999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>-1.246</v>
+        <v>-1.247</v>
       </c>
     </row>
     <row r="59">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>-1.283</v>
+        <v>-1.284</v>
       </c>
     </row>
     <row r="60">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>-1.15</v>
+        <v>-1.151</v>
       </c>
     </row>
     <row r="70">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.9419999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>-0.666</v>
+        <v>-0.667</v>
       </c>
     </row>
     <row r="82">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>-0.508</v>
+        <v>-0.509</v>
       </c>
     </row>
     <row r="89">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>-0.507</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="91">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>-0.337</v>
+        <v>-0.338</v>
       </c>
     </row>
     <row r="97">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>-0.236</v>
+        <v>-0.237</v>
       </c>
     </row>
     <row r="98">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="108">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="125">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="127">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>0.607</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="155">
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>0.639</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="158">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="166">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="198">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="J203" t="n">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="204">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="213">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="J213" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="214">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>0.883</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="216">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="218">
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>0.904</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="219">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>0.852</v>
+        <v>0.853</v>
       </c>
     </row>
     <row r="220">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>0.977</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="224">
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>0.97</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="227">
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>0.958</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="229">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>0.975</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="231">
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>1.071</v>
+        <v>1.072</v>
       </c>
     </row>
     <row r="233">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>1.03</v>
+        <v>1.031</v>
       </c>
     </row>
     <row r="234">
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>1.053</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="235">
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>1.08</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="236">
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>1.011</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="241">
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>1.028</v>
+        <v>1.029</v>
       </c>
     </row>
     <row r="243">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="J245" t="n">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="246">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="249">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="250">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>0.979</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="253">
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="254">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>0.83</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="256">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="257">
@@ -3432,7 +3432,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="258">
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="J258" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="259">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="260">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.83</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="261">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="262">
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -4197,11 +4197,11 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66377.81</v>
+        <v>66215.34</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -4225,11 +4225,11 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>162.329</v>
+        <v>158.848</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -32014,7 +32014,7 @@
         <v>66377.81050000001</v>
       </c>
       <c r="AA261" t="n">
-        <v>162.3295</v>
+        <v>158.8476</v>
       </c>
       <c r="AB261" t="n">
         <v>3.1152</v>
@@ -32117,10 +32117,10 @@
         <v>3957.6278</v>
       </c>
       <c r="Z262" t="n">
-        <v>66377.81050000001</v>
+        <v>66215.34</v>
       </c>
       <c r="AA262" t="n">
-        <v>162.3295</v>
+        <v>158.8476</v>
       </c>
       <c r="AB262" t="n">
         <v>3.1152</v>
@@ -32319,7 +32319,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5399</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="C5" t="n">
         <v>-0.0692</v>
@@ -32340,7 +32340,7 @@
         <v>-0.3807</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.547</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5197</v>
@@ -32353,7 +32353,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5118</v>
+        <v>-0.5117</v>
       </c>
       <c r="C6" t="n">
         <v>-0.0915</v>
@@ -32374,7 +32374,7 @@
         <v>-0.3807</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5365</v>
+        <v>-0.5364</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4262</v>
@@ -32408,7 +32408,7 @@
         <v>-0.3462</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4907</v>
+        <v>-0.4905</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5169</v>
@@ -32421,7 +32421,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.5145</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2175</v>
@@ -32430,7 +32430,7 @@
         <v>0.1284</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6753</v>
+        <v>-0.6752</v>
       </c>
       <c r="F8" t="n">
         <v>0.1284</v>
@@ -32442,7 +32442,7 @@
         <v>-0.3462</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.412</v>
+        <v>-0.4117</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3664</v>
@@ -32476,7 +32476,7 @@
         <v>-0.3462</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4155</v>
+        <v>-0.4152</v>
       </c>
       <c r="J9" t="n">
         <v>-1.398</v>
@@ -32489,7 +32489,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.4918</v>
+        <v>-0.4917</v>
       </c>
       <c r="C10" t="n">
         <v>-0.2832</v>
@@ -32510,7 +32510,7 @@
         <v>-0.2239</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3909</v>
+        <v>-0.3906</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2524</v>
@@ -32523,7 +32523,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.5004</v>
+        <v>-0.5003</v>
       </c>
       <c r="C11" t="n">
         <v>-0.3532</v>
@@ -32532,7 +32532,7 @@
         <v>0.1039</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6515</v>
+        <v>-0.6514</v>
       </c>
       <c r="F11" t="n">
         <v>0.1039</v>
@@ -32544,7 +32544,7 @@
         <v>-0.2239</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3074</v>
+        <v>-0.3069</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2897</v>
@@ -32557,7 +32557,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.4743</v>
+        <v>-0.4741</v>
       </c>
       <c r="C12" t="n">
         <v>-0.3965</v>
@@ -32566,7 +32566,7 @@
         <v>0.101</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6181</v>
+        <v>-0.6179</v>
       </c>
       <c r="F12" t="n">
         <v>0.101</v>
@@ -32578,7 +32578,7 @@
         <v>-0.2239</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2115</v>
+        <v>-0.2108</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2144</v>
@@ -32591,7 +32591,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.4675</v>
+        <v>-0.4674</v>
       </c>
       <c r="C13" t="n">
         <v>-0.3974</v>
@@ -32600,7 +32600,7 @@
         <v>0.1008</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6096</v>
+        <v>-0.6095</v>
       </c>
       <c r="F13" t="n">
         <v>0.1008</v>
@@ -32612,7 +32612,7 @@
         <v>-0.1869</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1887</v>
+        <v>-0.1881</v>
       </c>
       <c r="J13" t="n">
         <v>-1.2048</v>
@@ -32625,7 +32625,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4724</v>
+        <v>-0.4723</v>
       </c>
       <c r="C14" t="n">
         <v>-0.3666</v>
@@ -32634,7 +32634,7 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6147</v>
+        <v>-0.6146</v>
       </c>
       <c r="F14" t="n">
         <v>0.09669999999999999</v>
@@ -32646,7 +32646,7 @@
         <v>-0.1869</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2205</v>
+        <v>-0.22</v>
       </c>
       <c r="J14" t="n">
         <v>-1.1566</v>
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.4597</v>
+        <v>-0.4596</v>
       </c>
       <c r="C15" t="n">
         <v>-0.4095</v>
@@ -32668,7 +32668,7 @@
         <v>0.1058</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6011</v>
+        <v>-0.601</v>
       </c>
       <c r="F15" t="n">
         <v>0.1058</v>
@@ -32680,7 +32680,7 @@
         <v>-0.1869</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1602</v>
+        <v>-0.1596</v>
       </c>
       <c r="J15" t="n">
         <v>-1.1332</v>
@@ -32693,7 +32693,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.4352</v>
+        <v>-0.4351</v>
       </c>
       <c r="C16" t="n">
         <v>-0.4508</v>
@@ -32702,7 +32702,7 @@
         <v>0.0902</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5665</v>
+        <v>-0.5664</v>
       </c>
       <c r="F16" t="n">
         <v>0.0902</v>
@@ -32714,7 +32714,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1622</v>
+        <v>-0.1616</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0288</v>
@@ -32727,7 +32727,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.4622</v>
+        <v>-0.462</v>
       </c>
       <c r="C17" t="n">
         <v>-0.4753</v>
@@ -32736,7 +32736,7 @@
         <v>-0.0541</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5642</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>-0.0541</v>
@@ -32748,7 +32748,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1397</v>
+        <v>-0.1391</v>
       </c>
       <c r="J17" t="n">
         <v>-1.024</v>
@@ -32761,7 +32761,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.4789</v>
+        <v>-0.4788</v>
       </c>
       <c r="C18" t="n">
         <v>-0.5001</v>
@@ -32770,7 +32770,7 @@
         <v>-0.031</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5909</v>
+        <v>-0.5908</v>
       </c>
       <c r="F18" t="n">
         <v>-0.031</v>
@@ -32782,7 +32782,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2202</v>
+        <v>-0.2198</v>
       </c>
       <c r="J18" t="n">
         <v>-0.9921</v>
@@ -32795,7 +32795,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.4456</v>
+        <v>-0.4455</v>
       </c>
       <c r="C19" t="n">
         <v>-0.4789</v>
@@ -32804,7 +32804,7 @@
         <v>0.0359</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5659</v>
+        <v>-0.5658</v>
       </c>
       <c r="F19" t="n">
         <v>0.0359</v>
@@ -32816,7 +32816,7 @@
         <v>-0.1201</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1878</v>
+        <v>-0.1873</v>
       </c>
       <c r="J19" t="n">
         <v>-0.8633</v>
@@ -32829,7 +32829,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.449</v>
+        <v>-0.4489</v>
       </c>
       <c r="C20" t="n">
         <v>-0.2827</v>
@@ -32838,7 +32838,7 @@
         <v>0.0136</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5647</v>
+        <v>-0.5646</v>
       </c>
       <c r="F20" t="n">
         <v>0.0136</v>
@@ -32850,7 +32850,7 @@
         <v>-0.1201</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1492</v>
+        <v>-0.1487</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8303</v>
@@ -32863,7 +32863,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.4225</v>
+        <v>-0.4224</v>
       </c>
       <c r="C21" t="n">
         <v>-0.3155</v>
@@ -32872,7 +32872,7 @@
         <v>0.1089</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5554</v>
+        <v>-0.5552</v>
       </c>
       <c r="F21" t="n">
         <v>0.1089</v>
@@ -32884,7 +32884,7 @@
         <v>-0.1201</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1206</v>
+        <v>-0.12</v>
       </c>
       <c r="J21" t="n">
         <v>-0.7752</v>
@@ -32897,7 +32897,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3692</v>
+        <v>-0.3691</v>
       </c>
       <c r="C22" t="n">
         <v>-0.2635</v>
@@ -32906,7 +32906,7 @@
         <v>0.1092</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4889</v>
+        <v>-0.4887</v>
       </c>
       <c r="F22" t="n">
         <v>0.1092</v>
@@ -32918,7 +32918,7 @@
         <v>0.0916</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1001</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>-0.7529</v>
@@ -32931,7 +32931,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3964</v>
+        <v>-0.3963</v>
       </c>
       <c r="C23" t="n">
         <v>-0.3</v>
@@ -32940,7 +32940,7 @@
         <v>0.0243</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5016</v>
+        <v>-0.5014</v>
       </c>
       <c r="F23" t="n">
         <v>0.0243</v>
@@ -32952,7 +32952,7 @@
         <v>0.0916</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0564</v>
+        <v>-0.0558</v>
       </c>
       <c r="J23" t="n">
         <v>-0.721</v>
@@ -32965,7 +32965,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3622</v>
+        <v>-0.362</v>
       </c>
       <c r="C24" t="n">
         <v>-0.3018</v>
@@ -32974,7 +32974,7 @@
         <v>0.0527</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4659</v>
+        <v>-0.4657</v>
       </c>
       <c r="F24" t="n">
         <v>0.0527</v>
@@ -32986,7 +32986,7 @@
         <v>0.0916</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0621</v>
+        <v>-0.0615</v>
       </c>
       <c r="J24" t="n">
         <v>-0.5664</v>
@@ -32999,7 +32999,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3366</v>
+        <v>-0.3365</v>
       </c>
       <c r="C25" t="n">
         <v>-0.2463</v>
@@ -33008,7 +33008,7 @@
         <v>0.0983</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4453</v>
+        <v>-0.4452</v>
       </c>
       <c r="F25" t="n">
         <v>0.0983</v>
@@ -33020,7 +33020,7 @@
         <v>0.1733</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0422</v>
+        <v>-0.0416</v>
       </c>
       <c r="J25" t="n">
         <v>-0.5352</v>
@@ -33033,7 +33033,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.35</v>
+        <v>-0.3499</v>
       </c>
       <c r="C26" t="n">
         <v>-0.3078</v>
@@ -33042,7 +33042,7 @@
         <v>-0.0387</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4279</v>
+        <v>-0.4277</v>
       </c>
       <c r="F26" t="n">
         <v>-0.0387</v>
@@ -33054,7 +33054,7 @@
         <v>0.1733</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0237</v>
+        <v>0.0244</v>
       </c>
       <c r="J26" t="n">
         <v>-0.4942</v>
@@ -33067,7 +33067,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3814</v>
+        <v>-0.3812</v>
       </c>
       <c r="C27" t="n">
         <v>-0.0248</v>
@@ -33076,7 +33076,7 @@
         <v>-0.0774</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4574</v>
+        <v>-0.4572</v>
       </c>
       <c r="F27" t="n">
         <v>-0.0774</v>
@@ -33088,7 +33088,7 @@
         <v>0.1733</v>
       </c>
       <c r="I27" t="n">
-        <v>0.056</v>
+        <v>0.0567</v>
       </c>
       <c r="J27" t="n">
         <v>-0.5547</v>
@@ -33101,7 +33101,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4037</v>
+        <v>-0.4036</v>
       </c>
       <c r="C28" t="n">
         <v>0.0306</v>
@@ -33110,7 +33110,7 @@
         <v>-0.1715</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4618</v>
+        <v>-0.4616</v>
       </c>
       <c r="F28" t="n">
         <v>-0.1715</v>
@@ -33122,7 +33122,7 @@
         <v>0.1317</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0057</v>
+        <v>0.0063</v>
       </c>
       <c r="J28" t="n">
         <v>-0.4281</v>
@@ -33135,7 +33135,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3942</v>
+        <v>-0.3941</v>
       </c>
       <c r="C29" t="n">
         <v>-0.0319</v>
@@ -33144,7 +33144,7 @@
         <v>-0.0901</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4702</v>
+        <v>-0.4701</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0901</v>
@@ -33156,7 +33156,7 @@
         <v>0.1317</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0541</v>
+        <v>0.0548</v>
       </c>
       <c r="J29" t="n">
         <v>-0.465</v>
@@ -33169,7 +33169,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3808</v>
+        <v>-0.3807</v>
       </c>
       <c r="C30" t="n">
         <v>-0.0653</v>
@@ -33178,7 +33178,7 @@
         <v>-0.1164</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4469</v>
+        <v>-0.4467</v>
       </c>
       <c r="F30" t="n">
         <v>-0.1164</v>
@@ -33190,7 +33190,7 @@
         <v>0.1317</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0847</v>
+        <v>0.0854</v>
       </c>
       <c r="J30" t="n">
         <v>-0.3403</v>
@@ -33203,7 +33203,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3671</v>
+        <v>-0.367</v>
       </c>
       <c r="C31" t="n">
         <v>-0.08649999999999999</v>
@@ -33212,7 +33212,7 @@
         <v>-0.1817</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4135</v>
+        <v>-0.4133</v>
       </c>
       <c r="F31" t="n">
         <v>-0.1817</v>
@@ -33224,7 +33224,7 @@
         <v>0.2291</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1322</v>
+        <v>0.133</v>
       </c>
       <c r="J31" t="n">
         <v>-0.3408</v>
@@ -33237,7 +33237,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3551</v>
+        <v>-0.3549</v>
       </c>
       <c r="C32" t="n">
         <v>-0.0707</v>
@@ -33246,7 +33246,7 @@
         <v>-0.1743</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4003</v>
+        <v>-0.4001</v>
       </c>
       <c r="F32" t="n">
         <v>-0.1743</v>
@@ -33258,7 +33258,7 @@
         <v>0.2291</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0796</v>
+        <v>0.0804</v>
       </c>
       <c r="J32" t="n">
         <v>-0.2256</v>
@@ -33271,7 +33271,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3603</v>
+        <v>-0.3601</v>
       </c>
       <c r="C33" t="n">
         <v>-0.1744</v>
@@ -33280,7 +33280,7 @@
         <v>-0.1093</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.423</v>
+        <v>-0.4229</v>
       </c>
       <c r="F33" t="n">
         <v>-0.1093</v>
@@ -33292,7 +33292,7 @@
         <v>0.2291</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0466</v>
+        <v>-0.0461</v>
       </c>
       <c r="J33" t="n">
         <v>-0.1822</v>
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4331</v>
+        <v>-0.433</v>
       </c>
       <c r="C34" t="n">
         <v>-0.1655</v>
@@ -33314,7 +33314,7 @@
         <v>-0.0979</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5169</v>
+        <v>-0.5168</v>
       </c>
       <c r="F34" t="n">
         <v>-0.0979</v>
@@ -33326,7 +33326,7 @@
         <v>-0.2291</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>-0.0413</v>
@@ -33339,7 +33339,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4167</v>
+        <v>-0.4166</v>
       </c>
       <c r="C35" t="n">
         <v>-0.1623</v>
@@ -33348,7 +33348,7 @@
         <v>-0.0022</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5204</v>
+        <v>-0.5202</v>
       </c>
       <c r="F35" t="n">
         <v>-0.0022</v>
@@ -33360,7 +33360,7 @@
         <v>-0.2291</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1033</v>
+        <v>-0.1028</v>
       </c>
       <c r="J35" t="n">
         <v>0.0192</v>
@@ -33373,7 +33373,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3918</v>
+        <v>-0.3917</v>
       </c>
       <c r="C36" t="n">
         <v>-0.244</v>
@@ -33394,7 +33394,7 @@
         <v>-0.2291</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2406</v>
+        <v>-0.2403</v>
       </c>
       <c r="J36" t="n">
         <v>0.0668</v>
@@ -33407,7 +33407,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.3865</v>
+        <v>-0.3864</v>
       </c>
       <c r="C37" t="n">
         <v>-0.1966</v>
@@ -33416,7 +33416,7 @@
         <v>0.487</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6048</v>
+        <v>-0.6047</v>
       </c>
       <c r="F37" t="n">
         <v>0.487</v>
@@ -33428,7 +33428,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2443</v>
+        <v>-0.2439</v>
       </c>
       <c r="J37" t="n">
         <v>0.1554</v>
@@ -33450,7 +33450,7 @@
         <v>0.4011</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6443</v>
+        <v>-0.6442</v>
       </c>
       <c r="F38" t="n">
         <v>0.4011</v>
@@ -33462,7 +33462,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3793</v>
+        <v>-0.3791</v>
       </c>
       <c r="J38" t="n">
         <v>0.2096</v>
@@ -33484,7 +33484,7 @@
         <v>0.4918</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.637</v>
+        <v>-0.6369</v>
       </c>
       <c r="F39" t="n">
         <v>0.4918</v>
@@ -33496,7 +33496,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4244</v>
+        <v>-0.4242</v>
       </c>
       <c r="J39" t="n">
         <v>0.2367</v>
@@ -33518,7 +33518,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.7688</v>
+        <v>-0.7689</v>
       </c>
       <c r="F40" t="n">
         <v>0.6104000000000001</v>
@@ -33530,7 +33530,7 @@
         <v>-1.0608</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5642</v>
       </c>
       <c r="J40" t="n">
         <v>0.3596</v>
@@ -33564,7 +33564,7 @@
         <v>-1.0608</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5607</v>
+        <v>-0.5608</v>
       </c>
       <c r="J41" t="n">
         <v>0.3749</v>
@@ -33632,7 +33632,7 @@
         <v>-1.425</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.526</v>
+        <v>-0.5259</v>
       </c>
       <c r="J43" t="n">
         <v>0.5421</v>
@@ -33645,7 +33645,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.4285</v>
+        <v>-0.4284</v>
       </c>
       <c r="C44" t="n">
         <v>-0.2935</v>
@@ -33666,7 +33666,7 @@
         <v>-1.425</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5648</v>
+        <v>-0.5647</v>
       </c>
       <c r="J44" t="n">
         <v>0.5810999999999999</v>
@@ -33679,7 +33679,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4096</v>
+        <v>-0.4095</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3257</v>
@@ -33688,7 +33688,7 @@
         <v>1.0381</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.7715</v>
+        <v>-0.7714</v>
       </c>
       <c r="F45" t="n">
         <v>1.0381</v>
@@ -33700,7 +33700,7 @@
         <v>-1.425</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5601</v>
+        <v>-0.5599</v>
       </c>
       <c r="J45" t="n">
         <v>0.7406</v>
@@ -33713,7 +33713,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4892</v>
+        <v>-0.4891</v>
       </c>
       <c r="C46" t="n">
         <v>-0.3034</v>
@@ -33734,7 +33734,7 @@
         <v>-1.7882</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6504</v>
+        <v>-0.6503</v>
       </c>
       <c r="J46" t="n">
         <v>0.7887</v>
@@ -33768,7 +33768,7 @@
         <v>-1.7882</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8488</v>
+        <v>-0.849</v>
       </c>
       <c r="J47" t="n">
         <v>0.7399</v>
@@ -33790,7 +33790,7 @@
         <v>0.4544</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.9079</v>
+        <v>-0.908</v>
       </c>
       <c r="F48" t="n">
         <v>0.4544</v>
@@ -33802,7 +33802,7 @@
         <v>-1.7882</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9288</v>
+        <v>-0.9291</v>
       </c>
       <c r="J48" t="n">
         <v>0.7819</v>
@@ -33815,7 +33815,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8136</v>
+        <v>-0.8137</v>
       </c>
       <c r="C49" t="n">
         <v>-0.1283</v>
@@ -33824,7 +33824,7 @@
         <v>-0.0877</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.9951</v>
+        <v>-0.9953</v>
       </c>
       <c r="F49" t="n">
         <v>-0.0877</v>
@@ -33836,7 +33836,7 @@
         <v>-2.2537</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0476</v>
+        <v>-1.0482</v>
       </c>
       <c r="J49" t="n">
         <v>0.9823</v>
@@ -33849,7 +33849,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.8124</v>
+        <v>-0.8125</v>
       </c>
       <c r="C50" t="n">
         <v>0.0205</v>
@@ -33858,7 +33858,7 @@
         <v>0.1314</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.0483</v>
+        <v>-1.0485</v>
       </c>
       <c r="F50" t="n">
         <v>0.1314</v>
@@ -33870,7 +33870,7 @@
         <v>-2.2537</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0934</v>
+        <v>-1.0941</v>
       </c>
       <c r="J50" t="n">
         <v>0.7637</v>
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.8314</v>
+        <v>-0.8315</v>
       </c>
       <c r="C51" t="n">
         <v>0.2917</v>
@@ -33892,7 +33892,7 @@
         <v>0.1171</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0685</v>
+        <v>-1.0686</v>
       </c>
       <c r="F51" t="n">
         <v>0.1171</v>
@@ -33904,7 +33904,7 @@
         <v>-2.2537</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1046</v>
+        <v>-1.1051</v>
       </c>
       <c r="J51" t="n">
         <v>0.6063</v>
@@ -33917,7 +33917,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-0.9331</v>
       </c>
       <c r="C52" t="n">
         <v>0.4357</v>
@@ -33926,7 +33926,7 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.1837</v>
+        <v>-1.1838</v>
       </c>
       <c r="F52" t="n">
         <v>0.06950000000000001</v>
@@ -33938,7 +33938,7 @@
         <v>-2.717</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0134</v>
+        <v>-1.0137</v>
       </c>
       <c r="J52" t="n">
         <v>0.4723</v>
@@ -33972,7 +33972,7 @@
         <v>-2.717</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9875</v>
+        <v>-0.9877</v>
       </c>
       <c r="J53" t="n">
         <v>0.1885</v>
@@ -33985,7 +33985,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.0576</v>
+        <v>-1.0577</v>
       </c>
       <c r="C54" t="n">
         <v>0.8923</v>
@@ -33994,7 +33994,7 @@
         <v>-0.3301</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.2395</v>
+        <v>-1.2396</v>
       </c>
       <c r="F54" t="n">
         <v>-0.3301</v>
@@ -34006,7 +34006,7 @@
         <v>-2.717</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0134</v>
+        <v>-1.0137</v>
       </c>
       <c r="J54" t="n">
         <v>0.1057</v>
@@ -34019,7 +34019,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1585</v>
+        <v>-1.1586</v>
       </c>
       <c r="C55" t="n">
         <v>1.0633</v>
@@ -34028,7 +34028,7 @@
         <v>-0.5716</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.3052</v>
+        <v>-1.3053</v>
       </c>
       <c r="F55" t="n">
         <v>-0.5716</v>
@@ -34040,7 +34040,7 @@
         <v>-2.9765</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9885</v>
+        <v>-0.9888</v>
       </c>
       <c r="J55" t="n">
         <v>-0.024</v>
@@ -34053,7 +34053,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.2463</v>
+        <v>-1.2464</v>
       </c>
       <c r="C56" t="n">
         <v>1.0216</v>
@@ -34062,7 +34062,7 @@
         <v>-0.8158</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.3539</v>
+        <v>-1.354</v>
       </c>
       <c r="F56" t="n">
         <v>-0.8158</v>
@@ -34074,7 +34074,7 @@
         <v>-2.9765</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0435</v>
+        <v>-1.0439</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2474</v>
@@ -34087,7 +34087,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2971</v>
+        <v>-1.2972</v>
       </c>
       <c r="C57" t="n">
         <v>1.0128</v>
@@ -34096,7 +34096,7 @@
         <v>-0.8938</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.398</v>
+        <v>-1.3981</v>
       </c>
       <c r="F57" t="n">
         <v>-0.8938</v>
@@ -34108,7 +34108,7 @@
         <v>-2.9765</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0063</v>
+        <v>-1.0068</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4425</v>
@@ -34121,7 +34121,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.2464</v>
+        <v>-1.2465</v>
       </c>
       <c r="C58" t="n">
         <v>0.9933</v>
@@ -34130,7 +34130,7 @@
         <v>-0.8337</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.3496</v>
+        <v>-1.3497</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8337</v>
@@ -34142,7 +34142,7 @@
         <v>-2.674</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0835</v>
+        <v>-1.084</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5804</v>
@@ -34155,7 +34155,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.2834</v>
+        <v>-1.2835</v>
       </c>
       <c r="C59" t="n">
         <v>0.9619</v>
@@ -34164,7 +34164,7 @@
         <v>-0.8126</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4011</v>
+        <v>-1.4012</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8126</v>
@@ -34176,7 +34176,7 @@
         <v>-2.674</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0982</v>
+        <v>-1.0989</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8199</v>
@@ -34189,7 +34189,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.249</v>
+        <v>-1.2491</v>
       </c>
       <c r="C60" t="n">
         <v>0.9198</v>
@@ -34198,7 +34198,7 @@
         <v>-0.5419</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.4258</v>
+        <v>-1.4259</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5419</v>
@@ -34210,7 +34210,7 @@
         <v>-2.674</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1131</v>
+        <v>-1.1138</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9876</v>
@@ -34223,7 +34223,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.1935</v>
+        <v>-1.1937</v>
       </c>
       <c r="C61" t="n">
         <v>0.8397</v>
@@ -34232,7 +34232,7 @@
         <v>-0.3879</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.395</v>
+        <v>-1.3951</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3879</v>
@@ -34244,7 +34244,7 @@
         <v>-2.444</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0943</v>
+        <v>-1.0949</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1704</v>
@@ -34257,7 +34257,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.1862</v>
+        <v>-1.1863</v>
       </c>
       <c r="C62" t="n">
         <v>0.8124</v>
@@ -34266,7 +34266,7 @@
         <v>-0.2602</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.4177</v>
+        <v>-1.4179</v>
       </c>
       <c r="F62" t="n">
         <v>-0.2602</v>
@@ -34278,7 +34278,7 @@
         <v>-2.444</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0592</v>
+        <v>-1.0598</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3403</v>
@@ -34291,7 +34291,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.1926</v>
+        <v>-1.1927</v>
       </c>
       <c r="C63" t="n">
         <v>0.7577</v>
@@ -34300,7 +34300,7 @@
         <v>-0.2135</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.4374</v>
+        <v>-1.4375</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2135</v>
@@ -34312,7 +34312,7 @@
         <v>-2.444</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0881</v>
+        <v>-1.0888</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4638</v>
@@ -34325,7 +34325,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1631</v>
+        <v>-1.1632</v>
       </c>
       <c r="C64" t="n">
         <v>0.6857</v>
@@ -34334,7 +34334,7 @@
         <v>-0.2624</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3883</v>
+        <v>-1.3884</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2624</v>
@@ -34346,7 +34346,7 @@
         <v>-2.124</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0675</v>
+        <v>-1.0682</v>
       </c>
       <c r="J64" t="n">
         <v>-1.699</v>
@@ -34359,7 +34359,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1791</v>
+        <v>-1.1792</v>
       </c>
       <c r="C65" t="n">
         <v>0.6964</v>
@@ -34368,7 +34368,7 @@
         <v>-0.3024</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.3983</v>
+        <v>-1.3985</v>
       </c>
       <c r="F65" t="n">
         <v>-0.3024</v>
@@ -34380,7 +34380,7 @@
         <v>-2.124</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.027</v>
+        <v>-1.0275</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8219</v>
@@ -34393,7 +34393,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.1867</v>
+        <v>-1.1868</v>
       </c>
       <c r="C66" t="n">
         <v>0.585</v>
@@ -34402,7 +34402,7 @@
         <v>-0.2086</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.4312</v>
+        <v>-1.4313</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2086</v>
@@ -34414,7 +34414,7 @@
         <v>-2.124</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0677</v>
+        <v>-1.0682</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9708</v>
@@ -34427,7 +34427,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1448</v>
+        <v>-1.1449</v>
       </c>
       <c r="C67" t="n">
         <v>0.6892</v>
@@ -34436,7 +34436,7 @@
         <v>-0.1876</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.3841</v>
+        <v>-1.3842</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1876</v>
@@ -34448,7 +34448,7 @@
         <v>-1.791</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0887</v>
+        <v>-1.0893</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1397</v>
@@ -34461,7 +34461,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1681</v>
+        <v>-1.1683</v>
       </c>
       <c r="C68" t="n">
         <v>0.6511</v>
@@ -34470,7 +34470,7 @@
         <v>-0.2734</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.3918</v>
+        <v>-1.392</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2734</v>
@@ -34482,7 +34482,7 @@
         <v>-1.791</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1549</v>
+        <v>-1.1556</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1129</v>
@@ -34495,7 +34495,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1504</v>
+        <v>-1.1505</v>
       </c>
       <c r="C69" t="n">
         <v>0.5633</v>
@@ -34504,7 +34504,7 @@
         <v>-0.2619</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.3725</v>
+        <v>-1.3727</v>
       </c>
       <c r="F69" t="n">
         <v>-0.2619</v>
@@ -34516,7 +34516,7 @@
         <v>-1.791</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1891</v>
+        <v>-1.1899</v>
       </c>
       <c r="J69" t="n">
         <v>-2.064</v>
@@ -34529,7 +34529,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0623</v>
+        <v>-1.0625</v>
       </c>
       <c r="C70" t="n">
         <v>0.5677</v>
@@ -34538,7 +34538,7 @@
         <v>-0.2931</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2546</v>
+        <v>-1.2548</v>
       </c>
       <c r="F70" t="n">
         <v>-0.2931</v>
@@ -34550,7 +34550,7 @@
         <v>-1.4266</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2067</v>
+        <v>-1.2076</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9686</v>
@@ -34563,7 +34563,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0186</v>
+        <v>-1.0188</v>
       </c>
       <c r="C71" t="n">
         <v>0.5209</v>
@@ -34572,7 +34572,7 @@
         <v>-0.1104</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2456</v>
+        <v>-1.2459</v>
       </c>
       <c r="F71" t="n">
         <v>-0.1104</v>
@@ -34584,7 +34584,7 @@
         <v>-1.4266</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2397</v>
+        <v>-1.2407</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9298</v>
@@ -34597,7 +34597,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0167</v>
+        <v>-1.0169</v>
       </c>
       <c r="C72" t="n">
         <v>0.5194</v>
@@ -34606,7 +34606,7 @@
         <v>-0.1504</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2333</v>
+        <v>-1.2335</v>
       </c>
       <c r="F72" t="n">
         <v>-0.1504</v>
@@ -34618,7 +34618,7 @@
         <v>-1.4266</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.227</v>
+        <v>-1.228</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8991</v>
@@ -34631,7 +34631,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.953</v>
+        <v>-0.9532</v>
       </c>
       <c r="C73" t="n">
         <v>0.4411</v>
@@ -34640,7 +34640,7 @@
         <v>-0.1177</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1618</v>
+        <v>-1.1621</v>
       </c>
       <c r="F73" t="n">
         <v>-0.1177</v>
@@ -34652,7 +34652,7 @@
         <v>-1.1836</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1896</v>
+        <v>-1.1906</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8612</v>
@@ -34665,7 +34665,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.9604</v>
       </c>
       <c r="C74" t="n">
         <v>0.4026</v>
@@ -34674,7 +34674,7 @@
         <v>-0.1687</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1581</v>
+        <v>-1.1583</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1687</v>
@@ -34686,7 +34686,7 @@
         <v>-1.1836</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2151</v>
+        <v>-1.2161</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8374</v>
@@ -34699,7 +34699,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9414</v>
+        <v>-0.9416</v>
       </c>
       <c r="C75" t="n">
         <v>0.3874</v>
@@ -34708,7 +34708,7 @@
         <v>-0.1839</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1308</v>
+        <v>-1.131</v>
       </c>
       <c r="F75" t="n">
         <v>-0.1839</v>
@@ -34720,7 +34720,7 @@
         <v>-1.1836</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2055</v>
+        <v>-1.2065</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8155</v>
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.8248</v>
+        <v>-0.825</v>
       </c>
       <c r="C76" t="n">
         <v>0.2978</v>
@@ -34742,7 +34742,7 @@
         <v>-0.08649999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.0093</v>
+        <v>-1.0096</v>
       </c>
       <c r="F76" t="n">
         <v>-0.08649999999999999</v>
@@ -34754,7 +34754,7 @@
         <v>-0.7586000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2353</v>
+        <v>-1.2363</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7064</v>
@@ -34767,7 +34767,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7477</v>
+        <v>-0.7479</v>
       </c>
       <c r="C77" t="n">
         <v>0.3431</v>
@@ -34776,7 +34776,7 @@
         <v>0.0526</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9478</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="F77" t="n">
         <v>0.0526</v>
@@ -34788,7 +34788,7 @@
         <v>-0.7586000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2029</v>
+        <v>-1.2039</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6015</v>
@@ -34801,7 +34801,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7516</v>
+        <v>-0.7518</v>
       </c>
       <c r="C78" t="n">
         <v>0.2407</v>
@@ -34810,7 +34810,7 @@
         <v>0.1135</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9679</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="F78" t="n">
         <v>0.1135</v>
@@ -34822,7 +34822,7 @@
         <v>-0.7586000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2416</v>
+        <v>-1.2426</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6343</v>
@@ -34835,7 +34835,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7212</v>
+        <v>-0.7214</v>
       </c>
       <c r="C79" t="n">
         <v>0.1954</v>
@@ -34844,7 +34844,7 @@
         <v>0.1228</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9322</v>
+        <v>-0.9325</v>
       </c>
       <c r="F79" t="n">
         <v>0.1228</v>
@@ -34856,7 +34856,7 @@
         <v>-0.6929999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2633</v>
+        <v>-1.2644</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5363</v>
@@ -34869,7 +34869,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.6842</v>
+        <v>-0.6845</v>
       </c>
       <c r="C80" t="n">
         <v>0.1919</v>
@@ -34878,7 +34878,7 @@
         <v>0.2633</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.9211</v>
+        <v>-0.9214</v>
       </c>
       <c r="F80" t="n">
         <v>0.2633</v>
@@ -34890,7 +34890,7 @@
         <v>-0.6929999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2644</v>
+        <v>-1.2655</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5187</v>
@@ -34903,7 +34903,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.6663</v>
+        <v>-0.6666</v>
       </c>
       <c r="C81" t="n">
         <v>0.2028</v>
@@ -34912,7 +34912,7 @@
         <v>0.3198</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.9131</v>
       </c>
       <c r="F81" t="n">
         <v>0.3198</v>
@@ -34924,7 +34924,7 @@
         <v>-0.6929999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3104</v>
+        <v>-1.3116</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4818</v>
@@ -34937,7 +34937,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.6251</v>
+        <v>-0.6253</v>
       </c>
       <c r="C82" t="n">
         <v>0.2131</v>
@@ -34946,7 +34946,7 @@
         <v>0.326</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8628</v>
+        <v>-0.8631</v>
       </c>
       <c r="F82" t="n">
         <v>0.326</v>
@@ -34958,7 +34958,7 @@
         <v>-0.6052</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3259</v>
+        <v>-1.3271</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3497</v>
@@ -34971,7 +34971,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.66</v>
+        <v>-0.6602</v>
       </c>
       <c r="C83" t="n">
         <v>0.09279999999999999</v>
@@ -34980,7 +34980,7 @@
         <v>0.1817</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.8704</v>
+        <v>-0.8707</v>
       </c>
       <c r="F83" t="n">
         <v>0.1817</v>
@@ -34992,7 +34992,7 @@
         <v>-0.6052</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3228</v>
+        <v>-1.324</v>
       </c>
       <c r="J83" t="n">
         <v>-1.364</v>
@@ -35005,7 +35005,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6521</v>
+        <v>-0.6523</v>
       </c>
       <c r="C84" t="n">
         <v>0.1093</v>
@@ -35014,7 +35014,7 @@
         <v>0.1347</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8488</v>
+        <v>-0.8491</v>
       </c>
       <c r="F84" t="n">
         <v>0.1347</v>
@@ -35026,7 +35026,7 @@
         <v>-0.6052</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3096</v>
+        <v>-1.3108</v>
       </c>
       <c r="J84" t="n">
         <v>-1.326</v>
@@ -35039,7 +35039,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.6202</v>
+        <v>-0.6204</v>
       </c>
       <c r="C85" t="n">
         <v>0.0525</v>
@@ -35048,7 +35048,7 @@
         <v>0.1894</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.8226</v>
+        <v>-0.8229</v>
       </c>
       <c r="F85" t="n">
         <v>0.1894</v>
@@ -35060,7 +35060,7 @@
         <v>-0.581</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3145</v>
+        <v>-1.3157</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2826</v>
@@ -35073,7 +35073,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5841</v>
+        <v>-0.5843</v>
       </c>
       <c r="C86" t="n">
         <v>0.0257</v>
@@ -35082,7 +35082,7 @@
         <v>0.2363</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7892</v>
+        <v>-0.7895</v>
       </c>
       <c r="F86" t="n">
         <v>0.2363</v>
@@ -35094,7 +35094,7 @@
         <v>-0.581</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3366</v>
+        <v>-1.3378</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1266</v>
@@ -35107,7 +35107,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5574</v>
+        <v>-0.5576</v>
       </c>
       <c r="C87" t="n">
         <v>0.0584</v>
@@ -35116,7 +35116,7 @@
         <v>0.285</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.768</v>
+        <v>-0.7682</v>
       </c>
       <c r="F87" t="n">
         <v>0.285</v>
@@ -35128,7 +35128,7 @@
         <v>-0.581</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2862</v>
+        <v>-1.2873</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1351</v>
@@ -35141,7 +35141,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.5083</v>
+        <v>-0.5085</v>
       </c>
       <c r="C88" t="n">
         <v>-0.0463</v>
@@ -35150,7 +35150,7 @@
         <v>0.3315</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7183</v>
+        <v>-0.7185</v>
       </c>
       <c r="F88" t="n">
         <v>0.3315</v>
@@ -35162,7 +35162,7 @@
         <v>-0.5274</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2067</v>
+        <v>-1.2077</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0599</v>
@@ -35175,7 +35175,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.5036</v>
+        <v>-0.5038</v>
       </c>
       <c r="C89" t="n">
         <v>-0.0515</v>
@@ -35184,7 +35184,7 @@
         <v>0.3377</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.7139</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="F89" t="n">
         <v>0.3377</v>
@@ -35196,7 +35196,7 @@
         <v>-0.5274</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2296</v>
+        <v>-1.2307</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0936</v>
@@ -35209,7 +35209,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.5074</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="C90" t="n">
         <v>-0.0336</v>
@@ -35218,7 +35218,7 @@
         <v>0.2128</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.6874</v>
+        <v>-0.6877</v>
       </c>
       <c r="F90" t="n">
         <v>0.2128</v>
@@ -35230,7 +35230,7 @@
         <v>-0.5274</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2821</v>
+        <v>-1.2832</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9181</v>
@@ -35243,7 +35243,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.4846</v>
+        <v>-0.4848</v>
       </c>
       <c r="C91" t="n">
         <v>-0.1676</v>
@@ -35252,7 +35252,7 @@
         <v>0.1758</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.6499</v>
       </c>
       <c r="F91" t="n">
         <v>0.1758</v>
@@ -35264,7 +35264,7 @@
         <v>-0.393</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2841</v>
+        <v>-1.2853</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9463</v>
@@ -35277,7 +35277,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.471</v>
+        <v>-0.4712</v>
       </c>
       <c r="C92" t="n">
         <v>-0.2331</v>
@@ -35286,7 +35286,7 @@
         <v>0.1327</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.6219</v>
+        <v>-0.6222</v>
       </c>
       <c r="F92" t="n">
         <v>0.1327</v>
@@ -35298,7 +35298,7 @@
         <v>-0.393</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2881</v>
+        <v>-1.2892</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8314</v>
@@ -35311,7 +35311,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4641</v>
+        <v>-0.4643</v>
       </c>
       <c r="C93" t="n">
         <v>-0.2228</v>
@@ -35320,7 +35320,7 @@
         <v>0.1761</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6241</v>
+        <v>-0.6244</v>
       </c>
       <c r="F93" t="n">
         <v>0.1761</v>
@@ -35332,7 +35332,7 @@
         <v>-0.393</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2861</v>
+        <v>-1.2873</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8204</v>
@@ -35345,7 +35345,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4022</v>
+        <v>-0.4024</v>
       </c>
       <c r="C94" t="n">
         <v>-0.3182</v>
@@ -35354,7 +35354,7 @@
         <v>0.2713</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5705</v>
+        <v>-0.5708</v>
       </c>
       <c r="F94" t="n">
         <v>0.2713</v>
@@ -35366,7 +35366,7 @@
         <v>-0.2552</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2956</v>
+        <v>-1.2968</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7851</v>
@@ -35379,7 +35379,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.3946</v>
+        <v>-0.3948</v>
       </c>
       <c r="C95" t="n">
         <v>-0.2685</v>
@@ -35388,7 +35388,7 @@
         <v>0.2715</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5611</v>
+        <v>-0.5614</v>
       </c>
       <c r="F95" t="n">
         <v>0.2715</v>
@@ -35400,7 +35400,7 @@
         <v>-0.2552</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2828</v>
+        <v>-1.2839</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7911</v>
@@ -35413,7 +35413,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3373</v>
+        <v>-0.3375</v>
       </c>
       <c r="C96" t="n">
         <v>-0.2964</v>
@@ -35422,7 +35422,7 @@
         <v>0.2768</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.4908</v>
+        <v>-0.4911</v>
       </c>
       <c r="F96" t="n">
         <v>0.2768</v>
@@ -35434,7 +35434,7 @@
         <v>-0.2552</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2519</v>
+        <v>-1.2529</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5896</v>
@@ -35447,7 +35447,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.2363</v>
+        <v>-0.2365</v>
       </c>
       <c r="C97" t="n">
         <v>-0.3238</v>
@@ -35456,7 +35456,7 @@
         <v>0.5887</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.4426</v>
+        <v>-0.4428</v>
       </c>
       <c r="F97" t="n">
         <v>0.5887</v>
@@ -35468,7 +35468,7 @@
         <v>-0.2092</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1889</v>
+        <v>-1.1898</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5685</v>
@@ -35481,7 +35481,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.3188</v>
+        <v>-0.3189</v>
       </c>
       <c r="C98" t="n">
         <v>-0.3705</v>
@@ -35490,7 +35490,7 @@
         <v>0.1387</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.4332</v>
+        <v>-0.4333</v>
       </c>
       <c r="F98" t="n">
         <v>0.1387</v>
@@ -35502,7 +35502,7 @@
         <v>-0.2092</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.054</v>
+        <v>-1.0547</v>
       </c>
       <c r="J98" t="n">
         <v>-0.6209</v>
@@ -35515,7 +35515,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.2684</v>
+        <v>-0.2685</v>
       </c>
       <c r="C99" t="n">
         <v>-0.3883</v>
@@ -35524,7 +35524,7 @@
         <v>0.1589</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.3752</v>
+        <v>-0.3753</v>
       </c>
       <c r="F99" t="n">
         <v>0.1589</v>
@@ -35536,7 +35536,7 @@
         <v>-0.2092</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9683</v>
+        <v>-0.9688</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5077</v>
@@ -35549,7 +35549,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2549</v>
+        <v>-0.255</v>
       </c>
       <c r="C100" t="n">
         <v>-0.3899</v>
@@ -35558,7 +35558,7 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.3416</v>
+        <v>-0.3417</v>
       </c>
       <c r="F100" t="n">
         <v>0.09180000000000001</v>
@@ -35570,7 +35570,7 @@
         <v>-0.1696</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9206</v>
+        <v>-0.921</v>
       </c>
       <c r="J100" t="n">
         <v>-0.5042</v>
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.2131</v>
+        <v>-0.2132</v>
       </c>
       <c r="C101" t="n">
         <v>-0.4367</v>
@@ -35592,7 +35592,7 @@
         <v>0.1066</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.293</v>
+        <v>-0.2931</v>
       </c>
       <c r="F101" t="n">
         <v>0.1066</v>
@@ -35604,7 +35604,7 @@
         <v>-0.1696</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8361</v>
+        <v>-0.8364</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4175</v>
@@ -35626,7 +35626,7 @@
         <v>0.2464</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.2624</v>
+        <v>-0.2625</v>
       </c>
       <c r="F102" t="n">
         <v>0.2464</v>
@@ -35638,7 +35638,7 @@
         <v>-0.1696</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7405</v>
+        <v>-0.7406</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4088</v>
@@ -35660,7 +35660,7 @@
         <v>0.3909</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2387</v>
+        <v>-0.2388</v>
       </c>
       <c r="F103" t="n">
         <v>0.3909</v>
@@ -35672,7 +35672,7 @@
         <v>-0.1049</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8155</v>
+        <v>-0.8158</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3586</v>
@@ -35685,7 +35685,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.043</v>
+        <v>-0.0431</v>
       </c>
       <c r="C104" t="n">
         <v>-0.5427999999999999</v>
@@ -35694,7 +35694,7 @@
         <v>0.5313</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.1866</v>
+        <v>-0.1867</v>
       </c>
       <c r="F104" t="n">
         <v>0.5313</v>
@@ -35706,7 +35706,7 @@
         <v>-0.1049</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.7265</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2361</v>
@@ -35719,7 +35719,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0387</v>
+        <v>-0.0388</v>
       </c>
       <c r="C105" t="n">
         <v>-0.5632</v>
@@ -35728,7 +35728,7 @@
         <v>0.5886</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.1955</v>
+        <v>-0.1956</v>
       </c>
       <c r="F105" t="n">
         <v>0.5886</v>
@@ -35740,7 +35740,7 @@
         <v>-0.1049</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7657</v>
+        <v>-0.766</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2483</v>
@@ -35762,7 +35762,7 @@
         <v>0.5482</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.1965</v>
+        <v>-0.1966</v>
       </c>
       <c r="F106" t="n">
         <v>0.5482</v>
@@ -35774,7 +35774,7 @@
         <v>-0.0474</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7156</v>
+        <v>-0.7158</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3663</v>
@@ -35796,7 +35796,7 @@
         <v>0.6534</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.1689</v>
+        <v>-0.169</v>
       </c>
       <c r="F107" t="n">
         <v>0.6534</v>
@@ -35808,7 +35808,7 @@
         <v>-0.0474</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7121</v>
+        <v>-0.7124</v>
       </c>
       <c r="J107" t="n">
         <v>-0.2624</v>
@@ -35842,7 +35842,7 @@
         <v>-0.0474</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6531</v>
+        <v>-0.6532</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2937</v>
@@ -35944,7 +35944,7 @@
         <v>0.1388</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5702</v>
+        <v>-0.5703</v>
       </c>
       <c r="J111" t="n">
         <v>-0.241</v>
@@ -35978,7 +35978,7 @@
         <v>0.1656</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5547</v>
+        <v>-0.5548</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2436</v>
@@ -36046,7 +36046,7 @@
         <v>0.1656</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5279</v>
+        <v>-0.528</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2216</v>
@@ -36080,7 +36080,7 @@
         <v>0.1891</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.5107</v>
       </c>
       <c r="J115" t="n">
         <v>-0.2524</v>
@@ -36114,7 +36114,7 @@
         <v>0.1891</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4835</v>
+        <v>-0.4836</v>
       </c>
       <c r="J116" t="n">
         <v>-0.1374</v>
@@ -36170,7 +36170,7 @@
         <v>1.6179</v>
       </c>
       <c r="E118" t="n">
-        <v>0.058</v>
+        <v>0.0581</v>
       </c>
       <c r="F118" t="n">
         <v>1.6179</v>
@@ -36182,7 +36182,7 @@
         <v>0.2476</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.352</v>
+        <v>-0.3518</v>
       </c>
       <c r="J118" t="n">
         <v>-0.163</v>
@@ -36204,7 +36204,7 @@
         <v>1.5829</v>
       </c>
       <c r="E119" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0871</v>
       </c>
       <c r="F119" t="n">
         <v>1.5829</v>
@@ -36216,7 +36216,7 @@
         <v>0.2476</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3379</v>
+        <v>-0.3377</v>
       </c>
       <c r="J119" t="n">
         <v>-0.0795</v>
@@ -36229,7 +36229,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4037</v>
+        <v>0.4039</v>
       </c>
       <c r="C120" t="n">
         <v>-0.4894</v>
@@ -36238,7 +36238,7 @@
         <v>1.4576</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1403</v>
+        <v>0.1404</v>
       </c>
       <c r="F120" t="n">
         <v>1.4576</v>
@@ -36250,7 +36250,7 @@
         <v>0.2476</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1663</v>
+        <v>-0.1657</v>
       </c>
       <c r="J120" t="n">
         <v>-0.0602</v>
@@ -36263,7 +36263,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.2106</v>
+        <v>0.2108</v>
       </c>
       <c r="C121" t="n">
         <v>-0.4829</v>
@@ -36272,7 +36272,7 @@
         <v>0.353</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1751</v>
+        <v>0.1752</v>
       </c>
       <c r="F121" t="n">
         <v>0.353</v>
@@ -36284,7 +36284,7 @@
         <v>0.3286</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0805</v>
+        <v>-0.0799</v>
       </c>
       <c r="J121" t="n">
         <v>-0.0914</v>
@@ -36297,7 +36297,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.3982</v>
+        <v>0.3983</v>
       </c>
       <c r="C122" t="n">
         <v>-0.4206</v>
@@ -36306,7 +36306,7 @@
         <v>1.3545</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1591</v>
+        <v>0.1593</v>
       </c>
       <c r="F122" t="n">
         <v>1.3545</v>
@@ -36318,7 +36318,7 @@
         <v>0.3286</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0965</v>
+        <v>-0.0958</v>
       </c>
       <c r="J122" t="n">
         <v>-0.1516</v>
@@ -36331,7 +36331,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.3915</v>
+        <v>0.3917</v>
       </c>
       <c r="C123" t="n">
         <v>-0.3378</v>
@@ -36340,7 +36340,7 @@
         <v>1.2434</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1786</v>
+        <v>0.1787</v>
       </c>
       <c r="F123" t="n">
         <v>1.2434</v>
@@ -36352,7 +36352,7 @@
         <v>0.3286</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0595</v>
+        <v>-0.0589</v>
       </c>
       <c r="J123" t="n">
         <v>-0.1308</v>
@@ -36365,7 +36365,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4724</v>
+        <v>0.4725</v>
       </c>
       <c r="C124" t="n">
         <v>-0.3003</v>
@@ -36374,7 +36374,7 @@
         <v>1.28</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2705</v>
+        <v>0.2707</v>
       </c>
       <c r="F124" t="n">
         <v>1.28</v>
@@ -36386,7 +36386,7 @@
         <v>0.4813</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0014</v>
+        <v>0.0022</v>
       </c>
       <c r="J124" t="n">
         <v>-0.0382</v>
@@ -36399,7 +36399,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.2998</v>
+        <v>0.2999</v>
       </c>
       <c r="C125" t="n">
         <v>-0.213</v>
@@ -36408,7 +36408,7 @@
         <v>0.522</v>
       </c>
       <c r="E125" t="n">
-        <v>0.2442</v>
+        <v>0.2444</v>
       </c>
       <c r="F125" t="n">
         <v>0.522</v>
@@ -36420,7 +36420,7 @@
         <v>0.4813</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0146</v>
+        <v>0.0153</v>
       </c>
       <c r="J125" t="n">
         <v>-0.1106</v>
@@ -36433,7 +36433,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.3155</v>
+        <v>0.3157</v>
       </c>
       <c r="C126" t="n">
         <v>-0.2228</v>
@@ -36442,7 +36442,7 @@
         <v>0.4297</v>
       </c>
       <c r="E126" t="n">
-        <v>0.2869</v>
+        <v>0.2871</v>
       </c>
       <c r="F126" t="n">
         <v>0.4297</v>
@@ -36454,7 +36454,7 @@
         <v>0.4813</v>
       </c>
       <c r="I126" t="n">
-        <v>0.0529</v>
+        <v>0.0536</v>
       </c>
       <c r="J126" t="n">
         <v>0.0191</v>
@@ -36467,7 +36467,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3192</v>
+        <v>0.3194</v>
       </c>
       <c r="C127" t="n">
         <v>-0.2094</v>
@@ -36476,7 +36476,7 @@
         <v>0.3786</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3044</v>
+        <v>0.3046</v>
       </c>
       <c r="F127" t="n">
         <v>0.3786</v>
@@ -36488,7 +36488,7 @@
         <v>0.4672</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1259</v>
+        <v>0.1268</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0232</v>
@@ -36501,7 +36501,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3038</v>
+        <v>0.304</v>
       </c>
       <c r="C128" t="n">
         <v>-0.0979</v>
@@ -36510,7 +36510,7 @@
         <v>0.2945</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3061</v>
+        <v>0.3063</v>
       </c>
       <c r="F128" t="n">
         <v>0.2945</v>
@@ -36522,7 +36522,7 @@
         <v>0.4672</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1285</v>
+        <v>0.1294</v>
       </c>
       <c r="J128" t="n">
         <v>-0.0418</v>
@@ -36535,7 +36535,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.2856</v>
+        <v>0.2857</v>
       </c>
       <c r="C129" t="n">
         <v>-0.1422</v>
@@ -36544,7 +36544,7 @@
         <v>0.2553</v>
       </c>
       <c r="E129" t="n">
-        <v>0.2931</v>
+        <v>0.2934</v>
       </c>
       <c r="F129" t="n">
         <v>0.2553</v>
@@ -36556,7 +36556,7 @@
         <v>0.4672</v>
       </c>
       <c r="I129" t="n">
-        <v>0.12</v>
+        <v>0.1209</v>
       </c>
       <c r="J129" t="n">
         <v>-0.075</v>
@@ -36569,7 +36569,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.3031</v>
+        <v>0.3032</v>
       </c>
       <c r="C130" t="n">
         <v>-0.0697</v>
@@ -36578,7 +36578,7 @@
         <v>0.2582</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3143</v>
+        <v>0.3145</v>
       </c>
       <c r="F130" t="n">
         <v>0.2582</v>
@@ -36590,7 +36590,7 @@
         <v>0.5435</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0462</v>
+        <v>0.0469</v>
       </c>
       <c r="J130" t="n">
         <v>-0.0299</v>
@@ -36603,7 +36603,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.2983</v>
+        <v>0.2984</v>
       </c>
       <c r="C131" t="n">
         <v>-0.0621</v>
@@ -36612,7 +36612,7 @@
         <v>0.2221</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3173</v>
+        <v>0.3175</v>
       </c>
       <c r="F131" t="n">
         <v>0.2221</v>
@@ -36624,7 +36624,7 @@
         <v>0.5435</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0499</v>
+        <v>0.0506</v>
       </c>
       <c r="J131" t="n">
         <v>-0.0655</v>
@@ -36637,7 +36637,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.3336</v>
+        <v>0.3338</v>
       </c>
       <c r="C132" t="n">
         <v>-0.0043</v>
@@ -36646,7 +36646,7 @@
         <v>0.3561</v>
       </c>
       <c r="E132" t="n">
-        <v>0.328</v>
+        <v>0.3282</v>
       </c>
       <c r="F132" t="n">
         <v>0.3561</v>
@@ -36658,7 +36658,7 @@
         <v>0.5435</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1063</v>
+        <v>0.1071</v>
       </c>
       <c r="J132" t="n">
         <v>-0.0236</v>
@@ -36671,7 +36671,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.369</v>
+        <v>0.3691</v>
       </c>
       <c r="C133" t="n">
         <v>-0.0626</v>
@@ -36680,7 +36680,7 @@
         <v>0.3667</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3695</v>
+        <v>0.3697</v>
       </c>
       <c r="F133" t="n">
         <v>0.3667</v>
@@ -36692,7 +36692,7 @@
         <v>0.6225000000000001</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0973</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="J133" t="n">
         <v>0.0023</v>
@@ -36705,7 +36705,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3478</v>
+        <v>0.3479</v>
       </c>
       <c r="C134" t="n">
         <v>-0.0133</v>
@@ -36714,7 +36714,7 @@
         <v>0.3864</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3381</v>
+        <v>0.3383</v>
       </c>
       <c r="F134" t="n">
         <v>0.3864</v>
@@ -36726,7 +36726,7 @@
         <v>0.6225000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0153</v>
+        <v>0.016</v>
       </c>
       <c r="J134" t="n">
         <v>-0.0517</v>
@@ -36739,7 +36739,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.3628</v>
+        <v>0.3629</v>
       </c>
       <c r="C135" t="n">
         <v>0.034</v>
@@ -36748,7 +36748,7 @@
         <v>0.4548</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3398</v>
+        <v>0.3399</v>
       </c>
       <c r="F135" t="n">
         <v>0.4548</v>
@@ -36760,7 +36760,7 @@
         <v>0.6225000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0687</v>
+        <v>-0.0682</v>
       </c>
       <c r="J135" t="n">
         <v>-0.008699999999999999</v>
@@ -36773,7 +36773,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3521</v>
+        <v>0.3522</v>
       </c>
       <c r="C136" t="n">
         <v>0.0503</v>
@@ -36782,7 +36782,7 @@
         <v>0.3204</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3601</v>
+        <v>0.3602</v>
       </c>
       <c r="F136" t="n">
         <v>0.3204</v>
@@ -36794,7 +36794,7 @@
         <v>0.6726</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0789</v>
+        <v>-0.0785</v>
       </c>
       <c r="J136" t="n">
         <v>0.0327</v>
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.3269</v>
+        <v>0.327</v>
       </c>
       <c r="C137" t="n">
         <v>0.0897</v>
@@ -36828,7 +36828,7 @@
         <v>0.6726</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1443</v>
+        <v>-0.1441</v>
       </c>
       <c r="J137" t="n">
         <v>0.0431</v>
@@ -36841,7 +36841,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.3391</v>
+        <v>0.3392</v>
       </c>
       <c r="C138" t="n">
         <v>0.1277</v>
@@ -36862,7 +36862,7 @@
         <v>0.6726</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1454</v>
+        <v>-0.1451</v>
       </c>
       <c r="J138" t="n">
         <v>0.0408</v>
@@ -36896,7 +36896,7 @@
         <v>0.771</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2021</v>
+        <v>-0.202</v>
       </c>
       <c r="J139" t="n">
         <v>0.1184</v>
@@ -36964,7 +36964,7 @@
         <v>0.771</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2579</v>
+        <v>-0.258</v>
       </c>
       <c r="J141" t="n">
         <v>0.13</v>
@@ -36998,7 +36998,7 @@
         <v>0.7752</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2489</v>
+        <v>-0.249</v>
       </c>
       <c r="J142" t="n">
         <v>0.1719</v>
@@ -37045,7 +37045,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4247</v>
+        <v>0.4248</v>
       </c>
       <c r="C144" t="n">
         <v>0.221</v>
@@ -37054,7 +37054,7 @@
         <v>0.3332</v>
       </c>
       <c r="E144" t="n">
-        <v>0.4476</v>
+        <v>0.4477</v>
       </c>
       <c r="F144" t="n">
         <v>0.3332</v>
@@ -37066,7 +37066,7 @@
         <v>0.7752</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1072</v>
+        <v>-0.107</v>
       </c>
       <c r="J144" t="n">
         <v>0.3267</v>
@@ -37079,7 +37079,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5342</v>
+        <v>0.5343</v>
       </c>
       <c r="C145" t="n">
         <v>0.2364</v>
@@ -37088,7 +37088,7 @@
         <v>0.633</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5095</v>
+        <v>0.5097</v>
       </c>
       <c r="F145" t="n">
         <v>0.633</v>
@@ -37100,7 +37100,7 @@
         <v>0.765</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0343</v>
+        <v>0.0349</v>
       </c>
       <c r="J145" t="n">
         <v>0.4354</v>
@@ -37113,7 +37113,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5062</v>
+        <v>0.5063</v>
       </c>
       <c r="C146" t="n">
         <v>0.2588</v>
@@ -37122,7 +37122,7 @@
         <v>0.5053</v>
       </c>
       <c r="E146" t="n">
-        <v>0.5065</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="F146" t="n">
         <v>0.5053</v>
@@ -37134,7 +37134,7 @@
         <v>0.765</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0192</v>
+        <v>0.0197</v>
       </c>
       <c r="J146" t="n">
         <v>0.4351</v>
@@ -37156,7 +37156,7 @@
         <v>0.5476</v>
       </c>
       <c r="E147" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5016</v>
       </c>
       <c r="F147" t="n">
         <v>0.5476</v>
@@ -37168,7 +37168,7 @@
         <v>0.765</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0026</v>
+        <v>-0.0022</v>
       </c>
       <c r="J147" t="n">
         <v>0.4439</v>
@@ -37181,7 +37181,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5074</v>
+        <v>0.5075</v>
       </c>
       <c r="C148" t="n">
         <v>0.1796</v>
@@ -37190,7 +37190,7 @@
         <v>0.6009</v>
       </c>
       <c r="E148" t="n">
-        <v>0.484</v>
+        <v>0.4841</v>
       </c>
       <c r="F148" t="n">
         <v>0.6009</v>
@@ -37202,7 +37202,7 @@
         <v>0.7822</v>
       </c>
       <c r="I148" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="J148" t="n">
         <v>0.4392</v>
@@ -37236,7 +37236,7 @@
         <v>0.7822</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0502</v>
+        <v>-0.0499</v>
       </c>
       <c r="J149" t="n">
         <v>0.6198</v>
@@ -37258,7 +37258,7 @@
         <v>0.614</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5347</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="F150" t="n">
         <v>0.614</v>
@@ -37270,7 +37270,7 @@
         <v>0.7822</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0026</v>
+        <v>0.003</v>
       </c>
       <c r="J150" t="n">
         <v>0.5587</v>
@@ -37283,7 +37283,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5452</v>
+        <v>0.5453</v>
       </c>
       <c r="C151" t="n">
         <v>0.284</v>
@@ -37292,7 +37292,7 @@
         <v>0.5951</v>
       </c>
       <c r="E151" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5329</v>
       </c>
       <c r="F151" t="n">
         <v>0.5951</v>
@@ -37304,7 +37304,7 @@
         <v>0.8047</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.0183</v>
+        <v>-0.018</v>
       </c>
       <c r="J151" t="n">
         <v>0.5741000000000001</v>
@@ -37317,7 +37317,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5796</v>
+        <v>0.5797</v>
       </c>
       <c r="C152" t="n">
         <v>0.2722</v>
@@ -37326,7 +37326,7 @@
         <v>0.6333</v>
       </c>
       <c r="E152" t="n">
-        <v>0.5662</v>
+        <v>0.5663</v>
       </c>
       <c r="F152" t="n">
         <v>0.6333</v>
@@ -37338,7 +37338,7 @@
         <v>0.8047</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0187</v>
+        <v>0.0191</v>
       </c>
       <c r="J152" t="n">
         <v>0.705</v>
@@ -37360,7 +37360,7 @@
         <v>0.7339</v>
       </c>
       <c r="E153" t="n">
-        <v>0.5462</v>
+        <v>0.5463</v>
       </c>
       <c r="F153" t="n">
         <v>0.7339</v>
@@ -37372,7 +37372,7 @@
         <v>0.8047</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0229</v>
+        <v>-0.0227</v>
       </c>
       <c r="J153" t="n">
         <v>0.6838</v>
@@ -37406,7 +37406,7 @@
         <v>0.8094</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J154" t="n">
         <v>0.73</v>
@@ -37419,7 +37419,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6417</v>
       </c>
       <c r="C155" t="n">
         <v>0.2633</v>
@@ -37428,7 +37428,7 @@
         <v>0.7769</v>
       </c>
       <c r="E155" t="n">
-        <v>0.6078</v>
+        <v>0.6079</v>
       </c>
       <c r="F155" t="n">
         <v>0.7769</v>
@@ -37440,7 +37440,7 @@
         <v>0.8094</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0617</v>
+        <v>0.0621</v>
       </c>
       <c r="J155" t="n">
         <v>0.8474</v>
@@ -37453,7 +37453,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.6267</v>
+        <v>0.6268</v>
       </c>
       <c r="C156" t="n">
         <v>0.2997</v>
@@ -37462,7 +37462,7 @@
         <v>0.8369</v>
       </c>
       <c r="E156" t="n">
-        <v>0.5742</v>
+        <v>0.5743</v>
       </c>
       <c r="F156" t="n">
         <v>0.8369</v>
@@ -37474,7 +37474,7 @@
         <v>0.8094</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0728</v>
+        <v>0.0733</v>
       </c>
       <c r="J156" t="n">
         <v>0.7711</v>
@@ -37487,7 +37487,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.6395</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="C157" t="n">
         <v>0.3304</v>
@@ -37496,7 +37496,7 @@
         <v>0.7795</v>
       </c>
       <c r="E157" t="n">
-        <v>0.6045</v>
+        <v>0.6046</v>
       </c>
       <c r="F157" t="n">
         <v>0.7795</v>
@@ -37508,7 +37508,7 @@
         <v>0.7875</v>
       </c>
       <c r="I157" t="n">
-        <v>0.097</v>
+        <v>0.0974</v>
       </c>
       <c r="J157" t="n">
         <v>0.8091</v>
@@ -37530,7 +37530,7 @@
         <v>0.7729</v>
       </c>
       <c r="E158" t="n">
-        <v>0.6357</v>
+        <v>0.6358</v>
       </c>
       <c r="F158" t="n">
         <v>0.7729</v>
@@ -37542,7 +37542,7 @@
         <v>0.7875</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0761</v>
+        <v>0.0765</v>
       </c>
       <c r="J158" t="n">
         <v>1.0042</v>
@@ -37555,7 +37555,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.6476</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="C159" t="n">
         <v>0.3158</v>
@@ -37564,7 +37564,7 @@
         <v>0.8692</v>
       </c>
       <c r="E159" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.5923</v>
       </c>
       <c r="F159" t="n">
         <v>0.8692</v>
@@ -37576,7 +37576,7 @@
         <v>0.7875</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0127</v>
+        <v>0.0129</v>
       </c>
       <c r="J159" t="n">
         <v>0.9147</v>
@@ -37610,7 +37610,7 @@
         <v>0.8262</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.03</v>
+        <v>-0.0299</v>
       </c>
       <c r="J160" t="n">
         <v>1.0217</v>
@@ -37623,7 +37623,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.6485</v>
+        <v>0.6486</v>
       </c>
       <c r="C161" t="n">
         <v>0.2556</v>
@@ -37644,7 +37644,7 @@
         <v>0.8262</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0034</v>
+        <v>0.0036</v>
       </c>
       <c r="J161" t="n">
         <v>1.0293</v>
@@ -37678,7 +37678,7 @@
         <v>0.8262</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0581</v>
+        <v>0.0584</v>
       </c>
       <c r="J162" t="n">
         <v>1.1062</v>
@@ -37712,7 +37712,7 @@
         <v>0.8226</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0607</v>
+        <v>0.061</v>
       </c>
       <c r="J163" t="n">
         <v>1.2068</v>
@@ -37725,7 +37725,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.7089</v>
+        <v>0.709</v>
       </c>
       <c r="C164" t="n">
         <v>0.3525</v>
@@ -37746,7 +37746,7 @@
         <v>0.8226</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0863</v>
+        <v>0.0867</v>
       </c>
       <c r="J164" t="n">
         <v>1.2097</v>
@@ -37759,7 +37759,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.7335</v>
       </c>
       <c r="C165" t="n">
         <v>0.3708</v>
@@ -37780,7 +37780,7 @@
         <v>0.8226</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0759</v>
+        <v>0.0762</v>
       </c>
       <c r="J165" t="n">
         <v>1.3207</v>
@@ -37793,7 +37793,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.7401</v>
+        <v>0.7402</v>
       </c>
       <c r="C166" t="n">
         <v>0.4213</v>
@@ -37802,7 +37802,7 @@
         <v>0.8032</v>
       </c>
       <c r="E166" t="n">
-        <v>0.7244</v>
+        <v>0.7245</v>
       </c>
       <c r="F166" t="n">
         <v>0.8032</v>
@@ -37814,7 +37814,7 @@
         <v>0.8841</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1152</v>
+        <v>0.1156</v>
       </c>
       <c r="J166" t="n">
         <v>1.272</v>
@@ -37827,7 +37827,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.7649</v>
+        <v>0.765</v>
       </c>
       <c r="C167" t="n">
         <v>0.3612</v>
@@ -37836,7 +37836,7 @@
         <v>0.8495</v>
       </c>
       <c r="E167" t="n">
-        <v>0.7438</v>
+        <v>0.7439</v>
       </c>
       <c r="F167" t="n">
         <v>0.8495</v>
@@ -37848,7 +37848,7 @@
         <v>0.8841</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0862</v>
+        <v>0.0866</v>
       </c>
       <c r="J167" t="n">
         <v>1.3893</v>
@@ -37861,7 +37861,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.772</v>
+        <v>0.7721</v>
       </c>
       <c r="C168" t="n">
         <v>0.382</v>
@@ -37870,7 +37870,7 @@
         <v>0.8164</v>
       </c>
       <c r="E168" t="n">
-        <v>0.7609</v>
+        <v>0.761</v>
       </c>
       <c r="F168" t="n">
         <v>0.8164</v>
@@ -37882,7 +37882,7 @@
         <v>0.8841</v>
       </c>
       <c r="I168" t="n">
-        <v>0.076</v>
+        <v>0.0765</v>
       </c>
       <c r="J168" t="n">
         <v>1.443</v>
@@ -37904,7 +37904,7 @@
         <v>0.698</v>
       </c>
       <c r="E169" t="n">
-        <v>0.7197</v>
+        <v>0.7198</v>
       </c>
       <c r="F169" t="n">
         <v>0.698</v>
@@ -37916,7 +37916,7 @@
         <v>0.8655</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0215</v>
+        <v>0.0219</v>
       </c>
       <c r="J169" t="n">
         <v>1.4193</v>
@@ -37938,7 +37938,7 @@
         <v>0.7911</v>
       </c>
       <c r="E170" t="n">
-        <v>0.7436</v>
+        <v>0.7437</v>
       </c>
       <c r="F170" t="n">
         <v>0.7911</v>
@@ -37950,7 +37950,7 @@
         <v>0.8655</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0608</v>
+        <v>-0.0606</v>
       </c>
       <c r="J170" t="n">
         <v>1.539</v>
@@ -37984,7 +37984,7 @@
         <v>0.8655</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0436</v>
+        <v>-0.0433</v>
       </c>
       <c r="J171" t="n">
         <v>1.5071</v>
@@ -37997,7 +37997,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.7885</v>
+        <v>0.7886</v>
       </c>
       <c r="C172" t="n">
         <v>0.5012</v>
@@ -38006,7 +38006,7 @@
         <v>0.7993</v>
       </c>
       <c r="E172" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7859</v>
       </c>
       <c r="F172" t="n">
         <v>0.7993</v>
@@ -38018,7 +38018,7 @@
         <v>0.9504</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0386</v>
+        <v>-0.0382</v>
       </c>
       <c r="J172" t="n">
         <v>1.6571</v>
@@ -38040,7 +38040,7 @@
         <v>0.8366</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7744</v>
+        <v>0.7745</v>
       </c>
       <c r="F173" t="n">
         <v>0.8366</v>
@@ -38052,7 +38052,7 @@
         <v>0.9504</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0369</v>
+        <v>-0.0365</v>
       </c>
       <c r="J173" t="n">
         <v>1.6148</v>
@@ -38074,7 +38074,7 @@
         <v>0.7541</v>
       </c>
       <c r="E174" t="n">
-        <v>0.7827</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="F174" t="n">
         <v>0.7541</v>
@@ -38086,7 +38086,7 @@
         <v>0.9504</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0984</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J174" t="n">
         <v>1.6765</v>
@@ -38120,7 +38120,7 @@
         <v>0.9468</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1428</v>
+        <v>-0.1426</v>
       </c>
       <c r="J175" t="n">
         <v>1.8111</v>
@@ -38133,7 +38133,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.7903</v>
+        <v>0.7904</v>
       </c>
       <c r="C176" t="n">
         <v>0.6075</v>
@@ -38142,7 +38142,7 @@
         <v>0.7311</v>
       </c>
       <c r="E176" t="n">
-        <v>0.8051</v>
+        <v>0.8052</v>
       </c>
       <c r="F176" t="n">
         <v>0.7311</v>
@@ -38154,7 +38154,7 @@
         <v>0.9468</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1511</v>
+        <v>-0.1509</v>
       </c>
       <c r="J176" t="n">
         <v>1.824</v>
@@ -38176,7 +38176,7 @@
         <v>0.7198</v>
       </c>
       <c r="E177" t="n">
-        <v>0.7723</v>
+        <v>0.7724</v>
       </c>
       <c r="F177" t="n">
         <v>0.7198</v>
@@ -38188,7 +38188,7 @@
         <v>0.9468</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.2038</v>
+        <v>-0.2036</v>
       </c>
       <c r="J177" t="n">
         <v>1.8043</v>
@@ -38222,7 +38222,7 @@
         <v>0.4466</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1865</v>
+        <v>-0.1863</v>
       </c>
       <c r="J178" t="n">
         <v>1.9336</v>
@@ -38235,7 +38235,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.6861</v>
+        <v>0.6862</v>
       </c>
       <c r="C179" t="n">
         <v>0.6107</v>
@@ -38244,7 +38244,7 @@
         <v>0.6655</v>
       </c>
       <c r="E179" t="n">
-        <v>0.6913</v>
+        <v>0.6914</v>
       </c>
       <c r="F179" t="n">
         <v>0.6655</v>
@@ -38256,7 +38256,7 @@
         <v>0.4466</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1864</v>
+        <v>-0.1862</v>
       </c>
       <c r="J179" t="n">
         <v>1.9412</v>
@@ -38269,7 +38269,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.6706</v>
+        <v>0.6707</v>
       </c>
       <c r="C180" t="n">
         <v>0.6850000000000001</v>
@@ -38290,7 +38290,7 @@
         <v>0.4466</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1752</v>
+        <v>-0.1749</v>
       </c>
       <c r="J180" t="n">
         <v>1.9113</v>
@@ -38303,7 +38303,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.5868</v>
+        <v>0.5869</v>
       </c>
       <c r="C181" t="n">
         <v>0.6037</v>
@@ -38312,7 +38312,7 @@
         <v>0.5618</v>
       </c>
       <c r="E181" t="n">
-        <v>0.5931</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="F181" t="n">
         <v>0.5618</v>
@@ -38324,7 +38324,7 @@
         <v>0.0818</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1679</v>
+        <v>-0.1676</v>
       </c>
       <c r="J181" t="n">
         <v>1.9534</v>
@@ -38337,7 +38337,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.6442</v>
+        <v>0.6443</v>
       </c>
       <c r="C182" t="n">
         <v>0.5862000000000001</v>
@@ -38358,7 +38358,7 @@
         <v>0.0818</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1948</v>
+        <v>-0.1945</v>
       </c>
       <c r="J182" t="n">
         <v>2.05</v>
@@ -38380,7 +38380,7 @@
         <v>0.7167</v>
       </c>
       <c r="E183" t="n">
-        <v>0.6398</v>
+        <v>0.6399</v>
       </c>
       <c r="F183" t="n">
         <v>0.7167</v>
@@ -38392,7 +38392,7 @@
         <v>0.0818</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2095</v>
+        <v>-0.2092</v>
       </c>
       <c r="J183" t="n">
         <v>2.175</v>
@@ -38405,7 +38405,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.5062</v>
+        <v>0.5063</v>
       </c>
       <c r="C184" t="n">
         <v>0.5735</v>
@@ -38414,7 +38414,7 @@
         <v>0.718</v>
       </c>
       <c r="E184" t="n">
-        <v>0.4533</v>
+        <v>0.4534</v>
       </c>
       <c r="F184" t="n">
         <v>0.718</v>
@@ -38426,7 +38426,7 @@
         <v>-0.4501</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3452</v>
+        <v>-0.345</v>
       </c>
       <c r="J184" t="n">
         <v>2.1157</v>
@@ -38439,7 +38439,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.4509</v>
+        <v>0.451</v>
       </c>
       <c r="C185" t="n">
         <v>0.5709</v>
@@ -38460,7 +38460,7 @@
         <v>-0.4501</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3106</v>
+        <v>-0.3104</v>
       </c>
       <c r="J185" t="n">
         <v>2.1148</v>
@@ -38494,7 +38494,7 @@
         <v>-0.4501</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.271</v>
+        <v>-0.2708</v>
       </c>
       <c r="J186" t="n">
         <v>2.1851</v>
@@ -38507,7 +38507,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.4209</v>
+        <v>0.421</v>
       </c>
       <c r="C187" t="n">
         <v>0.5393</v>
@@ -38516,7 +38516,7 @@
         <v>0.3924</v>
       </c>
       <c r="E187" t="n">
-        <v>0.428</v>
+        <v>0.4281</v>
       </c>
       <c r="F187" t="n">
         <v>0.3924</v>
@@ -38528,7 +38528,7 @@
         <v>-0.8563</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.206</v>
+        <v>-0.2059</v>
       </c>
       <c r="J187" t="n">
         <v>2.2698</v>
@@ -38562,7 +38562,7 @@
         <v>-0.8563</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1882</v>
+        <v>-0.188</v>
       </c>
       <c r="J188" t="n">
         <v>2.0136</v>
@@ -38596,7 +38596,7 @@
         <v>-0.8563</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1532</v>
+        <v>-0.1531</v>
       </c>
       <c r="J189" t="n">
         <v>1.7741</v>
@@ -38630,7 +38630,7 @@
         <v>-0.7040999999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1454</v>
+        <v>-0.1453</v>
       </c>
       <c r="J190" t="n">
         <v>1.5321</v>
@@ -38664,7 +38664,7 @@
         <v>-0.7040999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1062</v>
+        <v>-0.1061</v>
       </c>
       <c r="J191" t="n">
         <v>1.3063</v>
@@ -38698,7 +38698,7 @@
         <v>-0.7040999999999999</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0626</v>
       </c>
       <c r="J192" t="n">
         <v>1.0395</v>
@@ -38711,7 +38711,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2065</v>
+        <v>0.2066</v>
       </c>
       <c r="C193" t="n">
         <v>0.2348</v>
@@ -38766,7 +38766,7 @@
         <v>-0.4991</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0348</v>
+        <v>0.0349</v>
       </c>
       <c r="J194" t="n">
         <v>0.5527</v>
@@ -38788,7 +38788,7 @@
         <v>0.1951</v>
       </c>
       <c r="E195" t="n">
-        <v>0.138</v>
+        <v>0.1381</v>
       </c>
       <c r="F195" t="n">
         <v>0.1951</v>
@@ -38800,7 +38800,7 @@
         <v>-0.4991</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0956</v>
+        <v>0.0958</v>
       </c>
       <c r="J195" t="n">
         <v>0.3537</v>
@@ -38813,7 +38813,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.1699</v>
+        <v>0.17</v>
       </c>
       <c r="C196" t="n">
         <v>0.031</v>
@@ -38822,7 +38822,7 @@
         <v>0.2427</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1517</v>
+        <v>0.1518</v>
       </c>
       <c r="F196" t="n">
         <v>0.2427</v>
@@ -38834,7 +38834,7 @@
         <v>-0.2881</v>
       </c>
       <c r="I196" t="n">
-        <v>0.166</v>
+        <v>0.1663</v>
       </c>
       <c r="J196" t="n">
         <v>0.07829999999999999</v>
@@ -38868,7 +38868,7 @@
         <v>-0.2881</v>
       </c>
       <c r="I197" t="n">
-        <v>0.209</v>
+        <v>0.2093</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1051</v>
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.0682</v>
+        <v>0.0683</v>
       </c>
       <c r="C198" t="n">
         <v>-0.0649</v>
@@ -38890,7 +38890,7 @@
         <v>0.1602</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0452</v>
+        <v>0.0453</v>
       </c>
       <c r="F198" t="n">
         <v>0.1602</v>
@@ -38902,7 +38902,7 @@
         <v>-0.2881</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2162</v>
+        <v>0.2165</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4298</v>
@@ -38915,7 +38915,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0622</v>
+        <v>0.0623</v>
       </c>
       <c r="C199" t="n">
         <v>-0.0964</v>
@@ -38924,7 +38924,7 @@
         <v>0.2048</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0266</v>
+        <v>0.0267</v>
       </c>
       <c r="F199" t="n">
         <v>0.2048</v>
@@ -38936,7 +38936,7 @@
         <v>-0.1724</v>
       </c>
       <c r="I199" t="n">
-        <v>0.262</v>
+        <v>0.2623</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6718</v>
@@ -38970,7 +38970,7 @@
         <v>-0.1724</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2686</v>
+        <v>0.2689</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6232</v>
@@ -38983,7 +38983,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.1346</v>
+        <v>0.1347</v>
       </c>
       <c r="C201" t="n">
         <v>-0.2562</v>
@@ -38992,7 +38992,7 @@
         <v>0.429</v>
       </c>
       <c r="E201" t="n">
-        <v>0.061</v>
+        <v>0.0611</v>
       </c>
       <c r="F201" t="n">
         <v>0.429</v>
@@ -39004,7 +39004,7 @@
         <v>-0.1724</v>
       </c>
       <c r="I201" t="n">
-        <v>0.282</v>
+        <v>0.2823</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6042999999999999</v>
@@ -39017,7 +39017,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2508</v>
+        <v>0.2509</v>
       </c>
       <c r="C202" t="n">
         <v>-0.2762</v>
@@ -39038,7 +39038,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3649</v>
+        <v>0.3652</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4186</v>
@@ -39051,7 +39051,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.2264</v>
+        <v>0.2265</v>
       </c>
       <c r="C203" t="n">
         <v>-0.2987</v>
@@ -39060,7 +39060,7 @@
         <v>0.5001</v>
       </c>
       <c r="E203" t="n">
-        <v>0.158</v>
+        <v>0.1581</v>
       </c>
       <c r="F203" t="n">
         <v>0.5001</v>
@@ -39072,7 +39072,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3781</v>
+        <v>0.3785</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5093</v>
@@ -39085,7 +39085,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.2901</v>
+        <v>0.2902</v>
       </c>
       <c r="C204" t="n">
         <v>-0.3445</v>
@@ -39094,7 +39094,7 @@
         <v>0.6373</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2033</v>
+        <v>0.2034</v>
       </c>
       <c r="F204" t="n">
         <v>0.6373</v>
@@ -39106,7 +39106,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4113</v>
+        <v>0.4118</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4293</v>
@@ -39119,7 +39119,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.555</v>
       </c>
       <c r="C205" t="n">
         <v>-0.4359</v>
@@ -39128,7 +39128,7 @@
         <v>1.7563</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2546</v>
+        <v>0.2547</v>
       </c>
       <c r="F205" t="n">
         <v>1.7563</v>
@@ -39140,7 +39140,7 @@
         <v>0.2093</v>
       </c>
       <c r="I205" t="n">
-        <v>0.417</v>
+        <v>0.4175</v>
       </c>
       <c r="J205" t="n">
         <v>-0.39</v>
@@ -39153,7 +39153,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3332</v>
+        <v>0.3333</v>
       </c>
       <c r="C206" t="n">
         <v>-0.5203</v>
@@ -39162,7 +39162,7 @@
         <v>0.526</v>
       </c>
       <c r="E206" t="n">
-        <v>0.285</v>
+        <v>0.2851</v>
       </c>
       <c r="F206" t="n">
         <v>0.526</v>
@@ -39174,7 +39174,7 @@
         <v>0.2093</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4084</v>
+        <v>0.4089</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2554</v>
@@ -39187,7 +39187,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3577</v>
+        <v>0.3578</v>
       </c>
       <c r="C207" t="n">
         <v>-0.5511</v>
@@ -39196,7 +39196,7 @@
         <v>0.6431</v>
       </c>
       <c r="E207" t="n">
-        <v>0.2864</v>
+        <v>0.2865</v>
       </c>
       <c r="F207" t="n">
         <v>0.6431</v>
@@ -39208,7 +39208,7 @@
         <v>0.2093</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4236</v>
+        <v>0.4241</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2947</v>
@@ -39221,7 +39221,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.4163</v>
+        <v>0.4164</v>
       </c>
       <c r="C208" t="n">
         <v>-0.5053</v>
@@ -39230,7 +39230,7 @@
         <v>0.7243000000000001</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3393</v>
+        <v>0.3395</v>
       </c>
       <c r="F208" t="n">
         <v>0.7243000000000001</v>
@@ -39242,7 +39242,7 @@
         <v>0.3943</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4537</v>
+        <v>0.4544</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2532</v>
@@ -39255,7 +39255,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.5946</v>
+        <v>0.5948</v>
       </c>
       <c r="C209" t="n">
         <v>-0.5758</v>
@@ -39264,7 +39264,7 @@
         <v>1.2981</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4187</v>
+        <v>0.419</v>
       </c>
       <c r="F209" t="n">
         <v>1.2981</v>
@@ -39276,7 +39276,7 @@
         <v>0.3943</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1722</v>
@@ -39289,7 +39289,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.5925</v>
+        <v>0.5928</v>
       </c>
       <c r="C210" t="n">
         <v>-0.6456</v>
@@ -39298,7 +39298,7 @@
         <v>1.2952</v>
       </c>
       <c r="E210" t="n">
-        <v>0.4169</v>
+        <v>0.4172</v>
       </c>
       <c r="F210" t="n">
         <v>1.2952</v>
@@ -39310,7 +39310,7 @@
         <v>0.3943</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6398</v>
+        <v>0.641</v>
       </c>
       <c r="J210" t="n">
         <v>-0.17</v>
@@ -39323,7 +39323,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.669</v>
+        <v>0.6693</v>
       </c>
       <c r="C211" t="n">
         <v>-0.7048</v>
@@ -39332,7 +39332,7 @@
         <v>1.3414</v>
       </c>
       <c r="E211" t="n">
-        <v>0.5009</v>
+        <v>0.5013</v>
       </c>
       <c r="F211" t="n">
         <v>1.3414</v>
@@ -39344,7 +39344,7 @@
         <v>0.5281</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7337</v>
+        <v>0.7351</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1145</v>
@@ -39357,7 +39357,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.6884</v>
+        <v>0.6887</v>
       </c>
       <c r="C212" t="n">
         <v>-0.7396</v>
@@ -39366,7 +39366,7 @@
         <v>1.4357</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5019</v>
       </c>
       <c r="F212" t="n">
         <v>1.4357</v>
@@ -39378,7 +39378,7 @@
         <v>0.5281</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7701</v>
+        <v>0.7716</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1294</v>
@@ -39391,7 +39391,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7306</v>
       </c>
       <c r="C213" t="n">
         <v>-0.7202</v>
@@ -39400,7 +39400,7 @@
         <v>1.5661</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5214</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="F213" t="n">
         <v>1.5661</v>
@@ -39412,7 +39412,7 @@
         <v>0.5281</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7917</v>
+        <v>0.7932</v>
       </c>
       <c r="J213" t="n">
         <v>-0.08309999999999999</v>
@@ -39425,7 +39425,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.8396</v>
+        <v>0.8399</v>
       </c>
       <c r="C214" t="n">
         <v>-0.7835</v>
@@ -39434,7 +39434,7 @@
         <v>1.7317</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6165</v>
+        <v>0.617</v>
       </c>
       <c r="F214" t="n">
         <v>1.7317</v>
@@ -39446,7 +39446,7 @@
         <v>0.6061</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8942</v>
+        <v>0.896</v>
       </c>
       <c r="J214" t="n">
         <v>0.0775</v>
@@ -39459,7 +39459,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.8832</v>
+        <v>0.8835</v>
       </c>
       <c r="C215" t="n">
         <v>-0.8632</v>
@@ -39468,7 +39468,7 @@
         <v>1.8952</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6301</v>
+        <v>0.6306</v>
       </c>
       <c r="F215" t="n">
         <v>1.8952</v>
@@ -39480,7 +39480,7 @@
         <v>0.6061</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9633</v>
+        <v>0.9653</v>
       </c>
       <c r="J215" t="n">
         <v>0.0268</v>
@@ -39493,7 +39493,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8709</v>
+        <v>0.8712</v>
       </c>
       <c r="C216" t="n">
         <v>-0.9258</v>
@@ -39502,7 +39502,7 @@
         <v>1.9742</v>
       </c>
       <c r="E216" t="n">
-        <v>0.595</v>
+        <v>0.5955</v>
       </c>
       <c r="F216" t="n">
         <v>1.9742</v>
@@ -39514,7 +39514,7 @@
         <v>0.6061</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9038</v>
+        <v>0.9055</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0208</v>
@@ -39527,7 +39527,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.8105</v>
+        <v>0.8107</v>
       </c>
       <c r="C217" t="n">
         <v>-0.9187</v>
@@ -39536,7 +39536,7 @@
         <v>1.5625</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6228</v>
       </c>
       <c r="F217" t="n">
         <v>1.5625</v>
@@ -39548,7 +39548,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7759</v>
+        <v>0.7774</v>
       </c>
       <c r="J217" t="n">
         <v>0.1657</v>
@@ -39561,7 +39561,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.9043</v>
+        <v>0.9046</v>
       </c>
       <c r="C218" t="n">
         <v>-1.0065</v>
@@ -39570,7 +39570,7 @@
         <v>2.1405</v>
       </c>
       <c r="E218" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5956</v>
       </c>
       <c r="F218" t="n">
         <v>2.1405</v>
@@ -39582,7 +39582,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7067</v>
+        <v>0.7079</v>
       </c>
       <c r="J218" t="n">
         <v>0.1362</v>
@@ -39595,7 +39595,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8526</v>
       </c>
       <c r="C219" t="n">
         <v>-1.0961</v>
@@ -39604,7 +39604,7 @@
         <v>1.6766</v>
       </c>
       <c r="E219" t="n">
-        <v>0.6462</v>
+        <v>0.6466</v>
       </c>
       <c r="F219" t="n">
         <v>1.6766</v>
@@ -39616,7 +39616,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>0.777</v>
+        <v>0.7784</v>
       </c>
       <c r="J219" t="n">
         <v>0.2413</v>
@@ -39629,7 +39629,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.9032</v>
+        <v>0.9034</v>
       </c>
       <c r="C220" t="n">
         <v>-1.2201</v>
@@ -39638,7 +39638,7 @@
         <v>1.74</v>
       </c>
       <c r="E220" t="n">
-        <v>0.6939</v>
+        <v>0.6943</v>
       </c>
       <c r="F220" t="n">
         <v>1.74</v>
@@ -39650,7 +39650,7 @@
         <v>0.8408</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7791</v>
+        <v>0.7804</v>
       </c>
       <c r="J220" t="n">
         <v>0.2668</v>
@@ -39663,7 +39663,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.9267</v>
+        <v>0.927</v>
       </c>
       <c r="C221" t="n">
         <v>-1.2861</v>
@@ -39672,7 +39672,7 @@
         <v>1.811</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7056</v>
+        <v>0.7059</v>
       </c>
       <c r="F221" t="n">
         <v>1.811</v>
@@ -39684,7 +39684,7 @@
         <v>0.8408</v>
       </c>
       <c r="I221" t="n">
-        <v>0.798</v>
+        <v>0.7994</v>
       </c>
       <c r="J221" t="n">
         <v>0.3082</v>
@@ -39697,7 +39697,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.9217</v>
+        <v>0.922</v>
       </c>
       <c r="C222" t="n">
         <v>-1.4025</v>
@@ -39706,7 +39706,7 @@
         <v>1.7246</v>
       </c>
       <c r="E222" t="n">
-        <v>0.721</v>
+        <v>0.7214</v>
       </c>
       <c r="F222" t="n">
         <v>1.7246</v>
@@ -39718,7 +39718,7 @@
         <v>0.8408</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8954</v>
+        <v>0.8969</v>
       </c>
       <c r="J222" t="n">
         <v>0.2473</v>
@@ -39731,7 +39731,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39740,7 +39740,7 @@
         <v>1.7748</v>
       </c>
       <c r="E223" t="n">
-        <v>0.7779</v>
+        <v>0.7783</v>
       </c>
       <c r="F223" t="n">
         <v>1.7748</v>
@@ -39752,7 +39752,7 @@
         <v>0.8397</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0181</v>
+        <v>1.0199</v>
       </c>
       <c r="J223" t="n">
         <v>0.3651</v>
@@ -39765,7 +39765,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.9691</v>
+        <v>0.9694</v>
       </c>
       <c r="C224" t="n">
         <v>-1.3976</v>
@@ -39774,7 +39774,7 @@
         <v>1.6971</v>
       </c>
       <c r="E224" t="n">
-        <v>0.7871</v>
+        <v>0.7875</v>
       </c>
       <c r="F224" t="n">
         <v>1.6971</v>
@@ -39786,7 +39786,7 @@
         <v>0.8397</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0363</v>
+        <v>1.038</v>
       </c>
       <c r="J224" t="n">
         <v>0.3748</v>
@@ -39799,7 +39799,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.9839</v>
+        <v>0.9843</v>
       </c>
       <c r="C225" t="n">
         <v>-1.3984</v>
@@ -39808,7 +39808,7 @@
         <v>1.6708</v>
       </c>
       <c r="E225" t="n">
-        <v>0.8122</v>
+        <v>0.8127</v>
       </c>
       <c r="F225" t="n">
         <v>1.6708</v>
@@ -39820,7 +39820,7 @@
         <v>0.8397</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1236</v>
+        <v>1.1255</v>
       </c>
       <c r="J225" t="n">
         <v>0.3928</v>
@@ -39833,7 +39833,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9702</v>
+        <v>0.9706</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
@@ -39842,7 +39842,7 @@
         <v>1.4774</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8434</v>
+        <v>0.8439</v>
       </c>
       <c r="F226" t="n">
         <v>1.4774</v>
@@ -39854,7 +39854,7 @@
         <v>0.944</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1915</v>
+        <v>1.1935</v>
       </c>
       <c r="J226" t="n">
         <v>0.3554</v>
@@ -39867,7 +39867,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.9785</v>
+        <v>0.979</v>
       </c>
       <c r="C227" t="n">
         <v>-1.4189</v>
@@ -39876,7 +39876,7 @@
         <v>1.5261</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8417</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="F227" t="n">
         <v>1.5261</v>
@@ -39888,7 +39888,7 @@
         <v>0.944</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2215</v>
+        <v>1.2236</v>
       </c>
       <c r="J227" t="n">
         <v>0.3534</v>
@@ -39901,7 +39901,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9581</v>
+        <v>0.9585</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39910,7 +39910,7 @@
         <v>1.3816</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8522</v>
+        <v>0.8527</v>
       </c>
       <c r="F228" t="n">
         <v>1.3816</v>
@@ -39922,7 +39922,7 @@
         <v>0.944</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2916</v>
+        <v>1.2937</v>
       </c>
       <c r="J228" t="n">
         <v>0.3566</v>
@@ -39935,7 +39935,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.987</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="C229" t="n">
         <v>-1.3839</v>
@@ -39944,7 +39944,7 @@
         <v>1.4513</v>
       </c>
       <c r="E229" t="n">
-        <v>0.871</v>
+        <v>0.8714</v>
       </c>
       <c r="F229" t="n">
         <v>1.4513</v>
@@ -39956,7 +39956,7 @@
         <v>1.0419</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2204</v>
+        <v>1.2223</v>
       </c>
       <c r="J229" t="n">
         <v>0.382</v>
@@ -39969,7 +39969,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.9755</v>
+        <v>0.9759</v>
       </c>
       <c r="C230" t="n">
         <v>-1.8168</v>
@@ -39978,7 +39978,7 @@
         <v>1.1744</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9257</v>
+        <v>0.9262</v>
       </c>
       <c r="F230" t="n">
         <v>1.1744</v>
@@ -39990,7 +39990,7 @@
         <v>1.0419</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3209</v>
+        <v>1.3229</v>
       </c>
       <c r="J230" t="n">
         <v>0.4824</v>
@@ -40003,7 +40003,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.0496</v>
+        <v>1.05</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -40012,7 +40012,7 @@
         <v>1.4903</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9394</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F231" t="n">
         <v>1.4903</v>
@@ -40024,7 +40024,7 @@
         <v>1.0419</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4596</v>
+        <v>1.4617</v>
       </c>
       <c r="J231" t="n">
         <v>0.4188</v>
@@ -40037,7 +40037,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0712</v>
+        <v>1.0716</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -40046,7 +40046,7 @@
         <v>1.3836</v>
       </c>
       <c r="E232" t="n">
-        <v>0.993</v>
+        <v>0.9936</v>
       </c>
       <c r="F232" t="n">
         <v>1.3836</v>
@@ -40058,7 +40058,7 @@
         <v>1.1418</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5228</v>
+        <v>1.525</v>
       </c>
       <c r="J232" t="n">
         <v>0.4799</v>
@@ -40071,7 +40071,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0302</v>
+        <v>1.0307</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -40080,7 +40080,7 @@
         <v>1.1824</v>
       </c>
       <c r="E233" t="n">
-        <v>0.9922</v>
+        <v>0.9928</v>
       </c>
       <c r="F233" t="n">
         <v>1.1824</v>
@@ -40092,7 +40092,7 @@
         <v>1.1418</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5851</v>
+        <v>1.5874</v>
       </c>
       <c r="J233" t="n">
         <v>0.4724</v>
@@ -40105,7 +40105,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.0533</v>
+        <v>1.0538</v>
       </c>
       <c r="C234" t="n">
         <v>-1.649</v>
@@ -40114,7 +40114,7 @@
         <v>1.2978</v>
       </c>
       <c r="E234" t="n">
-        <v>0.9921</v>
+        <v>0.9927</v>
       </c>
       <c r="F234" t="n">
         <v>1.2978</v>
@@ -40126,7 +40126,7 @@
         <v>1.1418</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6309</v>
+        <v>1.6333</v>
       </c>
       <c r="J234" t="n">
         <v>0.4729</v>
@@ -40139,7 +40139,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.0803</v>
+        <v>1.0808</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -40148,7 +40148,7 @@
         <v>1.3367</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0162</v>
+        <v>1.0169</v>
       </c>
       <c r="F235" t="n">
         <v>1.3367</v>
@@ -40160,7 +40160,7 @@
         <v>1.137</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7119</v>
+        <v>1.7144</v>
       </c>
       <c r="J235" t="n">
         <v>0.5405</v>
@@ -40173,7 +40173,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0769</v>
+        <v>1.0774</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -40182,7 +40182,7 @@
         <v>1.3711</v>
       </c>
       <c r="E236" t="n">
-        <v>1.0034</v>
+        <v>1.004</v>
       </c>
       <c r="F236" t="n">
         <v>1.3711</v>
@@ -40194,7 +40194,7 @@
         <v>1.137</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7465</v>
+        <v>1.749</v>
       </c>
       <c r="J236" t="n">
         <v>0.5567</v>
@@ -40207,7 +40207,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.0166</v>
+        <v>1.017</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -40216,7 +40216,7 @@
         <v>1.4207</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9156</v>
+        <v>0.9161</v>
       </c>
       <c r="F237" t="n">
         <v>1.4207</v>
@@ -40228,7 +40228,7 @@
         <v>1.137</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5242</v>
+        <v>1.5261</v>
       </c>
       <c r="J237" t="n">
         <v>0.518</v>
@@ -40241,7 +40241,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9705</v>
+        <v>0.9709</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40250,7 +40250,7 @@
         <v>1.2146</v>
       </c>
       <c r="E238" t="n">
-        <v>0.9095</v>
+        <v>0.91</v>
       </c>
       <c r="F238" t="n">
         <v>1.2146</v>
@@ -40262,7 +40262,7 @@
         <v>1.1197</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5099</v>
+        <v>1.5117</v>
       </c>
       <c r="J238" t="n">
         <v>0.5233</v>
@@ -40275,7 +40275,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.993</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40284,7 +40284,7 @@
         <v>1.1456</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9548</v>
+        <v>0.9554</v>
       </c>
       <c r="F239" t="n">
         <v>1.1456</v>
@@ -40296,7 +40296,7 @@
         <v>1.1197</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6712</v>
+        <v>1.6733</v>
       </c>
       <c r="J239" t="n">
         <v>0.6181</v>
@@ -40309,7 +40309,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0114</v>
+        <v>1.0119</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40318,7 +40318,7 @@
         <v>1.2522</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9512</v>
+        <v>0.9518</v>
       </c>
       <c r="F240" t="n">
         <v>1.2522</v>
@@ -40330,7 +40330,7 @@
         <v>1.1197</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7466</v>
+        <v>1.7489</v>
       </c>
       <c r="J240" t="n">
         <v>0.5888</v>
@@ -40343,7 +40343,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0178</v>
+        <v>1.0182</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40352,7 +40352,7 @@
         <v>1.293</v>
       </c>
       <c r="E241" t="n">
-        <v>0.949</v>
+        <v>0.9495</v>
       </c>
       <c r="F241" t="n">
         <v>1.293</v>
@@ -40364,7 +40364,7 @@
         <v>1.1068</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7655</v>
+        <v>1.7679</v>
       </c>
       <c r="J241" t="n">
         <v>0.6418</v>
@@ -40377,7 +40377,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0281</v>
+        <v>1.0286</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40386,7 +40386,7 @@
         <v>1.4351</v>
       </c>
       <c r="E242" t="n">
-        <v>0.9264</v>
+        <v>0.927</v>
       </c>
       <c r="F242" t="n">
         <v>1.4351</v>
@@ -40398,7 +40398,7 @@
         <v>1.1068</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8376</v>
+        <v>1.84</v>
       </c>
       <c r="J242" t="n">
         <v>0.6034</v>
@@ -40411,7 +40411,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9798</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="C243" t="n">
         <v>-1.1287</v>
@@ -40420,7 +40420,7 @@
         <v>1.3061</v>
       </c>
       <c r="E243" t="n">
-        <v>0.8983</v>
+        <v>0.8988</v>
       </c>
       <c r="F243" t="n">
         <v>1.3061</v>
@@ -40432,7 +40432,7 @@
         <v>1.1068</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7719</v>
+        <v>1.7741</v>
       </c>
       <c r="J243" t="n">
         <v>0.5849</v>
@@ -40445,7 +40445,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.0179</v>
+        <v>1.0183</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40454,7 +40454,7 @@
         <v>1.3528</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9342</v>
+        <v>0.9347</v>
       </c>
       <c r="F244" t="n">
         <v>1.3528</v>
@@ -40466,7 +40466,7 @@
         <v>1.1698</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7271</v>
+        <v>1.7292</v>
       </c>
       <c r="J244" t="n">
         <v>0.7014</v>
@@ -40479,7 +40479,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9958</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40488,7 +40488,7 @@
         <v>1.5766</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8502</v>
+        <v>0.8506</v>
       </c>
       <c r="F245" t="n">
         <v>1.5766</v>
@@ -40500,7 +40500,7 @@
         <v>1.1698</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6041</v>
+        <v>1.6059</v>
       </c>
       <c r="J245" t="n">
         <v>0.6095</v>
@@ -40513,7 +40513,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1.0209</v>
+        <v>1.0213</v>
       </c>
       <c r="C246" t="n">
         <v>-1.1393</v>
@@ -40522,7 +40522,7 @@
         <v>1.5802</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8811</v>
+        <v>0.8815</v>
       </c>
       <c r="F246" t="n">
         <v>1.5802</v>
@@ -40534,7 +40534,7 @@
         <v>1.1698</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6977</v>
+        <v>1.6996</v>
       </c>
       <c r="J246" t="n">
         <v>0.6883</v>
@@ -40547,7 +40547,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9648</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40556,7 +40556,7 @@
         <v>1.4545</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8424</v>
+        <v>0.8429</v>
       </c>
       <c r="F247" t="n">
         <v>1.4545</v>
@@ -40568,7 +40568,7 @@
         <v>1.0719</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7265</v>
+        <v>1.7284</v>
       </c>
       <c r="J247" t="n">
         <v>0.6103</v>
@@ -40581,7 +40581,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9352</v>
+        <v>0.9356</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40590,7 +40590,7 @@
         <v>1.3002</v>
       </c>
       <c r="E248" t="n">
-        <v>0.844</v>
+        <v>0.8445</v>
       </c>
       <c r="F248" t="n">
         <v>1.3002</v>
@@ -40602,7 +40602,7 @@
         <v>1.0719</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8402</v>
+        <v>1.8422</v>
       </c>
       <c r="J248" t="n">
         <v>0.6287</v>
@@ -40615,7 +40615,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9215</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40624,7 +40624,7 @@
         <v>1.1165</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8727</v>
+        <v>0.8732</v>
       </c>
       <c r="F249" t="n">
         <v>1.1165</v>
@@ -40636,7 +40636,7 @@
         <v>1.0719</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9055</v>
+        <v>1.9076</v>
       </c>
       <c r="J249" t="n">
         <v>0.6894</v>
@@ -40649,7 +40649,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9326</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40658,7 +40658,7 @@
         <v>1.2158</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8618</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="F250" t="n">
         <v>1.2158</v>
@@ -40670,7 +40670,7 @@
         <v>1.0983</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9701</v>
+        <v>1.9721</v>
       </c>
       <c r="J250" t="n">
         <v>0.6231</v>
@@ -40683,7 +40683,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.9735</v>
+        <v>0.974</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40692,7 +40692,7 @@
         <v>1.236</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9079</v>
+        <v>0.9085</v>
       </c>
       <c r="F251" t="n">
         <v>1.236</v>
@@ -40704,7 +40704,7 @@
         <v>1.0983</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1414</v>
+        <v>2.1436</v>
       </c>
       <c r="J251" t="n">
         <v>0.6374</v>
@@ -40717,7 +40717,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9794</v>
+        <v>0.9799</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40726,7 +40726,7 @@
         <v>1.2102</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9217</v>
+        <v>0.9223</v>
       </c>
       <c r="F252" t="n">
         <v>1.2102</v>
@@ -40738,7 +40738,7 @@
         <v>1.0983</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2661</v>
+        <v>2.2685</v>
       </c>
       <c r="J252" t="n">
         <v>0.6196</v>
@@ -40751,7 +40751,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7403</v>
+        <v>0.7408</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40760,7 +40760,7 @@
         <v>0.0331</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9171</v>
+        <v>0.9177</v>
       </c>
       <c r="F253" t="n">
         <v>0.0331</v>
@@ -40772,7 +40772,7 @@
         <v>1.1261</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2909</v>
+        <v>2.2933</v>
       </c>
       <c r="J253" t="n">
         <v>0.6133999999999999</v>
@@ -40785,7 +40785,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8689</v>
+        <v>0.8694</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40794,7 +40794,7 @@
         <v>0.6443</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9251</v>
+        <v>0.9257</v>
       </c>
       <c r="F254" t="n">
         <v>0.6443</v>
@@ -40806,7 +40806,7 @@
         <v>1.1261</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3949</v>
+        <v>2.3974</v>
       </c>
       <c r="J254" t="n">
         <v>0.5942</v>
@@ -40819,7 +40819,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8302</v>
+        <v>0.8307</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40828,7 +40828,7 @@
         <v>0.4423</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9271</v>
+        <v>0.9277</v>
       </c>
       <c r="F255" t="n">
         <v>0.4423</v>
@@ -40840,7 +40840,7 @@
         <v>1.1261</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4699</v>
+        <v>2.4723</v>
       </c>
       <c r="J255" t="n">
         <v>0.5617</v>
@@ -40853,7 +40853,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8091</v>
+        <v>0.8096</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40862,7 +40862,7 @@
         <v>0.4895</v>
       </c>
       <c r="E256" t="n">
-        <v>0.889</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="F256" t="n">
         <v>0.4895</v>
@@ -40874,7 +40874,7 @@
         <v>0.9971</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4937</v>
+        <v>2.4963</v>
       </c>
       <c r="J256" t="n">
         <v>0.6098</v>
@@ -40887,7 +40887,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7389</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40896,7 +40896,7 @@
         <v>0.3213</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8427</v>
+        <v>0.8433</v>
       </c>
       <c r="F257" t="n">
         <v>0.3213</v>
@@ -40908,7 +40908,7 @@
         <v>0.9971</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6176</v>
+        <v>2.6203</v>
       </c>
       <c r="J257" t="n">
         <v>0.4753</v>
@@ -40921,7 +40921,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7792</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40930,7 +40930,7 @@
         <v>0.2926</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9009</v>
+        <v>0.9015</v>
       </c>
       <c r="F258" t="n">
         <v>0.2926</v>
@@ -40942,7 +40942,7 @@
         <v>0.9971</v>
       </c>
       <c r="I258" t="n">
-        <v>2.764</v>
+        <v>2.7666</v>
       </c>
       <c r="J258" t="n">
         <v>0.5687</v>
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8145</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40964,7 +40964,7 @@
         <v>0.3237</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9372</v>
+        <v>0.9379</v>
       </c>
       <c r="F259" t="n">
         <v>0.3237</v>
@@ -40976,7 +40976,7 @@
         <v>1.0726</v>
       </c>
       <c r="I259" t="n">
-        <v>2.9512</v>
+        <v>2.9539</v>
       </c>
       <c r="J259" t="n">
         <v>0.5466</v>
@@ -40989,7 +40989,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8307</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
@@ -40998,7 +40998,7 @@
         <v>0.4117</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9347</v>
+        <v>0.9354</v>
       </c>
       <c r="F260" t="n">
         <v>0.4117</v>
@@ -41010,7 +41010,7 @@
         <v>1.0726</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9414</v>
+        <v>2.9442</v>
       </c>
       <c r="J260" t="n">
         <v>0.5466</v>
@@ -41023,13 +41023,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9341</v>
+        <v>0.9211</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9341</v>
+        <v>0.9211</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8217</v>
@@ -41038,7 +41038,7 @@
         <v>1.0726</v>
       </c>
       <c r="I261" t="n">
-        <v>2.939</v>
+        <v>2.8868</v>
       </c>
       <c r="J261" t="n">
         <v>0.5466</v>
@@ -41051,13 +41051,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.9341</v>
+        <v>0.9203</v>
       </c>
       <c r="C262" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E262" t="n">
-        <v>0.9341</v>
+        <v>0.9203</v>
       </c>
       <c r="G262" t="n">
         <v>-0.8217</v>
@@ -41066,7 +41066,7 @@
         <v>1.0726</v>
       </c>
       <c r="I262" t="n">
-        <v>2.939</v>
+        <v>2.8837</v>
       </c>
       <c r="J262" t="n">
         <v>0.5466</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -60,7 +60,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -97,11 +97,6 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -129,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -154,9 +149,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -801,7 +793,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-0.514</v>
+        <v>-0.515</v>
       </c>
     </row>
     <row r="9">
@@ -965,7 +957,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1372,7 +1364,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>-0.831</v>
+        <v>-0.832</v>
       </c>
     </row>
     <row r="52">
@@ -1562,7 +1554,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>-1.062</v>
+        <v>-1.063</v>
       </c>
     </row>
     <row r="71">
@@ -1662,7 +1654,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6850000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -2812,7 +2804,7 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="196">
@@ -3222,7 +3214,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>1.077</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="237">
@@ -3252,7 +3244,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>0.993</v>
+        <v>0.994</v>
       </c>
     </row>
     <row r="240">
@@ -3402,7 +3394,7 @@
         </is>
       </c>
       <c r="J254" t="n">
-        <v>0.869</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="255">
@@ -3482,7 +3474,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.92</v>
+        <v>0.916</v>
       </c>
     </row>
   </sheetData>
@@ -3591,11 +3583,11 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.404</v>
+        <v>1.527</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3617,11 +3609,11 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.655</v>
+        <v>1.802</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3643,11 +3635,11 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3669,11 +3661,11 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.871</v>
+        <v>2.987</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3695,11 +3687,11 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.015</v>
+        <v>4.131</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3803,19 +3795,19 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.575</v>
+        <v>-0.452</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>-0.11</v>
+      <c r="E13" s="10" t="n">
+        <v>-0.29</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Broadly neutral</t>
+          <t>Mildly restrictive</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3823,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.044</v>
+        <v>0.101</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3839,7 +3831,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.8</v>
+        <v>-1.05</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3859,7 +3851,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1.072</v>
+        <v>1.188</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3867,7 +3859,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-1.32</v>
+        <v>-1.47</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4201,7 +4193,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66215.34</v>
+        <v>65270.49</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4209,7 +4201,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -4355,172 +4347,172 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>policy_rate</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>jgb_1y</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>jgb_2y</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>jgb_5y</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>jgb_10y</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>jgb_30y</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>infexp_1y</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>infexp_3y</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>infexp_10y</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>real_1y</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="14" t="inlineStr">
         <is>
           <t>real_3y</t>
         </is>
       </c>
-      <c r="M1" s="15" t="inlineStr">
+      <c r="M1" s="14" t="inlineStr">
         <is>
           <t>real_10y</t>
         </is>
       </c>
-      <c r="N1" s="15" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
         <is>
           <t>real_policy_rate</t>
         </is>
       </c>
-      <c r="O1" s="15" t="inlineStr">
+      <c r="O1" s="14" t="inlineStr">
         <is>
           <t>real_1y_xp</t>
         </is>
       </c>
-      <c r="P1" s="15" t="inlineStr">
+      <c r="P1" s="14" t="inlineStr">
         <is>
           <t>real_3y_xp</t>
         </is>
       </c>
-      <c r="Q1" s="15" t="inlineStr">
+      <c r="Q1" s="14" t="inlineStr">
         <is>
           <t>real_10y_xp</t>
         </is>
       </c>
-      <c r="R1" s="15" t="inlineStr">
+      <c r="R1" s="14" t="inlineStr">
         <is>
           <t>lending_rate</t>
         </is>
       </c>
-      <c r="S1" s="15" t="inlineStr">
+      <c r="S1" s="14" t="inlineStr">
         <is>
           <t>cp_rate</t>
         </is>
       </c>
-      <c r="T1" s="15" t="inlineStr">
+      <c r="T1" s="14" t="inlineStr">
         <is>
           <t>corp_bond_spread</t>
         </is>
       </c>
-      <c r="U1" s="15" t="inlineStr">
+      <c r="U1" s="14" t="inlineStr">
         <is>
           <t>tankan_lend_large</t>
         </is>
       </c>
-      <c r="V1" s="15" t="inlineStr">
+      <c r="V1" s="14" t="inlineStr">
         <is>
           <t>tankan_lend_small</t>
         </is>
       </c>
-      <c r="W1" s="15" t="inlineStr">
+      <c r="W1" s="14" t="inlineStr">
         <is>
           <t>tankan_finpos_large</t>
         </is>
       </c>
-      <c r="X1" s="15" t="inlineStr">
+      <c r="X1" s="14" t="inlineStr">
         <is>
           <t>tankan_finpos_small</t>
         </is>
       </c>
-      <c r="Y1" s="15" t="inlineStr">
+      <c r="Y1" s="14" t="inlineStr">
         <is>
           <t>topix</t>
         </is>
       </c>
-      <c r="Z1" s="15" t="inlineStr">
+      <c r="Z1" s="14" t="inlineStr">
         <is>
           <t>nikkei225</t>
         </is>
       </c>
-      <c r="AA1" s="15" t="inlineStr">
+      <c r="AA1" s="14" t="inlineStr">
         <is>
           <t>usdjpy</t>
         </is>
       </c>
-      <c r="AB1" s="15" t="inlineStr">
+      <c r="AB1" s="14" t="inlineStr">
         <is>
           <t>bank_lending_yoy</t>
         </is>
       </c>
-      <c r="AC1" s="15" t="inlineStr">
+      <c r="AC1" s="14" t="inlineStr">
         <is>
           <t>cp_corpbond_yoy</t>
         </is>
       </c>
-      <c r="AD1" s="15" t="inlineStr">
+      <c r="AD1" s="14" t="inlineStr">
         <is>
           <t>core_cpi_yoy</t>
         </is>
       </c>
-      <c r="AE1" s="15" t="inlineStr">
+      <c r="AE1" s="14" t="inlineStr">
         <is>
           <t>potential_growth</t>
         </is>
       </c>
-      <c r="AF1" s="15" t="inlineStr">
+      <c r="AF1" s="14" t="inlineStr">
         <is>
           <t>natural_rate_low</t>
         </is>
       </c>
-      <c r="AG1" s="15" t="inlineStr">
+      <c r="AG1" s="14" t="inlineStr">
         <is>
           <t>natural_rate_mid</t>
         </is>
       </c>
-      <c r="AH1" s="15" t="inlineStr">
+      <c r="AH1" s="14" t="inlineStr">
         <is>
           <t>natural_rate_high</t>
         </is>
@@ -32048,19 +32040,19 @@
         <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>1.4038</v>
+        <v>1.527</v>
       </c>
       <c r="D262" t="n">
-        <v>1.6552</v>
+        <v>1.802</v>
       </c>
       <c r="E262" t="n">
-        <v>2.1399</v>
+        <v>2.28</v>
       </c>
       <c r="F262" t="n">
-        <v>2.8706</v>
+        <v>2.987</v>
       </c>
       <c r="G262" t="n">
-        <v>4.0149</v>
+        <v>4.131</v>
       </c>
       <c r="H262" t="n">
         <v>1.9793</v>
@@ -32072,13 +32064,13 @@
         <v>1.7988</v>
       </c>
       <c r="K262" t="n">
-        <v>-0.5755</v>
+        <v>-0.4523</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.0437</v>
+        <v>0.1008</v>
       </c>
       <c r="M262" t="n">
-        <v>1.0718</v>
+        <v>1.1882</v>
       </c>
       <c r="N262" t="n">
         <v>-0.9792999999999999</v>
@@ -32117,7 +32109,7 @@
         <v>3957.6278</v>
       </c>
       <c r="Z262" t="n">
-        <v>66215.34</v>
+        <v>65270.49</v>
       </c>
       <c r="AA262" t="n">
         <v>158.8476</v>
@@ -32171,52 +32163,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>FCI</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>rate_gap</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>stage1</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>stage2</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>real_rate</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>funding_costs</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>availability</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>asset_prices</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>funding_volumes</t>
         </is>
@@ -32229,13 +32221,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6135</v>
+        <v>-0.6136</v>
       </c>
       <c r="D2" t="n">
         <v>0.2568</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9036</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.2568</v>
@@ -32244,7 +32236,7 @@
         <v>-0.3444</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6435</v>
+        <v>-0.6437</v>
       </c>
       <c r="J2" t="n">
         <v>-1.723</v>
@@ -32272,7 +32264,7 @@
         <v>-0.3224</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.591</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>-1.6446</v>
@@ -32306,7 +32298,7 @@
         <v>-0.3807</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5683</v>
+        <v>-0.5684</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6535</v>
@@ -32319,7 +32311,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5399</v>
       </c>
       <c r="C5" t="n">
         <v>-0.0692</v>
@@ -32340,7 +32332,7 @@
         <v>-0.3807</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.547</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5197</v>
@@ -32353,7 +32345,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.5117</v>
+        <v>-0.5118</v>
       </c>
       <c r="C6" t="n">
         <v>-0.0915</v>
@@ -32374,7 +32366,7 @@
         <v>-0.3807</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5364</v>
+        <v>-0.5366</v>
       </c>
       <c r="J6" t="n">
         <v>-1.4262</v>
@@ -32408,7 +32400,7 @@
         <v>-0.3462</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4905</v>
+        <v>-0.4906</v>
       </c>
       <c r="J7" t="n">
         <v>-1.5169</v>
@@ -32430,7 +32422,7 @@
         <v>0.1284</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6752</v>
+        <v>-0.6753</v>
       </c>
       <c r="F8" t="n">
         <v>0.1284</v>
@@ -32442,7 +32434,7 @@
         <v>-0.3462</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4117</v>
+        <v>-0.4118</v>
       </c>
       <c r="J8" t="n">
         <v>-1.3664</v>
@@ -32476,7 +32468,7 @@
         <v>-0.3462</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4152</v>
+        <v>-0.4154</v>
       </c>
       <c r="J9" t="n">
         <v>-1.398</v>
@@ -32510,7 +32502,7 @@
         <v>-0.2239</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3906</v>
+        <v>-0.3907</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2524</v>
@@ -32544,7 +32536,7 @@
         <v>-0.2239</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3069</v>
+        <v>-0.307</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2897</v>
@@ -32557,7 +32549,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.4741</v>
+        <v>-0.4742</v>
       </c>
       <c r="C12" t="n">
         <v>-0.3965</v>
@@ -32578,7 +32570,7 @@
         <v>-0.2239</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2108</v>
+        <v>-0.2109</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2144</v>
@@ -32714,7 +32706,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1616</v>
+        <v>-0.1617</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0288</v>
@@ -32782,7 +32774,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2198</v>
+        <v>-0.2199</v>
       </c>
       <c r="J18" t="n">
         <v>-0.9921</v>
@@ -32816,7 +32808,7 @@
         <v>-0.1201</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1873</v>
+        <v>-0.1874</v>
       </c>
       <c r="J19" t="n">
         <v>-0.8633</v>
@@ -32884,7 +32876,7 @@
         <v>-0.1201</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.12</v>
+        <v>-0.1201</v>
       </c>
       <c r="J21" t="n">
         <v>-0.7752</v>
@@ -33271,7 +33263,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3601</v>
+        <v>-0.3602</v>
       </c>
       <c r="C33" t="n">
         <v>-0.1744</v>
@@ -33326,7 +33318,7 @@
         <v>-0.2291</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0953</v>
       </c>
       <c r="J34" t="n">
         <v>-0.0413</v>
@@ -33416,7 +33408,7 @@
         <v>0.487</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6047</v>
+        <v>-0.6048</v>
       </c>
       <c r="F37" t="n">
         <v>0.487</v>
@@ -33428,7 +33420,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2439</v>
+        <v>-0.244</v>
       </c>
       <c r="J37" t="n">
         <v>0.1554</v>
@@ -33462,7 +33454,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3791</v>
+        <v>-0.3792</v>
       </c>
       <c r="J38" t="n">
         <v>0.2096</v>
@@ -33484,7 +33476,7 @@
         <v>0.4918</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.6369</v>
+        <v>-0.637</v>
       </c>
       <c r="F39" t="n">
         <v>0.4918</v>
@@ -33496,7 +33488,7 @@
         <v>-0.6114000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4242</v>
+        <v>-0.4243</v>
       </c>
       <c r="J39" t="n">
         <v>0.2367</v>
@@ -33530,7 +33522,7 @@
         <v>-1.0608</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5642</v>
+        <v>-0.5643</v>
       </c>
       <c r="J40" t="n">
         <v>0.3596</v>
@@ -33564,7 +33556,7 @@
         <v>-1.0608</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5608</v>
+        <v>-0.5609</v>
       </c>
       <c r="J41" t="n">
         <v>0.3749</v>
@@ -33577,7 +33569,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.472</v>
+        <v>-0.4721</v>
       </c>
       <c r="C42" t="n">
         <v>-0.2345</v>
@@ -33632,7 +33624,7 @@
         <v>-1.425</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5259</v>
+        <v>-0.526</v>
       </c>
       <c r="J43" t="n">
         <v>0.5421</v>
@@ -33645,7 +33637,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.4284</v>
+        <v>-0.4285</v>
       </c>
       <c r="C44" t="n">
         <v>-0.2935</v>
@@ -33666,7 +33658,7 @@
         <v>-1.425</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5647</v>
+        <v>-0.5648</v>
       </c>
       <c r="J44" t="n">
         <v>0.5810999999999999</v>
@@ -33679,7 +33671,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.4095</v>
+        <v>-0.4096</v>
       </c>
       <c r="C45" t="n">
         <v>-0.3257</v>
@@ -33688,7 +33680,7 @@
         <v>1.0381</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.7714</v>
+        <v>-0.7715</v>
       </c>
       <c r="F45" t="n">
         <v>1.0381</v>
@@ -33700,7 +33692,7 @@
         <v>-1.425</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5599</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0.7406</v>
@@ -33713,7 +33705,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.4891</v>
+        <v>-0.4892</v>
       </c>
       <c r="C46" t="n">
         <v>-0.3034</v>
@@ -33734,7 +33726,7 @@
         <v>-1.7882</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6503</v>
+        <v>-0.6504</v>
       </c>
       <c r="J46" t="n">
         <v>0.7887</v>
@@ -33747,7 +33739,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.574</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="C47" t="n">
         <v>-0.3486</v>
@@ -33756,7 +33748,7 @@
         <v>0.7933</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.9159</v>
       </c>
       <c r="F47" t="n">
         <v>0.7933</v>
@@ -33768,7 +33760,7 @@
         <v>-1.7882</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.849</v>
+        <v>-0.8492</v>
       </c>
       <c r="J47" t="n">
         <v>0.7399</v>
@@ -33781,7 +33773,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.6355</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="C48" t="n">
         <v>-0.2059</v>
@@ -33790,7 +33782,7 @@
         <v>0.4544</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.908</v>
+        <v>-0.9081</v>
       </c>
       <c r="F48" t="n">
         <v>0.4544</v>
@@ -33802,7 +33794,7 @@
         <v>-1.7882</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9291</v>
+        <v>-0.9294</v>
       </c>
       <c r="J48" t="n">
         <v>0.7819</v>
@@ -33815,7 +33807,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8137</v>
+        <v>-0.8138</v>
       </c>
       <c r="C49" t="n">
         <v>-0.1283</v>
@@ -33836,7 +33828,7 @@
         <v>-2.2537</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0482</v>
+        <v>-1.0484</v>
       </c>
       <c r="J49" t="n">
         <v>0.9823</v>
@@ -33870,7 +33862,7 @@
         <v>-2.2537</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0941</v>
+        <v>-1.0943</v>
       </c>
       <c r="J50" t="n">
         <v>0.7637</v>
@@ -33892,7 +33884,7 @@
         <v>0.1171</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.0686</v>
+        <v>-1.0687</v>
       </c>
       <c r="F51" t="n">
         <v>0.1171</v>
@@ -33904,7 +33896,7 @@
         <v>-2.2537</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.1051</v>
+        <v>-1.1053</v>
       </c>
       <c r="J51" t="n">
         <v>0.6063</v>
@@ -33917,7 +33909,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.9331</v>
+        <v>-0.9332</v>
       </c>
       <c r="C52" t="n">
         <v>0.4357</v>
@@ -33938,7 +33930,7 @@
         <v>-2.717</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0137</v>
+        <v>-1.0139</v>
       </c>
       <c r="J52" t="n">
         <v>0.4723</v>
@@ -33951,7 +33943,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.9737</v>
+        <v>-0.9738</v>
       </c>
       <c r="C53" t="n">
         <v>0.6286</v>
@@ -33960,7 +33952,7 @@
         <v>0.0615</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.2325</v>
+        <v>-1.2326</v>
       </c>
       <c r="F53" t="n">
         <v>0.0615</v>
@@ -33972,7 +33964,7 @@
         <v>-2.717</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9877</v>
+        <v>-0.9879</v>
       </c>
       <c r="J53" t="n">
         <v>0.1885</v>
@@ -34006,7 +33998,7 @@
         <v>-2.717</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0137</v>
+        <v>-1.0139</v>
       </c>
       <c r="J54" t="n">
         <v>0.1057</v>
@@ -34028,7 +34020,7 @@
         <v>-0.5716</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.3053</v>
+        <v>-1.3054</v>
       </c>
       <c r="F55" t="n">
         <v>-0.5716</v>
@@ -34040,7 +34032,7 @@
         <v>-2.9765</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9888</v>
+        <v>-0.989</v>
       </c>
       <c r="J55" t="n">
         <v>-0.024</v>
@@ -34062,7 +34054,7 @@
         <v>-0.8158</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.354</v>
+        <v>-1.3541</v>
       </c>
       <c r="F56" t="n">
         <v>-0.8158</v>
@@ -34074,7 +34066,7 @@
         <v>-2.9765</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0439</v>
+        <v>-1.0441</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2474</v>
@@ -34108,7 +34100,7 @@
         <v>-2.9765</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0068</v>
+        <v>-1.0069</v>
       </c>
       <c r="J57" t="n">
         <v>-0.4425</v>
@@ -34121,7 +34113,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.2465</v>
+        <v>-1.2466</v>
       </c>
       <c r="C58" t="n">
         <v>0.9933</v>
@@ -34130,7 +34122,7 @@
         <v>-0.8337</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.3497</v>
+        <v>-1.3498</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8337</v>
@@ -34142,7 +34134,7 @@
         <v>-2.674</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.084</v>
+        <v>-1.0842</v>
       </c>
       <c r="J58" t="n">
         <v>-0.5804</v>
@@ -34164,7 +34156,7 @@
         <v>-0.8126</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.4012</v>
+        <v>-1.4013</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8126</v>
@@ -34176,7 +34168,7 @@
         <v>-2.674</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0989</v>
+        <v>-1.099</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8199</v>
@@ -34189,7 +34181,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.2491</v>
+        <v>-1.2492</v>
       </c>
       <c r="C60" t="n">
         <v>0.9198</v>
@@ -34198,7 +34190,7 @@
         <v>-0.5419</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.4259</v>
+        <v>-1.426</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5419</v>
@@ -34210,7 +34202,7 @@
         <v>-2.674</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1138</v>
+        <v>-1.114</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9876</v>
@@ -34232,7 +34224,7 @@
         <v>-0.3879</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.3951</v>
+        <v>-1.3952</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3879</v>
@@ -34244,7 +34236,7 @@
         <v>-2.444</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0949</v>
+        <v>-1.0951</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1704</v>
@@ -34257,7 +34249,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.1863</v>
+        <v>-1.1864</v>
       </c>
       <c r="C62" t="n">
         <v>0.8124</v>
@@ -34278,7 +34270,7 @@
         <v>-2.444</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0598</v>
+        <v>-1.06</v>
       </c>
       <c r="J62" t="n">
         <v>-1.3403</v>
@@ -34300,7 +34292,7 @@
         <v>-0.2135</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.4375</v>
+        <v>-1.4376</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2135</v>
@@ -34312,7 +34304,7 @@
         <v>-2.444</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0888</v>
+        <v>-1.089</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4638</v>
@@ -34346,7 +34338,7 @@
         <v>-2.124</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0682</v>
+        <v>-1.0683</v>
       </c>
       <c r="J64" t="n">
         <v>-1.699</v>
@@ -34359,7 +34351,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1792</v>
+        <v>-1.1793</v>
       </c>
       <c r="C65" t="n">
         <v>0.6964</v>
@@ -34380,7 +34372,7 @@
         <v>-2.124</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0275</v>
+        <v>-1.0276</v>
       </c>
       <c r="J65" t="n">
         <v>-1.8219</v>
@@ -34402,7 +34394,7 @@
         <v>-0.2086</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.4313</v>
+        <v>-1.4314</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2086</v>
@@ -34414,7 +34406,7 @@
         <v>-2.124</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0682</v>
+        <v>-1.0684</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9708</v>
@@ -34436,7 +34428,7 @@
         <v>-0.1876</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.3842</v>
+        <v>-1.3843</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1876</v>
@@ -34448,7 +34440,7 @@
         <v>-1.791</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0893</v>
+        <v>-1.0895</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1397</v>
@@ -34470,7 +34462,7 @@
         <v>-0.2734</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.392</v>
+        <v>-1.3921</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2734</v>
@@ -34482,7 +34474,7 @@
         <v>-1.791</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1556</v>
+        <v>-1.1558</v>
       </c>
       <c r="J68" t="n">
         <v>-2.1129</v>
@@ -34495,7 +34487,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1505</v>
+        <v>-1.1506</v>
       </c>
       <c r="C69" t="n">
         <v>0.5633</v>
@@ -34516,7 +34508,7 @@
         <v>-1.791</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1899</v>
+        <v>-1.1901</v>
       </c>
       <c r="J69" t="n">
         <v>-2.064</v>
@@ -34538,7 +34530,7 @@
         <v>-0.2931</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2548</v>
+        <v>-1.2549</v>
       </c>
       <c r="F70" t="n">
         <v>-0.2931</v>
@@ -34550,7 +34542,7 @@
         <v>-1.4266</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2076</v>
+        <v>-1.2078</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9686</v>
@@ -34584,7 +34576,7 @@
         <v>-1.4266</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2407</v>
+        <v>-1.2409</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9298</v>
@@ -34606,7 +34598,7 @@
         <v>-0.1504</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.2335</v>
+        <v>-1.2336</v>
       </c>
       <c r="F72" t="n">
         <v>-0.1504</v>
@@ -34618,7 +34610,7 @@
         <v>-1.4266</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.228</v>
+        <v>-1.2281</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8991</v>
@@ -34652,7 +34644,7 @@
         <v>-1.1836</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1906</v>
+        <v>-1.1908</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8612</v>
@@ -34674,7 +34666,7 @@
         <v>-0.1687</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1583</v>
+        <v>-1.1584</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1687</v>
@@ -34686,7 +34678,7 @@
         <v>-1.1836</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2161</v>
+        <v>-1.2162</v>
       </c>
       <c r="J74" t="n">
         <v>-1.8374</v>
@@ -34699,7 +34691,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9416</v>
+        <v>-0.9417</v>
       </c>
       <c r="C75" t="n">
         <v>0.3874</v>
@@ -34708,7 +34700,7 @@
         <v>-0.1839</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.131</v>
+        <v>-1.1311</v>
       </c>
       <c r="F75" t="n">
         <v>-0.1839</v>
@@ -34720,7 +34712,7 @@
         <v>-1.1836</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2065</v>
+        <v>-1.2067</v>
       </c>
       <c r="J75" t="n">
         <v>-1.8155</v>
@@ -34754,7 +34746,7 @@
         <v>-0.7586000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2363</v>
+        <v>-1.2365</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7064</v>
@@ -34767,7 +34759,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7479</v>
+        <v>-0.748</v>
       </c>
       <c r="C77" t="n">
         <v>0.3431</v>
@@ -34788,7 +34780,7 @@
         <v>-0.7586000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2039</v>
+        <v>-1.204</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6015</v>
@@ -34801,7 +34793,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.7518</v>
+        <v>-0.7519</v>
       </c>
       <c r="C78" t="n">
         <v>0.2407</v>
@@ -34822,7 +34814,7 @@
         <v>-0.7586000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2426</v>
+        <v>-1.2428</v>
       </c>
       <c r="J78" t="n">
         <v>-1.6343</v>
@@ -34856,7 +34848,7 @@
         <v>-0.6929999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2644</v>
+        <v>-1.2646</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5363</v>
@@ -34878,7 +34870,7 @@
         <v>0.2633</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.9214</v>
+        <v>-0.9215</v>
       </c>
       <c r="F80" t="n">
         <v>0.2633</v>
@@ -34890,7 +34882,7 @@
         <v>-0.6929999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2655</v>
+        <v>-1.2657</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5187</v>
@@ -34912,7 +34904,7 @@
         <v>0.3198</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.9131</v>
+        <v>-0.9132</v>
       </c>
       <c r="F81" t="n">
         <v>0.3198</v>
@@ -34924,7 +34916,7 @@
         <v>-0.6929999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3116</v>
+        <v>-1.3118</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4818</v>
@@ -34946,7 +34938,7 @@
         <v>0.326</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8631</v>
+        <v>-0.8632</v>
       </c>
       <c r="F82" t="n">
         <v>0.326</v>
@@ -34958,7 +34950,7 @@
         <v>-0.6052</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3271</v>
+        <v>-1.3273</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3497</v>
@@ -34971,7 +34963,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6602</v>
+        <v>-0.6603</v>
       </c>
       <c r="C83" t="n">
         <v>0.09279999999999999</v>
@@ -34992,7 +34984,7 @@
         <v>-0.6052</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.324</v>
+        <v>-1.3242</v>
       </c>
       <c r="J83" t="n">
         <v>-1.364</v>
@@ -35026,7 +35018,7 @@
         <v>-0.6052</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3108</v>
+        <v>-1.311</v>
       </c>
       <c r="J84" t="n">
         <v>-1.326</v>
@@ -35039,7 +35031,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.6204</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="C85" t="n">
         <v>0.0525</v>
@@ -35060,7 +35052,7 @@
         <v>-0.581</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3157</v>
+        <v>-1.3159</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2826</v>
@@ -35073,7 +35065,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5843</v>
+        <v>-0.5844</v>
       </c>
       <c r="C86" t="n">
         <v>0.0257</v>
@@ -35094,7 +35086,7 @@
         <v>-0.581</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3378</v>
+        <v>-1.338</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1266</v>
@@ -35116,7 +35108,7 @@
         <v>0.285</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.7682</v>
+        <v>-0.7683</v>
       </c>
       <c r="F87" t="n">
         <v>0.285</v>
@@ -35128,7 +35120,7 @@
         <v>-0.581</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2873</v>
+        <v>-1.2875</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1351</v>
@@ -35150,7 +35142,7 @@
         <v>0.3315</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7185</v>
+        <v>-0.7186</v>
       </c>
       <c r="F88" t="n">
         <v>0.3315</v>
@@ -35162,7 +35154,7 @@
         <v>-0.5274</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2077</v>
+        <v>-1.2079</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0599</v>
@@ -35196,7 +35188,7 @@
         <v>-0.5274</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2307</v>
+        <v>-1.2309</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0936</v>
@@ -35230,7 +35222,7 @@
         <v>-0.5274</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2832</v>
+        <v>-1.2834</v>
       </c>
       <c r="J90" t="n">
         <v>-0.9181</v>
@@ -35252,7 +35244,7 @@
         <v>0.1758</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6499</v>
+        <v>-0.65</v>
       </c>
       <c r="F91" t="n">
         <v>0.1758</v>
@@ -35264,7 +35256,7 @@
         <v>-0.393</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2853</v>
+        <v>-1.2855</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9463</v>
@@ -35298,7 +35290,7 @@
         <v>-0.393</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2892</v>
+        <v>-1.2894</v>
       </c>
       <c r="J92" t="n">
         <v>-0.8314</v>
@@ -35332,7 +35324,7 @@
         <v>-0.393</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2873</v>
+        <v>-1.2875</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8204</v>
@@ -35354,7 +35346,7 @@
         <v>0.2713</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.5708</v>
+        <v>-0.5709</v>
       </c>
       <c r="F94" t="n">
         <v>0.2713</v>
@@ -35366,7 +35358,7 @@
         <v>-0.2552</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2968</v>
+        <v>-1.297</v>
       </c>
       <c r="J94" t="n">
         <v>-0.7851</v>
@@ -35379,7 +35371,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.3948</v>
+        <v>-0.3949</v>
       </c>
       <c r="C95" t="n">
         <v>-0.2685</v>
@@ -35388,7 +35380,7 @@
         <v>0.2715</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5614</v>
+        <v>-0.5615</v>
       </c>
       <c r="F95" t="n">
         <v>0.2715</v>
@@ -35400,7 +35392,7 @@
         <v>-0.2552</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2839</v>
+        <v>-1.2841</v>
       </c>
       <c r="J95" t="n">
         <v>-0.7911</v>
@@ -35434,7 +35426,7 @@
         <v>-0.2552</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2529</v>
+        <v>-1.2531</v>
       </c>
       <c r="J96" t="n">
         <v>-0.5896</v>
@@ -35456,7 +35448,7 @@
         <v>0.5887</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.4428</v>
+        <v>-0.4429</v>
       </c>
       <c r="F97" t="n">
         <v>0.5887</v>
@@ -35468,7 +35460,7 @@
         <v>-0.2092</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1898</v>
+        <v>-1.19</v>
       </c>
       <c r="J97" t="n">
         <v>-0.5685</v>
@@ -35481,7 +35473,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.3189</v>
+        <v>-0.319</v>
       </c>
       <c r="C98" t="n">
         <v>-0.3705</v>
@@ -35490,7 +35482,7 @@
         <v>0.1387</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.4333</v>
+        <v>-0.4334</v>
       </c>
       <c r="F98" t="n">
         <v>0.1387</v>
@@ -35502,7 +35494,7 @@
         <v>-0.2092</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0547</v>
+        <v>-1.0549</v>
       </c>
       <c r="J98" t="n">
         <v>-0.6209</v>
@@ -35536,7 +35528,7 @@
         <v>-0.2092</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9688</v>
+        <v>-0.969</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5077</v>
@@ -35549,7 +35541,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.255</v>
+        <v>-0.2551</v>
       </c>
       <c r="C100" t="n">
         <v>-0.3899</v>
@@ -35558,7 +35550,7 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.3417</v>
+        <v>-0.3418</v>
       </c>
       <c r="F100" t="n">
         <v>0.09180000000000001</v>
@@ -35570,7 +35562,7 @@
         <v>-0.1696</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.921</v>
+        <v>-0.9211</v>
       </c>
       <c r="J100" t="n">
         <v>-0.5042</v>
@@ -35604,7 +35596,7 @@
         <v>-0.1696</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8364</v>
+        <v>-0.8365</v>
       </c>
       <c r="J101" t="n">
         <v>-0.4175</v>
@@ -35638,7 +35630,7 @@
         <v>-0.1696</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7406</v>
+        <v>-0.7407</v>
       </c>
       <c r="J102" t="n">
         <v>-0.4088</v>
@@ -35651,7 +35643,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.1128</v>
+        <v>-0.1129</v>
       </c>
       <c r="C103" t="n">
         <v>-0.4519</v>
@@ -35672,7 +35664,7 @@
         <v>-0.1049</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8158</v>
+        <v>-0.8159</v>
       </c>
       <c r="J103" t="n">
         <v>-0.3586</v>
@@ -35706,7 +35698,7 @@
         <v>-0.1049</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7265</v>
+        <v>-0.7266</v>
       </c>
       <c r="J104" t="n">
         <v>-0.2361</v>
@@ -35740,7 +35732,7 @@
         <v>-0.1049</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.766</v>
+        <v>-0.7661</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2483</v>
@@ -35774,7 +35766,7 @@
         <v>-0.0474</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7158</v>
+        <v>-0.7159</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3663</v>
@@ -35842,7 +35834,7 @@
         <v>-0.0474</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6532</v>
+        <v>-0.6533</v>
       </c>
       <c r="J108" t="n">
         <v>-0.2937</v>
@@ -35889,7 +35881,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.1083</v>
+        <v>0.1082</v>
       </c>
       <c r="C110" t="n">
         <v>-0.6982</v>
@@ -35910,7 +35902,7 @@
         <v>0.1388</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5473</v>
+        <v>-0.5474</v>
       </c>
       <c r="J110" t="n">
         <v>-0.3052</v>
@@ -35923,7 +35915,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.1116</v>
+        <v>0.1115</v>
       </c>
       <c r="C111" t="n">
         <v>-0.7007</v>
@@ -35932,7 +35924,7 @@
         <v>0.8895999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.0829</v>
+        <v>-0.083</v>
       </c>
       <c r="F111" t="n">
         <v>0.8895999999999999</v>
@@ -35944,7 +35936,7 @@
         <v>0.1388</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5703</v>
+        <v>-0.5704</v>
       </c>
       <c r="J111" t="n">
         <v>-0.241</v>
@@ -35966,7 +35958,7 @@
         <v>0.8885</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.0572</v>
+        <v>-0.0573</v>
       </c>
       <c r="F112" t="n">
         <v>0.8885</v>
@@ -36012,7 +36004,7 @@
         <v>0.1656</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5502</v>
+        <v>-0.5503</v>
       </c>
       <c r="J113" t="n">
         <v>-0.238</v>
@@ -36046,7 +36038,7 @@
         <v>0.1656</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.528</v>
+        <v>-0.5281</v>
       </c>
       <c r="J114" t="n">
         <v>-0.2216</v>
@@ -36114,7 +36106,7 @@
         <v>0.1891</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4836</v>
+        <v>-0.4837</v>
       </c>
       <c r="J116" t="n">
         <v>-0.1374</v>
@@ -36127,7 +36119,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.3484</v>
+        <v>0.3483</v>
       </c>
       <c r="C117" t="n">
         <v>-0.613</v>
@@ -36148,7 +36140,7 @@
         <v>0.1891</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4578</v>
+        <v>-0.4579</v>
       </c>
       <c r="J117" t="n">
         <v>-0.1151</v>
@@ -36182,7 +36174,7 @@
         <v>0.2476</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3518</v>
+        <v>-0.3519</v>
       </c>
       <c r="J118" t="n">
         <v>-0.163</v>
@@ -36216,7 +36208,7 @@
         <v>0.2476</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3377</v>
+        <v>-0.3378</v>
       </c>
       <c r="J119" t="n">
         <v>-0.0795</v>
@@ -36365,7 +36357,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4725</v>
+        <v>0.4726</v>
       </c>
       <c r="C124" t="n">
         <v>-0.3003</v>
@@ -36454,7 +36446,7 @@
         <v>0.4813</v>
       </c>
       <c r="I126" t="n">
-        <v>0.0536</v>
+        <v>0.0537</v>
       </c>
       <c r="J126" t="n">
         <v>0.0191</v>
@@ -36488,7 +36480,7 @@
         <v>0.4672</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1268</v>
+        <v>0.1269</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0232</v>
@@ -36510,7 +36502,7 @@
         <v>0.2945</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3063</v>
+        <v>0.3064</v>
       </c>
       <c r="F128" t="n">
         <v>0.2945</v>
@@ -36535,7 +36527,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.2857</v>
+        <v>0.2858</v>
       </c>
       <c r="C129" t="n">
         <v>-0.1422</v>
@@ -36556,7 +36548,7 @@
         <v>0.4672</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1209</v>
+        <v>0.121</v>
       </c>
       <c r="J129" t="n">
         <v>-0.075</v>
@@ -36624,7 +36616,7 @@
         <v>0.5435</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0506</v>
+        <v>0.0507</v>
       </c>
       <c r="J131" t="n">
         <v>-0.0655</v>
@@ -36646,7 +36638,7 @@
         <v>0.3561</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3282</v>
+        <v>0.3283</v>
       </c>
       <c r="F132" t="n">
         <v>0.3561</v>
@@ -36658,7 +36650,7 @@
         <v>0.5435</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1071</v>
+        <v>0.1072</v>
       </c>
       <c r="J132" t="n">
         <v>-0.0236</v>
@@ -36760,7 +36752,7 @@
         <v>0.6225000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0682</v>
+        <v>-0.0683</v>
       </c>
       <c r="J135" t="n">
         <v>-0.008699999999999999</v>
@@ -36841,7 +36833,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.3392</v>
+        <v>0.3391</v>
       </c>
       <c r="C138" t="n">
         <v>0.1277</v>
@@ -36862,7 +36854,7 @@
         <v>0.6726</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1451</v>
+        <v>-0.1452</v>
       </c>
       <c r="J138" t="n">
         <v>0.0408</v>
@@ -36896,7 +36888,7 @@
         <v>0.771</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.202</v>
+        <v>-0.2021</v>
       </c>
       <c r="J139" t="n">
         <v>0.1184</v>
@@ -36977,7 +36969,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.3528</v>
+        <v>0.3527</v>
       </c>
       <c r="C142" t="n">
         <v>0.1588</v>
@@ -37032,7 +37024,7 @@
         <v>0.7752</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1881</v>
+        <v>-0.1882</v>
       </c>
       <c r="J143" t="n">
         <v>0.2647</v>
@@ -37054,7 +37046,7 @@
         <v>0.3332</v>
       </c>
       <c r="E144" t="n">
-        <v>0.4477</v>
+        <v>0.4476</v>
       </c>
       <c r="F144" t="n">
         <v>0.3332</v>
@@ -37156,7 +37148,7 @@
         <v>0.5476</v>
       </c>
       <c r="E147" t="n">
-        <v>0.5016</v>
+        <v>0.5017</v>
       </c>
       <c r="F147" t="n">
         <v>0.5476</v>
@@ -37168,7 +37160,7 @@
         <v>0.765</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0022</v>
+        <v>-0.0021</v>
       </c>
       <c r="J147" t="n">
         <v>0.4439</v>
@@ -37202,7 +37194,7 @@
         <v>0.7822</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0083</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J148" t="n">
         <v>0.4392</v>
@@ -37304,7 +37296,7 @@
         <v>0.8047</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.018</v>
+        <v>-0.0179</v>
       </c>
       <c r="J151" t="n">
         <v>0.5741000000000001</v>
@@ -37372,7 +37364,7 @@
         <v>0.8047</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0227</v>
+        <v>-0.0226</v>
       </c>
       <c r="J153" t="n">
         <v>0.6838</v>
@@ -37428,7 +37420,7 @@
         <v>0.7769</v>
       </c>
       <c r="E155" t="n">
-        <v>0.6079</v>
+        <v>0.608</v>
       </c>
       <c r="F155" t="n">
         <v>0.7769</v>
@@ -37440,7 +37432,7 @@
         <v>0.8094</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0621</v>
+        <v>0.0622</v>
       </c>
       <c r="J155" t="n">
         <v>0.8474</v>
@@ -37474,7 +37466,7 @@
         <v>0.8094</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0733</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J156" t="n">
         <v>0.7711</v>
@@ -37508,7 +37500,7 @@
         <v>0.7875</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0974</v>
+        <v>0.0975</v>
       </c>
       <c r="J157" t="n">
         <v>0.8091</v>
@@ -37521,7 +37513,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.6632</v>
+        <v>0.6633</v>
       </c>
       <c r="C158" t="n">
         <v>0.3164</v>
@@ -37542,7 +37534,7 @@
         <v>0.7875</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0765</v>
+        <v>0.0766</v>
       </c>
       <c r="J158" t="n">
         <v>1.0042</v>
@@ -37576,7 +37568,7 @@
         <v>0.7875</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0129</v>
+        <v>0.013</v>
       </c>
       <c r="J159" t="n">
         <v>0.9147</v>
@@ -37610,7 +37602,7 @@
         <v>0.8262</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0299</v>
+        <v>-0.0298</v>
       </c>
       <c r="J160" t="n">
         <v>1.0217</v>
@@ -37644,7 +37636,7 @@
         <v>0.8262</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0036</v>
+        <v>0.0037</v>
       </c>
       <c r="J161" t="n">
         <v>1.0293</v>
@@ -37666,7 +37658,7 @@
         <v>0.7341</v>
       </c>
       <c r="E162" t="n">
-        <v>0.6622</v>
+        <v>0.6623</v>
       </c>
       <c r="F162" t="n">
         <v>0.7341</v>
@@ -37678,7 +37670,7 @@
         <v>0.8262</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0584</v>
+        <v>0.0585</v>
       </c>
       <c r="J162" t="n">
         <v>1.1062</v>
@@ -37700,7 +37692,7 @@
         <v>0.777</v>
       </c>
       <c r="E163" t="n">
-        <v>0.6871</v>
+        <v>0.6872</v>
       </c>
       <c r="F163" t="n">
         <v>0.777</v>
@@ -37712,7 +37704,7 @@
         <v>0.8226</v>
       </c>
       <c r="I163" t="n">
-        <v>0.061</v>
+        <v>0.0611</v>
       </c>
       <c r="J163" t="n">
         <v>1.2068</v>
@@ -37734,7 +37726,7 @@
         <v>0.7724</v>
       </c>
       <c r="E164" t="n">
-        <v>0.6931</v>
+        <v>0.6932</v>
       </c>
       <c r="F164" t="n">
         <v>0.7724</v>
@@ -37746,7 +37738,7 @@
         <v>0.8226</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0867</v>
+        <v>0.0868</v>
       </c>
       <c r="J164" t="n">
         <v>1.2097</v>
@@ -37768,7 +37760,7 @@
         <v>0.8058</v>
       </c>
       <c r="E165" t="n">
-        <v>0.7154</v>
+        <v>0.7155</v>
       </c>
       <c r="F165" t="n">
         <v>0.8058</v>
@@ -37780,7 +37772,7 @@
         <v>0.8226</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0762</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="J165" t="n">
         <v>1.3207</v>
@@ -37814,7 +37806,7 @@
         <v>0.8841</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1156</v>
+        <v>0.1157</v>
       </c>
       <c r="J166" t="n">
         <v>1.272</v>
@@ -37848,7 +37840,7 @@
         <v>0.8841</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0866</v>
+        <v>0.0867</v>
       </c>
       <c r="J167" t="n">
         <v>1.3893</v>
@@ -37882,7 +37874,7 @@
         <v>0.8841</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0765</v>
+        <v>0.0766</v>
       </c>
       <c r="J168" t="n">
         <v>1.443</v>
@@ -37895,7 +37887,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.7154</v>
+        <v>0.7155</v>
       </c>
       <c r="C169" t="n">
         <v>0.4257</v>
@@ -37916,7 +37908,7 @@
         <v>0.8655</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0219</v>
+        <v>0.022</v>
       </c>
       <c r="J169" t="n">
         <v>1.4193</v>
@@ -37950,7 +37942,7 @@
         <v>0.8655</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0606</v>
+        <v>-0.0605</v>
       </c>
       <c r="J170" t="n">
         <v>1.539</v>
@@ -37963,7 +37955,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="C171" t="n">
         <v>0.5024999999999999</v>
@@ -37972,7 +37964,7 @@
         <v>0.7524999999999999</v>
       </c>
       <c r="E171" t="n">
-        <v>0.7299</v>
+        <v>0.73</v>
       </c>
       <c r="F171" t="n">
         <v>0.7524999999999999</v>
@@ -37984,7 +37976,7 @@
         <v>0.8655</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0433</v>
+        <v>-0.0432</v>
       </c>
       <c r="J171" t="n">
         <v>1.5071</v>
@@ -38031,7 +38023,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.7869</v>
+        <v>0.787</v>
       </c>
       <c r="C173" t="n">
         <v>0.5595</v>
@@ -38052,7 +38044,7 @@
         <v>0.9504</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0365</v>
+        <v>-0.0364</v>
       </c>
       <c r="J173" t="n">
         <v>1.6148</v>
@@ -38065,7 +38057,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.777</v>
+        <v>0.7771</v>
       </c>
       <c r="C174" t="n">
         <v>0.5651</v>
@@ -38086,7 +38078,7 @@
         <v>0.9504</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.098</v>
       </c>
       <c r="J174" t="n">
         <v>1.6765</v>
@@ -38154,7 +38146,7 @@
         <v>0.9468</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1509</v>
+        <v>-0.1508</v>
       </c>
       <c r="J176" t="n">
         <v>1.824</v>
@@ -38167,7 +38159,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.7618</v>
+        <v>0.7619</v>
       </c>
       <c r="C177" t="n">
         <v>0.5458</v>
@@ -38256,7 +38248,7 @@
         <v>0.4466</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1862</v>
+        <v>-0.1861</v>
       </c>
       <c r="J179" t="n">
         <v>1.9412</v>
@@ -38290,7 +38282,7 @@
         <v>0.4466</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1749</v>
+        <v>-0.1748</v>
       </c>
       <c r="J180" t="n">
         <v>1.9113</v>
@@ -38324,7 +38316,7 @@
         <v>0.0818</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1676</v>
+        <v>-0.1675</v>
       </c>
       <c r="J181" t="n">
         <v>1.9534</v>
@@ -38346,7 +38338,7 @@
         <v>0.7828000000000001</v>
       </c>
       <c r="E182" t="n">
-        <v>0.6096</v>
+        <v>0.6097</v>
       </c>
       <c r="F182" t="n">
         <v>0.7828000000000001</v>
@@ -38358,7 +38350,7 @@
         <v>0.0818</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.1945</v>
+        <v>-0.1944</v>
       </c>
       <c r="J182" t="n">
         <v>2.05</v>
@@ -38392,7 +38384,7 @@
         <v>0.0818</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2092</v>
+        <v>-0.2091</v>
       </c>
       <c r="J183" t="n">
         <v>2.175</v>
@@ -38528,7 +38520,7 @@
         <v>-0.8563</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2059</v>
+        <v>-0.2058</v>
       </c>
       <c r="J187" t="n">
         <v>2.2698</v>
@@ -38550,7 +38542,7 @@
         <v>0.4358</v>
       </c>
       <c r="E188" t="n">
-        <v>0.3639</v>
+        <v>0.364</v>
       </c>
       <c r="F188" t="n">
         <v>0.4358</v>
@@ -38562,7 +38554,7 @@
         <v>-0.8563</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.188</v>
+        <v>-0.1879</v>
       </c>
       <c r="J188" t="n">
         <v>2.0136</v>
@@ -38596,7 +38588,7 @@
         <v>-0.8563</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1531</v>
+        <v>-0.153</v>
       </c>
       <c r="J189" t="n">
         <v>1.7741</v>
@@ -38630,7 +38622,7 @@
         <v>-0.7040999999999999</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1453</v>
+        <v>-0.1452</v>
       </c>
       <c r="J190" t="n">
         <v>1.5321</v>
@@ -38664,7 +38656,7 @@
         <v>-0.7040999999999999</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1061</v>
+        <v>-0.106</v>
       </c>
       <c r="J191" t="n">
         <v>1.3063</v>
@@ -38698,7 +38690,7 @@
         <v>-0.7040999999999999</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0626</v>
+        <v>-0.0624</v>
       </c>
       <c r="J192" t="n">
         <v>1.0395</v>
@@ -38720,7 +38712,7 @@
         <v>0.1266</v>
       </c>
       <c r="E193" t="n">
-        <v>0.2265</v>
+        <v>0.2266</v>
       </c>
       <c r="F193" t="n">
         <v>0.1266</v>
@@ -38732,7 +38724,7 @@
         <v>-0.4991</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0271</v>
+        <v>-0.0269</v>
       </c>
       <c r="J193" t="n">
         <v>0.854</v>
@@ -38745,7 +38737,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.1643</v>
+        <v>0.1644</v>
       </c>
       <c r="C194" t="n">
         <v>0.2157</v>
@@ -38766,7 +38758,7 @@
         <v>-0.4991</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0349</v>
+        <v>0.0351</v>
       </c>
       <c r="J194" t="n">
         <v>0.5527</v>
@@ -38800,7 +38792,7 @@
         <v>-0.4991</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0958</v>
+        <v>0.096</v>
       </c>
       <c r="J195" t="n">
         <v>0.3537</v>
@@ -38834,7 +38826,7 @@
         <v>-0.2881</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1663</v>
+        <v>0.1665</v>
       </c>
       <c r="J196" t="n">
         <v>0.07829999999999999</v>
@@ -38847,7 +38839,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.1215</v>
+        <v>0.1216</v>
       </c>
       <c r="C197" t="n">
         <v>-0.0422</v>
@@ -38856,7 +38848,7 @@
         <v>0.0731</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1336</v>
+        <v>0.1337</v>
       </c>
       <c r="F197" t="n">
         <v>0.0731</v>
@@ -38868,7 +38860,7 @@
         <v>-0.2881</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2093</v>
+        <v>0.2095</v>
       </c>
       <c r="J197" t="n">
         <v>-0.1051</v>
@@ -38902,7 +38894,7 @@
         <v>-0.2881</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2165</v>
+        <v>0.2167</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4298</v>
@@ -38915,7 +38907,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.0623</v>
+        <v>0.0624</v>
       </c>
       <c r="C199" t="n">
         <v>-0.0964</v>
@@ -38924,7 +38916,7 @@
         <v>0.2048</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0267</v>
+        <v>0.0268</v>
       </c>
       <c r="F199" t="n">
         <v>0.2048</v>
@@ -38936,7 +38928,7 @@
         <v>-0.1724</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2623</v>
+        <v>0.2625</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6718</v>
@@ -38949,7 +38941,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.1039</v>
+        <v>0.104</v>
       </c>
       <c r="C200" t="n">
         <v>-0.1771</v>
@@ -38958,7 +38950,7 @@
         <v>0.3394</v>
       </c>
       <c r="E200" t="n">
-        <v>0.045</v>
+        <v>0.0451</v>
       </c>
       <c r="F200" t="n">
         <v>0.3394</v>
@@ -38970,7 +38962,7 @@
         <v>-0.1724</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2689</v>
+        <v>0.2691</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6232</v>
@@ -38992,7 +38984,7 @@
         <v>0.429</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0611</v>
+        <v>0.0612</v>
       </c>
       <c r="F201" t="n">
         <v>0.429</v>
@@ -39004,7 +38996,7 @@
         <v>-0.1724</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2823</v>
+        <v>0.2825</v>
       </c>
       <c r="J201" t="n">
         <v>-0.6042999999999999</v>
@@ -39026,7 +39018,7 @@
         <v>0.4631</v>
       </c>
       <c r="E202" t="n">
-        <v>0.1978</v>
+        <v>0.1979</v>
       </c>
       <c r="F202" t="n">
         <v>0.4631</v>
@@ -39038,7 +39030,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3652</v>
+        <v>0.3655</v>
       </c>
       <c r="J202" t="n">
         <v>-0.4186</v>
@@ -39051,7 +39043,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.2265</v>
+        <v>0.2266</v>
       </c>
       <c r="C203" t="n">
         <v>-0.2987</v>
@@ -39060,7 +39052,7 @@
         <v>0.5001</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1581</v>
+        <v>0.1582</v>
       </c>
       <c r="F203" t="n">
         <v>0.5001</v>
@@ -39072,7 +39064,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3785</v>
+        <v>0.3788</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5093</v>
@@ -39094,7 +39086,7 @@
         <v>0.6373</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2034</v>
+        <v>0.2035</v>
       </c>
       <c r="F204" t="n">
         <v>0.6373</v>
@@ -39106,7 +39098,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4118</v>
+        <v>0.4121</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4293</v>
@@ -39119,7 +39111,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.555</v>
+        <v>0.5551</v>
       </c>
       <c r="C205" t="n">
         <v>-0.4359</v>
@@ -39128,7 +39120,7 @@
         <v>1.7563</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2547</v>
+        <v>0.2548</v>
       </c>
       <c r="F205" t="n">
         <v>1.7563</v>
@@ -39140,7 +39132,7 @@
         <v>0.2093</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4175</v>
+        <v>0.4178</v>
       </c>
       <c r="J205" t="n">
         <v>-0.39</v>
@@ -39153,7 +39145,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3333</v>
+        <v>0.3334</v>
       </c>
       <c r="C206" t="n">
         <v>-0.5203</v>
@@ -39162,7 +39154,7 @@
         <v>0.526</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2851</v>
+        <v>0.2852</v>
       </c>
       <c r="F206" t="n">
         <v>0.526</v>
@@ -39174,7 +39166,7 @@
         <v>0.2093</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4089</v>
+        <v>0.4091</v>
       </c>
       <c r="J206" t="n">
         <v>-0.2554</v>
@@ -39187,7 +39179,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.3578</v>
+        <v>0.3579</v>
       </c>
       <c r="C207" t="n">
         <v>-0.5511</v>
@@ -39196,7 +39188,7 @@
         <v>0.6431</v>
       </c>
       <c r="E207" t="n">
-        <v>0.2865</v>
+        <v>0.2866</v>
       </c>
       <c r="F207" t="n">
         <v>0.6431</v>
@@ -39208,7 +39200,7 @@
         <v>0.2093</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4241</v>
+        <v>0.4243</v>
       </c>
       <c r="J207" t="n">
         <v>-0.2947</v>
@@ -39221,7 +39213,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.4164</v>
+        <v>0.4165</v>
       </c>
       <c r="C208" t="n">
         <v>-0.5053</v>
@@ -39242,7 +39234,7 @@
         <v>0.3943</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4544</v>
+        <v>0.4545</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2532</v>
@@ -39276,7 +39268,7 @@
         <v>0.3943</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5945</v>
       </c>
       <c r="J209" t="n">
         <v>-0.1722</v>
@@ -39310,7 +39302,7 @@
         <v>0.3943</v>
       </c>
       <c r="I210" t="n">
-        <v>0.641</v>
+        <v>0.6412</v>
       </c>
       <c r="J210" t="n">
         <v>-0.17</v>
@@ -39344,7 +39336,7 @@
         <v>0.5281</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7351</v>
+        <v>0.7353</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1145</v>
@@ -39378,7 +39370,7 @@
         <v>0.5281</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7716</v>
+        <v>0.7718</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1294</v>
@@ -39391,7 +39383,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.7306</v>
+        <v>0.7307</v>
       </c>
       <c r="C213" t="n">
         <v>-0.7202</v>
@@ -39400,7 +39392,7 @@
         <v>1.5661</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5218</v>
       </c>
       <c r="F213" t="n">
         <v>1.5661</v>
@@ -39412,7 +39404,7 @@
         <v>0.5281</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7932</v>
+        <v>0.7934</v>
       </c>
       <c r="J213" t="n">
         <v>-0.08309999999999999</v>
@@ -39425,7 +39417,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.8399</v>
+        <v>0.84</v>
       </c>
       <c r="C214" t="n">
         <v>-0.7835</v>
@@ -39446,7 +39438,7 @@
         <v>0.6061</v>
       </c>
       <c r="I214" t="n">
-        <v>0.896</v>
+        <v>0.8962</v>
       </c>
       <c r="J214" t="n">
         <v>0.0775</v>
@@ -39459,7 +39451,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.8835</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="C215" t="n">
         <v>-0.8632</v>
@@ -39468,7 +39460,7 @@
         <v>1.8952</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6306</v>
+        <v>0.6307</v>
       </c>
       <c r="F215" t="n">
         <v>1.8952</v>
@@ -39480,7 +39472,7 @@
         <v>0.6061</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9653</v>
+        <v>0.9655</v>
       </c>
       <c r="J215" t="n">
         <v>0.0268</v>
@@ -39493,7 +39485,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8712</v>
+        <v>0.8713</v>
       </c>
       <c r="C216" t="n">
         <v>-0.9258</v>
@@ -39514,7 +39506,7 @@
         <v>0.6061</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9055</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0208</v>
@@ -39527,7 +39519,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.8107</v>
+        <v>0.8108</v>
       </c>
       <c r="C217" t="n">
         <v>-0.9187</v>
@@ -39536,7 +39528,7 @@
         <v>1.5625</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6228</v>
+        <v>0.6229</v>
       </c>
       <c r="F217" t="n">
         <v>1.5625</v>
@@ -39548,7 +39540,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7774</v>
+        <v>0.7776</v>
       </c>
       <c r="J217" t="n">
         <v>0.1657</v>
@@ -39582,7 +39574,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7079</v>
+        <v>0.7081</v>
       </c>
       <c r="J218" t="n">
         <v>0.1362</v>
@@ -39616,7 +39608,7 @@
         <v>0.6929999999999999</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7784</v>
+        <v>0.7786</v>
       </c>
       <c r="J219" t="n">
         <v>0.2413</v>
@@ -39629,7 +39621,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.9034</v>
+        <v>0.9035</v>
       </c>
       <c r="C220" t="n">
         <v>-1.2201</v>
@@ -39650,7 +39642,7 @@
         <v>0.8408</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7804</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="J220" t="n">
         <v>0.2668</v>
@@ -39672,7 +39664,7 @@
         <v>1.811</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7059</v>
+        <v>0.706</v>
       </c>
       <c r="F221" t="n">
         <v>1.811</v>
@@ -39684,7 +39676,7 @@
         <v>0.8408</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7994</v>
+        <v>0.7996</v>
       </c>
       <c r="J221" t="n">
         <v>0.3082</v>
@@ -39697,7 +39689,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.922</v>
+        <v>0.9221</v>
       </c>
       <c r="C222" t="n">
         <v>-1.4025</v>
@@ -39718,7 +39710,7 @@
         <v>0.8408</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8969</v>
+        <v>0.8972</v>
       </c>
       <c r="J222" t="n">
         <v>0.2473</v>
@@ -39731,7 +39723,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.9776</v>
+        <v>0.9777</v>
       </c>
       <c r="C223" t="n">
         <v>-1.412</v>
@@ -39740,7 +39732,7 @@
         <v>1.7748</v>
       </c>
       <c r="E223" t="n">
-        <v>0.7783</v>
+        <v>0.7784</v>
       </c>
       <c r="F223" t="n">
         <v>1.7748</v>
@@ -39752,7 +39744,7 @@
         <v>0.8397</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0199</v>
+        <v>1.0202</v>
       </c>
       <c r="J223" t="n">
         <v>0.3651</v>
@@ -39765,7 +39757,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.9694</v>
+        <v>0.9695</v>
       </c>
       <c r="C224" t="n">
         <v>-1.3976</v>
@@ -39774,7 +39766,7 @@
         <v>1.6971</v>
       </c>
       <c r="E224" t="n">
-        <v>0.7875</v>
+        <v>0.7876</v>
       </c>
       <c r="F224" t="n">
         <v>1.6971</v>
@@ -39786,7 +39778,7 @@
         <v>0.8397</v>
       </c>
       <c r="I224" t="n">
-        <v>1.038</v>
+        <v>1.0383</v>
       </c>
       <c r="J224" t="n">
         <v>0.3748</v>
@@ -39820,7 +39812,7 @@
         <v>0.8397</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1255</v>
+        <v>1.1258</v>
       </c>
       <c r="J225" t="n">
         <v>0.3928</v>
@@ -39833,7 +39825,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.9706</v>
+        <v>0.9707</v>
       </c>
       <c r="C226" t="n">
         <v>-1.3859</v>
@@ -39842,7 +39834,7 @@
         <v>1.4774</v>
       </c>
       <c r="E226" t="n">
-        <v>0.8439</v>
+        <v>0.844</v>
       </c>
       <c r="F226" t="n">
         <v>1.4774</v>
@@ -39854,7 +39846,7 @@
         <v>0.944</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1935</v>
+        <v>1.1938</v>
       </c>
       <c r="J226" t="n">
         <v>0.3554</v>
@@ -39876,7 +39868,7 @@
         <v>1.5261</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8423</v>
       </c>
       <c r="F227" t="n">
         <v>1.5261</v>
@@ -39888,7 +39880,7 @@
         <v>0.944</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2236</v>
+        <v>1.2239</v>
       </c>
       <c r="J227" t="n">
         <v>0.3534</v>
@@ -39901,7 +39893,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9585</v>
+        <v>0.9586</v>
       </c>
       <c r="C228" t="n">
         <v>-1.3575</v>
@@ -39910,7 +39902,7 @@
         <v>1.3816</v>
       </c>
       <c r="E228" t="n">
-        <v>0.8527</v>
+        <v>0.8528</v>
       </c>
       <c r="F228" t="n">
         <v>1.3816</v>
@@ -39922,7 +39914,7 @@
         <v>0.944</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2937</v>
+        <v>1.294</v>
       </c>
       <c r="J228" t="n">
         <v>0.3566</v>
@@ -39935,7 +39927,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9875</v>
       </c>
       <c r="C229" t="n">
         <v>-1.3839</v>
@@ -39944,7 +39936,7 @@
         <v>1.4513</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8714</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="F229" t="n">
         <v>1.4513</v>
@@ -39956,7 +39948,7 @@
         <v>1.0419</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2223</v>
+        <v>1.2226</v>
       </c>
       <c r="J229" t="n">
         <v>0.382</v>
@@ -39978,7 +39970,7 @@
         <v>1.1744</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9262</v>
+        <v>0.9263</v>
       </c>
       <c r="F230" t="n">
         <v>1.1744</v>
@@ -39990,7 +39982,7 @@
         <v>1.0419</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3229</v>
+        <v>1.3233</v>
       </c>
       <c r="J230" t="n">
         <v>0.4824</v>
@@ -40003,7 +39995,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.05</v>
+        <v>1.0501</v>
       </c>
       <c r="C231" t="n">
         <v>-1.8209</v>
@@ -40012,7 +40004,7 @@
         <v>1.4903</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9401</v>
       </c>
       <c r="F231" t="n">
         <v>1.4903</v>
@@ -40024,7 +40016,7 @@
         <v>1.0419</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4617</v>
+        <v>1.4621</v>
       </c>
       <c r="J231" t="n">
         <v>0.4188</v>
@@ -40037,7 +40029,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.0716</v>
+        <v>1.0717</v>
       </c>
       <c r="C232" t="n">
         <v>-1.713</v>
@@ -40046,7 +40038,7 @@
         <v>1.3836</v>
       </c>
       <c r="E232" t="n">
-        <v>0.9936</v>
+        <v>0.9937</v>
       </c>
       <c r="F232" t="n">
         <v>1.3836</v>
@@ -40058,7 +40050,7 @@
         <v>1.1418</v>
       </c>
       <c r="I232" t="n">
-        <v>1.525</v>
+        <v>1.5255</v>
       </c>
       <c r="J232" t="n">
         <v>0.4799</v>
@@ -40071,7 +40063,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.0307</v>
+        <v>1.0308</v>
       </c>
       <c r="C233" t="n">
         <v>-1.6442</v>
@@ -40080,7 +40072,7 @@
         <v>1.1824</v>
       </c>
       <c r="E233" t="n">
-        <v>0.9928</v>
+        <v>0.9929</v>
       </c>
       <c r="F233" t="n">
         <v>1.1824</v>
@@ -40092,7 +40084,7 @@
         <v>1.1418</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5874</v>
+        <v>1.5879</v>
       </c>
       <c r="J233" t="n">
         <v>0.4724</v>
@@ -40114,7 +40106,7 @@
         <v>1.2978</v>
       </c>
       <c r="E234" t="n">
-        <v>0.9927</v>
+        <v>0.9928</v>
       </c>
       <c r="F234" t="n">
         <v>1.2978</v>
@@ -40126,7 +40118,7 @@
         <v>1.1418</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6333</v>
+        <v>1.6337</v>
       </c>
       <c r="J234" t="n">
         <v>0.4729</v>
@@ -40139,7 +40131,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1.0808</v>
+        <v>1.0809</v>
       </c>
       <c r="C235" t="n">
         <v>-1.6562</v>
@@ -40148,7 +40140,7 @@
         <v>1.3367</v>
       </c>
       <c r="E235" t="n">
-        <v>1.0169</v>
+        <v>1.017</v>
       </c>
       <c r="F235" t="n">
         <v>1.3367</v>
@@ -40160,7 +40152,7 @@
         <v>1.137</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7144</v>
+        <v>1.7149</v>
       </c>
       <c r="J235" t="n">
         <v>0.5405</v>
@@ -40173,7 +40165,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.0774</v>
+        <v>1.0775</v>
       </c>
       <c r="C236" t="n">
         <v>-1.4374</v>
@@ -40182,7 +40174,7 @@
         <v>1.3711</v>
       </c>
       <c r="E236" t="n">
-        <v>1.004</v>
+        <v>1.0041</v>
       </c>
       <c r="F236" t="n">
         <v>1.3711</v>
@@ -40194,7 +40186,7 @@
         <v>1.137</v>
       </c>
       <c r="I236" t="n">
-        <v>1.749</v>
+        <v>1.7494</v>
       </c>
       <c r="J236" t="n">
         <v>0.5567</v>
@@ -40207,7 +40199,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1.017</v>
+        <v>1.0171</v>
       </c>
       <c r="C237" t="n">
         <v>-1.4719</v>
@@ -40216,7 +40208,7 @@
         <v>1.4207</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9161</v>
+        <v>0.9162</v>
       </c>
       <c r="F237" t="n">
         <v>1.4207</v>
@@ -40228,7 +40220,7 @@
         <v>1.137</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5261</v>
+        <v>1.5265</v>
       </c>
       <c r="J237" t="n">
         <v>0.518</v>
@@ -40241,7 +40233,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.9709</v>
+        <v>0.971</v>
       </c>
       <c r="C238" t="n">
         <v>-1.4868</v>
@@ -40250,7 +40242,7 @@
         <v>1.2146</v>
       </c>
       <c r="E238" t="n">
-        <v>0.91</v>
+        <v>0.9101</v>
       </c>
       <c r="F238" t="n">
         <v>1.2146</v>
@@ -40262,7 +40254,7 @@
         <v>1.1197</v>
       </c>
       <c r="I238" t="n">
-        <v>1.5117</v>
+        <v>1.5121</v>
       </c>
       <c r="J238" t="n">
         <v>0.5233</v>
@@ -40275,7 +40267,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9935</v>
       </c>
       <c r="C239" t="n">
         <v>-1.4036</v>
@@ -40284,7 +40276,7 @@
         <v>1.1456</v>
       </c>
       <c r="E239" t="n">
-        <v>0.9554</v>
+        <v>0.9555</v>
       </c>
       <c r="F239" t="n">
         <v>1.1456</v>
@@ -40296,7 +40288,7 @@
         <v>1.1197</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6733</v>
+        <v>1.6738</v>
       </c>
       <c r="J239" t="n">
         <v>0.6181</v>
@@ -40309,7 +40301,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1.0119</v>
+        <v>1.012</v>
       </c>
       <c r="C240" t="n">
         <v>-1.4187</v>
@@ -40318,7 +40310,7 @@
         <v>1.2522</v>
       </c>
       <c r="E240" t="n">
-        <v>0.9518</v>
+        <v>0.9519</v>
       </c>
       <c r="F240" t="n">
         <v>1.2522</v>
@@ -40330,7 +40322,7 @@
         <v>1.1197</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7489</v>
+        <v>1.7494</v>
       </c>
       <c r="J240" t="n">
         <v>0.5888</v>
@@ -40343,7 +40335,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1.0182</v>
+        <v>1.0183</v>
       </c>
       <c r="C241" t="n">
         <v>-1.4448</v>
@@ -40352,7 +40344,7 @@
         <v>1.293</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9495</v>
+        <v>0.9496</v>
       </c>
       <c r="F241" t="n">
         <v>1.293</v>
@@ -40364,7 +40356,7 @@
         <v>1.1068</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7679</v>
+        <v>1.7683</v>
       </c>
       <c r="J241" t="n">
         <v>0.6418</v>
@@ -40377,7 +40369,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1.0286</v>
+        <v>1.0287</v>
       </c>
       <c r="C242" t="n">
         <v>-1.1965</v>
@@ -40386,7 +40378,7 @@
         <v>1.4351</v>
       </c>
       <c r="E242" t="n">
-        <v>0.927</v>
+        <v>0.9271</v>
       </c>
       <c r="F242" t="n">
         <v>1.4351</v>
@@ -40398,7 +40390,7 @@
         <v>1.1068</v>
       </c>
       <c r="I242" t="n">
-        <v>1.84</v>
+        <v>1.8405</v>
       </c>
       <c r="J242" t="n">
         <v>0.6034</v>
@@ -40420,7 +40412,7 @@
         <v>1.3061</v>
       </c>
       <c r="E243" t="n">
-        <v>0.8988</v>
+        <v>0.8989</v>
       </c>
       <c r="F243" t="n">
         <v>1.3061</v>
@@ -40432,7 +40424,7 @@
         <v>1.1068</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7741</v>
+        <v>1.7745</v>
       </c>
       <c r="J243" t="n">
         <v>0.5849</v>
@@ -40445,7 +40437,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>1.0183</v>
+        <v>1.0184</v>
       </c>
       <c r="C244" t="n">
         <v>-1.0986</v>
@@ -40454,7 +40446,7 @@
         <v>1.3528</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9347</v>
+        <v>0.9348</v>
       </c>
       <c r="F244" t="n">
         <v>1.3528</v>
@@ -40466,7 +40458,7 @@
         <v>1.1698</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7292</v>
+        <v>1.7296</v>
       </c>
       <c r="J244" t="n">
         <v>0.7014</v>
@@ -40479,7 +40471,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.9958</v>
+        <v>0.9959</v>
       </c>
       <c r="C245" t="n">
         <v>-1.1237</v>
@@ -40488,7 +40480,7 @@
         <v>1.5766</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8506</v>
+        <v>0.8507</v>
       </c>
       <c r="F245" t="n">
         <v>1.5766</v>
@@ -40500,7 +40492,7 @@
         <v>1.1698</v>
       </c>
       <c r="I245" t="n">
-        <v>1.6059</v>
+        <v>1.6063</v>
       </c>
       <c r="J245" t="n">
         <v>0.6095</v>
@@ -40522,7 +40514,7 @@
         <v>1.5802</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8815</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="F246" t="n">
         <v>1.5802</v>
@@ -40534,7 +40526,7 @@
         <v>1.1698</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6996</v>
+        <v>1.7001</v>
       </c>
       <c r="J246" t="n">
         <v>0.6883</v>
@@ -40547,7 +40539,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9653</v>
       </c>
       <c r="C247" t="n">
         <v>-1.0799</v>
@@ -40556,7 +40548,7 @@
         <v>1.4545</v>
       </c>
       <c r="E247" t="n">
-        <v>0.8429</v>
+        <v>0.843</v>
       </c>
       <c r="F247" t="n">
         <v>1.4545</v>
@@ -40568,7 +40560,7 @@
         <v>1.0719</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7284</v>
+        <v>1.7289</v>
       </c>
       <c r="J247" t="n">
         <v>0.6103</v>
@@ -40581,7 +40573,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.9356</v>
+        <v>0.9357</v>
       </c>
       <c r="C248" t="n">
         <v>-1.1172</v>
@@ -40590,7 +40582,7 @@
         <v>1.3002</v>
       </c>
       <c r="E248" t="n">
-        <v>0.8445</v>
+        <v>0.8446</v>
       </c>
       <c r="F248" t="n">
         <v>1.3002</v>
@@ -40602,7 +40594,7 @@
         <v>1.0719</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8422</v>
+        <v>1.8427</v>
       </c>
       <c r="J248" t="n">
         <v>0.6287</v>
@@ -40615,7 +40607,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.922</v>
       </c>
       <c r="C249" t="n">
         <v>-1.1489</v>
@@ -40624,7 +40616,7 @@
         <v>1.1165</v>
       </c>
       <c r="E249" t="n">
-        <v>0.8732</v>
+        <v>0.8734</v>
       </c>
       <c r="F249" t="n">
         <v>1.1165</v>
@@ -40636,7 +40628,7 @@
         <v>1.0719</v>
       </c>
       <c r="I249" t="n">
-        <v>1.9076</v>
+        <v>1.9081</v>
       </c>
       <c r="J249" t="n">
         <v>0.6894</v>
@@ -40649,7 +40641,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9332</v>
       </c>
       <c r="C250" t="n">
         <v>-1.1722</v>
@@ -40658,7 +40650,7 @@
         <v>1.2158</v>
       </c>
       <c r="E250" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.8625</v>
       </c>
       <c r="F250" t="n">
         <v>1.2158</v>
@@ -40670,7 +40662,7 @@
         <v>1.0983</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9721</v>
+        <v>1.9727</v>
       </c>
       <c r="J250" t="n">
         <v>0.6231</v>
@@ -40683,7 +40675,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.974</v>
+        <v>0.9741</v>
       </c>
       <c r="C251" t="n">
         <v>-1.1771</v>
@@ -40692,7 +40684,7 @@
         <v>1.236</v>
       </c>
       <c r="E251" t="n">
-        <v>0.9085</v>
+        <v>0.9086</v>
       </c>
       <c r="F251" t="n">
         <v>1.236</v>
@@ -40704,7 +40696,7 @@
         <v>1.0983</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1436</v>
+        <v>2.1443</v>
       </c>
       <c r="J251" t="n">
         <v>0.6374</v>
@@ -40717,7 +40709,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.9799</v>
+        <v>0.98</v>
       </c>
       <c r="C252" t="n">
         <v>-1.116</v>
@@ -40726,7 +40718,7 @@
         <v>1.2102</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9223</v>
+        <v>0.9224</v>
       </c>
       <c r="F252" t="n">
         <v>1.2102</v>
@@ -40738,7 +40730,7 @@
         <v>1.0983</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2685</v>
+        <v>2.2692</v>
       </c>
       <c r="J252" t="n">
         <v>0.6196</v>
@@ -40751,7 +40743,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.7408</v>
+        <v>0.7409</v>
       </c>
       <c r="C253" t="n">
         <v>-0.9427</v>
@@ -40760,7 +40752,7 @@
         <v>0.0331</v>
       </c>
       <c r="E253" t="n">
-        <v>0.9177</v>
+        <v>0.9179</v>
       </c>
       <c r="F253" t="n">
         <v>0.0331</v>
@@ -40772,7 +40764,7 @@
         <v>1.1261</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2933</v>
+        <v>2.294</v>
       </c>
       <c r="J253" t="n">
         <v>0.6133999999999999</v>
@@ -40785,7 +40777,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.8694</v>
+        <v>0.8696</v>
       </c>
       <c r="C254" t="n">
         <v>-0.9089</v>
@@ -40794,7 +40786,7 @@
         <v>0.6443</v>
       </c>
       <c r="E254" t="n">
-        <v>0.9257</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="F254" t="n">
         <v>0.6443</v>
@@ -40806,7 +40798,7 @@
         <v>1.1261</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3974</v>
+        <v>2.3981</v>
       </c>
       <c r="J254" t="n">
         <v>0.5942</v>
@@ -40819,7 +40811,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.8307</v>
+        <v>0.8308</v>
       </c>
       <c r="C255" t="n">
         <v>-0.8995</v>
@@ -40828,7 +40820,7 @@
         <v>0.4423</v>
       </c>
       <c r="E255" t="n">
-        <v>0.9277</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="F255" t="n">
         <v>0.4423</v>
@@ -40840,7 +40832,7 @@
         <v>1.1261</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4723</v>
+        <v>2.4731</v>
       </c>
       <c r="J255" t="n">
         <v>0.5617</v>
@@ -40853,7 +40845,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.8096</v>
+        <v>0.8098</v>
       </c>
       <c r="C256" t="n">
         <v>-0.92</v>
@@ -40862,7 +40854,7 @@
         <v>0.4895</v>
       </c>
       <c r="E256" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8898</v>
       </c>
       <c r="F256" t="n">
         <v>0.4895</v>
@@ -40874,7 +40866,7 @@
         <v>0.9971</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4963</v>
+        <v>2.4971</v>
       </c>
       <c r="J256" t="n">
         <v>0.6098</v>
@@ -40887,7 +40879,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.7389</v>
+        <v>0.7391</v>
       </c>
       <c r="C257" t="n">
         <v>-0.8488</v>
@@ -40896,7 +40888,7 @@
         <v>0.3213</v>
       </c>
       <c r="E257" t="n">
-        <v>0.8433</v>
+        <v>0.8436</v>
       </c>
       <c r="F257" t="n">
         <v>0.3213</v>
@@ -40908,7 +40900,7 @@
         <v>0.9971</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6203</v>
+        <v>2.6211</v>
       </c>
       <c r="J257" t="n">
         <v>0.4753</v>
@@ -40921,7 +40913,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7799</v>
       </c>
       <c r="C258" t="n">
         <v>-0.9278999999999999</v>
@@ -40930,7 +40922,7 @@
         <v>0.2926</v>
       </c>
       <c r="E258" t="n">
-        <v>0.9015</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="F258" t="n">
         <v>0.2926</v>
@@ -40942,7 +40934,7 @@
         <v>0.9971</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7666</v>
+        <v>2.7676</v>
       </c>
       <c r="J258" t="n">
         <v>0.5687</v>
@@ -40955,7 +40947,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8153</v>
       </c>
       <c r="C259" t="n">
         <v>-0.6233</v>
@@ -40964,7 +40956,7 @@
         <v>0.3237</v>
       </c>
       <c r="E259" t="n">
-        <v>0.9379</v>
+        <v>0.9381</v>
       </c>
       <c r="F259" t="n">
         <v>0.3237</v>
@@ -40976,7 +40968,7 @@
         <v>1.0726</v>
       </c>
       <c r="I259" t="n">
-        <v>2.9539</v>
+        <v>2.955</v>
       </c>
       <c r="J259" t="n">
         <v>0.5466</v>
@@ -40989,7 +40981,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.8307</v>
+        <v>0.8309</v>
       </c>
       <c r="C260" t="n">
         <v>-0.6233</v>
@@ -40998,7 +40990,7 @@
         <v>0.4117</v>
       </c>
       <c r="E260" t="n">
-        <v>0.9354</v>
+        <v>0.9357</v>
       </c>
       <c r="F260" t="n">
         <v>0.4117</v>
@@ -41010,7 +41002,7 @@
         <v>1.0726</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9442</v>
+        <v>2.9452</v>
       </c>
       <c r="J260" t="n">
         <v>0.5466</v>
@@ -41023,13 +41015,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.9211</v>
+        <v>0.9213</v>
       </c>
       <c r="C261" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E261" t="n">
-        <v>0.9211</v>
+        <v>0.9213</v>
       </c>
       <c r="G261" t="n">
         <v>-0.8217</v>
@@ -41038,7 +41030,7 @@
         <v>1.0726</v>
       </c>
       <c r="I261" t="n">
-        <v>2.8868</v>
+        <v>2.8878</v>
       </c>
       <c r="J261" t="n">
         <v>0.5466</v>
@@ -41051,13 +41043,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.9203</v>
+        <v>0.9161</v>
       </c>
       <c r="C262" t="n">
         <v>-0.6233</v>
       </c>
       <c r="E262" t="n">
-        <v>0.9203</v>
+        <v>0.9161</v>
       </c>
       <c r="G262" t="n">
         <v>-0.8217</v>
@@ -41066,7 +41058,7 @@
         <v>1.0726</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8837</v>
+        <v>2.867</v>
       </c>
       <c r="J262" t="n">
         <v>0.5466</v>
@@ -41102,67 +41094,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>series_id</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>name</t>